--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="95">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,12 +196,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -211,13 +211,76 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.5 → 50.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>52.8 → 47.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.8</t>
+  </si>
+  <si>
+    <t>47.6</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -248,11 +311,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,8 +349,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,6 +380,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -370,27 +467,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -753,8 +858,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -887,10 +991,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>593.66</v>
+        <v>596.77</v>
       </c>
       <c r="D2">
-        <v>0.51</v>
+        <v>-0.34</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -899,43 +1003,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-6.64</v>
+        <v>-6.15</v>
       </c>
       <c r="H2">
-        <v>13.97</v>
+        <v>14.57</v>
       </c>
       <c r="I2">
-        <v>4.52</v>
+        <v>-0.1</v>
       </c>
       <c r="J2">
-        <v>7.51</v>
+        <v>-0.57</v>
       </c>
       <c r="K2">
-        <v>5.65</v>
+        <v>8.08</v>
       </c>
       <c r="L2">
-        <v>3.19</v>
+        <v>4.54</v>
       </c>
       <c r="M2">
-        <v>11.32</v>
+        <v>10.48</v>
       </c>
       <c r="N2">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>582.49</v>
+        <v>597.5599999999999</v>
       </c>
       <c r="Q2">
-        <v>567.5</v>
+        <v>594.97</v>
       </c>
       <c r="R2">
-        <v>569.08</v>
+        <v>590.48</v>
       </c>
       <c r="S2">
-        <v>588.4400000000001</v>
+        <v>593.17</v>
       </c>
       <c r="T2">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -944,49 +1048,49 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>70.08</v>
+        <v>53.14</v>
       </c>
       <c r="Z2">
-        <v>5.55</v>
+        <v>1.47</v>
       </c>
       <c r="AA2">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="AB2">
-        <v>3.89</v>
+        <v>0.18</v>
       </c>
       <c r="AC2">
-        <v>100</v>
+        <v>84.88</v>
       </c>
       <c r="AD2">
-        <v>99.51000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="AE2">
-        <v>9.710000000000001</v>
+        <v>6.99</v>
       </c>
       <c r="AF2">
-        <v>-0.34</v>
+        <v>-11.44</v>
       </c>
       <c r="AG2">
-        <v>590.85</v>
+        <v>604.59</v>
       </c>
       <c r="AH2">
-        <v>544.14</v>
+        <v>585.35</v>
       </c>
       <c r="AI2">
-        <v>563.51</v>
+        <v>580.51</v>
       </c>
       <c r="AJ2" t="s">
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>29.19</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1101,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>59.49</v>
+        <v>59.99</v>
       </c>
       <c r="D3">
-        <v>0.47</v>
+        <v>-0.22</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1009,43 +1113,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.66</v>
+        <v>-90.59</v>
       </c>
       <c r="H3">
-        <v>14.14</v>
+        <v>15.1</v>
       </c>
       <c r="I3">
-        <v>4.06</v>
+        <v>0.2</v>
       </c>
       <c r="J3">
-        <v>7.38</v>
+        <v>-0.27</v>
       </c>
       <c r="K3">
-        <v>5.74</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L3">
-        <v>-89.68000000000001</v>
+        <v>-89.48999999999999</v>
       </c>
       <c r="M3">
-        <v>-29.79</v>
+        <v>-30.26</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>58.41</v>
+        <v>60.01</v>
       </c>
       <c r="Q3">
-        <v>56.91</v>
+        <v>59.69</v>
       </c>
       <c r="R3">
-        <v>57.08</v>
+        <v>59.22</v>
       </c>
       <c r="S3">
-        <v>400.12</v>
+        <v>302.69</v>
       </c>
       <c r="T3">
-        <v>-85.13</v>
+        <v>-80.18000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1054,49 +1158,49 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>50.18</v>
+        <v>52.66</v>
       </c>
       <c r="Z3">
-        <v>-1.33</v>
+        <v>0.08</v>
       </c>
       <c r="AA3">
-        <v>-2.6</v>
+        <v>-0.01</v>
       </c>
       <c r="AB3">
-        <v>1.27</v>
+        <v>0.08</v>
       </c>
       <c r="AC3">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="AD3">
-        <v>99.59</v>
+        <v>83.34</v>
       </c>
       <c r="AE3">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>-74.69</v>
+        <v>-74.02</v>
       </c>
       <c r="AG3">
-        <v>59.25</v>
+        <v>60.71</v>
       </c>
       <c r="AH3">
-        <v>54.57</v>
+        <v>58.66</v>
       </c>
       <c r="AI3">
-        <v>60.16</v>
+        <v>57.31</v>
       </c>
       <c r="AJ3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>37.39</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1211,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>98.39</v>
+        <v>93.8</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1119,94 +1223,94 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-9.58</v>
+        <v>-13.79</v>
       </c>
       <c r="H4">
-        <v>12.02</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>0.72</v>
+        <v>-1.15</v>
       </c>
       <c r="J4">
-        <v>-6.19</v>
+        <v>-2.52</v>
       </c>
       <c r="K4">
-        <v>-2.63</v>
+        <v>-11.06</v>
       </c>
       <c r="L4">
-        <v>6.39</v>
+        <v>4.09</v>
       </c>
       <c r="M4">
-        <v>30.28</v>
+        <v>29.96</v>
       </c>
       <c r="N4">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="P4">
-        <v>97.37</v>
+        <v>94.33</v>
       </c>
       <c r="Q4">
-        <v>100.63</v>
+        <v>95.36</v>
       </c>
       <c r="R4">
-        <v>103.92</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
-        <v>97.12</v>
+        <v>97.95</v>
       </c>
       <c r="T4">
-        <v>1.31</v>
+        <v>-4.23</v>
       </c>
       <c r="U4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.03</v>
+        <v>31.82</v>
       </c>
       <c r="Z4">
-        <v>-1.94</v>
+        <v>-0.89</v>
       </c>
       <c r="AA4">
-        <v>-1.7</v>
+        <v>-0.87</v>
       </c>
       <c r="AB4">
-        <v>-0.23</v>
+        <v>-0.02</v>
       </c>
       <c r="AC4">
-        <v>40.57</v>
+        <v>27.95</v>
       </c>
       <c r="AD4">
-        <v>15.93</v>
+        <v>36.44</v>
       </c>
       <c r="AE4">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AF4">
-        <v>176.26</v>
+        <v>252.14</v>
       </c>
       <c r="AG4">
-        <v>105.98</v>
+        <v>97.45</v>
       </c>
       <c r="AH4">
-        <v>95.28</v>
+        <v>93.28</v>
       </c>
       <c r="AI4">
-        <v>104.61</v>
+        <v>100.76</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>63.1</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1217,10 +1321,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>53</v>
+        <v>52.98</v>
       </c>
       <c r="D5">
-        <v>-0.23</v>
+        <v>-0.02</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1229,43 +1333,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-13.11</v>
+        <v>-13.15</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I5">
-        <v>1.03</v>
+        <v>-0.09</v>
       </c>
       <c r="J5">
-        <v>-2.61</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
-        <v>2.44</v>
+        <v>-1.94</v>
       </c>
       <c r="L5">
-        <v>-9.710000000000001</v>
+        <v>-10.93</v>
       </c>
       <c r="M5">
-        <v>7.99</v>
+        <v>7.74</v>
       </c>
       <c r="N5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="P5">
-        <v>52.62</v>
+        <v>53.08</v>
       </c>
       <c r="Q5">
-        <v>52.63</v>
+        <v>52.75</v>
       </c>
       <c r="R5">
-        <v>53.35</v>
+        <v>52.7</v>
       </c>
       <c r="S5">
-        <v>56.14</v>
+        <v>54.87</v>
       </c>
       <c r="T5">
-        <v>-5.59</v>
+        <v>-3.44</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1274,40 +1378,40 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>51.85</v>
+        <v>51.22</v>
       </c>
       <c r="Z5">
-        <v>-0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA5">
-        <v>-0.37</v>
+        <v>0.04</v>
       </c>
       <c r="AB5">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="AC5">
-        <v>98.19</v>
+        <v>55.92</v>
       </c>
       <c r="AD5">
-        <v>92.59</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AE5">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AF5">
-        <v>-21.22</v>
+        <v>-28.03</v>
       </c>
       <c r="AG5">
-        <v>54.29</v>
+        <v>53.59</v>
       </c>
       <c r="AH5">
-        <v>50.98</v>
+        <v>51.91</v>
       </c>
       <c r="AI5">
         <v>54.72</v>
@@ -1316,7 +1420,7 @@
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>28.33</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1327,55 +1431,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>123.75</v>
+        <v>124.58</v>
       </c>
       <c r="D6">
-        <v>-0.31</v>
+        <v>0.96</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>79.81</v>
+        <v>82.08</v>
       </c>
       <c r="G6">
-        <v>-15.55</v>
+        <v>-14.98</v>
       </c>
       <c r="H6">
-        <v>55.06</v>
+        <v>51.78</v>
       </c>
       <c r="I6">
-        <v>2.15</v>
+        <v>6.24</v>
       </c>
       <c r="J6">
-        <v>-5.27</v>
+        <v>5.45</v>
       </c>
       <c r="K6">
-        <v>-2.73</v>
+        <v>-5.43</v>
       </c>
       <c r="L6">
-        <v>52.05</v>
+        <v>49</v>
       </c>
       <c r="M6">
-        <v>24.52</v>
+        <v>25.38</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>122.11</v>
+        <v>121.4</v>
       </c>
       <c r="Q6">
-        <v>126.47</v>
+        <v>118.3</v>
       </c>
       <c r="R6">
-        <v>125.74</v>
+        <v>119.67</v>
       </c>
       <c r="S6">
-        <v>114.73</v>
+        <v>119.1</v>
       </c>
       <c r="T6">
-        <v>7.86</v>
+        <v>4.6</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1387,46 +1491,46 @@
         <v>59</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.18</v>
+        <v>69.19</v>
       </c>
       <c r="Z6">
-        <v>-1.19</v>
+        <v>0.78</v>
       </c>
       <c r="AA6">
-        <v>-0.67</v>
+        <v>-0.17</v>
       </c>
       <c r="AB6">
-        <v>-0.52</v>
+        <v>0.95</v>
       </c>
       <c r="AC6">
-        <v>61.15</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>40.7</v>
+        <v>94.56</v>
       </c>
       <c r="AE6">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="AF6">
-        <v>-38.44</v>
+        <v>58.94</v>
       </c>
       <c r="AG6">
-        <v>133.7</v>
+        <v>123.23</v>
       </c>
       <c r="AH6">
-        <v>119.24</v>
+        <v>113.37</v>
       </c>
       <c r="AI6">
-        <v>124.77</v>
+        <v>119.05</v>
       </c>
       <c r="AJ6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>28.34</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1437,55 +1541,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>127.84</v>
+        <v>128.77</v>
       </c>
       <c r="D7">
-        <v>-0.34</v>
+        <v>1.04</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>82.37</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="G7">
-        <v>-15.55</v>
+        <v>-14.94</v>
       </c>
       <c r="H7">
-        <v>55.2</v>
+        <v>51.96</v>
       </c>
       <c r="I7">
-        <v>2.02</v>
+        <v>6.25</v>
       </c>
       <c r="J7">
-        <v>-5.21</v>
+        <v>5.48</v>
       </c>
       <c r="K7">
-        <v>-2.71</v>
+        <v>-5.11</v>
       </c>
       <c r="L7">
-        <v>52.06</v>
+        <v>49.25</v>
       </c>
       <c r="M7">
-        <v>34.43</v>
+        <v>32.89</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>126.68</v>
+        <v>125.44</v>
       </c>
       <c r="Q7">
-        <v>130.85</v>
+        <v>122.26</v>
       </c>
       <c r="R7">
-        <v>129.96</v>
+        <v>123.72</v>
       </c>
       <c r="S7">
-        <v>118.5</v>
+        <v>123.02</v>
       </c>
       <c r="T7">
-        <v>7.89</v>
+        <v>4.68</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1497,46 +1601,46 @@
         <v>59</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>44.72</v>
+        <v>69.44</v>
       </c>
       <c r="Z7">
-        <v>-1.14</v>
+        <v>0.8</v>
       </c>
       <c r="AA7">
-        <v>-0.59</v>
+        <v>-0.18</v>
       </c>
       <c r="AB7">
-        <v>-0.55</v>
+        <v>0.98</v>
       </c>
       <c r="AC7">
-        <v>55.39</v>
+        <v>100</v>
       </c>
       <c r="AD7">
-        <v>43.9</v>
+        <v>94.83</v>
       </c>
       <c r="AE7">
-        <v>2.73</v>
+        <v>2</v>
       </c>
       <c r="AF7">
-        <v>-42.87</v>
+        <v>43.07</v>
       </c>
       <c r="AG7">
-        <v>137.87</v>
+        <v>127.29</v>
       </c>
       <c r="AH7">
-        <v>123.82</v>
+        <v>117.23</v>
       </c>
       <c r="AI7">
-        <v>130.41</v>
+        <v>122.28</v>
       </c>
       <c r="AJ7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK7">
-        <v>33.5</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1547,106 +1651,106 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>493.28</v>
+        <v>488.49</v>
       </c>
       <c r="D8">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="E8">
         <v>566.34</v>
       </c>
       <c r="F8">
-        <v>378.12</v>
+        <v>431.97</v>
       </c>
       <c r="G8">
-        <v>-12.9</v>
+        <v>-13.75</v>
       </c>
       <c r="H8">
-        <v>30.46</v>
+        <v>13.08</v>
       </c>
       <c r="I8">
-        <v>1.9</v>
+        <v>-1.64</v>
       </c>
       <c r="J8">
-        <v>-9.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K8">
-        <v>-0.76</v>
+        <v>-10.12</v>
       </c>
       <c r="L8">
-        <v>28.81</v>
+        <v>14.89</v>
       </c>
       <c r="M8">
-        <v>6.92</v>
+        <v>8.01</v>
       </c>
       <c r="N8">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="P8">
-        <v>488.66</v>
+        <v>488.13</v>
       </c>
       <c r="Q8">
-        <v>508.5</v>
+        <v>487.1</v>
       </c>
       <c r="R8">
-        <v>522.16</v>
+        <v>486.09</v>
       </c>
       <c r="S8">
-        <v>517.99</v>
+        <v>512.12</v>
       </c>
       <c r="T8">
-        <v>-4.77</v>
+        <v>-4.61</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
       </c>
       <c r="V8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>41.33</v>
+        <v>50.7</v>
       </c>
       <c r="Z8">
-        <v>-10.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA8">
-        <v>-8.68</v>
+        <v>0.75</v>
       </c>
       <c r="AB8">
-        <v>-1.74</v>
+        <v>0.19</v>
       </c>
       <c r="AC8">
-        <v>64.65000000000001</v>
+        <v>29.82</v>
       </c>
       <c r="AD8">
-        <v>44.99</v>
+        <v>32.86</v>
       </c>
       <c r="AE8">
-        <v>15.76</v>
+        <v>11.04</v>
       </c>
       <c r="AF8">
-        <v>-47.98</v>
+        <v>-3.35</v>
       </c>
       <c r="AG8">
-        <v>545.37</v>
+        <v>497.98</v>
       </c>
       <c r="AH8">
-        <v>471.63</v>
+        <v>476.22</v>
       </c>
       <c r="AI8">
-        <v>528.7</v>
+        <v>511.37</v>
       </c>
       <c r="AJ8" t="s">
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>21.96</v>
+        <v>38.14</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1657,10 +1761,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>977.7</v>
+        <v>980.6</v>
       </c>
       <c r="D9">
-        <v>0.65</v>
+        <v>-0.23</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1669,94 +1773,94 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-3.09</v>
+        <v>-2.8</v>
       </c>
       <c r="H9">
-        <v>10.47</v>
+        <v>10.79</v>
       </c>
       <c r="I9">
-        <v>4.36</v>
+        <v>0.88</v>
       </c>
       <c r="J9">
-        <v>2.46</v>
+        <v>0.84</v>
       </c>
       <c r="K9">
-        <v>8.32</v>
+        <v>3.19</v>
       </c>
       <c r="L9">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
       <c r="M9">
-        <v>16.48</v>
+        <v>16.26</v>
       </c>
       <c r="N9">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>955.28</v>
+        <v>976.6900000000001</v>
       </c>
       <c r="Q9">
-        <v>957.8200000000001</v>
+        <v>968.55</v>
       </c>
       <c r="R9">
-        <v>958.9400000000001</v>
+        <v>966.5700000000001</v>
       </c>
       <c r="S9">
-        <v>960.04</v>
+        <v>966</v>
       </c>
       <c r="T9">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
       </c>
       <c r="V9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="s">
         <v>58</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9">
-        <v>61.25</v>
+        <v>59.14</v>
       </c>
       <c r="Z9">
-        <v>-0.18</v>
+        <v>2.8</v>
       </c>
       <c r="AA9">
-        <v>-2.35</v>
+        <v>1.01</v>
       </c>
       <c r="AB9">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>94.38</v>
+        <v>95.97</v>
       </c>
       <c r="AD9">
-        <v>61.48</v>
+        <v>95.66</v>
       </c>
       <c r="AE9">
-        <v>14.72</v>
+        <v>12.11</v>
       </c>
       <c r="AF9">
-        <v>-28.39</v>
+        <v>47.1</v>
       </c>
       <c r="AG9">
-        <v>989.1900000000001</v>
+        <v>983.04</v>
       </c>
       <c r="AH9">
-        <v>926.45</v>
+        <v>954.0599999999999</v>
       </c>
       <c r="AI9">
-        <v>930.9400000000001</v>
+        <v>947.23</v>
       </c>
       <c r="AJ9" t="s">
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>40.13</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1767,55 +1871,55 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>31.98</v>
+        <v>35.06</v>
       </c>
       <c r="D10">
-        <v>1.2</v>
+        <v>0.54</v>
       </c>
       <c r="E10">
         <v>43.17</v>
       </c>
       <c r="F10">
-        <v>30.23</v>
+        <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-25.92</v>
+        <v>-18.79</v>
       </c>
       <c r="H10">
-        <v>5.79</v>
+        <v>22.5</v>
       </c>
       <c r="I10">
-        <v>2.21</v>
+        <v>0.31</v>
       </c>
       <c r="J10">
-        <v>-1.11</v>
+        <v>13.06</v>
       </c>
       <c r="K10">
-        <v>-0.22</v>
+        <v>13.57</v>
       </c>
       <c r="L10">
-        <v>-23.36</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="M10">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="N10">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="P10">
-        <v>31.29</v>
+        <v>34.74</v>
       </c>
       <c r="Q10">
-        <v>31.99</v>
+        <v>33.32</v>
       </c>
       <c r="R10">
-        <v>32.47</v>
+        <v>31.93</v>
       </c>
       <c r="S10">
-        <v>37.06</v>
+        <v>35.85</v>
       </c>
       <c r="T10">
-        <v>-13.71</v>
+        <v>-2.21</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1824,49 +1928,49 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>50.26</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="Z10">
-        <v>-0.25</v>
+        <v>0.96</v>
       </c>
       <c r="AA10">
-        <v>-0.22</v>
+        <v>0.82</v>
       </c>
       <c r="AB10">
-        <v>-0.03</v>
+        <v>0.14</v>
       </c>
       <c r="AC10">
-        <v>25.55</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="AD10">
-        <v>13.95</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AE10">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="AF10">
-        <v>73.48</v>
+        <v>-37.95</v>
       </c>
       <c r="AG10">
-        <v>33.57</v>
+        <v>36</v>
       </c>
       <c r="AH10">
-        <v>30.41</v>
+        <v>30.63</v>
       </c>
       <c r="AI10">
-        <v>33.81</v>
+        <v>32.19</v>
       </c>
       <c r="AJ10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK10">
-        <v>17.41</v>
+        <v>48.02</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1877,55 +1981,55 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>31.9</v>
+        <v>35.11</v>
       </c>
       <c r="D11">
-        <v>0.57</v>
+        <v>0.37</v>
       </c>
       <c r="E11">
         <v>43.29</v>
       </c>
       <c r="F11">
-        <v>30.3</v>
+        <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-26.31</v>
+        <v>-18.9</v>
       </c>
       <c r="H11">
-        <v>5.28</v>
+        <v>22.63</v>
       </c>
       <c r="I11">
-        <v>1.53</v>
+        <v>0.37</v>
       </c>
       <c r="J11">
-        <v>-1.69</v>
+        <v>13.11</v>
       </c>
       <c r="K11">
-        <v>-0.31</v>
+        <v>13.62</v>
       </c>
       <c r="L11">
-        <v>-23.79</v>
+        <v>-8.31</v>
       </c>
       <c r="M11">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="N11">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="P11">
-        <v>31.31</v>
+        <v>34.81</v>
       </c>
       <c r="Q11">
-        <v>32.06</v>
+        <v>33.33</v>
       </c>
       <c r="R11">
-        <v>32.54</v>
+        <v>31.96</v>
       </c>
       <c r="S11">
-        <v>37.16</v>
+        <v>35.93</v>
       </c>
       <c r="T11">
-        <v>-14.16</v>
+        <v>-2.27</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -1934,49 +2038,49 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>48.92</v>
+        <v>68.7</v>
       </c>
       <c r="Z11">
-        <v>-0.26</v>
+        <v>0.98</v>
       </c>
       <c r="AA11">
-        <v>-0.22</v>
+        <v>0.83</v>
       </c>
       <c r="AB11">
-        <v>-0.04</v>
+        <v>0.15</v>
       </c>
       <c r="AC11">
-        <v>24.75</v>
+        <v>77.81</v>
       </c>
       <c r="AD11">
-        <v>13.91</v>
+        <v>75.69</v>
       </c>
       <c r="AE11">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>-37.11</v>
+        <v>-44.57</v>
       </c>
       <c r="AG11">
-        <v>33.67</v>
+        <v>36.06</v>
       </c>
       <c r="AH11">
-        <v>30.45</v>
+        <v>30.61</v>
       </c>
       <c r="AI11">
-        <v>34.31</v>
+        <v>32.2</v>
       </c>
       <c r="AJ11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK11">
-        <v>17.52</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1987,13 +2091,13 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>779.84</v>
+        <v>809</v>
       </c>
       <c r="D12">
-        <v>0.65</v>
+        <v>0.17</v>
       </c>
       <c r="E12">
-        <v>779.84</v>
+        <v>809</v>
       </c>
       <c r="F12">
         <v>651.9</v>
@@ -2002,91 +2106,91 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>19.63</v>
+        <v>24.1</v>
       </c>
       <c r="I12">
-        <v>4.45</v>
+        <v>0.92</v>
       </c>
       <c r="J12">
-        <v>4.7</v>
+        <v>3.47</v>
       </c>
       <c r="K12">
-        <v>12.42</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L12">
-        <v>7.79</v>
+        <v>12.87</v>
       </c>
       <c r="M12">
-        <v>14.12</v>
+        <v>14.42</v>
       </c>
       <c r="N12">
         <v>73</v>
       </c>
       <c r="P12">
-        <v>761</v>
+        <v>806.3200000000001</v>
       </c>
       <c r="Q12">
-        <v>759.17</v>
+        <v>788.3099999999999</v>
       </c>
       <c r="R12">
-        <v>754.38</v>
+        <v>777.26</v>
       </c>
       <c r="S12">
-        <v>738.33</v>
+        <v>747.9400000000001</v>
       </c>
       <c r="T12">
-        <v>5.62</v>
+        <v>8.16</v>
       </c>
       <c r="U12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X12">
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>61.87</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="Z12">
-        <v>3.73</v>
+        <v>8.76</v>
       </c>
       <c r="AA12">
-        <v>1.97</v>
+        <v>6.42</v>
       </c>
       <c r="AB12">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="AC12">
-        <v>87.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="AD12">
-        <v>56.27</v>
+        <v>100</v>
       </c>
       <c r="AE12">
-        <v>16.04</v>
+        <v>12.69</v>
       </c>
       <c r="AF12">
-        <v>13.07</v>
+        <v>-23.37</v>
       </c>
       <c r="AG12">
-        <v>784.09</v>
+        <v>813.25</v>
       </c>
       <c r="AH12">
-        <v>734.25</v>
+        <v>763.36</v>
       </c>
       <c r="AI12">
-        <v>734.04</v>
+        <v>772.14</v>
       </c>
       <c r="AJ12" t="s">
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>24.65</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2097,10 +2201,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>273.11</v>
+        <v>280.46</v>
       </c>
       <c r="D13">
-        <v>0.53</v>
+        <v>0.23</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2109,43 +2213,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-8.210000000000001</v>
+        <v>-5.74</v>
       </c>
       <c r="H13">
-        <v>7.76</v>
+        <v>10.66</v>
       </c>
       <c r="I13">
-        <v>3.81</v>
+        <v>0.21</v>
       </c>
       <c r="J13">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="K13">
-        <v>2.99</v>
+        <v>5.66</v>
       </c>
       <c r="L13">
-        <v>-2.09</v>
+        <v>0.83</v>
       </c>
       <c r="M13">
-        <v>10.1</v>
+        <v>9.81</v>
       </c>
       <c r="N13">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="P13">
-        <v>268.13</v>
+        <v>279.93</v>
       </c>
       <c r="Q13">
-        <v>267.4</v>
+        <v>276.05</v>
       </c>
       <c r="R13">
-        <v>269.96</v>
+        <v>272.82</v>
       </c>
       <c r="S13">
-        <v>281.71</v>
+        <v>280.22</v>
       </c>
       <c r="T13">
-        <v>-3.05</v>
+        <v>0.09</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2154,49 +2258,49 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y13">
-        <v>62.51</v>
+        <v>64.14</v>
       </c>
       <c r="Z13">
-        <v>-0.21</v>
+        <v>1.97</v>
       </c>
       <c r="AA13">
-        <v>-1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AB13">
-        <v>0.91</v>
+        <v>0.47</v>
       </c>
       <c r="AC13">
-        <v>100</v>
+        <v>92.58</v>
       </c>
       <c r="AD13">
-        <v>70.16</v>
+        <v>92.39</v>
       </c>
       <c r="AE13">
-        <v>3.45</v>
+        <v>3.09</v>
       </c>
       <c r="AF13">
-        <v>1.36</v>
+        <v>20.97</v>
       </c>
       <c r="AG13">
-        <v>274.5</v>
+        <v>282.07</v>
       </c>
       <c r="AH13">
-        <v>260.31</v>
+        <v>270.04</v>
       </c>
       <c r="AI13">
-        <v>262</v>
+        <v>271.55</v>
       </c>
       <c r="AJ13" t="s">
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>32.68</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2207,10 +2311,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>265.59</v>
+        <v>272.76</v>
       </c>
       <c r="D14">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2219,79 +2323,79 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-8.289999999999999</v>
+        <v>-5.82</v>
       </c>
       <c r="H14">
-        <v>7.72</v>
+        <v>10.63</v>
       </c>
       <c r="I14">
-        <v>3.72</v>
+        <v>0.25</v>
       </c>
       <c r="J14">
         <v>1.94</v>
       </c>
       <c r="K14">
-        <v>2.99</v>
+        <v>5.62</v>
       </c>
       <c r="M14">
-        <v>-14.15</v>
+        <v>-7.41</v>
       </c>
       <c r="P14">
-        <v>262.02</v>
+        <v>272.05</v>
       </c>
       <c r="Q14">
-        <v>260.51</v>
+        <v>268.62</v>
       </c>
       <c r="R14">
-        <v>262.97</v>
+        <v>265.65</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
       </c>
       <c r="W14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>61.19</v>
+        <v>64.48</v>
       </c>
       <c r="Z14">
-        <v>-0.06</v>
+        <v>1.82</v>
       </c>
       <c r="AA14">
-        <v>-0.96</v>
+        <v>1.37</v>
       </c>
       <c r="AB14">
-        <v>0.89</v>
+        <v>0.45</v>
       </c>
       <c r="AC14">
-        <v>100</v>
+        <v>97.95</v>
       </c>
       <c r="AD14">
-        <v>90.47</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="AE14">
-        <v>3.69</v>
+        <v>4.19</v>
       </c>
       <c r="AF14">
-        <v>98.58</v>
+        <v>-40.24</v>
       </c>
       <c r="AG14">
-        <v>266.96</v>
+        <v>274.21</v>
       </c>
       <c r="AH14">
-        <v>254.05</v>
+        <v>263.04</v>
       </c>
       <c r="AI14">
-        <v>255.29</v>
+        <v>261.89</v>
       </c>
       <c r="AJ14" t="s">
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>29.27</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2302,10 +2406,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>260.5</v>
+        <v>267.72</v>
       </c>
       <c r="D15">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2314,43 +2418,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-8.369999999999999</v>
+        <v>-5.84</v>
       </c>
       <c r="H15">
-        <v>7.86</v>
+        <v>10.85</v>
       </c>
       <c r="I15">
-        <v>3.65</v>
+        <v>0.01</v>
       </c>
       <c r="J15">
         <v>1.95</v>
       </c>
       <c r="K15">
-        <v>3.02</v>
+        <v>5.7</v>
       </c>
       <c r="L15">
-        <v>-2.39</v>
+        <v>0.79</v>
       </c>
       <c r="M15">
-        <v>10.12</v>
+        <v>9.83</v>
       </c>
       <c r="N15">
         <v>32</v>
       </c>
       <c r="P15">
-        <v>256.14</v>
+        <v>267.49</v>
       </c>
       <c r="Q15">
-        <v>255.25</v>
+        <v>263.88</v>
       </c>
       <c r="R15">
-        <v>257.71</v>
+        <v>260.61</v>
       </c>
       <c r="S15">
-        <v>268.9</v>
+        <v>267.51</v>
       </c>
       <c r="T15">
-        <v>-3.12</v>
+        <v>0.08</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2359,49 +2463,49 @@
         <v>0</v>
       </c>
       <c r="W15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y15">
         <v>62.22</v>
       </c>
       <c r="Z15">
-        <v>-0.16</v>
+        <v>1.91</v>
       </c>
       <c r="AA15">
-        <v>-1.02</v>
+        <v>1.49</v>
       </c>
       <c r="AB15">
-        <v>0.86</v>
+        <v>0.42</v>
       </c>
       <c r="AC15">
-        <v>100</v>
+        <v>90.84</v>
       </c>
       <c r="AD15">
-        <v>71.84999999999999</v>
+        <v>91.13</v>
       </c>
       <c r="AE15">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="AF15">
-        <v>-57.16</v>
+        <v>-66.36</v>
       </c>
       <c r="AG15">
-        <v>261.89</v>
+        <v>269.91</v>
       </c>
       <c r="AH15">
-        <v>248.62</v>
+        <v>257.84</v>
       </c>
       <c r="AI15">
-        <v>250.08</v>
+        <v>258.56</v>
       </c>
       <c r="AJ15" t="s">
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>25.92</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2412,10 +2516,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>271.61</v>
+        <v>279.5</v>
       </c>
       <c r="D16">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2424,43 +2528,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-8.23</v>
+        <v>-5.57</v>
       </c>
       <c r="H16">
-        <v>7.77</v>
+        <v>10.9</v>
       </c>
       <c r="I16">
-        <v>3.77</v>
+        <v>0.42</v>
       </c>
       <c r="J16">
         <v>2.11</v>
       </c>
       <c r="K16">
-        <v>2.97</v>
+        <v>5.86</v>
       </c>
       <c r="L16">
-        <v>-2.15</v>
+        <v>0.97</v>
       </c>
       <c r="M16">
-        <v>10.13</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="N16">
         <v>42</v>
       </c>
       <c r="P16">
-        <v>266.77</v>
+        <v>278.59</v>
       </c>
       <c r="Q16">
-        <v>266</v>
+        <v>274.65</v>
       </c>
       <c r="R16">
-        <v>268.63</v>
+        <v>271.44</v>
       </c>
       <c r="S16">
-        <v>280.32</v>
+        <v>278.83</v>
       </c>
       <c r="T16">
-        <v>-3.11</v>
+        <v>0.24</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2469,49 +2573,49 @@
         <v>0</v>
       </c>
       <c r="W16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16">
-        <v>62.31</v>
+        <v>65.42</v>
       </c>
       <c r="Z16">
-        <v>-0.22</v>
+        <v>1.99</v>
       </c>
       <c r="AA16">
-        <v>-1.12</v>
+        <v>1.49</v>
       </c>
       <c r="AB16">
-        <v>0.91</v>
+        <v>0.49</v>
       </c>
       <c r="AC16">
-        <v>100</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="AD16">
-        <v>70.45999999999999</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="AE16">
-        <v>4.16</v>
+        <v>3.78</v>
       </c>
       <c r="AF16">
-        <v>86.90000000000001</v>
+        <v>-39.1</v>
       </c>
       <c r="AG16">
-        <v>273.06</v>
+        <v>280.71</v>
       </c>
       <c r="AH16">
-        <v>258.94</v>
+        <v>268.6</v>
       </c>
       <c r="AI16">
-        <v>272.84</v>
+        <v>268.92</v>
       </c>
       <c r="AJ16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK16">
-        <v>34.58</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2522,106 +2626,106 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>97.53</v>
+        <v>96.44</v>
       </c>
       <c r="D17">
-        <v>1.7</v>
+        <v>-1.62</v>
       </c>
       <c r="E17">
         <v>109.87</v>
       </c>
       <c r="F17">
-        <v>75.2</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-11.23</v>
+        <v>-12.22</v>
       </c>
       <c r="H17">
-        <v>29.69</v>
+        <v>28.23</v>
       </c>
       <c r="I17">
-        <v>4.02</v>
+        <v>1.98</v>
       </c>
       <c r="J17">
-        <v>9.67</v>
+        <v>2.22</v>
       </c>
       <c r="K17">
-        <v>2.4</v>
+        <v>7.62</v>
       </c>
       <c r="L17">
-        <v>24.54</v>
+        <v>26.26</v>
       </c>
       <c r="M17">
-        <v>29.79</v>
+        <v>30.37</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>94.97</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="Q17">
-        <v>92.45</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="R17">
-        <v>93.95</v>
+        <v>94.42</v>
       </c>
       <c r="S17">
-        <v>92.98999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="T17">
-        <v>4.88</v>
+        <v>0.99</v>
       </c>
       <c r="U17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="s">
+        <v>59</v>
+      </c>
+      <c r="X17">
         <v>1</v>
       </c>
-      <c r="W17" t="s">
-        <v>58</v>
-      </c>
-      <c r="X17">
-        <v>2</v>
-      </c>
       <c r="Y17">
-        <v>64.79000000000001</v>
+        <v>57.59</v>
       </c>
       <c r="Z17">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="AA17">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="AB17">
-        <v>0.75</v>
+        <v>0.44</v>
       </c>
       <c r="AC17">
-        <v>99.63</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="AD17">
-        <v>86.18000000000001</v>
+        <v>91.28</v>
       </c>
       <c r="AE17">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AF17">
-        <v>99.69</v>
+        <v>218</v>
       </c>
       <c r="AG17">
-        <v>96.90000000000001</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="AH17">
-        <v>87.98999999999999</v>
+        <v>91.17</v>
       </c>
       <c r="AI17">
-        <v>88.78</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AJ17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AK17">
-        <v>37.56</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2632,10 +2736,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>283.22</v>
+        <v>281.49</v>
       </c>
       <c r="D18">
-        <v>-0.02</v>
+        <v>-0.86</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2644,49 +2748,49 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-4.49</v>
+        <v>-5.07</v>
       </c>
       <c r="H18">
-        <v>15.33</v>
+        <v>14.63</v>
       </c>
       <c r="I18">
-        <v>3.87</v>
+        <v>-0.74</v>
       </c>
       <c r="J18">
-        <v>7.22</v>
+        <v>-1.67</v>
       </c>
       <c r="K18">
-        <v>7.99</v>
+        <v>6.77</v>
       </c>
       <c r="L18">
-        <v>0.52</v>
+        <v>3.11</v>
       </c>
       <c r="M18">
-        <v>9.16</v>
+        <v>8.41</v>
       </c>
       <c r="N18">
         <v>53</v>
       </c>
       <c r="P18">
-        <v>279.53</v>
+        <v>283.21</v>
       </c>
       <c r="Q18">
-        <v>271.75</v>
+        <v>282.83</v>
       </c>
       <c r="R18">
-        <v>270.79</v>
+        <v>281.89</v>
       </c>
       <c r="S18">
-        <v>279.95</v>
+        <v>281.74</v>
       </c>
       <c r="T18">
-        <v>1.17</v>
+        <v>-0.09</v>
       </c>
       <c r="U18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="s">
         <v>58</v>
@@ -2695,43 +2799,43 @@
         <v>2</v>
       </c>
       <c r="Y18">
-        <v>69.77</v>
+        <v>47.64</v>
       </c>
       <c r="Z18">
-        <v>3.13</v>
+        <v>-0.02</v>
       </c>
       <c r="AA18">
-        <v>1.39</v>
+        <v>0.01</v>
       </c>
       <c r="AB18">
-        <v>1.73</v>
+        <v>-0.03</v>
       </c>
       <c r="AC18">
-        <v>99.84999999999999</v>
+        <v>82.13</v>
       </c>
       <c r="AD18">
-        <v>99.92</v>
+        <v>77.84</v>
       </c>
       <c r="AE18">
-        <v>6.28</v>
+        <v>5.3</v>
       </c>
       <c r="AF18">
-        <v>-54.79</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="AG18">
-        <v>282.89</v>
+        <v>289.06</v>
       </c>
       <c r="AH18">
-        <v>260.62</v>
+        <v>276.6</v>
       </c>
       <c r="AI18">
-        <v>265.49</v>
+        <v>273.93</v>
       </c>
       <c r="AJ18" t="s">
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>38.19</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2742,106 +2846,106 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>240.38</v>
+        <v>226.11</v>
       </c>
       <c r="D19">
-        <v>-0.61</v>
+        <v>0.17</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>104.62</v>
+        <v>109.64</v>
       </c>
       <c r="G19">
-        <v>-32.9</v>
+        <v>-36.88</v>
       </c>
       <c r="H19">
-        <v>129.76</v>
+        <v>106.23</v>
       </c>
       <c r="I19">
-        <v>6.25</v>
+        <v>6.83</v>
       </c>
       <c r="J19">
-        <v>-7.31</v>
+        <v>5.6</v>
       </c>
       <c r="K19">
-        <v>0.74</v>
+        <v>-17.92</v>
       </c>
       <c r="L19">
-        <v>128.98</v>
+        <v>103.08</v>
       </c>
       <c r="M19">
-        <v>64.43000000000001</v>
+        <v>54.16</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>236.13</v>
+        <v>220.53</v>
       </c>
       <c r="Q19">
-        <v>247.4</v>
+        <v>215.48</v>
       </c>
       <c r="R19">
-        <v>245.01</v>
+        <v>223.2</v>
       </c>
       <c r="S19">
-        <v>208.98</v>
+        <v>224.17</v>
       </c>
       <c r="T19">
-        <v>15.03</v>
+        <v>0.87</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="s">
         <v>59</v>
       </c>
       <c r="X19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>46.52</v>
+        <v>61.14</v>
       </c>
       <c r="Z19">
-        <v>-3.57</v>
+        <v>-0.28</v>
       </c>
       <c r="AA19">
-        <v>-2.25</v>
+        <v>-2.39</v>
       </c>
       <c r="AB19">
-        <v>-1.32</v>
+        <v>2.11</v>
       </c>
       <c r="AC19">
-        <v>67.06</v>
+        <v>100</v>
       </c>
       <c r="AD19">
-        <v>47.01</v>
+        <v>94.52</v>
       </c>
       <c r="AE19">
-        <v>7.88</v>
+        <v>4.64</v>
       </c>
       <c r="AF19">
-        <v>-51.86</v>
+        <v>48.51</v>
       </c>
       <c r="AG19">
-        <v>270.99</v>
+        <v>224.73</v>
       </c>
       <c r="AH19">
-        <v>223.81</v>
+        <v>206.24</v>
       </c>
       <c r="AI19">
-        <v>249.36</v>
+        <v>211.28</v>
       </c>
       <c r="AJ19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK19">
-        <v>25.71</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2852,10 +2956,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>258</v>
+        <v>264.97</v>
       </c>
       <c r="D20">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2864,43 +2968,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-8.25</v>
+        <v>-5.78</v>
       </c>
       <c r="H20">
-        <v>7.79</v>
+        <v>10.7</v>
       </c>
       <c r="I20">
-        <v>3.76</v>
+        <v>0.15</v>
       </c>
       <c r="J20">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>5.62</v>
       </c>
       <c r="L20">
-        <v>-2.19</v>
+        <v>0.87</v>
       </c>
       <c r="M20">
-        <v>10.07</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N20">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P20">
-        <v>253.43</v>
+        <v>264.48</v>
       </c>
       <c r="Q20">
-        <v>252.68</v>
+        <v>260.9</v>
       </c>
       <c r="R20">
-        <v>255.2</v>
+        <v>257.89</v>
       </c>
       <c r="S20">
-        <v>266.3</v>
+        <v>264.89</v>
       </c>
       <c r="T20">
-        <v>-3.12</v>
+        <v>0.03</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -2909,49 +3013,49 @@
         <v>0</v>
       </c>
       <c r="W20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y20">
-        <v>62.07</v>
+        <v>63.73</v>
       </c>
       <c r="Z20">
-        <v>-0.21</v>
+        <v>1.83</v>
       </c>
       <c r="AA20">
-        <v>-1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>0.85</v>
+        <v>0.43</v>
       </c>
       <c r="AC20">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AD20">
-        <v>70.47</v>
+        <v>92.02</v>
       </c>
       <c r="AE20">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="AF20">
-        <v>10.99</v>
+        <v>-49.51</v>
       </c>
       <c r="AG20">
-        <v>259.28</v>
+        <v>266.54</v>
       </c>
       <c r="AH20">
-        <v>246.08</v>
+        <v>255.25</v>
       </c>
       <c r="AI20">
-        <v>258.45</v>
+        <v>253.97</v>
       </c>
       <c r="AJ20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK20">
-        <v>28.73</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2962,13 +3066,13 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>771.36</v>
+        <v>803.25</v>
       </c>
       <c r="D21">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="E21">
-        <v>771.36</v>
+        <v>803.25</v>
       </c>
       <c r="F21">
         <v>642.67</v>
@@ -2977,91 +3081,91 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>20.02</v>
+        <v>24.99</v>
       </c>
       <c r="I21">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>4.43</v>
+        <v>3.76</v>
       </c>
       <c r="K21">
-        <v>12.35</v>
+        <v>8.84</v>
       </c>
       <c r="L21">
-        <v>7.72</v>
+        <v>13.48</v>
       </c>
       <c r="M21">
-        <v>14.09</v>
+        <v>14.46</v>
       </c>
       <c r="N21">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P21">
-        <v>753.75</v>
+        <v>796.35</v>
       </c>
       <c r="Q21">
-        <v>752.09</v>
+        <v>781.33</v>
       </c>
       <c r="R21">
-        <v>747.58</v>
+        <v>770.14</v>
       </c>
       <c r="S21">
-        <v>731.53</v>
+        <v>741.09</v>
       </c>
       <c r="T21">
-        <v>5.44</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="U21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X21">
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>61.76</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="Z21">
-        <v>3.58</v>
+        <v>8.32</v>
       </c>
       <c r="AA21">
-        <v>1.89</v>
+        <v>6.15</v>
       </c>
       <c r="AB21">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>89.69</v>
+        <v>96.81</v>
       </c>
       <c r="AD21">
-        <v>57.89</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="AE21">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="AF21">
-        <v>-37.46</v>
+        <v>49.65</v>
       </c>
       <c r="AG21">
-        <v>776.9400000000001</v>
+        <v>804.1</v>
       </c>
       <c r="AH21">
-        <v>727.24</v>
+        <v>758.5599999999999</v>
       </c>
       <c r="AI21">
-        <v>728.35</v>
+        <v>768.0599999999999</v>
       </c>
       <c r="AJ21" t="s">
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>24.48</v>
+        <v>13.96</v>
       </c>
     </row>
   </sheetData>
@@ -3202,7 +3306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3222,27 +3326,2874 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>65</v>
+      <c r="A6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-0.57</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-0.27</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-1.36</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-2.52</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>4.21</v>
+      </c>
+      <c r="D15" s="7">
+        <v>5.45</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.48</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2.16</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="7">
+        <v>14.25</v>
+      </c>
+      <c r="D19" s="7">
+        <v>13.06</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="7">
+        <v>14.88</v>
+      </c>
+      <c r="D20" s="7">
+        <v>13.11</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="7">
+        <v>4.64</v>
+      </c>
+      <c r="D21" s="7">
+        <v>3.47</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2.59</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.96</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2.83</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.94</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.95</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2.11</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="7">
+        <v>6.73</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2.22</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-4.51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-1.67</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="7">
+        <v>3.41</v>
+      </c>
+      <c r="D28" s="7">
+        <v>5.6</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2.52</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="7">
+        <v>4.67</v>
+      </c>
+      <c r="D30" s="7">
+        <v>3.76</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1.1</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-0.1</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="7">
+        <v>1.11</v>
+      </c>
+      <c r="D32" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-0.67</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-1.15</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-0.09</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="7">
+        <v>5.37</v>
+      </c>
+      <c r="D35" s="7">
+        <v>6.24</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="7">
+        <v>5.31</v>
+      </c>
+      <c r="D36" s="7">
+        <v>6.25</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-2.22</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-1.64</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="7">
+        <v>1.12</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="7">
+        <v>2.11</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0.31</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2.52</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="7">
+        <v>1.51</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="7">
+        <v>4.93</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1.98</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-0.74</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="7">
+        <v>6.66</v>
+      </c>
+      <c r="D48" s="7">
+        <v>6.83</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="D50" s="7">
+        <v>1</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="7">
+        <v>4.36</v>
+      </c>
+      <c r="D51" s="7">
+        <v>4.54</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-89.52</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-89.48999999999999</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="7">
+        <v>4.64</v>
+      </c>
+      <c r="D53" s="7">
+        <v>4.09</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-11.39</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-10.93</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="7">
+        <v>48.26</v>
+      </c>
+      <c r="D55" s="7">
+        <v>49</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="7">
+        <v>48.3</v>
+      </c>
+      <c r="D56" s="7">
+        <v>49.25</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="7">
+        <v>15.32</v>
+      </c>
+      <c r="D57" s="7">
+        <v>14.89</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="7">
+        <v>5.22</v>
+      </c>
+      <c r="D58" s="7">
+        <v>5.08</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="7">
+        <v>-8.65</v>
+      </c>
+      <c r="D59" s="7">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="D60" s="7">
+        <v>-8.31</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="7">
+        <v>12.33</v>
+      </c>
+      <c r="D61" s="7">
+        <v>12.87</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D62" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="D63" s="7">
+        <v>0.79</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="D64" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="7">
+        <v>28.04</v>
+      </c>
+      <c r="D65" s="7">
+        <v>26.26</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="7">
+        <v>3.36</v>
+      </c>
+      <c r="D66" s="7">
+        <v>3.11</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="7">
+        <v>103.69</v>
+      </c>
+      <c r="D67" s="7">
+        <v>103.08</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="D68" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="7">
+        <v>12.87</v>
+      </c>
+      <c r="D69" s="7">
+        <v>13.48</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="7">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="D70" s="7">
+        <v>8.08</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="D71" s="7">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-10.22</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-11.06</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-1.94</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-0.97</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-5.43</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-4.46</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-0.92</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-5.11</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-4.19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-10.7</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-10.12</v>
+      </c>
+      <c r="E76" s="9">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="7">
+        <v>4.12</v>
+      </c>
+      <c r="D77" s="7">
+        <v>3.19</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="7">
+        <v>11.87</v>
+      </c>
+      <c r="D78" s="7">
+        <v>13.57</v>
+      </c>
+      <c r="E78" s="9">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="7">
+        <v>11.9</v>
+      </c>
+      <c r="D79" s="7">
+        <v>13.62</v>
+      </c>
+      <c r="E79" s="9">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="7">
+        <v>9.07</v>
+      </c>
+      <c r="D80" s="7">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="7">
+        <v>5.58</v>
+      </c>
+      <c r="D81" s="7">
+        <v>5.66</v>
+      </c>
+      <c r="E81" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="7">
+        <v>5.75</v>
+      </c>
+      <c r="D82" s="7">
+        <v>5.62</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="7">
+        <v>5.77</v>
+      </c>
+      <c r="D83" s="7">
+        <v>5.7</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="7">
+        <v>5.61</v>
+      </c>
+      <c r="D84" s="7">
+        <v>5.86</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="7">
+        <v>9.35</v>
+      </c>
+      <c r="D85" s="7">
+        <v>7.62</v>
+      </c>
+      <c r="E85" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="7">
+        <v>7.59</v>
+      </c>
+      <c r="D86" s="7">
+        <v>6.77</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="7">
+        <v>-12.45</v>
+      </c>
+      <c r="D87" s="7">
+        <v>-17.92</v>
+      </c>
+      <c r="E87" s="8">
+        <v>-5.47</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="7">
+        <v>5.54</v>
+      </c>
+      <c r="D88" s="7">
+        <v>5.62</v>
+      </c>
+      <c r="E88" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="7">
+        <v>9.18</v>
+      </c>
+      <c r="D89" s="7">
+        <v>8.84</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="7">
+        <v>-5.83</v>
+      </c>
+      <c r="D90" s="7">
+        <v>-6.15</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="7">
+        <v>-90.56999999999999</v>
+      </c>
+      <c r="D91" s="7">
+        <v>-90.59</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="7">
+        <v>-13.36</v>
+      </c>
+      <c r="D92" s="7">
+        <v>-13.79</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="7">
+        <v>-13.13</v>
+      </c>
+      <c r="D93" s="7">
+        <v>-13.15</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="7">
+        <v>-15.79</v>
+      </c>
+      <c r="D94" s="7">
+        <v>-14.98</v>
+      </c>
+      <c r="E94" s="9">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="7">
+        <v>-15.81</v>
+      </c>
+      <c r="D95" s="7">
+        <v>-14.94</v>
+      </c>
+      <c r="E95" s="9">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="7">
+        <v>-14.09</v>
+      </c>
+      <c r="D96" s="7">
+        <v>-13.75</v>
+      </c>
+      <c r="E96" s="9">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="7">
+        <v>-2.58</v>
+      </c>
+      <c r="D97" s="7">
+        <v>-2.8</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="7">
+        <v>-19.23</v>
+      </c>
+      <c r="D98" s="7">
+        <v>-18.79</v>
+      </c>
+      <c r="E98" s="9">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="7">
+        <v>-19.2</v>
+      </c>
+      <c r="D99" s="7">
+        <v>-18.9</v>
+      </c>
+      <c r="E99" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="7">
+        <v>-5.96</v>
+      </c>
+      <c r="D100" s="7">
+        <v>-5.74</v>
+      </c>
+      <c r="E100" s="9">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="7">
+        <v>-5.92</v>
+      </c>
+      <c r="D101" s="7">
+        <v>-5.84</v>
+      </c>
+      <c r="E101" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="7">
+        <v>-5.99</v>
+      </c>
+      <c r="D102" s="7">
+        <v>-5.57</v>
+      </c>
+      <c r="E102" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="7">
+        <v>-10.78</v>
+      </c>
+      <c r="D103" s="7">
+        <v>-12.22</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="7">
+        <v>-4.25</v>
+      </c>
+      <c r="D104" s="7">
+        <v>-5.07</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="7">
+        <v>-36.99</v>
+      </c>
+      <c r="D105" s="7">
+        <v>-36.88</v>
+      </c>
+      <c r="E105" s="9">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="7">
+        <v>-5.97</v>
+      </c>
+      <c r="D106" s="7">
+        <v>-5.78</v>
+      </c>
+      <c r="E106" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" s="7">
+        <v>598.78</v>
+      </c>
+      <c r="D107" s="7">
+        <v>596.77</v>
+      </c>
+      <c r="E107" s="8">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" s="7">
+        <v>60.12</v>
+      </c>
+      <c r="D108" s="7">
+        <v>59.99</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" s="7">
+        <v>94.27</v>
+      </c>
+      <c r="D109" s="7">
+        <v>93.8</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="7">
+        <v>52.99</v>
+      </c>
+      <c r="D110" s="7">
+        <v>52.98</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" s="7">
+        <v>123.4</v>
+      </c>
+      <c r="D111" s="7">
+        <v>124.58</v>
+      </c>
+      <c r="E111" s="9">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" s="7">
+        <v>127.45</v>
+      </c>
+      <c r="D112" s="7">
+        <v>128.77</v>
+      </c>
+      <c r="E112" s="9">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="7">
+        <v>486.54</v>
+      </c>
+      <c r="D113" s="7">
+        <v>488.49</v>
+      </c>
+      <c r="E113" s="9">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" s="7">
+        <v>982.84</v>
+      </c>
+      <c r="D114" s="7">
+        <v>980.6</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" s="7">
+        <v>34.87</v>
+      </c>
+      <c r="D115" s="7">
+        <v>35.06</v>
+      </c>
+      <c r="E115" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" s="7">
+        <v>34.98</v>
+      </c>
+      <c r="D116" s="7">
+        <v>35.11</v>
+      </c>
+      <c r="E116" s="9">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" s="7">
+        <v>807.63</v>
+      </c>
+      <c r="D117" s="7">
+        <v>809</v>
+      </c>
+      <c r="E117" s="9">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" s="7">
+        <v>279.83</v>
+      </c>
+      <c r="D118" s="7">
+        <v>280.46</v>
+      </c>
+      <c r="E118" s="9">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" s="7">
+        <v>267.49</v>
+      </c>
+      <c r="D119" s="7">
+        <v>267.72</v>
+      </c>
+      <c r="E119" s="9">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" s="7">
+        <v>278.25</v>
+      </c>
+      <c r="D120" s="7">
+        <v>279.5</v>
+      </c>
+      <c r="E120" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" s="7">
+        <v>98.03</v>
+      </c>
+      <c r="D121" s="7">
+        <v>96.44</v>
+      </c>
+      <c r="E121" s="8">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C122" s="7">
+        <v>283.93</v>
+      </c>
+      <c r="D122" s="7">
+        <v>281.49</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" s="7">
+        <v>225.73</v>
+      </c>
+      <c r="D123" s="7">
+        <v>226.11</v>
+      </c>
+      <c r="E123" s="9">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" s="7">
+        <v>264.41</v>
+      </c>
+      <c r="D124" s="7">
+        <v>264.97</v>
+      </c>
+      <c r="E124" s="9">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" s="7">
+        <v>801.58</v>
+      </c>
+      <c r="D125" s="7">
+        <v>803.25</v>
+      </c>
+      <c r="E125" s="9">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="7">
+        <v>58</v>
+      </c>
+      <c r="D126" s="7">
+        <v>47</v>
+      </c>
+      <c r="E126" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" s="7">
+        <v>53</v>
+      </c>
+      <c r="D127" s="7">
+        <v>63</v>
+      </c>
+      <c r="E127" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="7">
+        <v>47</v>
+      </c>
+      <c r="D128" s="7">
+        <v>58</v>
+      </c>
+      <c r="E128" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="7">
+        <v>42</v>
+      </c>
+      <c r="D129" s="7">
+        <v>32</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130" s="7">
+        <v>32</v>
+      </c>
+      <c r="D130" s="7">
+        <v>42</v>
+      </c>
+      <c r="E130" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="7">
+        <v>63</v>
+      </c>
+      <c r="D131" s="7">
+        <v>53</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="7">
+        <v>55.66</v>
+      </c>
+      <c r="D132" s="7">
+        <v>53.14</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" s="7">
+        <v>54.11</v>
+      </c>
+      <c r="D133" s="7">
+        <v>52.66</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" s="7">
+        <v>34.7</v>
+      </c>
+      <c r="D134" s="7">
+        <v>31.82</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="7">
+        <v>51.36</v>
+      </c>
+      <c r="D135" s="7">
+        <v>51.22</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" s="7">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="D136" s="7">
+        <v>69.19</v>
+      </c>
+      <c r="E136" s="9">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" s="7">
+        <v>66.56</v>
+      </c>
+      <c r="D137" s="7">
+        <v>69.44</v>
+      </c>
+      <c r="E137" s="9">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" s="7">
+        <v>48.51</v>
+      </c>
+      <c r="D138" s="7">
+        <v>50.7</v>
+      </c>
+      <c r="E138" s="9">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" s="7">
+        <v>61.39</v>
+      </c>
+      <c r="D139" s="7">
+        <v>59.14</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" s="7">
+        <v>67.11</v>
+      </c>
+      <c r="D140" s="7">
+        <v>68.20999999999999</v>
+      </c>
+      <c r="E140" s="9">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" s="7">
+        <v>67.95</v>
+      </c>
+      <c r="D141" s="7">
+        <v>68.7</v>
+      </c>
+      <c r="E141" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" s="7">
+        <v>70.52</v>
+      </c>
+      <c r="D142" s="7">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="E142" s="9">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" s="7">
+        <v>62.75</v>
+      </c>
+      <c r="D143" s="7">
+        <v>64.14</v>
+      </c>
+      <c r="E143" s="9">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" s="7">
+        <v>61.72</v>
+      </c>
+      <c r="D144" s="7">
+        <v>62.22</v>
+      </c>
+      <c r="E144" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="7">
+        <v>62.68</v>
+      </c>
+      <c r="D145" s="7">
+        <v>65.42</v>
+      </c>
+      <c r="E145" s="9">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" s="7">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="D146" s="7">
+        <v>57.59</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-8.17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" s="7">
+        <v>52.81</v>
+      </c>
+      <c r="D147" s="7">
+        <v>47.64</v>
+      </c>
+      <c r="E147" s="8">
+        <v>-5.17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="7">
+        <v>60.72</v>
+      </c>
+      <c r="D148" s="7">
+        <v>61.14</v>
+      </c>
+      <c r="E148" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" s="7">
+        <v>62.42</v>
+      </c>
+      <c r="D149" s="7">
+        <v>63.73</v>
+      </c>
+      <c r="E149" s="9">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="7">
+        <v>67.14</v>
+      </c>
+      <c r="D150" s="7">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="E150" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C151" s="7">
+        <v>-47.02</v>
+      </c>
+      <c r="D151" s="7">
+        <v>-11.44</v>
+      </c>
+      <c r="E151" s="9">
+        <v>35.58</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C152" s="7">
+        <v>-29.32</v>
+      </c>
+      <c r="D152" s="7">
+        <v>-74.02</v>
+      </c>
+      <c r="E152" s="8">
+        <v>-44.7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C153" s="7">
+        <v>17.51</v>
+      </c>
+      <c r="D153" s="7">
+        <v>252.14</v>
+      </c>
+      <c r="E153" s="9">
+        <v>234.63</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C154" s="7">
+        <v>166.01</v>
+      </c>
+      <c r="D154" s="7">
+        <v>-28.03</v>
+      </c>
+      <c r="E154" s="8">
+        <v>-194.04</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155" s="7">
+        <v>45.77</v>
+      </c>
+      <c r="D155" s="7">
+        <v>58.94</v>
+      </c>
+      <c r="E155" s="9">
+        <v>13.17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C156" s="7">
+        <v>-23.55</v>
+      </c>
+      <c r="D156" s="7">
+        <v>43.07</v>
+      </c>
+      <c r="E156" s="9">
+        <v>66.62</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C157" s="7">
+        <v>19.35</v>
+      </c>
+      <c r="D157" s="7">
+        <v>-3.35</v>
+      </c>
+      <c r="E157" s="8">
+        <v>-22.7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C158" s="7">
+        <v>73.55</v>
+      </c>
+      <c r="D158" s="7">
+        <v>47.1</v>
+      </c>
+      <c r="E158" s="8">
+        <v>-26.45</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C159" s="7">
+        <v>-40.63</v>
+      </c>
+      <c r="D159" s="7">
+        <v>-37.95</v>
+      </c>
+      <c r="E159" s="9">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C160" s="7">
+        <v>-33.07</v>
+      </c>
+      <c r="D160" s="7">
+        <v>-44.57</v>
+      </c>
+      <c r="E160" s="8">
+        <v>-11.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C161" s="7">
+        <v>8</v>
+      </c>
+      <c r="D161" s="7">
+        <v>-23.37</v>
+      </c>
+      <c r="E161" s="8">
+        <v>-31.37</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C162" s="7">
+        <v>1.12</v>
+      </c>
+      <c r="D162" s="7">
+        <v>20.97</v>
+      </c>
+      <c r="E162" s="9">
+        <v>19.85</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C163" s="7">
+        <v>-82.05</v>
+      </c>
+      <c r="D163" s="7">
+        <v>-40.24</v>
+      </c>
+      <c r="E163" s="9">
+        <v>41.81</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C164" s="7">
+        <v>11.67</v>
+      </c>
+      <c r="D164" s="7">
+        <v>-66.36</v>
+      </c>
+      <c r="E164" s="8">
+        <v>-78.03</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C165" s="7">
+        <v>-52.22</v>
+      </c>
+      <c r="D165" s="7">
+        <v>-39.1</v>
+      </c>
+      <c r="E165" s="9">
+        <v>13.12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C166" s="7">
+        <v>122.68</v>
+      </c>
+      <c r="D166" s="7">
+        <v>218</v>
+      </c>
+      <c r="E166" s="9">
+        <v>95.31999999999999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167" s="7">
+        <v>-77.11</v>
+      </c>
+      <c r="D167" s="7">
+        <v>-78.43000000000001</v>
+      </c>
+      <c r="E167" s="8">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C168" s="7">
+        <v>80.34</v>
+      </c>
+      <c r="D168" s="7">
+        <v>48.51</v>
+      </c>
+      <c r="E168" s="8">
+        <v>-31.83</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C169" s="7">
+        <v>6.74</v>
+      </c>
+      <c r="D169" s="7">
+        <v>-49.51</v>
+      </c>
+      <c r="E169" s="8">
+        <v>-56.25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="7">
+        <v>-25.56</v>
+      </c>
+      <c r="D170" s="7">
+        <v>49.65</v>
+      </c>
+      <c r="E170" s="9">
+        <v>75.20999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3262,60 +6213,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>73</v>
+      <c r="B1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="6">
-        <v>51.04000000000001</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="12">
+        <v>55.04000000000001</v>
+      </c>
+      <c r="C2" s="13">
         <v>20</v>
       </c>
-      <c r="D2" s="6">
-        <v>55.6</v>
-      </c>
-      <c r="E2" s="6">
-        <v>50</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="G2" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="D2" s="12">
+        <v>60</v>
+      </c>
+      <c r="E2" s="12">
+        <v>60</v>
+      </c>
+      <c r="F2" s="12">
+        <v>3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>52.6</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -3417,131 +6368,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="9">
-        <v>0.6443000000000001</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.3443</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.3028</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.2979</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.2452</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.1648</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.1412</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0.1409</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0.1132</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0.1013</v>
+      <c r="A2" s="15">
+        <v>0.5416</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3289</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.3037</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2996</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.2538</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1626</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.1446</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.1442</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0.1048</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0.0989</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="9">
-        <v>0.1012</v>
-      </c>
-      <c r="B4" s="9">
-        <v>0.101</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0.1007</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0.0916</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.0799</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.0692</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0.022</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0.019</v>
-      </c>
-      <c r="I4" s="9">
-        <v>-0.1415</v>
-      </c>
-      <c r="J4" s="9">
-        <v>-0.2979</v>
+      <c r="A4" s="15">
+        <v>0.0983</v>
+      </c>
+      <c r="B4" s="15">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="C4" s="15">
+        <v>0.0978</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.08410000000000001</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0.0801</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.0774</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.0203</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.0171</v>
+      </c>
+      <c r="I4" s="15">
+        <v>-0.0741</v>
+      </c>
+      <c r="J4" s="15">
+        <v>-0.3026</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="92">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,40 +226,37 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.4 → 54.1</t>
+    <t>No → Yes</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.4</t>
-  </si>
-  <si>
-    <t>54.1</t>
-  </si>
-  <si>
     <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>52.2 → 48.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>73.0 → 68.1</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
+    <t>68.1</t>
+  </si>
+  <si>
+    <t>73.1 → 68.3</t>
+  </si>
+  <si>
+    <t>73.1</t>
+  </si>
+  <si>
+    <t>68.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -311,7 +308,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,13 +349,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,6 +390,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,12 +482,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -486,7 +496,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -985,10 +995,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>599.01</v>
+        <v>597.97</v>
       </c>
       <c r="D2">
-        <v>0.7</v>
+        <v>-0.17</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -997,43 +1007,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-5.8</v>
+        <v>-5.96</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="I2">
-        <v>0.45</v>
+        <v>-0.36</v>
       </c>
       <c r="J2">
-        <v>0.8100000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K2">
-        <v>8.199999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="L2">
-        <v>4.68</v>
+        <v>5.35</v>
       </c>
       <c r="M2">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>597.92</v>
+        <v>597.48</v>
       </c>
       <c r="Q2">
-        <v>595.08</v>
+        <v>595.12</v>
       </c>
       <c r="R2">
-        <v>592.05</v>
+        <v>592.78</v>
       </c>
       <c r="S2">
         <v>593.15</v>
       </c>
       <c r="T2">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1048,31 +1058,31 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.41</v>
+        <v>54.04</v>
       </c>
       <c r="Z2">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AA2">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB2">
         <v>0.14</v>
       </c>
       <c r="AC2">
-        <v>67.18000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AD2">
-        <v>73.43000000000001</v>
+        <v>68</v>
       </c>
       <c r="AE2">
-        <v>6.99</v>
+        <v>6.68</v>
       </c>
       <c r="AF2">
-        <v>-4.18</v>
+        <v>-55.8</v>
       </c>
       <c r="AG2">
-        <v>604.79</v>
+        <v>604.88</v>
       </c>
       <c r="AH2">
         <v>585.36</v>
@@ -1084,7 +1094,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>13.58</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1095,10 +1105,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>60.15</v>
+        <v>59.89</v>
       </c>
       <c r="D3">
-        <v>0.77</v>
+        <v>-0.43</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1107,43 +1117,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.56</v>
+        <v>-90.59999999999999</v>
       </c>
       <c r="H3">
-        <v>15.41</v>
+        <v>14.91</v>
       </c>
       <c r="I3">
-        <v>0.4</v>
+        <v>-0.76</v>
       </c>
       <c r="J3">
-        <v>0.64</v>
+        <v>-0.23</v>
       </c>
       <c r="K3">
-        <v>8.050000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="L3">
-        <v>-89.48999999999999</v>
+        <v>-89.43000000000001</v>
       </c>
       <c r="M3">
-        <v>-30.21</v>
+        <v>-30.34</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>60.06</v>
+        <v>59.97</v>
       </c>
       <c r="Q3">
         <v>59.69</v>
       </c>
       <c r="R3">
-        <v>59.38</v>
+        <v>59.45</v>
       </c>
       <c r="S3">
-        <v>297.29</v>
+        <v>294.58</v>
       </c>
       <c r="T3">
-        <v>-79.77</v>
+        <v>-79.67</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1158,31 +1168,31 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>54.1</v>
+        <v>51.2</v>
       </c>
       <c r="Z3">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AA3">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="AB3">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AC3">
-        <v>69.3</v>
+        <v>63.76</v>
       </c>
       <c r="AD3">
-        <v>74.95</v>
+        <v>67.63</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>-69.83</v>
+        <v>-79.16</v>
       </c>
       <c r="AG3">
-        <v>60.72</v>
+        <v>60.73</v>
       </c>
       <c r="AH3">
         <v>58.66</v>
@@ -1194,7 +1204,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>16.26</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1205,10 +1215,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>93.86</v>
+        <v>94.37</v>
       </c>
       <c r="D4">
-        <v>0.02</v>
+        <v>0.54</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1217,43 +1227,43 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-13.74</v>
+        <v>-13.27</v>
       </c>
       <c r="H4">
-        <v>6.87</v>
+        <v>7.45</v>
       </c>
       <c r="I4">
-        <v>-0.93</v>
+        <v>0.17</v>
       </c>
       <c r="J4">
-        <v>-2.79</v>
+        <v>-1.61</v>
       </c>
       <c r="K4">
-        <v>-11.36</v>
+        <v>-9.85</v>
       </c>
       <c r="L4">
-        <v>4.5</v>
+        <v>5.08</v>
       </c>
       <c r="M4">
-        <v>29.06</v>
+        <v>29.32</v>
       </c>
       <c r="N4">
         <v>16</v>
       </c>
       <c r="P4">
-        <v>94</v>
+        <v>94.03</v>
       </c>
       <c r="Q4">
-        <v>95.13</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="R4">
-        <v>96.64</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="S4">
         <v>97.94</v>
       </c>
       <c r="T4">
-        <v>-4.17</v>
+        <v>-3.64</v>
       </c>
       <c r="U4" t="s">
         <v>59</v>
@@ -1268,34 +1278,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.61</v>
+        <v>39.35</v>
       </c>
       <c r="Z4">
-        <v>-0.89</v>
+        <v>-0.84</v>
       </c>
       <c r="AA4">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="AB4">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AC4">
-        <v>22.61</v>
+        <v>48.22</v>
       </c>
       <c r="AD4">
-        <v>25.04</v>
+        <v>31.79</v>
       </c>
       <c r="AE4">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AF4">
-        <v>20</v>
+        <v>-26.57</v>
       </c>
       <c r="AG4">
-        <v>97.3</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="AH4">
-        <v>92.95</v>
+        <v>92.88</v>
       </c>
       <c r="AI4">
         <v>100.34</v>
@@ -1304,7 +1314,7 @@
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>11.35</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1315,10 +1325,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>52.04</v>
+        <v>52.43</v>
       </c>
       <c r="D5">
-        <v>-0.99</v>
+        <v>0.75</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1327,43 +1337,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-14.69</v>
+        <v>-14.05</v>
       </c>
       <c r="H5">
-        <v>6.92</v>
+        <v>7.73</v>
       </c>
       <c r="I5">
-        <v>-2.09</v>
+        <v>-1.15</v>
       </c>
       <c r="J5">
-        <v>-0.21</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>-4.53</v>
+        <v>-3.9</v>
       </c>
       <c r="L5">
-        <v>-11.78</v>
+        <v>-10.45</v>
       </c>
       <c r="M5">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>52.72</v>
+        <v>52.6</v>
       </c>
       <c r="Q5">
-        <v>52.78</v>
+        <v>52.8</v>
       </c>
       <c r="R5">
-        <v>52.72</v>
+        <v>52.73</v>
       </c>
       <c r="S5">
-        <v>54.79</v>
+        <v>54.75</v>
       </c>
       <c r="T5">
-        <v>-5.01</v>
+        <v>-4.23</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1378,34 +1388,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.96</v>
+        <v>45.49</v>
       </c>
       <c r="Z5">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="AA5">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AB5">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC5">
-        <v>17.53</v>
+        <v>11.8</v>
       </c>
       <c r="AD5">
-        <v>36.33</v>
+        <v>21.63</v>
       </c>
       <c r="AE5">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>114.41</v>
+        <v>-39.71</v>
       </c>
       <c r="AG5">
-        <v>53.55</v>
+        <v>53.5</v>
       </c>
       <c r="AH5">
-        <v>52</v>
+        <v>52.09</v>
       </c>
       <c r="AI5">
         <v>54.72</v>
@@ -1414,7 +1424,7 @@
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>27.61</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1425,10 +1435,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>126.45</v>
+        <v>125.48</v>
       </c>
       <c r="D6">
-        <v>0.74</v>
+        <v>-0.77</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1437,85 +1447,85 @@
         <v>82.08</v>
       </c>
       <c r="G6">
-        <v>-13.7</v>
+        <v>-14.37</v>
       </c>
       <c r="H6">
-        <v>54.06</v>
+        <v>52.88</v>
       </c>
       <c r="I6">
-        <v>5.91</v>
+        <v>2.45</v>
       </c>
       <c r="J6">
-        <v>9.029999999999999</v>
+        <v>7.81</v>
       </c>
       <c r="K6">
-        <v>-2.29</v>
+        <v>-3.25</v>
       </c>
       <c r="L6">
-        <v>50.64</v>
+        <v>48.74</v>
       </c>
       <c r="M6">
-        <v>25.54</v>
+        <v>25.38</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>124.49</v>
+        <v>125.09</v>
       </c>
       <c r="Q6">
-        <v>119.28</v>
+        <v>119.73</v>
       </c>
       <c r="R6">
-        <v>119.59</v>
+        <v>119.53</v>
       </c>
       <c r="S6">
-        <v>119.34</v>
+        <v>119.47</v>
       </c>
       <c r="T6">
-        <v>5.96</v>
+        <v>5.03</v>
       </c>
       <c r="U6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
       </c>
       <c r="W6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6">
-        <v>72.97</v>
+        <v>68.12</v>
       </c>
       <c r="Z6">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AA6">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="AB6">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="AD6">
-        <v>100</v>
+        <v>98.14</v>
       </c>
       <c r="AE6">
         <v>1.74</v>
       </c>
       <c r="AF6">
-        <v>-9.75</v>
+        <v>22.18</v>
       </c>
       <c r="AG6">
-        <v>125.86</v>
+        <v>126.72</v>
       </c>
       <c r="AH6">
-        <v>112.7</v>
+        <v>112.74</v>
       </c>
       <c r="AI6">
         <v>120.92</v>
@@ -1524,7 +1534,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>39.54</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1535,10 +1545,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>130.61</v>
+        <v>129.65</v>
       </c>
       <c r="D7">
-        <v>0.6899999999999999</v>
+        <v>-0.74</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1547,85 +1557,85 @@
         <v>84.73999999999999</v>
       </c>
       <c r="G7">
-        <v>-13.72</v>
+        <v>-14.35</v>
       </c>
       <c r="H7">
-        <v>54.13</v>
+        <v>53</v>
       </c>
       <c r="I7">
-        <v>5.81</v>
+        <v>2.54</v>
       </c>
       <c r="J7">
-        <v>8.91</v>
+        <v>7.73</v>
       </c>
       <c r="K7">
-        <v>-2.38</v>
+        <v>-3.25</v>
       </c>
       <c r="L7">
-        <v>50.8</v>
+        <v>49.01</v>
       </c>
       <c r="M7">
-        <v>33.42</v>
+        <v>33.08</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>128.6</v>
+        <v>129.24</v>
       </c>
       <c r="Q7">
-        <v>123.27</v>
+        <v>123.73</v>
       </c>
       <c r="R7">
-        <v>123.61</v>
+        <v>123.55</v>
       </c>
       <c r="S7">
-        <v>123.28</v>
+        <v>123.41</v>
       </c>
       <c r="T7">
-        <v>5.95</v>
+        <v>5.06</v>
       </c>
       <c r="U7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7">
-        <v>73.06</v>
+        <v>68.34</v>
       </c>
       <c r="Z7">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AA7">
-        <v>0.39</v>
+        <v>0.66</v>
       </c>
       <c r="AB7">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AC7">
-        <v>100</v>
+        <v>94.62</v>
       </c>
       <c r="AD7">
-        <v>100</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="AE7">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AF7">
-        <v>35.22</v>
+        <v>-33.8</v>
       </c>
       <c r="AG7">
-        <v>130.01</v>
+        <v>130.9</v>
       </c>
       <c r="AH7">
-        <v>116.52</v>
+        <v>116.55</v>
       </c>
       <c r="AI7">
         <v>123.87</v>
@@ -1634,7 +1644,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>41.16</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1645,55 +1655,55 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>480.32</v>
+        <v>480.01</v>
       </c>
       <c r="D8">
-        <v>-0.86</v>
+        <v>-0.06</v>
       </c>
       <c r="E8">
         <v>566.34</v>
       </c>
       <c r="F8">
-        <v>431.97</v>
+        <v>432.14</v>
       </c>
       <c r="G8">
-        <v>-15.19</v>
+        <v>-15.24</v>
       </c>
       <c r="H8">
-        <v>11.19</v>
+        <v>11.08</v>
       </c>
       <c r="I8">
-        <v>-1.86</v>
+        <v>-1.43</v>
       </c>
       <c r="J8">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="K8">
-        <v>-10.61</v>
+        <v>-10.71</v>
       </c>
       <c r="L8">
-        <v>9.77</v>
+        <v>11.12</v>
       </c>
       <c r="M8">
-        <v>7.76</v>
+        <v>7.7</v>
       </c>
       <c r="N8">
         <v>22</v>
       </c>
       <c r="P8">
-        <v>485.36</v>
+        <v>483.97</v>
       </c>
       <c r="Q8">
-        <v>487.32</v>
+        <v>487.11</v>
       </c>
       <c r="R8">
-        <v>484.7</v>
+        <v>484.09</v>
       </c>
       <c r="S8">
-        <v>511.82</v>
+        <v>511.65</v>
       </c>
       <c r="T8">
-        <v>-6.15</v>
+        <v>-6.18</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1708,34 +1718,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>42.28</v>
+        <v>41.98</v>
       </c>
       <c r="Z8">
-        <v>-0.14</v>
+        <v>-0.68</v>
       </c>
       <c r="AA8">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="AB8">
-        <v>-0.67</v>
+        <v>-0.97</v>
       </c>
       <c r="AC8">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>21.12</v>
+        <v>11.18</v>
       </c>
       <c r="AE8">
-        <v>10.61</v>
+        <v>10.28</v>
       </c>
       <c r="AF8">
-        <v>2.54</v>
+        <v>-17.51</v>
       </c>
       <c r="AG8">
-        <v>497.72</v>
+        <v>497.93</v>
       </c>
       <c r="AH8">
-        <v>476.93</v>
+        <v>476.28</v>
       </c>
       <c r="AI8">
         <v>511.37</v>
@@ -1744,7 +1754,7 @@
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>28.73</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1755,10 +1765,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>968.74</v>
+        <v>968.22</v>
       </c>
       <c r="D9">
-        <v>-0.44</v>
+        <v>-0.05</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1767,43 +1777,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-3.98</v>
+        <v>-4.03</v>
       </c>
       <c r="H9">
-        <v>9.449999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I9">
-        <v>-0.5600000000000001</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J9">
-        <v>0.3</v>
+        <v>0.53</v>
       </c>
       <c r="K9">
-        <v>0.62</v>
+        <v>1.2</v>
       </c>
       <c r="L9">
-        <v>4.46</v>
+        <v>5.64</v>
       </c>
       <c r="M9">
-        <v>15.69</v>
+        <v>15.49</v>
       </c>
       <c r="N9">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="P9">
-        <v>976.51</v>
+        <v>974.6799999999999</v>
       </c>
       <c r="Q9">
-        <v>969.1900000000001</v>
+        <v>969.5599999999999</v>
       </c>
       <c r="R9">
-        <v>967.26</v>
+        <v>967.58</v>
       </c>
       <c r="S9">
-        <v>966</v>
+        <v>965.92</v>
       </c>
       <c r="T9">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1818,34 +1828,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>48.68</v>
+        <v>48.26</v>
       </c>
       <c r="Z9">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="AA9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB9">
-        <v>0.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC9">
-        <v>56.69</v>
+        <v>33.52</v>
       </c>
       <c r="AD9">
-        <v>77.37</v>
+        <v>56.56</v>
       </c>
       <c r="AE9">
-        <v>12.05</v>
+        <v>11.72</v>
       </c>
       <c r="AF9">
-        <v>35.3</v>
+        <v>-62.43</v>
       </c>
       <c r="AG9">
-        <v>983.49</v>
+        <v>983.33</v>
       </c>
       <c r="AH9">
-        <v>954.89</v>
+        <v>955.79</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1854,7 +1864,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>24.07</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1865,10 +1875,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>34.66</v>
+        <v>34.74</v>
       </c>
       <c r="D10">
-        <v>-1.59</v>
+        <v>0.23</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1877,43 +1887,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-19.71</v>
+        <v>-19.53</v>
       </c>
       <c r="H10">
-        <v>21.1</v>
+        <v>21.38</v>
       </c>
       <c r="I10">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="J10">
-        <v>8.960000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K10">
-        <v>12.79</v>
+        <v>10.95</v>
       </c>
       <c r="L10">
-        <v>-8.279999999999999</v>
+        <v>-7.41</v>
       </c>
       <c r="M10">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="N10">
         <v>63</v>
       </c>
       <c r="P10">
-        <v>34.85</v>
+        <v>34.91</v>
       </c>
       <c r="Q10">
-        <v>33.64</v>
+        <v>33.78</v>
       </c>
       <c r="R10">
-        <v>31.99</v>
+        <v>32.03</v>
       </c>
       <c r="S10">
-        <v>35.81</v>
+        <v>35.78</v>
       </c>
       <c r="T10">
-        <v>-3.2</v>
+        <v>-2.92</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1928,34 +1938,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>62.22</v>
+        <v>62.8</v>
       </c>
       <c r="Z10">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="AA10">
         <v>0.87</v>
       </c>
       <c r="AB10">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="AC10">
-        <v>70.59999999999999</v>
+        <v>48.37</v>
       </c>
       <c r="AD10">
-        <v>75.39</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AF10">
-        <v>-62.52</v>
+        <v>-63.46</v>
       </c>
       <c r="AG10">
-        <v>36.26</v>
+        <v>36.31</v>
       </c>
       <c r="AH10">
-        <v>31.02</v>
+        <v>31.26</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -1964,7 +1974,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>49.41</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1975,10 +1985,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>34.65</v>
+        <v>34.77</v>
       </c>
       <c r="D11">
-        <v>-1.67</v>
+        <v>0.35</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1987,43 +1997,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-19.96</v>
+        <v>-19.68</v>
       </c>
       <c r="H11">
-        <v>21.03</v>
+        <v>21.45</v>
       </c>
       <c r="I11">
-        <v>-0.2</v>
+        <v>0.61</v>
       </c>
       <c r="J11">
-        <v>8.789999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="K11">
-        <v>12.94</v>
+        <v>10.87</v>
       </c>
       <c r="L11">
-        <v>-8.65</v>
+        <v>-7.5</v>
       </c>
       <c r="M11">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="N11">
         <v>58</v>
       </c>
       <c r="P11">
-        <v>34.91</v>
+        <v>34.95</v>
       </c>
       <c r="Q11">
-        <v>33.65</v>
+        <v>33.8</v>
       </c>
       <c r="R11">
-        <v>32.01</v>
+        <v>32.05</v>
       </c>
       <c r="S11">
-        <v>35.88</v>
+        <v>35.86</v>
       </c>
       <c r="T11">
-        <v>-3.43</v>
+        <v>-3.03</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2038,34 +2048,34 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>62.05</v>
+        <v>62.92</v>
       </c>
       <c r="Z11">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AA11">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AB11">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AC11">
-        <v>71.63</v>
+        <v>49.65</v>
       </c>
       <c r="AD11">
-        <v>78.14</v>
+        <v>68.75</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>-30.3</v>
+        <v>-64.38</v>
       </c>
       <c r="AG11">
-        <v>36.31</v>
+        <v>36.36</v>
       </c>
       <c r="AH11">
-        <v>30.99</v>
+        <v>31.23</v>
       </c>
       <c r="AI11">
         <v>32.2</v>
@@ -2074,7 +2084,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>41.46</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2085,10 +2095,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>806.3099999999999</v>
+        <v>807.6900000000001</v>
       </c>
       <c r="D12">
-        <v>-0.17</v>
+        <v>0.17</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2097,43 +2107,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="H12">
-        <v>23.69</v>
+        <v>23.9</v>
       </c>
       <c r="I12">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
-        <v>7.82</v>
+        <v>9.06</v>
       </c>
       <c r="L12">
-        <v>13.13</v>
+        <v>14.71</v>
       </c>
       <c r="M12">
-        <v>14.29</v>
+        <v>14.32</v>
       </c>
       <c r="N12">
         <v>73</v>
       </c>
       <c r="P12">
-        <v>807.58</v>
+        <v>807.67</v>
       </c>
       <c r="Q12">
-        <v>791.25</v>
+        <v>792.78</v>
       </c>
       <c r="R12">
-        <v>779.3200000000001</v>
+        <v>780.36</v>
       </c>
       <c r="S12">
-        <v>748.55</v>
+        <v>748.84</v>
       </c>
       <c r="T12">
-        <v>7.72</v>
+        <v>7.86</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2148,34 +2158,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>67.39</v>
+        <v>68.38</v>
       </c>
       <c r="Z12">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="AA12">
-        <v>7.3</v>
+        <v>7.59</v>
       </c>
       <c r="AB12">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="AC12">
-        <v>90.65000000000001</v>
+        <v>85.38</v>
       </c>
       <c r="AD12">
-        <v>95.87</v>
+        <v>91</v>
       </c>
       <c r="AE12">
-        <v>12.89</v>
+        <v>14.34</v>
       </c>
       <c r="AF12">
-        <v>-20.85</v>
+        <v>-32.96</v>
       </c>
       <c r="AG12">
-        <v>817.41</v>
+        <v>819.03</v>
       </c>
       <c r="AH12">
-        <v>765.08</v>
+        <v>766.54</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2184,7 +2194,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>19.16</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2195,10 +2205,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>278.32</v>
+        <v>278.16</v>
       </c>
       <c r="D13">
-        <v>-0.29</v>
+        <v>-0.06</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2207,43 +2217,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-6.46</v>
+        <v>-6.52</v>
       </c>
       <c r="H13">
-        <v>9.82</v>
+        <v>9.75</v>
       </c>
       <c r="I13">
-        <v>-0.59</v>
+        <v>-0.87</v>
       </c>
       <c r="J13">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="K13">
-        <v>4.12</v>
+        <v>3.95</v>
       </c>
       <c r="L13">
-        <v>0.37</v>
+        <v>1.1</v>
       </c>
       <c r="M13">
-        <v>9.58</v>
+        <v>9.35</v>
       </c>
       <c r="N13">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P13">
-        <v>279.67</v>
+        <v>279.18</v>
       </c>
       <c r="Q13">
-        <v>276.58</v>
+        <v>276.78</v>
       </c>
       <c r="R13">
-        <v>273.34</v>
+        <v>273.59</v>
       </c>
       <c r="S13">
-        <v>280.08</v>
+        <v>280.01</v>
       </c>
       <c r="T13">
-        <v>-0.63</v>
+        <v>-0.66</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2258,34 +2268,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>56.25</v>
+        <v>55.68</v>
       </c>
       <c r="Z13">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AA13">
         <v>1.62</v>
       </c>
       <c r="AB13">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="AC13">
-        <v>72.06</v>
+        <v>51.45</v>
       </c>
       <c r="AD13">
-        <v>82.33</v>
+        <v>68.62</v>
       </c>
       <c r="AE13">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AF13">
-        <v>2.49</v>
+        <v>-33.99</v>
       </c>
       <c r="AG13">
-        <v>282.52</v>
+        <v>282.64</v>
       </c>
       <c r="AH13">
-        <v>270.63</v>
+        <v>270.93</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2294,7 +2304,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>13.83</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2305,10 +2315,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>270.65</v>
+        <v>270.72</v>
       </c>
       <c r="D14">
-        <v>-0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2317,31 +2327,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-6.55</v>
+        <v>-6.52</v>
       </c>
       <c r="H14">
-        <v>9.77</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14">
-        <v>-0.2</v>
+        <v>-0.77</v>
       </c>
       <c r="J14">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="K14">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="M14">
-        <v>-8.44</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="P14">
-        <v>272.14</v>
+        <v>271.72</v>
       </c>
       <c r="Q14">
-        <v>269.11</v>
+        <v>269.32</v>
       </c>
       <c r="R14">
-        <v>266.14</v>
+        <v>266.38</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2353,34 +2363,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>55.96</v>
+        <v>56.17</v>
       </c>
       <c r="Z14">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="AC14">
-        <v>76.97</v>
+        <v>57.36</v>
       </c>
       <c r="AD14">
-        <v>88.51000000000001</v>
+        <v>74.98</v>
       </c>
       <c r="AE14">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
       <c r="AF14">
-        <v>-27.98</v>
+        <v>151.83</v>
       </c>
       <c r="AG14">
-        <v>274.66</v>
+        <v>274.78</v>
       </c>
       <c r="AH14">
-        <v>263.55</v>
+        <v>263.86</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2389,7 +2399,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>51.77</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2400,10 +2410,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>265.57</v>
+        <v>265.33</v>
       </c>
       <c r="D15">
-        <v>-0.38</v>
+        <v>-0.09</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2412,43 +2422,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-6.59</v>
+        <v>-6.68</v>
       </c>
       <c r="H15">
-        <v>9.960000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I15">
-        <v>-0.68</v>
+        <v>-1.12</v>
       </c>
       <c r="J15">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="L15">
-        <v>0.44</v>
+        <v>1.13</v>
       </c>
       <c r="M15">
-        <v>9.529999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="N15">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="P15">
-        <v>267.14</v>
+        <v>266.54</v>
       </c>
       <c r="Q15">
-        <v>264.31</v>
+        <v>264.49</v>
       </c>
       <c r="R15">
-        <v>261.1</v>
+        <v>261.33</v>
       </c>
       <c r="S15">
-        <v>267.38</v>
+        <v>267.31</v>
       </c>
       <c r="T15">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2463,34 +2473,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>54.73</v>
+        <v>53.92</v>
       </c>
       <c r="Z15">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AA15">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="AC15">
-        <v>69.89</v>
+        <v>49.88</v>
       </c>
       <c r="AD15">
-        <v>80.48999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="AE15">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="AF15">
-        <v>-27.27</v>
+        <v>-35.95</v>
       </c>
       <c r="AG15">
-        <v>270.29</v>
+        <v>270.37</v>
       </c>
       <c r="AH15">
-        <v>258.34</v>
+        <v>258.61</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2499,7 +2509,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>33.08</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2510,10 +2520,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>276.8</v>
+        <v>276.76</v>
       </c>
       <c r="D16">
-        <v>-0.31</v>
+        <v>-0.01</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2522,43 +2532,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-6.48</v>
+        <v>-6.49</v>
       </c>
       <c r="H16">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="I16">
-        <v>-0.6</v>
+        <v>-0.82</v>
       </c>
       <c r="J16">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="L16">
-        <v>0.26</v>
+        <v>1.05</v>
       </c>
       <c r="M16">
-        <v>9.6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="N16">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P16">
-        <v>278.25</v>
+        <v>277.79</v>
       </c>
       <c r="Q16">
-        <v>275.17</v>
+        <v>275.38</v>
       </c>
       <c r="R16">
-        <v>271.96</v>
+        <v>272.21</v>
       </c>
       <c r="S16">
-        <v>278.7</v>
+        <v>278.62</v>
       </c>
       <c r="T16">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2573,34 +2583,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>55.66</v>
+        <v>55.52</v>
       </c>
       <c r="Z16">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AA16">
         <v>1.62</v>
       </c>
       <c r="AB16">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="AC16">
-        <v>72.06</v>
+        <v>49.11</v>
       </c>
       <c r="AD16">
-        <v>83.19</v>
+        <v>68.08</v>
       </c>
       <c r="AE16">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="AF16">
-        <v>-24.28</v>
+        <v>-17.38</v>
       </c>
       <c r="AG16">
-        <v>281.14</v>
+        <v>281.25</v>
       </c>
       <c r="AH16">
-        <v>269.19</v>
+        <v>269.51</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2609,7 +2619,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>52.76</v>
+        <v>55.32</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2620,10 +2630,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>98.27</v>
+        <v>98.11</v>
       </c>
       <c r="D17">
-        <v>1.89</v>
+        <v>-0.16</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2632,43 +2642,43 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-10.56</v>
+        <v>-10.7</v>
       </c>
       <c r="H17">
-        <v>30.66</v>
+        <v>30.45</v>
       </c>
       <c r="I17">
-        <v>3.01</v>
+        <v>0.78</v>
       </c>
       <c r="J17">
-        <v>5.92</v>
+        <v>4.7</v>
       </c>
       <c r="K17">
-        <v>9.26</v>
+        <v>11.22</v>
       </c>
       <c r="L17">
-        <v>27.76</v>
+        <v>27.83</v>
       </c>
       <c r="M17">
-        <v>30.48</v>
+        <v>30.4</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>97.31</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="Q17">
-        <v>94.76000000000001</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="R17">
-        <v>94.68000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="S17">
-        <v>95.59</v>
+        <v>95.63</v>
       </c>
       <c r="T17">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2683,43 +2693,43 @@
         <v>2</v>
       </c>
       <c r="Y17">
-        <v>63.62</v>
+        <v>62.78</v>
       </c>
       <c r="Z17">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="AA17">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AB17">
         <v>0.45</v>
       </c>
       <c r="AC17">
-        <v>69.92</v>
+        <v>78.38</v>
       </c>
       <c r="AD17">
-        <v>76.67</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AE17">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AF17">
-        <v>42.18</v>
+        <v>-42.57</v>
       </c>
       <c r="AG17">
-        <v>98.37</v>
+        <v>98.83</v>
       </c>
       <c r="AH17">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="AI17">
-        <v>91.59999999999999</v>
+        <v>91.81</v>
       </c>
       <c r="AJ17" t="s">
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>36.4</v>
+        <v>38.82</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2730,10 +2740,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>280.02</v>
+        <v>279.31</v>
       </c>
       <c r="D18">
-        <v>-0.06</v>
+        <v>-0.25</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2742,43 +2752,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.57</v>
+        <v>-5.81</v>
       </c>
       <c r="H18">
-        <v>14.03</v>
+        <v>13.74</v>
       </c>
       <c r="I18">
-        <v>-1.27</v>
+        <v>-1.53</v>
       </c>
       <c r="J18">
-        <v>-1.85</v>
+        <v>-2.69</v>
       </c>
       <c r="K18">
-        <v>5.44</v>
+        <v>5.02</v>
       </c>
       <c r="L18">
-        <v>2.2</v>
+        <v>3.24</v>
       </c>
       <c r="M18">
-        <v>8.52</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N18">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P18">
-        <v>281.86</v>
+        <v>280.99</v>
       </c>
       <c r="Q18">
-        <v>282.22</v>
+        <v>281.97</v>
       </c>
       <c r="R18">
-        <v>282.36</v>
+        <v>282.6</v>
       </c>
       <c r="S18">
-        <v>281.61</v>
+        <v>281.56</v>
       </c>
       <c r="T18">
-        <v>-0.57</v>
+        <v>-0.8</v>
       </c>
       <c r="U18" t="s">
         <v>59</v>
@@ -2793,34 +2803,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>44.77</v>
+        <v>43.32</v>
       </c>
       <c r="Z18">
-        <v>-0.37</v>
+        <v>-0.55</v>
       </c>
       <c r="AA18">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="AB18">
-        <v>-0.27</v>
+        <v>-0.36</v>
       </c>
       <c r="AC18">
-        <v>27.76</v>
+        <v>12.3</v>
       </c>
       <c r="AD18">
-        <v>55.15</v>
+        <v>31.87</v>
       </c>
       <c r="AE18">
-        <v>5.01</v>
+        <v>4.79</v>
       </c>
       <c r="AF18">
-        <v>-89.36</v>
+        <v>-90.04000000000001</v>
       </c>
       <c r="AG18">
-        <v>288.17</v>
+        <v>287.96</v>
       </c>
       <c r="AH18">
-        <v>276.28</v>
+        <v>275.98</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2829,7 +2839,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>20.31</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2840,10 +2850,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>231.39</v>
+        <v>226.31</v>
       </c>
       <c r="D19">
-        <v>1.54</v>
+        <v>-2.2</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2852,43 +2862,43 @@
         <v>109.64</v>
       </c>
       <c r="G19">
-        <v>-35.41</v>
+        <v>-36.83</v>
       </c>
       <c r="H19">
-        <v>111.05</v>
+        <v>106.41</v>
       </c>
       <c r="I19">
-        <v>5.83</v>
+        <v>2.92</v>
       </c>
       <c r="J19">
-        <v>8.619999999999999</v>
+        <v>5.74</v>
       </c>
       <c r="K19">
-        <v>-9.210000000000001</v>
+        <v>-12.61</v>
       </c>
       <c r="L19">
-        <v>103.99</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="M19">
-        <v>55.69</v>
+        <v>53.96</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>226.2</v>
+        <v>227.48</v>
       </c>
       <c r="Q19">
-        <v>217.09</v>
+        <v>217.8</v>
       </c>
       <c r="R19">
-        <v>222.18</v>
+        <v>221.65</v>
       </c>
       <c r="S19">
-        <v>224.99</v>
+        <v>225.42</v>
       </c>
       <c r="T19">
-        <v>2.84</v>
+        <v>0.4</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2903,43 +2913,43 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>66.67</v>
+        <v>57.92</v>
       </c>
       <c r="Z19">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AA19">
-        <v>-1.17</v>
+        <v>-0.6</v>
       </c>
       <c r="AB19">
-        <v>2.57</v>
+        <v>2.28</v>
       </c>
       <c r="AC19">
-        <v>100</v>
+        <v>88.98</v>
       </c>
       <c r="AD19">
-        <v>100</v>
+        <v>96.33</v>
       </c>
       <c r="AE19">
-        <v>4.71</v>
+        <v>5.31</v>
       </c>
       <c r="AF19">
-        <v>50</v>
+        <v>14.35</v>
       </c>
       <c r="AG19">
-        <v>229.68</v>
+        <v>230.8</v>
       </c>
       <c r="AH19">
-        <v>204.51</v>
+        <v>204.81</v>
       </c>
       <c r="AI19">
-        <v>215.2</v>
+        <v>215.89</v>
       </c>
       <c r="AJ19" t="s">
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>35.58</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2950,10 +2960,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>262.98</v>
+        <v>262.84</v>
       </c>
       <c r="D20">
-        <v>-0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2962,43 +2972,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-6.48</v>
+        <v>-6.53</v>
       </c>
       <c r="H20">
-        <v>9.869999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="I20">
-        <v>-0.41</v>
+        <v>-0.88</v>
       </c>
       <c r="J20">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="K20">
-        <v>3.89</v>
+        <v>3.76</v>
       </c>
       <c r="L20">
-        <v>0.29</v>
+        <v>1.1</v>
       </c>
       <c r="M20">
-        <v>9.56</v>
+        <v>9.35</v>
       </c>
       <c r="N20">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P20">
-        <v>264.26</v>
+        <v>263.79</v>
       </c>
       <c r="Q20">
-        <v>261.39</v>
+        <v>261.59</v>
       </c>
       <c r="R20">
-        <v>258.38</v>
+        <v>258.62</v>
       </c>
       <c r="S20">
-        <v>264.76</v>
+        <v>264.69</v>
       </c>
       <c r="T20">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3013,34 +3023,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>56.02</v>
+        <v>55.49</v>
       </c>
       <c r="Z20">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AA20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB20">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>72.2</v>
+        <v>51.91</v>
       </c>
       <c r="AD20">
-        <v>82.39</v>
+        <v>68.83</v>
       </c>
       <c r="AE20">
-        <v>3.99</v>
+        <v>3.84</v>
       </c>
       <c r="AF20">
-        <v>1.4</v>
+        <v>-33.5</v>
       </c>
       <c r="AG20">
-        <v>266.96</v>
+        <v>267.06</v>
       </c>
       <c r="AH20">
-        <v>255.81</v>
+        <v>256.13</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3049,7 +3059,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>38.99</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3060,10 +3070,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>799.62</v>
+        <v>801.14</v>
       </c>
       <c r="D21">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3072,43 +3082,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-0.45</v>
+        <v>-0.26</v>
       </c>
       <c r="H21">
-        <v>24.42</v>
+        <v>24.66</v>
       </c>
       <c r="I21">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="K21">
-        <v>8.07</v>
+        <v>9.25</v>
       </c>
       <c r="L21">
-        <v>13.45</v>
+        <v>14.82</v>
       </c>
       <c r="M21">
-        <v>14.32</v>
+        <v>14.34</v>
       </c>
       <c r="N21">
         <v>78</v>
       </c>
       <c r="P21">
-        <v>800.4</v>
+        <v>801.29</v>
       </c>
       <c r="Q21">
-        <v>784.4</v>
+        <v>785.9400000000001</v>
       </c>
       <c r="R21">
-        <v>772.1900000000001</v>
+        <v>773.22</v>
       </c>
       <c r="S21">
-        <v>741.7</v>
+        <v>742</v>
       </c>
       <c r="T21">
-        <v>7.81</v>
+        <v>7.97</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3123,43 +3133,43 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>64.09</v>
+        <v>65.03</v>
       </c>
       <c r="Z21">
-        <v>8.59</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AA21">
-        <v>7.03</v>
+        <v>7.34</v>
       </c>
       <c r="AB21">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AC21">
-        <v>87.59999999999999</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="AD21">
-        <v>93.16</v>
+        <v>87.94</v>
       </c>
       <c r="AE21">
-        <v>10.96</v>
+        <v>10.7</v>
       </c>
       <c r="AF21">
-        <v>-6.24</v>
+        <v>-52.76</v>
       </c>
       <c r="AG21">
-        <v>808.28</v>
+        <v>809.98</v>
       </c>
       <c r="AH21">
-        <v>760.52</v>
+        <v>761.9</v>
       </c>
       <c r="AI21">
-        <v>768.78</v>
+        <v>770.55</v>
       </c>
       <c r="AJ21" t="s">
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>13.33</v>
+        <v>14.02</v>
       </c>
     </row>
   </sheetData>
@@ -3340,36 +3350,36 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>59</v>
@@ -3379,1301 +3389,1304 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>78</v>
+      <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="A6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="E7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-0.98</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.79</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D12" s="7">
-        <v>0.64</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" s="8">
-        <v>1.57</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-3.04</v>
+        <v>0.64</v>
       </c>
       <c r="D13" s="7">
-        <v>-2.79</v>
+        <v>-0.23</v>
       </c>
       <c r="E13" s="8">
-        <v>0.25</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>0.15</v>
+        <v>-2.79</v>
       </c>
       <c r="D14" s="7">
-        <v>-0.21</v>
+        <v>-1.61</v>
       </c>
       <c r="E14" s="9">
-        <v>-0.36</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>7.33</v>
+        <v>-0.21</v>
       </c>
       <c r="D15" s="7">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.7</v>
+        <v>1</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>7.45</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D16" s="7">
-        <v>8.91</v>
+        <v>7.81</v>
       </c>
       <c r="E16" s="8">
-        <v>1.46</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>0.53</v>
+        <v>8.91</v>
       </c>
       <c r="D17" s="7">
-        <v>0.34</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.19</v>
+        <v>7.73</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="D18" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-0.08</v>
+        <v>-0.34</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>9.550000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="7">
-        <v>8.960000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E19" s="9">
-        <v>-0.59</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>9.58</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D20" s="7">
-        <v>8.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E20" s="9">
-        <v>-0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>3.66</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D21" s="7">
-        <v>3.85</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.19</v>
+        <v>9.82</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>1.39</v>
+        <v>3.85</v>
       </c>
       <c r="D22" s="7">
-        <v>1.82</v>
+        <v>3.7</v>
       </c>
       <c r="E22" s="8">
-        <v>0.43</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>1.29</v>
+        <v>1.82</v>
       </c>
       <c r="D23" s="7">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="E23" s="8">
-        <v>0.38</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="D24" s="7">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="E24" s="8">
-        <v>0.13</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="D25" s="7">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="E25" s="8">
-        <v>0.49</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="D26" s="7">
-        <v>5.92</v>
+        <v>1.65</v>
       </c>
       <c r="E26" s="8">
-        <v>3.96</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>-2.65</v>
+        <v>5.92</v>
       </c>
       <c r="D27" s="7">
-        <v>-1.85</v>
+        <v>4.7</v>
       </c>
       <c r="E27" s="8">
-        <v>0.8</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>7.13</v>
+        <v>-1.85</v>
       </c>
       <c r="D28" s="7">
-        <v>8.619999999999999</v>
+        <v>-2.69</v>
       </c>
       <c r="E28" s="8">
-        <v>1.49</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="7">
-        <v>1.26</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D29" s="7">
-        <v>1.78</v>
+        <v>5.74</v>
       </c>
       <c r="E29" s="8">
-        <v>0.52</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="7">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="D30" s="7">
-        <v>4</v>
+        <v>1.64</v>
       </c>
       <c r="E30" s="8">
-        <v>0.44</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="7">
-        <v>-0.15</v>
+        <v>4</v>
       </c>
       <c r="D31" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.6</v>
+        <v>4.02</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="D32" s="7">
-        <v>0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="E32" s="8">
-        <v>0.4</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>-0.82</v>
+        <v>0.4</v>
       </c>
       <c r="D33" s="7">
-        <v>-0.93</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.11</v>
+        <v>-0.76</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>-1.3</v>
+        <v>-0.93</v>
       </c>
       <c r="D34" s="7">
-        <v>-2.09</v>
+        <v>0.17</v>
       </c>
       <c r="E34" s="9">
-        <v>-0.79</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>7.14</v>
+        <v>-2.09</v>
       </c>
       <c r="D35" s="7">
-        <v>5.91</v>
+        <v>-1.15</v>
       </c>
       <c r="E35" s="9">
-        <v>-1.23</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>7.1</v>
+        <v>5.91</v>
       </c>
       <c r="D36" s="7">
-        <v>5.81</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-1.29</v>
+        <v>2.45</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-3.46</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-0.97</v>
+        <v>5.81</v>
       </c>
       <c r="D37" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.89</v>
+        <v>2.54</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>0.46</v>
+        <v>-1.86</v>
       </c>
       <c r="D38" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-1.43</v>
       </c>
       <c r="E38" s="9">
-        <v>-1.02</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>1.47</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D39" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-1.33</v>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>1.56</v>
+        <v>0.14</v>
       </c>
       <c r="D40" s="7">
-        <v>-0.2</v>
+        <v>0.87</v>
       </c>
       <c r="E40" s="9">
-        <v>-1.76</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>0.71</v>
+        <v>-0.2</v>
       </c>
       <c r="D41" s="7">
-        <v>0.07000000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="E41" s="9">
-        <v>-0.64</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D42" s="7">
-        <v>-0.59</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.71</v>
+        <v>0.05</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>0.38</v>
+        <v>-0.59</v>
       </c>
       <c r="D43" s="7">
-        <v>-0.2</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.58</v>
+        <v>-0.87</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="D44" s="7">
-        <v>-0.68</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.7</v>
+        <v>-0.77</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="D45" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.6</v>
+        <v>-1.12</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>2.02</v>
+        <v>-0.6</v>
       </c>
       <c r="D46" s="7">
-        <v>3.01</v>
+        <v>-0.82</v>
       </c>
       <c r="E46" s="8">
-        <v>0.99</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="7">
-        <v>-1.11</v>
+        <v>3.01</v>
       </c>
       <c r="D47" s="7">
-        <v>-1.27</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.16</v>
+        <v>0.78</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="7">
-        <v>7.34</v>
+        <v>-1.27</v>
       </c>
       <c r="D48" s="7">
-        <v>5.83</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-1.51</v>
+        <v>-1.53</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="7">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="D49" s="7">
-        <v>-0.41</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.41</v>
+        <v>2.92</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-2.91</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="7">
-        <v>1.5</v>
+        <v>-0.41</v>
       </c>
       <c r="D50" s="7">
-        <v>1.06</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.44</v>
+        <v>-0.88</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51" s="7">
-        <v>4.1</v>
+        <v>1.06</v>
       </c>
       <c r="D51" s="7">
-        <v>4.68</v>
+        <v>0.55</v>
       </c>
       <c r="E51" s="8">
-        <v>0.58</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>-89.55</v>
+        <v>4.68</v>
       </c>
       <c r="D52" s="7">
-        <v>-89.48999999999999</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.06</v>
+        <v>5.35</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.67</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>4.24</v>
+        <v>-89.48999999999999</v>
       </c>
       <c r="D53" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.26</v>
+        <v>-89.43000000000001</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>-10.75</v>
+        <v>4.5</v>
       </c>
       <c r="D54" s="7">
-        <v>-11.78</v>
+        <v>5.08</v>
       </c>
       <c r="E54" s="9">
-        <v>-1.03</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>50.43</v>
+        <v>-11.78</v>
       </c>
       <c r="D55" s="7">
-        <v>50.64</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.21</v>
+        <v>-10.45</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1.33</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>50.66</v>
+        <v>50.64</v>
       </c>
       <c r="D56" s="7">
-        <v>50.8</v>
+        <v>48.74</v>
       </c>
       <c r="E56" s="8">
-        <v>0.14</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>11.22</v>
+        <v>50.8</v>
       </c>
       <c r="D57" s="7">
-        <v>9.77</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-1.45</v>
+        <v>49.01</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>4.64</v>
+        <v>9.77</v>
       </c>
       <c r="D58" s="7">
-        <v>4.46</v>
+        <v>11.12</v>
       </c>
       <c r="E58" s="9">
-        <v>-0.18</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>-5.9</v>
+        <v>4.46</v>
       </c>
       <c r="D59" s="7">
-        <v>-8.279999999999999</v>
+        <v>5.64</v>
       </c>
       <c r="E59" s="9">
-        <v>-2.38</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>-6.3</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D60" s="7">
-        <v>-8.65</v>
+        <v>-7.41</v>
       </c>
       <c r="E60" s="9">
-        <v>-2.35</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>13.59</v>
+        <v>-8.65</v>
       </c>
       <c r="D61" s="7">
-        <v>13.13</v>
+        <v>-7.5</v>
       </c>
       <c r="E61" s="9">
-        <v>-0.46</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>0.66</v>
+        <v>13.13</v>
       </c>
       <c r="D62" s="7">
-        <v>0.37</v>
+        <v>14.71</v>
       </c>
       <c r="E62" s="9">
-        <v>-0.29</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>0.79</v>
+        <v>0.37</v>
       </c>
       <c r="D63" s="7">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
       <c r="E63" s="9">
-        <v>-0.35</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="D64" s="7">
-        <v>0.26</v>
+        <v>1.13</v>
       </c>
       <c r="E64" s="9">
-        <v>-0.36</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>25.73</v>
+        <v>0.26</v>
       </c>
       <c r="D65" s="7">
-        <v>27.76</v>
-      </c>
-      <c r="E65" s="8">
-        <v>2.03</v>
+        <v>1.05</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0.79</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>2.72</v>
+        <v>27.76</v>
       </c>
       <c r="D66" s="7">
-        <v>2.2</v>
+        <v>27.83</v>
       </c>
       <c r="E66" s="9">
-        <v>-0.52</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>103.68</v>
+        <v>2.2</v>
       </c>
       <c r="D67" s="7">
-        <v>103.99</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.31</v>
+        <v>3.24</v>
+      </c>
+      <c r="E67" s="9">
+        <v>1.04</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>0.63</v>
+        <v>103.99</v>
       </c>
       <c r="D68" s="7">
-        <v>0.29</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-0.34</v>
+        <v>99.04000000000001</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-4.95</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>13.62</v>
+        <v>0.29</v>
       </c>
       <c r="D69" s="7">
-        <v>13.45</v>
+        <v>1.1</v>
       </c>
       <c r="E69" s="9">
-        <v>-0.17</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>6.48</v>
+        <v>13.45</v>
       </c>
       <c r="D70" s="7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E70" s="8">
-        <v>1.72</v>
+        <v>14.82</v>
+      </c>
+      <c r="E70" s="9">
+        <v>1.37</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>6.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D71" s="7">
-        <v>8.050000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="E71" s="8">
-        <v>1.57</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>-11.56</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="D72" s="7">
-        <v>-11.36</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.2</v>
+        <v>8.18</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0.13</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>-2.99</v>
+        <v>-11.36</v>
       </c>
       <c r="D73" s="7">
-        <v>-4.53</v>
+        <v>-9.85</v>
       </c>
       <c r="E73" s="9">
-        <v>-1.54</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="7">
-        <v>-4.75</v>
+        <v>-4.53</v>
       </c>
       <c r="D74" s="7">
-        <v>-2.29</v>
-      </c>
-      <c r="E74" s="8">
-        <v>2.46</v>
+        <v>-3.9</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0.63</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>-4.67</v>
+        <v>-2.29</v>
       </c>
       <c r="D75" s="7">
-        <v>-2.38</v>
+        <v>-3.25</v>
       </c>
       <c r="E75" s="8">
-        <v>2.29</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>-12.87</v>
+        <v>-2.38</v>
       </c>
       <c r="D76" s="7">
-        <v>-10.61</v>
+        <v>-3.25</v>
       </c>
       <c r="E76" s="8">
-        <v>2.26</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>0.6899999999999999</v>
+        <v>-10.61</v>
       </c>
       <c r="D77" s="7">
-        <v>0.62</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-0.07000000000000001</v>
+        <v>-10.71</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>16.51</v>
+        <v>0.62</v>
       </c>
       <c r="D78" s="7">
-        <v>12.79</v>
+        <v>1.2</v>
       </c>
       <c r="E78" s="9">
-        <v>-3.72</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>16.3</v>
+        <v>12.79</v>
       </c>
       <c r="D79" s="7">
-        <v>12.94</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-3.36</v>
+        <v>10.95</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>7.24</v>
+        <v>12.94</v>
       </c>
       <c r="D80" s="7">
-        <v>7.82</v>
+        <v>10.87</v>
       </c>
       <c r="E80" s="8">
-        <v>0.58</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>4</v>
+        <v>7.82</v>
       </c>
       <c r="D81" s="7">
-        <v>3.83</v>
+        <v>9.06</v>
       </c>
       <c r="E81" s="9">
-        <v>-0.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
@@ -4682,911 +4695,911 @@
         <v>4.12</v>
       </c>
       <c r="D82" s="7">
-        <v>4.1</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-0.02</v>
+        <v>3.95</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>3.98</v>
+        <v>3.83</v>
       </c>
       <c r="D83" s="7">
-        <v>3.95</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-0.03</v>
+        <v>3.76</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>6.12</v>
+        <v>4.1</v>
       </c>
       <c r="D84" s="7">
-        <v>9.26</v>
+        <v>3.89</v>
       </c>
       <c r="E84" s="8">
-        <v>3.14</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>5.07</v>
+        <v>3.95</v>
       </c>
       <c r="D85" s="7">
-        <v>5.44</v>
-      </c>
-      <c r="E85" s="8">
-        <v>0.37</v>
+        <v>3.97</v>
+      </c>
+      <c r="E85" s="9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="7">
-        <v>-17.7</v>
+        <v>9.26</v>
       </c>
       <c r="D86" s="7">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E86" s="8">
-        <v>8.49</v>
+        <v>11.22</v>
+      </c>
+      <c r="E86" s="9">
+        <v>1.96</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="7">
-        <v>4.07</v>
+        <v>5.44</v>
       </c>
       <c r="D87" s="7">
-        <v>3.89</v>
-      </c>
-      <c r="E87" s="9">
-        <v>-0.18</v>
+        <v>5.02</v>
+      </c>
+      <c r="E87" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="7">
-        <v>7.43</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="D88" s="7">
-        <v>8.07</v>
+        <v>-12.61</v>
       </c>
       <c r="E88" s="8">
-        <v>0.64</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89" s="7">
-        <v>-6.45</v>
+        <v>3.89</v>
       </c>
       <c r="D89" s="7">
-        <v>-5.8</v>
+        <v>3.76</v>
       </c>
       <c r="E89" s="8">
-        <v>0.65</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90" s="7">
-        <v>-90.63</v>
+        <v>8.07</v>
       </c>
       <c r="D90" s="7">
-        <v>-90.56</v>
-      </c>
-      <c r="E90" s="8">
-        <v>0.07000000000000001</v>
+        <v>9.25</v>
+      </c>
+      <c r="E90" s="9">
+        <v>1.18</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="7">
-        <v>-13.76</v>
+        <v>-5.8</v>
       </c>
       <c r="D91" s="7">
-        <v>-13.74</v>
+        <v>-5.96</v>
       </c>
       <c r="E91" s="8">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="7">
-        <v>-13.84</v>
+        <v>-90.56</v>
       </c>
       <c r="D92" s="7">
-        <v>-14.69</v>
-      </c>
-      <c r="E92" s="9">
-        <v>-0.85</v>
+        <v>-90.59999999999999</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="7">
-        <v>-14.34</v>
+        <v>-13.74</v>
       </c>
       <c r="D93" s="7">
-        <v>-13.7</v>
-      </c>
-      <c r="E93" s="8">
-        <v>0.64</v>
+        <v>-13.27</v>
+      </c>
+      <c r="E93" s="9">
+        <v>0.47</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="7">
-        <v>-14.31</v>
+        <v>-14.69</v>
       </c>
       <c r="D94" s="7">
-        <v>-13.72</v>
-      </c>
-      <c r="E94" s="8">
-        <v>0.59</v>
+        <v>-14.05</v>
+      </c>
+      <c r="E94" s="9">
+        <v>0.64</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-14.46</v>
+        <v>-13.7</v>
       </c>
       <c r="D95" s="7">
-        <v>-15.19</v>
-      </c>
-      <c r="E95" s="9">
-        <v>-0.73</v>
+        <v>-14.37</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-3.55</v>
+        <v>-13.72</v>
       </c>
       <c r="D96" s="7">
-        <v>-3.98</v>
-      </c>
-      <c r="E96" s="9">
-        <v>-0.43</v>
+        <v>-14.35</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-18.42</v>
+        <v>-15.19</v>
       </c>
       <c r="D97" s="7">
-        <v>-19.71</v>
-      </c>
-      <c r="E97" s="9">
-        <v>-1.29</v>
+        <v>-15.24</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-18.6</v>
+        <v>-3.98</v>
       </c>
       <c r="D98" s="7">
-        <v>-19.96</v>
-      </c>
-      <c r="E98" s="9">
-        <v>-1.36</v>
+        <v>-4.03</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-0.16</v>
+        <v>-19.71</v>
       </c>
       <c r="D99" s="7">
-        <v>-0.33</v>
+        <v>-19.53</v>
       </c>
       <c r="E99" s="9">
-        <v>-0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-6.19</v>
+        <v>-19.96</v>
       </c>
       <c r="D100" s="7">
-        <v>-6.46</v>
+        <v>-19.68</v>
       </c>
       <c r="E100" s="9">
-        <v>-0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-6.18</v>
+        <v>-0.33</v>
       </c>
       <c r="D101" s="7">
-        <v>-6.55</v>
+        <v>-0.16</v>
       </c>
       <c r="E101" s="9">
-        <v>-0.37</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-6.24</v>
+        <v>-6.46</v>
       </c>
       <c r="D102" s="7">
-        <v>-6.59</v>
-      </c>
-      <c r="E102" s="9">
-        <v>-0.35</v>
+        <v>-6.52</v>
+      </c>
+      <c r="E102" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-6.19</v>
+        <v>-6.55</v>
       </c>
       <c r="D103" s="7">
-        <v>-6.48</v>
+        <v>-6.52</v>
       </c>
       <c r="E103" s="9">
-        <v>-0.29</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-12.21</v>
+        <v>-6.59</v>
       </c>
       <c r="D104" s="7">
-        <v>-10.56</v>
+        <v>-6.68</v>
       </c>
       <c r="E104" s="8">
-        <v>1.65</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="7">
-        <v>-5.51</v>
+        <v>-6.48</v>
       </c>
       <c r="D105" s="7">
-        <v>-5.57</v>
-      </c>
-      <c r="E105" s="9">
-        <v>-0.06</v>
+        <v>-6.49</v>
+      </c>
+      <c r="E105" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="7">
-        <v>-36.39</v>
+        <v>-10.56</v>
       </c>
       <c r="D106" s="7">
-        <v>-35.41</v>
+        <v>-10.7</v>
       </c>
       <c r="E106" s="8">
-        <v>0.98</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="7">
-        <v>-6.2</v>
+        <v>-5.57</v>
       </c>
       <c r="D107" s="7">
-        <v>-6.48</v>
-      </c>
-      <c r="E107" s="9">
-        <v>-0.28</v>
+        <v>-5.81</v>
+      </c>
+      <c r="E107" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C108" s="7">
-        <v>-0.3</v>
+        <v>-35.41</v>
       </c>
       <c r="D108" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="E108" s="9">
-        <v>-0.15</v>
+        <v>-36.83</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C109" s="7">
-        <v>594.87</v>
+        <v>-6.48</v>
       </c>
       <c r="D109" s="7">
-        <v>599.01</v>
+        <v>-6.53</v>
       </c>
       <c r="E109" s="8">
-        <v>4.14</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C110" s="7">
-        <v>59.69</v>
+        <v>-0.45</v>
       </c>
       <c r="D110" s="7">
-        <v>60.15</v>
-      </c>
-      <c r="E110" s="8">
-        <v>0.46</v>
+        <v>-0.26</v>
+      </c>
+      <c r="E110" s="9">
+        <v>0.19</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C111" s="7">
-        <v>93.84</v>
+        <v>599.01</v>
       </c>
       <c r="D111" s="7">
-        <v>93.86</v>
+        <v>597.97</v>
       </c>
       <c r="E111" s="8">
-        <v>0.02</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="7">
-        <v>52.56</v>
+        <v>60.15</v>
       </c>
       <c r="D112" s="7">
-        <v>52.04</v>
-      </c>
-      <c r="E112" s="9">
-        <v>-0.52</v>
+        <v>59.89</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="7">
-        <v>125.52</v>
+        <v>93.86</v>
       </c>
       <c r="D113" s="7">
-        <v>126.45</v>
-      </c>
-      <c r="E113" s="8">
-        <v>0.93</v>
+        <v>94.37</v>
+      </c>
+      <c r="E113" s="9">
+        <v>0.51</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="7">
-        <v>129.72</v>
+        <v>52.04</v>
       </c>
       <c r="D114" s="7">
-        <v>130.61</v>
-      </c>
-      <c r="E114" s="8">
-        <v>0.89</v>
+        <v>52.43</v>
+      </c>
+      <c r="E114" s="9">
+        <v>0.39</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>484.47</v>
+        <v>126.45</v>
       </c>
       <c r="D115" s="7">
-        <v>480.32</v>
-      </c>
-      <c r="E115" s="9">
-        <v>-4.15</v>
+        <v>125.48</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>973.02</v>
+        <v>130.61</v>
       </c>
       <c r="D116" s="7">
-        <v>968.74</v>
-      </c>
-      <c r="E116" s="9">
-        <v>-4.28</v>
+        <v>129.65</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>35.22</v>
+        <v>480.32</v>
       </c>
       <c r="D117" s="7">
-        <v>34.66</v>
-      </c>
-      <c r="E117" s="9">
-        <v>-0.5600000000000001</v>
+        <v>480.01</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>35.24</v>
+        <v>968.74</v>
       </c>
       <c r="D118" s="7">
-        <v>34.65</v>
-      </c>
-      <c r="E118" s="9">
-        <v>-0.59</v>
+        <v>968.22</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>807.7</v>
+        <v>34.66</v>
       </c>
       <c r="D119" s="7">
-        <v>806.3099999999999</v>
+        <v>34.74</v>
       </c>
       <c r="E119" s="9">
-        <v>-1.39</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>279.13</v>
+        <v>34.65</v>
       </c>
       <c r="D120" s="7">
-        <v>278.32</v>
+        <v>34.77</v>
       </c>
       <c r="E120" s="9">
-        <v>-0.8100000000000001</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>271.72</v>
+        <v>806.3099999999999</v>
       </c>
       <c r="D121" s="7">
-        <v>270.65</v>
+        <v>807.6900000000001</v>
       </c>
       <c r="E121" s="9">
-        <v>-1.07</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>266.57</v>
+        <v>278.32</v>
       </c>
       <c r="D122" s="7">
-        <v>265.57</v>
-      </c>
-      <c r="E122" s="9">
-        <v>-1</v>
+        <v>278.16</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>277.66</v>
+        <v>270.65</v>
       </c>
       <c r="D123" s="7">
-        <v>276.8</v>
+        <v>270.72</v>
       </c>
       <c r="E123" s="9">
-        <v>-0.86</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>96.45</v>
+        <v>265.57</v>
       </c>
       <c r="D124" s="7">
-        <v>98.27</v>
+        <v>265.33</v>
       </c>
       <c r="E124" s="8">
-        <v>1.82</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="7">
-        <v>280.2</v>
+        <v>276.8</v>
       </c>
       <c r="D125" s="7">
-        <v>280.02</v>
-      </c>
-      <c r="E125" s="9">
-        <v>-0.18</v>
+        <v>276.76</v>
+      </c>
+      <c r="E125" s="8">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="7">
-        <v>227.88</v>
+        <v>98.27</v>
       </c>
       <c r="D126" s="7">
-        <v>231.39</v>
+        <v>98.11</v>
       </c>
       <c r="E126" s="8">
-        <v>3.51</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C127" s="7">
-        <v>263.77</v>
+        <v>280.02</v>
       </c>
       <c r="D127" s="7">
-        <v>262.98</v>
-      </c>
-      <c r="E127" s="9">
-        <v>-0.79</v>
+        <v>279.31</v>
+      </c>
+      <c r="E127" s="8">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C128" s="7">
-        <v>800.85</v>
+        <v>231.39</v>
       </c>
       <c r="D128" s="7">
-        <v>799.62</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-1.23</v>
+        <v>226.31</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-5.08</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C129" s="7">
-        <v>58</v>
+        <v>262.98</v>
       </c>
       <c r="D129" s="7">
-        <v>68</v>
+        <v>262.84</v>
       </c>
       <c r="E129" s="8">
-        <v>10</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C130" s="7">
-        <v>42</v>
+        <v>799.62</v>
       </c>
       <c r="D130" s="7">
-        <v>37</v>
+        <v>801.14</v>
       </c>
       <c r="E130" s="9">
-        <v>-5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C131" s="7">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="D131" s="7">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E131" s="9">
-        <v>-5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="7">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D132" s="7">
-        <v>58</v>
-      </c>
-      <c r="E132" s="9">
+        <v>42</v>
+      </c>
+      <c r="E132" s="8">
         <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C133" s="7">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D133" s="7">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E133" s="8">
-        <v>10</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="7">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D134" s="7">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E134" s="9">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="7">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D135" s="7">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E135" s="8">
-        <v>5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -5597,13 +5610,13 @@
         <v>13</v>
       </c>
       <c r="C136" s="7">
+        <v>27</v>
+      </c>
+      <c r="D136" s="7">
         <v>32</v>
       </c>
-      <c r="D136" s="7">
-        <v>27</v>
-      </c>
       <c r="E136" s="9">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -5614,13 +5627,13 @@
         <v>24</v>
       </c>
       <c r="C137" s="7">
-        <v>50.81</v>
+        <v>55.41</v>
       </c>
       <c r="D137" s="7">
-        <v>55.41</v>
+        <v>54.04</v>
       </c>
       <c r="E137" s="8">
-        <v>4.6</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -5631,13 +5644,13 @@
         <v>24</v>
       </c>
       <c r="C138" s="7">
-        <v>49.38</v>
+        <v>54.1</v>
       </c>
       <c r="D138" s="7">
-        <v>54.1</v>
+        <v>51.2</v>
       </c>
       <c r="E138" s="8">
-        <v>4.72</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -5648,13 +5661,13 @@
         <v>24</v>
       </c>
       <c r="C139" s="7">
-        <v>32.33</v>
+        <v>32.61</v>
       </c>
       <c r="D139" s="7">
-        <v>32.61</v>
-      </c>
-      <c r="E139" s="8">
-        <v>0.28</v>
+        <v>39.35</v>
+      </c>
+      <c r="E139" s="9">
+        <v>6.74</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -5665,13 +5678,13 @@
         <v>24</v>
       </c>
       <c r="C140" s="7">
-        <v>45.7</v>
+        <v>39.96</v>
       </c>
       <c r="D140" s="7">
-        <v>39.96</v>
+        <v>45.49</v>
       </c>
       <c r="E140" s="9">
-        <v>-5.74</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -5682,13 +5695,13 @@
         <v>24</v>
       </c>
       <c r="C141" s="7">
-        <v>71.14</v>
+        <v>72.97</v>
       </c>
       <c r="D141" s="7">
-        <v>72.97</v>
+        <v>68.12</v>
       </c>
       <c r="E141" s="8">
-        <v>1.83</v>
+        <v>-4.85</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -5699,13 +5712,13 @@
         <v>24</v>
       </c>
       <c r="C142" s="7">
-        <v>71.36</v>
+        <v>73.06</v>
       </c>
       <c r="D142" s="7">
-        <v>73.06</v>
+        <v>68.34</v>
       </c>
       <c r="E142" s="8">
-        <v>1.7</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -5716,13 +5729,13 @@
         <v>24</v>
       </c>
       <c r="C143" s="7">
-        <v>46.33</v>
+        <v>42.28</v>
       </c>
       <c r="D143" s="7">
-        <v>42.28</v>
-      </c>
-      <c r="E143" s="9">
-        <v>-4.05</v>
+        <v>41.98</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -5733,13 +5746,13 @@
         <v>24</v>
       </c>
       <c r="C144" s="7">
-        <v>52.17</v>
+        <v>48.68</v>
       </c>
       <c r="D144" s="7">
-        <v>48.68</v>
-      </c>
-      <c r="E144" s="9">
-        <v>-3.49</v>
+        <v>48.26</v>
+      </c>
+      <c r="E144" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -5750,13 +5763,13 @@
         <v>24</v>
       </c>
       <c r="C145" s="7">
-        <v>69.15000000000001</v>
+        <v>62.22</v>
       </c>
       <c r="D145" s="7">
-        <v>62.22</v>
+        <v>62.8</v>
       </c>
       <c r="E145" s="9">
-        <v>-6.93</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -5767,13 +5780,13 @@
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>69.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="D146" s="7">
-        <v>62.05</v>
+        <v>62.92</v>
       </c>
       <c r="E146" s="9">
-        <v>-7.41</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -5784,13 +5797,13 @@
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>69.43000000000001</v>
+        <v>67.39</v>
       </c>
       <c r="D147" s="7">
-        <v>67.39</v>
+        <v>68.38</v>
       </c>
       <c r="E147" s="9">
-        <v>-2.04</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -5801,13 +5814,13 @@
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>59.13</v>
+        <v>56.25</v>
       </c>
       <c r="D148" s="7">
-        <v>56.25</v>
-      </c>
-      <c r="E148" s="9">
-        <v>-2.88</v>
+        <v>55.68</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -5818,13 +5831,13 @@
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>60.13</v>
+        <v>55.96</v>
       </c>
       <c r="D149" s="7">
-        <v>55.96</v>
+        <v>56.17</v>
       </c>
       <c r="E149" s="9">
-        <v>-4.17</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -5835,13 +5848,13 @@
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>58.11</v>
+        <v>54.73</v>
       </c>
       <c r="D150" s="7">
-        <v>54.73</v>
-      </c>
-      <c r="E150" s="9">
-        <v>-3.38</v>
+        <v>53.92</v>
+      </c>
+      <c r="E150" s="8">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -5852,13 +5865,13 @@
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>58.59</v>
+        <v>55.66</v>
       </c>
       <c r="D151" s="7">
-        <v>55.66</v>
-      </c>
-      <c r="E151" s="9">
-        <v>-2.93</v>
+        <v>55.52</v>
+      </c>
+      <c r="E151" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -5869,13 +5882,13 @@
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>57.62</v>
+        <v>63.62</v>
       </c>
       <c r="D152" s="7">
-        <v>63.62</v>
+        <v>62.78</v>
       </c>
       <c r="E152" s="8">
-        <v>6</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -5886,13 +5899,13 @@
         <v>24</v>
       </c>
       <c r="C153" s="7">
-        <v>45.13</v>
+        <v>44.77</v>
       </c>
       <c r="D153" s="7">
-        <v>44.77</v>
-      </c>
-      <c r="E153" s="9">
-        <v>-0.36</v>
+        <v>43.32</v>
+      </c>
+      <c r="E153" s="8">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -5903,13 +5916,13 @@
         <v>24</v>
       </c>
       <c r="C154" s="7">
-        <v>63.09</v>
+        <v>66.67</v>
       </c>
       <c r="D154" s="7">
-        <v>66.67</v>
+        <v>57.92</v>
       </c>
       <c r="E154" s="8">
-        <v>3.58</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -5920,13 +5933,13 @@
         <v>24</v>
       </c>
       <c r="C155" s="7">
-        <v>58.98</v>
+        <v>56.02</v>
       </c>
       <c r="D155" s="7">
-        <v>56.02</v>
-      </c>
-      <c r="E155" s="9">
-        <v>-2.96</v>
+        <v>55.49</v>
+      </c>
+      <c r="E155" s="8">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -5937,13 +5950,13 @@
         <v>24</v>
       </c>
       <c r="C156" s="7">
-        <v>65.42</v>
+        <v>64.09</v>
       </c>
       <c r="D156" s="7">
-        <v>64.09</v>
+        <v>65.03</v>
       </c>
       <c r="E156" s="9">
-        <v>-1.33</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -5954,13 +5967,13 @@
         <v>31</v>
       </c>
       <c r="C157" s="7">
-        <v>-38.35</v>
+        <v>-4.18</v>
       </c>
       <c r="D157" s="7">
-        <v>-4.18</v>
+        <v>-55.8</v>
       </c>
       <c r="E157" s="8">
-        <v>34.17</v>
+        <v>-51.62</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -5971,13 +5984,13 @@
         <v>31</v>
       </c>
       <c r="C158" s="7">
-        <v>-69.09</v>
+        <v>-69.83</v>
       </c>
       <c r="D158" s="7">
-        <v>-69.83</v>
-      </c>
-      <c r="E158" s="9">
-        <v>-0.74</v>
+        <v>-79.16</v>
+      </c>
+      <c r="E158" s="8">
+        <v>-9.33</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -5988,13 +6001,13 @@
         <v>31</v>
       </c>
       <c r="C159" s="7">
-        <v>33.36</v>
+        <v>20</v>
       </c>
       <c r="D159" s="7">
-        <v>20</v>
-      </c>
-      <c r="E159" s="9">
-        <v>-13.36</v>
+        <v>-26.57</v>
+      </c>
+      <c r="E159" s="8">
+        <v>-46.57</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6005,13 +6018,13 @@
         <v>31</v>
       </c>
       <c r="C160" s="7">
-        <v>-10.79</v>
+        <v>114.41</v>
       </c>
       <c r="D160" s="7">
-        <v>114.41</v>
+        <v>-39.71</v>
       </c>
       <c r="E160" s="8">
-        <v>125.2</v>
+        <v>-154.12</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -6022,13 +6035,13 @@
         <v>31</v>
       </c>
       <c r="C161" s="7">
-        <v>52.18</v>
+        <v>-9.75</v>
       </c>
       <c r="D161" s="7">
-        <v>-9.75</v>
+        <v>22.18</v>
       </c>
       <c r="E161" s="9">
-        <v>-61.93</v>
+        <v>31.93</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6039,13 +6052,13 @@
         <v>31</v>
       </c>
       <c r="C162" s="7">
-        <v>29.91</v>
+        <v>35.22</v>
       </c>
       <c r="D162" s="7">
-        <v>35.22</v>
+        <v>-33.8</v>
       </c>
       <c r="E162" s="8">
-        <v>5.31</v>
+        <v>-69.02</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -6056,13 +6069,13 @@
         <v>31</v>
       </c>
       <c r="C163" s="7">
-        <v>9.49</v>
+        <v>2.54</v>
       </c>
       <c r="D163" s="7">
-        <v>2.54</v>
-      </c>
-      <c r="E163" s="9">
-        <v>-6.95</v>
+        <v>-17.51</v>
+      </c>
+      <c r="E163" s="8">
+        <v>-20.05</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6073,13 +6086,13 @@
         <v>31</v>
       </c>
       <c r="C164" s="7">
-        <v>58.52</v>
+        <v>35.3</v>
       </c>
       <c r="D164" s="7">
-        <v>35.3</v>
-      </c>
-      <c r="E164" s="9">
-        <v>-23.22</v>
+        <v>-62.43</v>
+      </c>
+      <c r="E164" s="8">
+        <v>-97.73</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -6090,13 +6103,13 @@
         <v>31</v>
       </c>
       <c r="C165" s="7">
-        <v>-54</v>
+        <v>-62.52</v>
       </c>
       <c r="D165" s="7">
-        <v>-62.52</v>
-      </c>
-      <c r="E165" s="9">
-        <v>-8.52</v>
+        <v>-63.46</v>
+      </c>
+      <c r="E165" s="8">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -6107,13 +6120,13 @@
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>-58.62</v>
+        <v>-30.3</v>
       </c>
       <c r="D166" s="7">
-        <v>-30.3</v>
+        <v>-64.38</v>
       </c>
       <c r="E166" s="8">
-        <v>28.32</v>
+        <v>-34.08</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -6124,13 +6137,13 @@
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>-5.97</v>
+        <v>-20.85</v>
       </c>
       <c r="D167" s="7">
-        <v>-20.85</v>
-      </c>
-      <c r="E167" s="9">
-        <v>-14.88</v>
+        <v>-32.96</v>
+      </c>
+      <c r="E167" s="8">
+        <v>-12.11</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -6141,13 +6154,13 @@
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>19.3</v>
+        <v>2.49</v>
       </c>
       <c r="D168" s="7">
-        <v>2.49</v>
-      </c>
-      <c r="E168" s="9">
-        <v>-16.81</v>
+        <v>-33.99</v>
+      </c>
+      <c r="E168" s="8">
+        <v>-36.48</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -6158,13 +6171,13 @@
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>-49.64</v>
+        <v>-27.98</v>
       </c>
       <c r="D169" s="7">
-        <v>-27.98</v>
-      </c>
-      <c r="E169" s="8">
-        <v>21.66</v>
+        <v>151.83</v>
+      </c>
+      <c r="E169" s="9">
+        <v>179.81</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -6175,13 +6188,13 @@
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>-55.29</v>
+        <v>-27.27</v>
       </c>
       <c r="D170" s="7">
-        <v>-27.27</v>
+        <v>-35.95</v>
       </c>
       <c r="E170" s="8">
-        <v>28.02</v>
+        <v>-8.68</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -6192,13 +6205,13 @@
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-65.63</v>
+        <v>-24.28</v>
       </c>
       <c r="D171" s="7">
-        <v>-24.28</v>
-      </c>
-      <c r="E171" s="8">
-        <v>41.35</v>
+        <v>-17.38</v>
+      </c>
+      <c r="E171" s="9">
+        <v>6.9</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -6209,13 +6222,13 @@
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>-43.46</v>
+        <v>42.18</v>
       </c>
       <c r="D172" s="7">
-        <v>42.18</v>
+        <v>-42.57</v>
       </c>
       <c r="E172" s="8">
-        <v>85.64</v>
+        <v>-84.75</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -6226,13 +6239,13 @@
         <v>31</v>
       </c>
       <c r="C173" s="7">
-        <v>324.83</v>
+        <v>-89.36</v>
       </c>
       <c r="D173" s="7">
-        <v>-89.36</v>
-      </c>
-      <c r="E173" s="9">
-        <v>-414.19</v>
+        <v>-90.04000000000001</v>
+      </c>
+      <c r="E173" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -6243,13 +6256,13 @@
         <v>31</v>
       </c>
       <c r="C174" s="7">
-        <v>5.91</v>
+        <v>50</v>
       </c>
       <c r="D174" s="7">
-        <v>50</v>
+        <v>14.35</v>
       </c>
       <c r="E174" s="8">
-        <v>44.09</v>
+        <v>-35.65</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -6260,13 +6273,13 @@
         <v>31</v>
       </c>
       <c r="C175" s="7">
-        <v>-45.7</v>
+        <v>1.4</v>
       </c>
       <c r="D175" s="7">
-        <v>1.4</v>
+        <v>-33.5</v>
       </c>
       <c r="E175" s="8">
-        <v>47.1</v>
+        <v>-34.9</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -6277,19 +6290,19 @@
         <v>31</v>
       </c>
       <c r="C176" s="7">
-        <v>-29.14</v>
+        <v>-6.24</v>
       </c>
       <c r="D176" s="7">
-        <v>-6.24</v>
+        <v>-52.76</v>
       </c>
       <c r="E176" s="8">
-        <v>22.9</v>
+        <v>-46.52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6313,28 +6326,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6348,16 +6361,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>56.4</v>
+        <v>55.8</v>
       </c>
       <c r="E2" s="12">
         <v>40</v>
       </c>
       <c r="F2" s="12">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G2" s="12">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H2" s="12">
         <v>52.6</v>
@@ -6497,42 +6510,42 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5569</v>
+        <v>0.5396</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3342</v>
+        <v>0.3308</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3048</v>
+        <v>0.304</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2906</v>
+        <v>0.2932</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2554</v>
+        <v>0.2538</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1569</v>
+        <v>0.1549</v>
       </c>
       <c r="G2" s="15">
+        <v>0.1434</v>
+      </c>
+      <c r="H2" s="15">
         <v>0.1432</v>
       </c>
-      <c r="H2" s="15">
-        <v>0.1429</v>
-      </c>
       <c r="I2" s="15">
-        <v>0.106</v>
+        <v>0.1045</v>
       </c>
       <c r="J2" s="15">
-        <v>0.096</v>
+        <v>0.09380000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>50</v>
@@ -6561,34 +6574,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0958</v>
+        <v>0.0935</v>
       </c>
       <c r="B4" s="15">
-        <v>0.0956</v>
+        <v>0.0935</v>
       </c>
       <c r="C4" s="15">
-        <v>0.0953</v>
+        <v>0.0931</v>
       </c>
       <c r="D4" s="15">
-        <v>0.0852</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="E4" s="15">
-        <v>0.0776</v>
+        <v>0.077</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0725</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="G4" s="15">
-        <v>0.0136</v>
+        <v>0.0117</v>
       </c>
       <c r="H4" s="15">
-        <v>0.0115</v>
+        <v>0.0086</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.08439999999999999</v>
+        <v>-0.0837</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.3021</v>
+        <v>-0.3034</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="95">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,37 +226,46 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
     <t>No → Yes</t>
   </si>
   <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>73.0 → 68.1</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>73.0</t>
-  </si>
-  <si>
-    <t>68.1</t>
-  </si>
-  <si>
-    <t>73.1 → 68.3</t>
-  </si>
-  <si>
-    <t>73.1</t>
-  </si>
-  <si>
-    <t>68.3</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.3 → 55.3</t>
+  </si>
+  <si>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>55.3</t>
+  </si>
+  <si>
+    <t>51.2 → 49.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -308,7 +317,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,20 +358,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,12 +392,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,12 +478,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -496,7 +492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -995,10 +991,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>597.97</v>
+        <v>596.37</v>
       </c>
       <c r="D2">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1007,85 +1003,85 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-5.96</v>
+        <v>-6.21</v>
       </c>
       <c r="H2">
-        <v>14.8</v>
+        <v>14.49</v>
       </c>
       <c r="I2">
-        <v>-0.36</v>
+        <v>-0.4</v>
       </c>
       <c r="J2">
-        <v>0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="K2">
-        <v>8.06</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>5.35</v>
+        <v>4.28</v>
       </c>
       <c r="M2">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>597.48</v>
+        <v>597</v>
       </c>
       <c r="Q2">
-        <v>595.12</v>
+        <v>594.6900000000001</v>
       </c>
       <c r="R2">
-        <v>592.78</v>
+        <v>593.45</v>
       </c>
       <c r="S2">
-        <v>593.15</v>
+        <v>593.13</v>
       </c>
       <c r="T2">
-        <v>0.8100000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
-        <v>54.04</v>
+        <v>51.92</v>
       </c>
       <c r="Z2">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AA2">
         <v>1.36</v>
       </c>
       <c r="AB2">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="AC2">
+        <v>70.03</v>
+      </c>
+      <c r="AD2">
         <v>68.59999999999999</v>
       </c>
-      <c r="AD2">
-        <v>68</v>
-      </c>
       <c r="AE2">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
       <c r="AF2">
-        <v>-55.8</v>
+        <v>-54.87</v>
       </c>
       <c r="AG2">
-        <v>604.88</v>
+        <v>603.34</v>
       </c>
       <c r="AH2">
-        <v>585.36</v>
+        <v>586.05</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1094,7 +1090,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>13.14</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1105,10 +1101,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>59.89</v>
+        <v>59.77</v>
       </c>
       <c r="D3">
-        <v>-0.43</v>
+        <v>-0.2</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1117,43 +1113,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.59999999999999</v>
+        <v>-90.62</v>
       </c>
       <c r="H3">
-        <v>14.91</v>
+        <v>14.68</v>
       </c>
       <c r="I3">
-        <v>-0.76</v>
+        <v>-0.58</v>
       </c>
       <c r="J3">
-        <v>-0.23</v>
+        <v>-0.13</v>
       </c>
       <c r="K3">
-        <v>8.18</v>
+        <v>7.89</v>
       </c>
       <c r="L3">
-        <v>-89.43000000000001</v>
+        <v>-89.58</v>
       </c>
       <c r="M3">
-        <v>-30.34</v>
+        <v>-30.36</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.97</v>
+        <v>59.9</v>
       </c>
       <c r="Q3">
-        <v>59.69</v>
+        <v>59.65</v>
       </c>
       <c r="R3">
-        <v>59.45</v>
+        <v>59.52</v>
       </c>
       <c r="S3">
-        <v>294.58</v>
+        <v>291.87</v>
       </c>
       <c r="T3">
-        <v>-79.67</v>
+        <v>-79.52</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1168,34 +1164,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>51.2</v>
+        <v>49.87</v>
       </c>
       <c r="Z3">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA3">
         <v>0.04</v>
       </c>
       <c r="AB3">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AC3">
-        <v>63.76</v>
+        <v>61.89</v>
       </c>
       <c r="AD3">
-        <v>67.63</v>
+        <v>64.98</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>-79.16</v>
+        <v>-86.98</v>
       </c>
       <c r="AG3">
-        <v>60.73</v>
+        <v>60.57</v>
       </c>
       <c r="AH3">
-        <v>58.66</v>
+        <v>58.73</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1204,7 +1200,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>19.62</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1215,10 +1211,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>94.37</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="D4">
-        <v>0.54</v>
+        <v>-0.55</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1227,43 +1223,43 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-13.27</v>
+        <v>-13.75</v>
       </c>
       <c r="H4">
-        <v>7.45</v>
+        <v>6.85</v>
       </c>
       <c r="I4">
-        <v>0.17</v>
+        <v>-0.45</v>
       </c>
       <c r="J4">
-        <v>-1.61</v>
+        <v>-1.76</v>
       </c>
       <c r="K4">
-        <v>-9.85</v>
+        <v>-10.52</v>
       </c>
       <c r="L4">
-        <v>5.08</v>
+        <v>4.25</v>
       </c>
       <c r="M4">
-        <v>29.32</v>
+        <v>29.38</v>
       </c>
       <c r="N4">
         <v>16</v>
       </c>
       <c r="P4">
-        <v>94.03</v>
+        <v>93.94</v>
       </c>
       <c r="Q4">
-        <v>95.06999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="R4">
-        <v>96.51000000000001</v>
+        <v>96.38</v>
       </c>
       <c r="S4">
         <v>97.94</v>
       </c>
       <c r="T4">
-        <v>-3.64</v>
+        <v>-4.18</v>
       </c>
       <c r="U4" t="s">
         <v>59</v>
@@ -1278,43 +1274,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.35</v>
+        <v>35.45</v>
       </c>
       <c r="Z4">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
       <c r="AA4">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="AB4">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AC4">
-        <v>48.22</v>
+        <v>62.07</v>
       </c>
       <c r="AD4">
-        <v>31.79</v>
+        <v>44.3</v>
       </c>
       <c r="AE4">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AF4">
-        <v>-26.57</v>
+        <v>-34.59</v>
       </c>
       <c r="AG4">
-        <v>97.26000000000001</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="AH4">
-        <v>92.88</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="AI4">
-        <v>100.34</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>11.08</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1325,10 +1321,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>52.43</v>
+        <v>52.36</v>
       </c>
       <c r="D5">
-        <v>0.75</v>
+        <v>-0.13</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1337,43 +1333,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-14.05</v>
+        <v>-14.16</v>
       </c>
       <c r="H5">
-        <v>7.73</v>
+        <v>7.58</v>
       </c>
       <c r="I5">
-        <v>-1.15</v>
+        <v>-1.19</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="K5">
-        <v>-3.9</v>
+        <v>-3.79</v>
       </c>
       <c r="L5">
-        <v>-10.45</v>
+        <v>-11.18</v>
       </c>
       <c r="M5">
-        <v>7.24</v>
+        <v>7.19</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>52.6</v>
+        <v>52.47</v>
       </c>
       <c r="Q5">
         <v>52.8</v>
       </c>
       <c r="R5">
-        <v>52.73</v>
+        <v>52.75</v>
       </c>
       <c r="S5">
-        <v>54.75</v>
+        <v>54.71</v>
       </c>
       <c r="T5">
-        <v>-4.23</v>
+        <v>-4.3</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1388,34 +1384,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>45.49</v>
+        <v>44.7</v>
       </c>
       <c r="Z5">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AA5">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AB5">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AC5">
-        <v>11.8</v>
+        <v>22.08</v>
       </c>
       <c r="AD5">
-        <v>21.63</v>
+        <v>17.13</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF5">
-        <v>-39.71</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AG5">
         <v>53.5</v>
       </c>
       <c r="AH5">
-        <v>52.09</v>
+        <v>52.1</v>
       </c>
       <c r="AI5">
         <v>54.72</v>
@@ -1424,7 +1420,7 @@
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>26.32</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1435,10 +1431,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>125.48</v>
+        <v>125.13</v>
       </c>
       <c r="D6">
-        <v>-0.77</v>
+        <v>-0.28</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1447,85 +1443,85 @@
         <v>82.08</v>
       </c>
       <c r="G6">
-        <v>-14.37</v>
+        <v>-14.6</v>
       </c>
       <c r="H6">
-        <v>52.88</v>
+        <v>52.45</v>
       </c>
       <c r="I6">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="J6">
-        <v>7.81</v>
+        <v>7.44</v>
       </c>
       <c r="K6">
-        <v>-3.25</v>
+        <v>-4.22</v>
       </c>
       <c r="L6">
-        <v>48.74</v>
+        <v>50.34</v>
       </c>
       <c r="M6">
-        <v>25.38</v>
+        <v>25.17</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>125.09</v>
+        <v>125.43</v>
       </c>
       <c r="Q6">
-        <v>119.73</v>
+        <v>120.2</v>
       </c>
       <c r="R6">
-        <v>119.53</v>
+        <v>119.47</v>
       </c>
       <c r="S6">
-        <v>119.47</v>
+        <v>119.61</v>
       </c>
       <c r="T6">
-        <v>5.03</v>
+        <v>4.62</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>68.12</v>
+        <v>66.41</v>
       </c>
       <c r="Z6">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA6">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="AB6">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="AC6">
-        <v>94.43000000000001</v>
+        <v>86.89</v>
       </c>
       <c r="AD6">
-        <v>98.14</v>
+        <v>93.77</v>
       </c>
       <c r="AE6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF6">
-        <v>22.18</v>
+        <v>3.61</v>
       </c>
       <c r="AG6">
-        <v>126.72</v>
+        <v>127.33</v>
       </c>
       <c r="AH6">
-        <v>112.74</v>
+        <v>113.07</v>
       </c>
       <c r="AI6">
         <v>120.92</v>
@@ -1534,7 +1530,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>40.98</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1545,10 +1541,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>129.65</v>
+        <v>129.33</v>
       </c>
       <c r="D7">
-        <v>-0.74</v>
+        <v>-0.25</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1557,85 +1553,85 @@
         <v>84.73999999999999</v>
       </c>
       <c r="G7">
-        <v>-14.35</v>
+        <v>-14.57</v>
       </c>
       <c r="H7">
-        <v>53</v>
+        <v>52.62</v>
       </c>
       <c r="I7">
-        <v>2.54</v>
+        <v>1.48</v>
       </c>
       <c r="J7">
-        <v>7.73</v>
+        <v>7.38</v>
       </c>
       <c r="K7">
-        <v>-3.25</v>
+        <v>-4.11</v>
       </c>
       <c r="L7">
-        <v>49.01</v>
+        <v>50.61</v>
       </c>
       <c r="M7">
-        <v>33.08</v>
+        <v>32.94</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>129.24</v>
+        <v>129.62</v>
       </c>
       <c r="Q7">
-        <v>123.73</v>
+        <v>124.21</v>
       </c>
       <c r="R7">
-        <v>123.55</v>
+        <v>123.5</v>
       </c>
       <c r="S7">
-        <v>123.41</v>
+        <v>123.56</v>
       </c>
       <c r="T7">
-        <v>5.06</v>
+        <v>4.67</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>68.34</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="Z7">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AA7">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="AB7">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AC7">
-        <v>94.62</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="AD7">
-        <v>98.20999999999999</v>
+        <v>94.03</v>
       </c>
       <c r="AE7">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="AF7">
-        <v>-33.8</v>
+        <v>-30.89</v>
       </c>
       <c r="AG7">
-        <v>130.9</v>
+        <v>131.54</v>
       </c>
       <c r="AH7">
-        <v>116.55</v>
+        <v>116.87</v>
       </c>
       <c r="AI7">
         <v>123.87</v>
@@ -1644,7 +1640,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>42.94</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1655,55 +1651,55 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>480.01</v>
+        <v>482.66</v>
       </c>
       <c r="D8">
-        <v>-0.06</v>
+        <v>0.55</v>
       </c>
       <c r="E8">
         <v>566.34</v>
       </c>
       <c r="F8">
-        <v>432.14</v>
+        <v>435.04</v>
       </c>
       <c r="G8">
-        <v>-15.24</v>
+        <v>-14.78</v>
       </c>
       <c r="H8">
-        <v>11.08</v>
+        <v>10.95</v>
       </c>
       <c r="I8">
-        <v>-1.43</v>
+        <v>-0.8</v>
       </c>
       <c r="J8">
         <v>-0.34</v>
       </c>
       <c r="K8">
-        <v>-10.71</v>
+        <v>-11.46</v>
       </c>
       <c r="L8">
-        <v>11.12</v>
+        <v>11.69</v>
       </c>
       <c r="M8">
-        <v>7.7</v>
+        <v>7.78</v>
       </c>
       <c r="N8">
         <v>22</v>
       </c>
       <c r="P8">
-        <v>483.97</v>
+        <v>483.19</v>
       </c>
       <c r="Q8">
-        <v>487.11</v>
+        <v>487.25</v>
       </c>
       <c r="R8">
-        <v>484.09</v>
+        <v>483.71</v>
       </c>
       <c r="S8">
-        <v>511.65</v>
+        <v>511.48</v>
       </c>
       <c r="T8">
-        <v>-6.18</v>
+        <v>-5.63</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1718,34 +1714,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>41.98</v>
+        <v>45.49</v>
       </c>
       <c r="Z8">
-        <v>-0.68</v>
+        <v>-0.88</v>
       </c>
       <c r="AA8">
-        <v>0.29</v>
+        <v>0.06</v>
       </c>
       <c r="AB8">
-        <v>-0.97</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="AD8">
-        <v>11.18</v>
+        <v>6.38</v>
       </c>
       <c r="AE8">
-        <v>10.28</v>
+        <v>10.48</v>
       </c>
       <c r="AF8">
-        <v>-17.51</v>
+        <v>-45.88</v>
       </c>
       <c r="AG8">
-        <v>497.93</v>
+        <v>497.74</v>
       </c>
       <c r="AH8">
-        <v>476.28</v>
+        <v>476.76</v>
       </c>
       <c r="AI8">
         <v>511.37</v>
@@ -1754,7 +1750,7 @@
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>25.33</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1765,10 +1761,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>968.22</v>
+        <v>976.9299999999999</v>
       </c>
       <c r="D9">
-        <v>-0.05</v>
+        <v>0.9</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1777,43 +1773,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-4.03</v>
+        <v>-3.16</v>
       </c>
       <c r="H9">
-        <v>9.4</v>
+        <v>10.38</v>
       </c>
       <c r="I9">
-        <v>-0.9399999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="J9">
-        <v>0.53</v>
+        <v>1.68</v>
       </c>
       <c r="K9">
-        <v>1.2</v>
+        <v>2.38</v>
       </c>
       <c r="L9">
-        <v>5.64</v>
+        <v>4.97</v>
       </c>
       <c r="M9">
-        <v>15.49</v>
+        <v>15.55</v>
       </c>
       <c r="N9">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="P9">
-        <v>974.6799999999999</v>
+        <v>973.5</v>
       </c>
       <c r="Q9">
-        <v>969.5599999999999</v>
+        <v>970.04</v>
       </c>
       <c r="R9">
-        <v>967.58</v>
+        <v>968.15</v>
       </c>
       <c r="S9">
-        <v>965.92</v>
+        <v>965.88</v>
       </c>
       <c r="T9">
-        <v>0.24</v>
+        <v>1.14</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1828,34 +1824,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>48.26</v>
+        <v>55.26</v>
       </c>
       <c r="Z9">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AA9">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AB9">
-        <v>0.07000000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="AC9">
-        <v>33.52</v>
+        <v>37.33</v>
       </c>
       <c r="AD9">
-        <v>56.56</v>
+        <v>42.51</v>
       </c>
       <c r="AE9">
-        <v>11.72</v>
+        <v>11.67</v>
       </c>
       <c r="AF9">
-        <v>-62.43</v>
+        <v>5.08</v>
       </c>
       <c r="AG9">
-        <v>983.33</v>
+        <v>984.14</v>
       </c>
       <c r="AH9">
-        <v>955.79</v>
+        <v>955.9400000000001</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1864,7 +1860,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>21.38</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1875,10 +1871,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>34.74</v>
+        <v>34.75</v>
       </c>
       <c r="D10">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1887,43 +1883,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-19.53</v>
+        <v>-19.5</v>
       </c>
       <c r="H10">
-        <v>21.38</v>
+        <v>21.42</v>
       </c>
       <c r="I10">
-        <v>0.87</v>
+        <v>-0.34</v>
       </c>
       <c r="J10">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>10.95</v>
+        <v>7.45</v>
       </c>
       <c r="L10">
-        <v>-7.41</v>
+        <v>-7.75</v>
       </c>
       <c r="M10">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="P10">
-        <v>34.91</v>
+        <v>34.89</v>
       </c>
       <c r="Q10">
-        <v>33.78</v>
+        <v>33.9</v>
       </c>
       <c r="R10">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="S10">
-        <v>35.78</v>
+        <v>35.76</v>
       </c>
       <c r="T10">
-        <v>-2.92</v>
+        <v>-2.83</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1938,34 +1934,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>62.8</v>
+        <v>62.87</v>
       </c>
       <c r="Z10">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="AA10">
         <v>0.87</v>
       </c>
       <c r="AB10">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="AC10">
-        <v>48.37</v>
+        <v>21.57</v>
       </c>
       <c r="AD10">
-        <v>66.98999999999999</v>
+        <v>46.85</v>
       </c>
       <c r="AE10">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AF10">
-        <v>-63.46</v>
+        <v>-57.72</v>
       </c>
       <c r="AG10">
-        <v>36.31</v>
+        <v>36.37</v>
       </c>
       <c r="AH10">
-        <v>31.26</v>
+        <v>31.43</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -1974,7 +1970,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>49.28</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1985,10 +1981,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>34.77</v>
+        <v>34.81</v>
       </c>
       <c r="D11">
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1997,43 +1993,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-19.68</v>
+        <v>-19.59</v>
       </c>
       <c r="H11">
-        <v>21.45</v>
+        <v>21.59</v>
       </c>
       <c r="I11">
-        <v>0.61</v>
+        <v>-0.49</v>
       </c>
       <c r="J11">
-        <v>9.82</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="K11">
-        <v>10.87</v>
+        <v>7.27</v>
       </c>
       <c r="L11">
-        <v>-7.5</v>
+        <v>-7.79</v>
       </c>
       <c r="M11">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="N11">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="P11">
-        <v>34.95</v>
+        <v>34.92</v>
       </c>
       <c r="Q11">
-        <v>33.8</v>
+        <v>33.92</v>
       </c>
       <c r="R11">
-        <v>32.05</v>
+        <v>32.1</v>
       </c>
       <c r="S11">
-        <v>35.86</v>
+        <v>35.83</v>
       </c>
       <c r="T11">
-        <v>-3.03</v>
+        <v>-2.86</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2048,34 +2044,34 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>62.92</v>
+        <v>63.22</v>
       </c>
       <c r="Z11">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AA11">
         <v>0.88</v>
       </c>
       <c r="AB11">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="AC11">
-        <v>49.65</v>
+        <v>24.11</v>
       </c>
       <c r="AD11">
-        <v>68.75</v>
+        <v>48.46</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>-64.38</v>
+        <v>-69.5</v>
       </c>
       <c r="AG11">
-        <v>36.36</v>
+        <v>36.44</v>
       </c>
       <c r="AH11">
-        <v>31.23</v>
+        <v>31.39</v>
       </c>
       <c r="AI11">
         <v>32.2</v>
@@ -2084,7 +2080,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>39.88</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2095,10 +2091,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>807.6900000000001</v>
+        <v>807.8099999999999</v>
       </c>
       <c r="D12">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2107,43 +2103,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="H12">
-        <v>23.9</v>
+        <v>23.92</v>
       </c>
       <c r="I12">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="K12">
-        <v>9.06</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L12">
-        <v>14.71</v>
+        <v>13.5</v>
       </c>
       <c r="M12">
-        <v>14.32</v>
+        <v>14.3</v>
       </c>
       <c r="N12">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>807.67</v>
+        <v>807.7</v>
       </c>
       <c r="Q12">
-        <v>792.78</v>
+        <v>794.37</v>
       </c>
       <c r="R12">
-        <v>780.36</v>
+        <v>781.36</v>
       </c>
       <c r="S12">
-        <v>748.84</v>
+        <v>749.16</v>
       </c>
       <c r="T12">
-        <v>7.86</v>
+        <v>7.83</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2158,34 +2154,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>68.38</v>
+        <v>68.47</v>
       </c>
       <c r="Z12">
-        <v>8.75</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AA12">
-        <v>7.59</v>
+        <v>7.79</v>
       </c>
       <c r="AB12">
-        <v>1.16</v>
+        <v>0.82</v>
       </c>
       <c r="AC12">
-        <v>85.38</v>
+        <v>83.3</v>
       </c>
       <c r="AD12">
-        <v>91</v>
+        <v>86.44</v>
       </c>
       <c r="AE12">
-        <v>14.34</v>
+        <v>14.82</v>
       </c>
       <c r="AF12">
-        <v>-32.96</v>
+        <v>82.19</v>
       </c>
       <c r="AG12">
-        <v>819.03</v>
+        <v>820.2</v>
       </c>
       <c r="AH12">
-        <v>766.54</v>
+        <v>768.54</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2194,7 +2190,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>22.04</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2205,10 +2201,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>278.16</v>
+        <v>278.35</v>
       </c>
       <c r="D13">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2217,43 +2213,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-6.52</v>
+        <v>-6.45</v>
       </c>
       <c r="H13">
-        <v>9.75</v>
+        <v>9.83</v>
       </c>
       <c r="I13">
-        <v>-0.87</v>
+        <v>-0.53</v>
       </c>
       <c r="J13">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="K13">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="L13">
-        <v>1.1</v>
+        <v>0.38</v>
       </c>
       <c r="M13">
-        <v>9.35</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N13">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P13">
-        <v>279.18</v>
+        <v>278.88</v>
       </c>
       <c r="Q13">
-        <v>276.78</v>
+        <v>276.88</v>
       </c>
       <c r="R13">
-        <v>273.59</v>
+        <v>273.85</v>
       </c>
       <c r="S13">
-        <v>280.01</v>
+        <v>279.93</v>
       </c>
       <c r="T13">
-        <v>-0.66</v>
+        <v>-0.57</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2268,34 +2264,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>55.68</v>
+        <v>56.25</v>
       </c>
       <c r="Z13">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AA13">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="AC13">
-        <v>51.45</v>
+        <v>40.09</v>
       </c>
       <c r="AD13">
-        <v>68.62</v>
+        <v>54.53</v>
       </c>
       <c r="AE13">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AF13">
-        <v>-33.99</v>
+        <v>-42.33</v>
       </c>
       <c r="AG13">
-        <v>282.64</v>
+        <v>282.78</v>
       </c>
       <c r="AH13">
-        <v>270.93</v>
+        <v>270.98</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2304,7 +2300,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>13.01</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2315,10 +2311,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>270.72</v>
+        <v>270.48</v>
       </c>
       <c r="D14">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2327,31 +2323,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-6.52</v>
+        <v>-6.61</v>
       </c>
       <c r="H14">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I14">
-        <v>-0.77</v>
+        <v>-0.84</v>
       </c>
       <c r="J14">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="K14">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="M14">
-        <v>-8.369999999999999</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="P14">
-        <v>271.72</v>
+        <v>271.27</v>
       </c>
       <c r="Q14">
-        <v>269.32</v>
+        <v>269.39</v>
       </c>
       <c r="R14">
-        <v>266.38</v>
+        <v>266.63</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2363,34 +2359,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>56.17</v>
+        <v>55.18</v>
       </c>
       <c r="Z14">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB14">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="AC14">
-        <v>57.36</v>
+        <v>42.42</v>
       </c>
       <c r="AD14">
-        <v>74.98</v>
+        <v>58.92</v>
       </c>
       <c r="AE14">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="AF14">
-        <v>151.83</v>
+        <v>-57.02</v>
       </c>
       <c r="AG14">
-        <v>274.78</v>
+        <v>274.87</v>
       </c>
       <c r="AH14">
-        <v>263.86</v>
+        <v>263.9</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2399,7 +2395,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>53.94</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2410,10 +2406,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>265.33</v>
+        <v>265.71</v>
       </c>
       <c r="D15">
-        <v>-0.09</v>
+        <v>0.14</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2422,43 +2418,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-6.68</v>
+        <v>-6.54</v>
       </c>
       <c r="H15">
-        <v>9.859999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I15">
-        <v>-1.12</v>
+        <v>-0.67</v>
       </c>
       <c r="J15">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="K15">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="L15">
-        <v>1.13</v>
+        <v>0.43</v>
       </c>
       <c r="M15">
-        <v>9.31</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N15">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="P15">
-        <v>266.54</v>
+        <v>266.18</v>
       </c>
       <c r="Q15">
-        <v>264.49</v>
+        <v>264.54</v>
       </c>
       <c r="R15">
-        <v>261.33</v>
+        <v>261.58</v>
       </c>
       <c r="S15">
-        <v>267.31</v>
+        <v>267.24</v>
       </c>
       <c r="T15">
-        <v>-0.74</v>
+        <v>-0.57</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2473,34 +2469,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>53.92</v>
+        <v>55.06</v>
       </c>
       <c r="Z15">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="AC15">
-        <v>49.88</v>
+        <v>38.73</v>
       </c>
       <c r="AD15">
-        <v>66.83</v>
+        <v>52.83</v>
       </c>
       <c r="AE15">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="AF15">
-        <v>-35.95</v>
+        <v>-78.41</v>
       </c>
       <c r="AG15">
-        <v>270.37</v>
+        <v>270.44</v>
       </c>
       <c r="AH15">
-        <v>258.61</v>
+        <v>258.64</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2509,7 +2505,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>31.8</v>
+        <v>32.43</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2520,10 +2516,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>276.76</v>
+        <v>276.84</v>
       </c>
       <c r="D16">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2532,43 +2528,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-6.49</v>
+        <v>-6.47</v>
       </c>
       <c r="H16">
-        <v>9.82</v>
+        <v>9.85</v>
       </c>
       <c r="I16">
-        <v>-0.82</v>
+        <v>-0.51</v>
       </c>
       <c r="J16">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="K16">
-        <v>3.97</v>
+        <v>4.08</v>
       </c>
       <c r="L16">
-        <v>1.05</v>
+        <v>0.41</v>
       </c>
       <c r="M16">
-        <v>9.380000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="N16">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="P16">
-        <v>277.79</v>
+        <v>277.51</v>
       </c>
       <c r="Q16">
-        <v>275.38</v>
+        <v>275.47</v>
       </c>
       <c r="R16">
-        <v>272.21</v>
+        <v>272.47</v>
       </c>
       <c r="S16">
-        <v>278.62</v>
+        <v>278.55</v>
       </c>
       <c r="T16">
-        <v>-0.67</v>
+        <v>-0.61</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2583,34 +2579,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>55.52</v>
+        <v>55.76</v>
       </c>
       <c r="Z16">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AA16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="AC16">
-        <v>49.11</v>
+        <v>36.88</v>
       </c>
       <c r="AD16">
-        <v>68.08</v>
+        <v>52.68</v>
       </c>
       <c r="AE16">
-        <v>4.22</v>
+        <v>4.01</v>
       </c>
       <c r="AF16">
-        <v>-17.38</v>
+        <v>-59.55</v>
       </c>
       <c r="AG16">
-        <v>281.25</v>
+        <v>281.38</v>
       </c>
       <c r="AH16">
-        <v>269.51</v>
+        <v>269.56</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2619,7 +2615,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>55.32</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2630,10 +2626,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>98.11</v>
+        <v>97.52</v>
       </c>
       <c r="D17">
-        <v>-0.16</v>
+        <v>-0.6</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2642,43 +2638,43 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-10.7</v>
+        <v>-11.24</v>
       </c>
       <c r="H17">
-        <v>30.45</v>
+        <v>29.66</v>
       </c>
       <c r="I17">
-        <v>0.78</v>
+        <v>-0.52</v>
       </c>
       <c r="J17">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="K17">
-        <v>11.22</v>
+        <v>9.66</v>
       </c>
       <c r="L17">
-        <v>27.83</v>
+        <v>24.13</v>
       </c>
       <c r="M17">
-        <v>30.4</v>
+        <v>30.51</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>97.45999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="Q17">
-        <v>95.01000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="R17">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="S17">
-        <v>95.63</v>
+        <v>95.67</v>
       </c>
       <c r="T17">
-        <v>2.59</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2693,34 +2689,34 @@
         <v>2</v>
       </c>
       <c r="Y17">
-        <v>62.78</v>
+        <v>59.65</v>
       </c>
       <c r="Z17">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AA17">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="AB17">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="AC17">
-        <v>78.38</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="AD17">
-        <v>73.90000000000001</v>
+        <v>76.66</v>
       </c>
       <c r="AE17">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AF17">
-        <v>-42.57</v>
+        <v>-35</v>
       </c>
       <c r="AG17">
-        <v>98.83</v>
+        <v>99.12</v>
       </c>
       <c r="AH17">
-        <v>91.18000000000001</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2729,7 +2725,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>38.82</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2740,10 +2736,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>279.31</v>
+        <v>279.76</v>
       </c>
       <c r="D18">
-        <v>-0.25</v>
+        <v>0.16</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2752,43 +2748,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.81</v>
+        <v>-5.66</v>
       </c>
       <c r="H18">
-        <v>13.74</v>
+        <v>13.92</v>
       </c>
       <c r="I18">
-        <v>-1.53</v>
+        <v>-1.47</v>
       </c>
       <c r="J18">
-        <v>-2.69</v>
+        <v>-1.63</v>
       </c>
       <c r="K18">
-        <v>5.02</v>
+        <v>5.91</v>
       </c>
       <c r="L18">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="M18">
-        <v>8.359999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N18">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="P18">
-        <v>280.99</v>
+        <v>280.16</v>
       </c>
       <c r="Q18">
-        <v>281.97</v>
+        <v>281.4</v>
       </c>
       <c r="R18">
-        <v>282.6</v>
+        <v>282.82</v>
       </c>
       <c r="S18">
-        <v>281.56</v>
+        <v>281.52</v>
       </c>
       <c r="T18">
-        <v>-0.8</v>
+        <v>-0.62</v>
       </c>
       <c r="U18" t="s">
         <v>59</v>
@@ -2803,34 +2799,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>43.32</v>
+        <v>44.55</v>
       </c>
       <c r="Z18">
-        <v>-0.55</v>
+        <v>-0.65</v>
       </c>
       <c r="AA18">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="AB18">
         <v>-0.36</v>
       </c>
       <c r="AC18">
-        <v>12.3</v>
+        <v>9.84</v>
       </c>
       <c r="AD18">
-        <v>31.87</v>
+        <v>16.63</v>
       </c>
       <c r="AE18">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="AF18">
-        <v>-90.04000000000001</v>
+        <v>-88.69</v>
       </c>
       <c r="AG18">
-        <v>287.96</v>
+        <v>285.58</v>
       </c>
       <c r="AH18">
-        <v>275.98</v>
+        <v>277.21</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2839,7 +2835,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>19.95</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2850,10 +2846,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>226.31</v>
+        <v>226.67</v>
       </c>
       <c r="D19">
-        <v>-2.2</v>
+        <v>0.16</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2862,43 +2858,43 @@
         <v>109.64</v>
       </c>
       <c r="G19">
-        <v>-36.83</v>
+        <v>-36.73</v>
       </c>
       <c r="H19">
-        <v>106.41</v>
+        <v>106.74</v>
       </c>
       <c r="I19">
-        <v>2.92</v>
+        <v>0.42</v>
       </c>
       <c r="J19">
-        <v>5.74</v>
+        <v>6.88</v>
       </c>
       <c r="K19">
-        <v>-12.61</v>
+        <v>-12.59</v>
       </c>
       <c r="L19">
-        <v>99.04000000000001</v>
+        <v>101.97</v>
       </c>
       <c r="M19">
-        <v>53.96</v>
+        <v>53.99</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>227.48</v>
+        <v>227.67</v>
       </c>
       <c r="Q19">
-        <v>217.8</v>
+        <v>218.64</v>
       </c>
       <c r="R19">
-        <v>221.65</v>
+        <v>221.2</v>
       </c>
       <c r="S19">
-        <v>225.42</v>
+        <v>225.87</v>
       </c>
       <c r="T19">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2913,34 +2909,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>57.92</v>
+        <v>58.33</v>
       </c>
       <c r="Z19">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AA19">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="AB19">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="AC19">
-        <v>88.98</v>
+        <v>78.48</v>
       </c>
       <c r="AD19">
-        <v>96.33</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="AE19">
-        <v>5.31</v>
+        <v>5.55</v>
       </c>
       <c r="AF19">
-        <v>14.35</v>
+        <v>-21.85</v>
       </c>
       <c r="AG19">
-        <v>230.8</v>
+        <v>231.66</v>
       </c>
       <c r="AH19">
-        <v>204.81</v>
+        <v>205.63</v>
       </c>
       <c r="AI19">
         <v>215.89</v>
@@ -2949,7 +2945,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>40.34</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2960,10 +2956,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>262.84</v>
+        <v>263.05</v>
       </c>
       <c r="D20">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2972,43 +2968,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-6.53</v>
+        <v>-6.46</v>
       </c>
       <c r="H20">
-        <v>9.81</v>
+        <v>9.9</v>
       </c>
       <c r="I20">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
       <c r="J20">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="K20">
-        <v>3.76</v>
+        <v>3.96</v>
       </c>
       <c r="L20">
-        <v>1.1</v>
+        <v>0.36</v>
       </c>
       <c r="M20">
-        <v>9.35</v>
+        <v>9.27</v>
       </c>
       <c r="N20">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="P20">
-        <v>263.79</v>
+        <v>263.52</v>
       </c>
       <c r="Q20">
-        <v>261.59</v>
+        <v>261.67</v>
       </c>
       <c r="R20">
-        <v>258.62</v>
+        <v>258.86</v>
       </c>
       <c r="S20">
-        <v>264.69</v>
+        <v>264.62</v>
       </c>
       <c r="T20">
-        <v>-0.7</v>
+        <v>-0.59</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3023,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>55.49</v>
+        <v>56.16</v>
       </c>
       <c r="Z20">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AA20">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AC20">
-        <v>51.91</v>
+        <v>40.75</v>
       </c>
       <c r="AD20">
-        <v>68.83</v>
+        <v>54.95</v>
       </c>
       <c r="AE20">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AF20">
-        <v>-33.5</v>
+        <v>-43.91</v>
       </c>
       <c r="AG20">
-        <v>267.06</v>
+        <v>267.17</v>
       </c>
       <c r="AH20">
-        <v>256.13</v>
+        <v>256.17</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3059,7 +3055,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>37.64</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3070,10 +3066,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>801.14</v>
+        <v>799.65</v>
       </c>
       <c r="D21">
-        <v>0.19</v>
+        <v>-0.19</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3082,43 +3078,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-0.26</v>
+        <v>-0.45</v>
       </c>
       <c r="H21">
-        <v>24.66</v>
+        <v>24.43</v>
       </c>
       <c r="I21">
-        <v>0.55</v>
+        <v>-0.24</v>
       </c>
       <c r="J21">
-        <v>4.02</v>
+        <v>3.8</v>
       </c>
       <c r="K21">
-        <v>9.25</v>
+        <v>8.26</v>
       </c>
       <c r="L21">
-        <v>14.82</v>
+        <v>13.44</v>
       </c>
       <c r="M21">
-        <v>14.34</v>
+        <v>14.25</v>
       </c>
       <c r="N21">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P21">
-        <v>801.29</v>
+        <v>800.9</v>
       </c>
       <c r="Q21">
-        <v>785.9400000000001</v>
+        <v>787.45</v>
       </c>
       <c r="R21">
-        <v>773.22</v>
+        <v>774.1900000000001</v>
       </c>
       <c r="S21">
-        <v>742</v>
+        <v>742.3099999999999</v>
       </c>
       <c r="T21">
-        <v>7.97</v>
+        <v>7.73</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3133,34 +3129,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>65.03</v>
+        <v>63.28</v>
       </c>
       <c r="Z21">
-        <v>8.609999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="AA21">
-        <v>7.34</v>
+        <v>7.56</v>
       </c>
       <c r="AB21">
-        <v>1.27</v>
+        <v>0.86</v>
       </c>
       <c r="AC21">
-        <v>81.15000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="AD21">
-        <v>87.94</v>
+        <v>81.5</v>
       </c>
       <c r="AE21">
-        <v>10.7</v>
+        <v>10.68</v>
       </c>
       <c r="AF21">
-        <v>-52.76</v>
+        <v>22.54</v>
       </c>
       <c r="AG21">
-        <v>809.98</v>
+        <v>810.9299999999999</v>
       </c>
       <c r="AH21">
-        <v>761.9</v>
+        <v>763.96</v>
       </c>
       <c r="AI21">
         <v>770.55</v>
@@ -3169,7 +3165,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>14.02</v>
+        <v>12.32</v>
       </c>
     </row>
   </sheetData>
@@ -3310,7 +3306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3350,16 +3346,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>59</v>
@@ -3370,16 +3366,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>59</v>
@@ -3390,42 +3386,42 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>58</v>
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3433,19 +3429,19 @@
         <v>41</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3453,1623 +3449,1629 @@
         <v>42</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>78</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0.64</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-0.23</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.87</v>
+      <c r="C13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-2.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D14" s="7">
-        <v>-1.61</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1.18</v>
+        <v>-0.12</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="D15" s="7">
-        <v>1</v>
+        <v>-0.13</v>
       </c>
       <c r="E15" s="9">
-        <v>1.21</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>9.029999999999999</v>
+        <v>-1.61</v>
       </c>
       <c r="D16" s="7">
-        <v>7.81</v>
+        <v>-1.76</v>
       </c>
       <c r="E16" s="8">
-        <v>-1.22</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>8.91</v>
+        <v>1</v>
       </c>
       <c r="D17" s="7">
-        <v>7.73</v>
+        <v>0.63</v>
       </c>
       <c r="E17" s="8">
-        <v>-1.18</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>0.34</v>
+        <v>7.81</v>
       </c>
       <c r="D18" s="7">
-        <v>-0.34</v>
+        <v>7.44</v>
       </c>
       <c r="E18" s="8">
-        <v>-0.68</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>0.3</v>
+        <v>7.73</v>
       </c>
       <c r="D19" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.23</v>
+        <v>7.38</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>8.960000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="D20" s="7">
-        <v>9.800000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="E20" s="9">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>8.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D21" s="7">
-        <v>9.82</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1.03</v>
+        <v>9</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>3.85</v>
+        <v>9.82</v>
       </c>
       <c r="D22" s="7">
-        <v>3.7</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.15</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>1.82</v>
+        <v>3.7</v>
       </c>
       <c r="D23" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.18</v>
+        <v>3.97</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.27</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="D24" s="7">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="D25" s="7">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="E25" s="8">
-        <v>-0.26</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="D26" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.15</v>
+        <v>1.47</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.17</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>5.92</v>
+        <v>1.65</v>
       </c>
       <c r="D27" s="7">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="E27" s="8">
-        <v>-1.22</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>-1.85</v>
+        <v>4.7</v>
       </c>
       <c r="D28" s="7">
-        <v>-2.69</v>
+        <v>4.59</v>
       </c>
       <c r="E28" s="8">
-        <v>-0.84</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="7">
-        <v>8.619999999999999</v>
+        <v>-2.69</v>
       </c>
       <c r="D29" s="7">
-        <v>5.74</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.88</v>
+        <v>-1.63</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.06</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="7">
-        <v>1.78</v>
+        <v>5.74</v>
       </c>
       <c r="D30" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.14</v>
+        <v>6.88</v>
+      </c>
+      <c r="E30" s="9">
+        <v>1.14</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="7">
-        <v>4</v>
+        <v>1.64</v>
       </c>
       <c r="D31" s="7">
-        <v>4.02</v>
+        <v>1.67</v>
       </c>
       <c r="E31" s="9">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="7">
-        <v>0.45</v>
+        <v>4.02</v>
       </c>
       <c r="D32" s="7">
-        <v>-0.36</v>
+        <v>3.8</v>
       </c>
       <c r="E32" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="D33" s="7">
-        <v>-0.76</v>
+        <v>-0.4</v>
       </c>
       <c r="E33" s="8">
-        <v>-1.16</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>-0.93</v>
+        <v>-0.76</v>
       </c>
       <c r="D34" s="7">
-        <v>0.17</v>
+        <v>-0.58</v>
       </c>
       <c r="E34" s="9">
-        <v>1.1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>-2.09</v>
+        <v>0.17</v>
       </c>
       <c r="D35" s="7">
-        <v>-1.15</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.9399999999999999</v>
+        <v>-0.45</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>5.91</v>
+        <v>-1.15</v>
       </c>
       <c r="D36" s="7">
-        <v>2.45</v>
+        <v>-1.19</v>
       </c>
       <c r="E36" s="8">
-        <v>-3.46</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>5.81</v>
+        <v>2.45</v>
       </c>
       <c r="D37" s="7">
-        <v>2.54</v>
+        <v>1.4</v>
       </c>
       <c r="E37" s="8">
-        <v>-3.27</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>-1.86</v>
+        <v>2.54</v>
       </c>
       <c r="D38" s="7">
-        <v>-1.43</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.43</v>
+        <v>1.48</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-1.43</v>
       </c>
       <c r="D39" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.38</v>
+        <v>-0.8</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.63</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>0.14</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D40" s="7">
-        <v>0.87</v>
+        <v>-0.6</v>
       </c>
       <c r="E40" s="9">
-        <v>0.73</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-0.2</v>
+        <v>0.87</v>
       </c>
       <c r="D41" s="7">
-        <v>0.61</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.8100000000000001</v>
+        <v>-0.34</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>0.07000000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="D42" s="7">
-        <v>0.05</v>
+        <v>-0.49</v>
       </c>
       <c r="E42" s="8">
-        <v>-0.02</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>-0.59</v>
+        <v>0.05</v>
       </c>
       <c r="D43" s="7">
-        <v>-0.87</v>
+        <v>0.02</v>
       </c>
       <c r="E43" s="8">
-        <v>-0.28</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>-0.2</v>
+        <v>-0.87</v>
       </c>
       <c r="D44" s="7">
-        <v>-0.77</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.57</v>
+        <v>-0.53</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.34</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>-0.68</v>
+        <v>-0.77</v>
       </c>
       <c r="D45" s="7">
-        <v>-1.12</v>
+        <v>-0.84</v>
       </c>
       <c r="E45" s="8">
-        <v>-0.44</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>-0.6</v>
+        <v>-1.12</v>
       </c>
       <c r="D46" s="7">
-        <v>-0.82</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.22</v>
+        <v>-0.67</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.45</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="7">
-        <v>3.01</v>
+        <v>-0.82</v>
       </c>
       <c r="D47" s="7">
-        <v>0.78</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.23</v>
+        <v>-0.51</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.31</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="7">
-        <v>-1.27</v>
+        <v>0.78</v>
       </c>
       <c r="D48" s="7">
-        <v>-1.53</v>
+        <v>-0.52</v>
       </c>
       <c r="E48" s="8">
-        <v>-0.26</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="7">
-        <v>5.83</v>
+        <v>-1.53</v>
       </c>
       <c r="D49" s="7">
-        <v>2.92</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-2.91</v>
+        <v>-1.47</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="7">
-        <v>-0.41</v>
+        <v>2.92</v>
       </c>
       <c r="D50" s="7">
-        <v>-0.88</v>
+        <v>0.42</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.47</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="7">
-        <v>1.06</v>
+        <v>-0.88</v>
       </c>
       <c r="D51" s="7">
-        <v>0.55</v>
-      </c>
-      <c r="E51" s="8">
         <v>-0.51</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.37</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C52" s="7">
-        <v>4.68</v>
+        <v>0.55</v>
       </c>
       <c r="D52" s="7">
-        <v>5.35</v>
-      </c>
-      <c r="E52" s="9">
-        <v>0.67</v>
+        <v>-0.24</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>-89.48999999999999</v>
+        <v>5.35</v>
       </c>
       <c r="D53" s="7">
-        <v>-89.43000000000001</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.06</v>
+        <v>4.28</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>4.5</v>
+        <v>-89.43000000000001</v>
       </c>
       <c r="D54" s="7">
-        <v>5.08</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.58</v>
+        <v>-89.58</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-11.78</v>
+        <v>5.08</v>
       </c>
       <c r="D55" s="7">
-        <v>-10.45</v>
-      </c>
-      <c r="E55" s="9">
-        <v>1.33</v>
+        <v>4.25</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>50.64</v>
+        <v>-10.45</v>
       </c>
       <c r="D56" s="7">
-        <v>48.74</v>
+        <v>-11.18</v>
       </c>
       <c r="E56" s="8">
-        <v>-1.9</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>50.8</v>
+        <v>48.74</v>
       </c>
       <c r="D57" s="7">
-        <v>49.01</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-1.79</v>
+        <v>50.34</v>
+      </c>
+      <c r="E57" s="9">
+        <v>1.6</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>9.77</v>
+        <v>49.01</v>
       </c>
       <c r="D58" s="7">
-        <v>11.12</v>
+        <v>50.61</v>
       </c>
       <c r="E58" s="9">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>4.46</v>
+        <v>11.12</v>
       </c>
       <c r="D59" s="7">
-        <v>5.64</v>
+        <v>11.69</v>
       </c>
       <c r="E59" s="9">
-        <v>1.18</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>-8.279999999999999</v>
+        <v>5.64</v>
       </c>
       <c r="D60" s="7">
-        <v>-7.41</v>
-      </c>
-      <c r="E60" s="9">
-        <v>0.87</v>
+        <v>4.97</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>-8.65</v>
+        <v>-7.41</v>
       </c>
       <c r="D61" s="7">
-        <v>-7.5</v>
-      </c>
-      <c r="E61" s="9">
-        <v>1.15</v>
+        <v>-7.75</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>13.13</v>
+        <v>-7.5</v>
       </c>
       <c r="D62" s="7">
-        <v>14.71</v>
-      </c>
-      <c r="E62" s="9">
-        <v>1.58</v>
+        <v>-7.79</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>0.37</v>
+        <v>14.71</v>
       </c>
       <c r="D63" s="7">
-        <v>1.1</v>
-      </c>
-      <c r="E63" s="9">
-        <v>0.73</v>
+        <v>13.5</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
       <c r="D64" s="7">
-        <v>1.13</v>
-      </c>
-      <c r="E64" s="9">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>0.26</v>
+        <v>1.13</v>
       </c>
       <c r="D65" s="7">
-        <v>1.05</v>
-      </c>
-      <c r="E65" s="9">
-        <v>0.79</v>
+        <v>0.43</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>27.76</v>
+        <v>1.05</v>
       </c>
       <c r="D66" s="7">
-        <v>27.83</v>
-      </c>
-      <c r="E66" s="9">
-        <v>0.07000000000000001</v>
+        <v>0.41</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>2.2</v>
+        <v>27.83</v>
       </c>
       <c r="D67" s="7">
-        <v>3.24</v>
-      </c>
-      <c r="E67" s="9">
-        <v>1.04</v>
+        <v>24.13</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-3.7</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>103.99</v>
+        <v>3.24</v>
       </c>
       <c r="D68" s="7">
-        <v>99.04000000000001</v>
+        <v>2.97</v>
       </c>
       <c r="E68" s="8">
-        <v>-4.95</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>0.29</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="D69" s="7">
-        <v>1.1</v>
+        <v>101.97</v>
       </c>
       <c r="E69" s="9">
-        <v>0.8100000000000001</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>13.45</v>
+        <v>1.1</v>
       </c>
       <c r="D70" s="7">
-        <v>14.82</v>
-      </c>
-      <c r="E70" s="9">
-        <v>1.37</v>
+        <v>0.36</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>8.199999999999999</v>
+        <v>14.82</v>
       </c>
       <c r="D71" s="7">
-        <v>8.06</v>
+        <v>13.44</v>
       </c>
       <c r="E71" s="8">
-        <v>-0.14</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>8.050000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="D72" s="7">
-        <v>8.18</v>
-      </c>
-      <c r="E72" s="9">
-        <v>0.13</v>
+        <v>8</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>-11.36</v>
+        <v>8.18</v>
       </c>
       <c r="D73" s="7">
-        <v>-9.85</v>
-      </c>
-      <c r="E73" s="9">
-        <v>1.51</v>
+        <v>7.89</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="7">
-        <v>-4.53</v>
+        <v>-9.85</v>
       </c>
       <c r="D74" s="7">
-        <v>-3.9</v>
-      </c>
-      <c r="E74" s="9">
-        <v>0.63</v>
+        <v>-10.52</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>-2.29</v>
+        <v>-3.9</v>
       </c>
       <c r="D75" s="7">
-        <v>-3.25</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-0.96</v>
+        <v>-3.79</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.11</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>-2.38</v>
+        <v>-3.25</v>
       </c>
       <c r="D76" s="7">
-        <v>-3.25</v>
+        <v>-4.22</v>
       </c>
       <c r="E76" s="8">
-        <v>-0.87</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>-10.61</v>
+        <v>-3.25</v>
       </c>
       <c r="D77" s="7">
-        <v>-10.71</v>
+        <v>-4.11</v>
       </c>
       <c r="E77" s="8">
-        <v>-0.1</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>0.62</v>
+        <v>-10.71</v>
       </c>
       <c r="D78" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="E78" s="9">
-        <v>0.58</v>
+        <v>-11.46</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>12.79</v>
+        <v>1.2</v>
       </c>
       <c r="D79" s="7">
-        <v>10.95</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-1.84</v>
+        <v>2.38</v>
+      </c>
+      <c r="E79" s="9">
+        <v>1.18</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>12.94</v>
+        <v>10.95</v>
       </c>
       <c r="D80" s="7">
-        <v>10.87</v>
+        <v>7.45</v>
       </c>
       <c r="E80" s="8">
-        <v>-2.07</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>7.82</v>
+        <v>10.87</v>
       </c>
       <c r="D81" s="7">
-        <v>9.06</v>
-      </c>
-      <c r="E81" s="9">
-        <v>1.24</v>
+        <v>7.27</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="7">
-        <v>4.12</v>
+        <v>9.06</v>
       </c>
       <c r="D82" s="7">
-        <v>3.95</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E82" s="8">
-        <v>-0.17</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="D83" s="7">
-        <v>3.76</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.07000000000000001</v>
+        <v>4.01</v>
+      </c>
+      <c r="E83" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="D84" s="7">
-        <v>3.89</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.21</v>
+        <v>3.82</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="D85" s="7">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="E85" s="9">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="7">
-        <v>9.26</v>
+        <v>3.97</v>
       </c>
       <c r="D86" s="7">
-        <v>11.22</v>
+        <v>4.08</v>
       </c>
       <c r="E86" s="9">
-        <v>1.96</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="7">
-        <v>5.44</v>
+        <v>11.22</v>
       </c>
       <c r="D87" s="7">
-        <v>5.02</v>
+        <v>9.66</v>
       </c>
       <c r="E87" s="8">
-        <v>-0.42</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="7">
-        <v>-9.210000000000001</v>
+        <v>5.02</v>
       </c>
       <c r="D88" s="7">
-        <v>-12.61</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-3.4</v>
+        <v>5.91</v>
+      </c>
+      <c r="E88" s="9">
+        <v>0.89</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C89" s="7">
-        <v>3.89</v>
+        <v>-12.61</v>
       </c>
       <c r="D89" s="7">
-        <v>3.76</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.13</v>
+        <v>-12.59</v>
+      </c>
+      <c r="E89" s="9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C90" s="7">
-        <v>8.07</v>
+        <v>3.76</v>
       </c>
       <c r="D90" s="7">
-        <v>9.25</v>
+        <v>3.96</v>
       </c>
       <c r="E90" s="9">
-        <v>1.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C91" s="7">
-        <v>-5.8</v>
+        <v>9.25</v>
       </c>
       <c r="D91" s="7">
-        <v>-5.96</v>
+        <v>8.26</v>
       </c>
       <c r="E91" s="8">
-        <v>-0.16</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="7">
-        <v>-90.56</v>
+        <v>-5.96</v>
       </c>
       <c r="D92" s="7">
-        <v>-90.59999999999999</v>
+        <v>-6.21</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.04</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="7">
-        <v>-13.74</v>
+        <v>-90.59999999999999</v>
       </c>
       <c r="D93" s="7">
-        <v>-13.27</v>
-      </c>
-      <c r="E93" s="9">
-        <v>0.47</v>
+        <v>-90.62</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="7">
-        <v>-14.69</v>
+        <v>-13.27</v>
       </c>
       <c r="D94" s="7">
-        <v>-14.05</v>
-      </c>
-      <c r="E94" s="9">
-        <v>0.64</v>
+        <v>-13.75</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-13.7</v>
+        <v>-14.05</v>
       </c>
       <c r="D95" s="7">
-        <v>-14.37</v>
+        <v>-14.16</v>
       </c>
       <c r="E95" s="8">
-        <v>-0.67</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-13.72</v>
+        <v>-14.37</v>
       </c>
       <c r="D96" s="7">
-        <v>-14.35</v>
+        <v>-14.6</v>
       </c>
       <c r="E96" s="8">
-        <v>-0.63</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-15.19</v>
+        <v>-14.35</v>
       </c>
       <c r="D97" s="7">
-        <v>-15.24</v>
+        <v>-14.57</v>
       </c>
       <c r="E97" s="8">
-        <v>-0.05</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-3.98</v>
+        <v>-15.24</v>
       </c>
       <c r="D98" s="7">
-        <v>-4.03</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-0.05</v>
+        <v>-14.78</v>
+      </c>
+      <c r="E98" s="9">
+        <v>0.46</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-19.71</v>
+        <v>-4.03</v>
       </c>
       <c r="D99" s="7">
-        <v>-19.53</v>
+        <v>-3.16</v>
       </c>
       <c r="E99" s="9">
-        <v>0.18</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-19.96</v>
+        <v>-19.53</v>
       </c>
       <c r="D100" s="7">
-        <v>-19.68</v>
+        <v>-19.5</v>
       </c>
       <c r="E100" s="9">
-        <v>0.28</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-0.33</v>
+        <v>-19.68</v>
       </c>
       <c r="D101" s="7">
-        <v>-0.16</v>
+        <v>-19.59</v>
       </c>
       <c r="E101" s="9">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-6.46</v>
+        <v>-0.16</v>
       </c>
       <c r="D102" s="7">
-        <v>-6.52</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-0.06</v>
+        <v>-0.15</v>
+      </c>
+      <c r="E102" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-6.55</v>
+        <v>-6.52</v>
       </c>
       <c r="D103" s="7">
-        <v>-6.52</v>
+        <v>-6.45</v>
       </c>
       <c r="E103" s="9">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-6.59</v>
+        <v>-6.52</v>
       </c>
       <c r="D104" s="7">
-        <v>-6.68</v>
+        <v>-6.61</v>
       </c>
       <c r="E104" s="8">
         <v>-0.09</v>
@@ -5077,339 +5079,339 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="7">
-        <v>-6.48</v>
+        <v>-6.68</v>
       </c>
       <c r="D105" s="7">
-        <v>-6.49</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-0.01</v>
+        <v>-6.54</v>
+      </c>
+      <c r="E105" s="9">
+        <v>0.14</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="7">
-        <v>-10.56</v>
+        <v>-6.49</v>
       </c>
       <c r="D106" s="7">
-        <v>-10.7</v>
-      </c>
-      <c r="E106" s="8">
-        <v>-0.14</v>
+        <v>-6.47</v>
+      </c>
+      <c r="E106" s="9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="7">
-        <v>-5.57</v>
+        <v>-10.7</v>
       </c>
       <c r="D107" s="7">
-        <v>-5.81</v>
+        <v>-11.24</v>
       </c>
       <c r="E107" s="8">
-        <v>-0.24</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C108" s="7">
-        <v>-35.41</v>
+        <v>-5.81</v>
       </c>
       <c r="D108" s="7">
-        <v>-36.83</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-1.42</v>
+        <v>-5.66</v>
+      </c>
+      <c r="E108" s="9">
+        <v>0.15</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C109" s="7">
-        <v>-6.48</v>
+        <v>-36.83</v>
       </c>
       <c r="D109" s="7">
-        <v>-6.53</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-0.05</v>
+        <v>-36.73</v>
+      </c>
+      <c r="E109" s="9">
+        <v>0.1</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C110" s="7">
-        <v>-0.45</v>
+        <v>-6.53</v>
       </c>
       <c r="D110" s="7">
-        <v>-0.26</v>
+        <v>-6.46</v>
       </c>
       <c r="E110" s="9">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C111" s="7">
-        <v>599.01</v>
+        <v>-0.26</v>
       </c>
       <c r="D111" s="7">
-        <v>597.97</v>
+        <v>-0.45</v>
       </c>
       <c r="E111" s="8">
-        <v>-1.04</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="7">
-        <v>60.15</v>
+        <v>597.97</v>
       </c>
       <c r="D112" s="7">
-        <v>59.89</v>
+        <v>596.37</v>
       </c>
       <c r="E112" s="8">
-        <v>-0.26</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="7">
-        <v>93.86</v>
+        <v>59.89</v>
       </c>
       <c r="D113" s="7">
-        <v>94.37</v>
-      </c>
-      <c r="E113" s="9">
-        <v>0.51</v>
+        <v>59.77</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="7">
-        <v>52.04</v>
+        <v>94.37</v>
       </c>
       <c r="D114" s="7">
-        <v>52.43</v>
-      </c>
-      <c r="E114" s="9">
-        <v>0.39</v>
+        <v>93.84999999999999</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>126.45</v>
+        <v>52.43</v>
       </c>
       <c r="D115" s="7">
-        <v>125.48</v>
+        <v>52.36</v>
       </c>
       <c r="E115" s="8">
-        <v>-0.97</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>130.61</v>
+        <v>125.48</v>
       </c>
       <c r="D116" s="7">
-        <v>129.65</v>
+        <v>125.13</v>
       </c>
       <c r="E116" s="8">
-        <v>-0.96</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>480.32</v>
+        <v>129.65</v>
       </c>
       <c r="D117" s="7">
-        <v>480.01</v>
+        <v>129.33</v>
       </c>
       <c r="E117" s="8">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>968.74</v>
+        <v>480.01</v>
       </c>
       <c r="D118" s="7">
-        <v>968.22</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-0.52</v>
+        <v>482.66</v>
+      </c>
+      <c r="E118" s="9">
+        <v>2.65</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>34.66</v>
+        <v>968.22</v>
       </c>
       <c r="D119" s="7">
-        <v>34.74</v>
+        <v>976.9299999999999</v>
       </c>
       <c r="E119" s="9">
-        <v>0.08</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>34.65</v>
+        <v>34.74</v>
       </c>
       <c r="D120" s="7">
-        <v>34.77</v>
+        <v>34.75</v>
       </c>
       <c r="E120" s="9">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>806.3099999999999</v>
+        <v>34.77</v>
       </c>
       <c r="D121" s="7">
-        <v>807.6900000000001</v>
+        <v>34.81</v>
       </c>
       <c r="E121" s="9">
-        <v>1.38</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>278.32</v>
+        <v>807.6900000000001</v>
       </c>
       <c r="D122" s="7">
-        <v>278.16</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-0.16</v>
+        <v>807.8099999999999</v>
+      </c>
+      <c r="E122" s="9">
+        <v>0.12</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>270.65</v>
+        <v>278.16</v>
       </c>
       <c r="D123" s="7">
-        <v>270.72</v>
+        <v>278.35</v>
       </c>
       <c r="E123" s="9">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>265.57</v>
+        <v>270.72</v>
       </c>
       <c r="D124" s="7">
-        <v>265.33</v>
+        <v>270.48</v>
       </c>
       <c r="E124" s="8">
         <v>-0.24</v>
@@ -5417,203 +5419,203 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="7">
-        <v>276.8</v>
+        <v>265.33</v>
       </c>
       <c r="D125" s="7">
-        <v>276.76</v>
-      </c>
-      <c r="E125" s="8">
-        <v>-0.04</v>
+        <v>265.71</v>
+      </c>
+      <c r="E125" s="9">
+        <v>0.38</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="7">
-        <v>98.27</v>
+        <v>276.76</v>
       </c>
       <c r="D126" s="7">
-        <v>98.11</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-0.16</v>
+        <v>276.84</v>
+      </c>
+      <c r="E126" s="9">
+        <v>0.08</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C127" s="7">
-        <v>280.02</v>
+        <v>98.11</v>
       </c>
       <c r="D127" s="7">
-        <v>279.31</v>
+        <v>97.52</v>
       </c>
       <c r="E127" s="8">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C128" s="7">
-        <v>231.39</v>
+        <v>279.31</v>
       </c>
       <c r="D128" s="7">
-        <v>226.31</v>
-      </c>
-      <c r="E128" s="8">
-        <v>-5.08</v>
+        <v>279.76</v>
+      </c>
+      <c r="E128" s="9">
+        <v>0.45</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C129" s="7">
-        <v>262.98</v>
+        <v>226.31</v>
       </c>
       <c r="D129" s="7">
-        <v>262.84</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-0.14</v>
+        <v>226.67</v>
+      </c>
+      <c r="E129" s="9">
+        <v>0.36</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C130" s="7">
-        <v>799.62</v>
+        <v>262.84</v>
       </c>
       <c r="D130" s="7">
-        <v>801.14</v>
+        <v>263.05</v>
       </c>
       <c r="E130" s="9">
-        <v>1.52</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C131" s="7">
-        <v>37</v>
+        <v>801.14</v>
       </c>
       <c r="D131" s="7">
-        <v>53</v>
-      </c>
-      <c r="E131" s="9">
-        <v>16</v>
+        <v>799.65</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="7">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D132" s="7">
-        <v>42</v>
-      </c>
-      <c r="E132" s="8">
-        <v>-5</v>
+        <v>63</v>
+      </c>
+      <c r="E132" s="9">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C133" s="7">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D133" s="7">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E133" s="8">
-        <v>-15</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="7">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D134" s="7">
-        <v>37</v>
-      </c>
-      <c r="E134" s="9">
-        <v>5</v>
+        <v>27</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-31</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="7">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D135" s="7">
-        <v>47</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-6</v>
+        <v>78</v>
+      </c>
+      <c r="E135" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C136" s="7">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D136" s="7">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E136" s="9">
         <v>5</v>
@@ -5621,688 +5623,773 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C137" s="7">
-        <v>55.41</v>
+        <v>27</v>
       </c>
       <c r="D137" s="7">
-        <v>54.04</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-1.37</v>
+        <v>40</v>
+      </c>
+      <c r="E137" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C138" s="7">
-        <v>54.1</v>
+        <v>37</v>
       </c>
       <c r="D138" s="7">
-        <v>51.2</v>
-      </c>
-      <c r="E138" s="8">
-        <v>-2.9</v>
+        <v>53</v>
+      </c>
+      <c r="E138" s="9">
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C139" s="7">
-        <v>32.61</v>
+        <v>47</v>
       </c>
       <c r="D139" s="7">
-        <v>39.35</v>
+        <v>58</v>
       </c>
       <c r="E139" s="9">
-        <v>6.74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="7">
+        <v>32</v>
+      </c>
+      <c r="D140" s="7">
         <v>40</v>
       </c>
-      <c r="B140" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C140" s="7">
-        <v>39.96</v>
-      </c>
-      <c r="D140" s="7">
-        <v>45.49</v>
-      </c>
       <c r="E140" s="9">
-        <v>5.53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C141" s="7">
-        <v>72.97</v>
+        <v>78</v>
       </c>
       <c r="D141" s="7">
-        <v>68.12</v>
+        <v>73</v>
       </c>
       <c r="E141" s="8">
-        <v>-4.85</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="7">
-        <v>73.06</v>
+        <v>54.04</v>
       </c>
       <c r="D142" s="7">
-        <v>68.34</v>
+        <v>51.92</v>
       </c>
       <c r="E142" s="8">
-        <v>-4.72</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="7">
-        <v>42.28</v>
+        <v>51.2</v>
       </c>
       <c r="D143" s="7">
-        <v>41.98</v>
+        <v>49.87</v>
       </c>
       <c r="E143" s="8">
-        <v>-0.3</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="7">
-        <v>48.68</v>
+        <v>39.35</v>
       </c>
       <c r="D144" s="7">
-        <v>48.26</v>
+        <v>35.45</v>
       </c>
       <c r="E144" s="8">
-        <v>-0.42</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="7">
-        <v>62.22</v>
+        <v>45.49</v>
       </c>
       <c r="D145" s="7">
-        <v>62.8</v>
-      </c>
-      <c r="E145" s="9">
-        <v>0.58</v>
+        <v>44.7</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>62.05</v>
+        <v>68.12</v>
       </c>
       <c r="D146" s="7">
-        <v>62.92</v>
-      </c>
-      <c r="E146" s="9">
-        <v>0.87</v>
+        <v>66.41</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>67.39</v>
+        <v>68.34</v>
       </c>
       <c r="D147" s="7">
-        <v>68.38</v>
-      </c>
-      <c r="E147" s="9">
-        <v>0.99</v>
+        <v>66.79000000000001</v>
+      </c>
+      <c r="E147" s="8">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>56.25</v>
+        <v>41.98</v>
       </c>
       <c r="D148" s="7">
-        <v>55.68</v>
-      </c>
-      <c r="E148" s="8">
-        <v>-0.57</v>
+        <v>45.49</v>
+      </c>
+      <c r="E148" s="9">
+        <v>3.51</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>55.96</v>
+        <v>48.26</v>
       </c>
       <c r="D149" s="7">
-        <v>56.17</v>
+        <v>55.26</v>
       </c>
       <c r="E149" s="9">
-        <v>0.21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>54.73</v>
+        <v>62.8</v>
       </c>
       <c r="D150" s="7">
-        <v>53.92</v>
-      </c>
-      <c r="E150" s="8">
-        <v>-0.8100000000000001</v>
+        <v>62.87</v>
+      </c>
+      <c r="E150" s="9">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>55.66</v>
+        <v>62.92</v>
       </c>
       <c r="D151" s="7">
-        <v>55.52</v>
-      </c>
-      <c r="E151" s="8">
-        <v>-0.14</v>
+        <v>63.22</v>
+      </c>
+      <c r="E151" s="9">
+        <v>0.3</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>63.62</v>
+        <v>68.38</v>
       </c>
       <c r="D152" s="7">
-        <v>62.78</v>
-      </c>
-      <c r="E152" s="8">
-        <v>-0.84</v>
+        <v>68.47</v>
+      </c>
+      <c r="E152" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="7">
-        <v>44.77</v>
+        <v>55.68</v>
       </c>
       <c r="D153" s="7">
-        <v>43.32</v>
-      </c>
-      <c r="E153" s="8">
-        <v>-1.45</v>
+        <v>56.25</v>
+      </c>
+      <c r="E153" s="9">
+        <v>0.57</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C154" s="7">
-        <v>66.67</v>
+        <v>56.17</v>
       </c>
       <c r="D154" s="7">
-        <v>57.92</v>
+        <v>55.18</v>
       </c>
       <c r="E154" s="8">
-        <v>-8.75</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C155" s="7">
-        <v>56.02</v>
+        <v>53.92</v>
       </c>
       <c r="D155" s="7">
-        <v>55.49</v>
-      </c>
-      <c r="E155" s="8">
-        <v>-0.53</v>
+        <v>55.06</v>
+      </c>
+      <c r="E155" s="9">
+        <v>1.14</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C156" s="7">
-        <v>64.09</v>
+        <v>55.52</v>
       </c>
       <c r="D156" s="7">
-        <v>65.03</v>
+        <v>55.76</v>
       </c>
       <c r="E156" s="9">
-        <v>0.9399999999999999</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="6" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C157" s="7">
-        <v>-4.18</v>
+        <v>62.78</v>
       </c>
       <c r="D157" s="7">
-        <v>-55.8</v>
+        <v>59.65</v>
       </c>
       <c r="E157" s="8">
-        <v>-51.62</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="6" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C158" s="7">
-        <v>-69.83</v>
+        <v>43.32</v>
       </c>
       <c r="D158" s="7">
-        <v>-79.16</v>
-      </c>
-      <c r="E158" s="8">
-        <v>-9.33</v>
+        <v>44.55</v>
+      </c>
+      <c r="E158" s="9">
+        <v>1.23</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C159" s="7">
-        <v>20</v>
+        <v>57.92</v>
       </c>
       <c r="D159" s="7">
-        <v>-26.57</v>
-      </c>
-      <c r="E159" s="8">
-        <v>-46.57</v>
+        <v>58.33</v>
+      </c>
+      <c r="E159" s="9">
+        <v>0.41</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C160" s="7">
-        <v>114.41</v>
+        <v>55.49</v>
       </c>
       <c r="D160" s="7">
-        <v>-39.71</v>
-      </c>
-      <c r="E160" s="8">
-        <v>-154.12</v>
+        <v>56.16</v>
+      </c>
+      <c r="E160" s="9">
+        <v>0.67</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C161" s="7">
-        <v>-9.75</v>
+        <v>65.03</v>
       </c>
       <c r="D161" s="7">
-        <v>22.18</v>
-      </c>
-      <c r="E161" s="9">
-        <v>31.93</v>
+        <v>63.28</v>
+      </c>
+      <c r="E161" s="8">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="7">
-        <v>35.22</v>
+        <v>-55.8</v>
       </c>
       <c r="D162" s="7">
-        <v>-33.8</v>
-      </c>
-      <c r="E162" s="8">
-        <v>-69.02</v>
+        <v>-54.87</v>
+      </c>
+      <c r="E162" s="9">
+        <v>0.93</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="7">
-        <v>2.54</v>
+        <v>-79.16</v>
       </c>
       <c r="D163" s="7">
-        <v>-17.51</v>
+        <v>-86.98</v>
       </c>
       <c r="E163" s="8">
-        <v>-20.05</v>
+        <v>-7.82</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="7">
-        <v>35.3</v>
+        <v>-26.57</v>
       </c>
       <c r="D164" s="7">
-        <v>-62.43</v>
+        <v>-34.59</v>
       </c>
       <c r="E164" s="8">
-        <v>-97.73</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="7">
-        <v>-62.52</v>
+        <v>-39.71</v>
       </c>
       <c r="D165" s="7">
-        <v>-63.46</v>
-      </c>
-      <c r="E165" s="8">
-        <v>-0.9399999999999999</v>
+        <v>75.04000000000001</v>
+      </c>
+      <c r="E165" s="9">
+        <v>114.75</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>-30.3</v>
+        <v>22.18</v>
       </c>
       <c r="D166" s="7">
-        <v>-64.38</v>
+        <v>3.61</v>
       </c>
       <c r="E166" s="8">
-        <v>-34.08</v>
+        <v>-18.57</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>-20.85</v>
+        <v>-33.8</v>
       </c>
       <c r="D167" s="7">
-        <v>-32.96</v>
-      </c>
-      <c r="E167" s="8">
-        <v>-12.11</v>
+        <v>-30.89</v>
+      </c>
+      <c r="E167" s="9">
+        <v>2.91</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>2.49</v>
+        <v>-17.51</v>
       </c>
       <c r="D168" s="7">
-        <v>-33.99</v>
+        <v>-45.88</v>
       </c>
       <c r="E168" s="8">
-        <v>-36.48</v>
+        <v>-28.37</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>-27.98</v>
+        <v>-62.43</v>
       </c>
       <c r="D169" s="7">
-        <v>151.83</v>
+        <v>5.08</v>
       </c>
       <c r="E169" s="9">
-        <v>179.81</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>-27.27</v>
+        <v>-63.46</v>
       </c>
       <c r="D170" s="7">
-        <v>-35.95</v>
-      </c>
-      <c r="E170" s="8">
-        <v>-8.68</v>
+        <v>-57.72</v>
+      </c>
+      <c r="E170" s="9">
+        <v>5.74</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-24.28</v>
+        <v>-64.38</v>
       </c>
       <c r="D171" s="7">
-        <v>-17.38</v>
-      </c>
-      <c r="E171" s="9">
-        <v>6.9</v>
+        <v>-69.5</v>
+      </c>
+      <c r="E171" s="8">
+        <v>-5.12</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>42.18</v>
+        <v>-32.96</v>
       </c>
       <c r="D172" s="7">
-        <v>-42.57</v>
-      </c>
-      <c r="E172" s="8">
-        <v>-84.75</v>
+        <v>82.19</v>
+      </c>
+      <c r="E172" s="9">
+        <v>115.15</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C173" s="7">
-        <v>-89.36</v>
+        <v>-33.99</v>
       </c>
       <c r="D173" s="7">
-        <v>-90.04000000000001</v>
+        <v>-42.33</v>
       </c>
       <c r="E173" s="8">
-        <v>-0.68</v>
+        <v>-8.34</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C174" s="7">
-        <v>50</v>
+        <v>151.83</v>
       </c>
       <c r="D174" s="7">
-        <v>14.35</v>
+        <v>-57.02</v>
       </c>
       <c r="E174" s="8">
-        <v>-35.65</v>
+        <v>-208.85</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C175" s="7">
-        <v>1.4</v>
+        <v>-35.95</v>
       </c>
       <c r="D175" s="7">
-        <v>-33.5</v>
+        <v>-78.41</v>
       </c>
       <c r="E175" s="8">
-        <v>-34.9</v>
+        <v>-42.46</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C176" s="7">
-        <v>-6.24</v>
+        <v>-17.38</v>
       </c>
       <c r="D176" s="7">
+        <v>-59.55</v>
+      </c>
+      <c r="E176" s="8">
+        <v>-42.17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177" s="7">
+        <v>-42.57</v>
+      </c>
+      <c r="D177" s="7">
+        <v>-35</v>
+      </c>
+      <c r="E177" s="9">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="7">
+        <v>-90.04000000000001</v>
+      </c>
+      <c r="D178" s="7">
+        <v>-88.69</v>
+      </c>
+      <c r="E178" s="9">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C179" s="7">
+        <v>14.35</v>
+      </c>
+      <c r="D179" s="7">
+        <v>-21.85</v>
+      </c>
+      <c r="E179" s="8">
+        <v>-36.2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C180" s="7">
+        <v>-33.5</v>
+      </c>
+      <c r="D180" s="7">
+        <v>-43.91</v>
+      </c>
+      <c r="E180" s="8">
+        <v>-10.41</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C181" s="7">
         <v>-52.76</v>
       </c>
-      <c r="E176" s="8">
-        <v>-46.52</v>
+      <c r="D181" s="7">
+        <v>22.54</v>
+      </c>
+      <c r="E181" s="9">
+        <v>75.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6326,28 +6413,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6361,7 +6448,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="E2" s="12">
         <v>40</v>
@@ -6370,7 +6457,7 @@
         <v>2.9</v>
       </c>
       <c r="G2" s="12">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H2" s="12">
         <v>52.6</v>
@@ -6496,10 +6583,10 @@
         <v>44</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>37</v>
@@ -6510,45 +6597,45 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5396</v>
+        <v>0.5399</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3308</v>
+        <v>0.3294</v>
       </c>
       <c r="C2" s="15">
-        <v>0.304</v>
+        <v>0.3051</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2932</v>
+        <v>0.2938</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2538</v>
+        <v>0.2517</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1549</v>
+        <v>0.1555</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1434</v>
+        <v>0.143</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1432</v>
+        <v>0.1425</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1045</v>
+        <v>0.1044</v>
       </c>
       <c r="J2" s="15">
-        <v>0.09380000000000001</v>
+        <v>0.0931</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>48</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>53</v>
@@ -6574,34 +6661,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0935</v>
+        <v>0.0929</v>
       </c>
       <c r="B4" s="15">
-        <v>0.0935</v>
+        <v>0.0929</v>
       </c>
       <c r="C4" s="15">
-        <v>0.0931</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="D4" s="15">
-        <v>0.08359999999999999</v>
+        <v>0.08460000000000001</v>
       </c>
       <c r="E4" s="15">
-        <v>0.077</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="F4" s="15">
-        <v>0.07240000000000001</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G4" s="15">
-        <v>0.0117</v>
+        <v>0.0105</v>
       </c>
       <c r="H4" s="15">
-        <v>0.0086</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.0837</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.3034</v>
+        <v>-0.3036</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="102">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,12 +196,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -211,7 +211,82 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.9 → 49.8</t>
+  </si>
+  <si>
+    <t>51.9</t>
+  </si>
+  <si>
+    <t>49.8</t>
+  </si>
+  <si>
+    <t>63.2 → 49.0</t>
+  </si>
+  <si>
+    <t>63.2</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>56.2 → 47.8</t>
+  </si>
+  <si>
+    <t>56.2</t>
+  </si>
+  <si>
+    <t>47.8</t>
+  </si>
+  <si>
+    <t>55.2 → 47.5</t>
+  </si>
+  <si>
+    <t>55.2</t>
+  </si>
+  <si>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>55.1 → 47.7</t>
+  </si>
+  <si>
+    <t>55.1</t>
+  </si>
+  <si>
+    <t>47.7</t>
+  </si>
+  <si>
+    <t>55.8 → 47.5</t>
+  </si>
+  <si>
+    <t>55.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -413,14 +488,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -935,10 +1011,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>596.37</v>
+        <v>594.86</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -947,25 +1023,25 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-6.21</v>
+        <v>-6.45</v>
       </c>
       <c r="H2">
-        <v>14.49</v>
+        <v>14.2</v>
       </c>
       <c r="I2">
-        <v>-0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="J2">
-        <v>-1.41</v>
+        <v>-0.89</v>
       </c>
       <c r="K2">
-        <v>7.82</v>
+        <v>7.69</v>
       </c>
       <c r="L2">
-        <v>4.71</v>
+        <v>4.25</v>
       </c>
       <c r="M2">
-        <v>10.54</v>
+        <v>10.66</v>
       </c>
       <c r="N2">
         <v>68</v>
@@ -974,16 +1050,16 @@
         <v>596.92</v>
       </c>
       <c r="Q2">
-        <v>594.5</v>
+        <v>594.27</v>
       </c>
       <c r="R2">
-        <v>594.2</v>
+        <v>594.71</v>
       </c>
       <c r="S2">
-        <v>593.1</v>
+        <v>593.0700000000001</v>
       </c>
       <c r="T2">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -995,37 +1071,37 @@
         <v>58</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>51.92</v>
+        <v>49.78</v>
       </c>
       <c r="Z2">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="AA2">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AB2">
-        <v>-0.07000000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="AC2">
-        <v>54.2</v>
+        <v>33.93</v>
       </c>
       <c r="AD2">
-        <v>64.28</v>
+        <v>52.72</v>
       </c>
       <c r="AE2">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="AF2">
-        <v>13.15</v>
+        <v>-18.36</v>
       </c>
       <c r="AG2">
-        <v>602.79</v>
+        <v>602.22</v>
       </c>
       <c r="AH2">
-        <v>586.21</v>
+        <v>586.3200000000001</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1034,7 +1110,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>19.46</v>
+        <v>22.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1045,10 +1121,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>59.77</v>
+        <v>59.63</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1057,43 +1133,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.62</v>
+        <v>-90.64</v>
       </c>
       <c r="H3">
-        <v>14.68</v>
+        <v>14.41</v>
       </c>
       <c r="I3">
-        <v>-0.37</v>
+        <v>-0.1</v>
       </c>
       <c r="J3">
-        <v>-1.55</v>
+        <v>-0.91</v>
       </c>
       <c r="K3">
-        <v>7.83</v>
+        <v>7.99</v>
       </c>
       <c r="L3">
-        <v>-89.51000000000001</v>
+        <v>-89.54000000000001</v>
       </c>
       <c r="M3">
-        <v>-30.27</v>
+        <v>-30.18</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.85</v>
+        <v>59.84</v>
       </c>
       <c r="Q3">
-        <v>59.62</v>
+        <v>59.61</v>
       </c>
       <c r="R3">
-        <v>59.59</v>
+        <v>59.64</v>
       </c>
       <c r="S3">
-        <v>289.16</v>
+        <v>286.45</v>
       </c>
       <c r="T3">
-        <v>-79.33</v>
+        <v>-79.18000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1102,37 +1178,37 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>49.87</v>
+        <v>48.17</v>
       </c>
       <c r="Z3">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="AA3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>44.24</v>
+        <v>28.81</v>
       </c>
       <c r="AD3">
-        <v>56.63</v>
+        <v>44.98</v>
       </c>
       <c r="AE3">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>-85</v>
+        <v>40.81</v>
       </c>
       <c r="AG3">
-        <v>60.51</v>
+        <v>60.48</v>
       </c>
       <c r="AH3">
         <v>58.74</v>
@@ -1144,7 +1220,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>15.63</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1155,10 +1231,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>93.84999999999999</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1167,94 +1243,94 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-13.75</v>
+        <v>-13.62</v>
       </c>
       <c r="H4">
-        <v>6.85</v>
+        <v>7.01</v>
       </c>
       <c r="I4">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="J4">
-        <v>-1.92</v>
+        <v>-2.87</v>
       </c>
       <c r="K4">
-        <v>-10.34</v>
+        <v>-10.21</v>
       </c>
       <c r="L4">
-        <v>3.92</v>
+        <v>3.19</v>
       </c>
       <c r="M4">
-        <v>29.54</v>
+        <v>29.74</v>
       </c>
       <c r="N4">
         <v>16</v>
       </c>
       <c r="P4">
-        <v>93.95</v>
+        <v>93.98</v>
       </c>
       <c r="Q4">
-        <v>94.83</v>
+        <v>94.69</v>
       </c>
       <c r="R4">
-        <v>96.26000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="S4">
         <v>97.93000000000001</v>
       </c>
       <c r="T4">
-        <v>-4.17</v>
+        <v>-4.02</v>
       </c>
       <c r="U4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.45</v>
+        <v>37.39</v>
       </c>
       <c r="Z4">
-        <v>-0.8100000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="AA4">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="AB4">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AC4">
-        <v>72.98999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="AD4">
-        <v>61.09</v>
+        <v>67.09</v>
       </c>
       <c r="AE4">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AF4">
-        <v>53.29</v>
+        <v>10.05</v>
       </c>
       <c r="AG4">
-        <v>96.95</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="AH4">
-        <v>92.70999999999999</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="AI4">
-        <v>99.72</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>11.03</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1265,10 +1341,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>51.98</v>
+        <v>51.35</v>
       </c>
       <c r="D5">
-        <v>-0.73</v>
+        <v>-1.21</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1277,43 +1353,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-14.79</v>
+        <v>-15.82</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>5.51</v>
       </c>
       <c r="I5">
-        <v>-1.89</v>
+        <v>-2.3</v>
       </c>
       <c r="J5">
-        <v>-0.63</v>
+        <v>-2.41</v>
       </c>
       <c r="K5">
-        <v>-3.94</v>
+        <v>-4.61</v>
       </c>
       <c r="L5">
-        <v>-11.37</v>
+        <v>-12.52</v>
       </c>
       <c r="M5">
-        <v>6.89</v>
+        <v>6.34</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>52.27</v>
+        <v>52.03</v>
       </c>
       <c r="Q5">
-        <v>52.77</v>
+        <v>52.71</v>
       </c>
       <c r="R5">
-        <v>52.76</v>
+        <v>52.75</v>
       </c>
       <c r="S5">
-        <v>54.67</v>
+        <v>54.63</v>
       </c>
       <c r="T5">
-        <v>-4.92</v>
+        <v>-6</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1322,40 +1398,40 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.55</v>
+        <v>34.79</v>
       </c>
       <c r="Z5">
-        <v>-0.13</v>
+        <v>-0.22</v>
       </c>
       <c r="AA5">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AB5">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="AC5">
-        <v>23.35</v>
+        <v>11.56</v>
       </c>
       <c r="AD5">
-        <v>19.07</v>
+        <v>19</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>24.43</v>
+        <v>208.84</v>
       </c>
       <c r="AG5">
-        <v>53.55</v>
+        <v>53.72</v>
       </c>
       <c r="AH5">
-        <v>51.98</v>
+        <v>51.71</v>
       </c>
       <c r="AI5">
         <v>54.72</v>
@@ -1364,7 +1440,7 @@
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>23.16</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1375,10 +1451,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>125.13</v>
+        <v>126.43</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1387,94 +1463,94 @@
         <v>82.08</v>
       </c>
       <c r="G6">
-        <v>-14.6</v>
+        <v>-13.72</v>
       </c>
       <c r="H6">
-        <v>52.45</v>
+        <v>54.03</v>
       </c>
       <c r="I6">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="J6">
-        <v>8.07</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K6">
-        <v>-3.89</v>
+        <v>-3.3</v>
       </c>
       <c r="L6">
-        <v>50.8</v>
+        <v>51.98</v>
       </c>
       <c r="M6">
-        <v>24.9</v>
+        <v>25.25</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>125.54</v>
+        <v>125.72</v>
       </c>
       <c r="Q6">
-        <v>120.61</v>
+        <v>121.05</v>
       </c>
       <c r="R6">
-        <v>119.49</v>
+        <v>119.51</v>
       </c>
       <c r="S6">
-        <v>119.74</v>
+        <v>119.87</v>
       </c>
       <c r="T6">
-        <v>4.51</v>
+        <v>5.47</v>
       </c>
       <c r="U6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X6">
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>66.41</v>
+        <v>69.69</v>
       </c>
       <c r="Z6">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AA6">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AB6">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AC6">
-        <v>79.33</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="AD6">
-        <v>86.88</v>
+        <v>82.39</v>
       </c>
       <c r="AE6">
         <v>1.71</v>
       </c>
       <c r="AF6">
-        <v>10.82</v>
+        <v>-33.97</v>
       </c>
       <c r="AG6">
-        <v>127.88</v>
+        <v>128.63</v>
       </c>
       <c r="AH6">
-        <v>113.34</v>
+        <v>113.47</v>
       </c>
       <c r="AI6">
-        <v>120.92</v>
+        <v>121.38</v>
       </c>
       <c r="AJ6" t="s">
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>38.1</v>
+        <v>39.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1485,10 +1561,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>130.62</v>
+        <v>130.71</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1497,22 +1573,22 @@
         <v>84.73999999999999</v>
       </c>
       <c r="G7">
-        <v>-13.71</v>
+        <v>-13.65</v>
       </c>
       <c r="H7">
-        <v>54.14</v>
+        <v>54.25</v>
       </c>
       <c r="I7">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="J7">
-        <v>9.1</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K7">
-        <v>-2.93</v>
+        <v>-3.2</v>
       </c>
       <c r="L7">
-        <v>52.58</v>
+        <v>52.18</v>
       </c>
       <c r="M7">
         <v>33.26</v>
@@ -1521,70 +1597,70 @@
         <v>94</v>
       </c>
       <c r="P7">
-        <v>129.99</v>
+        <v>130.18</v>
       </c>
       <c r="Q7">
-        <v>124.7</v>
+        <v>125.15</v>
       </c>
       <c r="R7">
-        <v>123.54</v>
+        <v>123.56</v>
       </c>
       <c r="S7">
-        <v>123.69</v>
+        <v>123.83</v>
       </c>
       <c r="T7">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="U7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X7">
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>69.77</v>
+        <v>69.97</v>
       </c>
       <c r="Z7">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA7">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AB7">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC7">
-        <v>83.70999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AD7">
-        <v>88.59999999999999</v>
+        <v>85.52</v>
       </c>
       <c r="AE7">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="AF7">
-        <v>15.19</v>
+        <v>-22.11</v>
       </c>
       <c r="AG7">
-        <v>132.38</v>
+        <v>133.14</v>
       </c>
       <c r="AH7">
-        <v>117.02</v>
+        <v>117.16</v>
       </c>
       <c r="AI7">
-        <v>123.87</v>
+        <v>124.53</v>
       </c>
       <c r="AJ7" t="s">
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>40.86</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1595,10 +1671,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>482.66</v>
+        <v>481.22</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1607,85 +1683,85 @@
         <v>441.2</v>
       </c>
       <c r="G8">
-        <v>-14.78</v>
+        <v>-15.03</v>
       </c>
       <c r="H8">
-        <v>9.4</v>
+        <v>9.07</v>
       </c>
       <c r="I8">
-        <v>-1.19</v>
+        <v>-0.67</v>
       </c>
       <c r="J8">
-        <v>0.59</v>
+        <v>-0.75</v>
       </c>
       <c r="K8">
-        <v>-10.08</v>
+        <v>-9.56</v>
       </c>
       <c r="L8">
-        <v>10.95</v>
+        <v>7.99</v>
       </c>
       <c r="M8">
-        <v>7.83</v>
+        <v>7.75</v>
       </c>
       <c r="N8">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>482.02</v>
+        <v>481.37</v>
       </c>
       <c r="Q8">
-        <v>487.14</v>
+        <v>487.04</v>
       </c>
       <c r="R8">
-        <v>483.58</v>
+        <v>483.23</v>
       </c>
       <c r="S8">
-        <v>511.26</v>
+        <v>511.05</v>
       </c>
       <c r="T8">
-        <v>-5.59</v>
+        <v>-5.84</v>
       </c>
       <c r="U8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>45.49</v>
+        <v>43.82</v>
       </c>
       <c r="Z8">
-        <v>-1.03</v>
+        <v>-1.25</v>
       </c>
       <c r="AA8">
-        <v>-0.16</v>
+        <v>-0.38</v>
       </c>
       <c r="AB8">
         <v>-0.87</v>
       </c>
       <c r="AC8">
-        <v>12.77</v>
+        <v>16.12</v>
       </c>
       <c r="AD8">
-        <v>6.39</v>
+        <v>11.76</v>
       </c>
       <c r="AE8">
-        <v>10.66</v>
+        <v>10.29</v>
       </c>
       <c r="AF8">
-        <v>-24.82</v>
+        <v>31.71</v>
       </c>
       <c r="AG8">
-        <v>497.78</v>
+        <v>497.88</v>
       </c>
       <c r="AH8">
-        <v>476.5</v>
+        <v>476.19</v>
       </c>
       <c r="AI8">
         <v>511.37</v>
@@ -1694,7 +1770,7 @@
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>23.96</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1705,10 +1781,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>976.9299999999999</v>
+        <v>973.6799999999999</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1717,82 +1793,82 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-3.16</v>
+        <v>-3.49</v>
       </c>
       <c r="H9">
-        <v>10.38</v>
+        <v>10.01</v>
       </c>
       <c r="I9">
-        <v>-0.37</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J9">
-        <v>0.99</v>
+        <v>-0.04</v>
       </c>
       <c r="K9">
-        <v>1.45</v>
+        <v>0.87</v>
       </c>
       <c r="L9">
-        <v>5.39</v>
+        <v>4.58</v>
       </c>
       <c r="M9">
-        <v>15.67</v>
+        <v>15.43</v>
       </c>
       <c r="N9">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="P9">
-        <v>972.77</v>
+        <v>972.9</v>
       </c>
       <c r="Q9">
-        <v>970.1799999999999</v>
+        <v>970.16</v>
       </c>
       <c r="R9">
-        <v>968.88</v>
+        <v>969.48</v>
       </c>
       <c r="S9">
-        <v>965.79</v>
+        <v>965.71</v>
       </c>
       <c r="T9">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="U9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X9">
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>55.26</v>
+        <v>52.2</v>
       </c>
       <c r="Z9">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AA9">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="AC9">
-        <v>44.52</v>
+        <v>48.41</v>
       </c>
       <c r="AD9">
-        <v>38.46</v>
+        <v>43.42</v>
       </c>
       <c r="AE9">
-        <v>11.63</v>
+        <v>11.33</v>
       </c>
       <c r="AF9">
-        <v>22.27</v>
+        <v>-49.16</v>
       </c>
       <c r="AG9">
-        <v>984.52</v>
+        <v>984.46</v>
       </c>
       <c r="AH9">
         <v>955.85</v>
@@ -1804,7 +1880,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>18.53</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1815,10 +1891,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>34.75</v>
+        <v>33.69</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>-3.05</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1827,85 +1903,85 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-19.5</v>
+        <v>-21.96</v>
       </c>
       <c r="H10">
-        <v>21.42</v>
+        <v>17.71</v>
       </c>
       <c r="I10">
-        <v>-0.88</v>
+        <v>-4.34</v>
       </c>
       <c r="J10">
-        <v>7.25</v>
+        <v>3.82</v>
       </c>
       <c r="K10">
-        <v>7.99</v>
+        <v>5.31</v>
       </c>
       <c r="L10">
-        <v>-8.039999999999999</v>
+        <v>-10.71</v>
       </c>
       <c r="M10">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="N10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P10">
-        <v>34.82</v>
+        <v>34.52</v>
       </c>
       <c r="Q10">
-        <v>34.01</v>
+        <v>34.09</v>
       </c>
       <c r="R10">
-        <v>32.15</v>
+        <v>32.19</v>
       </c>
       <c r="S10">
-        <v>35.74</v>
+        <v>35.71</v>
       </c>
       <c r="T10">
-        <v>-2.76</v>
+        <v>-5.66</v>
       </c>
       <c r="U10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X10">
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>62.87</v>
+        <v>50.28</v>
       </c>
       <c r="Z10">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="AA10">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AB10">
-        <v>-0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="AC10">
-        <v>9.890000000000001</v>
+        <v>4.69</v>
       </c>
       <c r="AD10">
-        <v>26.61</v>
+        <v>12.05</v>
       </c>
       <c r="AE10">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>-67.45999999999999</v>
+        <v>-60.76</v>
       </c>
       <c r="AG10">
-        <v>36.41</v>
+        <v>36.34</v>
       </c>
       <c r="AH10">
-        <v>31.61</v>
+        <v>31.84</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -1914,7 +1990,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>39.96</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1925,10 +2001,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>34.81</v>
+        <v>33.58</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>-3.53</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1937,85 +2013,85 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-19.59</v>
+        <v>-22.43</v>
       </c>
       <c r="H11">
-        <v>21.59</v>
+        <v>17.29</v>
       </c>
       <c r="I11">
-        <v>-0.85</v>
+        <v>-4.71</v>
       </c>
       <c r="J11">
-        <v>7.31</v>
+        <v>3.71</v>
       </c>
       <c r="K11">
-        <v>7.84</v>
+        <v>4.68</v>
       </c>
       <c r="L11">
-        <v>-8.1</v>
+        <v>-11.4</v>
       </c>
       <c r="M11">
-        <v>0.44</v>
+        <v>-0.28</v>
       </c>
       <c r="N11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P11">
-        <v>34.86</v>
+        <v>34.52</v>
       </c>
       <c r="Q11">
-        <v>34.04</v>
+        <v>34.11</v>
       </c>
       <c r="R11">
-        <v>32.17</v>
+        <v>32.2</v>
       </c>
       <c r="S11">
-        <v>35.81</v>
+        <v>35.78</v>
       </c>
       <c r="T11">
-        <v>-2.79</v>
+        <v>-6.15</v>
       </c>
       <c r="U11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>63.22</v>
+        <v>49.01</v>
       </c>
       <c r="Z11">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="AA11">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="AB11">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="AC11">
-        <v>14.64</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AD11">
-        <v>29.47</v>
+        <v>15.68</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>-55.27</v>
+        <v>-40.98</v>
       </c>
       <c r="AG11">
-        <v>36.48</v>
+        <v>36.4</v>
       </c>
       <c r="AH11">
-        <v>31.59</v>
+        <v>31.81</v>
       </c>
       <c r="AI11">
         <v>32.2</v>
@@ -2024,7 +2100,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>39.1</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2035,10 +2111,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>807.8099999999999</v>
+        <v>805.9</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2047,85 +2123,85 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-0.15</v>
+        <v>-0.38</v>
       </c>
       <c r="H12">
-        <v>23.92</v>
+        <v>23.62</v>
       </c>
       <c r="I12">
-        <v>-0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="J12">
-        <v>4.08</v>
+        <v>3.12</v>
       </c>
       <c r="K12">
-        <v>8.07</v>
+        <v>7.51</v>
       </c>
       <c r="L12">
-        <v>13.64</v>
+        <v>12.56</v>
       </c>
       <c r="M12">
-        <v>14.2</v>
+        <v>14.02</v>
       </c>
       <c r="N12">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P12">
-        <v>807.46</v>
+        <v>807.1</v>
       </c>
       <c r="Q12">
-        <v>795.6799999999999</v>
+        <v>796.76</v>
       </c>
       <c r="R12">
-        <v>782.62</v>
+        <v>783.63</v>
       </c>
       <c r="S12">
-        <v>749.4299999999999</v>
+        <v>749.7</v>
       </c>
       <c r="T12">
-        <v>7.79</v>
+        <v>7.5</v>
       </c>
       <c r="U12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X12">
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>68.47</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="Z12">
-        <v>8.41</v>
+        <v>7.99</v>
       </c>
       <c r="AA12">
-        <v>7.92</v>
+        <v>7.93</v>
       </c>
       <c r="AB12">
-        <v>0.49</v>
+        <v>0.06</v>
       </c>
       <c r="AC12">
-        <v>83.52</v>
+        <v>74.73</v>
       </c>
       <c r="AD12">
-        <v>84.06999999999999</v>
+        <v>80.52</v>
       </c>
       <c r="AE12">
-        <v>15.27</v>
+        <v>14.89</v>
       </c>
       <c r="AF12">
-        <v>-21.81</v>
+        <v>-22.06</v>
       </c>
       <c r="AG12">
-        <v>821.4299999999999</v>
+        <v>822.3200000000001</v>
       </c>
       <c r="AH12">
-        <v>769.9299999999999</v>
+        <v>771.1900000000001</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2134,7 +2210,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>26.7</v>
+        <v>28.58</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2145,10 +2221,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>278.35</v>
+        <v>276.1</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2157,85 +2233,85 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-6.45</v>
+        <v>-7.21</v>
       </c>
       <c r="H13">
-        <v>9.83</v>
+        <v>8.94</v>
       </c>
       <c r="I13">
-        <v>-0.75</v>
+        <v>-1.09</v>
       </c>
       <c r="J13">
-        <v>0.68</v>
+        <v>0.19</v>
       </c>
       <c r="K13">
-        <v>3.84</v>
+        <v>2.94</v>
       </c>
       <c r="L13">
-        <v>0.65</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M13">
-        <v>9.24</v>
+        <v>9.08</v>
       </c>
       <c r="N13">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="P13">
-        <v>278.46</v>
+        <v>277.86</v>
       </c>
       <c r="Q13">
-        <v>277.02</v>
+        <v>277.07</v>
       </c>
       <c r="R13">
-        <v>274.17</v>
+        <v>274.41</v>
       </c>
       <c r="S13">
-        <v>279.85</v>
+        <v>279.77</v>
       </c>
       <c r="T13">
-        <v>-0.54</v>
+        <v>-1.31</v>
       </c>
       <c r="U13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>56.25</v>
+        <v>47.76</v>
       </c>
       <c r="Z13">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB13">
-        <v>-0.15</v>
+        <v>-0.34</v>
       </c>
       <c r="AC13">
-        <v>23.65</v>
+        <v>13.44</v>
       </c>
       <c r="AD13">
-        <v>38.4</v>
+        <v>25.73</v>
       </c>
       <c r="AE13">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AF13">
-        <v>-9.08</v>
+        <v>-13.01</v>
       </c>
       <c r="AG13">
         <v>282.92</v>
       </c>
       <c r="AH13">
-        <v>271.12</v>
+        <v>271.22</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2244,7 +2320,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>11.67</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2255,10 +2331,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>270.55</v>
+        <v>268.59</v>
       </c>
       <c r="D14">
-        <v>0.03</v>
+        <v>-0.72</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2267,70 +2343,70 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-6.58</v>
+        <v>-7.26</v>
       </c>
       <c r="H14">
-        <v>9.73</v>
+        <v>8.93</v>
       </c>
       <c r="I14">
-        <v>-0.8100000000000001</v>
+        <v>-1.15</v>
       </c>
       <c r="J14">
-        <v>0.5600000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="K14">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="M14">
-        <v>-8.33</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="P14">
-        <v>270.82</v>
+        <v>270.2</v>
       </c>
       <c r="Q14">
-        <v>269.48</v>
+        <v>269.53</v>
       </c>
       <c r="R14">
-        <v>266.93</v>
+        <v>267.17</v>
       </c>
       <c r="U14" t="s">
+        <v>59</v>
+      </c>
+      <c r="W14" t="s">
         <v>58</v>
-      </c>
-      <c r="W14" t="s">
-        <v>59</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>55.43</v>
+        <v>47.52</v>
       </c>
       <c r="Z14">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AA14">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
       <c r="AC14">
-        <v>24.38</v>
+        <v>11.46</v>
       </c>
       <c r="AD14">
-        <v>41.39</v>
+        <v>26.09</v>
       </c>
       <c r="AE14">
-        <v>3.67</v>
+        <v>3.79</v>
       </c>
       <c r="AF14">
-        <v>-28.48</v>
+        <v>-12.95</v>
       </c>
       <c r="AG14">
         <v>274.98</v>
       </c>
       <c r="AH14">
-        <v>263.99</v>
+        <v>264.08</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2339,7 +2415,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>54.58</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2350,10 +2426,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>265.71</v>
+        <v>263.65</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2362,85 +2438,85 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-6.54</v>
+        <v>-7.27</v>
       </c>
       <c r="H15">
-        <v>10.02</v>
+        <v>9.17</v>
       </c>
       <c r="I15">
-        <v>-0.75</v>
+        <v>-1.1</v>
       </c>
       <c r="J15">
-        <v>0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="K15">
-        <v>3.87</v>
+        <v>3.22</v>
       </c>
       <c r="L15">
-        <v>0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="M15">
-        <v>9.220000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="N15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P15">
-        <v>265.78</v>
+        <v>265.19</v>
       </c>
       <c r="Q15">
-        <v>264.6</v>
+        <v>264.63</v>
       </c>
       <c r="R15">
-        <v>261.89</v>
+        <v>262.12</v>
       </c>
       <c r="S15">
-        <v>267.16</v>
+        <v>267.08</v>
       </c>
       <c r="T15">
-        <v>-0.54</v>
+        <v>-1.28</v>
       </c>
       <c r="U15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
       </c>
       <c r="W15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>55.06</v>
+        <v>47.67</v>
       </c>
       <c r="Z15">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AA15">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AB15">
-        <v>-0.2</v>
+        <v>-0.37</v>
       </c>
       <c r="AC15">
-        <v>24.53</v>
+        <v>15.25</v>
       </c>
       <c r="AD15">
-        <v>37.71</v>
+        <v>26.17</v>
       </c>
       <c r="AE15">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AF15">
-        <v>-12.87</v>
+        <v>61.19</v>
       </c>
       <c r="AG15">
         <v>270.53</v>
       </c>
       <c r="AH15">
-        <v>258.68</v>
+        <v>258.72</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2449,7 +2525,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>32.97</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2460,10 +2536,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>276.84</v>
+        <v>274.6</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2472,85 +2548,85 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-6.47</v>
+        <v>-7.22</v>
       </c>
       <c r="H16">
-        <v>9.85</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I16">
-        <v>-0.95</v>
+        <v>-1.1</v>
       </c>
       <c r="J16">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="K16">
-        <v>3.76</v>
+        <v>2.93</v>
       </c>
       <c r="L16">
-        <v>0.6</v>
+        <v>-0.75</v>
       </c>
       <c r="M16">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N16">
         <v>37</v>
       </c>
       <c r="P16">
-        <v>276.98</v>
+        <v>276.37</v>
       </c>
       <c r="Q16">
-        <v>275.6</v>
+        <v>275.64</v>
       </c>
       <c r="R16">
-        <v>272.78</v>
+        <v>273.02</v>
       </c>
       <c r="S16">
-        <v>278.47</v>
+        <v>278.38</v>
       </c>
       <c r="T16">
-        <v>-0.58</v>
+        <v>-1.36</v>
       </c>
       <c r="U16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V16" t="b">
         <v>0</v>
       </c>
       <c r="W16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>55.76</v>
+        <v>47.51</v>
       </c>
       <c r="Z16">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="AA16">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB16">
-        <v>-0.16</v>
+        <v>-0.35</v>
       </c>
       <c r="AC16">
-        <v>20.27</v>
+        <v>10.52</v>
       </c>
       <c r="AD16">
-        <v>35.42</v>
+        <v>22.56</v>
       </c>
       <c r="AE16">
-        <v>3.81</v>
+        <v>4.06</v>
       </c>
       <c r="AF16">
-        <v>5.7</v>
+        <v>-51.29</v>
       </c>
       <c r="AG16">
         <v>281.51</v>
       </c>
       <c r="AH16">
-        <v>269.7</v>
+        <v>269.78</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2559,7 +2635,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>59.3</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2570,10 +2646,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>97.52</v>
+        <v>96.52</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2582,85 +2658,85 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-11.24</v>
+        <v>-12.15</v>
       </c>
       <c r="H17">
-        <v>29.66</v>
+        <v>28.33</v>
       </c>
       <c r="I17">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J17">
-        <v>4.21</v>
+        <v>0.37</v>
       </c>
       <c r="K17">
-        <v>9.279999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="L17">
-        <v>24.28</v>
+        <v>23.14</v>
       </c>
       <c r="M17">
-        <v>30.87</v>
+        <v>30.6</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>97.56999999999999</v>
+        <v>97.59</v>
       </c>
       <c r="Q17">
-        <v>95.27</v>
+        <v>95.33</v>
       </c>
       <c r="R17">
-        <v>95.02</v>
+        <v>95.05</v>
       </c>
       <c r="S17">
-        <v>95.7</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="T17">
-        <v>1.9</v>
+        <v>0.82</v>
       </c>
       <c r="U17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V17" t="b">
         <v>0</v>
       </c>
       <c r="W17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X17">
         <v>2</v>
       </c>
       <c r="Y17">
-        <v>59.65</v>
+        <v>54.32</v>
       </c>
       <c r="Z17">
-        <v>1.01</v>
+        <v>0.93</v>
       </c>
       <c r="AA17">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AB17">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="AC17">
-        <v>74.64</v>
+        <v>58.99</v>
       </c>
       <c r="AD17">
-        <v>78.23</v>
+        <v>71.77</v>
       </c>
       <c r="AE17">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AF17">
-        <v>-35.25</v>
+        <v>-49.64</v>
       </c>
       <c r="AG17">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AH17">
-        <v>91.23999999999999</v>
+        <v>91.25</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2669,7 +2745,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>42.72</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2680,10 +2756,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>279.76</v>
+        <v>278.01</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2692,85 +2768,85 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.66</v>
+        <v>-6.25</v>
       </c>
       <c r="H18">
-        <v>13.92</v>
+        <v>13.21</v>
       </c>
       <c r="I18">
-        <v>-0.61</v>
+        <v>-0.78</v>
       </c>
       <c r="J18">
-        <v>-3.94</v>
+        <v>-2.36</v>
       </c>
       <c r="K18">
-        <v>5.41</v>
+        <v>4.74</v>
       </c>
       <c r="L18">
-        <v>3.42</v>
+        <v>2.33</v>
       </c>
       <c r="M18">
-        <v>8.470000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="N18">
+        <v>63</v>
+      </c>
+      <c r="P18">
+        <v>279.37</v>
+      </c>
+      <c r="Q18">
+        <v>280.82</v>
+      </c>
+      <c r="R18">
+        <v>283.24</v>
+      </c>
+      <c r="S18">
+        <v>281.41</v>
+      </c>
+      <c r="T18">
+        <v>-1.21</v>
+      </c>
+      <c r="U18" t="s">
         <v>58</v>
-      </c>
-      <c r="P18">
-        <v>279.81</v>
-      </c>
-      <c r="Q18">
-        <v>281.15</v>
-      </c>
-      <c r="R18">
-        <v>283.08</v>
-      </c>
-      <c r="S18">
-        <v>281.46</v>
-      </c>
-      <c r="T18">
-        <v>-0.61</v>
-      </c>
-      <c r="U18" t="s">
-        <v>59</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
       </c>
       <c r="W18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>44.55</v>
+        <v>40.59</v>
       </c>
       <c r="Z18">
-        <v>-0.71</v>
+        <v>-0.9</v>
       </c>
       <c r="AA18">
-        <v>-0.37</v>
+        <v>-0.47</v>
       </c>
       <c r="AB18">
-        <v>-0.35</v>
+        <v>-0.43</v>
       </c>
       <c r="AC18">
         <v>8.6</v>
       </c>
       <c r="AD18">
-        <v>10.25</v>
+        <v>9.01</v>
       </c>
       <c r="AE18">
         <v>4.43</v>
       </c>
       <c r="AF18">
-        <v>-90.37</v>
+        <v>-13.55</v>
       </c>
       <c r="AG18">
-        <v>285.08</v>
+        <v>284.66</v>
       </c>
       <c r="AH18">
-        <v>277.22</v>
+        <v>276.99</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2779,7 +2855,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>18.54</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2790,10 +2866,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>226.67</v>
+        <v>227.17</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2802,85 +2878,85 @@
         <v>109.64</v>
       </c>
       <c r="G19">
-        <v>-36.73</v>
+        <v>-36.59</v>
       </c>
       <c r="H19">
-        <v>106.74</v>
+        <v>107.2</v>
       </c>
       <c r="I19">
-        <v>0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="J19">
-        <v>7.98</v>
+        <v>6.58</v>
       </c>
       <c r="K19">
-        <v>-12.45</v>
+        <v>-11.85</v>
       </c>
       <c r="L19">
-        <v>102.51</v>
+        <v>99.31</v>
       </c>
       <c r="M19">
-        <v>53.73</v>
+        <v>53.81</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>227.78</v>
+        <v>227.64</v>
       </c>
       <c r="Q19">
-        <v>219.32</v>
+        <v>219.81</v>
       </c>
       <c r="R19">
-        <v>221.06</v>
+        <v>220.85</v>
       </c>
       <c r="S19">
-        <v>226.28</v>
+        <v>226.69</v>
       </c>
       <c r="T19">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="U19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V19" t="b">
         <v>0</v>
       </c>
       <c r="W19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>58.33</v>
+        <v>58.99</v>
       </c>
       <c r="Z19">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="AA19">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AB19">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC19">
-        <v>67.81999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="AD19">
-        <v>78.42</v>
+        <v>71.78</v>
       </c>
       <c r="AE19">
-        <v>5.78</v>
+        <v>5.72</v>
       </c>
       <c r="AF19">
-        <v>-15.38</v>
+        <v>-34.68</v>
       </c>
       <c r="AG19">
-        <v>232.53</v>
+        <v>233.44</v>
       </c>
       <c r="AH19">
-        <v>206.1</v>
+        <v>206.19</v>
       </c>
       <c r="AI19">
         <v>215.89</v>
@@ -2889,7 +2965,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>43.97</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2900,10 +2976,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>263.05</v>
+        <v>260.94</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2912,85 +2988,85 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-6.46</v>
+        <v>-7.21</v>
       </c>
       <c r="H20">
-        <v>9.9</v>
+        <v>9.02</v>
       </c>
       <c r="I20">
-        <v>-0.72</v>
+        <v>-1.07</v>
       </c>
       <c r="J20">
-        <v>0.62</v>
+        <v>0.21</v>
       </c>
       <c r="K20">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="L20">
-        <v>0.59</v>
+        <v>-0.75</v>
       </c>
       <c r="M20">
-        <v>9.24</v>
+        <v>9.06</v>
       </c>
       <c r="N20">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="P20">
-        <v>263.14</v>
+        <v>262.57</v>
       </c>
       <c r="Q20">
-        <v>261.81</v>
+        <v>261.84</v>
       </c>
       <c r="R20">
-        <v>259.16</v>
+        <v>259.39</v>
       </c>
       <c r="S20">
-        <v>264.54</v>
+        <v>264.46</v>
       </c>
       <c r="T20">
-        <v>-0.5600000000000001</v>
+        <v>-1.33</v>
       </c>
       <c r="U20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V20" t="b">
         <v>0</v>
       </c>
       <c r="W20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>56.16</v>
+        <v>47.76</v>
       </c>
       <c r="Z20">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="AA20">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AB20">
-        <v>-0.14</v>
+        <v>-0.32</v>
       </c>
       <c r="AC20">
-        <v>24.6</v>
+        <v>14.21</v>
       </c>
       <c r="AD20">
-        <v>39.09</v>
+        <v>26.52</v>
       </c>
       <c r="AE20">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="AF20">
-        <v>12.91</v>
+        <v>-41.13</v>
       </c>
       <c r="AG20">
         <v>267.31</v>
       </c>
       <c r="AH20">
-        <v>256.31</v>
+        <v>256.38</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -2999,7 +3075,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>28.35</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3010,10 +3086,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>799.65</v>
+        <v>798.66</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3022,94 +3098,94 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-0.45</v>
+        <v>-0.57</v>
       </c>
       <c r="H21">
-        <v>24.43</v>
+        <v>24.27</v>
       </c>
       <c r="I21">
-        <v>-0.45</v>
+        <v>-0.27</v>
       </c>
       <c r="J21">
-        <v>3.91</v>
+        <v>3.16</v>
       </c>
       <c r="K21">
-        <v>8.08</v>
+        <v>7.38</v>
       </c>
       <c r="L21">
-        <v>13.63</v>
+        <v>12.94</v>
       </c>
       <c r="M21">
-        <v>14.21</v>
+        <v>14.03</v>
       </c>
       <c r="N21">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P21">
-        <v>800.1799999999999</v>
+        <v>799.74</v>
       </c>
       <c r="Q21">
-        <v>788.72</v>
+        <v>789.66</v>
       </c>
       <c r="R21">
-        <v>775.4299999999999</v>
+        <v>776.45</v>
       </c>
       <c r="S21">
-        <v>742.5700000000001</v>
+        <v>742.84</v>
       </c>
       <c r="T21">
-        <v>7.69</v>
+        <v>7.51</v>
       </c>
       <c r="U21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X21">
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>63.28</v>
+        <v>61.99</v>
       </c>
       <c r="Z21">
-        <v>8.17</v>
+        <v>7.8</v>
       </c>
       <c r="AA21">
-        <v>7.68</v>
+        <v>7.71</v>
       </c>
       <c r="AB21">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="AC21">
-        <v>69.77</v>
+        <v>59.04</v>
       </c>
       <c r="AD21">
-        <v>75.56</v>
+        <v>68.19</v>
       </c>
       <c r="AE21">
-        <v>10.65</v>
+        <v>11.65</v>
       </c>
       <c r="AF21">
-        <v>118.3</v>
+        <v>58.26</v>
       </c>
       <c r="AG21">
-        <v>811.9400000000001</v>
+        <v>812.88</v>
       </c>
       <c r="AH21">
-        <v>765.5</v>
+        <v>766.4400000000001</v>
       </c>
       <c r="AI21">
-        <v>770.55</v>
+        <v>773.79</v>
       </c>
       <c r="AJ21" t="s">
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>10.85</v>
+        <v>15.14</v>
       </c>
     </row>
   </sheetData>
@@ -3250,7 +3326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3270,1943 +3346,3164 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-0.12</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-1.41</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.29</v>
+      <c r="D7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-0.13</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-1.55</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.42</v>
+      <c r="A8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-1.76</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-1.92</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.16</v>
+      <c r="A9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-0.63</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.26</v>
+      <c r="A10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>7.44</v>
-      </c>
-      <c r="D11" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.63</v>
+      <c r="A11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>7.38</v>
-      </c>
-      <c r="D12" s="5">
-        <v>9.1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.72</v>
+      <c r="A12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.34</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.68</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.99</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.6899999999999999</v>
+      <c r="A13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>9</v>
-      </c>
-      <c r="D15" s="5">
-        <v>7.25</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-1.75</v>
-      </c>
+      <c r="A15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-0.12</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.89</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.13</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.91</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.76</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.41</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6">
+        <v>7.44</v>
+      </c>
+      <c r="D21" s="6">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="6">
+        <v>7.38</v>
+      </c>
+      <c r="D22" s="6">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.34</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1.68</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-0.04</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="6">
+        <v>9</v>
+      </c>
+      <c r="D25" s="6">
+        <v>3.82</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-5.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C26" s="6">
         <v>9.220000000000001</v>
       </c>
-      <c r="D16" s="5">
-        <v>7.31</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="D26" s="6">
+        <v>3.71</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3.97</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3.12</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1.59</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1.47</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-0.03</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1.47</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-0.29</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="6">
+        <v>4.59</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-4.22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-1.63</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-2.36</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="6">
+        <v>6.88</v>
+      </c>
+      <c r="D34" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="D36" s="6">
+        <v>3.16</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-0.4</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-2.3</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1.48</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.76</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-0.8</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-0.67</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-0.34</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-4.34</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-0.49</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-4.71</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-4.22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-0.22</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-0.53</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-1.09</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-0.84</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-1.15</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-0.67</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-1.1</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-0.51</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-1.1</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-0.52</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-1.47</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-0.78</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="6">
+        <v>0.42</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-0.31</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="6">
+        <v>-0.51</v>
+      </c>
+      <c r="D55" s="6">
+        <v>-1.07</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-0.24</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-0.27</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="6">
+        <v>4.28</v>
+      </c>
+      <c r="D57" s="6">
+        <v>4.25</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-89.58</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-89.54000000000001</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="6">
+        <v>4.25</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3.19</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-11.18</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-12.52</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="6">
+        <v>50.34</v>
+      </c>
+      <c r="D61" s="6">
+        <v>51.98</v>
+      </c>
+      <c r="E61" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="6">
+        <v>50.61</v>
+      </c>
+      <c r="D62" s="6">
+        <v>52.18</v>
+      </c>
+      <c r="E62" s="8">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="6">
+        <v>11.69</v>
+      </c>
+      <c r="D63" s="6">
+        <v>7.99</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="6">
+        <v>4.97</v>
+      </c>
+      <c r="D64" s="6">
+        <v>4.58</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-7.75</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-10.71</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-7.79</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-11.4</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-3.61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="6">
+        <v>13.5</v>
+      </c>
+      <c r="D67" s="6">
+        <v>12.56</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-0.64</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="6">
+        <v>0.41</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="6">
+        <v>24.13</v>
+      </c>
+      <c r="D71" s="6">
+        <v>23.14</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="6">
+        <v>2.97</v>
+      </c>
+      <c r="D72" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="6">
+        <v>101.97</v>
+      </c>
+      <c r="D73" s="6">
+        <v>99.31</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="6">
+        <v>13.44</v>
+      </c>
+      <c r="D75" s="6">
+        <v>12.94</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="6">
+        <v>8</v>
+      </c>
+      <c r="D76" s="6">
+        <v>7.69</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="6">
+        <v>7.89</v>
+      </c>
+      <c r="D77" s="6">
+        <v>7.99</v>
+      </c>
+      <c r="E77" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-10.52</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-10.21</v>
+      </c>
+      <c r="E78" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-4.61</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-4.22</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E80" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-4.11</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-3.2</v>
+      </c>
+      <c r="E81" s="8">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-11.46</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-9.56</v>
+      </c>
+      <c r="E82" s="8">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="6">
+        <v>2.38</v>
+      </c>
+      <c r="D83" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="6">
+        <v>7.45</v>
+      </c>
+      <c r="D84" s="6">
+        <v>5.31</v>
+      </c>
+      <c r="E84" s="7">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="6">
+        <v>7.27</v>
+      </c>
+      <c r="D85" s="6">
+        <v>4.68</v>
+      </c>
+      <c r="E85" s="7">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="6">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="D86" s="6">
+        <v>7.51</v>
+      </c>
+      <c r="E86" s="7">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="6">
+        <v>4.01</v>
+      </c>
+      <c r="D87" s="6">
+        <v>2.94</v>
+      </c>
+      <c r="E87" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="6">
+        <v>3.82</v>
+      </c>
+      <c r="D88" s="6">
+        <v>2.96</v>
+      </c>
+      <c r="E88" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="6">
+        <v>3.99</v>
+      </c>
+      <c r="D89" s="6">
+        <v>3.22</v>
+      </c>
+      <c r="E89" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="6">
+        <v>4.08</v>
+      </c>
+      <c r="D90" s="6">
+        <v>2.93</v>
+      </c>
+      <c r="E90" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="6">
+        <v>9.66</v>
+      </c>
+      <c r="D91" s="6">
+        <v>8.1</v>
+      </c>
+      <c r="E91" s="7">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="6">
+        <v>5.91</v>
+      </c>
+      <c r="D92" s="6">
+        <v>4.74</v>
+      </c>
+      <c r="E92" s="7">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="6">
+        <v>-12.59</v>
+      </c>
+      <c r="D93" s="6">
+        <v>-11.85</v>
+      </c>
+      <c r="E93" s="8">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="6">
+        <v>3.96</v>
+      </c>
+      <c r="D94" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="E94" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="6">
+        <v>8.26</v>
+      </c>
+      <c r="D95" s="6">
+        <v>7.38</v>
+      </c>
+      <c r="E95" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="6">
+        <v>-6.21</v>
+      </c>
+      <c r="D96" s="6">
+        <v>-6.45</v>
+      </c>
+      <c r="E96" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6">
+        <v>-90.62</v>
+      </c>
+      <c r="D97" s="6">
+        <v>-90.64</v>
+      </c>
+      <c r="E97" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6">
+        <v>-13.75</v>
+      </c>
+      <c r="D98" s="6">
+        <v>-13.62</v>
+      </c>
+      <c r="E98" s="8">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6">
+        <v>-14.16</v>
+      </c>
+      <c r="D99" s="6">
+        <v>-15.82</v>
+      </c>
+      <c r="E99" s="7">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="6">
+        <v>-14.6</v>
+      </c>
+      <c r="D100" s="6">
+        <v>-13.72</v>
+      </c>
+      <c r="E100" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6">
+        <v>-14.57</v>
+      </c>
+      <c r="D101" s="6">
+        <v>-13.65</v>
+      </c>
+      <c r="E101" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="6">
+        <v>-14.78</v>
+      </c>
+      <c r="D102" s="6">
+        <v>-15.03</v>
+      </c>
+      <c r="E102" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="6">
+        <v>-3.16</v>
+      </c>
+      <c r="D103" s="6">
+        <v>-3.49</v>
+      </c>
+      <c r="E103" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="6">
+        <v>-19.5</v>
+      </c>
+      <c r="D104" s="6">
+        <v>-21.96</v>
+      </c>
+      <c r="E104" s="7">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="6">
+        <v>-19.59</v>
+      </c>
+      <c r="D105" s="6">
+        <v>-22.43</v>
+      </c>
+      <c r="E105" s="7">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="6">
+        <v>-0.15</v>
+      </c>
+      <c r="D106" s="6">
+        <v>-0.38</v>
+      </c>
+      <c r="E106" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="6">
+        <v>-6.45</v>
+      </c>
+      <c r="D107" s="6">
+        <v>-7.21</v>
+      </c>
+      <c r="E107" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="6">
+        <v>-6.61</v>
+      </c>
+      <c r="D108" s="6">
+        <v>-7.26</v>
+      </c>
+      <c r="E108" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="6">
+        <v>-6.54</v>
+      </c>
+      <c r="D109" s="6">
+        <v>-7.27</v>
+      </c>
+      <c r="E109" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="6">
+        <v>-6.47</v>
+      </c>
+      <c r="D110" s="6">
+        <v>-7.22</v>
+      </c>
+      <c r="E110" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="6">
+        <v>-11.24</v>
+      </c>
+      <c r="D111" s="6">
+        <v>-12.15</v>
+      </c>
+      <c r="E111" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="6">
+        <v>-5.66</v>
+      </c>
+      <c r="D112" s="6">
+        <v>-6.25</v>
+      </c>
+      <c r="E112" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="6">
+        <v>-36.73</v>
+      </c>
+      <c r="D113" s="6">
+        <v>-36.59</v>
+      </c>
+      <c r="E113" s="8">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="6">
+        <v>-6.46</v>
+      </c>
+      <c r="D114" s="6">
+        <v>-7.21</v>
+      </c>
+      <c r="E114" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="D115" s="6">
+        <v>-0.57</v>
+      </c>
+      <c r="E115" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" s="6">
+        <v>596.37</v>
+      </c>
+      <c r="D116" s="6">
+        <v>594.86</v>
+      </c>
+      <c r="E116" s="7">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" s="6">
+        <v>59.77</v>
+      </c>
+      <c r="D117" s="6">
+        <v>59.63</v>
+      </c>
+      <c r="E117" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" s="6">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="D118" s="6">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="E118" s="8">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" s="6">
+        <v>52.36</v>
+      </c>
+      <c r="D119" s="6">
+        <v>51.35</v>
+      </c>
+      <c r="E119" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" s="6">
+        <v>125.13</v>
+      </c>
+      <c r="D120" s="6">
+        <v>126.43</v>
+      </c>
+      <c r="E120" s="8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" s="6">
+        <v>129.33</v>
+      </c>
+      <c r="D121" s="6">
+        <v>130.71</v>
+      </c>
+      <c r="E121" s="8">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C122" s="6">
+        <v>482.66</v>
+      </c>
+      <c r="D122" s="6">
+        <v>481.22</v>
+      </c>
+      <c r="E122" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" s="6">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="D123" s="6">
+        <v>973.6799999999999</v>
+      </c>
+      <c r="E123" s="7">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" s="6">
+        <v>34.75</v>
+      </c>
+      <c r="D124" s="6">
+        <v>33.69</v>
+      </c>
+      <c r="E124" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" s="6">
+        <v>34.81</v>
+      </c>
+      <c r="D125" s="6">
+        <v>33.58</v>
+      </c>
+      <c r="E125" s="7">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" s="6">
+        <v>807.8099999999999</v>
+      </c>
+      <c r="D126" s="6">
+        <v>805.9</v>
+      </c>
+      <c r="E126" s="7">
         <v>-1.91</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+    <row r="127" spans="1:5">
+      <c r="A127" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" s="6">
+        <v>278.35</v>
+      </c>
+      <c r="D127" s="6">
+        <v>276.1</v>
+      </c>
+      <c r="E127" s="7">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" s="6">
+        <v>270.48</v>
+      </c>
+      <c r="D128" s="6">
+        <v>268.59</v>
+      </c>
+      <c r="E128" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" s="6">
+        <v>265.71</v>
+      </c>
+      <c r="D129" s="6">
+        <v>263.65</v>
+      </c>
+      <c r="E129" s="7">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" s="6">
+        <v>276.84</v>
+      </c>
+      <c r="D130" s="6">
+        <v>274.6</v>
+      </c>
+      <c r="E130" s="7">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" s="6">
+        <v>97.52</v>
+      </c>
+      <c r="D131" s="6">
+        <v>96.52</v>
+      </c>
+      <c r="E131" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C132" s="6">
+        <v>279.76</v>
+      </c>
+      <c r="D132" s="6">
+        <v>278.01</v>
+      </c>
+      <c r="E132" s="7">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C133" s="6">
+        <v>226.67</v>
+      </c>
+      <c r="D133" s="6">
+        <v>227.17</v>
+      </c>
+      <c r="E133" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134" s="6">
+        <v>263.05</v>
+      </c>
+      <c r="D134" s="6">
+        <v>260.94</v>
+      </c>
+      <c r="E134" s="7">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" s="6">
+        <v>799.65</v>
+      </c>
+      <c r="D135" s="6">
+        <v>798.66</v>
+      </c>
+      <c r="E135" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" s="6">
+        <v>22</v>
+      </c>
+      <c r="D136" s="6">
+        <v>32</v>
+      </c>
+      <c r="E136" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" s="6">
+        <v>63</v>
+      </c>
+      <c r="D137" s="6">
+        <v>58</v>
+      </c>
+      <c r="E137" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="6">
+        <v>32</v>
+      </c>
+      <c r="D138" s="6">
+        <v>27</v>
+      </c>
+      <c r="E138" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" s="6">
+        <v>27</v>
+      </c>
+      <c r="D139" s="6">
+        <v>22</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="5">
-        <v>3.97</v>
-      </c>
-      <c r="D17" s="5">
-        <v>4.08</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B140" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="6">
+        <v>78</v>
+      </c>
+      <c r="D140" s="6">
+        <v>73</v>
+      </c>
+      <c r="E140" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.59</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B141" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" s="6">
+        <v>47</v>
+      </c>
+      <c r="D141" s="6">
+        <v>42</v>
+      </c>
+      <c r="E141" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="6">
+        <v>40</v>
+      </c>
+      <c r="D142" s="6">
+        <v>47</v>
+      </c>
+      <c r="E142" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" s="6">
+        <v>53</v>
+      </c>
+      <c r="D143" s="6">
+        <v>37</v>
+      </c>
+      <c r="E143" s="7">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="6">
+        <v>58</v>
+      </c>
+      <c r="D144" s="6">
+        <v>63</v>
+      </c>
+      <c r="E144" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" s="6">
+        <v>40</v>
+      </c>
+      <c r="D145" s="6">
+        <v>53</v>
+      </c>
+      <c r="E145" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" s="6">
+        <v>73</v>
+      </c>
+      <c r="D146" s="6">
+        <v>78</v>
+      </c>
+      <c r="E146" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" s="6">
+        <v>51.92</v>
+      </c>
+      <c r="D147" s="6">
+        <v>49.78</v>
+      </c>
+      <c r="E147" s="7">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="6">
+        <v>49.87</v>
+      </c>
+      <c r="D148" s="6">
+        <v>48.17</v>
+      </c>
+      <c r="E148" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" s="6">
+        <v>35.45</v>
+      </c>
+      <c r="D149" s="6">
+        <v>37.39</v>
+      </c>
+      <c r="E149" s="8">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="6">
+        <v>44.7</v>
+      </c>
+      <c r="D150" s="6">
+        <v>34.79</v>
+      </c>
+      <c r="E150" s="7">
+        <v>-9.91</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C151" s="6">
+        <v>66.41</v>
+      </c>
+      <c r="D151" s="6">
+        <v>69.69</v>
+      </c>
+      <c r="E151" s="8">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" s="6">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="D152" s="6">
+        <v>69.97</v>
+      </c>
+      <c r="E152" s="8">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C153" s="6">
+        <v>45.49</v>
+      </c>
+      <c r="D153" s="6">
+        <v>43.82</v>
+      </c>
+      <c r="E153" s="7">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C154" s="6">
+        <v>55.26</v>
+      </c>
+      <c r="D154" s="6">
+        <v>52.2</v>
+      </c>
+      <c r="E154" s="7">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C155" s="6">
+        <v>62.87</v>
+      </c>
+      <c r="D155" s="6">
+        <v>50.28</v>
+      </c>
+      <c r="E155" s="7">
+        <v>-12.59</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C156" s="6">
+        <v>63.22</v>
+      </c>
+      <c r="D156" s="6">
+        <v>49.01</v>
+      </c>
+      <c r="E156" s="7">
+        <v>-14.21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C157" s="6">
+        <v>68.47</v>
+      </c>
+      <c r="D157" s="6">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="E157" s="7">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C158" s="6">
+        <v>56.25</v>
+      </c>
+      <c r="D158" s="6">
+        <v>47.76</v>
+      </c>
+      <c r="E158" s="7">
+        <v>-8.49</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B159" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C159" s="6">
+        <v>55.18</v>
+      </c>
+      <c r="D159" s="6">
+        <v>47.52</v>
+      </c>
+      <c r="E159" s="7">
+        <v>-7.66</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B160" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C160" s="6">
+        <v>55.06</v>
+      </c>
+      <c r="D160" s="6">
+        <v>47.67</v>
+      </c>
+      <c r="E160" s="7">
+        <v>-7.39</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B161" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C161" s="6">
+        <v>55.76</v>
+      </c>
+      <c r="D161" s="6">
+        <v>47.51</v>
+      </c>
+      <c r="E161" s="7">
+        <v>-8.25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="5">
-        <v>4.59</v>
-      </c>
-      <c r="D22" s="5">
-        <v>4.21</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B162" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C162" s="6">
+        <v>59.65</v>
+      </c>
+      <c r="D162" s="6">
+        <v>54.32</v>
+      </c>
+      <c r="E162" s="7">
+        <v>-5.33</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-1.63</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-3.94</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B163" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C163" s="6">
+        <v>44.55</v>
+      </c>
+      <c r="D163" s="6">
+        <v>40.59</v>
+      </c>
+      <c r="E163" s="7">
+        <v>-3.96</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="5">
-        <v>6.88</v>
-      </c>
-      <c r="D24" s="5">
-        <v>7.98</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B164" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C164" s="6">
+        <v>58.33</v>
+      </c>
+      <c r="D164" s="6">
+        <v>58.99</v>
+      </c>
+      <c r="E164" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="5">
-        <v>1.67</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0.62</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B165" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C165" s="6">
+        <v>56.16</v>
+      </c>
+      <c r="D165" s="6">
+        <v>47.76</v>
+      </c>
+      <c r="E165" s="7">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="5">
-        <v>3.8</v>
-      </c>
-      <c r="D26" s="5">
-        <v>3.91</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B166" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C166" s="6">
+        <v>63.28</v>
+      </c>
+      <c r="D166" s="6">
+        <v>61.99</v>
+      </c>
+      <c r="E166" s="7">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-0.4</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B167" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167" s="6">
+        <v>-54.87</v>
+      </c>
+      <c r="D167" s="6">
+        <v>-18.36</v>
+      </c>
+      <c r="E167" s="8">
+        <v>36.51</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-0.58</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-0.37</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B168" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C168" s="6">
+        <v>-86.98</v>
+      </c>
+      <c r="D168" s="6">
+        <v>40.81</v>
+      </c>
+      <c r="E168" s="8">
+        <v>127.79</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-0.45</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B169" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C169" s="6">
+        <v>-34.59</v>
+      </c>
+      <c r="D169" s="6">
+        <v>10.05</v>
+      </c>
+      <c r="E169" s="8">
+        <v>44.64</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-1.89</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B170" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="6">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="D170" s="6">
+        <v>208.84</v>
+      </c>
+      <c r="E170" s="8">
+        <v>133.8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0.44</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B171" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="6">
+        <v>3.61</v>
+      </c>
+      <c r="D171" s="6">
+        <v>-33.97</v>
+      </c>
+      <c r="E171" s="7">
+        <v>-37.58</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1.44</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B172" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" s="6">
+        <v>-30.89</v>
+      </c>
+      <c r="D172" s="6">
+        <v>-22.11</v>
+      </c>
+      <c r="E172" s="8">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-0.8</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B173" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C173" s="6">
+        <v>-45.88</v>
+      </c>
+      <c r="D173" s="6">
+        <v>31.71</v>
+      </c>
+      <c r="E173" s="8">
+        <v>77.59</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-0.6</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-0.37</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B174" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="6">
+        <v>5.08</v>
+      </c>
+      <c r="D174" s="6">
+        <v>-49.16</v>
+      </c>
+      <c r="E174" s="7">
+        <v>-54.24</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-0.34</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-0.88</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B175" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="6">
+        <v>-57.72</v>
+      </c>
+      <c r="D175" s="6">
+        <v>-60.76</v>
+      </c>
+      <c r="E175" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-0.49</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-0.85</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B176" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C176" s="6">
+        <v>-69.5</v>
+      </c>
+      <c r="D176" s="6">
+        <v>-40.98</v>
+      </c>
+      <c r="E176" s="8">
+        <v>28.52</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-0.15</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B177" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177" s="6">
+        <v>82.19</v>
+      </c>
+      <c r="D177" s="6">
+        <v>-22.06</v>
+      </c>
+      <c r="E177" s="7">
+        <v>-104.25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-0.75</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B178" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="6">
+        <v>-42.33</v>
+      </c>
+      <c r="D178" s="6">
+        <v>-13.01</v>
+      </c>
+      <c r="E178" s="8">
+        <v>29.32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-0.84</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B179" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C179" s="6">
+        <v>-57.02</v>
+      </c>
+      <c r="D179" s="6">
+        <v>-12.95</v>
+      </c>
+      <c r="E179" s="8">
+        <v>44.07</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-0.67</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-0.75</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B180" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C180" s="6">
+        <v>-78.41</v>
+      </c>
+      <c r="D180" s="6">
+        <v>61.19</v>
+      </c>
+      <c r="E180" s="8">
+        <v>139.6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-0.95</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B181" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C181" s="6">
+        <v>-59.55</v>
+      </c>
+      <c r="D181" s="6">
+        <v>-51.29</v>
+      </c>
+      <c r="E181" s="8">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-0.52</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1.12</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B182" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C182" s="6">
+        <v>-35</v>
+      </c>
+      <c r="D182" s="6">
+        <v>-49.64</v>
+      </c>
+      <c r="E182" s="7">
+        <v>-14.64</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-1.47</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-0.61</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B183" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C183" s="6">
+        <v>-88.69</v>
+      </c>
+      <c r="D183" s="6">
+        <v>-13.55</v>
+      </c>
+      <c r="E183" s="8">
+        <v>75.14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="D44" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B184" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C184" s="6">
+        <v>-21.85</v>
+      </c>
+      <c r="D184" s="6">
+        <v>-34.68</v>
+      </c>
+      <c r="E184" s="7">
+        <v>-12.83</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-0.72</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B185" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C185" s="6">
+        <v>-43.91</v>
+      </c>
+      <c r="D185" s="6">
+        <v>-41.13</v>
+      </c>
+      <c r="E185" s="8">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-0.24</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-0.45</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="5">
-        <v>4.28</v>
-      </c>
-      <c r="D47" s="5">
-        <v>4.71</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-89.58</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-89.51000000000001</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="5">
-        <v>4.25</v>
-      </c>
-      <c r="D49" s="5">
-        <v>3.92</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-11.18</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-11.37</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="5">
-        <v>50.34</v>
-      </c>
-      <c r="D51" s="5">
-        <v>50.8</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="5">
-        <v>50.61</v>
-      </c>
-      <c r="D52" s="5">
-        <v>52.58</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="5">
-        <v>11.69</v>
-      </c>
-      <c r="D53" s="5">
-        <v>10.95</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="5">
-        <v>4.97</v>
-      </c>
-      <c r="D54" s="5">
-        <v>5.39</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="D55" s="5">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="5">
-        <v>-7.79</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-8.1</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="5">
-        <v>13.5</v>
-      </c>
-      <c r="D57" s="5">
-        <v>13.64</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="D58" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="5">
-        <v>0.43</v>
-      </c>
-      <c r="D59" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="D60" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="5">
-        <v>24.13</v>
-      </c>
-      <c r="D61" s="5">
-        <v>24.28</v>
-      </c>
-      <c r="E61" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="5">
-        <v>2.97</v>
-      </c>
-      <c r="D62" s="5">
-        <v>3.42</v>
-      </c>
-      <c r="E62" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="5">
-        <v>101.97</v>
-      </c>
-      <c r="D63" s="5">
-        <v>102.51</v>
-      </c>
-      <c r="E63" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="D64" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="E64" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="5">
-        <v>13.44</v>
-      </c>
-      <c r="D65" s="5">
-        <v>13.63</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="5">
-        <v>8</v>
-      </c>
-      <c r="D66" s="5">
-        <v>7.82</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="5">
-        <v>7.89</v>
-      </c>
-      <c r="D67" s="5">
-        <v>7.83</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-10.52</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-10.34</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-3.79</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-3.94</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-4.22</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-3.89</v>
-      </c>
-      <c r="E70" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-4.11</v>
-      </c>
-      <c r="D71" s="5">
-        <v>-2.93</v>
-      </c>
-      <c r="E71" s="7">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-11.46</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-10.08</v>
-      </c>
-      <c r="E72" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="5">
-        <v>2.38</v>
-      </c>
-      <c r="D73" s="5">
-        <v>1.45</v>
-      </c>
-      <c r="E73" s="6">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="5">
-        <v>7.45</v>
-      </c>
-      <c r="D74" s="5">
-        <v>7.99</v>
-      </c>
-      <c r="E74" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="5">
-        <v>7.27</v>
-      </c>
-      <c r="D75" s="5">
-        <v>7.84</v>
-      </c>
-      <c r="E75" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="5">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="D76" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="E76" s="6">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="D77" s="5">
-        <v>3.84</v>
-      </c>
-      <c r="E77" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="D78" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="E78" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="5">
-        <v>3.99</v>
-      </c>
-      <c r="D79" s="5">
-        <v>3.87</v>
-      </c>
-      <c r="E79" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="5">
-        <v>4.08</v>
-      </c>
-      <c r="D80" s="5">
-        <v>3.76</v>
-      </c>
-      <c r="E80" s="6">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="5">
-        <v>9.66</v>
-      </c>
-      <c r="D81" s="5">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="E81" s="6">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="5">
-        <v>5.91</v>
-      </c>
-      <c r="D82" s="5">
-        <v>5.41</v>
-      </c>
-      <c r="E82" s="6">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="5">
-        <v>-12.59</v>
-      </c>
-      <c r="D83" s="5">
-        <v>-12.45</v>
-      </c>
-      <c r="E83" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="5">
-        <v>3.96</v>
-      </c>
-      <c r="D84" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="E84" s="6">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="5">
-        <v>8.26</v>
-      </c>
-      <c r="D85" s="5">
-        <v>8.08</v>
-      </c>
-      <c r="E85" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="5">
-        <v>-14.16</v>
-      </c>
-      <c r="D86" s="5">
-        <v>-14.79</v>
-      </c>
-      <c r="E86" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="5">
-        <v>-14.57</v>
-      </c>
-      <c r="D87" s="5">
-        <v>-13.71</v>
-      </c>
-      <c r="E87" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="5">
-        <v>-6.61</v>
-      </c>
-      <c r="D88" s="5">
-        <v>-6.58</v>
-      </c>
-      <c r="E88" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C89" s="5">
-        <v>52.36</v>
-      </c>
-      <c r="D89" s="5">
-        <v>51.98</v>
-      </c>
-      <c r="E89" s="6">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C90" s="5">
-        <v>129.33</v>
-      </c>
-      <c r="D90" s="5">
-        <v>130.62</v>
-      </c>
-      <c r="E90" s="7">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C91" s="5">
-        <v>270.48</v>
-      </c>
-      <c r="D91" s="5">
-        <v>270.55</v>
-      </c>
-      <c r="E91" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92" s="5">
-        <v>47</v>
-      </c>
-      <c r="D92" s="5">
-        <v>53</v>
-      </c>
-      <c r="E92" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" s="5">
-        <v>40</v>
-      </c>
-      <c r="D93" s="5">
-        <v>45</v>
-      </c>
-      <c r="E93" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C94" s="5">
-        <v>53</v>
-      </c>
-      <c r="D94" s="5">
-        <v>37</v>
-      </c>
-      <c r="E94" s="6">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" s="5">
-        <v>40</v>
-      </c>
-      <c r="D95" s="5">
-        <v>45</v>
-      </c>
-      <c r="E95" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" s="5">
-        <v>44.7</v>
-      </c>
-      <c r="D96" s="5">
-        <v>40.55</v>
-      </c>
-      <c r="E96" s="6">
-        <v>-4.15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" s="5">
-        <v>66.79000000000001</v>
-      </c>
-      <c r="D97" s="5">
-        <v>69.77</v>
-      </c>
-      <c r="E97" s="7">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98" s="5">
-        <v>55.18</v>
-      </c>
-      <c r="D98" s="5">
-        <v>55.43</v>
-      </c>
-      <c r="E98" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B99" s="3" t="s">
+      <c r="B186" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C99" s="5">
-        <v>-54.87</v>
-      </c>
-      <c r="D99" s="5">
-        <v>13.15</v>
-      </c>
-      <c r="E99" s="7">
-        <v>68.02</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C100" s="5">
-        <v>-86.98</v>
-      </c>
-      <c r="D100" s="5">
-        <v>-85</v>
-      </c>
-      <c r="E100" s="7">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C101" s="5">
-        <v>-34.59</v>
-      </c>
-      <c r="D101" s="5">
-        <v>53.29</v>
-      </c>
-      <c r="E101" s="7">
-        <v>87.88</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C102" s="5">
-        <v>75.04000000000001</v>
-      </c>
-      <c r="D102" s="5">
-        <v>24.43</v>
-      </c>
-      <c r="E102" s="6">
-        <v>-50.61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C103" s="5">
-        <v>3.61</v>
-      </c>
-      <c r="D103" s="5">
-        <v>10.82</v>
-      </c>
-      <c r="E103" s="7">
-        <v>7.21</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C104" s="5">
-        <v>-30.89</v>
-      </c>
-      <c r="D104" s="5">
-        <v>15.19</v>
-      </c>
-      <c r="E104" s="7">
-        <v>46.08</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C105" s="5">
-        <v>-45.88</v>
-      </c>
-      <c r="D105" s="5">
-        <v>-24.82</v>
-      </c>
-      <c r="E105" s="7">
-        <v>21.06</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C106" s="5">
-        <v>5.08</v>
-      </c>
-      <c r="D106" s="5">
-        <v>22.27</v>
-      </c>
-      <c r="E106" s="7">
-        <v>17.19</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C107" s="5">
-        <v>-57.72</v>
-      </c>
-      <c r="D107" s="5">
-        <v>-67.45999999999999</v>
-      </c>
-      <c r="E107" s="6">
-        <v>-9.74</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C108" s="5">
-        <v>-69.5</v>
-      </c>
-      <c r="D108" s="5">
-        <v>-55.27</v>
-      </c>
-      <c r="E108" s="7">
-        <v>14.23</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C109" s="5">
-        <v>82.19</v>
-      </c>
-      <c r="D109" s="5">
-        <v>-21.81</v>
-      </c>
-      <c r="E109" s="6">
-        <v>-104</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C110" s="5">
-        <v>-42.33</v>
-      </c>
-      <c r="D110" s="5">
-        <v>-9.08</v>
-      </c>
-      <c r="E110" s="7">
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C111" s="5">
-        <v>-57.02</v>
-      </c>
-      <c r="D111" s="5">
-        <v>-28.48</v>
-      </c>
-      <c r="E111" s="7">
-        <v>28.54</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C112" s="5">
-        <v>-78.41</v>
-      </c>
-      <c r="D112" s="5">
-        <v>-12.87</v>
-      </c>
-      <c r="E112" s="7">
-        <v>65.54000000000001</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C113" s="5">
-        <v>-59.55</v>
-      </c>
-      <c r="D113" s="5">
-        <v>5.7</v>
-      </c>
-      <c r="E113" s="7">
-        <v>65.25</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C114" s="5">
-        <v>-35</v>
-      </c>
-      <c r="D114" s="5">
-        <v>-35.25</v>
-      </c>
-      <c r="E114" s="6">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C115" s="5">
-        <v>-88.69</v>
-      </c>
-      <c r="D115" s="5">
-        <v>-90.37</v>
-      </c>
-      <c r="E115" s="6">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C116" s="5">
-        <v>-21.85</v>
-      </c>
-      <c r="D116" s="5">
-        <v>-15.38</v>
-      </c>
-      <c r="E116" s="7">
-        <v>6.47</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C117" s="5">
-        <v>-43.91</v>
-      </c>
-      <c r="D117" s="5">
-        <v>12.91</v>
-      </c>
-      <c r="E117" s="7">
-        <v>56.82</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C118" s="5">
+      <c r="C186" s="6">
         <v>22.54</v>
       </c>
-      <c r="D118" s="5">
-        <v>118.3</v>
-      </c>
-      <c r="E118" s="7">
-        <v>95.76000000000001</v>
+      <c r="D186" s="6">
+        <v>58.26</v>
+      </c>
+      <c r="E186" s="8">
+        <v>35.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5226,60 +6523,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>76</v>
+      <c r="B1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>47.04000000000001</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>20</v>
       </c>
-      <c r="D2" s="10">
-        <v>55.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>2.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>2</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>52.6</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -5381,131 +6678,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="13">
-        <v>0.5373</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="14">
+        <v>0.5381</v>
+      </c>
+      <c r="B2" s="14">
         <v>0.3326</v>
       </c>
-      <c r="C2" s="13">
-        <v>0.3087</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.2954</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.249</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1567</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.1421</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0.142</v>
-      </c>
-      <c r="I2" s="13">
-        <v>0.1054</v>
-      </c>
-      <c r="J2" s="13">
-        <v>0.0925</v>
+      <c r="C2" s="14">
+        <v>0.306</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2974</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.2525</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1543</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1403</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.1402</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0.1066</v>
+      </c>
+      <c r="J2" s="14">
+        <v>0.0911</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="13">
-        <v>0.0924</v>
-      </c>
-      <c r="B4" s="13">
-        <v>0.0924</v>
-      </c>
-      <c r="C4" s="13">
-        <v>0.0922</v>
-      </c>
-      <c r="D4" s="13">
-        <v>0.08470000000000001</v>
-      </c>
-      <c r="E4" s="13">
-        <v>0.07829999999999999</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0.0689</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0.006</v>
-      </c>
-      <c r="H4" s="13">
-        <v>0.0044</v>
-      </c>
-      <c r="I4" s="13">
-        <v>-0.0833</v>
-      </c>
-      <c r="J4" s="13">
-        <v>-0.3027</v>
+      <c r="A4" s="14">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="B4" s="14">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="C4" s="14">
+        <v>0.0906</v>
+      </c>
+      <c r="D4" s="14">
+        <v>0.0859</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0.0775</v>
+      </c>
+      <c r="F4" s="14">
+        <v>0.0634</v>
+      </c>
+      <c r="G4" s="14">
+        <v>0.0012</v>
+      </c>
+      <c r="H4" s="14">
+        <v>-0.0028</v>
+      </c>
+      <c r="I4" s="14">
+        <v>-0.09279999999999999</v>
+      </c>
+      <c r="J4" s="14">
+        <v>-0.3018</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="89">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,67 +226,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Yes → No</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.2 → 44.3</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.9 → 49.8</t>
-  </si>
-  <si>
-    <t>51.9</t>
-  </si>
-  <si>
-    <t>49.8</t>
-  </si>
-  <si>
-    <t>63.2 → 49.0</t>
-  </si>
-  <si>
-    <t>63.2</t>
-  </si>
-  <si>
-    <t>49.0</t>
-  </si>
-  <si>
-    <t>56.2 → 47.8</t>
-  </si>
-  <si>
-    <t>56.2</t>
-  </si>
-  <si>
-    <t>47.8</t>
-  </si>
-  <si>
-    <t>55.2 → 47.5</t>
-  </si>
-  <si>
-    <t>55.2</t>
-  </si>
-  <si>
-    <t>47.5</t>
-  </si>
-  <si>
-    <t>55.1 → 47.7</t>
-  </si>
-  <si>
-    <t>55.1</t>
-  </si>
-  <si>
-    <t>47.7</t>
-  </si>
-  <si>
-    <t>55.8 → 47.5</t>
-  </si>
-  <si>
-    <t>55.8</t>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>44.3</t>
+  </si>
+  <si>
+    <t>59.0 → 49.9</t>
+  </si>
+  <si>
+    <t>59.0</t>
+  </si>
+  <si>
+    <t>49.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1011,10 +972,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>594.86</v>
+        <v>593.26</v>
       </c>
       <c r="D2">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1023,43 +984,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-6.45</v>
+        <v>-6.7</v>
       </c>
       <c r="H2">
-        <v>14.2</v>
+        <v>13.89</v>
       </c>
       <c r="I2">
-        <v>-0</v>
+        <v>-0.96</v>
       </c>
       <c r="J2">
-        <v>-0.89</v>
+        <v>-1.05</v>
       </c>
       <c r="K2">
-        <v>7.69</v>
+        <v>6.01</v>
       </c>
       <c r="L2">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="M2">
-        <v>10.66</v>
+        <v>10.95</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>596.92</v>
+        <v>595.77</v>
       </c>
       <c r="Q2">
-        <v>594.27</v>
+        <v>594.3200000000001</v>
       </c>
       <c r="R2">
-        <v>594.71</v>
+        <v>595.22</v>
       </c>
       <c r="S2">
-        <v>593.0700000000001</v>
+        <v>593.05</v>
       </c>
       <c r="T2">
-        <v>0.3</v>
+        <v>0.04</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1074,34 +1035,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.78</v>
+        <v>47.54</v>
       </c>
       <c r="Z2">
-        <v>1.05</v>
+        <v>0.74</v>
       </c>
       <c r="AA2">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AB2">
-        <v>-0.23</v>
+        <v>-0.44</v>
       </c>
       <c r="AC2">
-        <v>33.93</v>
+        <v>15.82</v>
       </c>
       <c r="AD2">
-        <v>52.72</v>
+        <v>34.65</v>
       </c>
       <c r="AE2">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="AF2">
-        <v>-18.36</v>
+        <v>-41.91</v>
       </c>
       <c r="AG2">
-        <v>602.22</v>
+        <v>602.23</v>
       </c>
       <c r="AH2">
-        <v>586.3200000000001</v>
+        <v>586.41</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1110,7 +1071,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>22.01</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1121,10 +1082,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>59.63</v>
+        <v>59.44</v>
       </c>
       <c r="D3">
-        <v>-0.23</v>
+        <v>-0.32</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1133,43 +1094,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.64</v>
+        <v>-90.67</v>
       </c>
       <c r="H3">
-        <v>14.41</v>
+        <v>14.04</v>
       </c>
       <c r="I3">
-        <v>-0.1</v>
+        <v>-1.18</v>
       </c>
       <c r="J3">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="K3">
-        <v>7.99</v>
+        <v>5.86</v>
       </c>
       <c r="L3">
-        <v>-89.54000000000001</v>
+        <v>-89.59</v>
       </c>
       <c r="M3">
-        <v>-30.18</v>
+        <v>-30.03</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.84</v>
+        <v>59.7</v>
       </c>
       <c r="Q3">
-        <v>59.61</v>
+        <v>59.62</v>
       </c>
       <c r="R3">
-        <v>59.64</v>
+        <v>59.69</v>
       </c>
       <c r="S3">
-        <v>286.45</v>
+        <v>283.75</v>
       </c>
       <c r="T3">
-        <v>-79.18000000000001</v>
+        <v>-79.05</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1184,34 +1145,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>48.17</v>
+        <v>45.89</v>
       </c>
       <c r="Z3">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="AA3">
         <v>0.04</v>
       </c>
       <c r="AB3">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>28.81</v>
+        <v>13.21</v>
       </c>
       <c r="AD3">
-        <v>44.98</v>
+        <v>28.75</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF3">
-        <v>40.81</v>
+        <v>-13.49</v>
       </c>
       <c r="AG3">
-        <v>60.48</v>
+        <v>60.47</v>
       </c>
       <c r="AH3">
-        <v>58.74</v>
+        <v>58.77</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1220,7 +1181,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>14.56</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1231,10 +1192,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>93.98999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D4">
-        <v>0.15</v>
+        <v>-0.9</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1243,43 +1204,43 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-13.62</v>
+        <v>-14.4</v>
       </c>
       <c r="H4">
-        <v>7.01</v>
+        <v>6.05</v>
       </c>
       <c r="I4">
-        <v>0.16</v>
+        <v>-0.77</v>
       </c>
       <c r="J4">
-        <v>-2.87</v>
+        <v>-3.7</v>
       </c>
       <c r="K4">
-        <v>-10.21</v>
+        <v>-10.28</v>
       </c>
       <c r="L4">
-        <v>3.19</v>
+        <v>2.92</v>
       </c>
       <c r="M4">
-        <v>29.74</v>
+        <v>30.12</v>
       </c>
       <c r="N4">
         <v>16</v>
       </c>
       <c r="P4">
-        <v>93.98</v>
+        <v>93.84</v>
       </c>
       <c r="Q4">
-        <v>94.69</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="R4">
-        <v>96.15000000000001</v>
+        <v>96.06</v>
       </c>
       <c r="S4">
-        <v>97.93000000000001</v>
+        <v>97.92</v>
       </c>
       <c r="T4">
-        <v>-4.02</v>
+        <v>-4.88</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1294,43 +1255,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.39</v>
+        <v>31.26</v>
       </c>
       <c r="Z4">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="AA4">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
       <c r="AB4">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="AC4">
-        <v>66.22</v>
+        <v>45.44</v>
       </c>
       <c r="AD4">
-        <v>67.09</v>
+        <v>61.55</v>
       </c>
       <c r="AE4">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AF4">
-        <v>10.05</v>
+        <v>22.52</v>
       </c>
       <c r="AG4">
-        <v>96.65000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="AH4">
-        <v>92.73999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="AI4">
-        <v>99.29000000000001</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>11.34</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1341,10 +1302,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>51.35</v>
+        <v>51.05</v>
       </c>
       <c r="D5">
-        <v>-1.21</v>
+        <v>-0.58</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1353,43 +1314,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-15.82</v>
+        <v>-16.31</v>
       </c>
       <c r="H5">
-        <v>5.51</v>
+        <v>4.89</v>
       </c>
       <c r="I5">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="J5">
-        <v>-2.41</v>
+        <v>-2.65</v>
       </c>
       <c r="K5">
-        <v>-4.61</v>
+        <v>-4.9</v>
       </c>
       <c r="L5">
-        <v>-12.52</v>
+        <v>-12.51</v>
       </c>
       <c r="M5">
-        <v>6.34</v>
+        <v>5.88</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>52.03</v>
+        <v>51.83</v>
       </c>
       <c r="Q5">
-        <v>52.71</v>
+        <v>52.62</v>
       </c>
       <c r="R5">
-        <v>52.75</v>
+        <v>52.72</v>
       </c>
       <c r="S5">
-        <v>54.63</v>
+        <v>54.58</v>
       </c>
       <c r="T5">
-        <v>-6</v>
+        <v>-6.47</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1404,43 +1365,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>34.79</v>
+        <v>32.42</v>
       </c>
       <c r="Z5">
-        <v>-0.22</v>
+        <v>-0.31</v>
       </c>
       <c r="AA5">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AB5">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="AC5">
-        <v>11.56</v>
+        <v>1.28</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>12.06</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>208.84</v>
+        <v>-29.41</v>
       </c>
       <c r="AG5">
-        <v>53.72</v>
+        <v>53.87</v>
       </c>
       <c r="AH5">
-        <v>51.71</v>
+        <v>51.38</v>
       </c>
       <c r="AI5">
-        <v>54.72</v>
+        <v>54.3</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>22.36</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1451,10 +1412,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>126.43</v>
+        <v>125.73</v>
       </c>
       <c r="D6">
-        <v>1.04</v>
+        <v>-0.55</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1463,43 +1424,43 @@
         <v>82.08</v>
       </c>
       <c r="G6">
-        <v>-13.72</v>
+        <v>-14.2</v>
       </c>
       <c r="H6">
-        <v>54.03</v>
+        <v>53.18</v>
       </c>
       <c r="I6">
-        <v>0.72</v>
+        <v>-0.57</v>
       </c>
       <c r="J6">
-        <v>8.210000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="K6">
-        <v>-3.3</v>
+        <v>-3.66</v>
       </c>
       <c r="L6">
-        <v>51.98</v>
+        <v>51.23</v>
       </c>
       <c r="M6">
-        <v>25.25</v>
+        <v>25.16</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>125.72</v>
+        <v>125.58</v>
       </c>
       <c r="Q6">
-        <v>121.05</v>
+        <v>121.38</v>
       </c>
       <c r="R6">
-        <v>119.51</v>
+        <v>119.6</v>
       </c>
       <c r="S6">
-        <v>119.87</v>
+        <v>120</v>
       </c>
       <c r="T6">
-        <v>5.47</v>
+        <v>4.78</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1514,34 +1475,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>69.69</v>
+        <v>65.95</v>
       </c>
       <c r="Z6">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AA6">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AB6">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="AC6">
-        <v>80.95999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="AD6">
-        <v>82.39</v>
+        <v>80.11</v>
       </c>
       <c r="AE6">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AF6">
-        <v>-33.97</v>
+        <v>-22.13</v>
       </c>
       <c r="AG6">
-        <v>128.63</v>
+        <v>129.18</v>
       </c>
       <c r="AH6">
-        <v>113.47</v>
+        <v>113.58</v>
       </c>
       <c r="AI6">
         <v>121.38</v>
@@ -1550,7 +1511,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>39.01</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1561,10 +1522,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>130.71</v>
+        <v>130.07</v>
       </c>
       <c r="D7">
-        <v>0.07000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1573,43 +1534,43 @@
         <v>84.73999999999999</v>
       </c>
       <c r="G7">
-        <v>-13.65</v>
+        <v>-14.08</v>
       </c>
       <c r="H7">
-        <v>54.25</v>
+        <v>53.49</v>
       </c>
       <c r="I7">
-        <v>0.76</v>
+        <v>-0.41</v>
       </c>
       <c r="J7">
-        <v>8.210000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="K7">
-        <v>-3.2</v>
+        <v>-3.51</v>
       </c>
       <c r="L7">
-        <v>52.18</v>
+        <v>51.56</v>
       </c>
       <c r="M7">
-        <v>33.26</v>
+        <v>33.02</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>130.18</v>
+        <v>130.08</v>
       </c>
       <c r="Q7">
-        <v>125.15</v>
+        <v>125.5</v>
       </c>
       <c r="R7">
-        <v>123.56</v>
+        <v>123.66</v>
       </c>
       <c r="S7">
-        <v>123.83</v>
+        <v>123.97</v>
       </c>
       <c r="T7">
-        <v>5.55</v>
+        <v>4.92</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1624,34 +1585,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>69.97</v>
+        <v>66.56</v>
       </c>
       <c r="Z7">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AA7">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AB7">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="AC7">
-        <v>85.40000000000001</v>
+        <v>84.78</v>
       </c>
       <c r="AD7">
-        <v>85.52</v>
+        <v>84.63</v>
       </c>
       <c r="AE7">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
       <c r="AF7">
-        <v>-22.11</v>
+        <v>-12.4</v>
       </c>
       <c r="AG7">
-        <v>133.14</v>
+        <v>133.71</v>
       </c>
       <c r="AH7">
-        <v>117.16</v>
+        <v>117.28</v>
       </c>
       <c r="AI7">
         <v>124.53</v>
@@ -1660,7 +1621,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>42.82</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1671,10 +1632,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>481.22</v>
+        <v>479.18</v>
       </c>
       <c r="D8">
-        <v>-0.3</v>
+        <v>-0.42</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1683,43 +1644,43 @@
         <v>441.2</v>
       </c>
       <c r="G8">
-        <v>-15.03</v>
+        <v>-15.39</v>
       </c>
       <c r="H8">
-        <v>9.07</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="I8">
-        <v>-0.67</v>
+        <v>-0.24</v>
       </c>
       <c r="J8">
-        <v>-0.75</v>
+        <v>-0.86</v>
       </c>
       <c r="K8">
-        <v>-9.56</v>
+        <v>-10.31</v>
       </c>
       <c r="L8">
-        <v>7.99</v>
+        <v>3.72</v>
       </c>
       <c r="M8">
-        <v>7.75</v>
+        <v>8.4</v>
       </c>
       <c r="N8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P8">
-        <v>481.37</v>
+        <v>481.15</v>
       </c>
       <c r="Q8">
-        <v>487.04</v>
+        <v>487.06</v>
       </c>
       <c r="R8">
-        <v>483.23</v>
+        <v>483.14</v>
       </c>
       <c r="S8">
-        <v>511.05</v>
+        <v>510.83</v>
       </c>
       <c r="T8">
-        <v>-5.84</v>
+        <v>-6.2</v>
       </c>
       <c r="U8" t="s">
         <v>59</v>
@@ -1734,34 +1695,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>43.82</v>
+        <v>41.5</v>
       </c>
       <c r="Z8">
-        <v>-1.25</v>
+        <v>-1.57</v>
       </c>
       <c r="AA8">
-        <v>-0.38</v>
+        <v>-0.62</v>
       </c>
       <c r="AB8">
-        <v>-0.87</v>
+        <v>-0.96</v>
       </c>
       <c r="AC8">
-        <v>16.12</v>
+        <v>9.73</v>
       </c>
       <c r="AD8">
-        <v>11.76</v>
+        <v>12.88</v>
       </c>
       <c r="AE8">
-        <v>10.29</v>
+        <v>10.58</v>
       </c>
       <c r="AF8">
-        <v>31.71</v>
+        <v>-28.34</v>
       </c>
       <c r="AG8">
-        <v>497.88</v>
+        <v>497.82</v>
       </c>
       <c r="AH8">
-        <v>476.19</v>
+        <v>476.29</v>
       </c>
       <c r="AI8">
         <v>511.37</v>
@@ -1770,7 +1731,7 @@
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>23.41</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1781,10 +1742,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>973.6799999999999</v>
+        <v>963.99</v>
       </c>
       <c r="D9">
-        <v>-0.33</v>
+        <v>-1</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1793,43 +1754,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-3.49</v>
+        <v>-4.45</v>
       </c>
       <c r="H9">
-        <v>10.01</v>
+        <v>8.92</v>
       </c>
       <c r="I9">
-        <v>0.07000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="J9">
-        <v>-0.04</v>
+        <v>-1.05</v>
       </c>
       <c r="K9">
-        <v>0.87</v>
+        <v>-0.02</v>
       </c>
       <c r="L9">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="M9">
-        <v>15.43</v>
+        <v>15.71</v>
       </c>
       <c r="N9">
         <v>58</v>
       </c>
       <c r="P9">
-        <v>972.9</v>
+        <v>971.95</v>
       </c>
       <c r="Q9">
-        <v>970.16</v>
+        <v>970.08</v>
       </c>
       <c r="R9">
-        <v>969.48</v>
+        <v>970.03</v>
       </c>
       <c r="S9">
-        <v>965.71</v>
+        <v>965.6</v>
       </c>
       <c r="T9">
-        <v>0.83</v>
+        <v>-0.17</v>
       </c>
       <c r="U9" t="s">
         <v>59</v>
@@ -1841,37 +1802,37 @@
         <v>59</v>
       </c>
       <c r="X9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>52.2</v>
+        <v>44.33</v>
       </c>
       <c r="Z9">
-        <v>1.94</v>
+        <v>1.05</v>
       </c>
       <c r="AA9">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AB9">
-        <v>0.22</v>
+        <v>-0.53</v>
       </c>
       <c r="AC9">
-        <v>48.41</v>
+        <v>27.78</v>
       </c>
       <c r="AD9">
-        <v>43.42</v>
+        <v>40.24</v>
       </c>
       <c r="AE9">
-        <v>11.33</v>
+        <v>11.65</v>
       </c>
       <c r="AF9">
-        <v>-49.16</v>
+        <v>32.4</v>
       </c>
       <c r="AG9">
-        <v>984.46</v>
+        <v>984.51</v>
       </c>
       <c r="AH9">
-        <v>955.85</v>
+        <v>955.64</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1880,7 +1841,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>17.39</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1891,10 +1852,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>33.69</v>
+        <v>33.67</v>
       </c>
       <c r="D10">
-        <v>-3.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1903,43 +1864,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-21.96</v>
+        <v>-22.01</v>
       </c>
       <c r="H10">
-        <v>17.71</v>
+        <v>17.64</v>
       </c>
       <c r="I10">
-        <v>-4.34</v>
+        <v>-2.86</v>
       </c>
       <c r="J10">
-        <v>3.82</v>
+        <v>4.57</v>
       </c>
       <c r="K10">
-        <v>5.31</v>
+        <v>5.75</v>
       </c>
       <c r="L10">
-        <v>-10.71</v>
+        <v>-10.95</v>
       </c>
       <c r="M10">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="N10">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P10">
-        <v>34.52</v>
+        <v>34.32</v>
       </c>
       <c r="Q10">
-        <v>34.09</v>
+        <v>34.18</v>
       </c>
       <c r="R10">
-        <v>32.19</v>
+        <v>32.24</v>
       </c>
       <c r="S10">
-        <v>35.71</v>
+        <v>35.68</v>
       </c>
       <c r="T10">
-        <v>-5.66</v>
+        <v>-5.64</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1954,34 +1915,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>50.28</v>
+        <v>50.07</v>
       </c>
       <c r="Z10">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="AA10">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="AB10">
-        <v>-0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="AC10">
-        <v>4.69</v>
+        <v>2.35</v>
       </c>
       <c r="AD10">
-        <v>12.05</v>
+        <v>5.64</v>
       </c>
       <c r="AE10">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="AF10">
-        <v>-60.76</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="AG10">
-        <v>36.34</v>
+        <v>36.16</v>
       </c>
       <c r="AH10">
-        <v>31.84</v>
+        <v>32.2</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -1990,7 +1951,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>34.82</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2001,10 +1962,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>33.58</v>
+        <v>33.68</v>
       </c>
       <c r="D11">
-        <v>-3.53</v>
+        <v>0.3</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -2013,43 +1974,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-22.43</v>
+        <v>-22.2</v>
       </c>
       <c r="H11">
-        <v>17.29</v>
+        <v>17.64</v>
       </c>
       <c r="I11">
-        <v>-4.71</v>
+        <v>-2.8</v>
       </c>
       <c r="J11">
-        <v>3.71</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
-        <v>4.68</v>
+        <v>5.18</v>
       </c>
       <c r="L11">
-        <v>-11.4</v>
+        <v>-11.65</v>
       </c>
       <c r="M11">
-        <v>-0.28</v>
+        <v>-0.15</v>
       </c>
       <c r="N11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P11">
-        <v>34.52</v>
+        <v>34.33</v>
       </c>
       <c r="Q11">
-        <v>34.11</v>
+        <v>34.2</v>
       </c>
       <c r="R11">
-        <v>32.2</v>
+        <v>32.25</v>
       </c>
       <c r="S11">
-        <v>35.78</v>
+        <v>35.75</v>
       </c>
       <c r="T11">
-        <v>-6.15</v>
+        <v>-5.8</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -2064,34 +2025,34 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>49.01</v>
+        <v>49.99</v>
       </c>
       <c r="Z11">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="AA11">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="AB11">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="AC11">
-        <v>8.289999999999999</v>
+        <v>5.69</v>
       </c>
       <c r="AD11">
-        <v>15.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>-40.98</v>
+        <v>-57.95</v>
       </c>
       <c r="AG11">
-        <v>36.4</v>
+        <v>36.22</v>
       </c>
       <c r="AH11">
-        <v>31.81</v>
+        <v>32.19</v>
       </c>
       <c r="AI11">
         <v>32.2</v>
@@ -2100,7 +2061,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>33.88</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2111,10 +2072,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>805.9</v>
+        <v>799.85</v>
       </c>
       <c r="D12">
-        <v>-0.24</v>
+        <v>-0.75</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2123,43 +2084,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-0.38</v>
+        <v>-1.13</v>
       </c>
       <c r="H12">
-        <v>23.62</v>
+        <v>22.7</v>
       </c>
       <c r="I12">
-        <v>-0.22</v>
+        <v>-0.8</v>
       </c>
       <c r="J12">
-        <v>3.12</v>
+        <v>1.97</v>
       </c>
       <c r="K12">
-        <v>7.51</v>
+        <v>6.17</v>
       </c>
       <c r="L12">
-        <v>12.56</v>
+        <v>11.83</v>
       </c>
       <c r="M12">
-        <v>14.02</v>
+        <v>14.14</v>
       </c>
       <c r="N12">
         <v>73</v>
       </c>
       <c r="P12">
-        <v>807.1</v>
+        <v>805.8099999999999</v>
       </c>
       <c r="Q12">
-        <v>796.76</v>
+        <v>797.77</v>
       </c>
       <c r="R12">
-        <v>783.63</v>
+        <v>784.6900000000001</v>
       </c>
       <c r="S12">
-        <v>749.7</v>
+        <v>749.9400000000001</v>
       </c>
       <c r="T12">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -2174,34 +2135,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>65.06999999999999</v>
+        <v>55.63</v>
       </c>
       <c r="Z12">
-        <v>7.99</v>
+        <v>7.1</v>
       </c>
       <c r="AA12">
-        <v>7.93</v>
+        <v>7.77</v>
       </c>
       <c r="AB12">
-        <v>0.06</v>
+        <v>-0.67</v>
       </c>
       <c r="AC12">
-        <v>74.73</v>
+        <v>46.5</v>
       </c>
       <c r="AD12">
-        <v>80.52</v>
+        <v>68.25</v>
       </c>
       <c r="AE12">
-        <v>14.89</v>
+        <v>14.32</v>
       </c>
       <c r="AF12">
-        <v>-22.06</v>
+        <v>365.76</v>
       </c>
       <c r="AG12">
-        <v>822.3200000000001</v>
+        <v>822.05</v>
       </c>
       <c r="AH12">
-        <v>771.1900000000001</v>
+        <v>773.49</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2210,7 +2171,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>28.58</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2221,10 +2182,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>276.1</v>
+        <v>274.62</v>
       </c>
       <c r="D13">
-        <v>-0.8100000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2233,43 +2194,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-7.21</v>
+        <v>-7.71</v>
       </c>
       <c r="H13">
-        <v>8.94</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I13">
-        <v>-1.09</v>
+        <v>-1.33</v>
       </c>
       <c r="J13">
-        <v>0.19</v>
+        <v>-0.19</v>
       </c>
       <c r="K13">
-        <v>2.94</v>
+        <v>2.05</v>
       </c>
       <c r="L13">
-        <v>-0.6899999999999999</v>
+        <v>-1.3</v>
       </c>
       <c r="M13">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="N13">
         <v>42</v>
       </c>
       <c r="P13">
-        <v>277.86</v>
+        <v>277.12</v>
       </c>
       <c r="Q13">
-        <v>277.07</v>
+        <v>277.13</v>
       </c>
       <c r="R13">
-        <v>274.41</v>
+        <v>274.64</v>
       </c>
       <c r="S13">
-        <v>279.77</v>
+        <v>279.69</v>
       </c>
       <c r="T13">
-        <v>-1.31</v>
+        <v>-1.81</v>
       </c>
       <c r="U13" t="s">
         <v>59</v>
@@ -2284,34 +2245,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>47.76</v>
+        <v>43.15</v>
       </c>
       <c r="Z13">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AA13">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>-0.34</v>
+        <v>-0.55</v>
       </c>
       <c r="AC13">
-        <v>13.44</v>
+        <v>1.9</v>
       </c>
       <c r="AD13">
-        <v>25.73</v>
+        <v>13</v>
       </c>
       <c r="AE13">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="AF13">
-        <v>-13.01</v>
+        <v>14.15</v>
       </c>
       <c r="AG13">
-        <v>282.92</v>
+        <v>282.84</v>
       </c>
       <c r="AH13">
-        <v>271.22</v>
+        <v>271.42</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2320,7 +2281,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>11.74</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2331,10 +2292,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>268.59</v>
+        <v>267.46</v>
       </c>
       <c r="D14">
-        <v>-0.72</v>
+        <v>-0.42</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2343,31 +2304,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-7.26</v>
+        <v>-7.65</v>
       </c>
       <c r="H14">
-        <v>8.93</v>
+        <v>8.48</v>
       </c>
       <c r="I14">
-        <v>-1.15</v>
+        <v>-1.18</v>
       </c>
       <c r="J14">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="K14">
-        <v>2.96</v>
+        <v>2.08</v>
       </c>
       <c r="M14">
-        <v>-9.279999999999999</v>
+        <v>-9.81</v>
       </c>
       <c r="P14">
-        <v>270.2</v>
+        <v>269.56</v>
       </c>
       <c r="Q14">
-        <v>269.53</v>
+        <v>269.6</v>
       </c>
       <c r="R14">
-        <v>267.17</v>
+        <v>267.39</v>
       </c>
       <c r="U14" t="s">
         <v>59</v>
@@ -2379,34 +2340,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>47.52</v>
+        <v>43.66</v>
       </c>
       <c r="Z14">
-        <v>1.03</v>
+        <v>0.72</v>
       </c>
       <c r="AA14">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AB14">
-        <v>-0.33</v>
+        <v>-0.51</v>
       </c>
       <c r="AC14">
-        <v>11.46</v>
+        <v>0.84</v>
       </c>
       <c r="AD14">
-        <v>26.09</v>
+        <v>12.23</v>
       </c>
       <c r="AE14">
-        <v>3.79</v>
+        <v>3.64</v>
       </c>
       <c r="AF14">
-        <v>-12.95</v>
+        <v>-33.38</v>
       </c>
       <c r="AG14">
-        <v>274.98</v>
+        <v>274.9</v>
       </c>
       <c r="AH14">
-        <v>264.08</v>
+        <v>264.29</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2415,7 +2376,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>55.74</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2426,10 +2387,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>263.65</v>
+        <v>262.19</v>
       </c>
       <c r="D15">
-        <v>-0.78</v>
+        <v>-0.55</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2438,43 +2399,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-7.27</v>
+        <v>-7.78</v>
       </c>
       <c r="H15">
-        <v>9.17</v>
+        <v>8.56</v>
       </c>
       <c r="I15">
-        <v>-1.1</v>
+        <v>-1.27</v>
       </c>
       <c r="J15">
-        <v>-0.29</v>
+        <v>-0.37</v>
       </c>
       <c r="K15">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="L15">
-        <v>-0.64</v>
+        <v>-1.27</v>
       </c>
       <c r="M15">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="N15">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P15">
-        <v>265.19</v>
+        <v>264.52</v>
       </c>
       <c r="Q15">
-        <v>264.63</v>
+        <v>264.68</v>
       </c>
       <c r="R15">
-        <v>262.12</v>
+        <v>262.34</v>
       </c>
       <c r="S15">
-        <v>267.08</v>
+        <v>267</v>
       </c>
       <c r="T15">
-        <v>-1.28</v>
+        <v>-1.8</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -2489,34 +2450,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>47.67</v>
+        <v>43.24</v>
       </c>
       <c r="Z15">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA15">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AB15">
-        <v>-0.37</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AC15">
-        <v>15.25</v>
+        <v>3.47</v>
       </c>
       <c r="AD15">
-        <v>26.17</v>
+        <v>14.42</v>
       </c>
       <c r="AE15">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="AF15">
-        <v>61.19</v>
+        <v>127.94</v>
       </c>
       <c r="AG15">
-        <v>270.53</v>
+        <v>270.47</v>
       </c>
       <c r="AH15">
-        <v>258.72</v>
+        <v>258.9</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2525,7 +2486,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>33.55</v>
+        <v>35.21</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2536,10 +2497,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>274.6</v>
+        <v>273.27</v>
       </c>
       <c r="D16">
-        <v>-0.8100000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2548,43 +2509,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-7.22</v>
+        <v>-7.67</v>
       </c>
       <c r="H16">
-        <v>8.960000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="I16">
-        <v>-1.1</v>
+        <v>-1.28</v>
       </c>
       <c r="J16">
-        <v>0.16</v>
+        <v>-0.21</v>
       </c>
       <c r="K16">
-        <v>2.93</v>
+        <v>2.06</v>
       </c>
       <c r="L16">
-        <v>-0.75</v>
+        <v>-1.29</v>
       </c>
       <c r="M16">
-        <v>9.109999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="N16">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="P16">
-        <v>276.37</v>
+        <v>275.66</v>
       </c>
       <c r="Q16">
-        <v>275.64</v>
+        <v>275.71</v>
       </c>
       <c r="R16">
-        <v>273.02</v>
+        <v>273.26</v>
       </c>
       <c r="S16">
-        <v>278.38</v>
+        <v>278.3</v>
       </c>
       <c r="T16">
-        <v>-1.36</v>
+        <v>-1.81</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -2599,34 +2560,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>47.51</v>
+        <v>43.4</v>
       </c>
       <c r="Z16">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="AA16">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB16">
-        <v>-0.35</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AC16">
+        <v>0.77</v>
+      </c>
+      <c r="AD16">
         <v>10.52</v>
       </c>
-      <c r="AD16">
-        <v>22.56</v>
-      </c>
       <c r="AE16">
-        <v>4.06</v>
+        <v>4.37</v>
       </c>
       <c r="AF16">
-        <v>-51.29</v>
+        <v>-25.36</v>
       </c>
       <c r="AG16">
-        <v>281.51</v>
+        <v>281.42</v>
       </c>
       <c r="AH16">
-        <v>269.78</v>
+        <v>269.99</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2635,7 +2596,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>52.41</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2646,10 +2607,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>96.52</v>
+        <v>96.13</v>
       </c>
       <c r="D17">
-        <v>-1.03</v>
+        <v>-0.4</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2658,43 +2619,43 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-12.15</v>
+        <v>-12.51</v>
       </c>
       <c r="H17">
-        <v>28.33</v>
+        <v>27.82</v>
       </c>
       <c r="I17">
-        <v>0.07000000000000001</v>
+        <v>-2.18</v>
       </c>
       <c r="J17">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
       <c r="K17">
-        <v>8.1</v>
+        <v>7.26</v>
       </c>
       <c r="L17">
-        <v>23.14</v>
+        <v>22.55</v>
       </c>
       <c r="M17">
-        <v>30.6</v>
+        <v>31.39</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>97.59</v>
+        <v>97.16</v>
       </c>
       <c r="Q17">
-        <v>95.33</v>
+        <v>95.45</v>
       </c>
       <c r="R17">
-        <v>95.05</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S17">
-        <v>95.73999999999999</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="T17">
-        <v>0.82</v>
+        <v>0.38</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -2709,34 +2670,34 @@
         <v>2</v>
       </c>
       <c r="Y17">
-        <v>54.32</v>
+        <v>52.36</v>
       </c>
       <c r="Z17">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="AA17">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="AB17">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC17">
-        <v>58.99</v>
+        <v>43.28</v>
       </c>
       <c r="AD17">
-        <v>71.77</v>
+        <v>58.97</v>
       </c>
       <c r="AE17">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AF17">
-        <v>-49.64</v>
+        <v>-68.34999999999999</v>
       </c>
       <c r="AG17">
-        <v>99.40000000000001</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="AH17">
-        <v>91.25</v>
+        <v>91.44</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2745,7 +2706,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>39.74</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2756,10 +2717,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>278.01</v>
+        <v>278.82</v>
       </c>
       <c r="D18">
-        <v>-0.63</v>
+        <v>0.29</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2768,43 +2729,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-6.25</v>
+        <v>-5.97</v>
       </c>
       <c r="H18">
-        <v>13.21</v>
+        <v>13.54</v>
       </c>
       <c r="I18">
-        <v>-0.78</v>
+        <v>-0.43</v>
       </c>
       <c r="J18">
-        <v>-2.36</v>
+        <v>-2</v>
       </c>
       <c r="K18">
-        <v>4.74</v>
+        <v>3.92</v>
       </c>
       <c r="L18">
-        <v>2.33</v>
+        <v>2.84</v>
       </c>
       <c r="M18">
-        <v>8.59</v>
+        <v>8.91</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>279.37</v>
+        <v>279.13</v>
       </c>
       <c r="Q18">
-        <v>280.82</v>
+        <v>280.7</v>
       </c>
       <c r="R18">
-        <v>283.24</v>
+        <v>283.36</v>
       </c>
       <c r="S18">
-        <v>281.41</v>
+        <v>281.38</v>
       </c>
       <c r="T18">
-        <v>-1.21</v>
+        <v>-0.91</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2819,34 +2780,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>40.59</v>
+        <v>43.11</v>
       </c>
       <c r="Z18">
-        <v>-0.9</v>
+        <v>-0.97</v>
       </c>
       <c r="AA18">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AB18">
-        <v>-0.43</v>
+        <v>-0.4</v>
       </c>
       <c r="AC18">
-        <v>8.6</v>
+        <v>11.17</v>
       </c>
       <c r="AD18">
-        <v>9.01</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AE18">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="AF18">
-        <v>-13.55</v>
+        <v>-82.36</v>
       </c>
       <c r="AG18">
-        <v>284.66</v>
+        <v>284.64</v>
       </c>
       <c r="AH18">
-        <v>276.99</v>
+        <v>276.77</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2855,7 +2816,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>18.32</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2866,10 +2827,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>227.17</v>
+        <v>221.77</v>
       </c>
       <c r="D19">
-        <v>0.22</v>
+        <v>-2.38</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2878,43 +2839,43 @@
         <v>109.64</v>
       </c>
       <c r="G19">
-        <v>-36.59</v>
+        <v>-38.09</v>
       </c>
       <c r="H19">
-        <v>107.2</v>
+        <v>102.27</v>
       </c>
       <c r="I19">
-        <v>-0.31</v>
+        <v>-4.16</v>
       </c>
       <c r="J19">
-        <v>6.58</v>
+        <v>2.08</v>
       </c>
       <c r="K19">
-        <v>-11.85</v>
+        <v>-14.2</v>
       </c>
       <c r="L19">
-        <v>99.31</v>
+        <v>95.41</v>
       </c>
       <c r="M19">
-        <v>53.81</v>
+        <v>51.98</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>227.64</v>
+        <v>225.72</v>
       </c>
       <c r="Q19">
-        <v>219.81</v>
+        <v>219.98</v>
       </c>
       <c r="R19">
-        <v>220.85</v>
+        <v>220.76</v>
       </c>
       <c r="S19">
-        <v>226.69</v>
+        <v>227.07</v>
       </c>
       <c r="T19">
-        <v>0.21</v>
+        <v>-2.33</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -2926,37 +2887,37 @@
         <v>58</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>58.99</v>
+        <v>49.86</v>
       </c>
       <c r="Z19">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="AA19">
-        <v>0.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AB19">
-        <v>1.5</v>
+        <v>0.92</v>
       </c>
       <c r="AC19">
-        <v>69.03</v>
+        <v>58.05</v>
       </c>
       <c r="AD19">
-        <v>71.78</v>
+        <v>64.97</v>
       </c>
       <c r="AE19">
-        <v>5.72</v>
+        <v>5.79</v>
       </c>
       <c r="AF19">
-        <v>-34.68</v>
+        <v>-3.37</v>
       </c>
       <c r="AG19">
-        <v>233.44</v>
+        <v>233.62</v>
       </c>
       <c r="AH19">
-        <v>206.19</v>
+        <v>206.35</v>
       </c>
       <c r="AI19">
         <v>215.89</v>
@@ -2965,7 +2926,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>45.43</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2976,10 +2937,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>260.94</v>
+        <v>259.51</v>
       </c>
       <c r="D20">
-        <v>-0.8</v>
+        <v>-0.55</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2988,43 +2949,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-7.21</v>
+        <v>-7.72</v>
       </c>
       <c r="H20">
-        <v>9.02</v>
+        <v>8.42</v>
       </c>
       <c r="I20">
-        <v>-1.07</v>
+        <v>-1.32</v>
       </c>
       <c r="J20">
-        <v>0.21</v>
+        <v>-0.26</v>
       </c>
       <c r="K20">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="L20">
-        <v>-0.75</v>
+        <v>-1.37</v>
       </c>
       <c r="M20">
-        <v>9.06</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N20">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="P20">
-        <v>262.57</v>
+        <v>261.88</v>
       </c>
       <c r="Q20">
-        <v>261.84</v>
+        <v>261.9</v>
       </c>
       <c r="R20">
-        <v>259.39</v>
+        <v>259.61</v>
       </c>
       <c r="S20">
-        <v>264.46</v>
+        <v>264.39</v>
       </c>
       <c r="T20">
-        <v>-1.33</v>
+        <v>-1.84</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -3039,34 +3000,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>47.76</v>
+        <v>43.06</v>
       </c>
       <c r="Z20">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="AA20">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AB20">
-        <v>-0.32</v>
+        <v>-0.52</v>
       </c>
       <c r="AC20">
-        <v>14.21</v>
+        <v>2.26</v>
       </c>
       <c r="AD20">
-        <v>26.52</v>
+        <v>13.69</v>
       </c>
       <c r="AE20">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="AF20">
-        <v>-41.13</v>
+        <v>-0.93</v>
       </c>
       <c r="AG20">
-        <v>267.31</v>
+        <v>267.23</v>
       </c>
       <c r="AH20">
-        <v>256.38</v>
+        <v>256.57</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3075,7 +3036,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>30.66</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3086,10 +3047,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>798.66</v>
+        <v>793.1900000000001</v>
       </c>
       <c r="D21">
-        <v>-0.12</v>
+        <v>-0.68</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3098,43 +3059,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-0.57</v>
+        <v>-1.25</v>
       </c>
       <c r="H21">
-        <v>24.27</v>
+        <v>23.42</v>
       </c>
       <c r="I21">
-        <v>-0.27</v>
+        <v>-0.8</v>
       </c>
       <c r="J21">
-        <v>3.16</v>
+        <v>1.72</v>
       </c>
       <c r="K21">
-        <v>7.38</v>
+        <v>6.61</v>
       </c>
       <c r="L21">
-        <v>12.94</v>
+        <v>12.03</v>
       </c>
       <c r="M21">
-        <v>14.03</v>
+        <v>14.08</v>
       </c>
       <c r="N21">
         <v>78</v>
       </c>
       <c r="P21">
-        <v>799.74</v>
+        <v>798.46</v>
       </c>
       <c r="Q21">
-        <v>789.66</v>
+        <v>790.59</v>
       </c>
       <c r="R21">
-        <v>776.45</v>
+        <v>777.53</v>
       </c>
       <c r="S21">
-        <v>742.84</v>
+        <v>743.08</v>
       </c>
       <c r="T21">
-        <v>7.51</v>
+        <v>6.74</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -3149,34 +3110,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>61.99</v>
+        <v>55.28</v>
       </c>
       <c r="Z21">
-        <v>7.8</v>
+        <v>6.99</v>
       </c>
       <c r="AA21">
-        <v>7.71</v>
+        <v>7.56</v>
       </c>
       <c r="AB21">
-        <v>0.1</v>
+        <v>-0.57</v>
       </c>
       <c r="AC21">
-        <v>59.04</v>
+        <v>36.02</v>
       </c>
       <c r="AD21">
-        <v>68.19</v>
+        <v>54.94</v>
       </c>
       <c r="AE21">
-        <v>11.65</v>
+        <v>11.44</v>
       </c>
       <c r="AF21">
-        <v>58.26</v>
+        <v>-34.07</v>
       </c>
       <c r="AG21">
-        <v>812.88</v>
+        <v>812.74</v>
       </c>
       <c r="AH21">
-        <v>766.4400000000001</v>
+        <v>768.45</v>
       </c>
       <c r="AI21">
         <v>773.79</v>
@@ -3185,7 +3146,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>15.14</v>
+        <v>16.24</v>
       </c>
     </row>
   </sheetData>
@@ -3326,7 +3287,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3366,3144 +3327,2879 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-0.89</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-0.91</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-3.7</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>86</v>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.41</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.65</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>83</v>
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="D12" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>80</v>
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="D13" s="6">
+        <v>6.87</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.86</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.04</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.01</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>93</v>
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>3.82</v>
+      </c>
+      <c r="D16" s="6">
+        <v>4.57</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.12</v>
+        <v>3.71</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.89</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.77</v>
+        <v>4.6</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.13</v>
+        <v>3.12</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.91</v>
+        <v>1.97</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.78</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.76</v>
+        <v>0.19</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.87</v>
+        <v>-0.19</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.11</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>0.63</v>
+        <v>-0.03</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.41</v>
+        <v>-0.08</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.04</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>7.44</v>
+        <v>-0.29</v>
       </c>
       <c r="D21" s="6">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.77</v>
+        <v>-0.37</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>7.38</v>
+        <v>0.16</v>
       </c>
       <c r="D22" s="6">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.83</v>
+        <v>-0.21</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.34</v>
+        <v>0.37</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.75</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.41</v>
+        <v>0.73</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>1.68</v>
+        <v>-2.36</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.04</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.72</v>
+        <v>-2</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>9</v>
+        <v>6.58</v>
       </c>
       <c r="D25" s="6">
-        <v>3.82</v>
+        <v>2.08</v>
       </c>
       <c r="E25" s="7">
-        <v>-5.18</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>9.220000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="D26" s="6">
-        <v>3.71</v>
+        <v>-0.26</v>
       </c>
       <c r="E26" s="7">
-        <v>-5.51</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>3.97</v>
+        <v>3.16</v>
       </c>
       <c r="D27" s="6">
-        <v>3.12</v>
+        <v>1.72</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.85</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>1.59</v>
+        <v>-0</v>
       </c>
       <c r="D28" s="6">
-        <v>0.19</v>
+        <v>-0.96</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.4</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>1.47</v>
+        <v>-0.1</v>
       </c>
       <c r="D29" s="6">
-        <v>-0.03</v>
+        <v>-1.18</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.5</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>1.47</v>
+        <v>0.16</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.29</v>
+        <v>-0.77</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.76</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>1.6</v>
+        <v>-2.3</v>
       </c>
       <c r="D31" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.44</v>
+        <v>-1.9</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>4.59</v>
+        <v>0.72</v>
       </c>
       <c r="D32" s="6">
-        <v>0.37</v>
+        <v>-0.57</v>
       </c>
       <c r="E32" s="7">
-        <v>-4.22</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.63</v>
+        <v>0.76</v>
       </c>
       <c r="D33" s="6">
-        <v>-2.36</v>
+        <v>-0.41</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.73</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>6.88</v>
+        <v>-0.67</v>
       </c>
       <c r="D34" s="6">
-        <v>6.58</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.3</v>
+        <v>-0.24</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>1.67</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D35" s="6">
-        <v>0.21</v>
+        <v>-0.49</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.46</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>3.8</v>
+        <v>-4.34</v>
       </c>
       <c r="D36" s="6">
-        <v>3.16</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.64</v>
+        <v>-2.86</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-0.4</v>
+        <v>-4.71</v>
       </c>
       <c r="D37" s="6">
-        <v>-0</v>
+        <v>-2.8</v>
       </c>
       <c r="E37" s="8">
-        <v>0.4</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
+        <v>-0.22</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-0.8</v>
+      </c>
+      <c r="E38" s="7">
         <v>-0.58</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.48</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.45</v>
+        <v>-1.09</v>
       </c>
       <c r="D39" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.61</v>
+        <v>-1.33</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.19</v>
+        <v>-1.15</v>
       </c>
       <c r="D40" s="6">
-        <v>-2.3</v>
+        <v>-1.18</v>
       </c>
       <c r="E40" s="7">
-        <v>-1.11</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="D41" s="6">
-        <v>0.72</v>
+        <v>-1.27</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.68</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>1.48</v>
+        <v>-1.1</v>
       </c>
       <c r="D42" s="6">
-        <v>0.76</v>
+        <v>-1.28</v>
       </c>
       <c r="E42" s="7">
-        <v>-0.72</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D43" s="6">
-        <v>-0.67</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.13</v>
+        <v>-2.18</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>-0.6</v>
+        <v>-0.78</v>
       </c>
       <c r="D44" s="6">
-        <v>0.07000000000000001</v>
+        <v>-0.43</v>
       </c>
       <c r="E44" s="8">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="D45" s="6">
-        <v>-4.34</v>
+        <v>-4.16</v>
       </c>
       <c r="E45" s="7">
-        <v>-4</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>-0.49</v>
+        <v>-1.07</v>
       </c>
       <c r="D46" s="6">
-        <v>-4.71</v>
+        <v>-1.32</v>
       </c>
       <c r="E46" s="7">
-        <v>-4.22</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="6">
-        <v>0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="D47" s="6">
-        <v>-0.22</v>
+        <v>-0.8</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.24</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-0.53</v>
+        <v>4.25</v>
       </c>
       <c r="D48" s="6">
-        <v>-1.09</v>
+        <v>3.7</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-0.84</v>
+        <v>-89.54000000000001</v>
       </c>
       <c r="D49" s="6">
-        <v>-1.15</v>
+        <v>-89.59</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.31</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-0.67</v>
+        <v>3.19</v>
       </c>
       <c r="D50" s="6">
-        <v>-1.1</v>
+        <v>2.92</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.43</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-0.51</v>
+        <v>-12.52</v>
       </c>
       <c r="D51" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.59</v>
+        <v>-12.51</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.01</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-0.52</v>
+        <v>51.98</v>
       </c>
       <c r="D52" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.59</v>
+        <v>51.23</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-1.47</v>
+        <v>52.18</v>
       </c>
       <c r="D53" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.6899999999999999</v>
+        <v>51.56</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>0.42</v>
+        <v>7.99</v>
       </c>
       <c r="D54" s="6">
-        <v>-0.31</v>
+        <v>3.72</v>
       </c>
       <c r="E54" s="7">
-        <v>-0.73</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-0.51</v>
+        <v>4.58</v>
       </c>
       <c r="D55" s="6">
-        <v>-1.07</v>
+        <v>3.91</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C56" s="6">
+        <v>-10.71</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-10.95</v>
+      </c>
+      <c r="E56" s="7">
         <v>-0.24</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-0.27</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.03</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>4.28</v>
+        <v>-11.4</v>
       </c>
       <c r="D57" s="6">
-        <v>4.25</v>
+        <v>-11.65</v>
       </c>
       <c r="E57" s="7">
-        <v>-0.03</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-89.58</v>
+        <v>12.56</v>
       </c>
       <c r="D58" s="6">
-        <v>-89.54000000000001</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.04</v>
+        <v>11.83</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>4.25</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D59" s="6">
-        <v>3.19</v>
+        <v>-1.3</v>
       </c>
       <c r="E59" s="7">
-        <v>-1.06</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>-11.18</v>
+        <v>-0.64</v>
       </c>
       <c r="D60" s="6">
-        <v>-12.52</v>
+        <v>-1.27</v>
       </c>
       <c r="E60" s="7">
-        <v>-1.34</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>50.34</v>
+        <v>-0.75</v>
       </c>
       <c r="D61" s="6">
-        <v>51.98</v>
-      </c>
-      <c r="E61" s="8">
-        <v>1.64</v>
+        <v>-1.29</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>50.61</v>
+        <v>23.14</v>
       </c>
       <c r="D62" s="6">
-        <v>52.18</v>
-      </c>
-      <c r="E62" s="8">
-        <v>1.57</v>
+        <v>22.55</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>11.69</v>
+        <v>2.33</v>
       </c>
       <c r="D63" s="6">
-        <v>7.99</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-3.7</v>
+        <v>2.84</v>
+      </c>
+      <c r="E63" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>4.97</v>
+        <v>99.31</v>
       </c>
       <c r="D64" s="6">
-        <v>4.58</v>
+        <v>95.41</v>
       </c>
       <c r="E64" s="7">
-        <v>-0.39</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-7.75</v>
+        <v>-0.75</v>
       </c>
       <c r="D65" s="6">
-        <v>-10.71</v>
+        <v>-1.37</v>
       </c>
       <c r="E65" s="7">
-        <v>-2.96</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-7.79</v>
+        <v>12.94</v>
       </c>
       <c r="D66" s="6">
-        <v>-11.4</v>
+        <v>12.03</v>
       </c>
       <c r="E66" s="7">
-        <v>-3.61</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>13.5</v>
+        <v>7.69</v>
       </c>
       <c r="D67" s="6">
-        <v>12.56</v>
+        <v>6.01</v>
       </c>
       <c r="E67" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>0.38</v>
+        <v>7.99</v>
       </c>
       <c r="D68" s="6">
-        <v>-0.6899999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="E68" s="7">
-        <v>-1.07</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>0.43</v>
+        <v>-10.21</v>
       </c>
       <c r="D69" s="6">
-        <v>-0.64</v>
+        <v>-10.28</v>
       </c>
       <c r="E69" s="7">
-        <v>-1.07</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>0.41</v>
+        <v>-4.61</v>
       </c>
       <c r="D70" s="6">
-        <v>-0.75</v>
+        <v>-4.9</v>
       </c>
       <c r="E70" s="7">
-        <v>-1.16</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>24.13</v>
+        <v>-3.3</v>
       </c>
       <c r="D71" s="6">
-        <v>23.14</v>
+        <v>-3.66</v>
       </c>
       <c r="E71" s="7">
-        <v>-0.99</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>2.97</v>
+        <v>-3.2</v>
       </c>
       <c r="D72" s="6">
-        <v>2.33</v>
+        <v>-3.51</v>
       </c>
       <c r="E72" s="7">
-        <v>-0.64</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>101.97</v>
+        <v>-9.56</v>
       </c>
       <c r="D73" s="6">
-        <v>99.31</v>
+        <v>-10.31</v>
       </c>
       <c r="E73" s="7">
-        <v>-2.66</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>0.36</v>
+        <v>0.87</v>
       </c>
       <c r="D74" s="6">
-        <v>-0.75</v>
+        <v>-0.02</v>
       </c>
       <c r="E74" s="7">
-        <v>-1.11</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>13.44</v>
+        <v>5.31</v>
       </c>
       <c r="D75" s="6">
-        <v>12.94</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-0.5</v>
+        <v>5.75</v>
+      </c>
+      <c r="E75" s="8">
+        <v>0.44</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>8</v>
+        <v>4.68</v>
       </c>
       <c r="D76" s="6">
-        <v>7.69</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-0.31</v>
+        <v>5.18</v>
+      </c>
+      <c r="E76" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>7.89</v>
+        <v>7.51</v>
       </c>
       <c r="D77" s="6">
-        <v>7.99</v>
-      </c>
-      <c r="E77" s="8">
-        <v>0.1</v>
+        <v>6.17</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>-10.52</v>
+        <v>2.94</v>
       </c>
       <c r="D78" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="E78" s="8">
-        <v>0.31</v>
+        <v>2.05</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>-3.79</v>
+        <v>2.96</v>
       </c>
       <c r="D79" s="6">
-        <v>-4.61</v>
+        <v>2.08</v>
       </c>
       <c r="E79" s="7">
-        <v>-0.82</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>-4.22</v>
+        <v>3.22</v>
       </c>
       <c r="D80" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E80" s="8">
-        <v>0.92</v>
+        <v>2.2</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>-4.11</v>
+        <v>2.93</v>
       </c>
       <c r="D81" s="6">
-        <v>-3.2</v>
-      </c>
-      <c r="E81" s="8">
-        <v>0.91</v>
+        <v>2.06</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-11.46</v>
+        <v>8.1</v>
       </c>
       <c r="D82" s="6">
-        <v>-9.56</v>
-      </c>
-      <c r="E82" s="8">
-        <v>1.9</v>
+        <v>7.26</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>2.38</v>
+        <v>4.74</v>
       </c>
       <c r="D83" s="6">
-        <v>0.87</v>
+        <v>3.92</v>
       </c>
       <c r="E83" s="7">
-        <v>-1.51</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>7.45</v>
+        <v>-11.85</v>
       </c>
       <c r="D84" s="6">
-        <v>5.31</v>
+        <v>-14.2</v>
       </c>
       <c r="E84" s="7">
-        <v>-2.14</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>7.27</v>
+        <v>3.1</v>
       </c>
       <c r="D85" s="6">
-        <v>4.68</v>
+        <v>2.1</v>
       </c>
       <c r="E85" s="7">
-        <v>-2.59</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="6">
-        <v>8.460000000000001</v>
+        <v>7.38</v>
       </c>
       <c r="D86" s="6">
-        <v>7.51</v>
+        <v>6.61</v>
       </c>
       <c r="E86" s="7">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>4.01</v>
+        <v>-6.45</v>
       </c>
       <c r="D87" s="6">
-        <v>2.94</v>
+        <v>-6.7</v>
       </c>
       <c r="E87" s="7">
-        <v>-1.07</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>3.82</v>
+        <v>-90.64</v>
       </c>
       <c r="D88" s="6">
-        <v>2.96</v>
+        <v>-90.67</v>
       </c>
       <c r="E88" s="7">
-        <v>-0.86</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>3.99</v>
+        <v>-13.62</v>
       </c>
       <c r="D89" s="6">
-        <v>3.22</v>
+        <v>-14.4</v>
       </c>
       <c r="E89" s="7">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>4.08</v>
+        <v>-15.82</v>
       </c>
       <c r="D90" s="6">
-        <v>2.93</v>
+        <v>-16.31</v>
       </c>
       <c r="E90" s="7">
-        <v>-1.15</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91" s="6">
-        <v>9.66</v>
+        <v>-13.72</v>
       </c>
       <c r="D91" s="6">
-        <v>8.1</v>
+        <v>-14.2</v>
       </c>
       <c r="E91" s="7">
-        <v>-1.56</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>5.91</v>
+        <v>-13.65</v>
       </c>
       <c r="D92" s="6">
-        <v>4.74</v>
+        <v>-14.08</v>
       </c>
       <c r="E92" s="7">
-        <v>-1.17</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-12.59</v>
+        <v>-15.03</v>
       </c>
       <c r="D93" s="6">
-        <v>-11.85</v>
-      </c>
-      <c r="E93" s="8">
-        <v>0.74</v>
+        <v>-15.39</v>
+      </c>
+      <c r="E93" s="7">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>3.96</v>
+        <v>-3.49</v>
       </c>
       <c r="D94" s="6">
-        <v>3.1</v>
+        <v>-4.45</v>
       </c>
       <c r="E94" s="7">
-        <v>-0.86</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>8.26</v>
+        <v>-21.96</v>
       </c>
       <c r="D95" s="6">
-        <v>7.38</v>
+        <v>-22.01</v>
       </c>
       <c r="E95" s="7">
-        <v>-0.88</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-6.21</v>
+        <v>-22.43</v>
       </c>
       <c r="D96" s="6">
-        <v>-6.45</v>
-      </c>
-      <c r="E96" s="7">
-        <v>-0.24</v>
+        <v>-22.2</v>
+      </c>
+      <c r="E96" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-90.62</v>
+        <v>-0.38</v>
       </c>
       <c r="D97" s="6">
-        <v>-90.64</v>
+        <v>-1.13</v>
       </c>
       <c r="E97" s="7">
-        <v>-0.02</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-13.75</v>
+        <v>-7.21</v>
       </c>
       <c r="D98" s="6">
-        <v>-13.62</v>
-      </c>
-      <c r="E98" s="8">
-        <v>0.13</v>
+        <v>-7.71</v>
+      </c>
+      <c r="E98" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-14.16</v>
+        <v>-7.26</v>
       </c>
       <c r="D99" s="6">
-        <v>-15.82</v>
+        <v>-7.65</v>
       </c>
       <c r="E99" s="7">
-        <v>-1.66</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-14.6</v>
+        <v>-7.27</v>
       </c>
       <c r="D100" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="E100" s="8">
-        <v>0.88</v>
+        <v>-7.78</v>
+      </c>
+      <c r="E100" s="7">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-14.57</v>
+        <v>-7.22</v>
       </c>
       <c r="D101" s="6">
-        <v>-13.65</v>
-      </c>
-      <c r="E101" s="8">
-        <v>0.92</v>
+        <v>-7.67</v>
+      </c>
+      <c r="E101" s="7">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-14.78</v>
+        <v>-12.15</v>
       </c>
       <c r="D102" s="6">
-        <v>-15.03</v>
+        <v>-12.51</v>
       </c>
       <c r="E102" s="7">
-        <v>-0.25</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>-3.16</v>
+        <v>-6.25</v>
       </c>
       <c r="D103" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="E103" s="7">
-        <v>-0.33</v>
+        <v>-5.97</v>
+      </c>
+      <c r="E103" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>-19.5</v>
+        <v>-36.59</v>
       </c>
       <c r="D104" s="6">
-        <v>-21.96</v>
+        <v>-38.09</v>
       </c>
       <c r="E104" s="7">
-        <v>-2.46</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>-19.59</v>
+        <v>-7.21</v>
       </c>
       <c r="D105" s="6">
-        <v>-22.43</v>
+        <v>-7.72</v>
       </c>
       <c r="E105" s="7">
-        <v>-2.84</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="6">
-        <v>-0.15</v>
+        <v>-0.57</v>
       </c>
       <c r="D106" s="6">
-        <v>-0.38</v>
+        <v>-1.25</v>
       </c>
       <c r="E106" s="7">
-        <v>-0.23</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C107" s="6">
-        <v>-6.45</v>
+        <v>594.86</v>
       </c>
       <c r="D107" s="6">
-        <v>-7.21</v>
+        <v>593.26</v>
       </c>
       <c r="E107" s="7">
-        <v>-0.76</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C108" s="6">
-        <v>-6.61</v>
+        <v>59.63</v>
       </c>
       <c r="D108" s="6">
-        <v>-7.26</v>
+        <v>59.44</v>
       </c>
       <c r="E108" s="7">
-        <v>-0.65</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C109" s="6">
-        <v>-6.54</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="D109" s="6">
-        <v>-7.27</v>
+        <v>93.14</v>
       </c>
       <c r="E109" s="7">
-        <v>-0.73</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C110" s="6">
-        <v>-6.47</v>
+        <v>51.35</v>
       </c>
       <c r="D110" s="6">
-        <v>-7.22</v>
+        <v>51.05</v>
       </c>
       <c r="E110" s="7">
-        <v>-0.75</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C111" s="6">
-        <v>-11.24</v>
+        <v>126.43</v>
       </c>
       <c r="D111" s="6">
-        <v>-12.15</v>
+        <v>125.73</v>
       </c>
       <c r="E111" s="7">
-        <v>-0.91</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>-5.66</v>
+        <v>130.71</v>
       </c>
       <c r="D112" s="6">
-        <v>-6.25</v>
+        <v>130.07</v>
       </c>
       <c r="E112" s="7">
-        <v>-0.59</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>-36.73</v>
+        <v>481.22</v>
       </c>
       <c r="D113" s="6">
-        <v>-36.59</v>
-      </c>
-      <c r="E113" s="8">
-        <v>0.14</v>
+        <v>479.18</v>
+      </c>
+      <c r="E113" s="7">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>-6.46</v>
+        <v>973.6799999999999</v>
       </c>
       <c r="D114" s="6">
-        <v>-7.21</v>
+        <v>963.99</v>
       </c>
       <c r="E114" s="7">
-        <v>-0.75</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>-0.45</v>
+        <v>33.69</v>
       </c>
       <c r="D115" s="6">
-        <v>-0.57</v>
+        <v>33.67</v>
       </c>
       <c r="E115" s="7">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>596.37</v>
+        <v>33.58</v>
       </c>
       <c r="D116" s="6">
-        <v>594.86</v>
-      </c>
-      <c r="E116" s="7">
-        <v>-1.51</v>
+        <v>33.68</v>
+      </c>
+      <c r="E116" s="8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>59.77</v>
+        <v>805.9</v>
       </c>
       <c r="D117" s="6">
-        <v>59.63</v>
+        <v>799.85</v>
       </c>
       <c r="E117" s="7">
-        <v>-0.14</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>93.84999999999999</v>
+        <v>276.1</v>
       </c>
       <c r="D118" s="6">
-        <v>93.98999999999999</v>
-      </c>
-      <c r="E118" s="8">
-        <v>0.14</v>
+        <v>274.62</v>
+      </c>
+      <c r="E118" s="7">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>52.36</v>
+        <v>268.59</v>
       </c>
       <c r="D119" s="6">
-        <v>51.35</v>
+        <v>267.46</v>
       </c>
       <c r="E119" s="7">
-        <v>-1.01</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>125.13</v>
+        <v>263.65</v>
       </c>
       <c r="D120" s="6">
-        <v>126.43</v>
-      </c>
-      <c r="E120" s="8">
-        <v>1.3</v>
+        <v>262.19</v>
+      </c>
+      <c r="E120" s="7">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>129.33</v>
+        <v>274.6</v>
       </c>
       <c r="D121" s="6">
-        <v>130.71</v>
-      </c>
-      <c r="E121" s="8">
-        <v>1.38</v>
+        <v>273.27</v>
+      </c>
+      <c r="E121" s="7">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>482.66</v>
+        <v>96.52</v>
       </c>
       <c r="D122" s="6">
-        <v>481.22</v>
+        <v>96.13</v>
       </c>
       <c r="E122" s="7">
-        <v>-1.44</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>976.9299999999999</v>
+        <v>278.01</v>
       </c>
       <c r="D123" s="6">
-        <v>973.6799999999999</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-3.25</v>
+        <v>278.82</v>
+      </c>
+      <c r="E123" s="8">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>34.75</v>
+        <v>227.17</v>
       </c>
       <c r="D124" s="6">
-        <v>33.69</v>
+        <v>221.77</v>
       </c>
       <c r="E124" s="7">
-        <v>-1.06</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>34.81</v>
+        <v>260.94</v>
       </c>
       <c r="D125" s="6">
-        <v>33.58</v>
+        <v>259.51</v>
       </c>
       <c r="E125" s="7">
-        <v>-1.23</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="6">
-        <v>807.8099999999999</v>
+        <v>798.66</v>
       </c>
       <c r="D126" s="6">
-        <v>805.9</v>
+        <v>793.1900000000001</v>
       </c>
       <c r="E126" s="7">
-        <v>-1.91</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C127" s="6">
-        <v>278.35</v>
+        <v>32</v>
       </c>
       <c r="D127" s="6">
-        <v>276.1</v>
+        <v>22</v>
       </c>
       <c r="E127" s="7">
-        <v>-2.25</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C128" s="6">
-        <v>270.48</v>
+        <v>27</v>
       </c>
       <c r="D128" s="6">
-        <v>268.59</v>
-      </c>
-      <c r="E128" s="7">
-        <v>-1.89</v>
+        <v>32</v>
+      </c>
+      <c r="E128" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C129" s="6">
-        <v>265.71</v>
+        <v>22</v>
       </c>
       <c r="D129" s="6">
-        <v>263.65</v>
-      </c>
-      <c r="E129" s="7">
-        <v>-2.06</v>
+        <v>27</v>
+      </c>
+      <c r="E129" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C130" s="6">
-        <v>276.84</v>
+        <v>47</v>
       </c>
       <c r="D130" s="6">
-        <v>274.6</v>
-      </c>
-      <c r="E130" s="7">
-        <v>-2.24</v>
+        <v>53</v>
+      </c>
+      <c r="E130" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C131" s="6">
-        <v>97.52</v>
+        <v>37</v>
       </c>
       <c r="D131" s="6">
-        <v>96.52</v>
-      </c>
-      <c r="E131" s="7">
-        <v>-1</v>
+        <v>47</v>
+      </c>
+      <c r="E131" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="6">
         <v>53</v>
       </c>
-      <c r="B132" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C132" s="6">
-        <v>279.76</v>
-      </c>
       <c r="D132" s="6">
-        <v>278.01</v>
+        <v>37</v>
       </c>
       <c r="E132" s="7">
-        <v>-1.75</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C133" s="6">
-        <v>226.67</v>
+        <v>49.78</v>
       </c>
       <c r="D133" s="6">
-        <v>227.17</v>
-      </c>
-      <c r="E133" s="8">
-        <v>0.5</v>
+        <v>47.54</v>
+      </c>
+      <c r="E133" s="7">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C134" s="6">
-        <v>263.05</v>
+        <v>48.17</v>
       </c>
       <c r="D134" s="6">
-        <v>260.94</v>
+        <v>45.89</v>
       </c>
       <c r="E134" s="7">
-        <v>-2.11</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C135" s="6">
-        <v>799.65</v>
+        <v>37.39</v>
       </c>
       <c r="D135" s="6">
-        <v>798.66</v>
+        <v>31.26</v>
       </c>
       <c r="E135" s="7">
-        <v>-0.99</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C136" s="6">
-        <v>22</v>
+        <v>34.79</v>
       </c>
       <c r="D136" s="6">
-        <v>32</v>
-      </c>
-      <c r="E136" s="8">
-        <v>10</v>
+        <v>32.42</v>
+      </c>
+      <c r="E136" s="7">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C137" s="6">
-        <v>63</v>
+        <v>69.69</v>
       </c>
       <c r="D137" s="6">
-        <v>58</v>
+        <v>65.95</v>
       </c>
       <c r="E137" s="7">
-        <v>-5</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C138" s="6">
-        <v>32</v>
+        <v>69.97</v>
       </c>
       <c r="D138" s="6">
-        <v>27</v>
+        <v>66.56</v>
       </c>
       <c r="E138" s="7">
-        <v>-5</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>27</v>
+        <v>43.82</v>
       </c>
       <c r="D139" s="6">
-        <v>22</v>
+        <v>41.5</v>
       </c>
       <c r="E139" s="7">
-        <v>-5</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>78</v>
+        <v>52.2</v>
       </c>
       <c r="D140" s="6">
-        <v>73</v>
+        <v>44.33</v>
       </c>
       <c r="E140" s="7">
-        <v>-5</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>47</v>
+        <v>50.28</v>
       </c>
       <c r="D141" s="6">
-        <v>42</v>
+        <v>50.07</v>
       </c>
       <c r="E141" s="7">
-        <v>-5</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>40</v>
+        <v>49.01</v>
       </c>
       <c r="D142" s="6">
-        <v>47</v>
+        <v>49.99</v>
       </c>
       <c r="E142" s="8">
-        <v>7</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>53</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="D143" s="6">
-        <v>37</v>
+        <v>55.63</v>
       </c>
       <c r="E143" s="7">
-        <v>-16</v>
+        <v>-9.44</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>58</v>
+        <v>47.76</v>
       </c>
       <c r="D144" s="6">
-        <v>63</v>
-      </c>
-      <c r="E144" s="8">
-        <v>5</v>
+        <v>43.15</v>
+      </c>
+      <c r="E144" s="7">
+        <v>-4.61</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>40</v>
+        <v>47.52</v>
       </c>
       <c r="D145" s="6">
-        <v>53</v>
-      </c>
-      <c r="E145" s="8">
-        <v>13</v>
+        <v>43.66</v>
+      </c>
+      <c r="E145" s="7">
+        <v>-3.86</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>73</v>
+        <v>47.67</v>
       </c>
       <c r="D146" s="6">
-        <v>78</v>
-      </c>
-      <c r="E146" s="8">
-        <v>5</v>
+        <v>43.24</v>
+      </c>
+      <c r="E146" s="7">
+        <v>-4.43</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>51.92</v>
+        <v>47.51</v>
       </c>
       <c r="D147" s="6">
-        <v>49.78</v>
+        <v>43.4</v>
       </c>
       <c r="E147" s="7">
-        <v>-2.14</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>49.87</v>
+        <v>54.32</v>
       </c>
       <c r="D148" s="6">
-        <v>48.17</v>
+        <v>52.36</v>
       </c>
       <c r="E148" s="7">
-        <v>-1.7</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>35.45</v>
+        <v>40.59</v>
       </c>
       <c r="D149" s="6">
-        <v>37.39</v>
+        <v>43.11</v>
       </c>
       <c r="E149" s="8">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>44.7</v>
+        <v>58.99</v>
       </c>
       <c r="D150" s="6">
-        <v>34.79</v>
+        <v>49.86</v>
       </c>
       <c r="E150" s="7">
-        <v>-9.91</v>
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>66.41</v>
+        <v>47.76</v>
       </c>
       <c r="D151" s="6">
-        <v>69.69</v>
-      </c>
-      <c r="E151" s="8">
-        <v>3.28</v>
+        <v>43.06</v>
+      </c>
+      <c r="E151" s="7">
+        <v>-4.7</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>66.79000000000001</v>
+        <v>61.99</v>
       </c>
       <c r="D152" s="6">
-        <v>69.97</v>
-      </c>
-      <c r="E152" s="8">
-        <v>3.18</v>
+        <v>55.28</v>
+      </c>
+      <c r="E152" s="7">
+        <v>-6.71</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C153" s="6">
-        <v>45.49</v>
+        <v>-18.36</v>
       </c>
       <c r="D153" s="6">
-        <v>43.82</v>
+        <v>-41.91</v>
       </c>
       <c r="E153" s="7">
-        <v>-1.67</v>
+        <v>-23.55</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C154" s="6">
-        <v>55.26</v>
+        <v>40.81</v>
       </c>
       <c r="D154" s="6">
-        <v>52.2</v>
+        <v>-13.49</v>
       </c>
       <c r="E154" s="7">
-        <v>-3.06</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C155" s="6">
-        <v>62.87</v>
+        <v>10.05</v>
       </c>
       <c r="D155" s="6">
-        <v>50.28</v>
-      </c>
-      <c r="E155" s="7">
-        <v>-12.59</v>
+        <v>22.52</v>
+      </c>
+      <c r="E155" s="8">
+        <v>12.47</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C156" s="6">
-        <v>63.22</v>
+        <v>208.84</v>
       </c>
       <c r="D156" s="6">
-        <v>49.01</v>
+        <v>-29.41</v>
       </c>
       <c r="E156" s="7">
-        <v>-14.21</v>
+        <v>-238.25</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C157" s="6">
-        <v>68.47</v>
+        <v>-33.97</v>
       </c>
       <c r="D157" s="6">
-        <v>65.06999999999999</v>
-      </c>
-      <c r="E157" s="7">
-        <v>-3.4</v>
+        <v>-22.13</v>
+      </c>
+      <c r="E157" s="8">
+        <v>11.84</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C158" s="6">
-        <v>56.25</v>
+        <v>-22.11</v>
       </c>
       <c r="D158" s="6">
-        <v>47.76</v>
-      </c>
-      <c r="E158" s="7">
-        <v>-8.49</v>
+        <v>-12.4</v>
+      </c>
+      <c r="E158" s="8">
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>55.18</v>
+        <v>31.71</v>
       </c>
       <c r="D159" s="6">
-        <v>47.52</v>
+        <v>-28.34</v>
       </c>
       <c r="E159" s="7">
-        <v>-7.66</v>
+        <v>-60.05</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>55.06</v>
+        <v>-49.16</v>
       </c>
       <c r="D160" s="6">
-        <v>47.67</v>
-      </c>
-      <c r="E160" s="7">
-        <v>-7.39</v>
+        <v>32.4</v>
+      </c>
+      <c r="E160" s="8">
+        <v>81.56</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>55.76</v>
+        <v>-60.76</v>
       </c>
       <c r="D161" s="6">
-        <v>47.51</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="E161" s="7">
-        <v>-8.25</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>59.65</v>
+        <v>-40.98</v>
       </c>
       <c r="D162" s="6">
-        <v>54.32</v>
+        <v>-57.95</v>
       </c>
       <c r="E162" s="7">
-        <v>-5.33</v>
+        <v>-16.97</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>44.55</v>
+        <v>-22.06</v>
       </c>
       <c r="D163" s="6">
-        <v>40.59</v>
-      </c>
-      <c r="E163" s="7">
-        <v>-3.96</v>
+        <v>365.76</v>
+      </c>
+      <c r="E163" s="8">
+        <v>387.82</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>58.33</v>
+        <v>-13.01</v>
       </c>
       <c r="D164" s="6">
-        <v>58.99</v>
+        <v>14.15</v>
       </c>
       <c r="E164" s="8">
-        <v>0.66</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>56.16</v>
+        <v>-12.95</v>
       </c>
       <c r="D165" s="6">
-        <v>47.76</v>
+        <v>-33.38</v>
       </c>
       <c r="E165" s="7">
-        <v>-8.4</v>
+        <v>-20.43</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>63.28</v>
+        <v>61.19</v>
       </c>
       <c r="D166" s="6">
-        <v>61.99</v>
-      </c>
-      <c r="E166" s="7">
-        <v>-1.29</v>
+        <v>127.94</v>
+      </c>
+      <c r="E166" s="8">
+        <v>66.75</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-54.87</v>
+        <v>-51.29</v>
       </c>
       <c r="D167" s="6">
-        <v>-18.36</v>
+        <v>-25.36</v>
       </c>
       <c r="E167" s="8">
-        <v>36.51</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-86.98</v>
+        <v>-49.64</v>
       </c>
       <c r="D168" s="6">
-        <v>40.81</v>
-      </c>
-      <c r="E168" s="8">
-        <v>127.79</v>
+        <v>-68.34999999999999</v>
+      </c>
+      <c r="E168" s="7">
+        <v>-18.71</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>-34.59</v>
+        <v>-13.55</v>
       </c>
       <c r="D169" s="6">
-        <v>10.05</v>
-      </c>
-      <c r="E169" s="8">
-        <v>44.64</v>
+        <v>-82.36</v>
+      </c>
+      <c r="E169" s="7">
+        <v>-68.81</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="6">
-        <v>75.04000000000001</v>
+        <v>-34.68</v>
       </c>
       <c r="D170" s="6">
-        <v>208.84</v>
+        <v>-3.37</v>
       </c>
       <c r="E170" s="8">
-        <v>133.8</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="6">
-        <v>3.61</v>
+        <v>-41.13</v>
       </c>
       <c r="D171" s="6">
-        <v>-33.97</v>
-      </c>
-      <c r="E171" s="7">
-        <v>-37.58</v>
+        <v>-0.93</v>
+      </c>
+      <c r="E171" s="8">
+        <v>40.2</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="5" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="6">
-        <v>-30.89</v>
+        <v>58.26</v>
       </c>
       <c r="D172" s="6">
-        <v>-22.11</v>
-      </c>
-      <c r="E172" s="8">
-        <v>8.779999999999999</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C173" s="6">
-        <v>-45.88</v>
-      </c>
-      <c r="D173" s="6">
-        <v>31.71</v>
-      </c>
-      <c r="E173" s="8">
-        <v>77.59</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C174" s="6">
-        <v>5.08</v>
-      </c>
-      <c r="D174" s="6">
-        <v>-49.16</v>
-      </c>
-      <c r="E174" s="7">
-        <v>-54.24</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C175" s="6">
-        <v>-57.72</v>
-      </c>
-      <c r="D175" s="6">
-        <v>-60.76</v>
-      </c>
-      <c r="E175" s="7">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C176" s="6">
-        <v>-69.5</v>
-      </c>
-      <c r="D176" s="6">
-        <v>-40.98</v>
-      </c>
-      <c r="E176" s="8">
-        <v>28.52</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C177" s="6">
-        <v>82.19</v>
-      </c>
-      <c r="D177" s="6">
-        <v>-22.06</v>
-      </c>
-      <c r="E177" s="7">
-        <v>-104.25</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C178" s="6">
-        <v>-42.33</v>
-      </c>
-      <c r="D178" s="6">
-        <v>-13.01</v>
-      </c>
-      <c r="E178" s="8">
-        <v>29.32</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C179" s="6">
-        <v>-57.02</v>
-      </c>
-      <c r="D179" s="6">
-        <v>-12.95</v>
-      </c>
-      <c r="E179" s="8">
-        <v>44.07</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C180" s="6">
-        <v>-78.41</v>
-      </c>
-      <c r="D180" s="6">
-        <v>61.19</v>
-      </c>
-      <c r="E180" s="8">
-        <v>139.6</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C181" s="6">
-        <v>-59.55</v>
-      </c>
-      <c r="D181" s="6">
-        <v>-51.29</v>
-      </c>
-      <c r="E181" s="8">
-        <v>8.26</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C182" s="6">
-        <v>-35</v>
-      </c>
-      <c r="D182" s="6">
-        <v>-49.64</v>
-      </c>
-      <c r="E182" s="7">
-        <v>-14.64</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C183" s="6">
-        <v>-88.69</v>
-      </c>
-      <c r="D183" s="6">
-        <v>-13.55</v>
-      </c>
-      <c r="E183" s="8">
-        <v>75.14</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C184" s="6">
-        <v>-21.85</v>
-      </c>
-      <c r="D184" s="6">
-        <v>-34.68</v>
-      </c>
-      <c r="E184" s="7">
-        <v>-12.83</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C185" s="6">
-        <v>-43.91</v>
-      </c>
-      <c r="D185" s="6">
-        <v>-41.13</v>
-      </c>
-      <c r="E185" s="8">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C186" s="6">
-        <v>22.54</v>
-      </c>
-      <c r="D186" s="6">
-        <v>58.26</v>
-      </c>
-      <c r="E186" s="8">
-        <v>35.72</v>
+        <v>-34.07</v>
+      </c>
+      <c r="E172" s="7">
+        <v>-92.33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6527,28 +6223,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6556,22 +6252,22 @@
         <v>57</v>
       </c>
       <c r="B2" s="11">
-        <v>47.04000000000001</v>
+        <v>43.04000000000001</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>51.2</v>
+        <v>47.4</v>
       </c>
       <c r="E2" s="11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="G2" s="11">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="11">
         <v>52.6</v>
@@ -6697,10 +6393,10 @@
         <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>37</v>
@@ -6711,34 +6407,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.5381</v>
+        <v>0.5197999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3326</v>
+        <v>0.3302</v>
       </c>
       <c r="C2" s="14">
-        <v>0.306</v>
+        <v>0.3139</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2974</v>
+        <v>0.3012</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2525</v>
+        <v>0.2516</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1543</v>
+        <v>0.1571</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1403</v>
+        <v>0.1414</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1402</v>
+        <v>0.1408</v>
       </c>
       <c r="I2" s="14">
-        <v>0.1066</v>
+        <v>0.1095</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0911</v>
+        <v>0.0917</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6775,34 +6471,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.09080000000000001</v>
+        <v>0.0915</v>
       </c>
       <c r="B4" s="14">
-        <v>0.09080000000000001</v>
+        <v>0.0915</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0906</v>
+        <v>0.09119999999999999</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0859</v>
+        <v>0.0891</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0775</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0634</v>
+        <v>0.0588</v>
       </c>
       <c r="G4" s="14">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0028</v>
+        <v>-0.0015</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.09279999999999999</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3018</v>
+        <v>-0.3003</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="105">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,76 +226,76 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>44.8 → 53.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>44.8</t>
+    <t>47.6 → 51.4</t>
+  </si>
+  <si>
+    <t>47.6</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>48.4 → 53.0</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>47.8 → 52.2</t>
+  </si>
+  <si>
+    <t>47.8</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>48.4 → 51.1</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>47.1 → 51.5</t>
+  </si>
+  <si>
+    <t>47.1</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>48.1 → 51.1</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>53.2 → 49.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>53.2</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>51.6 → 49.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>49.3</t>
-  </si>
-  <si>
-    <t>50.4 → 47.1</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>47.1</t>
-  </si>
-  <si>
-    <t>50.0 → 47.6</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>47.6</t>
-  </si>
-  <si>
-    <t>51.0 → 48.4</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>50.2 → 48.4</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>53.1 → 47.1</t>
-  </si>
-  <si>
-    <t>53.1</t>
+    <t>49.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -508,8 +508,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1021,10 +1021,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>594.7</v>
+        <v>595.0700000000001</v>
       </c>
       <c r="D2">
-        <v>-0.51</v>
+        <v>0.06</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1033,43 +1033,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-6.47</v>
+        <v>-6.41</v>
       </c>
       <c r="H2">
-        <v>14.17</v>
+        <v>14.24</v>
       </c>
       <c r="I2">
-        <v>-0.28</v>
+        <v>0.04</v>
       </c>
       <c r="J2">
-        <v>1.18</v>
+        <v>0.61</v>
       </c>
       <c r="K2">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="L2">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="M2">
-        <v>10.59</v>
+        <v>10.66</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>595.33</v>
+        <v>595.37</v>
       </c>
       <c r="Q2">
-        <v>595.45</v>
+        <v>595.83</v>
       </c>
       <c r="R2">
-        <v>596.4299999999999</v>
+        <v>596.52</v>
       </c>
       <c r="S2">
-        <v>593.03</v>
+        <v>593.02</v>
       </c>
       <c r="T2">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1084,34 +1084,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.34</v>
+        <v>49.9</v>
       </c>
       <c r="Z2">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="AA2">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AB2">
-        <v>-0.31</v>
+        <v>-0.34</v>
       </c>
       <c r="AC2">
-        <v>41.76</v>
+        <v>35.89</v>
       </c>
       <c r="AD2">
-        <v>31.68</v>
+        <v>37.78</v>
       </c>
       <c r="AE2">
-        <v>7.09</v>
+        <v>6.94</v>
       </c>
       <c r="AF2">
-        <v>-5.49</v>
+        <v>0.39</v>
       </c>
       <c r="AG2">
-        <v>601.5599999999999</v>
+        <v>600.6900000000001</v>
       </c>
       <c r="AH2">
-        <v>589.34</v>
+        <v>590.96</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1120,7 +1120,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>35.4</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1131,10 +1131,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>59.53</v>
+        <v>59.61</v>
       </c>
       <c r="D3">
-        <v>-0.55</v>
+        <v>0.13</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1143,43 +1143,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.66</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="H3">
-        <v>14.22</v>
+        <v>14.37</v>
       </c>
       <c r="I3">
-        <v>-0.4</v>
+        <v>-0.03</v>
       </c>
       <c r="J3">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="K3">
-        <v>4.82</v>
+        <v>4.97</v>
       </c>
       <c r="L3">
-        <v>-89.67</v>
+        <v>-89.66</v>
       </c>
       <c r="M3">
-        <v>-30.23</v>
+        <v>-30.19</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.65</v>
+        <v>59.64</v>
       </c>
       <c r="Q3">
-        <v>59.73</v>
+        <v>59.76</v>
       </c>
       <c r="R3">
-        <v>59.8</v>
+        <v>59.81</v>
       </c>
       <c r="S3">
-        <v>275.68</v>
+        <v>272.98</v>
       </c>
       <c r="T3">
-        <v>-78.41</v>
+        <v>-78.16</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1194,34 +1194,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>47.1</v>
+        <v>48.24</v>
       </c>
       <c r="Z3">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AA3">
         <v>0.02</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>34.91</v>
+        <v>28.19</v>
       </c>
       <c r="AD3">
-        <v>27.9</v>
+        <v>31.42</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>2550.46</v>
+        <v>1694.46</v>
       </c>
       <c r="AG3">
-        <v>60.37</v>
+        <v>60.3</v>
       </c>
       <c r="AH3">
-        <v>59.08</v>
+        <v>59.22</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1230,7 +1230,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>11.9</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1241,10 +1241,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>94.06999999999999</v>
+        <v>93.78</v>
       </c>
       <c r="D4">
-        <v>-0.21</v>
+        <v>-0.31</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1253,43 +1253,43 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-13.55</v>
+        <v>-13.81</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>6.77</v>
       </c>
       <c r="I4">
-        <v>0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="J4">
-        <v>-2.24</v>
+        <v>-2.37</v>
       </c>
       <c r="K4">
-        <v>-9.539999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="L4">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
       <c r="M4">
-        <v>30.19</v>
+        <v>29.87</v>
       </c>
       <c r="N4">
         <v>16</v>
       </c>
       <c r="P4">
-        <v>93.8</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="Q4">
-        <v>94.15000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="R4">
-        <v>95.88</v>
+        <v>95.8</v>
       </c>
       <c r="S4">
         <v>97.94</v>
       </c>
       <c r="T4">
-        <v>-3.95</v>
+        <v>-4.25</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1304,34 +1304,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.18</v>
+        <v>40.81</v>
       </c>
       <c r="Z4">
-        <v>-0.65</v>
+        <v>-0.63</v>
       </c>
       <c r="AA4">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="AB4">
         <v>0.12</v>
       </c>
       <c r="AC4">
-        <v>84.3</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="AD4">
-        <v>61.92</v>
+        <v>75.12</v>
       </c>
       <c r="AE4">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AF4">
-        <v>-31.2</v>
+        <v>-46.16</v>
       </c>
       <c r="AG4">
-        <v>95.06</v>
+        <v>95.05</v>
       </c>
       <c r="AH4">
-        <v>93.25</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="AI4">
         <v>98.52</v>
@@ -1340,7 +1340,7 @@
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>15.67</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1351,10 +1351,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>51</v>
+        <v>51.17</v>
       </c>
       <c r="D5">
-        <v>-0.39</v>
+        <v>0.33</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1363,43 +1363,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-16.39</v>
+        <v>-16.11</v>
       </c>
       <c r="H5">
-        <v>4.79</v>
+        <v>5.14</v>
       </c>
       <c r="I5">
-        <v>-1.89</v>
+        <v>-0.35</v>
       </c>
       <c r="J5">
-        <v>-3.21</v>
+        <v>-3.78</v>
       </c>
       <c r="K5">
-        <v>-4.8</v>
+        <v>-4.48</v>
       </c>
       <c r="L5">
-        <v>-15.49</v>
+        <v>-14.75</v>
       </c>
       <c r="M5">
-        <v>5.91</v>
+        <v>5.81</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>51.23</v>
+        <v>51.2</v>
       </c>
       <c r="Q5">
-        <v>52.38</v>
+        <v>52.32</v>
       </c>
       <c r="R5">
-        <v>52.65</v>
+        <v>52.61</v>
       </c>
       <c r="S5">
-        <v>54.46</v>
+        <v>54.41</v>
       </c>
       <c r="T5">
-        <v>-6.35</v>
+        <v>-5.96</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1414,43 +1414,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35.17</v>
+        <v>37.7</v>
       </c>
       <c r="Z5">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="AA5">
-        <v>-0.25</v>
+        <v>-0.29</v>
       </c>
       <c r="AB5">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="AC5">
-        <v>22.2</v>
+        <v>19.94</v>
       </c>
       <c r="AD5">
-        <v>17.09</v>
+        <v>19.99</v>
       </c>
       <c r="AE5">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>-12.79</v>
+        <v>-61.97</v>
       </c>
       <c r="AG5">
-        <v>53.95</v>
+        <v>53.98</v>
       </c>
       <c r="AH5">
-        <v>50.81</v>
+        <v>50.66</v>
       </c>
       <c r="AI5">
-        <v>54.06</v>
+        <v>53.66</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>16.69</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1461,55 +1461,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>133.02</v>
+        <v>132.78</v>
       </c>
       <c r="D6">
-        <v>1.29</v>
+        <v>-0.18</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>82.55</v>
+        <v>82.62</v>
       </c>
       <c r="G6">
-        <v>-9.220000000000001</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="H6">
-        <v>61.14</v>
+        <v>60.71</v>
       </c>
       <c r="I6">
-        <v>6.31</v>
+        <v>5.02</v>
       </c>
       <c r="J6">
-        <v>12.81</v>
+        <v>11.94</v>
       </c>
       <c r="K6">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="L6">
-        <v>62.06</v>
+        <v>60.85</v>
       </c>
       <c r="M6">
-        <v>26.43</v>
+        <v>26.47</v>
       </c>
       <c r="N6">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P6">
-        <v>129.08</v>
+        <v>130.35</v>
       </c>
       <c r="Q6">
-        <v>123.28</v>
+        <v>124.07</v>
       </c>
       <c r="R6">
-        <v>120.22</v>
+        <v>120.39</v>
       </c>
       <c r="S6">
-        <v>120.46</v>
+        <v>120.63</v>
       </c>
       <c r="T6">
-        <v>10.42</v>
+        <v>10.07</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1524,34 +1524,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>79.23999999999999</v>
+        <v>78.06</v>
       </c>
       <c r="Z6">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA6">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="AB6">
         <v>0.98</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>97.37</v>
       </c>
       <c r="AD6">
-        <v>93.06</v>
+        <v>96.31</v>
       </c>
       <c r="AE6">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AF6">
-        <v>102.08</v>
+        <v>63.78</v>
       </c>
       <c r="AG6">
-        <v>133.34</v>
+        <v>134.5</v>
       </c>
       <c r="AH6">
-        <v>113.21</v>
+        <v>113.64</v>
       </c>
       <c r="AI6">
         <v>127.24</v>
@@ -1560,7 +1560,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>44.79</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1571,10 +1571,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>137.53</v>
+        <v>137.09</v>
       </c>
       <c r="D7">
-        <v>1.41</v>
+        <v>-0.32</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1583,43 +1583,43 @@
         <v>85.23999999999999</v>
       </c>
       <c r="G7">
-        <v>-9.15</v>
+        <v>-9.44</v>
       </c>
       <c r="H7">
-        <v>61.34</v>
+        <v>60.83</v>
       </c>
       <c r="I7">
-        <v>5.29</v>
+        <v>4.88</v>
       </c>
       <c r="J7">
-        <v>12.92</v>
+        <v>11.85</v>
       </c>
       <c r="K7">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="L7">
-        <v>62.3</v>
+        <v>60.83</v>
       </c>
       <c r="M7">
-        <v>35.19</v>
+        <v>35.02</v>
       </c>
       <c r="N7">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P7">
-        <v>133.4</v>
+        <v>134.68</v>
       </c>
       <c r="Q7">
-        <v>127.46</v>
+        <v>128.27</v>
       </c>
       <c r="R7">
-        <v>124.24</v>
+        <v>124.42</v>
       </c>
       <c r="S7">
-        <v>124.45</v>
+        <v>124.62</v>
       </c>
       <c r="T7">
-        <v>10.51</v>
+        <v>10.01</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1634,34 +1634,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>79.77</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="Z7">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="AA7">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="AB7">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AC7">
-        <v>100</v>
+        <v>95.48</v>
       </c>
       <c r="AD7">
-        <v>93.59</v>
+        <v>95.91</v>
       </c>
       <c r="AE7">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="AF7">
-        <v>107.57</v>
+        <v>102.26</v>
       </c>
       <c r="AG7">
-        <v>137.9</v>
+        <v>139.06</v>
       </c>
       <c r="AH7">
-        <v>117.01</v>
+        <v>117.48</v>
       </c>
       <c r="AI7">
         <v>126.74</v>
@@ -1670,7 +1670,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>45.88</v>
+        <v>48.26</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1681,55 +1681,55 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>474.44</v>
+        <v>472</v>
       </c>
       <c r="D8">
-        <v>-1.82</v>
+        <v>-0.51</v>
       </c>
       <c r="E8">
         <v>566.34</v>
       </c>
       <c r="F8">
-        <v>444.37</v>
+        <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-16.23</v>
+        <v>-16.66</v>
       </c>
       <c r="H8">
-        <v>6.77</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
-        <v>-1.7</v>
+        <v>-1.92</v>
       </c>
       <c r="J8">
-        <v>-2.04</v>
+        <v>-3.32</v>
       </c>
       <c r="K8">
-        <v>-9.279999999999999</v>
+        <v>-9.75</v>
       </c>
       <c r="L8">
-        <v>7.53</v>
+        <v>6.22</v>
       </c>
       <c r="M8">
-        <v>7.74</v>
+        <v>7.49</v>
       </c>
       <c r="N8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>479.88</v>
+        <v>478.04</v>
       </c>
       <c r="Q8">
-        <v>486</v>
+        <v>485.14</v>
       </c>
       <c r="R8">
-        <v>482.74</v>
+        <v>482.36</v>
       </c>
       <c r="S8">
-        <v>510.19</v>
+        <v>509.96</v>
       </c>
       <c r="T8">
-        <v>-7.01</v>
+        <v>-7.44</v>
       </c>
       <c r="U8" t="s">
         <v>59</v>
@@ -1744,43 +1744,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>37.96</v>
+        <v>35.78</v>
       </c>
       <c r="Z8">
-        <v>-2.1</v>
+        <v>-2.74</v>
       </c>
       <c r="AA8">
-        <v>-1.19</v>
+        <v>-1.5</v>
       </c>
       <c r="AB8">
-        <v>-0.92</v>
+        <v>-1.24</v>
       </c>
       <c r="AC8">
-        <v>26.86</v>
+        <v>20.6</v>
       </c>
       <c r="AD8">
-        <v>21.11</v>
+        <v>24.77</v>
       </c>
       <c r="AE8">
-        <v>9.99</v>
+        <v>10.27</v>
       </c>
       <c r="AF8">
-        <v>99.16</v>
+        <v>52.21</v>
       </c>
       <c r="AG8">
-        <v>498.36</v>
+        <v>498.89</v>
       </c>
       <c r="AH8">
-        <v>473.64</v>
+        <v>471.4</v>
       </c>
       <c r="AI8">
-        <v>509.42</v>
+        <v>502.73</v>
       </c>
       <c r="AJ8" t="s">
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>27.28</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1791,10 +1791,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>966.1</v>
+        <v>968.17</v>
       </c>
       <c r="D9">
-        <v>-0.2</v>
+        <v>0.21</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1803,85 +1803,85 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-4.24</v>
+        <v>-4.03</v>
       </c>
       <c r="H9">
-        <v>9.16</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I9">
-        <v>-1.11</v>
+        <v>-0.57</v>
       </c>
       <c r="J9">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="K9">
-        <v>-1.29</v>
+        <v>-1.08</v>
       </c>
       <c r="L9">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="M9">
-        <v>15.56</v>
+        <v>15.53</v>
       </c>
       <c r="N9">
         <v>58</v>
       </c>
       <c r="P9">
-        <v>967.96</v>
+        <v>966.86</v>
       </c>
       <c r="Q9">
-        <v>971.24</v>
+        <v>971.64</v>
       </c>
       <c r="R9">
-        <v>971.52</v>
+        <v>971.46</v>
       </c>
       <c r="S9">
         <v>965.34</v>
       </c>
       <c r="T9">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="U9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9">
-        <v>46.23</v>
+        <v>48.26</v>
       </c>
       <c r="Z9">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="AA9">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AB9">
-        <v>-0.99</v>
+        <v>-0.91</v>
       </c>
       <c r="AC9">
-        <v>17.46</v>
+        <v>18.28</v>
       </c>
       <c r="AD9">
-        <v>16.02</v>
+        <v>16.49</v>
       </c>
       <c r="AE9">
-        <v>11.04</v>
+        <v>10.94</v>
       </c>
       <c r="AF9">
-        <v>44.68</v>
+        <v>-23.3</v>
       </c>
       <c r="AG9">
-        <v>982.83</v>
+        <v>982.1</v>
       </c>
       <c r="AH9">
-        <v>959.64</v>
+        <v>961.1900000000001</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1890,7 +1890,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>18.81</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1901,7 +1901,7 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>33.83</v>
+        <v>33.93</v>
       </c>
       <c r="D10">
         <v>0.3</v>
@@ -1913,43 +1913,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-21.64</v>
+        <v>-21.4</v>
       </c>
       <c r="H10">
-        <v>18.2</v>
+        <v>18.55</v>
       </c>
       <c r="I10">
-        <v>-2.65</v>
+        <v>0.71</v>
       </c>
       <c r="J10">
-        <v>5.75</v>
+        <v>3.63</v>
       </c>
       <c r="K10">
-        <v>5.62</v>
+        <v>5.93</v>
       </c>
       <c r="L10">
-        <v>-12.79</v>
+        <v>-12.71</v>
       </c>
       <c r="M10">
-        <v>-0.21</v>
+        <v>-0.09</v>
       </c>
       <c r="N10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P10">
-        <v>33.78</v>
+        <v>33.83</v>
       </c>
       <c r="Q10">
-        <v>34.44</v>
+        <v>34.45</v>
       </c>
       <c r="R10">
-        <v>32.41</v>
+        <v>32.46</v>
       </c>
       <c r="S10">
-        <v>35.61</v>
+        <v>35.59</v>
       </c>
       <c r="T10">
-        <v>-5</v>
+        <v>-4.66</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1964,34 +1964,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>51.52</v>
+        <v>52.63</v>
       </c>
       <c r="Z10">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="AA10">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="AB10">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="AC10">
-        <v>8.76</v>
+        <v>7.65</v>
       </c>
       <c r="AD10">
-        <v>6.85</v>
+        <v>7.55</v>
       </c>
       <c r="AE10">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="AF10">
-        <v>-64.01000000000001</v>
+        <v>-58.31</v>
       </c>
       <c r="AG10">
-        <v>35.43</v>
+        <v>35.42</v>
       </c>
       <c r="AH10">
-        <v>33.45</v>
+        <v>33.48</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -2000,7 +2000,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>28.46</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2014,7 +2014,7 @@
         <v>33.92</v>
       </c>
       <c r="D11">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -2029,37 +2029,37 @@
         <v>18.48</v>
       </c>
       <c r="I11">
-        <v>-2.56</v>
+        <v>1.01</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>3.73</v>
       </c>
       <c r="K11">
         <v>5.8</v>
       </c>
       <c r="L11">
-        <v>-12.89</v>
+        <v>-13.05</v>
       </c>
       <c r="M11">
-        <v>-0.22</v>
+        <v>-0.39</v>
       </c>
       <c r="N11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P11">
-        <v>33.82</v>
+        <v>33.89</v>
       </c>
       <c r="Q11">
         <v>34.48</v>
       </c>
       <c r="R11">
-        <v>32.43</v>
+        <v>32.47</v>
       </c>
       <c r="S11">
-        <v>35.68</v>
+        <v>35.65</v>
       </c>
       <c r="T11">
-        <v>-4.93</v>
+        <v>-4.86</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -2077,31 +2077,31 @@
         <v>52.12</v>
       </c>
       <c r="Z11">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="AA11">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB11">
         <v>-0.22</v>
       </c>
       <c r="AC11">
-        <v>16.75</v>
+        <v>14.37</v>
       </c>
       <c r="AD11">
-        <v>13</v>
+        <v>14.78</v>
       </c>
       <c r="AE11">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="AF11">
-        <v>-64.42</v>
+        <v>-63.36</v>
       </c>
       <c r="AG11">
-        <v>35.49</v>
+        <v>35.48</v>
       </c>
       <c r="AH11">
-        <v>33.46</v>
+        <v>33.49</v>
       </c>
       <c r="AI11">
         <v>32.2</v>
@@ -2110,7 +2110,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>20.97</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2121,10 +2121,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>799.9400000000001</v>
+        <v>804.14</v>
       </c>
       <c r="D12">
-        <v>-0.04</v>
+        <v>0.53</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2133,43 +2133,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-1.12</v>
+        <v>-0.6</v>
       </c>
       <c r="H12">
-        <v>22.71</v>
+        <v>23.35</v>
       </c>
       <c r="I12">
-        <v>-0.97</v>
+        <v>-0.22</v>
       </c>
       <c r="J12">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="K12">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="L12">
-        <v>9.25</v>
+        <v>10.2</v>
       </c>
       <c r="M12">
-        <v>14.05</v>
+        <v>14.15</v>
       </c>
       <c r="N12">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>801.8099999999999</v>
+        <v>801.46</v>
       </c>
       <c r="Q12">
-        <v>801.13</v>
+        <v>802.36</v>
       </c>
       <c r="R12">
-        <v>787.75</v>
+        <v>788.34</v>
       </c>
       <c r="S12">
-        <v>750.67</v>
+        <v>750.96</v>
       </c>
       <c r="T12">
-        <v>6.56</v>
+        <v>7.08</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -2184,34 +2184,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>54.6</v>
+        <v>59.3</v>
       </c>
       <c r="Z12">
-        <v>5.22</v>
+        <v>4.98</v>
       </c>
       <c r="AA12">
-        <v>6.8</v>
+        <v>6.44</v>
       </c>
       <c r="AB12">
-        <v>-1.58</v>
+        <v>-1.45</v>
       </c>
       <c r="AC12">
-        <v>7.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AD12">
-        <v>13.75</v>
+        <v>8.01</v>
       </c>
       <c r="AE12">
-        <v>13.34</v>
+        <v>13.1</v>
       </c>
       <c r="AF12">
-        <v>-6.19</v>
+        <v>-51.01</v>
       </c>
       <c r="AG12">
-        <v>818.8</v>
+        <v>816.85</v>
       </c>
       <c r="AH12">
-        <v>783.46</v>
+        <v>787.87</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2220,7 +2220,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>37.27</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2231,10 +2231,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>275.87</v>
+        <v>276.94</v>
       </c>
       <c r="D13">
-        <v>-0.32</v>
+        <v>0.39</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2243,43 +2243,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-7.29</v>
+        <v>-6.93</v>
       </c>
       <c r="H13">
-        <v>8.85</v>
+        <v>9.27</v>
       </c>
       <c r="I13">
+        <v>0.3</v>
+      </c>
+      <c r="J13">
+        <v>1.22</v>
+      </c>
+      <c r="K13">
+        <v>2.21</v>
+      </c>
+      <c r="L13">
+        <v>-2.16</v>
+      </c>
+      <c r="M13">
+        <v>9.06</v>
+      </c>
+      <c r="N13">
+        <v>47</v>
+      </c>
+      <c r="P13">
+        <v>276.15</v>
+      </c>
+      <c r="Q13">
+        <v>277.92</v>
+      </c>
+      <c r="R13">
+        <v>275.41</v>
+      </c>
+      <c r="S13">
+        <v>279.43</v>
+      </c>
+      <c r="T13">
         <v>-0.89</v>
-      </c>
-      <c r="J13">
-        <v>1.72</v>
-      </c>
-      <c r="K13">
-        <v>1.82</v>
-      </c>
-      <c r="L13">
-        <v>-2.35</v>
-      </c>
-      <c r="M13">
-        <v>8.98</v>
-      </c>
-      <c r="N13">
-        <v>37</v>
-      </c>
-      <c r="P13">
-        <v>275.98</v>
-      </c>
-      <c r="Q13">
-        <v>277.75</v>
-      </c>
-      <c r="R13">
-        <v>275.31</v>
-      </c>
-      <c r="S13">
-        <v>279.49</v>
-      </c>
-      <c r="T13">
-        <v>-1.29</v>
       </c>
       <c r="U13" t="s">
         <v>59</v>
@@ -2294,34 +2294,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>47.63</v>
+        <v>51.36</v>
       </c>
       <c r="Z13">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AA13">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="AB13">
-        <v>-0.53</v>
+        <v>-0.45</v>
       </c>
       <c r="AC13">
-        <v>27.87</v>
+        <v>29.94</v>
       </c>
       <c r="AD13">
-        <v>19.74</v>
+        <v>26.34</v>
       </c>
       <c r="AE13">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="AF13">
-        <v>-33.54</v>
+        <v>-31.22</v>
       </c>
       <c r="AG13">
-        <v>281.72</v>
+        <v>281.39</v>
       </c>
       <c r="AH13">
-        <v>273.78</v>
+        <v>274.45</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2330,7 +2330,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>10.39</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2341,10 +2341,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>268.67</v>
+        <v>269.9</v>
       </c>
       <c r="D14">
-        <v>-0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2353,31 +2353,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-7.23</v>
+        <v>-6.81</v>
       </c>
       <c r="H14">
-        <v>8.970000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I14">
-        <v>-0.6899999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="J14">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="K14">
-        <v>2.02</v>
+        <v>2.49</v>
       </c>
       <c r="M14">
-        <v>-9.029999999999999</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="P14">
-        <v>268.59</v>
+        <v>268.85</v>
       </c>
       <c r="Q14">
-        <v>270.19</v>
+        <v>270.38</v>
       </c>
       <c r="R14">
-        <v>267.93</v>
+        <v>268.04</v>
       </c>
       <c r="U14" t="s">
         <v>59</v>
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>48.41</v>
+        <v>53.03</v>
       </c>
       <c r="Z14">
         <v>0.39</v>
       </c>
       <c r="AA14">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="AB14">
-        <v>-0.48</v>
+        <v>-0.38</v>
       </c>
       <c r="AC14">
-        <v>27.55</v>
+        <v>30.93</v>
       </c>
       <c r="AD14">
-        <v>19.68</v>
+        <v>26.17</v>
       </c>
       <c r="AE14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AF14">
-        <v>-53.99</v>
+        <v>316.02</v>
       </c>
       <c r="AG14">
-        <v>273.82</v>
+        <v>273.47</v>
       </c>
       <c r="AH14">
-        <v>266.55</v>
+        <v>267.28</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2425,7 +2425,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>55.76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2436,10 +2436,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>263.49</v>
+        <v>264.78</v>
       </c>
       <c r="D15">
-        <v>-0.26</v>
+        <v>0.49</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2448,43 +2448,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-7.32</v>
+        <v>-6.87</v>
       </c>
       <c r="H15">
-        <v>9.1</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I15">
-        <v>-0.84</v>
+        <v>0.43</v>
       </c>
       <c r="J15">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="K15">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="L15">
-        <v>-2.28</v>
+        <v>-2.11</v>
       </c>
       <c r="M15">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="N15">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="P15">
-        <v>263.5</v>
+        <v>263.73</v>
       </c>
       <c r="Q15">
-        <v>265.31</v>
+        <v>265.51</v>
       </c>
       <c r="R15">
-        <v>262.96</v>
+        <v>263.07</v>
       </c>
       <c r="S15">
-        <v>266.81</v>
+        <v>266.76</v>
       </c>
       <c r="T15">
-        <v>-1.24</v>
+        <v>-0.74</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -2499,34 +2499,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>47.79</v>
+        <v>52.21</v>
       </c>
       <c r="Z15">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AA15">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="AB15">
-        <v>-0.51</v>
+        <v>-0.41</v>
       </c>
       <c r="AC15">
-        <v>27.48</v>
+        <v>31.74</v>
       </c>
       <c r="AD15">
-        <v>19.2</v>
+        <v>26.54</v>
       </c>
       <c r="AE15">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="AF15">
-        <v>-14.07</v>
+        <v>-83.98</v>
       </c>
       <c r="AG15">
-        <v>269.29</v>
+        <v>268.89</v>
       </c>
       <c r="AH15">
-        <v>261.32</v>
+        <v>262.13</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2535,7 +2535,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>40.91</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2546,10 +2546,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>274.71</v>
+        <v>275.46</v>
       </c>
       <c r="D16">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2558,43 +2558,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-7.19</v>
+        <v>-6.93</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I16">
-        <v>-0.77</v>
+        <v>0.31</v>
       </c>
       <c r="J16">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="K16">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="L16">
-        <v>-2.26</v>
+        <v>-2.18</v>
       </c>
       <c r="M16">
-        <v>9.02</v>
+        <v>9.09</v>
       </c>
       <c r="N16">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="P16">
-        <v>274.6</v>
+        <v>274.78</v>
       </c>
       <c r="Q16">
-        <v>276.35</v>
+        <v>276.5</v>
       </c>
       <c r="R16">
-        <v>273.92</v>
+        <v>274.02</v>
       </c>
       <c r="S16">
-        <v>278.1</v>
+        <v>278.04</v>
       </c>
       <c r="T16">
-        <v>-1.22</v>
+        <v>-0.93</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -2609,34 +2609,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>48.44</v>
+        <v>51.15</v>
       </c>
       <c r="Z16">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AA16">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="AB16">
-        <v>-0.51</v>
+        <v>-0.44</v>
       </c>
       <c r="AC16">
-        <v>27.69</v>
+        <v>29.11</v>
       </c>
       <c r="AD16">
-        <v>19.34</v>
+        <v>25.67</v>
       </c>
       <c r="AE16">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="AF16">
-        <v>-34.86</v>
+        <v>-33.03</v>
       </c>
       <c r="AG16">
-        <v>280.28</v>
+        <v>279.98</v>
       </c>
       <c r="AH16">
-        <v>272.41</v>
+        <v>273.03</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2645,7 +2645,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>43.01</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2656,10 +2656,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>95.13</v>
+        <v>95.97</v>
       </c>
       <c r="D17">
-        <v>-0.72</v>
+        <v>0.88</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2668,43 +2668,43 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-13.42</v>
+        <v>-12.65</v>
       </c>
       <c r="H17">
-        <v>26.49</v>
+        <v>27.6</v>
       </c>
       <c r="I17">
-        <v>-2.45</v>
+        <v>-0.57</v>
       </c>
       <c r="J17">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="K17">
-        <v>3.3</v>
+        <v>4.21</v>
       </c>
       <c r="L17">
-        <v>20.13</v>
+        <v>21.68</v>
       </c>
       <c r="M17">
-        <v>30.87</v>
+        <v>30.99</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
+        <v>95.87</v>
+      </c>
+      <c r="Q17">
         <v>95.98</v>
-      </c>
-      <c r="Q17">
-        <v>95.81999999999999</v>
       </c>
       <c r="R17">
         <v>95.22</v>
       </c>
       <c r="S17">
-        <v>95.81</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="T17">
-        <v>-0.71</v>
+        <v>0.16</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -2716,37 +2716,37 @@
         <v>58</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17">
-        <v>47.06</v>
+        <v>51.5</v>
       </c>
       <c r="Z17">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="AA17">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="AB17">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="AC17">
-        <v>1.75</v>
+        <v>7.91</v>
       </c>
       <c r="AD17">
-        <v>11.13</v>
+        <v>6.35</v>
       </c>
       <c r="AE17">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AF17">
-        <v>28.9</v>
+        <v>-12.59</v>
       </c>
       <c r="AG17">
-        <v>99.38</v>
+        <v>99.23</v>
       </c>
       <c r="AH17">
-        <v>92.26000000000001</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2755,7 +2755,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>26.43</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2766,10 +2766,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>282.41</v>
+        <v>281.14</v>
       </c>
       <c r="D18">
-        <v>0.03</v>
+        <v>-0.45</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2778,43 +2778,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-4.76</v>
+        <v>-5.19</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>14.48</v>
       </c>
       <c r="I18">
-        <v>0.95</v>
+        <v>1.13</v>
       </c>
       <c r="J18">
-        <v>1.42</v>
+        <v>0.51</v>
       </c>
       <c r="K18">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="L18">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="M18">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>280.18</v>
+        <v>280.81</v>
       </c>
       <c r="Q18">
-        <v>281.05</v>
+        <v>281.18</v>
       </c>
       <c r="R18">
-        <v>283.62</v>
+        <v>283.58</v>
       </c>
       <c r="S18">
-        <v>281.32</v>
+        <v>281.3</v>
       </c>
       <c r="T18">
-        <v>0.39</v>
+        <v>-0.06</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2826,37 +2826,37 @@
         <v>58</v>
       </c>
       <c r="X18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>53.21</v>
+        <v>49.57</v>
       </c>
       <c r="Z18">
-        <v>-0.52</v>
+        <v>-0.45</v>
       </c>
       <c r="AA18">
-        <v>-0.64</v>
+        <v>-0.6</v>
       </c>
       <c r="AB18">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="AC18">
-        <v>78.04000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="AD18">
-        <v>49.28</v>
+        <v>73.33</v>
       </c>
       <c r="AE18">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="AF18">
-        <v>-93.53</v>
+        <v>-88.66</v>
       </c>
       <c r="AG18">
-        <v>284.87</v>
+        <v>284.81</v>
       </c>
       <c r="AH18">
-        <v>277.24</v>
+        <v>277.56</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2865,7 +2865,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>20.97</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2876,55 +2876,55 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>237.34</v>
+        <v>234.57</v>
       </c>
       <c r="D19">
-        <v>-0.38</v>
+        <v>-1.17</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>111.75</v>
+        <v>112.61</v>
       </c>
       <c r="G19">
-        <v>-33.75</v>
+        <v>-34.52</v>
       </c>
       <c r="H19">
-        <v>112.38</v>
+        <v>108.3</v>
       </c>
       <c r="I19">
-        <v>4.71</v>
+        <v>3.26</v>
       </c>
       <c r="J19">
-        <v>9.890000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="K19">
-        <v>-7.18</v>
+        <v>-8.26</v>
       </c>
       <c r="L19">
-        <v>116.47</v>
+        <v>109.91</v>
       </c>
       <c r="M19">
-        <v>56.49</v>
+        <v>55.54</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>231.06</v>
+        <v>232.54</v>
       </c>
       <c r="Q19">
-        <v>222.77</v>
+        <v>223.93</v>
       </c>
       <c r="R19">
-        <v>220.92</v>
+        <v>220.78</v>
       </c>
       <c r="S19">
-        <v>228.43</v>
+        <v>228.87</v>
       </c>
       <c r="T19">
-        <v>3.9</v>
+        <v>2.49</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2939,34 +2939,34 @@
         <v>2</v>
       </c>
       <c r="Y19">
-        <v>65.75</v>
+        <v>61.54</v>
       </c>
       <c r="Z19">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="AA19">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="AB19">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AC19">
-        <v>89.79000000000001</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="AD19">
-        <v>73.98999999999999</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="AE19">
-        <v>6.11</v>
+        <v>5.93</v>
       </c>
       <c r="AF19">
-        <v>26.88</v>
+        <v>28.91</v>
       </c>
       <c r="AG19">
-        <v>240.23</v>
+        <v>241.29</v>
       </c>
       <c r="AH19">
-        <v>205.32</v>
+        <v>206.57</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2975,7 +2975,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>43.73</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2986,10 +2986,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>260.85</v>
+        <v>261.66</v>
       </c>
       <c r="D20">
-        <v>-0.27</v>
+        <v>0.31</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2998,43 +2998,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-7.24</v>
+        <v>-6.95</v>
       </c>
       <c r="H20">
-        <v>8.98</v>
+        <v>9.32</v>
       </c>
       <c r="I20">
-        <v>-0.84</v>
+        <v>0.28</v>
       </c>
       <c r="J20">
-        <v>1.79</v>
+        <v>1.15</v>
       </c>
       <c r="K20">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="L20">
-        <v>-2.33</v>
+        <v>-2.19</v>
       </c>
       <c r="M20">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="N20">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P20">
-        <v>260.82</v>
+        <v>260.96</v>
       </c>
       <c r="Q20">
-        <v>262.48</v>
+        <v>262.63</v>
       </c>
       <c r="R20">
-        <v>260.23</v>
+        <v>260.33</v>
       </c>
       <c r="S20">
-        <v>264.19</v>
+        <v>264.14</v>
       </c>
       <c r="T20">
-        <v>-1.27</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -3049,34 +3049,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>48.11</v>
+        <v>51.13</v>
       </c>
       <c r="Z20">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="AA20">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="AB20">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="AC20">
-        <v>28.42</v>
+        <v>30.9</v>
       </c>
       <c r="AD20">
-        <v>19.62</v>
+        <v>26.73</v>
       </c>
       <c r="AE20">
-        <v>4.69</v>
+        <v>4.88</v>
       </c>
       <c r="AF20">
-        <v>-0.26</v>
+        <v>-55.59</v>
       </c>
       <c r="AG20">
-        <v>266.19</v>
+        <v>265.88</v>
       </c>
       <c r="AH20">
-        <v>258.76</v>
+        <v>259.39</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3085,7 +3085,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>35.89</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3096,10 +3096,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>792.9400000000001</v>
+        <v>795.3200000000001</v>
       </c>
       <c r="D21">
-        <v>-0.13</v>
+        <v>0.3</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3108,43 +3108,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="H21">
-        <v>23.38</v>
+        <v>23.75</v>
       </c>
       <c r="I21">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="J21">
-        <v>3.02</v>
+        <v>2.24</v>
       </c>
       <c r="K21">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="L21">
-        <v>9.41</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M21">
-        <v>14.08</v>
+        <v>14.03</v>
       </c>
       <c r="N21">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P21">
-        <v>794.99</v>
+        <v>794.3200000000001</v>
       </c>
       <c r="Q21">
-        <v>793.6900000000001</v>
+        <v>794.8</v>
       </c>
       <c r="R21">
-        <v>780.62</v>
+        <v>781.16</v>
       </c>
       <c r="S21">
-        <v>743.83</v>
+        <v>744.1</v>
       </c>
       <c r="T21">
-        <v>6.6</v>
+        <v>6.88</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -3159,34 +3159,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>54.09</v>
+        <v>56.5</v>
       </c>
       <c r="Z21">
-        <v>5.25</v>
+        <v>4.88</v>
       </c>
       <c r="AA21">
-        <v>6.7</v>
+        <v>6.33</v>
       </c>
       <c r="AB21">
-        <v>-1.45</v>
+        <v>-1.46</v>
       </c>
       <c r="AC21">
-        <v>7.19</v>
+        <v>5.93</v>
       </c>
       <c r="AD21">
-        <v>12.53</v>
+        <v>6.77</v>
       </c>
       <c r="AE21">
-        <v>10.79</v>
+        <v>11.84</v>
       </c>
       <c r="AF21">
-        <v>-21.34</v>
+        <v>-17.47</v>
       </c>
       <c r="AG21">
-        <v>810.21</v>
+        <v>808.23</v>
       </c>
       <c r="AH21">
-        <v>777.17</v>
+        <v>781.37</v>
       </c>
       <c r="AI21">
         <v>773.79</v>
@@ -3195,7 +3195,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>16.33</v>
+        <v>19.97</v>
       </c>
     </row>
   </sheetData>
@@ -3336,7 +3336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3376,36 +3376,36 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>58</v>
@@ -3415,1322 +3415,1325 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F7" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="5" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="D9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="5" t="s">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="F10" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0.65</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.18</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="D15" s="7">
-        <v>1.07</v>
+        <v>0.61</v>
       </c>
       <c r="E15" s="8">
-        <v>0.06</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-3.33</v>
+        <v>1.07</v>
       </c>
       <c r="D16" s="7">
-        <v>-2.24</v>
+        <v>0.42</v>
       </c>
       <c r="E16" s="8">
-        <v>1.09</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-2.39</v>
+        <v>-2.24</v>
       </c>
       <c r="D17" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.82</v>
+        <v>-2.37</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>8.18</v>
+        <v>-3.21</v>
       </c>
       <c r="D18" s="7">
-        <v>12.81</v>
+        <v>-3.78</v>
       </c>
       <c r="E18" s="8">
-        <v>4.63</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>8.15</v>
+        <v>12.81</v>
       </c>
       <c r="D19" s="7">
-        <v>12.92</v>
+        <v>11.94</v>
       </c>
       <c r="E19" s="8">
-        <v>4.77</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>0.55</v>
+        <v>12.92</v>
       </c>
       <c r="D20" s="7">
-        <v>-2.04</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-2.59</v>
+        <v>11.85</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>0.24</v>
+        <v>-2.04</v>
       </c>
       <c r="D21" s="7">
-        <v>0.92</v>
+        <v>-3.32</v>
       </c>
       <c r="E21" s="8">
-        <v>0.68</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>7.05</v>
+        <v>0.92</v>
       </c>
       <c r="D22" s="7">
-        <v>5.75</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.3</v>
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>7.44</v>
+        <v>5.75</v>
       </c>
       <c r="D23" s="7">
-        <v>6</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-1.44</v>
+        <v>3.63</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>3.01</v>
+        <v>6</v>
       </c>
       <c r="D24" s="7">
-        <v>3.05</v>
+        <v>3.73</v>
       </c>
       <c r="E24" s="8">
-        <v>0.04</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>1.17</v>
+        <v>3.05</v>
       </c>
       <c r="D25" s="7">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="E25" s="8">
-        <v>0.55</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="D26" s="7">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="E26" s="8">
-        <v>0.55</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="D27" s="7">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="E27" s="8">
-        <v>0.82</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>1.21</v>
+        <v>1.93</v>
       </c>
       <c r="D28" s="7">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="E28" s="8">
-        <v>0.62</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="7">
-        <v>2.79</v>
+        <v>1.83</v>
       </c>
       <c r="D29" s="7">
-        <v>1.83</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.96</v>
+        <v>1.22</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="7">
-        <v>-0.66</v>
+        <v>1.83</v>
       </c>
       <c r="D30" s="7">
-        <v>1.42</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.08</v>
+        <v>2.62</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.79</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="7">
-        <v>5.67</v>
+        <v>1.42</v>
       </c>
       <c r="D31" s="7">
-        <v>9.890000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="E31" s="8">
-        <v>4.22</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="7">
-        <v>1.11</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="D32" s="7">
-        <v>1.79</v>
+        <v>7.45</v>
       </c>
       <c r="E32" s="8">
-        <v>0.68</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="7">
-        <v>2.79</v>
+        <v>1.79</v>
       </c>
       <c r="D33" s="7">
-        <v>3.02</v>
+        <v>1.15</v>
       </c>
       <c r="E33" s="8">
-        <v>0.23</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" s="7">
-        <v>-0.32</v>
+        <v>3.02</v>
       </c>
       <c r="D34" s="7">
-        <v>-0.28</v>
+        <v>2.24</v>
       </c>
       <c r="E34" s="8">
-        <v>0.04</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>-0.18</v>
+        <v>-0.28</v>
       </c>
       <c r="D35" s="7">
-        <v>-0.4</v>
+        <v>0.04</v>
       </c>
       <c r="E35" s="9">
-        <v>-0.22</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-0.88</v>
+        <v>-0.4</v>
       </c>
       <c r="D36" s="7">
-        <v>0.23</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.11</v>
+        <v>-0.03</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.37</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-1.66</v>
+        <v>0.23</v>
       </c>
       <c r="D37" s="7">
-        <v>-1.89</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.23</v>
+        <v>-0.22</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>2.71</v>
+        <v>-1.89</v>
       </c>
       <c r="D38" s="7">
-        <v>6.31</v>
-      </c>
-      <c r="E38" s="8">
-        <v>3.6</v>
+        <v>-0.35</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1.54</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>2.64</v>
+        <v>6.31</v>
       </c>
       <c r="D39" s="7">
-        <v>5.29</v>
+        <v>5.02</v>
       </c>
       <c r="E39" s="8">
-        <v>2.65</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>0.27</v>
+        <v>5.29</v>
       </c>
       <c r="D40" s="7">
-        <v>-1.7</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.97</v>
+        <v>4.88</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-0.02</v>
+        <v>-1.7</v>
       </c>
       <c r="D41" s="7">
-        <v>-1.11</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-1.09</v>
+        <v>-1.92</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>-2.13</v>
+        <v>-1.11</v>
       </c>
       <c r="D42" s="7">
-        <v>-2.65</v>
+        <v>-0.57</v>
       </c>
       <c r="E42" s="9">
-        <v>-0.52</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>-2.01</v>
+        <v>-2.65</v>
       </c>
       <c r="D43" s="7">
-        <v>-2.56</v>
+        <v>0.71</v>
       </c>
       <c r="E43" s="9">
-        <v>-0.55</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>-0.57</v>
+        <v>-2.56</v>
       </c>
       <c r="D44" s="7">
-        <v>-0.97</v>
+        <v>1.01</v>
       </c>
       <c r="E44" s="9">
-        <v>-0.4</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>-0.57</v>
+        <v>-0.97</v>
       </c>
       <c r="D45" s="7">
-        <v>-0.89</v>
+        <v>-0.22</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.32</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>-0.49</v>
+        <v>-0.89</v>
       </c>
       <c r="D46" s="7">
-        <v>-0.6899999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="E46" s="9">
-        <v>-0.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="7">
-        <v>-0.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D47" s="7">
-        <v>-0.84</v>
+        <v>0.49</v>
       </c>
       <c r="E47" s="9">
-        <v>-0.34</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-0.84</v>
       </c>
       <c r="D48" s="7">
-        <v>-0.77</v>
+        <v>0.43</v>
       </c>
       <c r="E48" s="9">
-        <v>-0.21</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="7">
-        <v>-1.87</v>
+        <v>-0.77</v>
       </c>
       <c r="D49" s="7">
-        <v>-2.45</v>
+        <v>0.31</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.58</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="7">
-        <v>0.01</v>
+        <v>-2.45</v>
       </c>
       <c r="D50" s="7">
-        <v>0.95</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.9399999999999999</v>
+        <v>-0.57</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1.88</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="7">
-        <v>1.98</v>
+        <v>0.95</v>
       </c>
       <c r="D51" s="7">
-        <v>4.71</v>
-      </c>
-      <c r="E51" s="8">
-        <v>2.73</v>
+        <v>1.13</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.18</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="7">
-        <v>-0.62</v>
+        <v>4.71</v>
       </c>
       <c r="D52" s="7">
-        <v>-0.84</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.22</v>
+        <v>3.26</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="7">
-        <v>-0.62</v>
+        <v>-0.84</v>
       </c>
       <c r="D53" s="7">
-        <v>-0.84</v>
+        <v>0.28</v>
       </c>
       <c r="E53" s="9">
-        <v>-0.22</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C54" s="7">
-        <v>3.56</v>
+        <v>-0.84</v>
       </c>
       <c r="D54" s="7">
-        <v>3.35</v>
+        <v>-0.42</v>
       </c>
       <c r="E54" s="9">
-        <v>-0.21</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-89.62</v>
+        <v>3.35</v>
       </c>
       <c r="D55" s="7">
-        <v>-89.67</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.05</v>
+        <v>3.24</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>3.27</v>
+        <v>-89.67</v>
       </c>
       <c r="D56" s="7">
-        <v>4.13</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.86</v>
+        <v>-89.66</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>-12.79</v>
+        <v>4.13</v>
       </c>
       <c r="D57" s="7">
-        <v>-15.49</v>
+        <v>4.23</v>
       </c>
       <c r="E57" s="9">
-        <v>-2.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>55.75</v>
+        <v>-15.49</v>
       </c>
       <c r="D58" s="7">
-        <v>62.06</v>
-      </c>
-      <c r="E58" s="8">
-        <v>6.31</v>
+        <v>-14.75</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0.74</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>55.51</v>
+        <v>62.06</v>
       </c>
       <c r="D59" s="7">
-        <v>62.3</v>
+        <v>60.85</v>
       </c>
       <c r="E59" s="8">
-        <v>6.79</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>5.08</v>
+        <v>62.3</v>
       </c>
       <c r="D60" s="7">
-        <v>7.53</v>
+        <v>60.83</v>
       </c>
       <c r="E60" s="8">
-        <v>2.45</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>3.29</v>
+        <v>7.53</v>
       </c>
       <c r="D61" s="7">
-        <v>1.85</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-1.44</v>
+        <v>6.22</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>-9.859999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="D62" s="7">
-        <v>-12.79</v>
+        <v>2.12</v>
       </c>
       <c r="E62" s="9">
-        <v>-2.93</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>-9.94</v>
+        <v>-12.79</v>
       </c>
       <c r="D63" s="7">
-        <v>-12.89</v>
+        <v>-12.71</v>
       </c>
       <c r="E63" s="9">
-        <v>-2.95</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>10.86</v>
+        <v>-12.89</v>
       </c>
       <c r="D64" s="7">
-        <v>9.25</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-1.61</v>
+        <v>-13.05</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>-1.6</v>
+        <v>9.25</v>
       </c>
       <c r="D65" s="7">
-        <v>-2.35</v>
+        <v>10.2</v>
       </c>
       <c r="E65" s="9">
-        <v>-0.75</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>-1.62</v>
+        <v>-2.35</v>
       </c>
       <c r="D66" s="7">
-        <v>-2.28</v>
+        <v>-2.16</v>
       </c>
       <c r="E66" s="9">
-        <v>-0.66</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>-1.63</v>
+        <v>-2.28</v>
       </c>
       <c r="D67" s="7">
-        <v>-2.26</v>
+        <v>-2.11</v>
       </c>
       <c r="E67" s="9">
-        <v>-0.63</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>22.2</v>
+        <v>-2.26</v>
       </c>
       <c r="D68" s="7">
-        <v>20.13</v>
+        <v>-2.18</v>
       </c>
       <c r="E68" s="9">
-        <v>-2.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>1.89</v>
+        <v>20.13</v>
       </c>
       <c r="D69" s="7">
-        <v>2.98</v>
-      </c>
-      <c r="E69" s="8">
-        <v>1.09</v>
+        <v>21.68</v>
+      </c>
+      <c r="E69" s="9">
+        <v>1.55</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>104.59</v>
+        <v>2.98</v>
       </c>
       <c r="D70" s="7">
-        <v>116.47</v>
+        <v>2.34</v>
       </c>
       <c r="E70" s="8">
-        <v>11.88</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>-1.68</v>
+        <v>116.47</v>
       </c>
       <c r="D71" s="7">
-        <v>-2.33</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-0.65</v>
+        <v>109.91</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-6.56</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="7">
-        <v>11.18</v>
+        <v>-2.33</v>
       </c>
       <c r="D72" s="7">
-        <v>9.41</v>
+        <v>-2.19</v>
       </c>
       <c r="E72" s="9">
-        <v>-1.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C73" s="7">
-        <v>4.39</v>
+        <v>9.41</v>
       </c>
       <c r="D73" s="7">
-        <v>4.83</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.44</v>
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0.37</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="7">
-        <v>4.42</v>
+        <v>4.83</v>
       </c>
       <c r="D74" s="7">
-        <v>4.82</v>
-      </c>
-      <c r="E74" s="8">
-        <v>0.4</v>
+        <v>4.89</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>-10.01</v>
+        <v>4.82</v>
       </c>
       <c r="D75" s="7">
-        <v>-9.539999999999999</v>
-      </c>
-      <c r="E75" s="8">
-        <v>0.47</v>
+        <v>4.97</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.15</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>-3.99</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="D76" s="7">
-        <v>-4.8</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-0.8100000000000001</v>
+        <v>-9.82</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>-1.25</v>
+        <v>-4.8</v>
       </c>
       <c r="D77" s="7">
-        <v>3.08</v>
-      </c>
-      <c r="E77" s="8">
-        <v>4.33</v>
+        <v>-4.48</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0.32</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>-1.28</v>
+        <v>3.08</v>
       </c>
       <c r="D78" s="7">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="E78" s="8">
-        <v>4.41</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>-10.27</v>
+        <v>3.13</v>
       </c>
       <c r="D79" s="7">
-        <v>-9.279999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="E79" s="8">
-        <v>0.99</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>-0.59</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="D80" s="7">
-        <v>-1.29</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-0.7</v>
+        <v>-9.75</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>6.02</v>
+        <v>-1.29</v>
       </c>
       <c r="D81" s="7">
-        <v>5.62</v>
+        <v>-1.08</v>
       </c>
       <c r="E81" s="9">
-        <v>-0.4</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="7">
-        <v>5.97</v>
+        <v>5.62</v>
       </c>
       <c r="D82" s="7">
-        <v>5.8</v>
+        <v>5.93</v>
       </c>
       <c r="E82" s="9">
-        <v>-0.17</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4741,13 +4744,13 @@
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>5.01</v>
+        <v>3.2</v>
       </c>
       <c r="D83" s="7">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="E83" s="9">
-        <v>-1.81</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4758,13 +4761,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="D84" s="7">
-        <v>1.82</v>
-      </c>
-      <c r="E84" s="8">
-        <v>0.14</v>
+        <v>2.21</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0.39</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4775,13 +4778,13 @@
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="D85" s="7">
-        <v>2.02</v>
-      </c>
-      <c r="E85" s="8">
-        <v>0.41</v>
+        <v>2.49</v>
+      </c>
+      <c r="E85" s="9">
+        <v>0.47</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4792,13 +4795,13 @@
         <v>10</v>
       </c>
       <c r="C86" s="7">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="D86" s="7">
-        <v>1.79</v>
-      </c>
-      <c r="E86" s="8">
-        <v>0.05</v>
+        <v>2.29</v>
+      </c>
+      <c r="E86" s="9">
+        <v>0.5</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4809,13 +4812,13 @@
         <v>10</v>
       </c>
       <c r="C87" s="7">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="D87" s="7">
-        <v>1.93</v>
-      </c>
-      <c r="E87" s="8">
-        <v>0.33</v>
+        <v>2.21</v>
+      </c>
+      <c r="E87" s="9">
+        <v>0.28</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4826,13 +4829,13 @@
         <v>10</v>
       </c>
       <c r="C88" s="7">
-        <v>4.48</v>
+        <v>3.3</v>
       </c>
       <c r="D88" s="7">
-        <v>3.3</v>
+        <v>4.21</v>
       </c>
       <c r="E88" s="9">
-        <v>-1.18</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4843,13 +4846,13 @@
         <v>10</v>
       </c>
       <c r="C89" s="7">
-        <v>2.01</v>
+        <v>4.33</v>
       </c>
       <c r="D89" s="7">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="E89" s="8">
-        <v>2.32</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4860,13 +4863,13 @@
         <v>10</v>
       </c>
       <c r="C90" s="7">
-        <v>-11.96</v>
+        <v>-7.18</v>
       </c>
       <c r="D90" s="7">
-        <v>-7.18</v>
+        <v>-8.26</v>
       </c>
       <c r="E90" s="8">
-        <v>4.78</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4877,13 +4880,13 @@
         <v>10</v>
       </c>
       <c r="C91" s="7">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="D91" s="7">
-        <v>1.94</v>
-      </c>
-      <c r="E91" s="8">
-        <v>0.35</v>
+        <v>2.26</v>
+      </c>
+      <c r="E91" s="9">
+        <v>0.32</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4894,13 +4897,13 @@
         <v>10</v>
       </c>
       <c r="C92" s="7">
-        <v>5.04</v>
+        <v>3.36</v>
       </c>
       <c r="D92" s="7">
-        <v>3.36</v>
+        <v>3.67</v>
       </c>
       <c r="E92" s="9">
-        <v>-1.68</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4911,13 +4914,13 @@
         <v>6</v>
       </c>
       <c r="C93" s="7">
-        <v>-6.26</v>
+        <v>-6.47</v>
       </c>
       <c r="D93" s="7">
-        <v>-6.47</v>
+        <v>-6.41</v>
       </c>
       <c r="E93" s="9">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4928,13 +4931,13 @@
         <v>6</v>
       </c>
       <c r="C94" s="7">
-        <v>-90.62</v>
+        <v>-90.66</v>
       </c>
       <c r="D94" s="7">
-        <v>-90.66</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="E94" s="9">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4945,13 +4948,13 @@
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-14.03</v>
+        <v>-13.55</v>
       </c>
       <c r="D95" s="7">
-        <v>-13.55</v>
+        <v>-13.81</v>
       </c>
       <c r="E95" s="8">
-        <v>0.48</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4962,13 +4965,13 @@
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-15.48</v>
+        <v>-16.39</v>
       </c>
       <c r="D96" s="7">
-        <v>-16.39</v>
+        <v>-16.11</v>
       </c>
       <c r="E96" s="9">
-        <v>-0.91</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4979,13 +4982,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-12.05</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="D97" s="7">
-        <v>-9.220000000000001</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="E97" s="8">
-        <v>2.83</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4996,13 +4999,13 @@
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-12.1</v>
+        <v>-9.15</v>
       </c>
       <c r="D98" s="7">
-        <v>-9.15</v>
+        <v>-9.44</v>
       </c>
       <c r="E98" s="8">
-        <v>2.95</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5013,13 +5016,13 @@
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-15.01</v>
+        <v>-16.23</v>
       </c>
       <c r="D99" s="7">
-        <v>-16.23</v>
-      </c>
-      <c r="E99" s="9">
-        <v>-1.22</v>
+        <v>-16.66</v>
+      </c>
+      <c r="E99" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5030,13 +5033,13 @@
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-4.05</v>
+        <v>-4.24</v>
       </c>
       <c r="D100" s="7">
-        <v>-4.24</v>
+        <v>-4.03</v>
       </c>
       <c r="E100" s="9">
-        <v>-0.19</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5047,647 +5050,647 @@
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-21.24</v>
+        <v>-21.64</v>
       </c>
       <c r="D101" s="7">
-        <v>-21.64</v>
+        <v>-21.4</v>
       </c>
       <c r="E101" s="9">
-        <v>-0.4</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-21.3</v>
+        <v>-1.12</v>
       </c>
       <c r="D102" s="7">
-        <v>-21.64</v>
+        <v>-0.6</v>
       </c>
       <c r="E102" s="9">
-        <v>-0.34</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-0.73</v>
+        <v>-7.29</v>
       </c>
       <c r="D103" s="7">
-        <v>-1.12</v>
+        <v>-6.93</v>
       </c>
       <c r="E103" s="9">
-        <v>-0.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-7.05</v>
+        <v>-7.23</v>
       </c>
       <c r="D104" s="7">
-        <v>-7.29</v>
+        <v>-6.81</v>
       </c>
       <c r="E104" s="9">
-        <v>-0.24</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="7">
-        <v>-6.98</v>
+        <v>-7.32</v>
       </c>
       <c r="D105" s="7">
-        <v>-7.23</v>
+        <v>-6.87</v>
       </c>
       <c r="E105" s="9">
-        <v>-0.25</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="7">
-        <v>-7.14</v>
+        <v>-7.19</v>
       </c>
       <c r="D106" s="7">
-        <v>-7.32</v>
+        <v>-6.93</v>
       </c>
       <c r="E106" s="9">
-        <v>-0.18</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="7">
-        <v>-7.01</v>
+        <v>-13.42</v>
       </c>
       <c r="D107" s="7">
-        <v>-7.19</v>
+        <v>-12.65</v>
       </c>
       <c r="E107" s="9">
-        <v>-0.18</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C108" s="7">
-        <v>-12.37</v>
+        <v>-4.76</v>
       </c>
       <c r="D108" s="7">
-        <v>-13.42</v>
-      </c>
-      <c r="E108" s="9">
-        <v>-1.05</v>
+        <v>-5.19</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C109" s="7">
-        <v>-5.79</v>
+        <v>-33.75</v>
       </c>
       <c r="D109" s="7">
-        <v>-4.76</v>
+        <v>-34.52</v>
       </c>
       <c r="E109" s="8">
-        <v>1.03</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C110" s="7">
-        <v>-35.57</v>
+        <v>-7.24</v>
       </c>
       <c r="D110" s="7">
-        <v>-33.75</v>
-      </c>
-      <c r="E110" s="8">
-        <v>1.82</v>
+        <v>-6.95</v>
+      </c>
+      <c r="E110" s="9">
+        <v>0.29</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C111" s="7">
-        <v>-7.11</v>
+        <v>-1.28</v>
       </c>
       <c r="D111" s="7">
-        <v>-7.24</v>
+        <v>-0.99</v>
       </c>
       <c r="E111" s="9">
-        <v>-0.13</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C112" s="7">
-        <v>-0.88</v>
+        <v>594.7</v>
       </c>
       <c r="D112" s="7">
-        <v>-1.28</v>
+        <v>595.0700000000001</v>
       </c>
       <c r="E112" s="9">
-        <v>-0.4</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="7">
-        <v>596.0599999999999</v>
+        <v>59.53</v>
       </c>
       <c r="D113" s="7">
-        <v>594.7</v>
+        <v>59.61</v>
       </c>
       <c r="E113" s="9">
-        <v>-1.36</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="7">
-        <v>59.78</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="D114" s="7">
-        <v>59.53</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-0.25</v>
+        <v>93.78</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>93.54000000000001</v>
+        <v>51</v>
       </c>
       <c r="D115" s="7">
-        <v>94.06999999999999</v>
-      </c>
-      <c r="E115" s="8">
-        <v>0.53</v>
+        <v>51.17</v>
+      </c>
+      <c r="E115" s="9">
+        <v>0.17</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>51.56</v>
+        <v>133.02</v>
       </c>
       <c r="D116" s="7">
-        <v>51</v>
-      </c>
-      <c r="E116" s="9">
-        <v>-0.5600000000000001</v>
+        <v>132.78</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>128.88</v>
+        <v>137.53</v>
       </c>
       <c r="D117" s="7">
-        <v>133.02</v>
+        <v>137.09</v>
       </c>
       <c r="E117" s="8">
-        <v>4.14</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>133.07</v>
+        <v>474.44</v>
       </c>
       <c r="D118" s="7">
-        <v>137.53</v>
+        <v>472</v>
       </c>
       <c r="E118" s="8">
-        <v>4.46</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>481.33</v>
+        <v>966.1</v>
       </c>
       <c r="D119" s="7">
-        <v>474.44</v>
+        <v>968.17</v>
       </c>
       <c r="E119" s="9">
-        <v>-6.89</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>968.01</v>
+        <v>33.83</v>
       </c>
       <c r="D120" s="7">
-        <v>966.1</v>
+        <v>33.93</v>
       </c>
       <c r="E120" s="9">
-        <v>-1.91</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>34</v>
+        <v>799.9400000000001</v>
       </c>
       <c r="D121" s="7">
-        <v>33.83</v>
+        <v>804.14</v>
       </c>
       <c r="E121" s="9">
-        <v>-0.17</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>34.07</v>
+        <v>275.87</v>
       </c>
       <c r="D122" s="7">
-        <v>33.92</v>
+        <v>276.94</v>
       </c>
       <c r="E122" s="9">
-        <v>-0.15</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>803.11</v>
+        <v>268.67</v>
       </c>
       <c r="D123" s="7">
-        <v>799.9400000000001</v>
+        <v>269.9</v>
       </c>
       <c r="E123" s="9">
-        <v>-3.17</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>276.57</v>
+        <v>263.49</v>
       </c>
       <c r="D124" s="7">
-        <v>275.87</v>
+        <v>264.78</v>
       </c>
       <c r="E124" s="9">
-        <v>-0.7</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="7">
-        <v>269.39</v>
+        <v>274.71</v>
       </c>
       <c r="D125" s="7">
-        <v>268.67</v>
+        <v>275.46</v>
       </c>
       <c r="E125" s="9">
-        <v>-0.72</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="7">
-        <v>264.01</v>
+        <v>95.13</v>
       </c>
       <c r="D126" s="7">
-        <v>263.49</v>
+        <v>95.97</v>
       </c>
       <c r="E126" s="9">
-        <v>-0.52</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C127" s="7">
-        <v>275.22</v>
+        <v>282.41</v>
       </c>
       <c r="D127" s="7">
-        <v>274.71</v>
-      </c>
-      <c r="E127" s="9">
-        <v>-0.51</v>
+        <v>281.14</v>
+      </c>
+      <c r="E127" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C128" s="7">
-        <v>96.28</v>
+        <v>237.34</v>
       </c>
       <c r="D128" s="7">
-        <v>95.13</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-1.15</v>
+        <v>234.57</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C129" s="7">
-        <v>279.35</v>
+        <v>260.85</v>
       </c>
       <c r="D129" s="7">
-        <v>282.41</v>
-      </c>
-      <c r="E129" s="8">
-        <v>3.06</v>
+        <v>261.66</v>
+      </c>
+      <c r="E129" s="9">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C130" s="7">
-        <v>230.8</v>
+        <v>792.9400000000001</v>
       </c>
       <c r="D130" s="7">
-        <v>237.34</v>
-      </c>
-      <c r="E130" s="8">
-        <v>6.54</v>
+        <v>795.3200000000001</v>
+      </c>
+      <c r="E130" s="9">
+        <v>2.38</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C131" s="7">
-        <v>261.22</v>
+        <v>89</v>
       </c>
       <c r="D131" s="7">
-        <v>260.85</v>
+        <v>94</v>
       </c>
       <c r="E131" s="9">
-        <v>-0.37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C132" s="7">
-        <v>796.1900000000001</v>
+        <v>94</v>
       </c>
       <c r="D132" s="7">
-        <v>792.9400000000001</v>
-      </c>
-      <c r="E132" s="9">
-        <v>-3.25</v>
+        <v>89</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C133" s="7">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D133" s="7">
-        <v>89</v>
-      </c>
-      <c r="E133" s="9">
+        <v>27</v>
+      </c>
+      <c r="E133" s="8">
         <v>-5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="7">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="D134" s="7">
-        <v>94</v>
-      </c>
-      <c r="E134" s="8">
-        <v>5</v>
+        <v>32</v>
+      </c>
+      <c r="E134" s="9">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="7">
+        <v>27</v>
+      </c>
+      <c r="D135" s="7">
         <v>22</v>
       </c>
-      <c r="D135" s="7">
-        <v>32</v>
-      </c>
       <c r="E135" s="8">
-        <v>10</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C136" s="7">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D136" s="7">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="E136" s="9">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C137" s="7">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D137" s="7">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E137" s="9">
-        <v>-5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C138" s="7">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D138" s="7">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E138" s="9">
-        <v>-10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>13</v>
@@ -5696,44 +5699,44 @@
         <v>53</v>
       </c>
       <c r="D139" s="7">
-        <v>42</v>
-      </c>
-      <c r="E139" s="9">
-        <v>-11</v>
+        <v>37</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-16</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C140" s="7">
+        <v>47</v>
+      </c>
+      <c r="D140" s="7">
         <v>42</v>
       </c>
-      <c r="D140" s="7">
-        <v>53</v>
-      </c>
       <c r="E140" s="8">
-        <v>11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C141" s="7">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D141" s="7">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E141" s="8">
-        <v>10</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -5744,13 +5747,13 @@
         <v>24</v>
       </c>
       <c r="C142" s="7">
-        <v>51.64</v>
+        <v>49.34</v>
       </c>
       <c r="D142" s="7">
-        <v>49.34</v>
+        <v>49.9</v>
       </c>
       <c r="E142" s="9">
-        <v>-2.3</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -5761,13 +5764,13 @@
         <v>24</v>
       </c>
       <c r="C143" s="7">
-        <v>50.41</v>
+        <v>47.1</v>
       </c>
       <c r="D143" s="7">
-        <v>47.1</v>
+        <v>48.24</v>
       </c>
       <c r="E143" s="9">
-        <v>-3.31</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -5778,13 +5781,13 @@
         <v>24</v>
       </c>
       <c r="C144" s="7">
-        <v>36.53</v>
+        <v>43.18</v>
       </c>
       <c r="D144" s="7">
-        <v>43.18</v>
+        <v>40.81</v>
       </c>
       <c r="E144" s="8">
-        <v>6.65</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -5795,13 +5798,13 @@
         <v>24</v>
       </c>
       <c r="C145" s="7">
-        <v>39.9</v>
+        <v>35.17</v>
       </c>
       <c r="D145" s="7">
-        <v>35.17</v>
+        <v>37.7</v>
       </c>
       <c r="E145" s="9">
-        <v>-4.73</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -5812,13 +5815,13 @@
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>72.98</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="D146" s="7">
-        <v>79.23999999999999</v>
+        <v>78.06</v>
       </c>
       <c r="E146" s="8">
-        <v>6.26</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -5829,13 +5832,13 @@
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>73.16</v>
+        <v>79.77</v>
       </c>
       <c r="D147" s="7">
-        <v>79.77</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="E147" s="8">
-        <v>6.61</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -5846,13 +5849,13 @@
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>44.82</v>
+        <v>37.96</v>
       </c>
       <c r="D148" s="7">
-        <v>37.96</v>
-      </c>
-      <c r="E148" s="9">
-        <v>-6.86</v>
+        <v>35.78</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -5863,13 +5866,13 @@
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>47.84</v>
+        <v>46.23</v>
       </c>
       <c r="D149" s="7">
-        <v>46.23</v>
+        <v>48.26</v>
       </c>
       <c r="E149" s="9">
-        <v>-1.61</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -5880,546 +5883,529 @@
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>53.43</v>
+        <v>51.52</v>
       </c>
       <c r="D150" s="7">
-        <v>51.52</v>
+        <v>52.63</v>
       </c>
       <c r="E150" s="9">
-        <v>-1.91</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>53.74</v>
+        <v>54.6</v>
       </c>
       <c r="D151" s="7">
-        <v>52.12</v>
+        <v>59.3</v>
       </c>
       <c r="E151" s="9">
-        <v>-1.62</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>59.07</v>
+        <v>47.63</v>
       </c>
       <c r="D152" s="7">
-        <v>54.6</v>
+        <v>51.36</v>
       </c>
       <c r="E152" s="9">
-        <v>-4.47</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="7">
-        <v>50</v>
+        <v>48.41</v>
       </c>
       <c r="D153" s="7">
-        <v>47.63</v>
+        <v>53.03</v>
       </c>
       <c r="E153" s="9">
-        <v>-2.37</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C154" s="7">
-        <v>50.99</v>
+        <v>47.79</v>
       </c>
       <c r="D154" s="7">
-        <v>48.41</v>
+        <v>52.21</v>
       </c>
       <c r="E154" s="9">
-        <v>-2.58</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C155" s="7">
-        <v>49.53</v>
+        <v>48.44</v>
       </c>
       <c r="D155" s="7">
-        <v>47.79</v>
+        <v>51.15</v>
       </c>
       <c r="E155" s="9">
-        <v>-1.74</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C156" s="7">
-        <v>50.2</v>
+        <v>47.06</v>
       </c>
       <c r="D156" s="7">
-        <v>48.44</v>
+        <v>51.5</v>
       </c>
       <c r="E156" s="9">
-        <v>-1.76</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C157" s="7">
-        <v>53.06</v>
+        <v>53.21</v>
       </c>
       <c r="D157" s="7">
-        <v>47.06</v>
-      </c>
-      <c r="E157" s="9">
-        <v>-6</v>
+        <v>49.57</v>
+      </c>
+      <c r="E157" s="8">
+        <v>-3.64</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C158" s="7">
-        <v>44.76</v>
+        <v>65.75</v>
       </c>
       <c r="D158" s="7">
-        <v>53.21</v>
+        <v>61.54</v>
       </c>
       <c r="E158" s="8">
-        <v>8.449999999999999</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C159" s="7">
-        <v>60.79</v>
+        <v>48.11</v>
       </c>
       <c r="D159" s="7">
-        <v>65.75</v>
-      </c>
-      <c r="E159" s="8">
-        <v>4.96</v>
+        <v>51.13</v>
+      </c>
+      <c r="E159" s="9">
+        <v>3.02</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C160" s="7">
-        <v>49.47</v>
+        <v>54.09</v>
       </c>
       <c r="D160" s="7">
-        <v>48.11</v>
+        <v>56.5</v>
       </c>
       <c r="E160" s="9">
-        <v>-1.36</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="6" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C161" s="7">
-        <v>57.97</v>
+        <v>-5.49</v>
       </c>
       <c r="D161" s="7">
-        <v>54.09</v>
+        <v>0.39</v>
       </c>
       <c r="E161" s="9">
-        <v>-3.88</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="7">
-        <v>-19.79</v>
+        <v>2550.46</v>
       </c>
       <c r="D162" s="7">
-        <v>-5.49</v>
+        <v>1694.46</v>
       </c>
       <c r="E162" s="8">
-        <v>14.3</v>
+        <v>-856</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="7">
-        <v>-57.65</v>
+        <v>-31.2</v>
       </c>
       <c r="D163" s="7">
-        <v>2550.46</v>
+        <v>-46.16</v>
       </c>
       <c r="E163" s="8">
-        <v>2608.11</v>
+        <v>-14.96</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="7">
-        <v>-35.28</v>
+        <v>-12.79</v>
       </c>
       <c r="D164" s="7">
-        <v>-31.2</v>
+        <v>-61.97</v>
       </c>
       <c r="E164" s="8">
-        <v>4.08</v>
+        <v>-49.18</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="7">
-        <v>-29.48</v>
+        <v>102.08</v>
       </c>
       <c r="D165" s="7">
-        <v>-12.79</v>
+        <v>63.78</v>
       </c>
       <c r="E165" s="8">
-        <v>16.69</v>
+        <v>-38.3</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>74.64</v>
+        <v>107.57</v>
       </c>
       <c r="D166" s="7">
-        <v>102.08</v>
+        <v>102.26</v>
       </c>
       <c r="E166" s="8">
-        <v>27.44</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>50.73</v>
+        <v>99.16</v>
       </c>
       <c r="D167" s="7">
-        <v>107.57</v>
+        <v>52.21</v>
       </c>
       <c r="E167" s="8">
-        <v>56.84</v>
+        <v>-46.95</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>-43.82</v>
+        <v>44.68</v>
       </c>
       <c r="D168" s="7">
-        <v>99.16</v>
+        <v>-23.3</v>
       </c>
       <c r="E168" s="8">
-        <v>142.98</v>
+        <v>-67.98</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>-50.39</v>
+        <v>-64.01000000000001</v>
       </c>
       <c r="D169" s="7">
-        <v>44.68</v>
-      </c>
-      <c r="E169" s="8">
-        <v>95.06999999999999</v>
+        <v>-58.31</v>
+      </c>
+      <c r="E169" s="9">
+        <v>5.7</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>-48.01</v>
+        <v>-64.42</v>
       </c>
       <c r="D170" s="7">
-        <v>-64.01000000000001</v>
+        <v>-63.36</v>
       </c>
       <c r="E170" s="9">
-        <v>-16</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-56.59</v>
+        <v>-6.19</v>
       </c>
       <c r="D171" s="7">
-        <v>-64.42</v>
-      </c>
-      <c r="E171" s="9">
-        <v>-7.83</v>
+        <v>-51.01</v>
+      </c>
+      <c r="E171" s="8">
+        <v>-44.82</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>-19.16</v>
+        <v>-33.54</v>
       </c>
       <c r="D172" s="7">
-        <v>-6.19</v>
-      </c>
-      <c r="E172" s="8">
-        <v>12.97</v>
+        <v>-31.22</v>
+      </c>
+      <c r="E172" s="9">
+        <v>2.32</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C173" s="7">
-        <v>-33.97</v>
+        <v>-53.99</v>
       </c>
       <c r="D173" s="7">
-        <v>-33.54</v>
-      </c>
-      <c r="E173" s="8">
-        <v>0.43</v>
+        <v>316.02</v>
+      </c>
+      <c r="E173" s="9">
+        <v>370.01</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C174" s="7">
-        <v>264.95</v>
+        <v>-14.07</v>
       </c>
       <c r="D174" s="7">
-        <v>-53.99</v>
-      </c>
-      <c r="E174" s="9">
-        <v>-318.94</v>
+        <v>-83.98</v>
+      </c>
+      <c r="E174" s="8">
+        <v>-69.91</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C175" s="7">
-        <v>-9.880000000000001</v>
+        <v>-34.86</v>
       </c>
       <c r="D175" s="7">
-        <v>-14.07</v>
+        <v>-33.03</v>
       </c>
       <c r="E175" s="9">
-        <v>-4.19</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C176" s="7">
-        <v>221.54</v>
+        <v>28.9</v>
       </c>
       <c r="D176" s="7">
-        <v>-34.86</v>
-      </c>
-      <c r="E176" s="9">
-        <v>-256.4</v>
+        <v>-12.59</v>
+      </c>
+      <c r="E176" s="8">
+        <v>-41.49</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C177" s="7">
-        <v>-71.51000000000001</v>
+        <v>-93.53</v>
       </c>
       <c r="D177" s="7">
-        <v>28.9</v>
-      </c>
-      <c r="E177" s="8">
-        <v>100.41</v>
+        <v>-88.66</v>
+      </c>
+      <c r="E177" s="9">
+        <v>4.87</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C178" s="7">
-        <v>-75.62</v>
+        <v>26.88</v>
       </c>
       <c r="D178" s="7">
-        <v>-93.53</v>
+        <v>28.91</v>
       </c>
       <c r="E178" s="9">
-        <v>-17.91</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C179" s="7">
-        <v>167.36</v>
+        <v>-0.26</v>
       </c>
       <c r="D179" s="7">
-        <v>26.88</v>
-      </c>
-      <c r="E179" s="9">
-        <v>-140.48</v>
+        <v>-55.59</v>
+      </c>
+      <c r="E179" s="8">
+        <v>-55.33</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C180" s="7">
-        <v>224.38</v>
+        <v>-21.34</v>
       </c>
       <c r="D180" s="7">
-        <v>-0.26</v>
+        <v>-17.47</v>
       </c>
       <c r="E180" s="9">
-        <v>-224.64</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C181" s="7">
-        <v>-43.69</v>
-      </c>
-      <c r="D181" s="7">
-        <v>-21.34</v>
-      </c>
-      <c r="E181" s="8">
-        <v>22.35</v>
+        <v>3.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6478,22 +6464,22 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>51.8</v>
+        <v>52.9</v>
       </c>
       <c r="E2" s="12">
         <v>40</v>
       </c>
       <c r="F2" s="12">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="G2" s="12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H2" s="12">
         <v>52.6</v>
       </c>
       <c r="I2" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -6613,62 +6599,62 @@
         <v>44</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5649000000000001</v>
+        <v>0.5554</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3519</v>
+        <v>0.3502</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3087</v>
+        <v>0.3099</v>
       </c>
       <c r="D2" s="15">
-        <v>0.3019</v>
+        <v>0.2987</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2643</v>
+        <v>0.2647</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1556</v>
+        <v>0.1553</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1408</v>
+        <v>0.1415</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1405</v>
+        <v>0.1403</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1059</v>
+        <v>0.1066</v>
       </c>
       <c r="J2" s="15">
-        <v>0.09039999999999999</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>43</v>
@@ -6691,34 +6677,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0902</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="B4" s="15">
-        <v>0.0901</v>
+        <v>0.0906</v>
       </c>
       <c r="C4" s="15">
-        <v>0.0901</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="D4" s="15">
-        <v>0.0898</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="E4" s="15">
-        <v>0.0774</v>
+        <v>0.07490000000000001</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0591</v>
+        <v>0.0581</v>
       </c>
       <c r="G4" s="15">
-        <v>-0.0021</v>
+        <v>-0.0009</v>
       </c>
       <c r="H4" s="15">
-        <v>-0.0022</v>
+        <v>-0.0039</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.09029999999999999</v>
+        <v>-0.0839</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.3023</v>
+        <v>-0.3019</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="95">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,76 +226,46 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>49.9 → 56.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.6 → 51.4</t>
-  </si>
-  <si>
-    <t>47.6</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>48.4 → 53.0</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>47.8 → 52.2</t>
-  </si>
-  <si>
-    <t>47.8</t>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>56.2</t>
+  </si>
+  <si>
+    <t>48.2 → 54.0</t>
+  </si>
+  <si>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>54.0</t>
+  </si>
+  <si>
+    <t>49.6 → 56.5</t>
+  </si>
+  <si>
+    <t>49.6</t>
+  </si>
+  <si>
+    <t>56.5</t>
+  </si>
+  <si>
+    <t>52.2 → 49.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.2</t>
-  </si>
-  <si>
-    <t>48.4 → 51.1</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>47.1 → 51.5</t>
-  </si>
-  <si>
-    <t>47.1</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>48.1 → 51.1</t>
-  </si>
-  <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>53.2 → 49.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.2</t>
-  </si>
-  <si>
-    <t>49.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -508,8 +478,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1021,10 +991,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>595.0700000000001</v>
+        <v>599.5700000000001</v>
       </c>
       <c r="D2">
-        <v>0.06</v>
+        <v>0.76</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1033,43 +1003,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-6.41</v>
+        <v>-5.71</v>
       </c>
       <c r="H2">
-        <v>14.24</v>
+        <v>15.1</v>
       </c>
       <c r="I2">
-        <v>0.04</v>
+        <v>1.06</v>
       </c>
       <c r="J2">
-        <v>0.61</v>
+        <v>2.05</v>
       </c>
       <c r="K2">
-        <v>4.89</v>
+        <v>6.81</v>
       </c>
       <c r="L2">
-        <v>3.24</v>
+        <v>5.18</v>
       </c>
       <c r="M2">
-        <v>10.66</v>
+        <v>10.78</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>595.37</v>
+        <v>596.63</v>
       </c>
       <c r="Q2">
-        <v>595.83</v>
+        <v>596.22</v>
       </c>
       <c r="R2">
-        <v>596.52</v>
+        <v>596.63</v>
       </c>
       <c r="S2">
-        <v>593.02</v>
+        <v>593.03</v>
       </c>
       <c r="T2">
-        <v>0.35</v>
+        <v>1.1</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1084,34 +1054,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.9</v>
+        <v>56.25</v>
       </c>
       <c r="Z2">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="AA2">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="AB2">
-        <v>-0.34</v>
+        <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>35.89</v>
+        <v>47.41</v>
       </c>
       <c r="AD2">
-        <v>37.78</v>
+        <v>41.69</v>
       </c>
       <c r="AE2">
-        <v>6.94</v>
+        <v>6.86</v>
       </c>
       <c r="AF2">
-        <v>0.39</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AG2">
-        <v>600.6900000000001</v>
+        <v>600.95</v>
       </c>
       <c r="AH2">
-        <v>590.96</v>
+        <v>591.48</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1120,7 +1090,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>41.18</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1131,10 +1101,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>59.61</v>
+        <v>60.04</v>
       </c>
       <c r="D3">
-        <v>0.13</v>
+        <v>0.72</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1143,43 +1113,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.65000000000001</v>
+        <v>-90.58</v>
       </c>
       <c r="H3">
-        <v>14.37</v>
+        <v>15.2</v>
       </c>
       <c r="I3">
-        <v>-0.03</v>
+        <v>1.01</v>
       </c>
       <c r="J3">
-        <v>0.42</v>
+        <v>1.83</v>
       </c>
       <c r="K3">
-        <v>4.97</v>
+        <v>6.76</v>
       </c>
       <c r="L3">
-        <v>-89.66</v>
+        <v>-89.48</v>
       </c>
       <c r="M3">
-        <v>-30.19</v>
+        <v>-30.11</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.64</v>
+        <v>59.76</v>
       </c>
       <c r="Q3">
-        <v>59.76</v>
+        <v>59.79</v>
       </c>
       <c r="R3">
-        <v>59.81</v>
+        <v>59.82</v>
       </c>
       <c r="S3">
-        <v>272.98</v>
+        <v>270.28</v>
       </c>
       <c r="T3">
-        <v>-78.16</v>
+        <v>-77.79000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1194,34 +1164,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>48.24</v>
+        <v>53.98</v>
       </c>
       <c r="Z3">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AA3">
         <v>0.02</v>
       </c>
       <c r="AB3">
-        <v>-0.03</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>28.19</v>
+        <v>43.84</v>
       </c>
       <c r="AD3">
-        <v>31.42</v>
+        <v>35.65</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1694.46</v>
+        <v>35.76</v>
       </c>
       <c r="AG3">
-        <v>60.3</v>
+        <v>60.32</v>
       </c>
       <c r="AH3">
-        <v>59.22</v>
+        <v>59.27</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1230,7 +1200,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>14.48</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1241,10 +1211,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>93.78</v>
+        <v>93.19</v>
       </c>
       <c r="D4">
-        <v>-0.31</v>
+        <v>-0.63</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1253,43 +1223,43 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-13.81</v>
+        <v>-14.36</v>
       </c>
       <c r="H4">
-        <v>6.77</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
-        <v>-0.22</v>
+        <v>0.05</v>
       </c>
       <c r="J4">
-        <v>-2.37</v>
+        <v>-1.15</v>
       </c>
       <c r="K4">
-        <v>-9.82</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L4">
-        <v>4.23</v>
+        <v>4.04</v>
       </c>
       <c r="M4">
-        <v>29.87</v>
+        <v>29.93</v>
       </c>
       <c r="N4">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>93.76000000000001</v>
+        <v>93.77</v>
       </c>
       <c r="Q4">
-        <v>94.13</v>
+        <v>94.09</v>
       </c>
       <c r="R4">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="S4">
-        <v>97.94</v>
+        <v>97.95</v>
       </c>
       <c r="T4">
-        <v>-4.25</v>
+        <v>-4.86</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1304,34 +1274,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.81</v>
+        <v>36.42</v>
       </c>
       <c r="Z4">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
       <c r="AA4">
-        <v>-0.74</v>
+        <v>-0.72</v>
       </c>
       <c r="AB4">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="AC4">
-        <v>85.98999999999999</v>
+        <v>65.33</v>
       </c>
       <c r="AD4">
-        <v>75.12</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="AE4">
         <v>1.65</v>
       </c>
       <c r="AF4">
-        <v>-46.16</v>
+        <v>22.62</v>
       </c>
       <c r="AG4">
-        <v>95.05</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AH4">
-        <v>93.20999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="AI4">
         <v>98.52</v>
@@ -1340,7 +1310,7 @@
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>14.53</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1351,10 +1321,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>51.17</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>0.33</v>
+        <v>-0.33</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1363,43 +1333,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-16.11</v>
+        <v>-16.39</v>
       </c>
       <c r="H5">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="I5">
-        <v>-0.35</v>
+        <v>-0.1</v>
       </c>
       <c r="J5">
-        <v>-3.78</v>
+        <v>-2.73</v>
       </c>
       <c r="K5">
-        <v>-4.48</v>
+        <v>-3.13</v>
       </c>
       <c r="L5">
-        <v>-14.75</v>
+        <v>-14.39</v>
       </c>
       <c r="M5">
-        <v>5.81</v>
+        <v>5.53</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>51.2</v>
+        <v>51.19</v>
       </c>
       <c r="Q5">
-        <v>52.32</v>
+        <v>52.2</v>
       </c>
       <c r="R5">
-        <v>52.61</v>
+        <v>52.57</v>
       </c>
       <c r="S5">
-        <v>54.41</v>
+        <v>54.37</v>
       </c>
       <c r="T5">
-        <v>-5.96</v>
+        <v>-6.21</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1414,34 +1384,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>37.7</v>
+        <v>36.18</v>
       </c>
       <c r="Z5">
-        <v>-0.45</v>
+        <v>-0.47</v>
       </c>
       <c r="AA5">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="AB5">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="AC5">
-        <v>19.94</v>
+        <v>19.97</v>
       </c>
       <c r="AD5">
-        <v>19.99</v>
+        <v>20.7</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>-61.97</v>
+        <v>7.3</v>
       </c>
       <c r="AG5">
-        <v>53.98</v>
+        <v>53.9</v>
       </c>
       <c r="AH5">
-        <v>50.66</v>
+        <v>50.51</v>
       </c>
       <c r="AI5">
         <v>53.66</v>
@@ -1450,7 +1420,7 @@
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>19.39</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1461,55 +1431,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>132.78</v>
+        <v>132.37</v>
       </c>
       <c r="D6">
-        <v>-0.18</v>
+        <v>-0.31</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>82.62</v>
+        <v>83.5</v>
       </c>
       <c r="G6">
-        <v>-9.380000000000001</v>
+        <v>-9.66</v>
       </c>
       <c r="H6">
-        <v>60.71</v>
+        <v>58.53</v>
       </c>
       <c r="I6">
-        <v>5.02</v>
+        <v>5.28</v>
       </c>
       <c r="J6">
-        <v>11.94</v>
+        <v>13.3</v>
       </c>
       <c r="K6">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="L6">
-        <v>60.85</v>
+        <v>60.22</v>
       </c>
       <c r="M6">
-        <v>26.47</v>
+        <v>26.54</v>
       </c>
       <c r="N6">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P6">
-        <v>130.35</v>
+        <v>131.67</v>
       </c>
       <c r="Q6">
-        <v>124.07</v>
+        <v>124.85</v>
       </c>
       <c r="R6">
-        <v>120.39</v>
+        <v>120.56</v>
       </c>
       <c r="S6">
-        <v>120.63</v>
+        <v>120.78</v>
       </c>
       <c r="T6">
-        <v>10.07</v>
+        <v>9.59</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1524,43 +1494,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>78.06</v>
+        <v>75.98</v>
       </c>
       <c r="Z6">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="AA6">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="AB6">
-        <v>0.98</v>
+        <v>0.89</v>
       </c>
       <c r="AC6">
-        <v>97.37</v>
+        <v>89.19</v>
       </c>
       <c r="AD6">
-        <v>96.31</v>
+        <v>95.52</v>
       </c>
       <c r="AE6">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AF6">
-        <v>63.78</v>
+        <v>-9.65</v>
       </c>
       <c r="AG6">
-        <v>134.5</v>
+        <v>135.33</v>
       </c>
       <c r="AH6">
-        <v>113.64</v>
+        <v>114.37</v>
       </c>
       <c r="AI6">
-        <v>127.24</v>
+        <v>127.28</v>
       </c>
       <c r="AJ6" t="s">
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>47.13</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1571,55 +1541,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>137.09</v>
+        <v>136.73</v>
       </c>
       <c r="D7">
-        <v>-0.32</v>
+        <v>-0.26</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>85.23999999999999</v>
+        <v>86.17</v>
       </c>
       <c r="G7">
-        <v>-9.44</v>
+        <v>-9.68</v>
       </c>
       <c r="H7">
-        <v>60.83</v>
+        <v>58.67</v>
       </c>
       <c r="I7">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="J7">
-        <v>11.85</v>
+        <v>13.21</v>
       </c>
       <c r="K7">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="L7">
-        <v>60.83</v>
+        <v>60.41</v>
       </c>
       <c r="M7">
-        <v>35.02</v>
+        <v>34.87</v>
       </c>
       <c r="N7">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>134.68</v>
+        <v>136.01</v>
       </c>
       <c r="Q7">
-        <v>128.27</v>
+        <v>129.07</v>
       </c>
       <c r="R7">
-        <v>124.42</v>
+        <v>124.59</v>
       </c>
       <c r="S7">
-        <v>124.62</v>
+        <v>124.78</v>
       </c>
       <c r="T7">
-        <v>10.01</v>
+        <v>9.58</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1634,43 +1604,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>77.65000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="Z7">
-        <v>3.36</v>
+        <v>3.49</v>
       </c>
       <c r="AA7">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AB7">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="AC7">
-        <v>95.48</v>
+        <v>85.66</v>
       </c>
       <c r="AD7">
-        <v>95.91</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="AE7">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AF7">
-        <v>102.26</v>
+        <v>-45.28</v>
       </c>
       <c r="AG7">
-        <v>139.06</v>
+        <v>139.88</v>
       </c>
       <c r="AH7">
-        <v>117.48</v>
+        <v>118.27</v>
       </c>
       <c r="AI7">
-        <v>126.74</v>
+        <v>127.29</v>
       </c>
       <c r="AJ7" t="s">
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>48.26</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1681,10 +1651,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>472</v>
+        <v>475.86</v>
       </c>
       <c r="D8">
-        <v>-0.51</v>
+        <v>0.82</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1693,43 +1663,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-16.66</v>
+        <v>-15.98</v>
       </c>
       <c r="H8">
-        <v>4.7</v>
+        <v>5.56</v>
       </c>
       <c r="I8">
-        <v>-1.92</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J8">
-        <v>-3.32</v>
+        <v>-2.71</v>
       </c>
       <c r="K8">
-        <v>-9.75</v>
+        <v>-8.23</v>
       </c>
       <c r="L8">
-        <v>6.22</v>
+        <v>5.07</v>
       </c>
       <c r="M8">
-        <v>7.49</v>
+        <v>7.72</v>
       </c>
       <c r="N8">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>478.04</v>
+        <v>477.37</v>
       </c>
       <c r="Q8">
-        <v>485.14</v>
+        <v>484.38</v>
       </c>
       <c r="R8">
-        <v>482.36</v>
+        <v>482.01</v>
       </c>
       <c r="S8">
-        <v>509.96</v>
+        <v>509.7</v>
       </c>
       <c r="T8">
-        <v>-7.44</v>
+        <v>-6.64</v>
       </c>
       <c r="U8" t="s">
         <v>59</v>
@@ -1744,34 +1714,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>35.78</v>
+        <v>41.49</v>
       </c>
       <c r="Z8">
-        <v>-2.74</v>
+        <v>-2.89</v>
       </c>
       <c r="AA8">
-        <v>-1.5</v>
+        <v>-1.78</v>
       </c>
       <c r="AB8">
-        <v>-1.24</v>
+        <v>-1.12</v>
       </c>
       <c r="AC8">
-        <v>20.6</v>
+        <v>12.76</v>
       </c>
       <c r="AD8">
-        <v>24.77</v>
+        <v>20.07</v>
       </c>
       <c r="AE8">
-        <v>10.27</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AF8">
-        <v>52.21</v>
+        <v>-47.47</v>
       </c>
       <c r="AG8">
-        <v>498.89</v>
+        <v>498.41</v>
       </c>
       <c r="AH8">
-        <v>471.4</v>
+        <v>470.35</v>
       </c>
       <c r="AI8">
         <v>502.73</v>
@@ -1780,7 +1750,7 @@
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>26.69</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1791,10 +1761,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>968.17</v>
+        <v>965.09</v>
       </c>
       <c r="D9">
-        <v>0.21</v>
+        <v>-0.32</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1803,43 +1773,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-4.03</v>
+        <v>-4.34</v>
       </c>
       <c r="H9">
-        <v>9.390000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I9">
-        <v>-0.57</v>
+        <v>0.11</v>
       </c>
       <c r="J9">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="K9">
-        <v>-1.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L9">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="M9">
-        <v>15.53</v>
+        <v>15.62</v>
       </c>
       <c r="N9">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P9">
-        <v>966.86</v>
+        <v>967.08</v>
       </c>
       <c r="Q9">
-        <v>971.64</v>
+        <v>971.66</v>
       </c>
       <c r="R9">
-        <v>971.46</v>
+        <v>971.21</v>
       </c>
       <c r="S9">
-        <v>965.34</v>
+        <v>965.3</v>
       </c>
       <c r="T9">
-        <v>0.29</v>
+        <v>-0.02</v>
       </c>
       <c r="U9" t="s">
         <v>59</v>
@@ -1851,37 +1821,37 @@
         <v>59</v>
       </c>
       <c r="X9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>48.26</v>
+        <v>45.51</v>
       </c>
       <c r="Z9">
-        <v>-0.2</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AA9">
-        <v>0.71</v>
+        <v>0.46</v>
       </c>
       <c r="AB9">
-        <v>-0.91</v>
+        <v>-1.01</v>
       </c>
       <c r="AC9">
-        <v>18.28</v>
+        <v>13.72</v>
       </c>
       <c r="AD9">
         <v>16.49</v>
       </c>
       <c r="AE9">
-        <v>10.94</v>
+        <v>10.87</v>
       </c>
       <c r="AF9">
-        <v>-23.3</v>
+        <v>-17.49</v>
       </c>
       <c r="AG9">
-        <v>982.1</v>
+        <v>982.08</v>
       </c>
       <c r="AH9">
-        <v>961.1900000000001</v>
+        <v>961.23</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1890,7 +1860,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>16.87</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1901,10 +1871,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>33.93</v>
+        <v>33.79</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>-0.41</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1913,43 +1883,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-21.4</v>
+        <v>-21.73</v>
       </c>
       <c r="H10">
-        <v>18.55</v>
+        <v>18.06</v>
       </c>
       <c r="I10">
-        <v>0.71</v>
+        <v>0.36</v>
       </c>
       <c r="J10">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>5.93</v>
+        <v>5.04</v>
       </c>
       <c r="L10">
-        <v>-12.71</v>
+        <v>-12.48</v>
       </c>
       <c r="M10">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="N10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P10">
-        <v>33.83</v>
+        <v>33.86</v>
       </c>
       <c r="Q10">
-        <v>34.45</v>
+        <v>34.41</v>
       </c>
       <c r="R10">
-        <v>32.46</v>
+        <v>32.49</v>
       </c>
       <c r="S10">
-        <v>35.59</v>
+        <v>35.56</v>
       </c>
       <c r="T10">
-        <v>-4.66</v>
+        <v>-4.98</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1964,34 +1934,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>52.63</v>
+        <v>50.87</v>
       </c>
       <c r="Z10">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AA10">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AB10">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="AC10">
-        <v>7.65</v>
+        <v>8.41</v>
       </c>
       <c r="AD10">
-        <v>7.55</v>
+        <v>8.27</v>
       </c>
       <c r="AE10">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="AF10">
-        <v>-58.31</v>
+        <v>-78.19</v>
       </c>
       <c r="AG10">
         <v>35.42</v>
       </c>
       <c r="AH10">
-        <v>33.48</v>
+        <v>33.4</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -2000,7 +1970,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>29.36</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2011,10 +1981,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>33.92</v>
+        <v>33.76</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -2023,43 +1993,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-21.64</v>
+        <v>-22.01</v>
       </c>
       <c r="H11">
-        <v>18.48</v>
+        <v>17.92</v>
       </c>
       <c r="I11">
-        <v>1.01</v>
+        <v>0.24</v>
       </c>
       <c r="J11">
-        <v>3.73</v>
+        <v>-0.03</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>4.62</v>
       </c>
       <c r="L11">
-        <v>-13.05</v>
+        <v>-12.81</v>
       </c>
       <c r="M11">
-        <v>-0.39</v>
+        <v>-0.54</v>
       </c>
       <c r="N11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P11">
-        <v>33.89</v>
+        <v>33.91</v>
       </c>
       <c r="Q11">
-        <v>34.48</v>
+        <v>34.44</v>
       </c>
       <c r="R11">
-        <v>32.47</v>
+        <v>32.51</v>
       </c>
       <c r="S11">
-        <v>35.65</v>
+        <v>35.63</v>
       </c>
       <c r="T11">
-        <v>-4.86</v>
+        <v>-5.24</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -2074,34 +2044,34 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>52.12</v>
+        <v>50.15</v>
       </c>
       <c r="Z11">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="AA11">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AB11">
         <v>-0.22</v>
       </c>
       <c r="AC11">
+        <v>11.99</v>
+      </c>
+      <c r="AD11">
         <v>14.37</v>
       </c>
-      <c r="AD11">
-        <v>14.78</v>
-      </c>
       <c r="AE11">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="AF11">
-        <v>-63.36</v>
+        <v>-56.6</v>
       </c>
       <c r="AG11">
-        <v>35.48</v>
+        <v>35.49</v>
       </c>
       <c r="AH11">
-        <v>33.49</v>
+        <v>33.4</v>
       </c>
       <c r="AI11">
         <v>32.2</v>
@@ -2110,7 +2080,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>20.15</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2121,10 +2091,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>804.14</v>
+        <v>806.9</v>
       </c>
       <c r="D12">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2133,43 +2103,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-0.6</v>
+        <v>-0.26</v>
       </c>
       <c r="H12">
-        <v>23.35</v>
+        <v>23.78</v>
       </c>
       <c r="I12">
-        <v>-0.22</v>
+        <v>0.88</v>
       </c>
       <c r="J12">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>5.08</v>
       </c>
       <c r="L12">
-        <v>10.2</v>
+        <v>11.26</v>
       </c>
       <c r="M12">
-        <v>14.15</v>
+        <v>14.08</v>
       </c>
       <c r="N12">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P12">
-        <v>801.46</v>
+        <v>802.87</v>
       </c>
       <c r="Q12">
-        <v>802.36</v>
+        <v>803.53</v>
       </c>
       <c r="R12">
-        <v>788.34</v>
+        <v>788.88</v>
       </c>
       <c r="S12">
-        <v>750.96</v>
+        <v>751.25</v>
       </c>
       <c r="T12">
-        <v>7.08</v>
+        <v>7.41</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -2184,34 +2154,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>59.3</v>
+        <v>62.08</v>
       </c>
       <c r="Z12">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="AA12">
-        <v>6.44</v>
+        <v>6.14</v>
       </c>
       <c r="AB12">
-        <v>-1.45</v>
+        <v>-1.18</v>
       </c>
       <c r="AC12">
-        <v>9.380000000000001</v>
+        <v>24.31</v>
       </c>
       <c r="AD12">
-        <v>8.01</v>
+        <v>13.68</v>
       </c>
       <c r="AE12">
-        <v>13.1</v>
+        <v>12.97</v>
       </c>
       <c r="AF12">
-        <v>-51.01</v>
+        <v>-24.51</v>
       </c>
       <c r="AG12">
-        <v>816.85</v>
+        <v>815.1</v>
       </c>
       <c r="AH12">
-        <v>787.87</v>
+        <v>791.97</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2220,7 +2190,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>39.58</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2231,10 +2201,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>276.94</v>
+        <v>277.02</v>
       </c>
       <c r="D13">
-        <v>0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2243,43 +2213,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-6.93</v>
+        <v>-6.9</v>
       </c>
       <c r="H13">
-        <v>9.27</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I13">
-        <v>0.3</v>
+        <v>0.87</v>
       </c>
       <c r="J13">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="K13">
-        <v>2.21</v>
+        <v>3.45</v>
       </c>
       <c r="L13">
-        <v>-2.16</v>
+        <v>-1.33</v>
       </c>
       <c r="M13">
         <v>9.06</v>
       </c>
       <c r="N13">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P13">
-        <v>276.15</v>
+        <v>276.63</v>
       </c>
       <c r="Q13">
-        <v>277.92</v>
+        <v>277.98</v>
       </c>
       <c r="R13">
-        <v>275.41</v>
+        <v>275.49</v>
       </c>
       <c r="S13">
-        <v>279.43</v>
+        <v>279.37</v>
       </c>
       <c r="T13">
-        <v>-0.89</v>
+        <v>-0.84</v>
       </c>
       <c r="U13" t="s">
         <v>59</v>
@@ -2294,34 +2264,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>51.36</v>
+        <v>51.64</v>
       </c>
       <c r="Z13">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AA13">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="AB13">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
       <c r="AC13">
-        <v>29.94</v>
+        <v>32.31</v>
       </c>
       <c r="AD13">
-        <v>26.34</v>
+        <v>30.04</v>
       </c>
       <c r="AE13">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AF13">
-        <v>-31.22</v>
+        <v>-16.27</v>
       </c>
       <c r="AG13">
-        <v>281.39</v>
+        <v>281.34</v>
       </c>
       <c r="AH13">
-        <v>274.45</v>
+        <v>274.62</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2330,7 +2300,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>9.039999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2341,10 +2311,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>269.9</v>
+        <v>269.92</v>
       </c>
       <c r="D14">
-        <v>0.46</v>
+        <v>0.01</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2353,31 +2323,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-6.81</v>
+        <v>-6.8</v>
       </c>
       <c r="H14">
         <v>9.470000000000001</v>
       </c>
       <c r="I14">
-        <v>0.49</v>
+        <v>0.92</v>
       </c>
       <c r="J14">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="K14">
-        <v>2.49</v>
+        <v>3.69</v>
       </c>
       <c r="M14">
-        <v>-8.390000000000001</v>
+        <v>-8.35</v>
       </c>
       <c r="P14">
-        <v>268.85</v>
+        <v>269.35</v>
       </c>
       <c r="Q14">
-        <v>270.38</v>
+        <v>270.44</v>
       </c>
       <c r="R14">
-        <v>268.04</v>
+        <v>268.13</v>
       </c>
       <c r="U14" t="s">
         <v>59</v>
@@ -2389,34 +2359,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>53.03</v>
+        <v>53.1</v>
       </c>
       <c r="Z14">
         <v>0.39</v>
       </c>
       <c r="AA14">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="AB14">
-        <v>-0.38</v>
+        <v>-0.31</v>
       </c>
       <c r="AC14">
-        <v>30.93</v>
+        <v>37.49</v>
       </c>
       <c r="AD14">
-        <v>26.17</v>
+        <v>31.99</v>
       </c>
       <c r="AE14">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AF14">
-        <v>316.02</v>
+        <v>-77.22</v>
       </c>
       <c r="AG14">
-        <v>273.47</v>
+        <v>273.43</v>
       </c>
       <c r="AH14">
-        <v>267.28</v>
+        <v>267.44</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2425,7 +2395,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>55</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2436,10 +2406,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>264.78</v>
+        <v>264.05</v>
       </c>
       <c r="D15">
-        <v>0.49</v>
+        <v>-0.28</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2448,43 +2418,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-6.87</v>
+        <v>-7.13</v>
       </c>
       <c r="H15">
-        <v>9.640000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="I15">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="J15">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="K15">
-        <v>2.29</v>
+        <v>3.46</v>
       </c>
       <c r="L15">
-        <v>-2.11</v>
+        <v>-1.6</v>
       </c>
       <c r="M15">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="N15">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="P15">
-        <v>263.73</v>
+        <v>264.1</v>
       </c>
       <c r="Q15">
-        <v>265.51</v>
+        <v>265.52</v>
       </c>
       <c r="R15">
-        <v>263.07</v>
+        <v>263.14</v>
       </c>
       <c r="S15">
-        <v>266.76</v>
+        <v>266.7</v>
       </c>
       <c r="T15">
-        <v>-0.74</v>
+        <v>-0.99</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -2499,34 +2469,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>52.21</v>
+        <v>49.65</v>
       </c>
       <c r="Z15">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AA15">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="AB15">
-        <v>-0.41</v>
+        <v>-0.38</v>
       </c>
       <c r="AC15">
-        <v>31.74</v>
+        <v>32.32</v>
       </c>
       <c r="AD15">
-        <v>26.54</v>
+        <v>30.51</v>
       </c>
       <c r="AE15">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="AF15">
-        <v>-83.98</v>
+        <v>-38.14</v>
       </c>
       <c r="AG15">
-        <v>268.89</v>
+        <v>268.88</v>
       </c>
       <c r="AH15">
-        <v>262.13</v>
+        <v>262.17</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2535,7 +2505,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>43.72</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2546,10 +2516,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>275.46</v>
+        <v>275.6</v>
       </c>
       <c r="D16">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2558,43 +2528,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-6.93</v>
+        <v>-6.89</v>
       </c>
       <c r="H16">
-        <v>9.300000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I16">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="J16">
         <v>1.22</v>
       </c>
       <c r="K16">
-        <v>2.21</v>
+        <v>3.61</v>
       </c>
       <c r="L16">
-        <v>-2.18</v>
+        <v>-1.37</v>
       </c>
       <c r="M16">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="N16">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P16">
-        <v>274.78</v>
+        <v>275.24</v>
       </c>
       <c r="Q16">
-        <v>276.5</v>
+        <v>276.56</v>
       </c>
       <c r="R16">
-        <v>274.02</v>
+        <v>274.1</v>
       </c>
       <c r="S16">
-        <v>278.04</v>
+        <v>277.98</v>
       </c>
       <c r="T16">
-        <v>-0.93</v>
+        <v>-0.86</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -2609,34 +2579,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>51.15</v>
+        <v>51.67</v>
       </c>
       <c r="Z16">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="AA16">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="AB16">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="AC16">
-        <v>29.11</v>
+        <v>31.52</v>
       </c>
       <c r="AD16">
-        <v>25.67</v>
+        <v>29.44</v>
       </c>
       <c r="AE16">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="AF16">
-        <v>-33.03</v>
+        <v>-66.22</v>
       </c>
       <c r="AG16">
-        <v>279.98</v>
+        <v>279.92</v>
       </c>
       <c r="AH16">
-        <v>273.03</v>
+        <v>273.2</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2645,7 +2615,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>42.85</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2656,10 +2626,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>95.97</v>
+        <v>96.91</v>
       </c>
       <c r="D17">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2668,43 +2638,43 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-12.65</v>
+        <v>-11.8</v>
       </c>
       <c r="H17">
-        <v>27.6</v>
+        <v>28.85</v>
       </c>
       <c r="I17">
-        <v>-0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J17">
-        <v>2.62</v>
+        <v>4.51</v>
       </c>
       <c r="K17">
-        <v>4.21</v>
+        <v>6.26</v>
       </c>
       <c r="L17">
-        <v>21.68</v>
+        <v>24.34</v>
       </c>
       <c r="M17">
-        <v>30.99</v>
+        <v>31.45</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>95.87</v>
+        <v>96.02</v>
       </c>
       <c r="Q17">
-        <v>95.98</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="R17">
-        <v>95.22</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="S17">
-        <v>95.81999999999999</v>
+        <v>95.84</v>
       </c>
       <c r="T17">
-        <v>0.16</v>
+        <v>1.12</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -2719,34 +2689,34 @@
         <v>2</v>
       </c>
       <c r="Y17">
-        <v>51.5</v>
+        <v>55.95</v>
       </c>
       <c r="Z17">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="AA17">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="AB17">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="AC17">
-        <v>7.91</v>
+        <v>23.76</v>
       </c>
       <c r="AD17">
-        <v>6.35</v>
+        <v>11.14</v>
       </c>
       <c r="AE17">
         <v>1.99</v>
       </c>
       <c r="AF17">
-        <v>-12.59</v>
+        <v>-19.06</v>
       </c>
       <c r="AG17">
-        <v>99.23</v>
+        <v>99.12</v>
       </c>
       <c r="AH17">
-        <v>92.73999999999999</v>
+        <v>93.23</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2755,7 +2725,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>23.69</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2766,10 +2736,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>281.14</v>
+        <v>283.9</v>
       </c>
       <c r="D18">
-        <v>-0.45</v>
+        <v>0.98</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2778,43 +2748,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.19</v>
+        <v>-4.26</v>
       </c>
       <c r="H18">
-        <v>14.48</v>
+        <v>15.61</v>
       </c>
       <c r="I18">
-        <v>1.13</v>
+        <v>1.82</v>
       </c>
       <c r="J18">
-        <v>0.51</v>
+        <v>1.93</v>
       </c>
       <c r="K18">
-        <v>3.86</v>
+        <v>5.62</v>
       </c>
       <c r="L18">
-        <v>2.34</v>
+        <v>4.34</v>
       </c>
       <c r="M18">
-        <v>9.029999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>280.81</v>
+        <v>281.83</v>
       </c>
       <c r="Q18">
-        <v>281.18</v>
+        <v>281.31</v>
       </c>
       <c r="R18">
-        <v>283.58</v>
+        <v>283.59</v>
       </c>
       <c r="S18">
         <v>281.3</v>
       </c>
       <c r="T18">
-        <v>-0.06</v>
+        <v>0.92</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2826,37 +2796,37 @@
         <v>58</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18">
-        <v>49.57</v>
+        <v>56.54</v>
       </c>
       <c r="Z18">
-        <v>-0.45</v>
+        <v>-0.17</v>
       </c>
       <c r="AA18">
-        <v>-0.6</v>
+        <v>-0.51</v>
       </c>
       <c r="AB18">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="AC18">
         <v>90.38</v>
       </c>
       <c r="AD18">
-        <v>73.33</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="AE18">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="AF18">
-        <v>-88.66</v>
+        <v>112.73</v>
       </c>
       <c r="AG18">
-        <v>284.81</v>
+        <v>285.13</v>
       </c>
       <c r="AH18">
-        <v>277.56</v>
+        <v>277.48</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2865,7 +2835,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>21.44</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2876,55 +2846,55 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>234.57</v>
+        <v>235.87</v>
       </c>
       <c r="D19">
-        <v>-1.17</v>
+        <v>0.55</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>112.61</v>
+        <v>114.56</v>
       </c>
       <c r="G19">
-        <v>-34.52</v>
+        <v>-34.16</v>
       </c>
       <c r="H19">
-        <v>108.3</v>
+        <v>105.89</v>
       </c>
       <c r="I19">
-        <v>3.26</v>
+        <v>6.36</v>
       </c>
       <c r="J19">
-        <v>7.45</v>
+        <v>11.56</v>
       </c>
       <c r="K19">
-        <v>-8.26</v>
+        <v>-7.61</v>
       </c>
       <c r="L19">
-        <v>109.91</v>
+        <v>109.46</v>
       </c>
       <c r="M19">
-        <v>55.54</v>
+        <v>55.85</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>232.54</v>
+        <v>235.36</v>
       </c>
       <c r="Q19">
-        <v>223.93</v>
+        <v>225.13</v>
       </c>
       <c r="R19">
-        <v>220.78</v>
+        <v>220.69</v>
       </c>
       <c r="S19">
-        <v>228.87</v>
+        <v>229.31</v>
       </c>
       <c r="T19">
-        <v>2.49</v>
+        <v>2.86</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2939,34 +2909,34 @@
         <v>2</v>
       </c>
       <c r="Y19">
-        <v>61.54</v>
+        <v>62.74</v>
       </c>
       <c r="Z19">
-        <v>3.99</v>
+        <v>4.21</v>
       </c>
       <c r="AA19">
-        <v>2.43</v>
+        <v>2.79</v>
       </c>
       <c r="AB19">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AC19">
-        <v>86.51000000000001</v>
+        <v>78.03</v>
       </c>
       <c r="AD19">
-        <v>82.43000000000001</v>
+        <v>84.78</v>
       </c>
       <c r="AE19">
-        <v>5.93</v>
+        <v>5.76</v>
       </c>
       <c r="AF19">
-        <v>28.91</v>
+        <v>-42.15</v>
       </c>
       <c r="AG19">
-        <v>241.29</v>
+        <v>242.29</v>
       </c>
       <c r="AH19">
-        <v>206.57</v>
+        <v>207.96</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2975,7 +2945,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>42.65</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2986,10 +2956,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>261.66</v>
+        <v>261.7</v>
       </c>
       <c r="D20">
-        <v>0.31</v>
+        <v>0.02</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2998,43 +2968,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-6.95</v>
+        <v>-6.94</v>
       </c>
       <c r="H20">
-        <v>9.32</v>
+        <v>9.34</v>
       </c>
       <c r="I20">
-        <v>0.28</v>
+        <v>0.84</v>
       </c>
       <c r="J20">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="K20">
-        <v>2.26</v>
+        <v>3.49</v>
       </c>
       <c r="L20">
-        <v>-2.19</v>
+        <v>-1.41</v>
       </c>
       <c r="M20">
-        <v>9.029999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="N20">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P20">
-        <v>260.96</v>
+        <v>261.4</v>
       </c>
       <c r="Q20">
-        <v>262.63</v>
+        <v>262.69</v>
       </c>
       <c r="R20">
-        <v>260.33</v>
+        <v>260.4</v>
       </c>
       <c r="S20">
-        <v>264.14</v>
+        <v>264.08</v>
       </c>
       <c r="T20">
-        <v>-0.9399999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -3049,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>51.13</v>
+        <v>51.28</v>
       </c>
       <c r="Z20">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="AA20">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="AB20">
-        <v>-0.42</v>
+        <v>-0.36</v>
       </c>
       <c r="AC20">
-        <v>30.9</v>
+        <v>32.82</v>
       </c>
       <c r="AD20">
-        <v>26.73</v>
+        <v>30.71</v>
       </c>
       <c r="AE20">
-        <v>4.88</v>
+        <v>4.74</v>
       </c>
       <c r="AF20">
-        <v>-55.59</v>
+        <v>-50.08</v>
       </c>
       <c r="AG20">
-        <v>265.88</v>
+        <v>265.82</v>
       </c>
       <c r="AH20">
-        <v>259.39</v>
+        <v>259.56</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3085,7 +3055,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>37.22</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3096,10 +3066,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>795.3200000000001</v>
+        <v>802</v>
       </c>
       <c r="D21">
-        <v>0.3</v>
+        <v>0.84</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3108,43 +3078,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-0.99</v>
+        <v>-0.16</v>
       </c>
       <c r="H21">
-        <v>23.75</v>
+        <v>24.79</v>
       </c>
       <c r="I21">
-        <v>-0.42</v>
+        <v>1.11</v>
       </c>
       <c r="J21">
-        <v>2.24</v>
+        <v>3.72</v>
       </c>
       <c r="K21">
-        <v>3.67</v>
+        <v>5.08</v>
       </c>
       <c r="L21">
-        <v>9.779999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="M21">
-        <v>14.03</v>
+        <v>14.13</v>
       </c>
       <c r="N21">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P21">
-        <v>794.3200000000001</v>
+        <v>796.09</v>
       </c>
       <c r="Q21">
-        <v>794.8</v>
+        <v>795.91</v>
       </c>
       <c r="R21">
-        <v>781.16</v>
+        <v>781.77</v>
       </c>
       <c r="S21">
-        <v>744.1</v>
+        <v>744.41</v>
       </c>
       <c r="T21">
-        <v>6.88</v>
+        <v>7.74</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -3159,34 +3129,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>56.5</v>
+        <v>62.47</v>
       </c>
       <c r="Z21">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="AA21">
-        <v>6.33</v>
+        <v>6.08</v>
       </c>
       <c r="AB21">
-        <v>-1.46</v>
+        <v>-1.02</v>
       </c>
       <c r="AC21">
-        <v>5.93</v>
+        <v>25.93</v>
       </c>
       <c r="AD21">
-        <v>6.77</v>
+        <v>13.01</v>
       </c>
       <c r="AE21">
-        <v>11.84</v>
+        <v>11.64</v>
       </c>
       <c r="AF21">
-        <v>-17.47</v>
+        <v>-25.34</v>
       </c>
       <c r="AG21">
-        <v>808.23</v>
+        <v>807.6799999999999</v>
       </c>
       <c r="AH21">
-        <v>781.37</v>
+        <v>784.14</v>
       </c>
       <c r="AI21">
         <v>773.79</v>
@@ -3195,7 +3165,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>19.97</v>
+        <v>23.13</v>
       </c>
     </row>
   </sheetData>
@@ -3376,2219 +3346,2204 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="A6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>82</v>
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2.05</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>91</v>
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-2.37</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-1.15</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.22</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-3.78</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-2.73</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>96</v>
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>11.94</v>
+      </c>
+      <c r="D14" s="7">
+        <v>13.3</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.36</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>1.18</v>
+        <v>11.85</v>
       </c>
       <c r="D15" s="7">
-        <v>0.61</v>
+        <v>13.21</v>
       </c>
       <c r="E15" s="8">
-        <v>-0.57</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>1.07</v>
+        <v>-3.32</v>
       </c>
       <c r="D16" s="7">
-        <v>0.42</v>
+        <v>-2.71</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.65</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-2.24</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="7">
-        <v>-2.37</v>
+        <v>0.53</v>
       </c>
       <c r="E17" s="8">
-        <v>-0.13</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-3.21</v>
+        <v>3.63</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.78</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.57</v>
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-3.63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>12.81</v>
+        <v>3.73</v>
       </c>
       <c r="D19" s="7">
-        <v>11.94</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.87</v>
+        <v>-0.03</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-3.76</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>12.92</v>
+        <v>2.64</v>
       </c>
       <c r="D20" s="7">
-        <v>11.85</v>
+        <v>3.5</v>
       </c>
       <c r="E20" s="8">
-        <v>-1.07</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-2.04</v>
+        <v>1.22</v>
       </c>
       <c r="D21" s="7">
-        <v>-3.32</v>
+        <v>1.28</v>
       </c>
       <c r="E21" s="8">
-        <v>-1.28</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="D22" s="7">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.42</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>5.75</v>
+        <v>1.35</v>
       </c>
       <c r="D23" s="7">
-        <v>3.63</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.12</v>
+        <v>1.27</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>6</v>
+        <v>2.62</v>
       </c>
       <c r="D24" s="7">
-        <v>3.73</v>
+        <v>4.51</v>
       </c>
       <c r="E24" s="8">
-        <v>-2.27</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>3.05</v>
+        <v>0.51</v>
       </c>
       <c r="D25" s="7">
-        <v>2.64</v>
+        <v>1.93</v>
       </c>
       <c r="E25" s="8">
-        <v>-0.41</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>1.72</v>
+        <v>7.45</v>
       </c>
       <c r="D26" s="7">
-        <v>1.22</v>
+        <v>11.56</v>
       </c>
       <c r="E26" s="8">
-        <v>-0.5</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>1.78</v>
+        <v>1.15</v>
       </c>
       <c r="D27" s="7">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.45</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="D28" s="7">
-        <v>1.35</v>
+        <v>3.72</v>
       </c>
       <c r="E28" s="8">
-        <v>-0.58</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="7">
-        <v>1.83</v>
+        <v>0.04</v>
       </c>
       <c r="D29" s="7">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="E29" s="8">
-        <v>-0.61</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>1.83</v>
+        <v>-0.03</v>
       </c>
       <c r="D30" s="7">
-        <v>2.62</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0.79</v>
+        <v>1.01</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.04</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>1.42</v>
+        <v>-0.22</v>
       </c>
       <c r="D31" s="7">
-        <v>0.51</v>
+        <v>0.05</v>
       </c>
       <c r="E31" s="8">
-        <v>-0.91</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>9.890000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="D32" s="7">
-        <v>7.45</v>
+        <v>-0.1</v>
       </c>
       <c r="E32" s="8">
-        <v>-2.44</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>1.79</v>
+        <v>5.02</v>
       </c>
       <c r="D33" s="7">
-        <v>1.15</v>
+        <v>5.28</v>
       </c>
       <c r="E33" s="8">
-        <v>-0.64</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>3.02</v>
+        <v>4.88</v>
       </c>
       <c r="D34" s="7">
-        <v>2.24</v>
+        <v>5.12</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.78</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>-0.28</v>
+        <v>-1.92</v>
       </c>
       <c r="D35" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.32</v>
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.23</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-0.4</v>
+        <v>-0.57</v>
       </c>
       <c r="D36" s="7">
-        <v>-0.03</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.37</v>
+        <v>0.11</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>0.23</v>
+        <v>0.71</v>
       </c>
       <c r="D37" s="7">
-        <v>-0.22</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.45</v>
+        <v>0.36</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>-1.89</v>
+        <v>1.01</v>
       </c>
       <c r="D38" s="7">
-        <v>-0.35</v>
+        <v>0.24</v>
       </c>
       <c r="E38" s="9">
-        <v>1.54</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>6.31</v>
+        <v>-0.22</v>
       </c>
       <c r="D39" s="7">
-        <v>5.02</v>
+        <v>0.88</v>
       </c>
       <c r="E39" s="8">
-        <v>-1.29</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>5.29</v>
+        <v>0.3</v>
       </c>
       <c r="D40" s="7">
-        <v>4.88</v>
+        <v>0.87</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.41</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-1.7</v>
+        <v>0.49</v>
       </c>
       <c r="D41" s="7">
-        <v>-1.92</v>
+        <v>0.92</v>
       </c>
       <c r="E41" s="8">
-        <v>-0.22</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>-1.11</v>
+        <v>0.43</v>
       </c>
       <c r="D42" s="7">
-        <v>-0.57</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.54</v>
+        <v>0.71</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>-2.65</v>
+        <v>0.31</v>
       </c>
       <c r="D43" s="7">
-        <v>0.71</v>
-      </c>
-      <c r="E43" s="9">
-        <v>3.36</v>
+        <v>0.85</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.54</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>-2.56</v>
+        <v>-0.57</v>
       </c>
       <c r="D44" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="E44" s="9">
-        <v>3.57</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.38</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>-0.97</v>
+        <v>1.13</v>
       </c>
       <c r="D45" s="7">
-        <v>-0.22</v>
-      </c>
-      <c r="E45" s="9">
-        <v>0.75</v>
+        <v>1.82</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>-0.89</v>
+        <v>3.26</v>
       </c>
       <c r="D46" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.19</v>
+        <v>6.36</v>
+      </c>
+      <c r="E46" s="8">
+        <v>3.1</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="7">
-        <v>-0.6899999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="D47" s="7">
-        <v>0.49</v>
-      </c>
-      <c r="E47" s="9">
-        <v>1.18</v>
+        <v>0.84</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="7">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="D48" s="7">
-        <v>0.43</v>
-      </c>
-      <c r="E48" s="9">
-        <v>1.27</v>
+        <v>1.11</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.53</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C49" s="7">
-        <v>-0.77</v>
+        <v>3.24</v>
       </c>
       <c r="D49" s="7">
-        <v>0.31</v>
-      </c>
-      <c r="E49" s="9">
-        <v>1.08</v>
+        <v>5.18</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.94</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>-2.45</v>
+        <v>-89.66</v>
       </c>
       <c r="D50" s="7">
-        <v>-0.57</v>
-      </c>
-      <c r="E50" s="9">
-        <v>1.88</v>
+        <v>-89.48</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.18</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>0.95</v>
+        <v>4.23</v>
       </c>
       <c r="D51" s="7">
-        <v>1.13</v>
+        <v>4.04</v>
       </c>
       <c r="E51" s="9">
-        <v>0.18</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>4.71</v>
+        <v>-14.75</v>
       </c>
       <c r="D52" s="7">
-        <v>3.26</v>
+        <v>-14.39</v>
       </c>
       <c r="E52" s="8">
-        <v>-1.45</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>-0.84</v>
+        <v>60.85</v>
       </c>
       <c r="D53" s="7">
-        <v>0.28</v>
+        <v>60.22</v>
       </c>
       <c r="E53" s="9">
-        <v>1.12</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>-0.84</v>
+        <v>60.83</v>
       </c>
       <c r="D54" s="7">
+        <v>60.41</v>
+      </c>
+      <c r="E54" s="9">
         <v>-0.42</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.42</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>3.35</v>
+        <v>6.22</v>
       </c>
       <c r="D55" s="7">
-        <v>3.24</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.11</v>
+        <v>5.07</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>-89.67</v>
+        <v>2.12</v>
       </c>
       <c r="D56" s="7">
-        <v>-89.66</v>
-      </c>
-      <c r="E56" s="9">
-        <v>0.01</v>
+        <v>2.38</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>4.13</v>
+        <v>-12.71</v>
       </c>
       <c r="D57" s="7">
-        <v>4.23</v>
-      </c>
-      <c r="E57" s="9">
-        <v>0.1</v>
+        <v>-12.48</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>-15.49</v>
+        <v>-13.05</v>
       </c>
       <c r="D58" s="7">
-        <v>-14.75</v>
-      </c>
-      <c r="E58" s="9">
-        <v>0.74</v>
+        <v>-12.81</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>62.06</v>
+        <v>10.2</v>
       </c>
       <c r="D59" s="7">
-        <v>60.85</v>
+        <v>11.26</v>
       </c>
       <c r="E59" s="8">
-        <v>-1.21</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>62.3</v>
+        <v>-2.16</v>
       </c>
       <c r="D60" s="7">
-        <v>60.83</v>
+        <v>-1.33</v>
       </c>
       <c r="E60" s="8">
-        <v>-1.47</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>7.53</v>
+        <v>-2.11</v>
       </c>
       <c r="D61" s="7">
-        <v>6.22</v>
+        <v>-1.6</v>
       </c>
       <c r="E61" s="8">
-        <v>-1.31</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>1.85</v>
+        <v>-2.18</v>
       </c>
       <c r="D62" s="7">
-        <v>2.12</v>
-      </c>
-      <c r="E62" s="9">
-        <v>0.27</v>
+        <v>-1.37</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>-12.79</v>
+        <v>21.68</v>
       </c>
       <c r="D63" s="7">
-        <v>-12.71</v>
-      </c>
-      <c r="E63" s="9">
-        <v>0.08</v>
+        <v>24.34</v>
+      </c>
+      <c r="E63" s="8">
+        <v>2.66</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>-12.89</v>
+        <v>2.34</v>
       </c>
       <c r="D64" s="7">
-        <v>-13.05</v>
+        <v>4.34</v>
       </c>
       <c r="E64" s="8">
-        <v>-0.16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>9.25</v>
+        <v>109.91</v>
       </c>
       <c r="D65" s="7">
-        <v>10.2</v>
+        <v>109.46</v>
       </c>
       <c r="E65" s="9">
-        <v>0.95</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>-2.35</v>
+        <v>-2.19</v>
       </c>
       <c r="D66" s="7">
-        <v>-2.16</v>
-      </c>
-      <c r="E66" s="9">
-        <v>0.19</v>
+        <v>-1.41</v>
+      </c>
+      <c r="E66" s="8">
+        <v>0.78</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>-2.28</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D67" s="7">
-        <v>-2.11</v>
-      </c>
-      <c r="E67" s="9">
-        <v>0.17</v>
+        <v>11.44</v>
+      </c>
+      <c r="E67" s="8">
+        <v>1.66</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" s="7">
-        <v>-2.26</v>
+        <v>4.89</v>
       </c>
       <c r="D68" s="7">
-        <v>-2.18</v>
-      </c>
-      <c r="E68" s="9">
-        <v>0.08</v>
+        <v>6.81</v>
+      </c>
+      <c r="E68" s="8">
+        <v>1.92</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>20.13</v>
+        <v>4.97</v>
       </c>
       <c r="D69" s="7">
-        <v>21.68</v>
-      </c>
-      <c r="E69" s="9">
-        <v>1.55</v>
+        <v>6.76</v>
+      </c>
+      <c r="E69" s="8">
+        <v>1.79</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>2.98</v>
+        <v>-9.82</v>
       </c>
       <c r="D70" s="7">
-        <v>2.34</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="E70" s="8">
-        <v>-0.64</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>116.47</v>
+        <v>-4.48</v>
       </c>
       <c r="D71" s="7">
-        <v>109.91</v>
+        <v>-3.13</v>
       </c>
       <c r="E71" s="8">
-        <v>-6.56</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>-2.33</v>
+        <v>2.9</v>
       </c>
       <c r="D72" s="7">
-        <v>-2.19</v>
+        <v>2.89</v>
       </c>
       <c r="E72" s="9">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>9.41</v>
+        <v>2.8</v>
       </c>
       <c r="D73" s="7">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="E73" s="9">
-        <v>0.37</v>
+        <v>2.95</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="7">
-        <v>4.83</v>
+        <v>-9.75</v>
       </c>
       <c r="D74" s="7">
-        <v>4.89</v>
-      </c>
-      <c r="E74" s="9">
-        <v>0.06</v>
+        <v>-8.23</v>
+      </c>
+      <c r="E74" s="8">
+        <v>1.52</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>4.82</v>
+        <v>-1.08</v>
       </c>
       <c r="D75" s="7">
-        <v>4.97</v>
-      </c>
-      <c r="E75" s="9">
-        <v>0.15</v>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E75" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>-9.539999999999999</v>
+        <v>5.93</v>
       </c>
       <c r="D76" s="7">
-        <v>-9.82</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.28</v>
+        <v>5.04</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>-4.8</v>
+        <v>5.8</v>
       </c>
       <c r="D77" s="7">
-        <v>-4.48</v>
+        <v>4.62</v>
       </c>
       <c r="E77" s="9">
-        <v>0.32</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="D78" s="7">
-        <v>2.9</v>
+        <v>5.08</v>
       </c>
       <c r="E78" s="8">
-        <v>-0.18</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>3.13</v>
+        <v>2.21</v>
       </c>
       <c r="D79" s="7">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="E79" s="8">
-        <v>-0.33</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>-9.279999999999999</v>
+        <v>2.49</v>
       </c>
       <c r="D80" s="7">
-        <v>-9.75</v>
+        <v>3.69</v>
       </c>
       <c r="E80" s="8">
-        <v>-0.47</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>-1.29</v>
+        <v>2.29</v>
       </c>
       <c r="D81" s="7">
-        <v>-1.08</v>
-      </c>
-      <c r="E81" s="9">
-        <v>0.21</v>
+        <v>3.46</v>
+      </c>
+      <c r="E81" s="8">
+        <v>1.17</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="7">
-        <v>5.62</v>
+        <v>2.21</v>
       </c>
       <c r="D82" s="7">
-        <v>5.93</v>
-      </c>
-      <c r="E82" s="9">
-        <v>0.31</v>
+        <v>3.61</v>
+      </c>
+      <c r="E82" s="8">
+        <v>1.4</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>3.2</v>
+        <v>4.21</v>
       </c>
       <c r="D83" s="7">
-        <v>3.75</v>
-      </c>
-      <c r="E83" s="9">
-        <v>0.55</v>
+        <v>6.26</v>
+      </c>
+      <c r="E83" s="8">
+        <v>2.05</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>1.82</v>
+        <v>3.86</v>
       </c>
       <c r="D84" s="7">
-        <v>2.21</v>
-      </c>
-      <c r="E84" s="9">
-        <v>0.39</v>
+        <v>5.62</v>
+      </c>
+      <c r="E84" s="8">
+        <v>1.76</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>2.02</v>
+        <v>-8.26</v>
       </c>
       <c r="D85" s="7">
-        <v>2.49</v>
-      </c>
-      <c r="E85" s="9">
-        <v>0.47</v>
+        <v>-7.61</v>
+      </c>
+      <c r="E85" s="8">
+        <v>0.65</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="7">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="D86" s="7">
-        <v>2.29</v>
-      </c>
-      <c r="E86" s="9">
-        <v>0.5</v>
+        <v>3.49</v>
+      </c>
+      <c r="E86" s="8">
+        <v>1.23</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="7">
-        <v>1.93</v>
+        <v>3.67</v>
       </c>
       <c r="D87" s="7">
-        <v>2.21</v>
-      </c>
-      <c r="E87" s="9">
-        <v>0.28</v>
+        <v>5.08</v>
+      </c>
+      <c r="E87" s="8">
+        <v>1.41</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7">
-        <v>3.3</v>
+        <v>-6.41</v>
       </c>
       <c r="D88" s="7">
-        <v>4.21</v>
-      </c>
-      <c r="E88" s="9">
-        <v>0.91</v>
+        <v>-5.71</v>
+      </c>
+      <c r="E88" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89" s="7">
-        <v>4.33</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="D89" s="7">
-        <v>3.86</v>
+        <v>-90.58</v>
       </c>
       <c r="E89" s="8">
-        <v>-0.47</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C90" s="7">
-        <v>-7.18</v>
+        <v>-13.81</v>
       </c>
       <c r="D90" s="7">
-        <v>-8.26</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-1.08</v>
+        <v>-14.36</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91" s="7">
-        <v>1.94</v>
+        <v>-16.11</v>
       </c>
       <c r="D91" s="7">
-        <v>2.26</v>
+        <v>-16.39</v>
       </c>
       <c r="E91" s="9">
-        <v>0.32</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C92" s="7">
-        <v>3.36</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D92" s="7">
-        <v>3.67</v>
+        <v>-9.66</v>
       </c>
       <c r="E92" s="9">
-        <v>0.31</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="7">
-        <v>-6.47</v>
+        <v>-9.44</v>
       </c>
       <c r="D93" s="7">
-        <v>-6.41</v>
+        <v>-9.68</v>
       </c>
       <c r="E93" s="9">
-        <v>0.06</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="7">
-        <v>-90.66</v>
+        <v>-16.66</v>
       </c>
       <c r="D94" s="7">
-        <v>-90.65000000000001</v>
-      </c>
-      <c r="E94" s="9">
-        <v>0.01</v>
+        <v>-15.98</v>
+      </c>
+      <c r="E94" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-13.55</v>
+        <v>-4.03</v>
       </c>
       <c r="D95" s="7">
-        <v>-13.81</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-0.26</v>
+        <v>-4.34</v>
+      </c>
+      <c r="E95" s="9">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-16.39</v>
+        <v>-21.4</v>
       </c>
       <c r="D96" s="7">
-        <v>-16.11</v>
+        <v>-21.73</v>
       </c>
       <c r="E96" s="9">
-        <v>0.28</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-9.220000000000001</v>
+        <v>-21.64</v>
       </c>
       <c r="D97" s="7">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="E97" s="8">
-        <v>-0.16</v>
+        <v>-22.01</v>
+      </c>
+      <c r="E97" s="9">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-9.15</v>
+        <v>-0.6</v>
       </c>
       <c r="D98" s="7">
-        <v>-9.44</v>
+        <v>-0.26</v>
       </c>
       <c r="E98" s="8">
-        <v>-0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-16.23</v>
+        <v>-6.93</v>
       </c>
       <c r="D99" s="7">
-        <v>-16.66</v>
+        <v>-6.9</v>
       </c>
       <c r="E99" s="8">
-        <v>-0.43</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-4.24</v>
+        <v>-6.81</v>
       </c>
       <c r="D100" s="7">
-        <v>-4.03</v>
-      </c>
-      <c r="E100" s="9">
-        <v>0.21</v>
+        <v>-6.8</v>
+      </c>
+      <c r="E100" s="8">
+        <v>0.01</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-21.64</v>
+        <v>-6.87</v>
       </c>
       <c r="D101" s="7">
-        <v>-21.4</v>
+        <v>-7.13</v>
       </c>
       <c r="E101" s="9">
-        <v>0.24</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-1.12</v>
+        <v>-6.93</v>
       </c>
       <c r="D102" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="E102" s="9">
-        <v>0.52</v>
+        <v>-6.89</v>
+      </c>
+      <c r="E102" s="8">
+        <v>0.04</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-7.29</v>
+        <v>-12.65</v>
       </c>
       <c r="D103" s="7">
-        <v>-6.93</v>
-      </c>
-      <c r="E103" s="9">
-        <v>0.36</v>
+        <v>-11.8</v>
+      </c>
+      <c r="E103" s="8">
+        <v>0.85</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-7.23</v>
+        <v>-5.19</v>
       </c>
       <c r="D104" s="7">
-        <v>-6.81</v>
-      </c>
-      <c r="E104" s="9">
-        <v>0.42</v>
+        <v>-4.26</v>
+      </c>
+      <c r="E104" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="7">
-        <v>-7.32</v>
+        <v>-34.52</v>
       </c>
       <c r="D105" s="7">
-        <v>-6.87</v>
-      </c>
-      <c r="E105" s="9">
-        <v>0.45</v>
+        <v>-34.16</v>
+      </c>
+      <c r="E105" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="7">
-        <v>-7.19</v>
+        <v>-6.95</v>
       </c>
       <c r="D106" s="7">
-        <v>-6.93</v>
-      </c>
-      <c r="E106" s="9">
-        <v>0.26</v>
+        <v>-6.94</v>
+      </c>
+      <c r="E106" s="8">
+        <v>0.01</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="7">
-        <v>-13.42</v>
+        <v>-0.99</v>
       </c>
       <c r="D107" s="7">
-        <v>-12.65</v>
-      </c>
-      <c r="E107" s="9">
-        <v>0.77</v>
+        <v>-0.16</v>
+      </c>
+      <c r="E107" s="8">
+        <v>0.83</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C108" s="7">
-        <v>-4.76</v>
+        <v>595.0700000000001</v>
       </c>
       <c r="D108" s="7">
-        <v>-5.19</v>
+        <v>599.5700000000001</v>
       </c>
       <c r="E108" s="8">
-        <v>-0.43</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C109" s="7">
-        <v>-33.75</v>
+        <v>59.61</v>
       </c>
       <c r="D109" s="7">
-        <v>-34.52</v>
+        <v>60.04</v>
       </c>
       <c r="E109" s="8">
-        <v>-0.77</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C110" s="7">
-        <v>-7.24</v>
+        <v>93.78</v>
       </c>
       <c r="D110" s="7">
-        <v>-6.95</v>
+        <v>93.19</v>
       </c>
       <c r="E110" s="9">
-        <v>0.29</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C111" s="7">
-        <v>-1.28</v>
+        <v>51.17</v>
       </c>
       <c r="D111" s="7">
-        <v>-0.99</v>
+        <v>51</v>
       </c>
       <c r="E111" s="9">
-        <v>0.29</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="7">
-        <v>594.7</v>
+        <v>132.78</v>
       </c>
       <c r="D112" s="7">
-        <v>595.0700000000001</v>
+        <v>132.37</v>
       </c>
       <c r="E112" s="9">
-        <v>0.37</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="7">
-        <v>59.53</v>
+        <v>137.09</v>
       </c>
       <c r="D113" s="7">
-        <v>59.61</v>
+        <v>136.73</v>
       </c>
       <c r="E113" s="9">
-        <v>0.08</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="7">
-        <v>94.06999999999999</v>
+        <v>472</v>
       </c>
       <c r="D114" s="7">
-        <v>93.78</v>
+        <v>475.86</v>
       </c>
       <c r="E114" s="8">
-        <v>-0.29</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>51</v>
+        <v>968.17</v>
       </c>
       <c r="D115" s="7">
-        <v>51.17</v>
+        <v>965.09</v>
       </c>
       <c r="E115" s="9">
-        <v>0.17</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>133.02</v>
+        <v>33.93</v>
       </c>
       <c r="D116" s="7">
-        <v>132.78</v>
-      </c>
-      <c r="E116" s="8">
-        <v>-0.24</v>
+        <v>33.79</v>
+      </c>
+      <c r="E116" s="9">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>137.53</v>
+        <v>33.92</v>
       </c>
       <c r="D117" s="7">
-        <v>137.09</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-0.44</v>
+        <v>33.76</v>
+      </c>
+      <c r="E117" s="9">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>474.44</v>
+        <v>804.14</v>
       </c>
       <c r="D118" s="7">
-        <v>472</v>
+        <v>806.9</v>
       </c>
       <c r="E118" s="8">
-        <v>-2.44</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>966.1</v>
+        <v>276.94</v>
       </c>
       <c r="D119" s="7">
-        <v>968.17</v>
-      </c>
-      <c r="E119" s="9">
-        <v>2.07</v>
+        <v>277.02</v>
+      </c>
+      <c r="E119" s="8">
+        <v>0.08</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>33.83</v>
+        <v>269.9</v>
       </c>
       <c r="D120" s="7">
-        <v>33.93</v>
-      </c>
-      <c r="E120" s="9">
-        <v>0.1</v>
+        <v>269.92</v>
+      </c>
+      <c r="E120" s="8">
+        <v>0.02</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>799.9400000000001</v>
+        <v>264.78</v>
       </c>
       <c r="D121" s="7">
-        <v>804.14</v>
+        <v>264.05</v>
       </c>
       <c r="E121" s="9">
-        <v>4.2</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>275.87</v>
+        <v>275.46</v>
       </c>
       <c r="D122" s="7">
-        <v>276.94</v>
-      </c>
-      <c r="E122" s="9">
-        <v>1.07</v>
+        <v>275.6</v>
+      </c>
+      <c r="E122" s="8">
+        <v>0.14</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>268.67</v>
+        <v>95.97</v>
       </c>
       <c r="D123" s="7">
-        <v>269.9</v>
-      </c>
-      <c r="E123" s="9">
-        <v>1.23</v>
+        <v>96.91</v>
+      </c>
+      <c r="E123" s="8">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>263.49</v>
+        <v>281.14</v>
       </c>
       <c r="D124" s="7">
-        <v>264.78</v>
-      </c>
-      <c r="E124" s="9">
-        <v>1.29</v>
+        <v>283.9</v>
+      </c>
+      <c r="E124" s="8">
+        <v>2.76</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="7">
-        <v>274.71</v>
+        <v>234.57</v>
       </c>
       <c r="D125" s="7">
-        <v>275.46</v>
-      </c>
-      <c r="E125" s="9">
-        <v>0.75</v>
+        <v>235.87</v>
+      </c>
+      <c r="E125" s="8">
+        <v>1.3</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="7">
-        <v>95.13</v>
+        <v>261.66</v>
       </c>
       <c r="D126" s="7">
-        <v>95.97</v>
-      </c>
-      <c r="E126" s="9">
-        <v>0.84</v>
+        <v>261.7</v>
+      </c>
+      <c r="E126" s="8">
+        <v>0.04</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C127" s="7">
-        <v>282.41</v>
+        <v>795.3200000000001</v>
       </c>
       <c r="D127" s="7">
-        <v>281.14</v>
+        <v>802</v>
       </c>
       <c r="E127" s="8">
-        <v>-1.27</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C128" s="7">
-        <v>237.34</v>
+        <v>16</v>
       </c>
       <c r="D128" s="7">
-        <v>234.57</v>
+        <v>27</v>
       </c>
       <c r="E128" s="8">
-        <v>-2.77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C129" s="7">
-        <v>260.85</v>
+        <v>94</v>
       </c>
       <c r="D129" s="7">
-        <v>261.66</v>
+        <v>89</v>
       </c>
       <c r="E129" s="9">
-        <v>0.8100000000000001</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C130" s="7">
-        <v>792.9400000000001</v>
+        <v>89</v>
       </c>
       <c r="D130" s="7">
-        <v>795.3200000000001</v>
-      </c>
-      <c r="E130" s="9">
-        <v>2.38</v>
+        <v>94</v>
+      </c>
+      <c r="E130" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C131" s="7">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="D131" s="7">
-        <v>94</v>
-      </c>
-      <c r="E131" s="9">
+        <v>32</v>
+      </c>
+      <c r="E131" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="7">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D132" s="7">
-        <v>89</v>
-      </c>
-      <c r="E132" s="8">
-        <v>-5</v>
+        <v>42</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-16</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>13</v>
@@ -5597,15 +5552,15 @@
         <v>32</v>
       </c>
       <c r="D133" s="7">
-        <v>27</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-5</v>
+        <v>22</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-10</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>13</v>
@@ -5614,282 +5569,282 @@
         <v>22</v>
       </c>
       <c r="D134" s="7">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E134" s="9">
-        <v>10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="7">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="D135" s="7">
-        <v>22</v>
-      </c>
-      <c r="E135" s="8">
+        <v>73</v>
+      </c>
+      <c r="E135" s="9">
         <v>-5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C136" s="7">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D136" s="7">
-        <v>78</v>
-      </c>
-      <c r="E136" s="9">
-        <v>5</v>
+        <v>53</v>
+      </c>
+      <c r="E136" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C137" s="7">
+        <v>53</v>
+      </c>
+      <c r="D137" s="7">
         <v>37</v>
       </c>
-      <c r="D137" s="7">
-        <v>47</v>
-      </c>
       <c r="E137" s="9">
-        <v>10</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C138" s="7">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D138" s="7">
-        <v>53</v>
-      </c>
-      <c r="E138" s="9">
-        <v>11</v>
+        <v>58</v>
+      </c>
+      <c r="E138" s="8">
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C139" s="7">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D139" s="7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E139" s="8">
-        <v>-16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C140" s="7">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D140" s="7">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E140" s="8">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C141" s="7">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="D141" s="7">
-        <v>73</v>
+        <v>56.25</v>
       </c>
       <c r="E141" s="8">
-        <v>-5</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="7">
-        <v>49.34</v>
+        <v>48.24</v>
       </c>
       <c r="D142" s="7">
-        <v>49.9</v>
-      </c>
-      <c r="E142" s="9">
-        <v>0.5600000000000001</v>
+        <v>53.98</v>
+      </c>
+      <c r="E142" s="8">
+        <v>5.74</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="7">
-        <v>47.1</v>
+        <v>40.81</v>
       </c>
       <c r="D143" s="7">
-        <v>48.24</v>
+        <v>36.42</v>
       </c>
       <c r="E143" s="9">
-        <v>1.14</v>
+        <v>-4.39</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="7">
-        <v>43.18</v>
+        <v>37.7</v>
       </c>
       <c r="D144" s="7">
-        <v>40.81</v>
-      </c>
-      <c r="E144" s="8">
-        <v>-2.37</v>
+        <v>36.18</v>
+      </c>
+      <c r="E144" s="9">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="7">
-        <v>35.17</v>
+        <v>78.06</v>
       </c>
       <c r="D145" s="7">
-        <v>37.7</v>
+        <v>75.98</v>
       </c>
       <c r="E145" s="9">
-        <v>2.53</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>79.23999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="D146" s="7">
-        <v>78.06</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-1.18</v>
+        <v>75.87</v>
+      </c>
+      <c r="E146" s="9">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>79.77</v>
+        <v>35.78</v>
       </c>
       <c r="D147" s="7">
-        <v>77.65000000000001</v>
+        <v>41.49</v>
       </c>
       <c r="E147" s="8">
-        <v>-2.12</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>37.96</v>
+        <v>48.26</v>
       </c>
       <c r="D148" s="7">
-        <v>35.78</v>
-      </c>
-      <c r="E148" s="8">
-        <v>-2.18</v>
+        <v>45.51</v>
+      </c>
+      <c r="E148" s="9">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>46.23</v>
+        <v>52.63</v>
       </c>
       <c r="D149" s="7">
-        <v>48.26</v>
+        <v>50.87</v>
       </c>
       <c r="E149" s="9">
-        <v>2.03</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>51.52</v>
+        <v>52.12</v>
       </c>
       <c r="D150" s="7">
-        <v>52.63</v>
+        <v>50.15</v>
       </c>
       <c r="E150" s="9">
-        <v>1.11</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -5900,13 +5855,13 @@
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>54.6</v>
+        <v>59.3</v>
       </c>
       <c r="D151" s="7">
-        <v>59.3</v>
-      </c>
-      <c r="E151" s="9">
-        <v>4.7</v>
+        <v>62.08</v>
+      </c>
+      <c r="E151" s="8">
+        <v>2.78</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -5917,13 +5872,13 @@
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>47.63</v>
+        <v>51.36</v>
       </c>
       <c r="D152" s="7">
-        <v>51.36</v>
-      </c>
-      <c r="E152" s="9">
-        <v>3.73</v>
+        <v>51.64</v>
+      </c>
+      <c r="E152" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -5934,13 +5889,13 @@
         <v>24</v>
       </c>
       <c r="C153" s="7">
-        <v>48.41</v>
+        <v>53.03</v>
       </c>
       <c r="D153" s="7">
-        <v>53.03</v>
-      </c>
-      <c r="E153" s="9">
-        <v>4.62</v>
+        <v>53.1</v>
+      </c>
+      <c r="E153" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -5951,13 +5906,13 @@
         <v>24</v>
       </c>
       <c r="C154" s="7">
-        <v>47.79</v>
+        <v>52.21</v>
       </c>
       <c r="D154" s="7">
-        <v>52.21</v>
+        <v>49.65</v>
       </c>
       <c r="E154" s="9">
-        <v>4.42</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -5968,13 +5923,13 @@
         <v>24</v>
       </c>
       <c r="C155" s="7">
-        <v>48.44</v>
+        <v>51.15</v>
       </c>
       <c r="D155" s="7">
-        <v>51.15</v>
-      </c>
-      <c r="E155" s="9">
-        <v>2.71</v>
+        <v>51.67</v>
+      </c>
+      <c r="E155" s="8">
+        <v>0.52</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -5985,13 +5940,13 @@
         <v>24</v>
       </c>
       <c r="C156" s="7">
-        <v>47.06</v>
+        <v>51.5</v>
       </c>
       <c r="D156" s="7">
-        <v>51.5</v>
-      </c>
-      <c r="E156" s="9">
-        <v>4.44</v>
+        <v>55.95</v>
+      </c>
+      <c r="E156" s="8">
+        <v>4.45</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -6002,13 +5957,13 @@
         <v>24</v>
       </c>
       <c r="C157" s="7">
-        <v>53.21</v>
+        <v>49.57</v>
       </c>
       <c r="D157" s="7">
-        <v>49.57</v>
+        <v>56.54</v>
       </c>
       <c r="E157" s="8">
-        <v>-3.64</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -6019,13 +5974,13 @@
         <v>24</v>
       </c>
       <c r="C158" s="7">
-        <v>65.75</v>
+        <v>61.54</v>
       </c>
       <c r="D158" s="7">
-        <v>61.54</v>
+        <v>62.74</v>
       </c>
       <c r="E158" s="8">
-        <v>-4.21</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -6036,13 +5991,13 @@
         <v>24</v>
       </c>
       <c r="C159" s="7">
-        <v>48.11</v>
+        <v>51.13</v>
       </c>
       <c r="D159" s="7">
-        <v>51.13</v>
-      </c>
-      <c r="E159" s="9">
-        <v>3.02</v>
+        <v>51.28</v>
+      </c>
+      <c r="E159" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6053,13 +6008,13 @@
         <v>24</v>
       </c>
       <c r="C160" s="7">
-        <v>54.09</v>
+        <v>56.5</v>
       </c>
       <c r="D160" s="7">
-        <v>56.5</v>
-      </c>
-      <c r="E160" s="9">
-        <v>2.41</v>
+        <v>62.47</v>
+      </c>
+      <c r="E160" s="8">
+        <v>5.97</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -6070,13 +6025,13 @@
         <v>31</v>
       </c>
       <c r="C161" s="7">
-        <v>-5.49</v>
+        <v>0.39</v>
       </c>
       <c r="D161" s="7">
-        <v>0.39</v>
-      </c>
-      <c r="E161" s="9">
-        <v>5.88</v>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="E161" s="8">
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6087,13 +6042,13 @@
         <v>31</v>
       </c>
       <c r="C162" s="7">
-        <v>2550.46</v>
+        <v>1694.46</v>
       </c>
       <c r="D162" s="7">
-        <v>1694.46</v>
-      </c>
-      <c r="E162" s="8">
-        <v>-856</v>
+        <v>35.76</v>
+      </c>
+      <c r="E162" s="9">
+        <v>-1658.7</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -6104,13 +6059,13 @@
         <v>31</v>
       </c>
       <c r="C163" s="7">
-        <v>-31.2</v>
+        <v>-46.16</v>
       </c>
       <c r="D163" s="7">
-        <v>-46.16</v>
+        <v>22.62</v>
       </c>
       <c r="E163" s="8">
-        <v>-14.96</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6121,13 +6076,13 @@
         <v>31</v>
       </c>
       <c r="C164" s="7">
-        <v>-12.79</v>
+        <v>-61.97</v>
       </c>
       <c r="D164" s="7">
-        <v>-61.97</v>
+        <v>7.3</v>
       </c>
       <c r="E164" s="8">
-        <v>-49.18</v>
+        <v>69.27</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -6138,13 +6093,13 @@
         <v>31</v>
       </c>
       <c r="C165" s="7">
-        <v>102.08</v>
+        <v>63.78</v>
       </c>
       <c r="D165" s="7">
-        <v>63.78</v>
-      </c>
-      <c r="E165" s="8">
-        <v>-38.3</v>
+        <v>-9.65</v>
+      </c>
+      <c r="E165" s="9">
+        <v>-73.43000000000001</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -6155,13 +6110,13 @@
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>107.57</v>
+        <v>102.26</v>
       </c>
       <c r="D166" s="7">
-        <v>102.26</v>
-      </c>
-      <c r="E166" s="8">
-        <v>-5.31</v>
+        <v>-45.28</v>
+      </c>
+      <c r="E166" s="9">
+        <v>-147.54</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -6172,13 +6127,13 @@
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>99.16</v>
+        <v>52.21</v>
       </c>
       <c r="D167" s="7">
-        <v>52.21</v>
-      </c>
-      <c r="E167" s="8">
-        <v>-46.95</v>
+        <v>-47.47</v>
+      </c>
+      <c r="E167" s="9">
+        <v>-99.68000000000001</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -6189,13 +6144,13 @@
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>44.68</v>
+        <v>-23.3</v>
       </c>
       <c r="D168" s="7">
-        <v>-23.3</v>
+        <v>-17.49</v>
       </c>
       <c r="E168" s="8">
-        <v>-67.98</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -6206,13 +6161,13 @@
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>-64.01000000000001</v>
+        <v>-58.31</v>
       </c>
       <c r="D169" s="7">
-        <v>-58.31</v>
+        <v>-78.19</v>
       </c>
       <c r="E169" s="9">
-        <v>5.7</v>
+        <v>-19.88</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -6223,13 +6178,13 @@
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>-64.42</v>
+        <v>-63.36</v>
       </c>
       <c r="D170" s="7">
-        <v>-63.36</v>
-      </c>
-      <c r="E170" s="9">
-        <v>1.06</v>
+        <v>-56.6</v>
+      </c>
+      <c r="E170" s="8">
+        <v>6.76</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -6240,13 +6195,13 @@
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-6.19</v>
+        <v>-51.01</v>
       </c>
       <c r="D171" s="7">
-        <v>-51.01</v>
+        <v>-24.51</v>
       </c>
       <c r="E171" s="8">
-        <v>-44.82</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -6257,13 +6212,13 @@
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>-33.54</v>
+        <v>-31.22</v>
       </c>
       <c r="D172" s="7">
-        <v>-31.22</v>
-      </c>
-      <c r="E172" s="9">
-        <v>2.32</v>
+        <v>-16.27</v>
+      </c>
+      <c r="E172" s="8">
+        <v>14.95</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -6274,13 +6229,13 @@
         <v>31</v>
       </c>
       <c r="C173" s="7">
-        <v>-53.99</v>
+        <v>316.02</v>
       </c>
       <c r="D173" s="7">
-        <v>316.02</v>
+        <v>-77.22</v>
       </c>
       <c r="E173" s="9">
-        <v>370.01</v>
+        <v>-393.24</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -6291,13 +6246,13 @@
         <v>31</v>
       </c>
       <c r="C174" s="7">
-        <v>-14.07</v>
+        <v>-83.98</v>
       </c>
       <c r="D174" s="7">
-        <v>-83.98</v>
+        <v>-38.14</v>
       </c>
       <c r="E174" s="8">
-        <v>-69.91</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -6308,13 +6263,13 @@
         <v>31</v>
       </c>
       <c r="C175" s="7">
-        <v>-34.86</v>
+        <v>-33.03</v>
       </c>
       <c r="D175" s="7">
-        <v>-33.03</v>
+        <v>-66.22</v>
       </c>
       <c r="E175" s="9">
-        <v>1.83</v>
+        <v>-33.19</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -6325,13 +6280,13 @@
         <v>31</v>
       </c>
       <c r="C176" s="7">
-        <v>28.9</v>
+        <v>-12.59</v>
       </c>
       <c r="D176" s="7">
-        <v>-12.59</v>
-      </c>
-      <c r="E176" s="8">
-        <v>-41.49</v>
+        <v>-19.06</v>
+      </c>
+      <c r="E176" s="9">
+        <v>-6.47</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -6342,13 +6297,13 @@
         <v>31</v>
       </c>
       <c r="C177" s="7">
-        <v>-93.53</v>
+        <v>-88.66</v>
       </c>
       <c r="D177" s="7">
-        <v>-88.66</v>
-      </c>
-      <c r="E177" s="9">
-        <v>4.87</v>
+        <v>112.73</v>
+      </c>
+      <c r="E177" s="8">
+        <v>201.39</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -6359,13 +6314,13 @@
         <v>31</v>
       </c>
       <c r="C178" s="7">
-        <v>26.88</v>
+        <v>28.91</v>
       </c>
       <c r="D178" s="7">
-        <v>28.91</v>
+        <v>-42.15</v>
       </c>
       <c r="E178" s="9">
-        <v>2.03</v>
+        <v>-71.06</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -6376,13 +6331,13 @@
         <v>31</v>
       </c>
       <c r="C179" s="7">
-        <v>-0.26</v>
+        <v>-55.59</v>
       </c>
       <c r="D179" s="7">
-        <v>-55.59</v>
+        <v>-50.08</v>
       </c>
       <c r="E179" s="8">
-        <v>-55.33</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -6393,19 +6348,19 @@
         <v>31</v>
       </c>
       <c r="C180" s="7">
-        <v>-21.34</v>
+        <v>-17.47</v>
       </c>
       <c r="D180" s="7">
-        <v>-17.47</v>
+        <v>-25.34</v>
       </c>
       <c r="E180" s="9">
-        <v>3.87</v>
+        <v>-7.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6429,28 +6384,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6464,16 +6419,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>52.9</v>
+        <v>54</v>
       </c>
       <c r="E2" s="12">
         <v>40</v>
       </c>
       <c r="F2" s="12">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G2" s="12">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="H2" s="12">
         <v>52.6</v>
@@ -6599,59 +6554,59 @@
         <v>44</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>56</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5554</v>
+        <v>0.5585</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3502</v>
+        <v>0.3487</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3099</v>
+        <v>0.3145</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2987</v>
+        <v>0.2993</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2647</v>
+        <v>0.2654</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1553</v>
+        <v>0.1562</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1415</v>
+        <v>0.1413</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1403</v>
+        <v>0.1408</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1066</v>
+        <v>0.1078</v>
       </c>
       <c r="J2" s="15">
-        <v>0.09089999999999999</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>53</v>
@@ -6677,34 +6632,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.09080000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="B4" s="15">
+        <v>0.0907</v>
+      </c>
+      <c r="C4" s="15">
         <v>0.0906</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.09029999999999999</v>
-      </c>
       <c r="D4" s="15">
-        <v>0.09029999999999999</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="E4" s="15">
-        <v>0.07490000000000001</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0581</v>
+        <v>0.0553</v>
       </c>
       <c r="G4" s="15">
-        <v>-0.0009</v>
+        <v>-0.0012</v>
       </c>
       <c r="H4" s="15">
-        <v>-0.0039</v>
+        <v>-0.0054</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.0839</v>
+        <v>-0.08349999999999999</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.3019</v>
+        <v>-0.3011</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="108">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,46 +226,85 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>76.0 → 65.4</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>76.0</t>
+  </si>
+  <si>
+    <t>65.4</t>
+  </si>
+  <si>
+    <t>75.9 → 66.3</t>
+  </si>
+  <si>
+    <t>75.9</t>
+  </si>
+  <si>
+    <t>66.3</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.9 → 56.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>56.2</t>
-  </si>
-  <si>
-    <t>48.2 → 54.0</t>
-  </si>
-  <si>
-    <t>48.2</t>
-  </si>
-  <si>
-    <t>54.0</t>
-  </si>
-  <si>
-    <t>49.6 → 56.5</t>
-  </si>
-  <si>
-    <t>49.6</t>
-  </si>
-  <si>
-    <t>56.5</t>
-  </si>
-  <si>
-    <t>52.2 → 49.6</t>
+    <t>50.9 → 49.5</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.2</t>
+    <t>50.9</t>
+  </si>
+  <si>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>50.1 → 49.5</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>51.6 → 47.0</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>47.0</t>
+  </si>
+  <si>
+    <t>53.1 → 46.6</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>46.6</t>
+  </si>
+  <si>
+    <t>51.7 → 46.5</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>51.3 → 46.7</t>
+  </si>
+  <si>
+    <t>51.3</t>
+  </si>
+  <si>
+    <t>46.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -317,7 +356,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,7 +390,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -363,8 +402,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -391,13 +437,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,12 +530,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -492,7 +544,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -991,10 +1043,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>599.5700000000001</v>
+        <v>596.79</v>
       </c>
       <c r="D2">
-        <v>0.76</v>
+        <v>-0.46</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1003,43 +1055,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-5.71</v>
+        <v>-6.14</v>
       </c>
       <c r="H2">
-        <v>15.1</v>
+        <v>14.57</v>
       </c>
       <c r="I2">
-        <v>1.06</v>
+        <v>0.12</v>
       </c>
       <c r="J2">
-        <v>2.05</v>
+        <v>0.85</v>
       </c>
       <c r="K2">
-        <v>6.81</v>
+        <v>7.82</v>
       </c>
       <c r="L2">
-        <v>5.18</v>
+        <v>4.8</v>
       </c>
       <c r="M2">
-        <v>10.78</v>
+        <v>10.64</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>596.63</v>
+        <v>596.78</v>
       </c>
       <c r="Q2">
-        <v>596.22</v>
+        <v>596.5</v>
       </c>
       <c r="R2">
-        <v>596.63</v>
+        <v>596.61</v>
       </c>
       <c r="S2">
-        <v>593.03</v>
+        <v>593.01</v>
       </c>
       <c r="T2">
-        <v>1.1</v>
+        <v>0.64</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1054,34 +1106,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>56.25</v>
+        <v>51.88</v>
       </c>
       <c r="Z2">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="AA2">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AB2">
         <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>47.41</v>
+        <v>57.92</v>
       </c>
       <c r="AD2">
-        <v>41.69</v>
+        <v>47.07</v>
       </c>
       <c r="AE2">
-        <v>6.86</v>
+        <v>6.69</v>
       </c>
       <c r="AF2">
-        <v>73.90000000000001</v>
+        <v>-12.45</v>
       </c>
       <c r="AG2">
-        <v>600.95</v>
+        <v>600.58</v>
       </c>
       <c r="AH2">
-        <v>591.48</v>
+        <v>592.4299999999999</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1090,7 +1142,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>42.81</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1101,10 +1153,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>60.04</v>
+        <v>59.76</v>
       </c>
       <c r="D3">
-        <v>0.72</v>
+        <v>-0.47</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1113,25 +1165,25 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.58</v>
+        <v>-90.62</v>
       </c>
       <c r="H3">
-        <v>15.2</v>
+        <v>14.66</v>
       </c>
       <c r="I3">
-        <v>1.01</v>
+        <v>-0.03</v>
       </c>
       <c r="J3">
-        <v>1.83</v>
+        <v>0.64</v>
       </c>
       <c r="K3">
-        <v>6.76</v>
+        <v>7.4</v>
       </c>
       <c r="L3">
-        <v>-89.48</v>
+        <v>-89.53</v>
       </c>
       <c r="M3">
-        <v>-30.11</v>
+        <v>-30.25</v>
       </c>
       <c r="N3">
         <v>6</v>
@@ -1140,16 +1192,16 @@
         <v>59.76</v>
       </c>
       <c r="Q3">
-        <v>59.79</v>
+        <v>59.82</v>
       </c>
       <c r="R3">
         <v>59.82</v>
       </c>
       <c r="S3">
-        <v>270.28</v>
+        <v>267.57</v>
       </c>
       <c r="T3">
-        <v>-77.79000000000001</v>
+        <v>-77.67</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1164,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>53.98</v>
+        <v>50.09</v>
       </c>
       <c r="Z3">
         <v>0.02</v>
@@ -1176,22 +1228,22 @@
         <v>-0</v>
       </c>
       <c r="AC3">
-        <v>43.84</v>
+        <v>57.12</v>
       </c>
       <c r="AD3">
-        <v>35.65</v>
+        <v>43.05</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>35.76</v>
+        <v>351.47</v>
       </c>
       <c r="AG3">
-        <v>60.32</v>
+        <v>60.29</v>
       </c>
       <c r="AH3">
-        <v>59.27</v>
+        <v>59.34</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1200,7 +1252,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>14.29</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1211,10 +1263,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>93.19</v>
+        <v>92.59</v>
       </c>
       <c r="D4">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1223,43 +1275,43 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-14.36</v>
+        <v>-14.91</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>5.42</v>
       </c>
       <c r="I4">
-        <v>0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="J4">
-        <v>-1.15</v>
+        <v>-1.53</v>
       </c>
       <c r="K4">
-        <v>-8.359999999999999</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L4">
-        <v>4.04</v>
+        <v>3.29</v>
       </c>
       <c r="M4">
-        <v>29.93</v>
+        <v>29.55</v>
       </c>
       <c r="N4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>93.77</v>
+        <v>93.58</v>
       </c>
       <c r="Q4">
-        <v>94.09</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="R4">
-        <v>95.7</v>
+        <v>95.56</v>
       </c>
       <c r="S4">
         <v>97.95</v>
       </c>
       <c r="T4">
-        <v>-4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1274,43 +1326,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.42</v>
+        <v>32.59</v>
       </c>
       <c r="Z4">
-        <v>-0.64</v>
+        <v>-0.7</v>
       </c>
       <c r="AA4">
         <v>-0.72</v>
       </c>
       <c r="AB4">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="AC4">
-        <v>65.33</v>
+        <v>39.35</v>
       </c>
       <c r="AD4">
-        <v>78.54000000000001</v>
+        <v>63.56</v>
       </c>
       <c r="AE4">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AF4">
-        <v>22.62</v>
+        <v>34.42</v>
       </c>
       <c r="AG4">
-        <v>95.09999999999999</v>
+        <v>95.17</v>
       </c>
       <c r="AH4">
-        <v>93.08</v>
+        <v>92.81</v>
       </c>
       <c r="AI4">
-        <v>98.52</v>
+        <v>97.98</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>15.17</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1321,10 +1373,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>51</v>
+        <v>50.61</v>
       </c>
       <c r="D5">
-        <v>-0.33</v>
+        <v>-0.76</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1333,43 +1385,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-16.39</v>
+        <v>-17.03</v>
       </c>
       <c r="H5">
-        <v>4.79</v>
+        <v>3.99</v>
       </c>
       <c r="I5">
-        <v>-0.1</v>
+        <v>-1.84</v>
       </c>
       <c r="J5">
-        <v>-2.73</v>
+        <v>-4.99</v>
       </c>
       <c r="K5">
-        <v>-3.13</v>
+        <v>-2.2</v>
       </c>
       <c r="L5">
-        <v>-14.39</v>
+        <v>-14.97</v>
       </c>
       <c r="M5">
-        <v>5.53</v>
+        <v>5.46</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>51.19</v>
+        <v>51</v>
       </c>
       <c r="Q5">
-        <v>52.2</v>
+        <v>52.07</v>
       </c>
       <c r="R5">
-        <v>52.57</v>
+        <v>52.53</v>
       </c>
       <c r="S5">
-        <v>54.37</v>
+        <v>54.33</v>
       </c>
       <c r="T5">
-        <v>-6.21</v>
+        <v>-6.85</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1384,34 +1436,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>36.18</v>
+        <v>32.9</v>
       </c>
       <c r="Z5">
-        <v>-0.47</v>
+        <v>-0.51</v>
       </c>
       <c r="AA5">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="AB5">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AC5">
-        <v>19.97</v>
+        <v>16.45</v>
       </c>
       <c r="AD5">
-        <v>20.7</v>
+        <v>18.79</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="AF5">
-        <v>7.3</v>
+        <v>-10.56</v>
       </c>
       <c r="AG5">
-        <v>53.9</v>
+        <v>53.84</v>
       </c>
       <c r="AH5">
-        <v>50.51</v>
+        <v>50.31</v>
       </c>
       <c r="AI5">
         <v>53.66</v>
@@ -1420,7 +1472,7 @@
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>20.15</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1431,55 +1483,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>132.37</v>
+        <v>130.05</v>
       </c>
       <c r="D6">
-        <v>-0.31</v>
+        <v>-1.75</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>83.5</v>
+        <v>83.83</v>
       </c>
       <c r="G6">
-        <v>-9.66</v>
+        <v>-11.25</v>
       </c>
       <c r="H6">
-        <v>58.53</v>
+        <v>55.14</v>
       </c>
       <c r="I6">
-        <v>5.28</v>
+        <v>0.91</v>
       </c>
       <c r="J6">
-        <v>13.3</v>
+        <v>11.3</v>
       </c>
       <c r="K6">
-        <v>2.89</v>
+        <v>2.01</v>
       </c>
       <c r="L6">
-        <v>60.22</v>
+        <v>55.75</v>
       </c>
       <c r="M6">
-        <v>26.54</v>
+        <v>26.06</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>131.67</v>
+        <v>131.91</v>
       </c>
       <c r="Q6">
-        <v>124.85</v>
+        <v>125.48</v>
       </c>
       <c r="R6">
-        <v>120.56</v>
+        <v>120.72</v>
       </c>
       <c r="S6">
-        <v>120.78</v>
+        <v>120.92</v>
       </c>
       <c r="T6">
-        <v>9.59</v>
+        <v>7.55</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1494,34 +1546,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>75.98</v>
+        <v>65.37</v>
       </c>
       <c r="Z6">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="AA6">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AB6">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="AC6">
-        <v>89.19</v>
+        <v>55.86</v>
       </c>
       <c r="AD6">
-        <v>95.52</v>
+        <v>80.81</v>
       </c>
       <c r="AE6">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF6">
-        <v>-9.65</v>
+        <v>69.98</v>
       </c>
       <c r="AG6">
-        <v>135.33</v>
+        <v>135.58</v>
       </c>
       <c r="AH6">
-        <v>114.37</v>
+        <v>115.38</v>
       </c>
       <c r="AI6">
         <v>127.28</v>
@@ -1530,7 +1582,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>49.09</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1541,55 +1593,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>136.73</v>
+        <v>134.63</v>
       </c>
       <c r="D7">
-        <v>-0.26</v>
+        <v>-1.54</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>86.17</v>
+        <v>86.48</v>
       </c>
       <c r="G7">
-        <v>-9.68</v>
+        <v>-11.06</v>
       </c>
       <c r="H7">
-        <v>58.67</v>
+        <v>55.68</v>
       </c>
       <c r="I7">
-        <v>5.12</v>
+        <v>1.17</v>
       </c>
       <c r="J7">
-        <v>13.21</v>
+        <v>11.51</v>
       </c>
       <c r="K7">
-        <v>2.95</v>
+        <v>2.18</v>
       </c>
       <c r="L7">
-        <v>60.41</v>
+        <v>56.24</v>
       </c>
       <c r="M7">
-        <v>34.87</v>
+        <v>34.19</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>136.01</v>
+        <v>136.32</v>
       </c>
       <c r="Q7">
-        <v>129.07</v>
+        <v>129.74</v>
       </c>
       <c r="R7">
-        <v>124.59</v>
+        <v>124.76</v>
       </c>
       <c r="S7">
-        <v>124.78</v>
+        <v>124.92</v>
       </c>
       <c r="T7">
-        <v>9.58</v>
+        <v>7.77</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1604,34 +1656,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>75.87</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="Z7">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="AA7">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AB7">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="AC7">
-        <v>85.66</v>
+        <v>52.33</v>
       </c>
       <c r="AD7">
-        <v>93.70999999999999</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="AE7">
-        <v>3.07</v>
+        <v>3.39</v>
       </c>
       <c r="AF7">
-        <v>-45.28</v>
+        <v>196.06</v>
       </c>
       <c r="AG7">
-        <v>139.88</v>
+        <v>140.16</v>
       </c>
       <c r="AH7">
-        <v>118.27</v>
+        <v>119.32</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1640,7 +1692,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>50.33</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1651,10 +1703,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>475.86</v>
+        <v>472.5</v>
       </c>
       <c r="D8">
-        <v>0.82</v>
+        <v>-0.71</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1663,43 +1715,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-15.98</v>
+        <v>-16.57</v>
       </c>
       <c r="H8">
-        <v>5.56</v>
+        <v>4.81</v>
       </c>
       <c r="I8">
-        <v>-0.6899999999999999</v>
+        <v>-1.83</v>
       </c>
       <c r="J8">
-        <v>-2.71</v>
+        <v>-3.8</v>
       </c>
       <c r="K8">
-        <v>-8.23</v>
+        <v>-7.71</v>
       </c>
       <c r="L8">
-        <v>5.07</v>
+        <v>1.89</v>
       </c>
       <c r="M8">
-        <v>7.72</v>
+        <v>7.55</v>
       </c>
       <c r="N8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>477.37</v>
+        <v>475.61</v>
       </c>
       <c r="Q8">
-        <v>484.38</v>
+        <v>483.24</v>
       </c>
       <c r="R8">
-        <v>482.01</v>
+        <v>481.67</v>
       </c>
       <c r="S8">
-        <v>509.7</v>
+        <v>509.44</v>
       </c>
       <c r="T8">
-        <v>-6.64</v>
+        <v>-7.25</v>
       </c>
       <c r="U8" t="s">
         <v>59</v>
@@ -1714,34 +1766,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>41.49</v>
+        <v>38.3</v>
       </c>
       <c r="Z8">
-        <v>-2.89</v>
+        <v>-3.25</v>
       </c>
       <c r="AA8">
-        <v>-1.78</v>
+        <v>-2.07</v>
       </c>
       <c r="AB8">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="AC8">
-        <v>12.76</v>
+        <v>18.39</v>
       </c>
       <c r="AD8">
-        <v>20.07</v>
+        <v>17.25</v>
       </c>
       <c r="AE8">
-        <v>9.960000000000001</v>
+        <v>10.46</v>
       </c>
       <c r="AF8">
-        <v>-47.47</v>
+        <v>-26.35</v>
       </c>
       <c r="AG8">
-        <v>498.41</v>
+        <v>497.24</v>
       </c>
       <c r="AH8">
-        <v>470.35</v>
+        <v>469.24</v>
       </c>
       <c r="AI8">
         <v>502.73</v>
@@ -1750,7 +1802,7 @@
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>26.19</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1761,10 +1813,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>965.09</v>
+        <v>959.2</v>
       </c>
       <c r="D9">
-        <v>-0.32</v>
+        <v>-0.61</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1773,43 +1825,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-4.34</v>
+        <v>-4.92</v>
       </c>
       <c r="H9">
-        <v>9.039999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I9">
-        <v>0.11</v>
+        <v>-0.91</v>
       </c>
       <c r="J9">
-        <v>0.53</v>
+        <v>-0.59</v>
       </c>
       <c r="K9">
-        <v>-0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="L9">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="M9">
-        <v>15.62</v>
+        <v>15.18</v>
       </c>
       <c r="N9">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="P9">
-        <v>967.08</v>
+        <v>965.3099999999999</v>
       </c>
       <c r="Q9">
-        <v>971.66</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="R9">
-        <v>971.21</v>
+        <v>970.8</v>
       </c>
       <c r="S9">
-        <v>965.3</v>
+        <v>965.2</v>
       </c>
       <c r="T9">
-        <v>-0.02</v>
+        <v>-0.62</v>
       </c>
       <c r="U9" t="s">
         <v>59</v>
@@ -1824,34 +1876,34 @@
         <v>2</v>
       </c>
       <c r="Y9">
-        <v>45.51</v>
+        <v>40.73</v>
       </c>
       <c r="Z9">
-        <v>-0.5600000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="AA9">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="AB9">
-        <v>-1.01</v>
+        <v>-1.41</v>
       </c>
       <c r="AC9">
-        <v>13.72</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>16.49</v>
+        <v>14</v>
       </c>
       <c r="AE9">
-        <v>10.87</v>
+        <v>10.7</v>
       </c>
       <c r="AF9">
-        <v>-17.49</v>
+        <v>51.47</v>
       </c>
       <c r="AG9">
-        <v>982.08</v>
+        <v>982.95</v>
       </c>
       <c r="AH9">
-        <v>961.23</v>
+        <v>959.41</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1860,7 +1912,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>15.32</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1871,10 +1923,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>33.79</v>
+        <v>33.68</v>
       </c>
       <c r="D10">
-        <v>-0.41</v>
+        <v>-0.33</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1883,43 +1935,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-21.73</v>
+        <v>-21.98</v>
       </c>
       <c r="H10">
-        <v>18.06</v>
+        <v>17.68</v>
       </c>
       <c r="I10">
-        <v>0.36</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>-2.55</v>
       </c>
       <c r="K10">
-        <v>5.04</v>
+        <v>1.91</v>
       </c>
       <c r="L10">
-        <v>-12.48</v>
+        <v>-14.84</v>
       </c>
       <c r="M10">
-        <v>-0.12</v>
+        <v>-0.39</v>
       </c>
       <c r="N10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P10">
-        <v>33.86</v>
+        <v>33.79</v>
       </c>
       <c r="Q10">
-        <v>34.41</v>
+        <v>34.36</v>
       </c>
       <c r="R10">
-        <v>32.49</v>
+        <v>32.54</v>
       </c>
       <c r="S10">
-        <v>35.56</v>
+        <v>35.53</v>
       </c>
       <c r="T10">
-        <v>-4.98</v>
+        <v>-5.21</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1934,34 +1986,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>50.87</v>
+        <v>49.47</v>
       </c>
       <c r="Z10">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="AA10">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AB10">
         <v>-0.21</v>
       </c>
       <c r="AC10">
-        <v>8.41</v>
+        <v>5.88</v>
       </c>
       <c r="AD10">
-        <v>8.27</v>
+        <v>7.31</v>
       </c>
       <c r="AE10">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="AF10">
-        <v>-78.19</v>
+        <v>-68.06999999999999</v>
       </c>
       <c r="AG10">
         <v>35.42</v>
       </c>
       <c r="AH10">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -1970,7 +2022,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>28.78</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1981,10 +2033,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>33.76</v>
+        <v>33.71</v>
       </c>
       <c r="D11">
-        <v>-0.47</v>
+        <v>-0.15</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1993,43 +2045,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-22.01</v>
+        <v>-22.13</v>
       </c>
       <c r="H11">
-        <v>17.92</v>
+        <v>17.74</v>
       </c>
       <c r="I11">
-        <v>0.24</v>
+        <v>-1.06</v>
       </c>
       <c r="J11">
-        <v>-0.03</v>
+        <v>-2.4</v>
       </c>
       <c r="K11">
-        <v>4.62</v>
+        <v>1.75</v>
       </c>
       <c r="L11">
-        <v>-12.81</v>
+        <v>-14.74</v>
       </c>
       <c r="M11">
-        <v>-0.54</v>
+        <v>-0.68</v>
       </c>
       <c r="N11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P11">
-        <v>33.91</v>
+        <v>33.84</v>
       </c>
       <c r="Q11">
-        <v>34.44</v>
+        <v>34.4</v>
       </c>
       <c r="R11">
-        <v>32.51</v>
+        <v>32.55</v>
       </c>
       <c r="S11">
-        <v>35.63</v>
+        <v>35.6</v>
       </c>
       <c r="T11">
-        <v>-5.24</v>
+        <v>-5.3</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -2044,34 +2096,34 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>50.15</v>
+        <v>49.52</v>
       </c>
       <c r="Z11">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="AA11">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AB11">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="AC11">
-        <v>11.99</v>
+        <v>7.75</v>
       </c>
       <c r="AD11">
-        <v>14.37</v>
+        <v>11.37</v>
       </c>
       <c r="AE11">
         <v>0.96</v>
       </c>
       <c r="AF11">
-        <v>-56.6</v>
+        <v>-49.98</v>
       </c>
       <c r="AG11">
         <v>35.49</v>
       </c>
       <c r="AH11">
-        <v>33.4</v>
+        <v>33.31</v>
       </c>
       <c r="AI11">
         <v>32.2</v>
@@ -2080,7 +2132,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>19.44</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2091,10 +2143,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>806.9</v>
+        <v>805.78</v>
       </c>
       <c r="D12">
-        <v>0.34</v>
+        <v>-0.14</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2103,43 +2155,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-0.26</v>
+        <v>-0.4</v>
       </c>
       <c r="H12">
-        <v>23.78</v>
+        <v>23.6</v>
       </c>
       <c r="I12">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="K12">
-        <v>5.08</v>
+        <v>6.7</v>
       </c>
       <c r="L12">
-        <v>11.26</v>
+        <v>10.7</v>
       </c>
       <c r="M12">
-        <v>14.08</v>
+        <v>13.81</v>
       </c>
       <c r="N12">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>802.87</v>
+        <v>803.41</v>
       </c>
       <c r="Q12">
-        <v>803.53</v>
+        <v>804.6</v>
       </c>
       <c r="R12">
-        <v>788.88</v>
+        <v>789.3200000000001</v>
       </c>
       <c r="S12">
-        <v>751.25</v>
+        <v>751.53</v>
       </c>
       <c r="T12">
-        <v>7.41</v>
+        <v>7.22</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -2154,34 +2206,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>62.08</v>
+        <v>60.28</v>
       </c>
       <c r="Z12">
-        <v>4.96</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>6.14</v>
+        <v>5.87</v>
       </c>
       <c r="AB12">
-        <v>-1.18</v>
+        <v>-1.07</v>
       </c>
       <c r="AC12">
-        <v>24.31</v>
+        <v>35.65</v>
       </c>
       <c r="AD12">
-        <v>13.68</v>
+        <v>23.12</v>
       </c>
       <c r="AE12">
-        <v>12.97</v>
+        <v>12.82</v>
       </c>
       <c r="AF12">
-        <v>-24.51</v>
+        <v>-4.35</v>
       </c>
       <c r="AG12">
-        <v>815.1</v>
+        <v>811.85</v>
       </c>
       <c r="AH12">
-        <v>791.97</v>
+        <v>797.36</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2190,7 +2242,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>38.5</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2201,10 +2253,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>277.02</v>
+        <v>275.74</v>
       </c>
       <c r="D13">
-        <v>0.03</v>
+        <v>-0.46</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2213,43 +2265,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-6.9</v>
+        <v>-7.33</v>
       </c>
       <c r="H13">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13">
-        <v>0.87</v>
+        <v>-0.3</v>
       </c>
       <c r="J13">
-        <v>1.28</v>
+        <v>-0.03</v>
       </c>
       <c r="K13">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
-        <v>-1.33</v>
+        <v>-2.11</v>
       </c>
       <c r="M13">
-        <v>9.06</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N13">
         <v>53</v>
       </c>
       <c r="P13">
-        <v>276.63</v>
+        <v>276.47</v>
       </c>
       <c r="Q13">
-        <v>277.98</v>
+        <v>277.94</v>
       </c>
       <c r="R13">
-        <v>275.49</v>
+        <v>275.53</v>
       </c>
       <c r="S13">
-        <v>279.37</v>
+        <v>279.29</v>
       </c>
       <c r="T13">
-        <v>-0.84</v>
+        <v>-1.27</v>
       </c>
       <c r="U13" t="s">
         <v>59</v>
@@ -2264,34 +2316,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>51.64</v>
+        <v>47.01</v>
       </c>
       <c r="Z13">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="AA13">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="AB13">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="AC13">
-        <v>32.31</v>
+        <v>31.8</v>
       </c>
       <c r="AD13">
-        <v>30.04</v>
+        <v>31.35</v>
       </c>
       <c r="AE13">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="AF13">
-        <v>-16.27</v>
+        <v>32.76</v>
       </c>
       <c r="AG13">
-        <v>281.34</v>
+        <v>281.39</v>
       </c>
       <c r="AH13">
-        <v>274.62</v>
+        <v>274.5</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2300,7 +2352,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>9.4</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2311,10 +2363,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>269.92</v>
+        <v>268.27</v>
       </c>
       <c r="D14">
-        <v>0.01</v>
+        <v>-0.61</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2323,31 +2375,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-6.8</v>
+        <v>-7.37</v>
       </c>
       <c r="H14">
-        <v>9.470000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="I14">
-        <v>0.92</v>
+        <v>-0.42</v>
       </c>
       <c r="J14">
-        <v>1.44</v>
+        <v>-0.14</v>
       </c>
       <c r="K14">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="M14">
-        <v>-8.35</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="P14">
-        <v>269.35</v>
+        <v>269.12</v>
       </c>
       <c r="Q14">
-        <v>270.44</v>
+        <v>270.39</v>
       </c>
       <c r="R14">
-        <v>268.13</v>
+        <v>268.16</v>
       </c>
       <c r="U14" t="s">
         <v>59</v>
@@ -2359,34 +2411,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>53.1</v>
+        <v>46.62</v>
       </c>
       <c r="Z14">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="AA14">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="AB14">
-        <v>-0.31</v>
+        <v>-0.35</v>
       </c>
       <c r="AC14">
-        <v>37.49</v>
+        <v>34.71</v>
       </c>
       <c r="AD14">
-        <v>31.99</v>
+        <v>34.38</v>
       </c>
       <c r="AE14">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AF14">
-        <v>-77.22</v>
+        <v>-4.01</v>
       </c>
       <c r="AG14">
-        <v>273.43</v>
+        <v>273.5</v>
       </c>
       <c r="AH14">
-        <v>267.44</v>
+        <v>267.28</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2395,7 +2447,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>54.62</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2406,10 +2458,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>264.05</v>
+        <v>262.89</v>
       </c>
       <c r="D15">
-        <v>-0.28</v>
+        <v>-0.44</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2418,43 +2470,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-7.13</v>
+        <v>-7.53</v>
       </c>
       <c r="H15">
-        <v>9.33</v>
+        <v>8.85</v>
       </c>
       <c r="I15">
-        <v>0.71</v>
+        <v>-0.42</v>
       </c>
       <c r="J15">
-        <v>1.27</v>
+        <v>-0.36</v>
       </c>
       <c r="K15">
-        <v>3.46</v>
+        <v>3.79</v>
       </c>
       <c r="L15">
-        <v>-1.6</v>
+        <v>-2.1</v>
       </c>
       <c r="M15">
-        <v>9.1</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N15">
         <v>37</v>
       </c>
       <c r="P15">
-        <v>264.1</v>
+        <v>263.88</v>
       </c>
       <c r="Q15">
-        <v>265.52</v>
+        <v>265.44</v>
       </c>
       <c r="R15">
-        <v>263.14</v>
+        <v>263.17</v>
       </c>
       <c r="S15">
-        <v>266.7</v>
+        <v>266.63</v>
       </c>
       <c r="T15">
-        <v>-0.99</v>
+        <v>-1.4</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -2469,34 +2521,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>49.65</v>
+        <v>45.8</v>
       </c>
       <c r="Z15">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="AA15">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="AB15">
-        <v>-0.38</v>
+        <v>-0.42</v>
       </c>
       <c r="AC15">
-        <v>32.32</v>
+        <v>29.73</v>
       </c>
       <c r="AD15">
-        <v>30.51</v>
+        <v>31.26</v>
       </c>
       <c r="AE15">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AF15">
-        <v>-38.14</v>
+        <v>-88.36</v>
       </c>
       <c r="AG15">
-        <v>268.88</v>
+        <v>268.97</v>
       </c>
       <c r="AH15">
-        <v>262.17</v>
+        <v>261.9</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2505,7 +2557,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>44.67</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2516,10 +2568,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>275.6</v>
+        <v>274.23</v>
       </c>
       <c r="D16">
-        <v>0.05</v>
+        <v>-0.5</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2528,43 +2580,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-6.89</v>
+        <v>-7.35</v>
       </c>
       <c r="H16">
-        <v>9.359999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="I16">
-        <v>0.85</v>
+        <v>-0.36</v>
       </c>
       <c r="J16">
-        <v>1.22</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K16">
-        <v>3.61</v>
+        <v>3.82</v>
       </c>
       <c r="L16">
-        <v>-1.37</v>
+        <v>-2.16</v>
       </c>
       <c r="M16">
-        <v>9.1</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N16">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P16">
-        <v>275.24</v>
+        <v>275.04</v>
       </c>
       <c r="Q16">
-        <v>276.56</v>
+        <v>276.52</v>
       </c>
       <c r="R16">
-        <v>274.1</v>
+        <v>274.14</v>
       </c>
       <c r="S16">
-        <v>277.98</v>
+        <v>277.9</v>
       </c>
       <c r="T16">
-        <v>-0.86</v>
+        <v>-1.32</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -2579,34 +2631,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>51.67</v>
+        <v>46.52</v>
       </c>
       <c r="Z16">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="AA16">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="AB16">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="AC16">
-        <v>31.52</v>
+        <v>28.76</v>
       </c>
       <c r="AD16">
-        <v>29.44</v>
+        <v>29.8</v>
       </c>
       <c r="AE16">
-        <v>3.87</v>
+        <v>3.74</v>
       </c>
       <c r="AF16">
-        <v>-66.22</v>
+        <v>-42.72</v>
       </c>
       <c r="AG16">
-        <v>279.92</v>
+        <v>279.98</v>
       </c>
       <c r="AH16">
-        <v>273.2</v>
+        <v>273.07</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2615,7 +2667,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>42.71</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2626,10 +2678,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>96.91</v>
+        <v>96.08</v>
       </c>
       <c r="D17">
-        <v>0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2638,43 +2690,43 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-11.8</v>
+        <v>-12.55</v>
       </c>
       <c r="H17">
-        <v>28.85</v>
+        <v>27.75</v>
       </c>
       <c r="I17">
-        <v>0.8100000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="J17">
-        <v>4.51</v>
+        <v>3.32</v>
       </c>
       <c r="K17">
-        <v>6.26</v>
+        <v>7.42</v>
       </c>
       <c r="L17">
-        <v>24.34</v>
+        <v>23.58</v>
       </c>
       <c r="M17">
-        <v>31.45</v>
+        <v>31.08</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>96.02</v>
+        <v>95.98</v>
       </c>
       <c r="Q17">
-        <v>96.18000000000001</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="R17">
-        <v>95.20999999999999</v>
+        <v>95.16</v>
       </c>
       <c r="S17">
-        <v>95.84</v>
+        <v>95.86</v>
       </c>
       <c r="T17">
-        <v>1.12</v>
+        <v>0.23</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -2689,34 +2741,34 @@
         <v>2</v>
       </c>
       <c r="Y17">
-        <v>55.95</v>
+        <v>51.46</v>
       </c>
       <c r="Z17">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="AA17">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB17">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AC17">
-        <v>23.76</v>
+        <v>32.61</v>
       </c>
       <c r="AD17">
-        <v>11.14</v>
+        <v>21.43</v>
       </c>
       <c r="AE17">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AF17">
-        <v>-19.06</v>
+        <v>-58.74</v>
       </c>
       <c r="AG17">
-        <v>99.12</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AH17">
-        <v>93.23</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2725,7 +2777,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>20.82</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2736,10 +2788,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>283.9</v>
+        <v>284.57</v>
       </c>
       <c r="D18">
-        <v>0.98</v>
+        <v>0.24</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2748,22 +2800,22 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-4.26</v>
+        <v>-4.03</v>
       </c>
       <c r="H18">
-        <v>15.61</v>
+        <v>15.88</v>
       </c>
       <c r="I18">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="J18">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="K18">
-        <v>5.62</v>
+        <v>7.17</v>
       </c>
       <c r="L18">
-        <v>4.34</v>
+        <v>4.69</v>
       </c>
       <c r="M18">
         <v>9.039999999999999</v>
@@ -2772,10 +2824,10 @@
         <v>63</v>
       </c>
       <c r="P18">
-        <v>281.83</v>
+        <v>282.87</v>
       </c>
       <c r="Q18">
-        <v>281.31</v>
+        <v>281.48</v>
       </c>
       <c r="R18">
         <v>283.59</v>
@@ -2784,7 +2836,7 @@
         <v>281.3</v>
       </c>
       <c r="T18">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2799,34 +2851,34 @@
         <v>2</v>
       </c>
       <c r="Y18">
-        <v>56.54</v>
+        <v>58.05</v>
       </c>
       <c r="Z18">
-        <v>-0.17</v>
+        <v>0.1</v>
       </c>
       <c r="AA18">
-        <v>-0.51</v>
+        <v>-0.39</v>
       </c>
       <c r="AB18">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="AC18">
         <v>90.38</v>
       </c>
       <c r="AD18">
-        <v>86.26000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="AE18">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="AF18">
-        <v>112.73</v>
+        <v>-74.98</v>
       </c>
       <c r="AG18">
-        <v>285.13</v>
+        <v>285.57</v>
       </c>
       <c r="AH18">
-        <v>277.48</v>
+        <v>277.39</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2835,7 +2887,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>22.92</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2846,10 +2898,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>235.87</v>
+        <v>231.97</v>
       </c>
       <c r="D19">
-        <v>0.55</v>
+        <v>-1.65</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2858,43 +2910,43 @@
         <v>114.56</v>
       </c>
       <c r="G19">
-        <v>-34.16</v>
+        <v>-35.25</v>
       </c>
       <c r="H19">
-        <v>105.89</v>
+        <v>102.49</v>
       </c>
       <c r="I19">
-        <v>6.36</v>
+        <v>0.51</v>
       </c>
       <c r="J19">
-        <v>11.56</v>
+        <v>9.49</v>
       </c>
       <c r="K19">
-        <v>-7.61</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L19">
-        <v>109.46</v>
+        <v>102.03</v>
       </c>
       <c r="M19">
-        <v>55.85</v>
+        <v>54.55</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>235.36</v>
+        <v>235.6</v>
       </c>
       <c r="Q19">
-        <v>225.13</v>
+        <v>226.13</v>
       </c>
       <c r="R19">
-        <v>220.69</v>
+        <v>220.62</v>
       </c>
       <c r="S19">
-        <v>229.31</v>
+        <v>229.71</v>
       </c>
       <c r="T19">
-        <v>2.86</v>
+        <v>0.98</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2909,34 +2961,34 @@
         <v>2</v>
       </c>
       <c r="Y19">
-        <v>62.74</v>
+        <v>56.97</v>
       </c>
       <c r="Z19">
-        <v>4.21</v>
+        <v>4.02</v>
       </c>
       <c r="AA19">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="AB19">
-        <v>1.42</v>
+        <v>0.99</v>
       </c>
       <c r="AC19">
-        <v>78.03</v>
+        <v>61.08</v>
       </c>
       <c r="AD19">
-        <v>84.78</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="AE19">
-        <v>5.76</v>
+        <v>6.24</v>
       </c>
       <c r="AF19">
-        <v>-42.15</v>
+        <v>11.75</v>
       </c>
       <c r="AG19">
-        <v>242.29</v>
+        <v>242.36</v>
       </c>
       <c r="AH19">
-        <v>207.96</v>
+        <v>209.9</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2945,7 +2997,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>42.26</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2956,10 +3008,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>261.7</v>
+        <v>260.51</v>
       </c>
       <c r="D20">
-        <v>0.02</v>
+        <v>-0.45</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2968,43 +3020,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-6.94</v>
+        <v>-7.36</v>
       </c>
       <c r="H20">
-        <v>9.34</v>
+        <v>8.84</v>
       </c>
       <c r="I20">
-        <v>0.84</v>
+        <v>-0.27</v>
       </c>
       <c r="J20">
-        <v>1.23</v>
+        <v>-0.03</v>
       </c>
       <c r="K20">
-        <v>3.49</v>
+        <v>3.83</v>
       </c>
       <c r="L20">
-        <v>-1.41</v>
+        <v>-2.18</v>
       </c>
       <c r="M20">
-        <v>9.07</v>
+        <v>8.85</v>
       </c>
       <c r="N20">
         <v>47</v>
       </c>
       <c r="P20">
-        <v>261.4</v>
+        <v>261.26</v>
       </c>
       <c r="Q20">
-        <v>262.69</v>
+        <v>262.65</v>
       </c>
       <c r="R20">
-        <v>260.4</v>
+        <v>260.43</v>
       </c>
       <c r="S20">
-        <v>264.08</v>
+        <v>264.01</v>
       </c>
       <c r="T20">
-        <v>-0.9</v>
+        <v>-1.33</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -3019,34 +3071,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>51.28</v>
+        <v>46.67</v>
       </c>
       <c r="Z20">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="AA20">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="AB20">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="AC20">
-        <v>32.82</v>
+        <v>31.1</v>
       </c>
       <c r="AD20">
-        <v>30.71</v>
+        <v>31.6</v>
       </c>
       <c r="AE20">
-        <v>4.74</v>
+        <v>4.61</v>
       </c>
       <c r="AF20">
-        <v>-50.08</v>
+        <v>70.25</v>
       </c>
       <c r="AG20">
-        <v>265.82</v>
+        <v>265.87</v>
       </c>
       <c r="AH20">
-        <v>259.56</v>
+        <v>259.43</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3055,7 +3107,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>38.38</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3066,10 +3118,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>802</v>
+        <v>795.26</v>
       </c>
       <c r="D21">
-        <v>0.84</v>
+        <v>-0.84</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3078,43 +3130,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-0.16</v>
+        <v>-0.99</v>
       </c>
       <c r="H21">
-        <v>24.79</v>
+        <v>23.74</v>
       </c>
       <c r="I21">
-        <v>1.11</v>
+        <v>-0.12</v>
       </c>
       <c r="J21">
-        <v>3.72</v>
+        <v>1.99</v>
       </c>
       <c r="K21">
-        <v>5.08</v>
+        <v>6.18</v>
       </c>
       <c r="L21">
-        <v>11.44</v>
+        <v>10.56</v>
       </c>
       <c r="M21">
-        <v>14.13</v>
+        <v>13.67</v>
       </c>
       <c r="N21">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P21">
-        <v>796.09</v>
+        <v>795.9</v>
       </c>
       <c r="Q21">
-        <v>795.91</v>
+        <v>796.74</v>
       </c>
       <c r="R21">
-        <v>781.77</v>
+        <v>782.1799999999999</v>
       </c>
       <c r="S21">
-        <v>744.41</v>
+        <v>744.6799999999999</v>
       </c>
       <c r="T21">
-        <v>7.74</v>
+        <v>6.79</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -3129,34 +3181,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>62.47</v>
+        <v>54.37</v>
       </c>
       <c r="Z21">
-        <v>5.06</v>
+        <v>4.61</v>
       </c>
       <c r="AA21">
-        <v>6.08</v>
+        <v>5.79</v>
       </c>
       <c r="AB21">
-        <v>-1.02</v>
+        <v>-1.17</v>
       </c>
       <c r="AC21">
-        <v>25.93</v>
+        <v>26.6</v>
       </c>
       <c r="AD21">
-        <v>13.01</v>
+        <v>19.48</v>
       </c>
       <c r="AE21">
-        <v>11.64</v>
+        <v>11.53</v>
       </c>
       <c r="AF21">
-        <v>-25.34</v>
+        <v>12.57</v>
       </c>
       <c r="AG21">
-        <v>807.6799999999999</v>
+        <v>805.28</v>
       </c>
       <c r="AH21">
-        <v>784.14</v>
+        <v>788.2</v>
       </c>
       <c r="AI21">
         <v>773.79</v>
@@ -3165,7 +3217,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>23.13</v>
+        <v>23.69</v>
       </c>
     </row>
   </sheetData>
@@ -3346,7 +3398,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3366,7 +3418,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>68</v>
@@ -3385,2279 +3437,2291 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>78</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>77</v>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0.61</v>
-      </c>
-      <c r="D10" s="7">
-        <v>2.05</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.42</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.83</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-2.37</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-1.15</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-3.78</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-2.73</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.05</v>
+      <c r="B13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>11.94</v>
+        <v>2.05</v>
       </c>
       <c r="D14" s="7">
-        <v>13.3</v>
+        <v>0.85</v>
       </c>
       <c r="E14" s="8">
-        <v>1.36</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>11.85</v>
+        <v>1.83</v>
       </c>
       <c r="D15" s="7">
-        <v>13.21</v>
+        <v>0.64</v>
       </c>
       <c r="E15" s="8">
-        <v>1.36</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-3.32</v>
+        <v>-1.15</v>
       </c>
       <c r="D16" s="7">
-        <v>-2.71</v>
+        <v>-1.53</v>
       </c>
       <c r="E16" s="8">
-        <v>0.61</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>0.5</v>
+        <v>-2.73</v>
       </c>
       <c r="D17" s="7">
-        <v>0.53</v>
+        <v>-4.99</v>
       </c>
       <c r="E17" s="8">
-        <v>0.03</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>3.63</v>
+        <v>13.3</v>
       </c>
       <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-3.63</v>
+        <v>11.3</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>3.73</v>
+        <v>13.21</v>
       </c>
       <c r="D19" s="7">
-        <v>-0.03</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-3.76</v>
+        <v>11.51</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>2.64</v>
+        <v>-2.71</v>
       </c>
       <c r="D20" s="7">
-        <v>3.5</v>
+        <v>-3.8</v>
       </c>
       <c r="E20" s="8">
-        <v>0.86</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>1.22</v>
+        <v>0.53</v>
       </c>
       <c r="D21" s="7">
-        <v>1.28</v>
+        <v>-0.59</v>
       </c>
       <c r="E21" s="8">
-        <v>0.06</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="D22" s="7">
-        <v>1.44</v>
+        <v>-2.55</v>
       </c>
       <c r="E22" s="8">
-        <v>0.11</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>1.35</v>
+        <v>-0.03</v>
       </c>
       <c r="D23" s="7">
-        <v>1.27</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.08</v>
+        <v>-2.4</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="D24" s="7">
-        <v>4.51</v>
+        <v>2.84</v>
       </c>
       <c r="E24" s="8">
-        <v>1.89</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>0.51</v>
+        <v>1.28</v>
       </c>
       <c r="D25" s="7">
-        <v>1.93</v>
+        <v>-0.03</v>
       </c>
       <c r="E25" s="8">
-        <v>1.42</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>7.45</v>
+        <v>1.44</v>
       </c>
       <c r="D26" s="7">
-        <v>11.56</v>
+        <v>-0.14</v>
       </c>
       <c r="E26" s="8">
-        <v>4.11</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="D27" s="7">
-        <v>1.23</v>
+        <v>-0.36</v>
       </c>
       <c r="E27" s="8">
-        <v>0.08</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>2.24</v>
+        <v>1.22</v>
       </c>
       <c r="D28" s="7">
-        <v>3.72</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E28" s="8">
-        <v>1.48</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" s="7">
-        <v>0.04</v>
+        <v>4.51</v>
       </c>
       <c r="D29" s="7">
-        <v>1.06</v>
+        <v>3.32</v>
       </c>
       <c r="E29" s="8">
-        <v>1.02</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="7">
-        <v>-0.03</v>
+        <v>1.93</v>
       </c>
       <c r="D30" s="7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="E30" s="8">
-        <v>1.04</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="7">
-        <v>-0.22</v>
+        <v>11.56</v>
       </c>
       <c r="D31" s="7">
-        <v>0.05</v>
+        <v>9.49</v>
       </c>
       <c r="E31" s="8">
-        <v>0.27</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="7">
-        <v>-0.35</v>
+        <v>1.23</v>
       </c>
       <c r="D32" s="7">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="E32" s="8">
-        <v>0.25</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" s="7">
-        <v>5.02</v>
+        <v>3.72</v>
       </c>
       <c r="D33" s="7">
-        <v>5.28</v>
+        <v>1.99</v>
       </c>
       <c r="E33" s="8">
-        <v>0.26</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>4.88</v>
+        <v>1.06</v>
       </c>
       <c r="D34" s="7">
-        <v>5.12</v>
+        <v>0.12</v>
       </c>
       <c r="E34" s="8">
-        <v>0.24</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>-1.92</v>
+        <v>1.01</v>
       </c>
       <c r="D35" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="E35" s="8">
-        <v>1.23</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-0.57</v>
+        <v>0.05</v>
       </c>
       <c r="D36" s="7">
-        <v>0.11</v>
+        <v>-1.02</v>
       </c>
       <c r="E36" s="8">
-        <v>0.68</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>0.71</v>
+        <v>-0.1</v>
       </c>
       <c r="D37" s="7">
-        <v>0.36</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.35</v>
+        <v>-1.84</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>1.01</v>
+        <v>5.28</v>
       </c>
       <c r="D38" s="7">
-        <v>0.24</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.77</v>
+        <v>0.91</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-4.37</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-0.22</v>
+        <v>5.12</v>
       </c>
       <c r="D39" s="7">
-        <v>0.88</v>
+        <v>1.17</v>
       </c>
       <c r="E39" s="8">
-        <v>1.1</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>0.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D40" s="7">
-        <v>0.87</v>
+        <v>-1.83</v>
       </c>
       <c r="E40" s="8">
-        <v>0.57</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>0.49</v>
+        <v>0.11</v>
       </c>
       <c r="D41" s="7">
-        <v>0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="E41" s="8">
-        <v>0.43</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="D42" s="7">
-        <v>0.71</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E42" s="8">
-        <v>0.28</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="D43" s="7">
-        <v>0.85</v>
+        <v>-1.06</v>
       </c>
       <c r="E43" s="8">
-        <v>0.54</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>-0.57</v>
+        <v>0.88</v>
       </c>
       <c r="D44" s="7">
-        <v>0.8100000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="E44" s="8">
-        <v>1.38</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="D45" s="7">
-        <v>1.82</v>
+        <v>-0.3</v>
       </c>
       <c r="E45" s="8">
-        <v>0.6899999999999999</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>3.26</v>
+        <v>0.92</v>
       </c>
       <c r="D46" s="7">
-        <v>6.36</v>
+        <v>-0.42</v>
       </c>
       <c r="E46" s="8">
-        <v>3.1</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="7">
-        <v>0.28</v>
+        <v>0.71</v>
       </c>
       <c r="D47" s="7">
-        <v>0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="E47" s="8">
-        <v>0.5600000000000001</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="7">
-        <v>-0.42</v>
+        <v>0.85</v>
       </c>
       <c r="D48" s="7">
-        <v>1.11</v>
+        <v>-0.36</v>
       </c>
       <c r="E48" s="8">
-        <v>1.53</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C49" s="7">
-        <v>3.24</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D49" s="7">
-        <v>5.18</v>
+        <v>-0.21</v>
       </c>
       <c r="E49" s="8">
-        <v>1.94</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C50" s="7">
-        <v>-89.66</v>
+        <v>1.82</v>
       </c>
       <c r="D50" s="7">
-        <v>-89.48</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.18</v>
+        <v>1.87</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.05</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51" s="7">
-        <v>4.23</v>
+        <v>6.36</v>
       </c>
       <c r="D51" s="7">
-        <v>4.04</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.19</v>
+        <v>0.51</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-5.85</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C52" s="7">
-        <v>-14.75</v>
+        <v>0.84</v>
       </c>
       <c r="D52" s="7">
-        <v>-14.39</v>
+        <v>-0.27</v>
       </c>
       <c r="E52" s="8">
-        <v>0.36</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C53" s="7">
-        <v>60.85</v>
+        <v>1.11</v>
       </c>
       <c r="D53" s="7">
-        <v>60.22</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.63</v>
+        <v>-0.12</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>60.83</v>
+        <v>5.18</v>
       </c>
       <c r="D54" s="7">
-        <v>60.41</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-0.42</v>
+        <v>4.8</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>6.22</v>
+        <v>-89.48</v>
       </c>
       <c r="D55" s="7">
-        <v>5.07</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-1.15</v>
+        <v>-89.53</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>2.12</v>
+        <v>4.04</v>
       </c>
       <c r="D56" s="7">
-        <v>2.38</v>
+        <v>3.29</v>
       </c>
       <c r="E56" s="8">
-        <v>0.26</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>-12.71</v>
+        <v>-14.39</v>
       </c>
       <c r="D57" s="7">
-        <v>-12.48</v>
+        <v>-14.97</v>
       </c>
       <c r="E57" s="8">
-        <v>0.23</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>-13.05</v>
+        <v>60.22</v>
       </c>
       <c r="D58" s="7">
-        <v>-12.81</v>
+        <v>55.75</v>
       </c>
       <c r="E58" s="8">
-        <v>0.24</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>10.2</v>
+        <v>60.41</v>
       </c>
       <c r="D59" s="7">
-        <v>11.26</v>
+        <v>56.24</v>
       </c>
       <c r="E59" s="8">
-        <v>1.06</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>-2.16</v>
+        <v>5.07</v>
       </c>
       <c r="D60" s="7">
-        <v>-1.33</v>
+        <v>1.89</v>
       </c>
       <c r="E60" s="8">
-        <v>0.83</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>-2.11</v>
+        <v>2.38</v>
       </c>
       <c r="D61" s="7">
-        <v>-1.6</v>
+        <v>1.71</v>
       </c>
       <c r="E61" s="8">
-        <v>0.51</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>-2.18</v>
+        <v>-12.48</v>
       </c>
       <c r="D62" s="7">
-        <v>-1.37</v>
+        <v>-14.84</v>
       </c>
       <c r="E62" s="8">
-        <v>0.8100000000000001</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>21.68</v>
+        <v>-12.81</v>
       </c>
       <c r="D63" s="7">
-        <v>24.34</v>
+        <v>-14.74</v>
       </c>
       <c r="E63" s="8">
-        <v>2.66</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>2.34</v>
+        <v>11.26</v>
       </c>
       <c r="D64" s="7">
-        <v>4.34</v>
+        <v>10.7</v>
       </c>
       <c r="E64" s="8">
-        <v>2</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>109.91</v>
+        <v>-1.33</v>
       </c>
       <c r="D65" s="7">
-        <v>109.46</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-0.45</v>
+        <v>-2.11</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>-2.19</v>
+        <v>-1.6</v>
       </c>
       <c r="D66" s="7">
-        <v>-1.41</v>
+        <v>-2.1</v>
       </c>
       <c r="E66" s="8">
-        <v>0.78</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>9.779999999999999</v>
+        <v>-1.37</v>
       </c>
       <c r="D67" s="7">
-        <v>11.44</v>
+        <v>-2.16</v>
       </c>
       <c r="E67" s="8">
-        <v>1.66</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>4.89</v>
+        <v>24.34</v>
       </c>
       <c r="D68" s="7">
-        <v>6.81</v>
+        <v>23.58</v>
       </c>
       <c r="E68" s="8">
-        <v>1.92</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>4.97</v>
+        <v>4.34</v>
       </c>
       <c r="D69" s="7">
-        <v>6.76</v>
-      </c>
-      <c r="E69" s="8">
-        <v>1.79</v>
+        <v>4.69</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0.35</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>-9.82</v>
+        <v>109.46</v>
       </c>
       <c r="D70" s="7">
-        <v>-8.359999999999999</v>
+        <v>102.03</v>
       </c>
       <c r="E70" s="8">
-        <v>1.46</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>-4.48</v>
+        <v>-1.41</v>
       </c>
       <c r="D71" s="7">
-        <v>-3.13</v>
+        <v>-2.18</v>
       </c>
       <c r="E71" s="8">
-        <v>1.35</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72" s="7">
-        <v>2.9</v>
+        <v>11.44</v>
       </c>
       <c r="D72" s="7">
-        <v>2.89</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-0.01</v>
+        <v>10.56</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>2.8</v>
+        <v>6.81</v>
       </c>
       <c r="D73" s="7">
-        <v>2.95</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.15</v>
+        <v>7.82</v>
+      </c>
+      <c r="E73" s="9">
+        <v>1.01</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="7">
-        <v>-9.75</v>
+        <v>6.76</v>
       </c>
       <c r="D74" s="7">
-        <v>-8.23</v>
-      </c>
-      <c r="E74" s="8">
-        <v>1.52</v>
+        <v>7.4</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0.64</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>-1.08</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="D75" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E75" s="8">
-        <v>1.01</v>
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>5.93</v>
+        <v>-3.13</v>
       </c>
       <c r="D76" s="7">
-        <v>5.04</v>
+        <v>-2.2</v>
       </c>
       <c r="E76" s="9">
-        <v>-0.89</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>5.8</v>
+        <v>2.89</v>
       </c>
       <c r="D77" s="7">
-        <v>4.62</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-1.18</v>
+        <v>2.01</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="D78" s="7">
-        <v>5.08</v>
+        <v>2.18</v>
       </c>
       <c r="E78" s="8">
-        <v>1.33</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>2.21</v>
+        <v>-8.23</v>
       </c>
       <c r="D79" s="7">
-        <v>3.45</v>
-      </c>
-      <c r="E79" s="8">
-        <v>1.24</v>
+        <v>-7.71</v>
+      </c>
+      <c r="E79" s="9">
+        <v>0.52</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>2.49</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D80" s="7">
-        <v>3.69</v>
-      </c>
-      <c r="E80" s="8">
-        <v>1.2</v>
+        <v>0.48</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0.55</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>2.29</v>
+        <v>5.04</v>
       </c>
       <c r="D81" s="7">
-        <v>3.46</v>
+        <v>1.91</v>
       </c>
       <c r="E81" s="8">
-        <v>1.17</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="7">
-        <v>2.21</v>
+        <v>4.62</v>
       </c>
       <c r="D82" s="7">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="E82" s="8">
-        <v>1.4</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>4.21</v>
+        <v>5.08</v>
       </c>
       <c r="D83" s="7">
-        <v>6.26</v>
-      </c>
-      <c r="E83" s="8">
-        <v>2.05</v>
+        <v>6.7</v>
+      </c>
+      <c r="E83" s="9">
+        <v>1.62</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="D84" s="7">
-        <v>5.62</v>
-      </c>
-      <c r="E84" s="8">
-        <v>1.76</v>
+        <v>3.85</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0.4</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>-8.26</v>
+        <v>3.69</v>
       </c>
       <c r="D85" s="7">
-        <v>-7.61</v>
-      </c>
-      <c r="E85" s="8">
-        <v>0.65</v>
+        <v>3.78</v>
+      </c>
+      <c r="E85" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="7">
-        <v>2.26</v>
+        <v>3.46</v>
       </c>
       <c r="D86" s="7">
-        <v>3.49</v>
-      </c>
-      <c r="E86" s="8">
-        <v>1.23</v>
+        <v>3.79</v>
+      </c>
+      <c r="E86" s="9">
+        <v>0.33</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="7">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="D87" s="7">
-        <v>5.08</v>
-      </c>
-      <c r="E87" s="8">
-        <v>1.41</v>
+        <v>3.82</v>
+      </c>
+      <c r="E87" s="9">
+        <v>0.21</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C88" s="7">
-        <v>-6.41</v>
+        <v>6.26</v>
       </c>
       <c r="D88" s="7">
-        <v>-5.71</v>
-      </c>
-      <c r="E88" s="8">
-        <v>0.7</v>
+        <v>7.42</v>
+      </c>
+      <c r="E88" s="9">
+        <v>1.16</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89" s="7">
-        <v>-90.65000000000001</v>
+        <v>5.62</v>
       </c>
       <c r="D89" s="7">
-        <v>-90.58</v>
-      </c>
-      <c r="E89" s="8">
-        <v>0.07000000000000001</v>
+        <v>7.17</v>
+      </c>
+      <c r="E89" s="9">
+        <v>1.55</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90" s="7">
-        <v>-13.81</v>
+        <v>-7.61</v>
       </c>
       <c r="D90" s="7">
-        <v>-14.36</v>
-      </c>
-      <c r="E90" s="9">
-        <v>-0.55</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C91" s="7">
-        <v>-16.11</v>
+        <v>3.49</v>
       </c>
       <c r="D91" s="7">
-        <v>-16.39</v>
+        <v>3.83</v>
       </c>
       <c r="E91" s="9">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C92" s="7">
-        <v>-9.380000000000001</v>
+        <v>5.08</v>
       </c>
       <c r="D92" s="7">
-        <v>-9.66</v>
+        <v>6.18</v>
       </c>
       <c r="E92" s="9">
-        <v>-0.28</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="7">
-        <v>-9.44</v>
+        <v>-5.71</v>
       </c>
       <c r="D93" s="7">
-        <v>-9.68</v>
-      </c>
-      <c r="E93" s="9">
-        <v>-0.24</v>
+        <v>-6.14</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="7">
-        <v>-16.66</v>
+        <v>-90.58</v>
       </c>
       <c r="D94" s="7">
-        <v>-15.98</v>
+        <v>-90.62</v>
       </c>
       <c r="E94" s="8">
-        <v>0.68</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-4.03</v>
+        <v>-14.36</v>
       </c>
       <c r="D95" s="7">
-        <v>-4.34</v>
-      </c>
-      <c r="E95" s="9">
-        <v>-0.31</v>
+        <v>-14.91</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-21.4</v>
+        <v>-16.39</v>
       </c>
       <c r="D96" s="7">
-        <v>-21.73</v>
-      </c>
-      <c r="E96" s="9">
-        <v>-0.33</v>
+        <v>-17.03</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-21.64</v>
+        <v>-9.66</v>
       </c>
       <c r="D97" s="7">
-        <v>-22.01</v>
-      </c>
-      <c r="E97" s="9">
-        <v>-0.37</v>
+        <v>-11.25</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-0.6</v>
+        <v>-9.68</v>
       </c>
       <c r="D98" s="7">
-        <v>-0.26</v>
+        <v>-11.06</v>
       </c>
       <c r="E98" s="8">
-        <v>0.34</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-6.93</v>
+        <v>-15.98</v>
       </c>
       <c r="D99" s="7">
-        <v>-6.9</v>
+        <v>-16.57</v>
       </c>
       <c r="E99" s="8">
-        <v>0.03</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-6.81</v>
+        <v>-4.34</v>
       </c>
       <c r="D100" s="7">
-        <v>-6.8</v>
+        <v>-4.92</v>
       </c>
       <c r="E100" s="8">
-        <v>0.01</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-6.87</v>
+        <v>-21.73</v>
       </c>
       <c r="D101" s="7">
-        <v>-7.13</v>
-      </c>
-      <c r="E101" s="9">
-        <v>-0.26</v>
+        <v>-21.98</v>
+      </c>
+      <c r="E101" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-6.93</v>
+        <v>-22.01</v>
       </c>
       <c r="D102" s="7">
-        <v>-6.89</v>
+        <v>-22.13</v>
       </c>
       <c r="E102" s="8">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-12.65</v>
+        <v>-0.26</v>
       </c>
       <c r="D103" s="7">
-        <v>-11.8</v>
+        <v>-0.4</v>
       </c>
       <c r="E103" s="8">
-        <v>0.85</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-5.19</v>
+        <v>-6.9</v>
       </c>
       <c r="D104" s="7">
-        <v>-4.26</v>
+        <v>-7.33</v>
       </c>
       <c r="E104" s="8">
-        <v>0.93</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="7">
-        <v>-34.52</v>
+        <v>-6.8</v>
       </c>
       <c r="D105" s="7">
-        <v>-34.16</v>
+        <v>-7.37</v>
       </c>
       <c r="E105" s="8">
-        <v>0.36</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="7">
-        <v>-6.95</v>
+        <v>-7.13</v>
       </c>
       <c r="D106" s="7">
-        <v>-6.94</v>
+        <v>-7.53</v>
       </c>
       <c r="E106" s="8">
-        <v>0.01</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="7">
-        <v>-0.99</v>
+        <v>-6.89</v>
       </c>
       <c r="D107" s="7">
-        <v>-0.16</v>
+        <v>-7.35</v>
       </c>
       <c r="E107" s="8">
-        <v>0.83</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C108" s="7">
-        <v>595.0700000000001</v>
+        <v>-11.8</v>
       </c>
       <c r="D108" s="7">
-        <v>599.5700000000001</v>
+        <v>-12.55</v>
       </c>
       <c r="E108" s="8">
-        <v>4.5</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C109" s="7">
-        <v>59.61</v>
+        <v>-4.26</v>
       </c>
       <c r="D109" s="7">
-        <v>60.04</v>
-      </c>
-      <c r="E109" s="8">
-        <v>0.43</v>
+        <v>-4.03</v>
+      </c>
+      <c r="E109" s="9">
+        <v>0.23</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C110" s="7">
-        <v>93.78</v>
+        <v>-34.16</v>
       </c>
       <c r="D110" s="7">
-        <v>93.19</v>
-      </c>
-      <c r="E110" s="9">
-        <v>-0.59</v>
+        <v>-35.25</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C111" s="7">
-        <v>51.17</v>
+        <v>-6.94</v>
       </c>
       <c r="D111" s="7">
-        <v>51</v>
-      </c>
-      <c r="E111" s="9">
-        <v>-0.17</v>
+        <v>-7.36</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C112" s="7">
-        <v>132.78</v>
+        <v>-0.16</v>
       </c>
       <c r="D112" s="7">
-        <v>132.37</v>
-      </c>
-      <c r="E112" s="9">
-        <v>-0.41</v>
+        <v>-0.99</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="7">
-        <v>137.09</v>
+        <v>599.5700000000001</v>
       </c>
       <c r="D113" s="7">
-        <v>136.73</v>
-      </c>
-      <c r="E113" s="9">
-        <v>-0.36</v>
+        <v>596.79</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="7">
-        <v>472</v>
+        <v>60.04</v>
       </c>
       <c r="D114" s="7">
-        <v>475.86</v>
+        <v>59.76</v>
       </c>
       <c r="E114" s="8">
-        <v>3.86</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>968.17</v>
+        <v>93.19</v>
       </c>
       <c r="D115" s="7">
-        <v>965.09</v>
-      </c>
-      <c r="E115" s="9">
-        <v>-3.08</v>
+        <v>92.59</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>33.93</v>
+        <v>51</v>
       </c>
       <c r="D116" s="7">
-        <v>33.79</v>
-      </c>
-      <c r="E116" s="9">
-        <v>-0.14</v>
+        <v>50.61</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>33.92</v>
+        <v>132.37</v>
       </c>
       <c r="D117" s="7">
-        <v>33.76</v>
-      </c>
-      <c r="E117" s="9">
-        <v>-0.16</v>
+        <v>130.05</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>804.14</v>
+        <v>136.73</v>
       </c>
       <c r="D118" s="7">
-        <v>806.9</v>
+        <v>134.63</v>
       </c>
       <c r="E118" s="8">
-        <v>2.76</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>276.94</v>
+        <v>475.86</v>
       </c>
       <c r="D119" s="7">
-        <v>277.02</v>
+        <v>472.5</v>
       </c>
       <c r="E119" s="8">
-        <v>0.08</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>269.9</v>
+        <v>965.09</v>
       </c>
       <c r="D120" s="7">
-        <v>269.92</v>
+        <v>959.2</v>
       </c>
       <c r="E120" s="8">
-        <v>0.02</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>264.78</v>
+        <v>33.79</v>
       </c>
       <c r="D121" s="7">
-        <v>264.05</v>
-      </c>
-      <c r="E121" s="9">
-        <v>-0.73</v>
+        <v>33.68</v>
+      </c>
+      <c r="E121" s="8">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>275.46</v>
+        <v>33.76</v>
       </c>
       <c r="D122" s="7">
-        <v>275.6</v>
+        <v>33.71</v>
       </c>
       <c r="E122" s="8">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>95.97</v>
+        <v>806.9</v>
       </c>
       <c r="D123" s="7">
-        <v>96.91</v>
+        <v>805.78</v>
       </c>
       <c r="E123" s="8">
-        <v>0.9399999999999999</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>281.14</v>
+        <v>277.02</v>
       </c>
       <c r="D124" s="7">
-        <v>283.9</v>
+        <v>275.74</v>
       </c>
       <c r="E124" s="8">
-        <v>2.76</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="7">
-        <v>234.57</v>
+        <v>269.92</v>
       </c>
       <c r="D125" s="7">
-        <v>235.87</v>
+        <v>268.27</v>
       </c>
       <c r="E125" s="8">
-        <v>1.3</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="7">
-        <v>261.66</v>
+        <v>264.05</v>
       </c>
       <c r="D126" s="7">
-        <v>261.7</v>
+        <v>262.89</v>
       </c>
       <c r="E126" s="8">
-        <v>0.04</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C127" s="7">
-        <v>795.3200000000001</v>
+        <v>275.6</v>
       </c>
       <c r="D127" s="7">
-        <v>802</v>
+        <v>274.23</v>
       </c>
       <c r="E127" s="8">
-        <v>6.68</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C128" s="7">
-        <v>16</v>
+        <v>96.91</v>
       </c>
       <c r="D128" s="7">
-        <v>27</v>
+        <v>96.08</v>
       </c>
       <c r="E128" s="8">
-        <v>11</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C129" s="7">
-        <v>94</v>
+        <v>283.9</v>
       </c>
       <c r="D129" s="7">
-        <v>89</v>
+        <v>284.57</v>
       </c>
       <c r="E129" s="9">
-        <v>-5</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C130" s="7">
-        <v>89</v>
+        <v>235.87</v>
       </c>
       <c r="D130" s="7">
-        <v>94</v>
+        <v>231.97</v>
       </c>
       <c r="E130" s="8">
-        <v>5</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C131" s="7">
-        <v>27</v>
+        <v>261.7</v>
       </c>
       <c r="D131" s="7">
-        <v>32</v>
+        <v>260.51</v>
       </c>
       <c r="E131" s="8">
-        <v>5</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C132" s="7">
-        <v>58</v>
+        <v>802</v>
       </c>
       <c r="D132" s="7">
-        <v>42</v>
-      </c>
-      <c r="E132" s="9">
-        <v>-16</v>
+        <v>795.26</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-6.74</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C133" s="7">
+        <v>27</v>
+      </c>
+      <c r="D133" s="7">
         <v>32</v>
       </c>
-      <c r="D133" s="7">
-        <v>22</v>
-      </c>
       <c r="E133" s="9">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="7">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D134" s="7">
-        <v>16</v>
-      </c>
-      <c r="E134" s="9">
-        <v>-6</v>
+        <v>27</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="7">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="D135" s="7">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E135" s="9">
-        <v>-5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C136" s="7">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D136" s="7">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E136" s="8">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C137" s="7">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="D137" s="7">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E137" s="9">
-        <v>-16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C138" s="7">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="D138" s="7">
-        <v>58</v>
-      </c>
-      <c r="E138" s="8">
-        <v>21</v>
+        <v>78</v>
+      </c>
+      <c r="E138" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C139" s="7">
+        <v>58</v>
+      </c>
+      <c r="D139" s="7">
         <v>42</v>
       </c>
-      <c r="D139" s="7">
-        <v>47</v>
-      </c>
       <c r="E139" s="8">
-        <v>5</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -5668,13 +5732,13 @@
         <v>13</v>
       </c>
       <c r="C140" s="7">
+        <v>78</v>
+      </c>
+      <c r="D140" s="7">
         <v>73</v>
       </c>
-      <c r="D140" s="7">
-        <v>78</v>
-      </c>
       <c r="E140" s="8">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -5685,13 +5749,13 @@
         <v>24</v>
       </c>
       <c r="C141" s="7">
-        <v>49.9</v>
+        <v>56.25</v>
       </c>
       <c r="D141" s="7">
-        <v>56.25</v>
+        <v>51.88</v>
       </c>
       <c r="E141" s="8">
-        <v>6.35</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -5702,13 +5766,13 @@
         <v>24</v>
       </c>
       <c r="C142" s="7">
-        <v>48.24</v>
+        <v>53.98</v>
       </c>
       <c r="D142" s="7">
-        <v>53.98</v>
+        <v>50.09</v>
       </c>
       <c r="E142" s="8">
-        <v>5.74</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -5719,13 +5783,13 @@
         <v>24</v>
       </c>
       <c r="C143" s="7">
-        <v>40.81</v>
+        <v>36.42</v>
       </c>
       <c r="D143" s="7">
-        <v>36.42</v>
-      </c>
-      <c r="E143" s="9">
-        <v>-4.39</v>
+        <v>32.59</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -5736,13 +5800,13 @@
         <v>24</v>
       </c>
       <c r="C144" s="7">
-        <v>37.7</v>
+        <v>36.18</v>
       </c>
       <c r="D144" s="7">
-        <v>36.18</v>
-      </c>
-      <c r="E144" s="9">
-        <v>-1.52</v>
+        <v>32.9</v>
+      </c>
+      <c r="E144" s="8">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -5753,13 +5817,13 @@
         <v>24</v>
       </c>
       <c r="C145" s="7">
-        <v>78.06</v>
+        <v>75.98</v>
       </c>
       <c r="D145" s="7">
-        <v>75.98</v>
-      </c>
-      <c r="E145" s="9">
-        <v>-2.08</v>
+        <v>65.37</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-10.61</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -5770,13 +5834,13 @@
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>77.65000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="D146" s="7">
-        <v>75.87</v>
-      </c>
-      <c r="E146" s="9">
-        <v>-1.78</v>
+        <v>66.34999999999999</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-9.52</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -5787,13 +5851,13 @@
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>35.78</v>
+        <v>41.49</v>
       </c>
       <c r="D147" s="7">
-        <v>41.49</v>
+        <v>38.3</v>
       </c>
       <c r="E147" s="8">
-        <v>5.71</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -5804,13 +5868,13 @@
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>48.26</v>
+        <v>45.51</v>
       </c>
       <c r="D148" s="7">
-        <v>45.51</v>
-      </c>
-      <c r="E148" s="9">
-        <v>-2.75</v>
+        <v>40.73</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-4.78</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -5821,13 +5885,13 @@
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>52.63</v>
+        <v>50.87</v>
       </c>
       <c r="D149" s="7">
-        <v>50.87</v>
-      </c>
-      <c r="E149" s="9">
-        <v>-1.76</v>
+        <v>49.47</v>
+      </c>
+      <c r="E149" s="8">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -5838,13 +5902,13 @@
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>52.12</v>
+        <v>50.15</v>
       </c>
       <c r="D150" s="7">
-        <v>50.15</v>
-      </c>
-      <c r="E150" s="9">
-        <v>-1.97</v>
+        <v>49.52</v>
+      </c>
+      <c r="E150" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -5855,13 +5919,13 @@
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>59.3</v>
+        <v>62.08</v>
       </c>
       <c r="D151" s="7">
-        <v>62.08</v>
+        <v>60.28</v>
       </c>
       <c r="E151" s="8">
-        <v>2.78</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -5872,13 +5936,13 @@
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>51.36</v>
+        <v>51.64</v>
       </c>
       <c r="D152" s="7">
-        <v>51.64</v>
+        <v>47.01</v>
       </c>
       <c r="E152" s="8">
-        <v>0.28</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -5889,13 +5953,13 @@
         <v>24</v>
       </c>
       <c r="C153" s="7">
-        <v>53.03</v>
+        <v>53.1</v>
       </c>
       <c r="D153" s="7">
-        <v>53.1</v>
+        <v>46.62</v>
       </c>
       <c r="E153" s="8">
-        <v>0.07000000000000001</v>
+        <v>-6.48</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -5906,13 +5970,13 @@
         <v>24</v>
       </c>
       <c r="C154" s="7">
-        <v>52.21</v>
+        <v>49.65</v>
       </c>
       <c r="D154" s="7">
-        <v>49.65</v>
-      </c>
-      <c r="E154" s="9">
-        <v>-2.56</v>
+        <v>45.8</v>
+      </c>
+      <c r="E154" s="8">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -5923,13 +5987,13 @@
         <v>24</v>
       </c>
       <c r="C155" s="7">
-        <v>51.15</v>
+        <v>51.67</v>
       </c>
       <c r="D155" s="7">
-        <v>51.67</v>
+        <v>46.52</v>
       </c>
       <c r="E155" s="8">
-        <v>0.52</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -5940,13 +6004,13 @@
         <v>24</v>
       </c>
       <c r="C156" s="7">
-        <v>51.5</v>
+        <v>55.95</v>
       </c>
       <c r="D156" s="7">
-        <v>55.95</v>
+        <v>51.46</v>
       </c>
       <c r="E156" s="8">
-        <v>4.45</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -5957,13 +6021,13 @@
         <v>24</v>
       </c>
       <c r="C157" s="7">
-        <v>49.57</v>
+        <v>56.54</v>
       </c>
       <c r="D157" s="7">
-        <v>56.54</v>
-      </c>
-      <c r="E157" s="8">
-        <v>6.97</v>
+        <v>58.05</v>
+      </c>
+      <c r="E157" s="9">
+        <v>1.51</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -5974,13 +6038,13 @@
         <v>24</v>
       </c>
       <c r="C158" s="7">
-        <v>61.54</v>
+        <v>62.74</v>
       </c>
       <c r="D158" s="7">
-        <v>62.74</v>
+        <v>56.97</v>
       </c>
       <c r="E158" s="8">
-        <v>1.2</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -5991,13 +6055,13 @@
         <v>24</v>
       </c>
       <c r="C159" s="7">
-        <v>51.13</v>
+        <v>51.28</v>
       </c>
       <c r="D159" s="7">
-        <v>51.28</v>
+        <v>46.67</v>
       </c>
       <c r="E159" s="8">
-        <v>0.15</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6008,13 +6072,13 @@
         <v>24</v>
       </c>
       <c r="C160" s="7">
-        <v>56.5</v>
+        <v>62.47</v>
       </c>
       <c r="D160" s="7">
-        <v>62.47</v>
+        <v>54.37</v>
       </c>
       <c r="E160" s="8">
-        <v>5.97</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -6025,13 +6089,13 @@
         <v>31</v>
       </c>
       <c r="C161" s="7">
-        <v>0.39</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D161" s="7">
-        <v>73.90000000000001</v>
+        <v>-12.45</v>
       </c>
       <c r="E161" s="8">
-        <v>73.51000000000001</v>
+        <v>-86.34999999999999</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6042,13 +6106,13 @@
         <v>31</v>
       </c>
       <c r="C162" s="7">
-        <v>1694.46</v>
+        <v>35.76</v>
       </c>
       <c r="D162" s="7">
-        <v>35.76</v>
+        <v>351.47</v>
       </c>
       <c r="E162" s="9">
-        <v>-1658.7</v>
+        <v>315.71</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -6059,13 +6123,13 @@
         <v>31</v>
       </c>
       <c r="C163" s="7">
-        <v>-46.16</v>
+        <v>22.62</v>
       </c>
       <c r="D163" s="7">
-        <v>22.62</v>
-      </c>
-      <c r="E163" s="8">
-        <v>68.78</v>
+        <v>34.42</v>
+      </c>
+      <c r="E163" s="9">
+        <v>11.8</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6076,13 +6140,13 @@
         <v>31</v>
       </c>
       <c r="C164" s="7">
-        <v>-61.97</v>
+        <v>7.3</v>
       </c>
       <c r="D164" s="7">
-        <v>7.3</v>
+        <v>-10.56</v>
       </c>
       <c r="E164" s="8">
-        <v>69.27</v>
+        <v>-17.86</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -6093,13 +6157,13 @@
         <v>31</v>
       </c>
       <c r="C165" s="7">
-        <v>63.78</v>
+        <v>-9.65</v>
       </c>
       <c r="D165" s="7">
-        <v>-9.65</v>
+        <v>69.98</v>
       </c>
       <c r="E165" s="9">
-        <v>-73.43000000000001</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -6110,13 +6174,13 @@
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>102.26</v>
+        <v>-45.28</v>
       </c>
       <c r="D166" s="7">
-        <v>-45.28</v>
+        <v>196.06</v>
       </c>
       <c r="E166" s="9">
-        <v>-147.54</v>
+        <v>241.34</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -6127,13 +6191,13 @@
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>52.21</v>
+        <v>-47.47</v>
       </c>
       <c r="D167" s="7">
-        <v>-47.47</v>
+        <v>-26.35</v>
       </c>
       <c r="E167" s="9">
-        <v>-99.68000000000001</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -6144,13 +6208,13 @@
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>-23.3</v>
+        <v>-17.49</v>
       </c>
       <c r="D168" s="7">
-        <v>-17.49</v>
-      </c>
-      <c r="E168" s="8">
-        <v>5.81</v>
+        <v>51.47</v>
+      </c>
+      <c r="E168" s="9">
+        <v>68.95999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -6161,13 +6225,13 @@
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>-58.31</v>
+        <v>-78.19</v>
       </c>
       <c r="D169" s="7">
-        <v>-78.19</v>
+        <v>-68.06999999999999</v>
       </c>
       <c r="E169" s="9">
-        <v>-19.88</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -6178,13 +6242,13 @@
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>-63.36</v>
+        <v>-56.6</v>
       </c>
       <c r="D170" s="7">
-        <v>-56.6</v>
-      </c>
-      <c r="E170" s="8">
-        <v>6.76</v>
+        <v>-49.98</v>
+      </c>
+      <c r="E170" s="9">
+        <v>6.62</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -6195,13 +6259,13 @@
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-51.01</v>
+        <v>-24.51</v>
       </c>
       <c r="D171" s="7">
-        <v>-24.51</v>
-      </c>
-      <c r="E171" s="8">
-        <v>26.5</v>
+        <v>-4.35</v>
+      </c>
+      <c r="E171" s="9">
+        <v>20.16</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -6212,13 +6276,13 @@
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>-31.22</v>
+        <v>-16.27</v>
       </c>
       <c r="D172" s="7">
-        <v>-16.27</v>
-      </c>
-      <c r="E172" s="8">
-        <v>14.95</v>
+        <v>32.76</v>
+      </c>
+      <c r="E172" s="9">
+        <v>49.03</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -6229,13 +6293,13 @@
         <v>31</v>
       </c>
       <c r="C173" s="7">
-        <v>316.02</v>
+        <v>-77.22</v>
       </c>
       <c r="D173" s="7">
-        <v>-77.22</v>
+        <v>-4.01</v>
       </c>
       <c r="E173" s="9">
-        <v>-393.24</v>
+        <v>73.20999999999999</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -6246,13 +6310,13 @@
         <v>31</v>
       </c>
       <c r="C174" s="7">
-        <v>-83.98</v>
+        <v>-38.14</v>
       </c>
       <c r="D174" s="7">
-        <v>-38.14</v>
+        <v>-88.36</v>
       </c>
       <c r="E174" s="8">
-        <v>45.84</v>
+        <v>-50.22</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -6263,13 +6327,13 @@
         <v>31</v>
       </c>
       <c r="C175" s="7">
-        <v>-33.03</v>
+        <v>-66.22</v>
       </c>
       <c r="D175" s="7">
-        <v>-66.22</v>
+        <v>-42.72</v>
       </c>
       <c r="E175" s="9">
-        <v>-33.19</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -6280,13 +6344,13 @@
         <v>31</v>
       </c>
       <c r="C176" s="7">
-        <v>-12.59</v>
+        <v>-19.06</v>
       </c>
       <c r="D176" s="7">
-        <v>-19.06</v>
-      </c>
-      <c r="E176" s="9">
-        <v>-6.47</v>
+        <v>-58.74</v>
+      </c>
+      <c r="E176" s="8">
+        <v>-39.68</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -6297,13 +6361,13 @@
         <v>31</v>
       </c>
       <c r="C177" s="7">
-        <v>-88.66</v>
+        <v>112.73</v>
       </c>
       <c r="D177" s="7">
-        <v>112.73</v>
+        <v>-74.98</v>
       </c>
       <c r="E177" s="8">
-        <v>201.39</v>
+        <v>-187.71</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -6314,13 +6378,13 @@
         <v>31</v>
       </c>
       <c r="C178" s="7">
-        <v>28.91</v>
+        <v>-42.15</v>
       </c>
       <c r="D178" s="7">
-        <v>-42.15</v>
+        <v>11.75</v>
       </c>
       <c r="E178" s="9">
-        <v>-71.06</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -6331,13 +6395,13 @@
         <v>31</v>
       </c>
       <c r="C179" s="7">
-        <v>-55.59</v>
+        <v>-50.08</v>
       </c>
       <c r="D179" s="7">
-        <v>-50.08</v>
-      </c>
-      <c r="E179" s="8">
-        <v>5.51</v>
+        <v>70.25</v>
+      </c>
+      <c r="E179" s="9">
+        <v>120.33</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -6348,19 +6412,19 @@
         <v>31</v>
       </c>
       <c r="C180" s="7">
-        <v>-17.47</v>
+        <v>-25.34</v>
       </c>
       <c r="D180" s="7">
-        <v>-25.34</v>
+        <v>12.57</v>
       </c>
       <c r="E180" s="9">
-        <v>-7.87</v>
+        <v>37.91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6384,28 +6448,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6419,13 +6483,13 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>54</v>
+        <v>49.5</v>
       </c>
       <c r="E2" s="12">
         <v>40</v>
       </c>
       <c r="F2" s="12">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="G2" s="12">
         <v>2.1</v>
@@ -6554,48 +6618,48 @@
         <v>44</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5585</v>
+        <v>0.5455</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3487</v>
+        <v>0.3419</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3145</v>
+        <v>0.3108</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2993</v>
+        <v>0.2955</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2654</v>
+        <v>0.2606</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1562</v>
+        <v>0.1518</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1413</v>
+        <v>0.1381</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1408</v>
+        <v>0.1367</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1078</v>
+        <v>0.1064</v>
       </c>
       <c r="J2" s="15">
-        <v>0.091</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6603,13 +6667,13 @@
         <v>51</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>55</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>53</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>43</v>
@@ -6632,34 +6696,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.091</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="B4" s="15">
-        <v>0.0907</v>
+        <v>0.0888</v>
       </c>
       <c r="C4" s="15">
-        <v>0.0906</v>
+        <v>0.0886</v>
       </c>
       <c r="D4" s="15">
-        <v>0.09039999999999999</v>
+        <v>0.0885</v>
       </c>
       <c r="E4" s="15">
-        <v>0.07719999999999999</v>
+        <v>0.0755</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0553</v>
+        <v>0.0546</v>
       </c>
       <c r="G4" s="15">
-        <v>-0.0012</v>
+        <v>-0.0039</v>
       </c>
       <c r="H4" s="15">
-        <v>-0.0054</v>
+        <v>-0.0068</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.08349999999999999</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.3011</v>
+        <v>-0.3025</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="97">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,31 +226,52 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>53.2 → 48.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>48.5</t>
   </si>
   <si>
     <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.5 → 59.8</t>
-  </si>
-  <si>
-    <t>49.5</t>
-  </si>
-  <si>
-    <t>59.8</t>
-  </si>
-  <si>
-    <t>49.5 → 60.2</t>
-  </si>
-  <si>
-    <t>60.2</t>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>53.6 → 44.7</t>
+  </si>
+  <si>
+    <t>53.6</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>51.2 → 46.7</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>46.7</t>
+  </si>
+  <si>
+    <t>53.9 → 46.5</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>46.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -336,14 +357,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -376,13 +397,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,8 +483,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -975,10 +996,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>596.0599999999999</v>
+        <v>595.58</v>
       </c>
       <c r="D2">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -987,43 +1008,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-6.26</v>
+        <v>-6.33</v>
       </c>
       <c r="H2">
-        <v>14.43</v>
+        <v>14.34</v>
       </c>
       <c r="I2">
-        <v>-0.28</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K2">
-        <v>7.22</v>
+        <v>6.42</v>
       </c>
       <c r="L2">
-        <v>5.86</v>
+        <v>6.97</v>
       </c>
       <c r="M2">
-        <v>10.23</v>
+        <v>10.16</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>596.4400000000001</v>
+        <v>596.61</v>
       </c>
       <c r="Q2">
-        <v>596.6900000000001</v>
+        <v>596.6</v>
       </c>
       <c r="R2">
-        <v>596.59</v>
+        <v>596.52</v>
       </c>
       <c r="S2">
-        <v>592.98</v>
+        <v>592.95</v>
       </c>
       <c r="T2">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1038,34 +1059,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.76</v>
+        <v>50</v>
       </c>
       <c r="Z2">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="AA2">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AB2">
-        <v>-0.12</v>
+        <v>-0.19</v>
       </c>
       <c r="AC2">
-        <v>62.25</v>
+        <v>38.32</v>
       </c>
       <c r="AD2">
-        <v>55.86</v>
+        <v>52.83</v>
       </c>
       <c r="AE2">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AF2">
-        <v>-7.33</v>
+        <v>-42.27</v>
       </c>
       <c r="AG2">
-        <v>600.26</v>
+        <v>600.1900000000001</v>
       </c>
       <c r="AH2">
-        <v>593.13</v>
+        <v>593.02</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1074,7 +1095,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>45.98</v>
+        <v>40.38</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1085,10 +1106,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>59.65</v>
       </c>
       <c r="D3">
-        <v>0.4</v>
+        <v>-0.58</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1097,43 +1118,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.58</v>
+        <v>-90.64</v>
       </c>
       <c r="H3">
-        <v>15.12</v>
+        <v>14.45</v>
       </c>
       <c r="I3">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="J3">
-        <v>1.16</v>
+        <v>0.32</v>
       </c>
       <c r="K3">
-        <v>7.95</v>
+        <v>6.46</v>
       </c>
       <c r="L3">
-        <v>-89.34999999999999</v>
+        <v>-89.31</v>
       </c>
       <c r="M3">
-        <v>-30.44</v>
+        <v>-30.52</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.79</v>
+        <v>59.81</v>
       </c>
       <c r="Q3">
-        <v>59.84</v>
+        <v>59.83</v>
       </c>
       <c r="R3">
-        <v>59.82</v>
+        <v>59.81</v>
       </c>
       <c r="S3">
-        <v>264.86</v>
+        <v>262.14</v>
       </c>
       <c r="T3">
-        <v>-77.34999999999999</v>
+        <v>-77.23999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1148,34 +1169,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>53.2</v>
+        <v>48.45</v>
       </c>
       <c r="Z3">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AA3">
         <v>0.02</v>
       </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>79.53</v>
+        <v>57.1</v>
       </c>
       <c r="AD3">
-        <v>60.16</v>
+        <v>64.58</v>
       </c>
       <c r="AE3">
         <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>-52.53</v>
+        <v>-75.20999999999999</v>
       </c>
       <c r="AG3">
         <v>60.29</v>
       </c>
       <c r="AH3">
-        <v>59.4</v>
+        <v>59.38</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1184,7 +1205,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>20.71</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1195,10 +1216,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>92.76000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="D4">
-        <v>0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1207,43 +1228,43 @@
         <v>87.83</v>
       </c>
       <c r="G4">
-        <v>-14.75</v>
+        <v>-14.92</v>
       </c>
       <c r="H4">
-        <v>5.61</v>
+        <v>5.41</v>
       </c>
       <c r="I4">
-        <v>-1.6</v>
+        <v>-1.58</v>
       </c>
       <c r="J4">
-        <v>-1.92</v>
+        <v>-2.45</v>
       </c>
       <c r="K4">
-        <v>-7.53</v>
+        <v>-7.99</v>
       </c>
       <c r="L4">
-        <v>4.74</v>
+        <v>5.36</v>
       </c>
       <c r="M4">
-        <v>29.21</v>
+        <v>28.99</v>
       </c>
       <c r="N4">
         <v>32</v>
       </c>
       <c r="P4">
-        <v>93.28</v>
+        <v>92.98</v>
       </c>
       <c r="Q4">
-        <v>93.88</v>
+        <v>93.77</v>
       </c>
       <c r="R4">
-        <v>95.43000000000001</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="S4">
         <v>97.95</v>
       </c>
       <c r="T4">
-        <v>-5.29</v>
+        <v>-5.48</v>
       </c>
       <c r="U4" t="s">
         <v>59</v>
@@ -1258,34 +1279,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.69</v>
+        <v>33.5</v>
       </c>
       <c r="Z4">
-        <v>-0.72</v>
+        <v>-0.74</v>
       </c>
       <c r="AA4">
         <v>-0.72</v>
       </c>
       <c r="AB4">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="AC4">
-        <v>24.34</v>
+        <v>17.16</v>
       </c>
       <c r="AD4">
-        <v>43.01</v>
+        <v>26.95</v>
       </c>
       <c r="AE4">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AF4">
-        <v>3.42</v>
+        <v>-42.01</v>
       </c>
       <c r="AG4">
-        <v>95.09999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="AH4">
-        <v>92.66</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="AI4">
         <v>97.98</v>
@@ -1294,7 +1315,7 @@
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>16.55</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1305,10 +1326,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>50.34</v>
+        <v>50.1</v>
       </c>
       <c r="D5">
-        <v>-0.53</v>
+        <v>-0.48</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1317,43 +1338,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-17.48</v>
+        <v>-17.87</v>
       </c>
       <c r="H5">
-        <v>3.43</v>
+        <v>2.94</v>
       </c>
       <c r="I5">
-        <v>-1.68</v>
+        <v>-1.76</v>
       </c>
       <c r="J5">
-        <v>-5.43</v>
+        <v>-4.97</v>
       </c>
       <c r="K5">
-        <v>-3.54</v>
+        <v>-2.94</v>
       </c>
       <c r="L5">
-        <v>-16.16</v>
+        <v>-15.47</v>
       </c>
       <c r="M5">
-        <v>5.13</v>
+        <v>4.92</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>50.82</v>
+        <v>50.64</v>
       </c>
       <c r="Q5">
-        <v>51.95</v>
+        <v>51.81</v>
       </c>
       <c r="R5">
-        <v>52.47</v>
+        <v>52.42</v>
       </c>
       <c r="S5">
-        <v>54.28</v>
+        <v>54.24</v>
       </c>
       <c r="T5">
-        <v>-7.27</v>
+        <v>-7.63</v>
       </c>
       <c r="U5" t="s">
         <v>59</v>
@@ -1368,43 +1389,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>30.82</v>
+        <v>29.06</v>
       </c>
       <c r="Z5">
-        <v>-0.5600000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="AA5">
-        <v>-0.4</v>
+        <v>-0.45</v>
       </c>
       <c r="AB5">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AC5">
-        <v>7.46</v>
+        <v>0.85</v>
       </c>
       <c r="AD5">
-        <v>14.63</v>
+        <v>8.25</v>
       </c>
       <c r="AE5">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AF5">
-        <v>7.13</v>
+        <v>3.73</v>
       </c>
       <c r="AG5">
-        <v>53.85</v>
+        <v>53.81</v>
       </c>
       <c r="AH5">
-        <v>50.06</v>
+        <v>49.81</v>
       </c>
       <c r="AI5">
-        <v>53.4</v>
+        <v>53.21</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>24.5</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1415,55 +1436,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>130.85</v>
+        <v>127.32</v>
       </c>
       <c r="D6">
-        <v>0.62</v>
+        <v>-2.7</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>84.42</v>
+        <v>85.34</v>
       </c>
       <c r="G6">
-        <v>-10.7</v>
+        <v>-13.11</v>
       </c>
       <c r="H6">
-        <v>55</v>
+        <v>49.19</v>
       </c>
       <c r="I6">
-        <v>-0.36</v>
+        <v>-4.29</v>
       </c>
       <c r="J6">
-        <v>11.49</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K6">
-        <v>1.69</v>
+        <v>-0.25</v>
       </c>
       <c r="L6">
-        <v>56.09</v>
+        <v>50.82</v>
       </c>
       <c r="M6">
-        <v>26.15</v>
+        <v>25.54</v>
       </c>
       <c r="N6">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P6">
-        <v>131.81</v>
+        <v>130.67</v>
       </c>
       <c r="Q6">
-        <v>126.17</v>
+        <v>126.67</v>
       </c>
       <c r="R6">
-        <v>120.94</v>
+        <v>121.06</v>
       </c>
       <c r="S6">
-        <v>121.06</v>
+        <v>121.17</v>
       </c>
       <c r="T6">
-        <v>8.09</v>
+        <v>5.08</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -1478,34 +1499,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>67.08</v>
+        <v>54.35</v>
       </c>
       <c r="Z6">
-        <v>3.19</v>
+        <v>2.81</v>
       </c>
       <c r="AA6">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AB6">
-        <v>0.43</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>29.27</v>
+        <v>4.1</v>
       </c>
       <c r="AD6">
-        <v>58.11</v>
+        <v>29.74</v>
       </c>
       <c r="AE6">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AF6">
-        <v>-1.7</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AG6">
-        <v>135.73</v>
+        <v>135.27</v>
       </c>
       <c r="AH6">
-        <v>116.61</v>
+        <v>118.08</v>
       </c>
       <c r="AI6">
         <v>127.28</v>
@@ -1514,7 +1535,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>38.28</v>
+        <v>36.03</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1525,55 +1546,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>135.29</v>
+        <v>131.82</v>
       </c>
       <c r="D7">
-        <v>0.49</v>
+        <v>-2.56</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>87.09</v>
+        <v>88.03</v>
       </c>
       <c r="G7">
-        <v>-10.63</v>
+        <v>-12.92</v>
       </c>
       <c r="H7">
-        <v>55.35</v>
+        <v>49.74</v>
       </c>
       <c r="I7">
-        <v>-0.24</v>
+        <v>-4.15</v>
       </c>
       <c r="J7">
-        <v>11.55</v>
+        <v>8.92</v>
       </c>
       <c r="K7">
-        <v>1.11</v>
+        <v>-0.08</v>
       </c>
       <c r="L7">
-        <v>56.44</v>
+        <v>51.36</v>
       </c>
       <c r="M7">
-        <v>34.36</v>
+        <v>33.18</v>
       </c>
       <c r="N7">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>136.25</v>
+        <v>135.11</v>
       </c>
       <c r="Q7">
-        <v>130.45</v>
+        <v>130.99</v>
       </c>
       <c r="R7">
-        <v>124.99</v>
+        <v>125.13</v>
       </c>
       <c r="S7">
-        <v>125.07</v>
+        <v>125.18</v>
       </c>
       <c r="T7">
-        <v>8.17</v>
+        <v>5.3</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -1588,34 +1609,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>67.72</v>
+        <v>55.03</v>
       </c>
       <c r="Z7">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="AA7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AB7">
-        <v>0.44</v>
+        <v>0.05</v>
       </c>
       <c r="AC7">
-        <v>26.92</v>
+        <v>3.41</v>
       </c>
       <c r="AD7">
-        <v>54.97</v>
+        <v>27.55</v>
       </c>
       <c r="AE7">
-        <v>3.53</v>
+        <v>3.63</v>
       </c>
       <c r="AF7">
-        <v>-9.300000000000001</v>
+        <v>37.52</v>
       </c>
       <c r="AG7">
-        <v>140.3</v>
+        <v>139.82</v>
       </c>
       <c r="AH7">
-        <v>120.61</v>
+        <v>122.15</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1624,7 +1645,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>42.52</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1635,10 +1656,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>473.21</v>
+        <v>470.43</v>
       </c>
       <c r="D8">
-        <v>0.15</v>
+        <v>-0.59</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1647,46 +1668,46 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-16.44</v>
+        <v>-16.94</v>
       </c>
       <c r="H8">
-        <v>4.97</v>
+        <v>4.35</v>
       </c>
       <c r="I8">
-        <v>-2.07</v>
+        <v>-0.85</v>
       </c>
       <c r="J8">
-        <v>-4.46</v>
+        <v>-5.46</v>
       </c>
       <c r="K8">
-        <v>-9.380000000000001</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L8">
-        <v>2.83</v>
+        <v>2.22</v>
       </c>
       <c r="M8">
-        <v>7.72</v>
+        <v>7.33</v>
       </c>
       <c r="N8">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="P8">
-        <v>473.6</v>
+        <v>472.8</v>
       </c>
       <c r="Q8">
-        <v>482.02</v>
+        <v>480.71</v>
       </c>
       <c r="R8">
-        <v>481.4</v>
+        <v>481.22</v>
       </c>
       <c r="S8">
-        <v>509.14</v>
+        <v>508.83</v>
       </c>
       <c r="T8">
-        <v>-7.06</v>
+        <v>-7.55</v>
       </c>
       <c r="U8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1695,46 +1716,46 @@
         <v>59</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.36</v>
+        <v>36.7</v>
       </c>
       <c r="Z8">
-        <v>-3.44</v>
+        <v>-3.76</v>
       </c>
       <c r="AA8">
-        <v>-2.34</v>
+        <v>-2.63</v>
       </c>
       <c r="AB8">
-        <v>-1.09</v>
+        <v>-1.14</v>
       </c>
       <c r="AC8">
-        <v>28.45</v>
+        <v>18.26</v>
       </c>
       <c r="AD8">
-        <v>19.87</v>
+        <v>21.7</v>
       </c>
       <c r="AE8">
-        <v>10.19</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AF8">
-        <v>-37.07</v>
+        <v>-17.48</v>
       </c>
       <c r="AG8">
-        <v>494.96</v>
+        <v>492.69</v>
       </c>
       <c r="AH8">
-        <v>469.08</v>
+        <v>468.73</v>
       </c>
       <c r="AI8">
-        <v>502.73</v>
+        <v>500.77</v>
       </c>
       <c r="AJ8" t="s">
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>22.91</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1745,10 +1766,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>955.87</v>
+        <v>953.22</v>
       </c>
       <c r="D9">
-        <v>-0.35</v>
+        <v>-0.28</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1757,85 +1778,85 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-5.25</v>
+        <v>-5.52</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="I9">
-        <v>-1.25</v>
+        <v>-1.33</v>
       </c>
       <c r="J9">
-        <v>-1.33</v>
+        <v>-1.93</v>
       </c>
       <c r="K9">
-        <v>0.22</v>
+        <v>-0.03</v>
       </c>
       <c r="L9">
-        <v>2.86</v>
+        <v>3.51</v>
       </c>
       <c r="M9">
-        <v>14.83</v>
+        <v>14.42</v>
       </c>
       <c r="N9">
         <v>58</v>
       </c>
       <c r="P9">
-        <v>962.89</v>
+        <v>960.3099999999999</v>
       </c>
       <c r="Q9">
-        <v>970.38</v>
+        <v>969.4299999999999</v>
       </c>
       <c r="R9">
-        <v>970.29</v>
+        <v>969.65</v>
       </c>
       <c r="S9">
-        <v>965.05</v>
+        <v>964.84</v>
       </c>
       <c r="T9">
-        <v>-0.95</v>
+        <v>-1.2</v>
       </c>
       <c r="U9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>38.28</v>
+        <v>36.4</v>
       </c>
       <c r="Z9">
-        <v>-2.14</v>
+        <v>-2.98</v>
       </c>
       <c r="AA9">
-        <v>-0.34</v>
+        <v>-0.87</v>
       </c>
       <c r="AB9">
-        <v>-1.79</v>
+        <v>-2.11</v>
       </c>
       <c r="AC9">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>8.68</v>
+        <v>4.1</v>
       </c>
       <c r="AE9">
-        <v>10.76</v>
+        <v>10.92</v>
       </c>
       <c r="AF9">
-        <v>86.7</v>
+        <v>-15.06</v>
       </c>
       <c r="AG9">
-        <v>983.98</v>
+        <v>985.01</v>
       </c>
       <c r="AH9">
-        <v>956.77</v>
+        <v>953.86</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1844,7 +1865,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>17.7</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,10 +1876,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>34.63</v>
+        <v>34.32</v>
       </c>
       <c r="D10">
-        <v>2.82</v>
+        <v>-0.9</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1867,43 +1888,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-19.78</v>
+        <v>-20.5</v>
       </c>
       <c r="H10">
-        <v>21</v>
+        <v>19.92</v>
       </c>
       <c r="I10">
-        <v>2.67</v>
+        <v>1.45</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K10">
-        <v>0.61</v>
+        <v>5.37</v>
       </c>
       <c r="L10">
-        <v>-11.66</v>
+        <v>-11.11</v>
       </c>
       <c r="M10">
-        <v>0.18</v>
+        <v>-0.26</v>
       </c>
       <c r="N10">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="P10">
-        <v>33.97</v>
+        <v>34.07</v>
       </c>
       <c r="Q10">
-        <v>34.39</v>
+        <v>34.35</v>
       </c>
       <c r="R10">
-        <v>32.62</v>
+        <v>32.69</v>
       </c>
       <c r="S10">
-        <v>35.5</v>
+        <v>35.48</v>
       </c>
       <c r="T10">
-        <v>-2.46</v>
+        <v>-3.26</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1918,31 +1939,31 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>59.77</v>
+        <v>55.78</v>
       </c>
       <c r="Z10">
         <v>0.27</v>
       </c>
       <c r="AA10">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="AB10">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AC10">
-        <v>18.85</v>
+        <v>33.12</v>
       </c>
       <c r="AD10">
-        <v>11.05</v>
+        <v>19.28</v>
       </c>
       <c r="AE10">
         <v>0.95</v>
       </c>
       <c r="AF10">
-        <v>29.31</v>
+        <v>-50.66</v>
       </c>
       <c r="AG10">
-        <v>35.45</v>
+        <v>35.38</v>
       </c>
       <c r="AH10">
         <v>33.33</v>
@@ -1954,7 +1975,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>27.6</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1965,10 +1986,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>34.7</v>
+        <v>34.32</v>
       </c>
       <c r="D11">
-        <v>2.94</v>
+        <v>-1.1</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1977,43 +1998,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-19.84</v>
+        <v>-20.72</v>
       </c>
       <c r="H11">
-        <v>21.2</v>
+        <v>19.87</v>
       </c>
       <c r="I11">
-        <v>2.45</v>
+        <v>1.18</v>
       </c>
       <c r="J11">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="K11">
-        <v>0.49</v>
+        <v>5.15</v>
       </c>
       <c r="L11">
-        <v>-11.61</v>
+        <v>-11.32</v>
       </c>
       <c r="M11">
-        <v>0.02</v>
+        <v>-0.41</v>
       </c>
       <c r="N11">
         <v>22</v>
       </c>
       <c r="P11">
-        <v>34</v>
+        <v>34.08</v>
       </c>
       <c r="Q11">
-        <v>34.43</v>
+        <v>34.39</v>
       </c>
       <c r="R11">
-        <v>32.64</v>
+        <v>32.71</v>
       </c>
       <c r="S11">
-        <v>35.57</v>
+        <v>35.54</v>
       </c>
       <c r="T11">
-        <v>-2.44</v>
+        <v>-3.43</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2028,31 +2049,31 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>60.19</v>
+        <v>55.35</v>
       </c>
       <c r="Z11">
         <v>0.27</v>
       </c>
       <c r="AA11">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="AB11">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AC11">
-        <v>20.9</v>
+        <v>33.92</v>
       </c>
       <c r="AD11">
-        <v>13.55</v>
+        <v>20.86</v>
       </c>
       <c r="AE11">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AF11">
-        <v>85.15000000000001</v>
+        <v>-14.41</v>
       </c>
       <c r="AG11">
-        <v>35.52</v>
+        <v>35.45</v>
       </c>
       <c r="AH11">
         <v>33.34</v>
@@ -2064,7 +2085,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>16.24</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2075,10 +2096,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>801.29</v>
+        <v>793.86</v>
       </c>
       <c r="D12">
-        <v>-0.5600000000000001</v>
+        <v>-0.93</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2087,43 +2108,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-0.95</v>
+        <v>-1.87</v>
       </c>
       <c r="H12">
-        <v>22.92</v>
+        <v>21.78</v>
       </c>
       <c r="I12">
-        <v>0.13</v>
+        <v>-0.76</v>
       </c>
       <c r="J12">
-        <v>2.16</v>
+        <v>-0.22</v>
       </c>
       <c r="K12">
-        <v>5.81</v>
+        <v>5.32</v>
       </c>
       <c r="L12">
-        <v>11.51</v>
+        <v>11.89</v>
       </c>
       <c r="M12">
-        <v>13.37</v>
+        <v>12.84</v>
       </c>
       <c r="N12">
         <v>73</v>
       </c>
       <c r="P12">
-        <v>803.61</v>
+        <v>802.39</v>
       </c>
       <c r="Q12">
-        <v>804.89</v>
+        <v>804.5</v>
       </c>
       <c r="R12">
-        <v>789.73</v>
+        <v>789.87</v>
       </c>
       <c r="S12">
-        <v>751.78</v>
+        <v>751.99</v>
       </c>
       <c r="T12">
-        <v>6.59</v>
+        <v>5.57</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2138,34 +2159,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>53.58</v>
+        <v>44.72</v>
       </c>
       <c r="Z12">
-        <v>4.26</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>5.55</v>
+        <v>5.08</v>
       </c>
       <c r="AB12">
-        <v>-1.29</v>
+        <v>-1.88</v>
       </c>
       <c r="AC12">
-        <v>26.27</v>
+        <v>11.34</v>
       </c>
       <c r="AD12">
-        <v>28.75</v>
+        <v>24.42</v>
       </c>
       <c r="AE12">
-        <v>13.44</v>
+        <v>13.7</v>
       </c>
       <c r="AF12">
-        <v>-50.44</v>
+        <v>-4.54</v>
       </c>
       <c r="AG12">
-        <v>811.02</v>
+        <v>812.26</v>
       </c>
       <c r="AH12">
-        <v>798.75</v>
+        <v>796.74</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2174,7 +2195,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>32.47</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2185,10 +2206,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>275.62</v>
+        <v>274.87</v>
       </c>
       <c r="D13">
-        <v>-0.04</v>
+        <v>-0.27</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2197,43 +2218,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-7.37</v>
+        <v>-7.62</v>
       </c>
       <c r="H13">
-        <v>8.75</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I13">
-        <v>-0.41</v>
+        <v>-0.36</v>
       </c>
       <c r="J13">
-        <v>-0.31</v>
+        <v>-0.92</v>
       </c>
       <c r="K13">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="L13">
-        <v>-1.23</v>
+        <v>-0.74</v>
       </c>
       <c r="M13">
-        <v>8.6</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N13">
         <v>47</v>
       </c>
       <c r="P13">
-        <v>276.24</v>
+        <v>276.04</v>
       </c>
       <c r="Q13">
-        <v>277.85</v>
+        <v>277.6</v>
       </c>
       <c r="R13">
-        <v>275.58</v>
+        <v>275.6</v>
       </c>
       <c r="S13">
-        <v>279.21</v>
+        <v>279.12</v>
       </c>
       <c r="T13">
-        <v>-1.28</v>
+        <v>-1.52</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2248,34 +2269,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>46.59</v>
+        <v>43.94</v>
       </c>
       <c r="Z13">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="AA13">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="AB13">
-        <v>-0.41</v>
+        <v>-0.45</v>
       </c>
       <c r="AC13">
-        <v>26.79</v>
+        <v>15.33</v>
       </c>
       <c r="AD13">
-        <v>30.3</v>
+        <v>24.64</v>
       </c>
       <c r="AE13">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="AF13">
-        <v>-37.05</v>
+        <v>-4.61</v>
       </c>
       <c r="AG13">
-        <v>281.44</v>
+        <v>281.3</v>
       </c>
       <c r="AH13">
-        <v>274.26</v>
+        <v>273.91</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2284,7 +2305,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>19.9</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2295,10 +2316,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>268.24</v>
+        <v>267.54</v>
       </c>
       <c r="D14">
-        <v>-0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2307,31 +2328,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-7.38</v>
+        <v>-7.62</v>
       </c>
       <c r="H14">
-        <v>8.789999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="I14">
-        <v>-0.23</v>
+        <v>-0.42</v>
       </c>
       <c r="J14">
-        <v>-0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="K14">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="M14">
-        <v>-9.1</v>
+        <v>-9.34</v>
       </c>
       <c r="P14">
-        <v>269</v>
+        <v>268.77</v>
       </c>
       <c r="Q14">
-        <v>270.29</v>
+        <v>270.06</v>
       </c>
       <c r="R14">
-        <v>268.21</v>
+        <v>268.25</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2343,34 +2364,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>46.51</v>
+        <v>43.88</v>
       </c>
       <c r="Z14">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="AA14">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="AB14">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="AC14">
-        <v>25.63</v>
+        <v>11.09</v>
       </c>
       <c r="AD14">
-        <v>32.61</v>
+        <v>23.81</v>
       </c>
       <c r="AE14">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AF14">
-        <v>-28.59</v>
+        <v>-20.89</v>
       </c>
       <c r="AG14">
-        <v>273.54</v>
+        <v>273.42</v>
       </c>
       <c r="AH14">
-        <v>267.03</v>
+        <v>266.7</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2379,7 +2400,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>50.94</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2390,10 +2411,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>262.96</v>
+        <v>261.92</v>
       </c>
       <c r="D15">
-        <v>0.03</v>
+        <v>-0.4</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2402,43 +2423,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-7.51</v>
+        <v>-7.88</v>
       </c>
       <c r="H15">
-        <v>8.880000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I15">
-        <v>-0.46</v>
+        <v>-0.6</v>
       </c>
       <c r="J15">
-        <v>-0.6</v>
+        <v>-1.33</v>
       </c>
       <c r="K15">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="L15">
-        <v>-1.18</v>
+        <v>-0.86</v>
       </c>
       <c r="M15">
-        <v>8.59</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N15">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P15">
-        <v>263.63</v>
+        <v>263.32</v>
       </c>
       <c r="Q15">
-        <v>265.31</v>
+        <v>265.02</v>
       </c>
       <c r="R15">
-        <v>263.22</v>
+        <v>263.23</v>
       </c>
       <c r="S15">
-        <v>266.54</v>
+        <v>266.46</v>
       </c>
       <c r="T15">
-        <v>-1.34</v>
+        <v>-1.7</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2453,34 +2474,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>46.07</v>
+        <v>42.65</v>
       </c>
       <c r="Z15">
-        <v>0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="AA15">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="AB15">
-        <v>-0.43</v>
+        <v>-0.48</v>
       </c>
       <c r="AC15">
-        <v>22.09</v>
+        <v>10.83</v>
       </c>
       <c r="AD15">
-        <v>28.04</v>
+        <v>20.88</v>
       </c>
       <c r="AE15">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="AF15">
-        <v>-62.81</v>
+        <v>-84.19</v>
       </c>
       <c r="AG15">
-        <v>269.02</v>
+        <v>268.84</v>
       </c>
       <c r="AH15">
-        <v>261.61</v>
+        <v>261.2</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2489,7 +2510,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>48.74</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2500,10 +2521,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>274.23</v>
+        <v>273.42</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2512,43 +2533,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-7.35</v>
+        <v>-7.62</v>
       </c>
       <c r="H16">
-        <v>8.81</v>
+        <v>8.49</v>
       </c>
       <c r="I16">
-        <v>-0.36</v>
+        <v>-0.47</v>
       </c>
       <c r="J16">
-        <v>-0.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K16">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="L16">
-        <v>-1.3</v>
+        <v>-0.74</v>
       </c>
       <c r="M16">
-        <v>8.6</v>
+        <v>8.31</v>
       </c>
       <c r="N16">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="P16">
-        <v>274.85</v>
+        <v>274.59</v>
       </c>
       <c r="Q16">
-        <v>276.43</v>
+        <v>276.19</v>
       </c>
       <c r="R16">
-        <v>274.19</v>
+        <v>274.21</v>
       </c>
       <c r="S16">
-        <v>277.82</v>
+        <v>277.73</v>
       </c>
       <c r="T16">
-        <v>-1.29</v>
+        <v>-1.55</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2563,34 +2584,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>46.52</v>
+        <v>43.55</v>
       </c>
       <c r="Z16">
-        <v>0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="AA16">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="AB16">
-        <v>-0.41</v>
+        <v>-0.45</v>
       </c>
       <c r="AC16">
-        <v>24.09</v>
+        <v>11.98</v>
       </c>
       <c r="AD16">
-        <v>28.12</v>
+        <v>21.61</v>
       </c>
       <c r="AE16">
-        <v>3.57</v>
+        <v>3.64</v>
       </c>
       <c r="AF16">
-        <v>27.82</v>
+        <v>34.33</v>
       </c>
       <c r="AG16">
-        <v>280.03</v>
+        <v>279.91</v>
       </c>
       <c r="AH16">
-        <v>272.84</v>
+        <v>272.47</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2599,7 +2620,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>37.05</v>
+        <v>33.73</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2610,10 +2631,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>96.04000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="D17">
-        <v>-0.04</v>
+        <v>-0.91</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2622,25 +2643,25 @@
         <v>75.20999999999999</v>
       </c>
       <c r="G17">
-        <v>-12.59</v>
+        <v>-13.38</v>
       </c>
       <c r="H17">
-        <v>27.7</v>
+        <v>26.54</v>
       </c>
       <c r="I17">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="J17">
-        <v>3.09</v>
+        <v>1.87</v>
       </c>
       <c r="K17">
-        <v>6.58</v>
+        <v>3.87</v>
       </c>
       <c r="L17">
-        <v>25.87</v>
+        <v>26.05</v>
       </c>
       <c r="M17">
-        <v>30.57</v>
+        <v>30.16</v>
       </c>
       <c r="N17">
         <v>84</v>
@@ -2649,16 +2670,16 @@
         <v>96.03</v>
       </c>
       <c r="Q17">
-        <v>96.45</v>
+        <v>96.48</v>
       </c>
       <c r="R17">
-        <v>95.13</v>
+        <v>95.08</v>
       </c>
       <c r="S17">
-        <v>95.87</v>
+        <v>95.88</v>
       </c>
       <c r="T17">
-        <v>0.18</v>
+        <v>-0.74</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2670,37 +2691,37 @@
         <v>59</v>
       </c>
       <c r="X17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>51.25</v>
+        <v>46.71</v>
       </c>
       <c r="Z17">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="AA17">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="AB17">
-        <v>-0.16</v>
+        <v>-0.21</v>
       </c>
       <c r="AC17">
-        <v>33.13</v>
+        <v>17.28</v>
       </c>
       <c r="AD17">
-        <v>29.83</v>
+        <v>27.67</v>
       </c>
       <c r="AE17">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AF17">
-        <v>-71.65000000000001</v>
+        <v>-42.32</v>
       </c>
       <c r="AG17">
-        <v>98.65000000000001</v>
+        <v>98.59</v>
       </c>
       <c r="AH17">
-        <v>94.25</v>
+        <v>94.38</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2709,7 +2730,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>16.38</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2720,10 +2741,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>283.64</v>
+        <v>283.45</v>
       </c>
       <c r="D18">
-        <v>-0.33</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2732,43 +2753,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-4.35</v>
+        <v>-4.41</v>
       </c>
       <c r="H18">
-        <v>15.5</v>
+        <v>15.43</v>
       </c>
       <c r="I18">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="J18">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="K18">
-        <v>5.27</v>
+        <v>6.04</v>
       </c>
       <c r="L18">
-        <v>5.48</v>
+        <v>6.48</v>
       </c>
       <c r="M18">
-        <v>8.58</v>
+        <v>8.52</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>283.13</v>
+        <v>283.34</v>
       </c>
       <c r="Q18">
         <v>281.64</v>
       </c>
       <c r="R18">
-        <v>283.59</v>
+        <v>283.55</v>
       </c>
       <c r="S18">
-        <v>281.28</v>
+        <v>281.27</v>
       </c>
       <c r="T18">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="U18" t="s">
         <v>59</v>
@@ -2783,31 +2804,31 @@
         <v>2</v>
       </c>
       <c r="Y18">
-        <v>55.18</v>
+        <v>54.58</v>
       </c>
       <c r="Z18">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="AA18">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="AB18">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="AC18">
-        <v>94.51000000000001</v>
+        <v>87.89</v>
       </c>
       <c r="AD18">
-        <v>91.75</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="AE18">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="AF18">
-        <v>-97.8</v>
+        <v>-85.13</v>
       </c>
       <c r="AG18">
-        <v>285.81</v>
+        <v>285.79</v>
       </c>
       <c r="AH18">
         <v>277.48</v>
@@ -2819,7 +2840,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>30.74</v>
+        <v>34.03</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2830,55 +2851,55 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>236.12</v>
+        <v>228.47</v>
       </c>
       <c r="D19">
-        <v>1.79</v>
+        <v>-3.24</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>115.58</v>
+        <v>116.32</v>
       </c>
       <c r="G19">
-        <v>-34.09</v>
+        <v>-36.22</v>
       </c>
       <c r="H19">
-        <v>104.29</v>
+        <v>96.42</v>
       </c>
       <c r="I19">
-        <v>-0.89</v>
+        <v>-3.74</v>
       </c>
       <c r="J19">
-        <v>11.42</v>
+        <v>7.95</v>
       </c>
       <c r="K19">
-        <v>-8.33</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L19">
-        <v>106.11</v>
+        <v>97.67</v>
       </c>
       <c r="M19">
-        <v>55.75</v>
+        <v>53.12</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>235.17</v>
+        <v>233.4</v>
       </c>
       <c r="Q19">
-        <v>227.35</v>
+        <v>228.2</v>
       </c>
       <c r="R19">
-        <v>220.81</v>
+        <v>220.76</v>
       </c>
       <c r="S19">
-        <v>230.12</v>
+        <v>230.46</v>
       </c>
       <c r="T19">
-        <v>2.61</v>
+        <v>-0.86</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -2890,37 +2911,37 @@
         <v>59</v>
       </c>
       <c r="X19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>61.07</v>
+        <v>51.35</v>
       </c>
       <c r="Z19">
-        <v>4.16</v>
+        <v>3.61</v>
       </c>
       <c r="AA19">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="AB19">
-        <v>0.9</v>
+        <v>0.28</v>
       </c>
       <c r="AC19">
-        <v>60.19</v>
+        <v>38.2</v>
       </c>
       <c r="AD19">
-        <v>66.43000000000001</v>
+        <v>53.15</v>
       </c>
       <c r="AE19">
-        <v>6.24</v>
+        <v>6.53</v>
       </c>
       <c r="AF19">
-        <v>32.72</v>
+        <v>71.17</v>
       </c>
       <c r="AG19">
-        <v>242.65</v>
+        <v>241.59</v>
       </c>
       <c r="AH19">
-        <v>212.06</v>
+        <v>214.8</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2929,7 +2950,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>34.03</v>
+        <v>31.32</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2940,10 +2961,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>260.49</v>
+        <v>259.76</v>
       </c>
       <c r="D20">
-        <v>-0.01</v>
+        <v>-0.28</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2952,43 +2973,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-7.37</v>
+        <v>-7.63</v>
       </c>
       <c r="H20">
-        <v>8.83</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I20">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="J20">
-        <v>-0.3</v>
+        <v>-1.02</v>
       </c>
       <c r="K20">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="L20">
-        <v>-1.33</v>
+        <v>-0.78</v>
       </c>
       <c r="M20">
-        <v>8.58</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N20">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="P20">
-        <v>261.04</v>
+        <v>260.82</v>
       </c>
       <c r="Q20">
-        <v>262.56</v>
+        <v>262.31</v>
       </c>
       <c r="R20">
-        <v>260.49</v>
+        <v>260.5</v>
       </c>
       <c r="S20">
-        <v>263.93</v>
+        <v>263.84</v>
       </c>
       <c r="T20">
-        <v>-1.3</v>
+        <v>-1.55</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3003,34 +3024,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>46.59</v>
+        <v>43.8</v>
       </c>
       <c r="Z20">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AA20">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="AB20">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AC20">
-        <v>26.46</v>
+        <v>15.08</v>
       </c>
       <c r="AD20">
-        <v>30.12</v>
+        <v>24.21</v>
       </c>
       <c r="AE20">
-        <v>4.39</v>
+        <v>4.3</v>
       </c>
       <c r="AF20">
-        <v>20.09</v>
+        <v>15.89</v>
       </c>
       <c r="AG20">
-        <v>265.92</v>
+        <v>265.76</v>
       </c>
       <c r="AH20">
-        <v>259.19</v>
+        <v>258.87</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3039,7 +3060,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>34.59</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3050,10 +3071,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>794.87</v>
+        <v>787.71</v>
       </c>
       <c r="D21">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3062,43 +3083,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-1.04</v>
+        <v>-1.93</v>
       </c>
       <c r="H21">
-        <v>23.68</v>
+        <v>22.57</v>
       </c>
       <c r="I21">
-        <v>0.11</v>
+        <v>-0.66</v>
       </c>
       <c r="J21">
-        <v>2.08</v>
+        <v>-0.2</v>
       </c>
       <c r="K21">
-        <v>6.01</v>
+        <v>5.27</v>
       </c>
       <c r="L21">
-        <v>11.8</v>
+        <v>12.04</v>
       </c>
       <c r="M21">
-        <v>13.34</v>
+        <v>12.79</v>
       </c>
       <c r="N21">
         <v>78</v>
       </c>
       <c r="P21">
-        <v>796.08</v>
+        <v>795.03</v>
       </c>
       <c r="Q21">
-        <v>797.02</v>
+        <v>796.64</v>
       </c>
       <c r="R21">
-        <v>782.62</v>
+        <v>782.77</v>
       </c>
       <c r="S21">
-        <v>744.9400000000001</v>
+        <v>745.15</v>
       </c>
       <c r="T21">
-        <v>6.7</v>
+        <v>5.71</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3113,34 +3134,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>53.93</v>
+        <v>46.55</v>
       </c>
       <c r="Z21">
-        <v>4.18</v>
+        <v>3.22</v>
       </c>
       <c r="AA21">
-        <v>5.46</v>
+        <v>5.02</v>
       </c>
       <c r="AB21">
-        <v>-1.29</v>
+        <v>-1.8</v>
       </c>
       <c r="AC21">
-        <v>20.8</v>
+        <v>0.67</v>
       </c>
       <c r="AD21">
-        <v>24.44</v>
+        <v>16.02</v>
       </c>
       <c r="AE21">
-        <v>11.52</v>
+        <v>11.81</v>
       </c>
       <c r="AF21">
-        <v>62.2</v>
+        <v>0.48</v>
       </c>
       <c r="AG21">
-        <v>804.86</v>
+        <v>805.5</v>
       </c>
       <c r="AH21">
-        <v>789.17</v>
+        <v>787.78</v>
       </c>
       <c r="AI21">
         <v>773.79</v>
@@ -3149,7 +3170,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>22.7</v>
+        <v>19.96</v>
       </c>
     </row>
   </sheetData>
@@ -3290,7 +3311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3330,1145 +3351,1151 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="E4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="E5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.64</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.52</v>
+      <c r="B12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.53</v>
+        <v>0.84</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.39</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.99</v>
+        <v>1.16</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.43</v>
+        <v>0.32</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.44</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>11.3</v>
+        <v>-1.92</v>
       </c>
       <c r="D15" s="6">
-        <v>11.49</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.19</v>
+        <v>-2.45</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>11.51</v>
+        <v>-5.43</v>
       </c>
       <c r="D16" s="6">
-        <v>11.55</v>
+        <v>-4.97</v>
       </c>
       <c r="E16" s="8">
-        <v>0.04</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.8</v>
+        <v>11.49</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.46</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.66</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.59</v>
+        <v>11.55</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.33</v>
+        <v>8.92</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.74</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.55</v>
+        <v>-4.46</v>
       </c>
       <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.55</v>
+        <v>-5.46</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.4</v>
+        <v>-1.33</v>
       </c>
       <c r="D20" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.63</v>
+        <v>-1.93</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="D21" s="6">
-        <v>2.16</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.68</v>
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-0.03</v>
+        <v>0.23</v>
       </c>
       <c r="D22" s="6">
-        <v>-0.31</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.28</v>
+        <v>0.59</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.14</v>
+        <v>2.16</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.38</v>
+        <v>-0.22</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.24</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.6</v>
+        <v>-0.92</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.24</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-0.07000000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="D25" s="6">
-        <v>-0.29</v>
+        <v>-1.02</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.22</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>3.32</v>
+        <v>-0.6</v>
       </c>
       <c r="D26" s="6">
-        <v>3.09</v>
+        <v>-1.33</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.23</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>1.11</v>
+        <v>-0.29</v>
       </c>
       <c r="D27" s="6">
-        <v>0.91</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.2</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>9.49</v>
+        <v>3.09</v>
       </c>
       <c r="D28" s="6">
-        <v>11.42</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.93</v>
+        <v>1.87</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.03</v>
+        <v>0.91</v>
       </c>
       <c r="D29" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.27</v>
+        <v>1.08</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>1.99</v>
+        <v>11.42</v>
       </c>
       <c r="D30" s="6">
-        <v>2.08</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.09</v>
+        <v>7.95</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.47</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>0.12</v>
+        <v>-0.3</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.28</v>
+        <v>-1.02</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.4</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-0.03</v>
+        <v>2.08</v>
       </c>
       <c r="D32" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.26</v>
+        <v>-0.2</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.02</v>
+        <v>-0.28</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.58</v>
+        <v>0.15</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-1.84</v>
+        <v>0.23</v>
       </c>
       <c r="D34" s="6">
-        <v>-1.68</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.16</v>
+        <v>0.2</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>0.91</v>
+        <v>-1.6</v>
       </c>
       <c r="D35" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.27</v>
+        <v>-1.58</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.02</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>1.17</v>
+        <v>-1.68</v>
       </c>
       <c r="D36" s="6">
-        <v>-0.24</v>
+        <v>-1.76</v>
       </c>
       <c r="E36" s="7">
-        <v>-1.41</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.83</v>
+        <v>-0.36</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.07</v>
+        <v>-4.29</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.24</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-0.91</v>
+        <v>-0.24</v>
       </c>
       <c r="D38" s="6">
-        <v>-1.25</v>
+        <v>-4.15</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.34</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-2.07</v>
       </c>
       <c r="D39" s="6">
-        <v>2.67</v>
+        <v>-0.85</v>
       </c>
       <c r="E39" s="8">
-        <v>3.61</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.06</v>
+        <v>-1.25</v>
       </c>
       <c r="D40" s="6">
-        <v>2.45</v>
-      </c>
-      <c r="E40" s="8">
-        <v>3.51</v>
+        <v>-1.33</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>0.33</v>
+        <v>2.67</v>
       </c>
       <c r="D41" s="6">
-        <v>0.13</v>
+        <v>1.45</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.2</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>-0.3</v>
+        <v>2.45</v>
       </c>
       <c r="D42" s="6">
-        <v>-0.41</v>
+        <v>1.18</v>
       </c>
       <c r="E42" s="7">
-        <v>-0.11</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.42</v>
+        <v>0.13</v>
       </c>
       <c r="D43" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.19</v>
+        <v>-0.76</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="D44" s="6">
-        <v>-0.46</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.04</v>
+        <v>-0.36</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="D45" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.44</v>
+        <v>-0.42</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>1.87</v>
+        <v>-0.46</v>
       </c>
       <c r="D46" s="6">
-        <v>0.46</v>
+        <v>-0.6</v>
       </c>
       <c r="E46" s="7">
-        <v>-1.41</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="6">
-        <v>0.51</v>
+        <v>-0.36</v>
       </c>
       <c r="D47" s="6">
-        <v>-0.89</v>
+        <v>-0.47</v>
       </c>
       <c r="E47" s="7">
-        <v>-1.4</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="6">
-        <v>-0.27</v>
+        <v>0.23</v>
       </c>
       <c r="D48" s="6">
-        <v>-0.41</v>
+        <v>0.04</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.14</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="6">
-        <v>-0.12</v>
+        <v>0.46</v>
       </c>
       <c r="D49" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.23</v>
+        <v>0.37</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C50" s="6">
-        <v>4.8</v>
+        <v>-0.89</v>
       </c>
       <c r="D50" s="6">
-        <v>5.86</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.06</v>
+        <v>-3.74</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51" s="6">
-        <v>-89.53</v>
+        <v>-0.41</v>
       </c>
       <c r="D51" s="6">
-        <v>-89.34999999999999</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.18</v>
+        <v>-0.42</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6">
-        <v>3.29</v>
+        <v>0.11</v>
       </c>
       <c r="D52" s="6">
-        <v>4.74</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.45</v>
+        <v>-0.66</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-14.97</v>
+        <v>5.86</v>
       </c>
       <c r="D53" s="6">
-        <v>-16.16</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.19</v>
+        <v>6.97</v>
+      </c>
+      <c r="E53" s="8">
+        <v>1.11</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>55.75</v>
+        <v>-89.34999999999999</v>
       </c>
       <c r="D54" s="6">
-        <v>56.09</v>
+        <v>-89.31</v>
       </c>
       <c r="E54" s="8">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>56.24</v>
+        <v>4.74</v>
       </c>
       <c r="D55" s="6">
-        <v>56.44</v>
+        <v>5.36</v>
       </c>
       <c r="E55" s="8">
-        <v>0.2</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>1.89</v>
+        <v>-16.16</v>
       </c>
       <c r="D56" s="6">
-        <v>2.83</v>
+        <v>-15.47</v>
       </c>
       <c r="E56" s="8">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>1.71</v>
+        <v>56.09</v>
       </c>
       <c r="D57" s="6">
-        <v>2.86</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.15</v>
+        <v>50.82</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-5.27</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-14.84</v>
+        <v>56.44</v>
       </c>
       <c r="D58" s="6">
-        <v>-11.66</v>
-      </c>
-      <c r="E58" s="8">
-        <v>3.18</v>
+        <v>51.36</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-5.08</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>-14.74</v>
+        <v>2.83</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.61</v>
-      </c>
-      <c r="E59" s="8">
-        <v>3.13</v>
+        <v>2.22</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>10.7</v>
+        <v>2.86</v>
       </c>
       <c r="D60" s="6">
-        <v>11.51</v>
+        <v>3.51</v>
       </c>
       <c r="E60" s="8">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>-2.11</v>
+        <v>-11.66</v>
       </c>
       <c r="D61" s="6">
-        <v>-1.23</v>
+        <v>-11.11</v>
       </c>
       <c r="E61" s="8">
-        <v>0.88</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>-2.1</v>
+        <v>-11.61</v>
       </c>
       <c r="D62" s="6">
-        <v>-1.18</v>
+        <v>-11.32</v>
       </c>
       <c r="E62" s="8">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>-2.16</v>
+        <v>11.51</v>
       </c>
       <c r="D63" s="6">
-        <v>-1.3</v>
+        <v>11.89</v>
       </c>
       <c r="E63" s="8">
-        <v>0.86</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>23.58</v>
+        <v>-1.23</v>
       </c>
       <c r="D64" s="6">
-        <v>25.87</v>
+        <v>-0.74</v>
       </c>
       <c r="E64" s="8">
-        <v>2.29</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>4.69</v>
+        <v>-1.18</v>
       </c>
       <c r="D65" s="6">
-        <v>5.48</v>
+        <v>-0.86</v>
       </c>
       <c r="E65" s="8">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>102.03</v>
+        <v>-1.3</v>
       </c>
       <c r="D66" s="6">
-        <v>106.11</v>
+        <v>-0.74</v>
       </c>
       <c r="E66" s="8">
-        <v>4.08</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-2.18</v>
+        <v>25.87</v>
       </c>
       <c r="D67" s="6">
-        <v>-1.33</v>
+        <v>26.05</v>
       </c>
       <c r="E67" s="8">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>10.56</v>
+        <v>5.48</v>
       </c>
       <c r="D68" s="6">
-        <v>11.8</v>
+        <v>6.48</v>
       </c>
       <c r="E68" s="8">
-        <v>1.24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>7.82</v>
+        <v>106.11</v>
       </c>
       <c r="D69" s="6">
-        <v>7.22</v>
+        <v>97.67</v>
       </c>
       <c r="E69" s="7">
-        <v>-0.6</v>
+        <v>-8.44</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>7.4</v>
+        <v>-1.33</v>
       </c>
       <c r="D70" s="6">
-        <v>7.95</v>
+        <v>-0.78</v>
       </c>
       <c r="E70" s="8">
         <v>0.55</v>
@@ -4476,1759 +4503,1844 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-8.289999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="D71" s="6">
-        <v>-7.53</v>
+        <v>12.04</v>
       </c>
       <c r="E71" s="8">
-        <v>0.76</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-2.2</v>
+        <v>7.22</v>
       </c>
       <c r="D72" s="6">
-        <v>-3.54</v>
+        <v>6.42</v>
       </c>
       <c r="E72" s="7">
-        <v>-1.34</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>2.01</v>
+        <v>7.95</v>
       </c>
       <c r="D73" s="6">
-        <v>1.69</v>
+        <v>6.46</v>
       </c>
       <c r="E73" s="7">
-        <v>-0.32</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>2.18</v>
+        <v>-7.53</v>
       </c>
       <c r="D74" s="6">
-        <v>1.11</v>
+        <v>-7.99</v>
       </c>
       <c r="E74" s="7">
-        <v>-1.07</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>-7.71</v>
+        <v>-3.54</v>
       </c>
       <c r="D75" s="6">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-1.67</v>
+        <v>-2.94</v>
+      </c>
+      <c r="E75" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>0.48</v>
+        <v>1.69</v>
       </c>
       <c r="D76" s="6">
-        <v>0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="E76" s="7">
-        <v>-0.26</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="D77" s="6">
-        <v>0.61</v>
+        <v>-0.08</v>
       </c>
       <c r="E77" s="7">
-        <v>-1.3</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>1.75</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D78" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-1.26</v>
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="E78" s="8">
+        <v>1.24</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>6.7</v>
+        <v>0.22</v>
       </c>
       <c r="D79" s="6">
-        <v>5.81</v>
+        <v>-0.03</v>
       </c>
       <c r="E79" s="7">
-        <v>-0.89</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>3.85</v>
+        <v>0.61</v>
       </c>
       <c r="D80" s="6">
-        <v>3.61</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-0.24</v>
+        <v>5.37</v>
+      </c>
+      <c r="E80" s="8">
+        <v>4.76</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>3.78</v>
+        <v>0.49</v>
       </c>
       <c r="D81" s="6">
-        <v>3.53</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-0.25</v>
+        <v>5.15</v>
+      </c>
+      <c r="E81" s="8">
+        <v>4.66</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>3.79</v>
+        <v>5.81</v>
       </c>
       <c r="D82" s="6">
-        <v>3.58</v>
+        <v>5.32</v>
       </c>
       <c r="E82" s="7">
-        <v>-0.21</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="D83" s="6">
-        <v>3.69</v>
+        <v>3.51</v>
       </c>
       <c r="E83" s="7">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>7.42</v>
+        <v>3.53</v>
       </c>
       <c r="D84" s="6">
-        <v>6.58</v>
+        <v>3.49</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.84</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>7.17</v>
+        <v>3.58</v>
       </c>
       <c r="D85" s="6">
-        <v>5.27</v>
+        <v>3.26</v>
       </c>
       <c r="E85" s="7">
-        <v>-1.9</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="6">
-        <v>-9.199999999999999</v>
+        <v>3.69</v>
       </c>
       <c r="D86" s="6">
-        <v>-8.33</v>
-      </c>
-      <c r="E86" s="8">
-        <v>0.87</v>
+        <v>3.47</v>
+      </c>
+      <c r="E86" s="7">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="6">
-        <v>3.83</v>
+        <v>6.58</v>
       </c>
       <c r="D87" s="6">
-        <v>3.56</v>
+        <v>3.87</v>
       </c>
       <c r="E87" s="7">
-        <v>-0.27</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="6">
-        <v>6.18</v>
+        <v>5.27</v>
       </c>
       <c r="D88" s="6">
-        <v>6.01</v>
-      </c>
-      <c r="E88" s="7">
-        <v>-0.17</v>
+        <v>6.04</v>
+      </c>
+      <c r="E88" s="8">
+        <v>0.77</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89" s="6">
-        <v>-6.14</v>
+        <v>-8.33</v>
       </c>
       <c r="D89" s="6">
-        <v>-6.26</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="E89" s="7">
-        <v>-0.12</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90" s="6">
-        <v>-90.62</v>
+        <v>3.56</v>
       </c>
       <c r="D90" s="6">
-        <v>-90.58</v>
+        <v>3.63</v>
       </c>
       <c r="E90" s="8">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C91" s="6">
-        <v>-14.91</v>
+        <v>6.01</v>
       </c>
       <c r="D91" s="6">
-        <v>-14.75</v>
-      </c>
-      <c r="E91" s="8">
-        <v>0.16</v>
+        <v>5.27</v>
+      </c>
+      <c r="E91" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-17.03</v>
+        <v>-6.26</v>
       </c>
       <c r="D92" s="6">
-        <v>-17.48</v>
+        <v>-6.33</v>
       </c>
       <c r="E92" s="7">
-        <v>-0.45</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-11.25</v>
+        <v>-90.58</v>
       </c>
       <c r="D93" s="6">
-        <v>-10.7</v>
-      </c>
-      <c r="E93" s="8">
-        <v>0.55</v>
+        <v>-90.64</v>
+      </c>
+      <c r="E93" s="7">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-11.06</v>
+        <v>-14.75</v>
       </c>
       <c r="D94" s="6">
-        <v>-10.63</v>
-      </c>
-      <c r="E94" s="8">
-        <v>0.43</v>
+        <v>-14.92</v>
+      </c>
+      <c r="E94" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-16.57</v>
+        <v>-17.48</v>
       </c>
       <c r="D95" s="6">
-        <v>-16.44</v>
-      </c>
-      <c r="E95" s="8">
-        <v>0.13</v>
+        <v>-17.87</v>
+      </c>
+      <c r="E95" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-4.92</v>
+        <v>-10.7</v>
       </c>
       <c r="D96" s="6">
-        <v>-5.25</v>
+        <v>-13.11</v>
       </c>
       <c r="E96" s="7">
-        <v>-0.33</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-21.98</v>
+        <v>-10.63</v>
       </c>
       <c r="D97" s="6">
-        <v>-19.78</v>
-      </c>
-      <c r="E97" s="8">
-        <v>2.2</v>
+        <v>-12.92</v>
+      </c>
+      <c r="E97" s="7">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-22.13</v>
+        <v>-16.44</v>
       </c>
       <c r="D98" s="6">
-        <v>-19.84</v>
-      </c>
-      <c r="E98" s="8">
-        <v>2.29</v>
+        <v>-16.94</v>
+      </c>
+      <c r="E98" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-0.4</v>
+        <v>-5.25</v>
       </c>
       <c r="D99" s="6">
-        <v>-0.95</v>
+        <v>-5.52</v>
       </c>
       <c r="E99" s="7">
-        <v>-0.55</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-7.33</v>
+        <v>-19.78</v>
       </c>
       <c r="D100" s="6">
-        <v>-7.37</v>
+        <v>-20.5</v>
       </c>
       <c r="E100" s="7">
-        <v>-0.04</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-7.37</v>
+        <v>-19.84</v>
       </c>
       <c r="D101" s="6">
-        <v>-7.38</v>
+        <v>-20.72</v>
       </c>
       <c r="E101" s="7">
-        <v>-0.01</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-7.53</v>
+        <v>-0.95</v>
       </c>
       <c r="D102" s="6">
-        <v>-7.51</v>
-      </c>
-      <c r="E102" s="8">
-        <v>0.02</v>
+        <v>-1.87</v>
+      </c>
+      <c r="E102" s="7">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>-12.55</v>
+        <v>-7.37</v>
       </c>
       <c r="D103" s="6">
-        <v>-12.59</v>
+        <v>-7.62</v>
       </c>
       <c r="E103" s="7">
-        <v>-0.04</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>-4.03</v>
+        <v>-7.38</v>
       </c>
       <c r="D104" s="6">
-        <v>-4.35</v>
+        <v>-7.62</v>
       </c>
       <c r="E104" s="7">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>-35.25</v>
+        <v>-7.51</v>
       </c>
       <c r="D105" s="6">
-        <v>-34.09</v>
-      </c>
-      <c r="E105" s="8">
-        <v>1.16</v>
+        <v>-7.88</v>
+      </c>
+      <c r="E105" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="6">
-        <v>-7.36</v>
+        <v>-7.35</v>
       </c>
       <c r="D106" s="6">
-        <v>-7.37</v>
+        <v>-7.62</v>
       </c>
       <c r="E106" s="7">
-        <v>-0.01</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="6">
-        <v>-0.99</v>
+        <v>-12.59</v>
       </c>
       <c r="D107" s="6">
-        <v>-1.04</v>
+        <v>-13.38</v>
       </c>
       <c r="E107" s="7">
-        <v>-0.05</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C108" s="6">
-        <v>596.79</v>
+        <v>-4.35</v>
       </c>
       <c r="D108" s="6">
-        <v>596.0599999999999</v>
+        <v>-4.41</v>
       </c>
       <c r="E108" s="7">
-        <v>-0.73</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C109" s="6">
-        <v>59.76</v>
+        <v>-34.09</v>
       </c>
       <c r="D109" s="6">
-        <v>60</v>
-      </c>
-      <c r="E109" s="8">
-        <v>0.24</v>
+        <v>-36.22</v>
+      </c>
+      <c r="E109" s="7">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C110" s="6">
-        <v>92.59</v>
+        <v>-7.37</v>
       </c>
       <c r="D110" s="6">
-        <v>92.76000000000001</v>
-      </c>
-      <c r="E110" s="8">
-        <v>0.17</v>
+        <v>-7.63</v>
+      </c>
+      <c r="E110" s="7">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C111" s="6">
-        <v>50.61</v>
+        <v>-1.04</v>
       </c>
       <c r="D111" s="6">
-        <v>50.34</v>
+        <v>-1.93</v>
       </c>
       <c r="E111" s="7">
-        <v>-0.27</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>130.05</v>
+        <v>596.0599999999999</v>
       </c>
       <c r="D112" s="6">
-        <v>130.85</v>
-      </c>
-      <c r="E112" s="8">
-        <v>0.8</v>
+        <v>595.58</v>
+      </c>
+      <c r="E112" s="7">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>134.63</v>
+        <v>60</v>
       </c>
       <c r="D113" s="6">
-        <v>135.29</v>
-      </c>
-      <c r="E113" s="8">
-        <v>0.66</v>
+        <v>59.65</v>
+      </c>
+      <c r="E113" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>472.5</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="D114" s="6">
-        <v>473.21</v>
-      </c>
-      <c r="E114" s="8">
-        <v>0.71</v>
+        <v>92.58</v>
+      </c>
+      <c r="E114" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>959.2</v>
+        <v>50.34</v>
       </c>
       <c r="D115" s="6">
-        <v>955.87</v>
+        <v>50.1</v>
       </c>
       <c r="E115" s="7">
-        <v>-3.33</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>33.68</v>
+        <v>130.85</v>
       </c>
       <c r="D116" s="6">
-        <v>34.63</v>
-      </c>
-      <c r="E116" s="8">
-        <v>0.95</v>
+        <v>127.32</v>
+      </c>
+      <c r="E116" s="7">
+        <v>-3.53</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>33.71</v>
+        <v>135.29</v>
       </c>
       <c r="D117" s="6">
-        <v>34.7</v>
-      </c>
-      <c r="E117" s="8">
-        <v>0.99</v>
+        <v>131.82</v>
+      </c>
+      <c r="E117" s="7">
+        <v>-3.47</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>805.78</v>
+        <v>473.21</v>
       </c>
       <c r="D118" s="6">
-        <v>801.29</v>
+        <v>470.43</v>
       </c>
       <c r="E118" s="7">
-        <v>-4.49</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>275.74</v>
+        <v>955.87</v>
       </c>
       <c r="D119" s="6">
-        <v>275.62</v>
+        <v>953.22</v>
       </c>
       <c r="E119" s="7">
-        <v>-0.12</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>268.27</v>
+        <v>34.63</v>
       </c>
       <c r="D120" s="6">
-        <v>268.24</v>
+        <v>34.32</v>
       </c>
       <c r="E120" s="7">
-        <v>-0.03</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>262.89</v>
+        <v>34.7</v>
       </c>
       <c r="D121" s="6">
-        <v>262.96</v>
-      </c>
-      <c r="E121" s="8">
-        <v>0.07000000000000001</v>
+        <v>34.32</v>
+      </c>
+      <c r="E121" s="7">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>96.08</v>
+        <v>801.29</v>
       </c>
       <c r="D122" s="6">
-        <v>96.04000000000001</v>
+        <v>793.86</v>
       </c>
       <c r="E122" s="7">
-        <v>-0.04</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>284.57</v>
+        <v>275.62</v>
       </c>
       <c r="D123" s="6">
-        <v>283.64</v>
+        <v>274.87</v>
       </c>
       <c r="E123" s="7">
-        <v>-0.93</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>231.97</v>
+        <v>268.24</v>
       </c>
       <c r="D124" s="6">
-        <v>236.12</v>
-      </c>
-      <c r="E124" s="8">
-        <v>4.15</v>
+        <v>267.54</v>
+      </c>
+      <c r="E124" s="7">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>260.51</v>
+        <v>262.96</v>
       </c>
       <c r="D125" s="6">
-        <v>260.49</v>
+        <v>261.92</v>
       </c>
       <c r="E125" s="7">
-        <v>-0.02</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="6">
-        <v>795.26</v>
+        <v>274.23</v>
       </c>
       <c r="D126" s="6">
-        <v>794.87</v>
+        <v>273.42</v>
       </c>
       <c r="E126" s="7">
-        <v>-0.39</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C127" s="6">
-        <v>89</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="D127" s="6">
-        <v>94</v>
-      </c>
-      <c r="E127" s="8">
-        <v>5</v>
+        <v>95.17</v>
+      </c>
+      <c r="E127" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C128" s="6">
-        <v>94</v>
+        <v>283.64</v>
       </c>
       <c r="D128" s="6">
-        <v>89</v>
+        <v>283.45</v>
       </c>
       <c r="E128" s="7">
-        <v>-5</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C129" s="6">
-        <v>78</v>
+        <v>236.12</v>
       </c>
       <c r="D129" s="6">
-        <v>73</v>
+        <v>228.47</v>
       </c>
       <c r="E129" s="7">
-        <v>-5</v>
+        <v>-7.65</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C130" s="6">
-        <v>53</v>
+        <v>260.49</v>
       </c>
       <c r="D130" s="6">
-        <v>47</v>
+        <v>259.76</v>
       </c>
       <c r="E130" s="7">
-        <v>-6</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C131" s="6">
-        <v>37</v>
+        <v>794.87</v>
       </c>
       <c r="D131" s="6">
-        <v>42</v>
-      </c>
-      <c r="E131" s="8">
-        <v>5</v>
+        <v>787.71</v>
+      </c>
+      <c r="E131" s="7">
+        <v>-7.16</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D132" s="6">
-        <v>53</v>
-      </c>
-      <c r="E132" s="8">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="E132" s="7">
+        <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C133" s="6">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D133" s="6">
-        <v>37</v>
-      </c>
-      <c r="E133" s="7">
-        <v>-10</v>
+        <v>94</v>
+      </c>
+      <c r="E133" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="6">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="D134" s="6">
-        <v>78</v>
-      </c>
-      <c r="E134" s="8">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E134" s="7">
+        <v>-11</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C135" s="6">
-        <v>51.88</v>
+        <v>16</v>
       </c>
       <c r="D135" s="6">
-        <v>50.76</v>
-      </c>
-      <c r="E135" s="7">
-        <v>-1.12</v>
+        <v>27</v>
+      </c>
+      <c r="E135" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C136" s="6">
-        <v>50.09</v>
+        <v>42</v>
       </c>
       <c r="D136" s="6">
-        <v>53.2</v>
-      </c>
-      <c r="E136" s="8">
-        <v>3.11</v>
+        <v>37</v>
+      </c>
+      <c r="E136" s="7">
+        <v>-5</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C137" s="6">
-        <v>32.59</v>
+        <v>53</v>
       </c>
       <c r="D137" s="6">
-        <v>34.69</v>
-      </c>
-      <c r="E137" s="8">
-        <v>2.1</v>
+        <v>42</v>
+      </c>
+      <c r="E137" s="7">
+        <v>-11</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C138" s="6">
-        <v>32.9</v>
+        <v>37</v>
       </c>
       <c r="D138" s="6">
-        <v>30.82</v>
-      </c>
-      <c r="E138" s="7">
-        <v>-2.08</v>
+        <v>53</v>
+      </c>
+      <c r="E138" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>65.37</v>
+        <v>50.76</v>
       </c>
       <c r="D139" s="6">
-        <v>67.08</v>
-      </c>
-      <c r="E139" s="8">
-        <v>1.71</v>
+        <v>50</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>66.34999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="D140" s="6">
-        <v>67.72</v>
-      </c>
-      <c r="E140" s="8">
-        <v>1.37</v>
+        <v>48.45</v>
+      </c>
+      <c r="E140" s="7">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>38.3</v>
+        <v>34.69</v>
       </c>
       <c r="D141" s="6">
-        <v>39.36</v>
-      </c>
-      <c r="E141" s="8">
-        <v>1.06</v>
+        <v>33.5</v>
+      </c>
+      <c r="E141" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>40.73</v>
+        <v>30.82</v>
       </c>
       <c r="D142" s="6">
-        <v>38.28</v>
+        <v>29.06</v>
       </c>
       <c r="E142" s="7">
-        <v>-2.45</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>49.47</v>
+        <v>67.08</v>
       </c>
       <c r="D143" s="6">
-        <v>59.77</v>
-      </c>
-      <c r="E143" s="8">
-        <v>10.3</v>
+        <v>54.35</v>
+      </c>
+      <c r="E143" s="7">
+        <v>-12.73</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>49.52</v>
+        <v>67.72</v>
       </c>
       <c r="D144" s="6">
-        <v>60.19</v>
-      </c>
-      <c r="E144" s="8">
-        <v>10.67</v>
+        <v>55.03</v>
+      </c>
+      <c r="E144" s="7">
+        <v>-12.69</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>60.28</v>
+        <v>39.36</v>
       </c>
       <c r="D145" s="6">
-        <v>53.58</v>
+        <v>36.7</v>
       </c>
       <c r="E145" s="7">
-        <v>-6.7</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>47.01</v>
+        <v>38.28</v>
       </c>
       <c r="D146" s="6">
-        <v>46.59</v>
+        <v>36.4</v>
       </c>
       <c r="E146" s="7">
-        <v>-0.42</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>46.62</v>
+        <v>59.77</v>
       </c>
       <c r="D147" s="6">
-        <v>46.51</v>
+        <v>55.78</v>
       </c>
       <c r="E147" s="7">
-        <v>-0.11</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>45.8</v>
+        <v>60.19</v>
       </c>
       <c r="D148" s="6">
-        <v>46.07</v>
-      </c>
-      <c r="E148" s="8">
-        <v>0.27</v>
+        <v>55.35</v>
+      </c>
+      <c r="E148" s="7">
+        <v>-4.84</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>51.46</v>
+        <v>53.58</v>
       </c>
       <c r="D149" s="6">
-        <v>51.25</v>
+        <v>44.72</v>
       </c>
       <c r="E149" s="7">
-        <v>-0.21</v>
+        <v>-8.859999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>58.05</v>
+        <v>46.59</v>
       </c>
       <c r="D150" s="6">
-        <v>55.18</v>
+        <v>43.94</v>
       </c>
       <c r="E150" s="7">
-        <v>-2.87</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>56.97</v>
+        <v>46.51</v>
       </c>
       <c r="D151" s="6">
-        <v>61.07</v>
-      </c>
-      <c r="E151" s="8">
-        <v>4.1</v>
+        <v>43.88</v>
+      </c>
+      <c r="E151" s="7">
+        <v>-2.63</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>46.67</v>
+        <v>46.07</v>
       </c>
       <c r="D152" s="6">
-        <v>46.59</v>
+        <v>42.65</v>
       </c>
       <c r="E152" s="7">
-        <v>-0.08</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="6">
-        <v>54.37</v>
+        <v>46.52</v>
       </c>
       <c r="D153" s="6">
-        <v>53.93</v>
+        <v>43.55</v>
       </c>
       <c r="E153" s="7">
-        <v>-0.44</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C154" s="6">
-        <v>-12.45</v>
+        <v>51.25</v>
       </c>
       <c r="D154" s="6">
-        <v>-7.33</v>
-      </c>
-      <c r="E154" s="8">
-        <v>5.12</v>
+        <v>46.71</v>
+      </c>
+      <c r="E154" s="7">
+        <v>-4.54</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C155" s="6">
-        <v>351.47</v>
+        <v>55.18</v>
       </c>
       <c r="D155" s="6">
-        <v>-52.53</v>
+        <v>54.58</v>
       </c>
       <c r="E155" s="7">
-        <v>-404</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C156" s="6">
-        <v>34.42</v>
+        <v>61.07</v>
       </c>
       <c r="D156" s="6">
-        <v>3.42</v>
+        <v>51.35</v>
       </c>
       <c r="E156" s="7">
-        <v>-31</v>
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C157" s="6">
-        <v>-10.56</v>
+        <v>46.59</v>
       </c>
       <c r="D157" s="6">
-        <v>7.13</v>
-      </c>
-      <c r="E157" s="8">
-        <v>17.69</v>
+        <v>43.8</v>
+      </c>
+      <c r="E157" s="7">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C158" s="6">
-        <v>69.98</v>
+        <v>53.93</v>
       </c>
       <c r="D158" s="6">
-        <v>-1.7</v>
+        <v>46.55</v>
       </c>
       <c r="E158" s="7">
-        <v>-71.68000000000001</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>196.06</v>
+        <v>-7.33</v>
       </c>
       <c r="D159" s="6">
-        <v>-9.300000000000001</v>
+        <v>-42.27</v>
       </c>
       <c r="E159" s="7">
-        <v>-205.36</v>
+        <v>-34.94</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>-26.35</v>
+        <v>-52.53</v>
       </c>
       <c r="D160" s="6">
-        <v>-37.07</v>
+        <v>-75.20999999999999</v>
       </c>
       <c r="E160" s="7">
-        <v>-10.72</v>
+        <v>-22.68</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>51.47</v>
+        <v>3.42</v>
       </c>
       <c r="D161" s="6">
-        <v>86.7</v>
-      </c>
-      <c r="E161" s="8">
-        <v>35.23</v>
+        <v>-42.01</v>
+      </c>
+      <c r="E161" s="7">
+        <v>-45.43</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>-68.06999999999999</v>
+        <v>7.13</v>
       </c>
       <c r="D162" s="6">
-        <v>29.31</v>
-      </c>
-      <c r="E162" s="8">
-        <v>97.38</v>
+        <v>3.73</v>
+      </c>
+      <c r="E162" s="7">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>-49.98</v>
+        <v>-1.7</v>
       </c>
       <c r="D163" s="6">
-        <v>85.15000000000001</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="E163" s="8">
-        <v>135.13</v>
+        <v>80.34999999999999</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>-4.35</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="D164" s="6">
-        <v>-50.44</v>
-      </c>
-      <c r="E164" s="7">
-        <v>-46.09</v>
+        <v>37.52</v>
+      </c>
+      <c r="E164" s="8">
+        <v>46.82</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>32.76</v>
+        <v>-37.07</v>
       </c>
       <c r="D165" s="6">
-        <v>-37.05</v>
-      </c>
-      <c r="E165" s="7">
-        <v>-69.81</v>
+        <v>-17.48</v>
+      </c>
+      <c r="E165" s="8">
+        <v>19.59</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>-4.01</v>
+        <v>86.7</v>
       </c>
       <c r="D166" s="6">
-        <v>-28.59</v>
+        <v>-15.06</v>
       </c>
       <c r="E166" s="7">
-        <v>-24.58</v>
+        <v>-101.76</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-88.36</v>
+        <v>29.31</v>
       </c>
       <c r="D167" s="6">
-        <v>-62.81</v>
-      </c>
-      <c r="E167" s="8">
-        <v>25.55</v>
+        <v>-50.66</v>
+      </c>
+      <c r="E167" s="7">
+        <v>-79.97</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-42.72</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="D168" s="6">
-        <v>27.82</v>
-      </c>
-      <c r="E168" s="8">
-        <v>70.54000000000001</v>
+        <v>-14.41</v>
+      </c>
+      <c r="E168" s="7">
+        <v>-99.56</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>-58.74</v>
+        <v>-50.44</v>
       </c>
       <c r="D169" s="6">
-        <v>-71.65000000000001</v>
-      </c>
-      <c r="E169" s="7">
-        <v>-12.91</v>
+        <v>-4.54</v>
+      </c>
+      <c r="E169" s="8">
+        <v>45.9</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="6">
-        <v>-74.98</v>
+        <v>-37.05</v>
       </c>
       <c r="D170" s="6">
-        <v>-97.8</v>
-      </c>
-      <c r="E170" s="7">
-        <v>-22.82</v>
+        <v>-4.61</v>
+      </c>
+      <c r="E170" s="8">
+        <v>32.44</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="6">
-        <v>11.75</v>
+        <v>-28.59</v>
       </c>
       <c r="D171" s="6">
-        <v>32.72</v>
+        <v>-20.89</v>
       </c>
       <c r="E171" s="8">
-        <v>20.97</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="6">
-        <v>70.25</v>
+        <v>-62.81</v>
       </c>
       <c r="D172" s="6">
-        <v>20.09</v>
+        <v>-84.19</v>
       </c>
       <c r="E172" s="7">
-        <v>-50.16</v>
+        <v>-21.38</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C173" s="6">
-        <v>12.57</v>
+        <v>27.82</v>
       </c>
       <c r="D173" s="6">
+        <v>34.33</v>
+      </c>
+      <c r="E173" s="8">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="6">
+        <v>-71.65000000000001</v>
+      </c>
+      <c r="D174" s="6">
+        <v>-42.32</v>
+      </c>
+      <c r="E174" s="8">
+        <v>29.33</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="6">
+        <v>-97.8</v>
+      </c>
+      <c r="D175" s="6">
+        <v>-85.13</v>
+      </c>
+      <c r="E175" s="8">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C176" s="6">
+        <v>32.72</v>
+      </c>
+      <c r="D176" s="6">
+        <v>71.17</v>
+      </c>
+      <c r="E176" s="8">
+        <v>38.45</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177" s="6">
+        <v>20.09</v>
+      </c>
+      <c r="D177" s="6">
+        <v>15.89</v>
+      </c>
+      <c r="E177" s="7">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="6">
         <v>62.2</v>
       </c>
-      <c r="E173" s="8">
-        <v>49.63</v>
+      <c r="D178" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="E178" s="7">
+        <v>-61.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6252,28 +6364,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6281,19 +6393,19 @@
         <v>57</v>
       </c>
       <c r="B2" s="11">
-        <v>47.04000000000001</v>
+        <v>43.04000000000001</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>50.5</v>
+        <v>45.8</v>
       </c>
       <c r="E2" s="11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="11">
         <v>1.6</v>
@@ -6431,39 +6543,39 @@
         <v>37</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.5575</v>
+        <v>0.5312</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3436</v>
+        <v>0.3318</v>
       </c>
       <c r="C2" s="14">
-        <v>0.3057</v>
+        <v>0.3016</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2921</v>
+        <v>0.2899</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2615</v>
+        <v>0.2554</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1483</v>
+        <v>0.1442</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1337</v>
+        <v>0.1284</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1334</v>
+        <v>0.1279</v>
       </c>
       <c r="I2" s="14">
-        <v>0.1023</v>
+        <v>0.1016</v>
       </c>
       <c r="J2" s="14">
-        <v>0.08599999999999999</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6471,13 +6583,13 @@
         <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>43</v>
@@ -6500,34 +6612,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.08599999999999999</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0859</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0858</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0858</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E4" s="14">
-        <v>0.07719999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0513</v>
+        <v>0.0492</v>
       </c>
       <c r="G4" s="14">
-        <v>0.0018</v>
+        <v>-0.0026</v>
       </c>
       <c r="H4" s="14">
-        <v>0.0002</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.091</v>
+        <v>-0.0934</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3044</v>
+        <v>-0.3052</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="89">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,82 +226,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.9% → -2.6%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.9%</t>
-  </si>
-  <si>
-    <t>-2.6%</t>
-  </si>
-  <si>
-    <t>-1.9% → -2.4%</t>
-  </si>
-  <si>
-    <t>-2.4%</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.5 → 52.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.0 → 47.2</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>47.2</t>
-  </si>
-  <si>
-    <t>54.4 → 48.8</t>
-  </si>
-  <si>
-    <t>54.4</t>
-  </si>
-  <si>
-    <t>48.8</t>
-  </si>
-  <si>
-    <t>55.0 → 49.0</t>
-  </si>
-  <si>
-    <t>55.0</t>
-  </si>
-  <si>
-    <t>49.0</t>
-  </si>
-  <si>
-    <t>54.6 → 48.5</t>
-  </si>
-  <si>
-    <t>54.6</t>
-  </si>
-  <si>
-    <t>48.5</t>
-  </si>
-  <si>
-    <t>51.4 → 45.7</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>45.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -353,7 +299,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,7 +333,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -399,15 +345,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,19 +373,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -527,12 +460,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -541,7 +474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1040,10 +973,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>593.79</v>
+        <v>592.76</v>
       </c>
       <c r="D2">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1052,43 +985,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-6.62</v>
+        <v>-6.78</v>
       </c>
       <c r="H2">
-        <v>13.99</v>
+        <v>13.8</v>
       </c>
       <c r="I2">
-        <v>-0.22</v>
+        <v>-1.14</v>
       </c>
       <c r="J2">
-        <v>-0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="K2">
-        <v>5.79</v>
+        <v>5.27</v>
       </c>
       <c r="L2">
-        <v>6.99</v>
+        <v>6.24</v>
       </c>
       <c r="M2">
-        <v>9.960000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
+        <v>595</v>
+      </c>
+      <c r="Q2">
+        <v>596.33</v>
+      </c>
+      <c r="R2">
         <v>596.36</v>
       </c>
-      <c r="Q2">
-        <v>596.51</v>
-      </c>
-      <c r="R2">
-        <v>596.55</v>
-      </c>
       <c r="S2">
-        <v>592.9</v>
+        <v>592.83</v>
       </c>
       <c r="T2">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1100,37 +1033,37 @@
         <v>58</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>47.16</v>
+        <v>45.55</v>
       </c>
       <c r="Z2">
-        <v>0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA2">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB2">
-        <v>-0.34</v>
+        <v>-0.49</v>
       </c>
       <c r="AC2">
-        <v>21.73</v>
+        <v>9.41</v>
       </c>
       <c r="AD2">
-        <v>40.76</v>
+        <v>23.15</v>
       </c>
       <c r="AE2">
-        <v>7.03</v>
+        <v>6.79</v>
       </c>
       <c r="AF2">
-        <v>-18.96</v>
+        <v>92.19</v>
       </c>
       <c r="AG2">
-        <v>600.29</v>
+        <v>600.47</v>
       </c>
       <c r="AH2">
-        <v>592.72</v>
+        <v>592.1900000000001</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1139,7 +1072,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>35.23</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1150,10 +1083,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>59.31</v>
+        <v>59.3</v>
       </c>
       <c r="D3">
-        <v>-0.57</v>
+        <v>-0.02</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1165,43 +1098,43 @@
         <v>-90.69</v>
       </c>
       <c r="H3">
-        <v>13.8</v>
+        <v>13.78</v>
       </c>
       <c r="I3">
-        <v>-0.5</v>
+        <v>-1.23</v>
       </c>
       <c r="J3">
-        <v>-0.9399999999999999</v>
+        <v>-0.65</v>
       </c>
       <c r="K3">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="L3">
-        <v>-89.31</v>
+        <v>-89.38</v>
       </c>
       <c r="M3">
-        <v>-30.66</v>
+        <v>-30.76</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.75</v>
+        <v>59.6</v>
       </c>
       <c r="Q3">
-        <v>59.81</v>
+        <v>59.78</v>
       </c>
       <c r="R3">
-        <v>59.81</v>
+        <v>59.79</v>
       </c>
       <c r="S3">
-        <v>259.4</v>
+        <v>256.66</v>
       </c>
       <c r="T3">
-        <v>-77.14</v>
+        <v>-76.90000000000001</v>
       </c>
       <c r="U3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1210,37 +1143,37 @@
         <v>58</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>44.31</v>
+        <v>44.19</v>
       </c>
       <c r="Z3">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="AA3">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AB3">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>40.07</v>
+        <v>10.39</v>
       </c>
       <c r="AD3">
-        <v>58.9</v>
+        <v>35.86</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>-79.84</v>
+        <v>-74.95</v>
       </c>
       <c r="AG3">
-        <v>60.32</v>
+        <v>60.34</v>
       </c>
       <c r="AH3">
-        <v>59.3</v>
+        <v>59.23</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1249,7 +1182,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>22.67</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1260,10 +1193,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>92.53</v>
+        <v>93.64</v>
       </c>
       <c r="D4">
-        <v>-0.05</v>
+        <v>1.2</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1272,43 +1205,43 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-14.96</v>
+        <v>-13.94</v>
       </c>
       <c r="H4">
-        <v>4.83</v>
+        <v>6.08</v>
       </c>
       <c r="I4">
-        <v>-1.33</v>
+        <v>0.48</v>
       </c>
       <c r="J4">
-        <v>-2.49</v>
+        <v>-1.04</v>
       </c>
       <c r="K4">
-        <v>-8.4</v>
+        <v>-6.52</v>
       </c>
       <c r="L4">
-        <v>5.35</v>
+        <v>5.19</v>
       </c>
       <c r="M4">
-        <v>28.96</v>
+        <v>29.21</v>
       </c>
       <c r="N4">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>92.73</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="Q4">
-        <v>93.66</v>
+        <v>93.61</v>
       </c>
       <c r="R4">
-        <v>95.16</v>
+        <v>95.08</v>
       </c>
       <c r="S4">
         <v>97.94</v>
       </c>
       <c r="T4">
-        <v>-5.53</v>
+        <v>-4.39</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1323,34 +1256,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.16</v>
+        <v>46.21</v>
       </c>
       <c r="Z4">
-        <v>-0.76</v>
+        <v>-0.67</v>
       </c>
       <c r="AA4">
-        <v>-0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="AB4">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AC4">
-        <v>18.56</v>
+        <v>43.48</v>
       </c>
       <c r="AD4">
-        <v>20.02</v>
+        <v>26.4</v>
       </c>
       <c r="AE4">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AF4">
-        <v>-45.88</v>
+        <v>30.79</v>
       </c>
       <c r="AG4">
-        <v>94.97</v>
+        <v>94.81</v>
       </c>
       <c r="AH4">
-        <v>92.36</v>
+        <v>92.41</v>
       </c>
       <c r="AI4">
         <v>97.83</v>
@@ -1359,7 +1292,7 @@
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>14.81</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1370,10 +1303,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>49.78</v>
+        <v>49.74</v>
       </c>
       <c r="D5">
-        <v>-0.64</v>
+        <v>-0.08</v>
       </c>
       <c r="E5">
         <v>61</v>
@@ -1382,43 +1315,43 @@
         <v>48.67</v>
       </c>
       <c r="G5">
-        <v>-18.39</v>
+        <v>-18.46</v>
       </c>
       <c r="H5">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="I5">
-        <v>-2.72</v>
+        <v>-2.47</v>
       </c>
       <c r="J5">
-        <v>-6.13</v>
+        <v>-6.59</v>
       </c>
       <c r="K5">
-        <v>-3.75</v>
+        <v>-3.92</v>
       </c>
       <c r="L5">
-        <v>-17.02</v>
+        <v>-17.03</v>
       </c>
       <c r="M5">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>50.37</v>
+        <v>50.11</v>
       </c>
       <c r="Q5">
-        <v>51.63</v>
+        <v>51.46</v>
       </c>
       <c r="R5">
-        <v>52.36</v>
+        <v>52.31</v>
       </c>
       <c r="S5">
-        <v>54.19</v>
+        <v>54.14</v>
       </c>
       <c r="T5">
-        <v>-8.140000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1433,13 +1366,13 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>26.86</v>
+        <v>26.59</v>
       </c>
       <c r="Z5">
-        <v>-0.67</v>
+        <v>-0.72</v>
       </c>
       <c r="AA5">
-        <v>-0.49</v>
+        <v>-0.54</v>
       </c>
       <c r="AB5">
         <v>-0.18</v>
@@ -1448,28 +1381,28 @@
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>2.77</v>
+        <v>0.28</v>
       </c>
       <c r="AE5">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="AF5">
-        <v>212.78</v>
+        <v>-3.13</v>
       </c>
       <c r="AG5">
-        <v>53.71</v>
+        <v>53.57</v>
       </c>
       <c r="AH5">
-        <v>49.56</v>
+        <v>49.36</v>
       </c>
       <c r="AI5">
-        <v>52.92</v>
+        <v>52.8</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>30.55</v>
+        <v>34.03</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1480,10 +1413,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>125.34</v>
+        <v>123.52</v>
       </c>
       <c r="D6">
-        <v>-1.56</v>
+        <v>-1.45</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1492,43 +1425,43 @@
         <v>86.61</v>
       </c>
       <c r="G6">
-        <v>-14.46</v>
+        <v>-15.7</v>
       </c>
       <c r="H6">
-        <v>44.72</v>
+        <v>42.62</v>
       </c>
       <c r="I6">
-        <v>-5.6</v>
+        <v>-6.69</v>
       </c>
       <c r="J6">
-        <v>6.89</v>
+        <v>5.44</v>
       </c>
       <c r="K6">
-        <v>-2.46</v>
+        <v>-3.33</v>
       </c>
       <c r="L6">
-        <v>46.87</v>
+        <v>42.62</v>
       </c>
       <c r="M6">
-        <v>25.15</v>
+        <v>24.73</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>129.19</v>
+        <v>127.42</v>
       </c>
       <c r="Q6">
-        <v>127.08</v>
+        <v>127.29</v>
       </c>
       <c r="R6">
-        <v>121.19</v>
+        <v>121.31</v>
       </c>
       <c r="S6">
-        <v>121.27</v>
+        <v>121.38</v>
       </c>
       <c r="T6">
-        <v>3.35</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1543,43 +1476,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.76</v>
+        <v>44.26</v>
       </c>
       <c r="Z6">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="AA6">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="AB6">
-        <v>-0.35</v>
+        <v>-0.72</v>
       </c>
       <c r="AC6">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>12.49</v>
+        <v>2.74</v>
       </c>
       <c r="AE6">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AF6">
-        <v>22.09</v>
+        <v>21.1</v>
       </c>
       <c r="AG6">
-        <v>134.46</v>
+        <v>133.96</v>
       </c>
       <c r="AH6">
-        <v>119.71</v>
+        <v>120.62</v>
       </c>
       <c r="AI6">
-        <v>133.11</v>
+        <v>130.3</v>
       </c>
       <c r="AJ6" t="s">
         <v>61</v>
       </c>
       <c r="AK6">
-        <v>35.05</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1590,55 +1523,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>129.71</v>
+        <v>127.8</v>
       </c>
       <c r="D7">
-        <v>-1.6</v>
+        <v>-1.47</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>89.43000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="G7">
-        <v>-14.31</v>
+        <v>-15.58</v>
       </c>
       <c r="H7">
-        <v>45.04</v>
+        <v>42.81</v>
       </c>
       <c r="I7">
-        <v>-5.38</v>
+        <v>-6.53</v>
       </c>
       <c r="J7">
-        <v>7.02</v>
+        <v>5.52</v>
       </c>
       <c r="K7">
-        <v>-2.26</v>
+        <v>-3.19</v>
       </c>
       <c r="L7">
-        <v>47.35</v>
+        <v>42.91</v>
       </c>
       <c r="M7">
-        <v>32.49</v>
+        <v>31.85</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>133.64</v>
+        <v>131.85</v>
       </c>
       <c r="Q7">
-        <v>131.42</v>
+        <v>131.63</v>
       </c>
       <c r="R7">
-        <v>125.27</v>
+        <v>125.39</v>
       </c>
       <c r="S7">
-        <v>125.3</v>
+        <v>125.41</v>
       </c>
       <c r="T7">
-        <v>3.52</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1653,34 +1586,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>49.01</v>
+        <v>44.29</v>
       </c>
       <c r="Z7">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="AA7">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="AB7">
-        <v>-0.35</v>
+        <v>-0.73</v>
       </c>
       <c r="AC7">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>11.25</v>
+        <v>2.27</v>
       </c>
       <c r="AE7">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="AF7">
-        <v>70.8</v>
+        <v>23</v>
       </c>
       <c r="AG7">
-        <v>138.98</v>
+        <v>138.44</v>
       </c>
       <c r="AH7">
-        <v>123.85</v>
+        <v>124.82</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1689,7 +1622,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>35.6</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1700,10 +1633,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>469.33</v>
+        <v>468.63</v>
       </c>
       <c r="D8">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1712,43 +1645,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-17.13</v>
+        <v>-17.25</v>
       </c>
       <c r="H8">
-        <v>4.11</v>
+        <v>3.96</v>
       </c>
       <c r="I8">
-        <v>-0.57</v>
+        <v>-1.52</v>
       </c>
       <c r="J8">
-        <v>-5.5</v>
+        <v>-4.21</v>
       </c>
       <c r="K8">
-        <v>-8.1</v>
+        <v>-6.6</v>
       </c>
       <c r="L8">
-        <v>1.04</v>
+        <v>-1.9</v>
       </c>
       <c r="M8">
-        <v>7.13</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>16</v>
       </c>
       <c r="P8">
-        <v>472.27</v>
+        <v>470.82</v>
       </c>
       <c r="Q8">
-        <v>479.71</v>
+        <v>478.67</v>
       </c>
       <c r="R8">
-        <v>481.33</v>
+        <v>481.27</v>
       </c>
       <c r="S8">
-        <v>508.51</v>
+        <v>508.22</v>
       </c>
       <c r="T8">
-        <v>-7.7</v>
+        <v>-7.79</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1763,34 +1696,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>35.67</v>
+        <v>35</v>
       </c>
       <c r="Z8">
-        <v>-4.07</v>
+        <v>-4.31</v>
       </c>
       <c r="AA8">
-        <v>-2.92</v>
+        <v>-3.2</v>
       </c>
       <c r="AB8">
-        <v>-1.15</v>
+        <v>-1.12</v>
       </c>
       <c r="AC8">
-        <v>12.64</v>
+        <v>2.58</v>
       </c>
       <c r="AD8">
-        <v>19.78</v>
+        <v>11.16</v>
       </c>
       <c r="AE8">
-        <v>9.460000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="AF8">
-        <v>0.37</v>
+        <v>-40.44</v>
       </c>
       <c r="AG8">
-        <v>492.02</v>
+        <v>491.04</v>
       </c>
       <c r="AH8">
-        <v>467.41</v>
+        <v>466.31</v>
       </c>
       <c r="AI8">
         <v>498.33</v>
@@ -1799,7 +1732,7 @@
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>17.75</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1810,10 +1743,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>950.4</v>
+        <v>953.53</v>
       </c>
       <c r="D9">
-        <v>-0.3</v>
+        <v>0.33</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1822,43 +1755,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-5.79</v>
+        <v>-5.48</v>
       </c>
       <c r="H9">
-        <v>7.38</v>
+        <v>7.74</v>
       </c>
       <c r="I9">
-        <v>-1.84</v>
+        <v>-1.2</v>
       </c>
       <c r="J9">
-        <v>-2.23</v>
+        <v>-1.55</v>
       </c>
       <c r="K9">
-        <v>-0.19</v>
+        <v>0.52</v>
       </c>
       <c r="L9">
-        <v>3.46</v>
+        <v>2.96</v>
       </c>
       <c r="M9">
-        <v>14.19</v>
+        <v>14.02</v>
       </c>
       <c r="N9">
         <v>58</v>
       </c>
       <c r="P9">
-        <v>956.76</v>
+        <v>954.4400000000001</v>
       </c>
       <c r="Q9">
-        <v>968.53</v>
+        <v>967.5</v>
       </c>
       <c r="R9">
-        <v>969.13</v>
+        <v>968.62</v>
       </c>
       <c r="S9">
-        <v>964.63</v>
+        <v>964.4299999999999</v>
       </c>
       <c r="T9">
-        <v>-1.48</v>
+        <v>-1.13</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1873,34 +1806,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>34.46</v>
+        <v>38.38</v>
       </c>
       <c r="Z9">
-        <v>-3.83</v>
+        <v>-4.2</v>
       </c>
       <c r="AA9">
-        <v>-1.46</v>
+        <v>-2.01</v>
       </c>
       <c r="AB9">
-        <v>-2.37</v>
+        <v>-2.19</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="AD9">
-        <v>0.77</v>
+        <v>2.09</v>
       </c>
       <c r="AE9">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="AF9">
-        <v>98.40000000000001</v>
+        <v>42.78</v>
       </c>
       <c r="AG9">
-        <v>986.28</v>
+        <v>986.24</v>
       </c>
       <c r="AH9">
-        <v>950.77</v>
+        <v>948.75</v>
       </c>
       <c r="AI9">
         <v>947.23</v>
@@ -1909,7 +1842,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>23.71</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1920,10 +1853,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>34.72</v>
+        <v>34.36</v>
       </c>
       <c r="D10">
-        <v>1.17</v>
+        <v>-1.04</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1932,43 +1865,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-19.57</v>
+        <v>-20.41</v>
       </c>
       <c r="H10">
-        <v>21.31</v>
+        <v>20.06</v>
       </c>
       <c r="I10">
-        <v>2.33</v>
+        <v>1.69</v>
       </c>
       <c r="J10">
-        <v>-0.66</v>
+        <v>-1.01</v>
       </c>
       <c r="K10">
-        <v>6.86</v>
+        <v>7.14</v>
       </c>
       <c r="L10">
-        <v>-9.279999999999999</v>
+        <v>-11.78</v>
       </c>
       <c r="M10">
-        <v>0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="N10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P10">
-        <v>34.23</v>
+        <v>34.34</v>
       </c>
       <c r="Q10">
-        <v>34.35</v>
+        <v>34.34</v>
       </c>
       <c r="R10">
-        <v>32.79</v>
+        <v>32.87</v>
       </c>
       <c r="S10">
-        <v>35.45</v>
+        <v>35.42</v>
       </c>
       <c r="T10">
-        <v>-2.06</v>
+        <v>-3</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1983,34 +1916,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>59.53</v>
+        <v>55</v>
       </c>
       <c r="Z10">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AA10">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AB10">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AC10">
-        <v>58.15</v>
+        <v>54.46</v>
       </c>
       <c r="AD10">
-        <v>36.71</v>
+        <v>48.58</v>
       </c>
       <c r="AE10">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="AF10">
-        <v>75.41</v>
+        <v>-16.85</v>
       </c>
       <c r="AG10">
-        <v>35.38</v>
+        <v>35.36</v>
       </c>
       <c r="AH10">
-        <v>33.33</v>
+        <v>33.32</v>
       </c>
       <c r="AI10">
         <v>32.26</v>
@@ -2019,7 +1952,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>25.03</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2030,10 +1963,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>34.79</v>
+        <v>34.39</v>
       </c>
       <c r="D11">
-        <v>1.37</v>
+        <v>-1.15</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -2042,43 +1975,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-19.64</v>
+        <v>-20.56</v>
       </c>
       <c r="H11">
-        <v>21.52</v>
+        <v>20.12</v>
       </c>
       <c r="I11">
-        <v>2.56</v>
+        <v>1.87</v>
       </c>
       <c r="J11">
-        <v>-0.54</v>
+        <v>-0.89</v>
       </c>
       <c r="K11">
-        <v>6.85</v>
+        <v>6.64</v>
       </c>
       <c r="L11">
-        <v>-9.449999999999999</v>
+        <v>-11.73</v>
       </c>
       <c r="M11">
-        <v>0.01</v>
+        <v>-0.47</v>
       </c>
       <c r="N11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P11">
-        <v>34.26</v>
+        <v>34.38</v>
       </c>
       <c r="Q11">
-        <v>34.4</v>
+        <v>34.38</v>
       </c>
       <c r="R11">
-        <v>32.81</v>
+        <v>32.88</v>
       </c>
       <c r="S11">
-        <v>35.51</v>
+        <v>35.48</v>
       </c>
       <c r="T11">
-        <v>-2.03</v>
+        <v>-3.08</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -2093,31 +2026,31 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>59.67</v>
+        <v>54.81</v>
       </c>
       <c r="Z11">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AA11">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AB11">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AC11">
-        <v>58.1</v>
+        <v>53.49</v>
       </c>
       <c r="AD11">
-        <v>37.64</v>
+        <v>48.51</v>
       </c>
       <c r="AE11">
         <v>0.96</v>
       </c>
       <c r="AF11">
-        <v>36.3</v>
+        <v>-23.62</v>
       </c>
       <c r="AG11">
-        <v>35.46</v>
+        <v>35.44</v>
       </c>
       <c r="AH11">
         <v>33.33</v>
@@ -2129,7 +2062,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>16.18</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2140,10 +2073,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>788.17</v>
+        <v>788.4</v>
       </c>
       <c r="D12">
-        <v>-0.72</v>
+        <v>0.03</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2152,40 +2085,40 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-2.57</v>
+        <v>-2.55</v>
       </c>
       <c r="H12">
-        <v>20.9</v>
+        <v>20.94</v>
       </c>
       <c r="I12">
-        <v>-1.99</v>
+        <v>-2.29</v>
       </c>
       <c r="J12">
-        <v>-1.67</v>
+        <v>-1.7</v>
       </c>
       <c r="K12">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="L12">
-        <v>11.41</v>
+        <v>10.04</v>
       </c>
       <c r="M12">
-        <v>12.46</v>
+        <v>12.44</v>
       </c>
       <c r="N12">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>799.2</v>
+        <v>795.5</v>
       </c>
       <c r="Q12">
-        <v>803.8099999999999</v>
+        <v>802.9400000000001</v>
       </c>
       <c r="R12">
-        <v>790.0700000000001</v>
+        <v>790.27</v>
       </c>
       <c r="S12">
-        <v>752.17</v>
+        <v>752.34</v>
       </c>
       <c r="T12">
         <v>4.79</v>
@@ -2203,34 +2136,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>39.35</v>
+        <v>39.67</v>
       </c>
       <c r="Z12">
-        <v>1.87</v>
+        <v>0.83</v>
       </c>
       <c r="AA12">
-        <v>4.44</v>
+        <v>3.72</v>
       </c>
       <c r="AB12">
-        <v>-2.57</v>
+        <v>-2.88</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AD12">
-        <v>12.54</v>
+        <v>3.9</v>
       </c>
       <c r="AE12">
-        <v>14.4</v>
+        <v>15.5</v>
       </c>
       <c r="AF12">
-        <v>1.01</v>
+        <v>52.52</v>
       </c>
       <c r="AG12">
-        <v>814.4400000000001</v>
+        <v>815.55</v>
       </c>
       <c r="AH12">
-        <v>793.17</v>
+        <v>790.33</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2239,7 +2172,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>30</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2250,10 +2183,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>273.25</v>
+        <v>272.56</v>
       </c>
       <c r="D13">
-        <v>-0.59</v>
+        <v>-0.25</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2262,43 +2195,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-8.17</v>
+        <v>-8.4</v>
       </c>
       <c r="H13">
-        <v>7.82</v>
+        <v>7.54</v>
       </c>
       <c r="I13">
-        <v>-1.33</v>
+        <v>-1.61</v>
       </c>
       <c r="J13">
-        <v>-2.37</v>
+        <v>-2.23</v>
       </c>
       <c r="K13">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="L13">
-        <v>-1.02</v>
+        <v>-2.02</v>
       </c>
       <c r="M13">
-        <v>8.19</v>
+        <v>7.95</v>
       </c>
       <c r="N13">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="P13">
-        <v>275.3</v>
+        <v>274.41</v>
       </c>
       <c r="Q13">
-        <v>277.33</v>
+        <v>276.96</v>
       </c>
       <c r="R13">
         <v>275.65</v>
       </c>
       <c r="S13">
-        <v>279.02</v>
+        <v>278.91</v>
       </c>
       <c r="T13">
-        <v>-2.07</v>
+        <v>-2.28</v>
       </c>
       <c r="U13" t="s">
         <v>59</v>
@@ -2313,34 +2246,34 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>38.81</v>
+        <v>36.84</v>
       </c>
       <c r="Z13">
-        <v>-0.28</v>
+        <v>-0.52</v>
       </c>
       <c r="AA13">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="AB13">
-        <v>-0.5600000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="AC13">
-        <v>9.199999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="AD13">
-        <v>17.11</v>
+        <v>8.85</v>
       </c>
       <c r="AE13">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="AF13">
-        <v>13.79</v>
+        <v>60.4</v>
       </c>
       <c r="AG13">
-        <v>281.45</v>
+        <v>281.4</v>
       </c>
       <c r="AH13">
-        <v>273.2</v>
+        <v>272.51</v>
       </c>
       <c r="AI13">
         <v>271.55</v>
@@ -2349,7 +2282,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>16.94</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2360,10 +2293,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>266.38</v>
+        <v>265.48</v>
       </c>
       <c r="D14">
-        <v>-0.43</v>
+        <v>-0.34</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2372,28 +2305,28 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-8.02</v>
+        <v>-8.33</v>
       </c>
       <c r="H14">
-        <v>8.039999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="I14">
-        <v>-1.3</v>
+        <v>-1.64</v>
       </c>
       <c r="J14">
-        <v>-2.1</v>
+        <v>-1.93</v>
       </c>
       <c r="K14">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="M14">
-        <v>-9.859999999999999</v>
+        <v>-10.25</v>
       </c>
       <c r="P14">
-        <v>268.07</v>
+        <v>267.18</v>
       </c>
       <c r="Q14">
-        <v>269.84</v>
+        <v>269.56</v>
       </c>
       <c r="R14">
         <v>268.3</v>
@@ -2408,34 +2341,34 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>39.86</v>
+        <v>37.02</v>
       </c>
       <c r="Z14">
-        <v>-0.21</v>
+        <v>-0.44</v>
       </c>
       <c r="AA14">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="AB14">
-        <v>-0.5</v>
+        <v>-0.58</v>
       </c>
       <c r="AC14">
-        <v>6.35</v>
+        <v>0.59</v>
       </c>
       <c r="AD14">
-        <v>14.36</v>
+        <v>6.01</v>
       </c>
       <c r="AE14">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AF14">
-        <v>-70.97</v>
+        <v>135.85</v>
       </c>
       <c r="AG14">
-        <v>273.56</v>
+        <v>273.69</v>
       </c>
       <c r="AH14">
-        <v>266.12</v>
+        <v>265.42</v>
       </c>
       <c r="AI14">
         <v>261.89</v>
@@ -2444,7 +2377,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>46.7</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2455,10 +2388,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>260.72</v>
+        <v>260.05</v>
       </c>
       <c r="D15">
-        <v>-0.46</v>
+        <v>-0.26</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2467,43 +2400,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-8.300000000000001</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="H15">
-        <v>7.95</v>
+        <v>7.68</v>
       </c>
       <c r="I15">
-        <v>-1.53</v>
+        <v>-1.51</v>
       </c>
       <c r="J15">
-        <v>-2.6</v>
+        <v>-2.43</v>
       </c>
       <c r="K15">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="L15">
-        <v>-1.16</v>
+        <v>-2.13</v>
       </c>
       <c r="M15">
-        <v>8.199999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="N15">
         <v>37</v>
       </c>
       <c r="P15">
-        <v>262.51</v>
+        <v>261.71</v>
       </c>
       <c r="Q15">
-        <v>264.73</v>
+        <v>264.37</v>
       </c>
       <c r="R15">
-        <v>263.28</v>
+        <v>263.27</v>
       </c>
       <c r="S15">
-        <v>266.36</v>
+        <v>266.26</v>
       </c>
       <c r="T15">
-        <v>-2.12</v>
+        <v>-2.33</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -2518,34 +2451,34 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>39.05</v>
+        <v>37.16</v>
       </c>
       <c r="Z15">
-        <v>-0.38</v>
+        <v>-0.6</v>
       </c>
       <c r="AA15">
-        <v>0.19</v>
+        <v>0.03</v>
       </c>
       <c r="AB15">
-        <v>-0.5600000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="AC15">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>13.09</v>
+        <v>5.72</v>
       </c>
       <c r="AE15">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AF15">
-        <v>-53.54</v>
+        <v>12.53</v>
       </c>
       <c r="AG15">
-        <v>268.94</v>
+        <v>268.86</v>
       </c>
       <c r="AH15">
-        <v>260.53</v>
+        <v>259.87</v>
       </c>
       <c r="AI15">
         <v>258.56</v>
@@ -2554,7 +2487,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>52.82</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2565,10 +2498,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>272.12</v>
+        <v>271.22</v>
       </c>
       <c r="D16">
-        <v>-0.48</v>
+        <v>-0.33</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2577,43 +2510,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-8.06</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="H16">
-        <v>7.98</v>
+        <v>7.62</v>
       </c>
       <c r="I16">
-        <v>-1.21</v>
+        <v>-1.59</v>
       </c>
       <c r="J16">
-        <v>-2.23</v>
+        <v>-2.32</v>
       </c>
       <c r="K16">
-        <v>3.07</v>
+        <v>2.74</v>
       </c>
       <c r="L16">
-        <v>-1.12</v>
+        <v>-2.07</v>
       </c>
       <c r="M16">
-        <v>8.25</v>
+        <v>7.99</v>
       </c>
       <c r="N16">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P16">
-        <v>273.92</v>
+        <v>273.04</v>
       </c>
       <c r="Q16">
-        <v>275.91</v>
+        <v>275.55</v>
       </c>
       <c r="R16">
-        <v>274.26</v>
+        <v>274.25</v>
       </c>
       <c r="S16">
-        <v>277.64</v>
+        <v>277.53</v>
       </c>
       <c r="T16">
-        <v>-1.99</v>
+        <v>-2.27</v>
       </c>
       <c r="U16" t="s">
         <v>59</v>
@@ -2628,34 +2561,34 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>39.22</v>
+        <v>36.51</v>
       </c>
       <c r="Z16">
-        <v>-0.26</v>
+        <v>-0.5</v>
       </c>
       <c r="AA16">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="AB16">
-        <v>-0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="AC16">
-        <v>7.25</v>
+        <v>0.4</v>
       </c>
       <c r="AD16">
-        <v>14.44</v>
+        <v>6.54</v>
       </c>
       <c r="AE16">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="AF16">
-        <v>-16.54</v>
+        <v>3.08</v>
       </c>
       <c r="AG16">
-        <v>279.98</v>
+        <v>279.94</v>
       </c>
       <c r="AH16">
-        <v>271.84</v>
+        <v>271.16</v>
       </c>
       <c r="AI16">
         <v>269.25</v>
@@ -2664,7 +2597,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>30.55</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2675,55 +2608,55 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>94.65000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="D17">
-        <v>-0.55</v>
+        <v>0.13</v>
       </c>
       <c r="E17">
         <v>109.87</v>
       </c>
       <c r="F17">
-        <v>76.09999999999999</v>
+        <v>76.22</v>
       </c>
       <c r="G17">
-        <v>-13.85</v>
+        <v>-13.74</v>
       </c>
       <c r="H17">
-        <v>24.38</v>
+        <v>24.34</v>
       </c>
       <c r="I17">
-        <v>-1.38</v>
+        <v>-2.21</v>
       </c>
       <c r="J17">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="K17">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="L17">
-        <v>25.85</v>
+        <v>24.53</v>
       </c>
       <c r="M17">
-        <v>29.76</v>
+        <v>29.91</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>95.77</v>
+        <v>95.34</v>
       </c>
       <c r="Q17">
-        <v>96.48999999999999</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="R17">
-        <v>95.05</v>
+        <v>95.02</v>
       </c>
       <c r="S17">
         <v>95.89</v>
       </c>
       <c r="T17">
-        <v>-1.29</v>
+        <v>-1.17</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -2738,34 +2671,34 @@
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>44.19</v>
+        <v>44.93</v>
       </c>
       <c r="Z17">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="AA17">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AB17">
-        <v>-0.27</v>
+        <v>-0.29</v>
       </c>
       <c r="AC17">
-        <v>8.43</v>
+        <v>1.59</v>
       </c>
       <c r="AD17">
-        <v>19.61</v>
+        <v>9.1</v>
       </c>
       <c r="AE17">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF17">
-        <v>-58.84</v>
+        <v>-58.5</v>
       </c>
       <c r="AG17">
-        <v>98.56999999999999</v>
+        <v>98.63</v>
       </c>
       <c r="AH17">
-        <v>94.41</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2774,7 +2707,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>20.55</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2785,10 +2718,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>281.39</v>
+        <v>282.98</v>
       </c>
       <c r="D18">
-        <v>-0.73</v>
+        <v>0.57</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2797,43 +2730,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.11</v>
+        <v>-4.57</v>
       </c>
       <c r="H18">
-        <v>14.59</v>
+        <v>15.23</v>
       </c>
       <c r="I18">
-        <v>0.09</v>
+        <v>-0.32</v>
       </c>
       <c r="J18">
-        <v>-0.77</v>
+        <v>-0.13</v>
       </c>
       <c r="K18">
-        <v>5.27</v>
+        <v>5.38</v>
       </c>
       <c r="L18">
-        <v>5.73</v>
+        <v>5.61</v>
       </c>
       <c r="M18">
-        <v>8.19</v>
+        <v>8.1</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>283.39</v>
+        <v>283.21</v>
       </c>
       <c r="Q18">
-        <v>281.54</v>
+        <v>281.51</v>
       </c>
       <c r="R18">
-        <v>283.53</v>
+        <v>283.43</v>
       </c>
       <c r="S18">
-        <v>281.24</v>
+        <v>281.21</v>
       </c>
       <c r="T18">
-        <v>0.05</v>
+        <v>0.63</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2848,34 +2781,34 @@
         <v>2</v>
       </c>
       <c r="Y18">
-        <v>48.48</v>
+        <v>52.86</v>
       </c>
       <c r="Z18">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="AA18">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="AC18">
-        <v>69.62</v>
+        <v>65.2</v>
       </c>
       <c r="AD18">
-        <v>84.01000000000001</v>
+        <v>74.23</v>
       </c>
       <c r="AE18">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="AF18">
-        <v>-82.13</v>
+        <v>-74.86</v>
       </c>
       <c r="AG18">
-        <v>285.61</v>
+        <v>285.52</v>
       </c>
       <c r="AH18">
-        <v>277.46</v>
+        <v>277.49</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2884,7 +2817,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>32.86</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2895,10 +2828,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>222.99</v>
+        <v>220.81</v>
       </c>
       <c r="D19">
-        <v>-2.4</v>
+        <v>-0.98</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2907,43 +2840,43 @@
         <v>120.9</v>
       </c>
       <c r="G19">
-        <v>-37.75</v>
+        <v>-38.36</v>
       </c>
       <c r="H19">
-        <v>84.44</v>
+        <v>82.64</v>
       </c>
       <c r="I19">
-        <v>-4.94</v>
+        <v>-6.38</v>
       </c>
       <c r="J19">
-        <v>5.35</v>
+        <v>4.01</v>
       </c>
       <c r="K19">
-        <v>-11.68</v>
+        <v>-11.47</v>
       </c>
       <c r="L19">
-        <v>91.7</v>
+        <v>81.72</v>
       </c>
       <c r="M19">
-        <v>51.32</v>
+        <v>50.55</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>231.08</v>
+        <v>228.07</v>
       </c>
       <c r="Q19">
-        <v>228.73</v>
+        <v>228.84</v>
       </c>
       <c r="R19">
-        <v>220.82</v>
+        <v>220.86</v>
       </c>
       <c r="S19">
-        <v>230.79</v>
+        <v>231.13</v>
       </c>
       <c r="T19">
-        <v>-3.38</v>
+        <v>-4.46</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2958,34 +2891,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>45.73</v>
+        <v>43.68</v>
       </c>
       <c r="Z19">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="AA19">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="AB19">
-        <v>-0.5</v>
+        <v>-1.13</v>
       </c>
       <c r="AC19">
-        <v>24.49</v>
+        <v>2.86</v>
       </c>
       <c r="AD19">
-        <v>40.96</v>
+        <v>21.85</v>
       </c>
       <c r="AE19">
-        <v>6.55</v>
+        <v>6.36</v>
       </c>
       <c r="AF19">
-        <v>6.19</v>
+        <v>-29.78</v>
       </c>
       <c r="AG19">
-        <v>240.16</v>
+        <v>239.9</v>
       </c>
       <c r="AH19">
-        <v>217.29</v>
+        <v>217.77</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2994,7 +2927,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>30.49</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -3005,10 +2938,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>258.44</v>
+        <v>257.65</v>
       </c>
       <c r="D20">
-        <v>-0.51</v>
+        <v>-0.31</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -3017,43 +2950,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-8.1</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="H20">
-        <v>7.98</v>
+        <v>7.65</v>
       </c>
       <c r="I20">
-        <v>-1.23</v>
+        <v>-1.55</v>
       </c>
       <c r="J20">
         <v>-2.32</v>
       </c>
       <c r="K20">
-        <v>2.93</v>
+        <v>2.71</v>
       </c>
       <c r="L20">
-        <v>-0.98</v>
+        <v>-2.05</v>
       </c>
       <c r="M20">
-        <v>8.199999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="N20">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P20">
-        <v>260.18</v>
+        <v>259.37</v>
       </c>
       <c r="Q20">
-        <v>262.05</v>
+        <v>261.73</v>
       </c>
       <c r="R20">
-        <v>260.55</v>
+        <v>260.54</v>
       </c>
       <c r="S20">
-        <v>263.75</v>
+        <v>263.65</v>
       </c>
       <c r="T20">
-        <v>-2.01</v>
+        <v>-2.28</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
@@ -3068,34 +3001,34 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>39.22</v>
+        <v>36.74</v>
       </c>
       <c r="Z20">
-        <v>-0.26</v>
+        <v>-0.48</v>
       </c>
       <c r="AA20">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="AB20">
-        <v>-0.51</v>
+        <v>-0.59</v>
       </c>
       <c r="AC20">
-        <v>9.27</v>
+        <v>1.87</v>
       </c>
       <c r="AD20">
-        <v>16.94</v>
+        <v>8.74</v>
       </c>
       <c r="AE20">
-        <v>4.16</v>
+        <v>3.99</v>
       </c>
       <c r="AF20">
-        <v>33.99</v>
+        <v>54.21</v>
       </c>
       <c r="AG20">
-        <v>265.82</v>
+        <v>265.85</v>
       </c>
       <c r="AH20">
-        <v>258.27</v>
+        <v>257.6</v>
       </c>
       <c r="AI20">
         <v>253.97</v>
@@ -3104,7 +3037,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>26.42</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3115,10 +3048,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>784.0599999999999</v>
+        <v>779.13</v>
       </c>
       <c r="D21">
-        <v>-0.46</v>
+        <v>-0.63</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3127,43 +3060,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-2.39</v>
+        <v>-3</v>
       </c>
       <c r="H21">
-        <v>22</v>
+        <v>21.23</v>
       </c>
       <c r="I21">
-        <v>-1.42</v>
+        <v>-2.85</v>
       </c>
       <c r="J21">
-        <v>-1.41</v>
+        <v>-1.25</v>
       </c>
       <c r="K21">
-        <v>4.58</v>
+        <v>3.75</v>
       </c>
       <c r="L21">
-        <v>11.91</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M21">
-        <v>12.54</v>
+        <v>12.16</v>
       </c>
       <c r="N21">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P21">
-        <v>792.78</v>
+        <v>788.21</v>
       </c>
       <c r="Q21">
-        <v>796.39</v>
+        <v>795.79</v>
       </c>
       <c r="R21">
-        <v>783.02</v>
+        <v>783.23</v>
       </c>
       <c r="S21">
-        <v>745.35</v>
+        <v>745.52</v>
       </c>
       <c r="T21">
-        <v>5.19</v>
+        <v>4.51</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -3178,34 +3111,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>43.3</v>
+        <v>39.3</v>
       </c>
       <c r="Z21">
-        <v>2.14</v>
+        <v>0.88</v>
       </c>
       <c r="AA21">
-        <v>4.44</v>
+        <v>3.73</v>
       </c>
       <c r="AB21">
-        <v>-2.3</v>
+        <v>-2.85</v>
       </c>
       <c r="AC21">
         <v>0</v>
       </c>
       <c r="AD21">
-        <v>7.16</v>
+        <v>0.22</v>
       </c>
       <c r="AE21">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
       <c r="AF21">
-        <v>-13.59</v>
+        <v>19.26</v>
       </c>
       <c r="AG21">
-        <v>806.36</v>
+        <v>808.23</v>
       </c>
       <c r="AH21">
-        <v>786.42</v>
+        <v>783.34</v>
       </c>
       <c r="AI21">
         <v>773.79</v>
@@ -3214,7 +3147,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>19.54</v>
+        <v>21.64</v>
       </c>
     </row>
   </sheetData>
@@ -3355,7 +3288,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3395,7 +3328,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3414,2161 +3347,2140 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-0.59</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-0.65</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-2.49</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-1.04</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-6.13</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-6.59</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6.89</v>
+      </c>
+      <c r="D12" s="7">
+        <v>5.44</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>7.02</v>
+      </c>
+      <c r="D13" s="7">
+        <v>5.52</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>98</v>
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-5.5</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-4.21</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.29</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>0.5600000000000001</v>
+        <v>-2.23</v>
       </c>
       <c r="D15" s="7">
-        <v>-0.59</v>
+        <v>-1.55</v>
       </c>
       <c r="E15" s="8">
-        <v>-1.15</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>0.32</v>
+        <v>-0.66</v>
       </c>
       <c r="D16" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.26</v>
+        <v>-1.01</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-2.45</v>
+        <v>-0.54</v>
       </c>
       <c r="D17" s="7">
-        <v>-2.49</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.04</v>
+        <v>-0.89</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-4.97</v>
+        <v>-1.67</v>
       </c>
       <c r="D18" s="7">
-        <v>-6.13</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.16</v>
+        <v>-1.7</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>8.720000000000001</v>
+        <v>-2.37</v>
       </c>
       <c r="D19" s="7">
-        <v>6.89</v>
+        <v>-2.23</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.83</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>8.92</v>
+        <v>-2.1</v>
       </c>
       <c r="D20" s="7">
-        <v>7.02</v>
+        <v>-1.93</v>
       </c>
       <c r="E20" s="8">
-        <v>-1.9</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-5.46</v>
+        <v>-2.6</v>
       </c>
       <c r="D21" s="7">
-        <v>-5.5</v>
+        <v>-2.43</v>
       </c>
       <c r="E21" s="8">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>-1.93</v>
+        <v>-2.23</v>
       </c>
       <c r="D22" s="7">
-        <v>-2.23</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.3</v>
+        <v>-2.32</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="D23" s="7">
-        <v>-0.66</v>
+        <v>0.24</v>
       </c>
       <c r="E23" s="8">
-        <v>-1.16</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>0.59</v>
+        <v>-0.77</v>
       </c>
       <c r="D24" s="7">
-        <v>-0.54</v>
+        <v>-0.13</v>
       </c>
       <c r="E24" s="8">
-        <v>-1.13</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>-0.22</v>
+        <v>5.35</v>
       </c>
       <c r="D25" s="7">
-        <v>-1.67</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.45</v>
+        <v>4.01</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>-0.92</v>
+        <v>-1.41</v>
       </c>
       <c r="D26" s="7">
-        <v>-2.37</v>
+        <v>-1.25</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.45</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>-1.02</v>
+        <v>-0.22</v>
       </c>
       <c r="D27" s="7">
-        <v>-2.1</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.08</v>
+        <v>-1.14</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="7">
-        <v>-1.33</v>
+        <v>-0.5</v>
       </c>
       <c r="D28" s="7">
-        <v>-2.6</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.27</v>
+        <v>-1.23</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-1.33</v>
       </c>
       <c r="D29" s="7">
-        <v>-2.23</v>
+        <v>0.48</v>
       </c>
       <c r="E29" s="8">
-        <v>-1.29</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>1.87</v>
+        <v>-2.72</v>
       </c>
       <c r="D30" s="7">
-        <v>0.08</v>
+        <v>-2.47</v>
       </c>
       <c r="E30" s="8">
-        <v>-1.79</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>1.08</v>
+        <v>-5.6</v>
       </c>
       <c r="D31" s="7">
-        <v>-0.77</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.85</v>
+        <v>-6.69</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>7.95</v>
+        <v>-5.38</v>
       </c>
       <c r="D32" s="7">
-        <v>5.35</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.6</v>
+        <v>-6.53</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>-1.02</v>
+        <v>-0.57</v>
       </c>
       <c r="D33" s="7">
-        <v>-2.32</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.3</v>
+        <v>-1.52</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>-0.2</v>
+        <v>-1.84</v>
       </c>
       <c r="D34" s="7">
-        <v>-1.41</v>
+        <v>-1.2</v>
       </c>
       <c r="E34" s="8">
-        <v>-1.21</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>0.15</v>
+        <v>2.33</v>
       </c>
       <c r="D35" s="7">
-        <v>-0.22</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.37</v>
+        <v>1.69</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>0.2</v>
+        <v>2.56</v>
       </c>
       <c r="D36" s="7">
-        <v>-0.5</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.7</v>
+        <v>1.87</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-1.58</v>
+        <v>-1.99</v>
       </c>
       <c r="D37" s="7">
-        <v>-1.33</v>
+        <v>-2.29</v>
       </c>
       <c r="E37" s="9">
-        <v>0.25</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>-1.76</v>
+        <v>-1.33</v>
       </c>
       <c r="D38" s="7">
-        <v>-2.72</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.96</v>
+        <v>-1.61</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-4.29</v>
+        <v>-1.3</v>
       </c>
       <c r="D39" s="7">
-        <v>-5.6</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.31</v>
+        <v>-1.64</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>-4.15</v>
+        <v>-1.53</v>
       </c>
       <c r="D40" s="7">
-        <v>-5.38</v>
+        <v>-1.51</v>
       </c>
       <c r="E40" s="8">
-        <v>-1.23</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-0.85</v>
+        <v>-1.21</v>
       </c>
       <c r="D41" s="7">
-        <v>-0.57</v>
+        <v>-1.59</v>
       </c>
       <c r="E41" s="9">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>-1.33</v>
+        <v>-1.38</v>
       </c>
       <c r="D42" s="7">
-        <v>-1.84</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.51</v>
+        <v>-2.21</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>1.45</v>
+        <v>0.09</v>
       </c>
       <c r="D43" s="7">
-        <v>2.33</v>
+        <v>-0.32</v>
       </c>
       <c r="E43" s="9">
-        <v>0.88</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>1.18</v>
+        <v>-4.94</v>
       </c>
       <c r="D44" s="7">
-        <v>2.56</v>
+        <v>-6.38</v>
       </c>
       <c r="E44" s="9">
-        <v>1.38</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>-0.76</v>
+        <v>-1.23</v>
       </c>
       <c r="D45" s="7">
-        <v>-1.99</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.23</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>-0.36</v>
+        <v>-1.42</v>
       </c>
       <c r="D46" s="7">
-        <v>-1.33</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.97</v>
+        <v>-2.85</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C47" s="7">
-        <v>-0.42</v>
+        <v>6.99</v>
       </c>
       <c r="D47" s="7">
-        <v>-1.3</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.88</v>
+        <v>6.24</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C48" s="7">
-        <v>-0.6</v>
+        <v>-89.31</v>
       </c>
       <c r="D48" s="7">
-        <v>-1.53</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.93</v>
+        <v>-89.38</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C49" s="7">
-        <v>-0.47</v>
+        <v>5.35</v>
       </c>
       <c r="D49" s="7">
-        <v>-1.21</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.74</v>
+        <v>5.19</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>0.04</v>
+        <v>-17.02</v>
       </c>
       <c r="D50" s="7">
-        <v>-1.38</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.42</v>
+        <v>-17.03</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>0.37</v>
+        <v>46.87</v>
       </c>
       <c r="D51" s="7">
-        <v>0.09</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.28</v>
+        <v>42.62</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>-3.74</v>
+        <v>47.35</v>
       </c>
       <c r="D52" s="7">
-        <v>-4.94</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.2</v>
+        <v>42.91</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-4.44</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>-0.42</v>
+        <v>1.04</v>
       </c>
       <c r="D53" s="7">
-        <v>-1.23</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-1.9</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>-0.66</v>
+        <v>3.46</v>
       </c>
       <c r="D54" s="7">
-        <v>-1.42</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.76</v>
+        <v>2.96</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>6.97</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="D55" s="7">
-        <v>6.99</v>
+        <v>-11.78</v>
       </c>
       <c r="E55" s="9">
-        <v>0.02</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>5.36</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="D56" s="7">
-        <v>5.35</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.01</v>
+        <v>-11.73</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>-15.47</v>
+        <v>11.41</v>
       </c>
       <c r="D57" s="7">
-        <v>-17.02</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-1.55</v>
+        <v>10.04</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>50.82</v>
+        <v>-1.02</v>
       </c>
       <c r="D58" s="7">
-        <v>46.87</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-3.95</v>
+        <v>-2.02</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-1</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>51.36</v>
+        <v>-1.16</v>
       </c>
       <c r="D59" s="7">
-        <v>47.35</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-4.01</v>
+        <v>-2.13</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>2.22</v>
+        <v>-1.12</v>
       </c>
       <c r="D60" s="7">
-        <v>1.04</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.18</v>
+        <v>-2.07</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>3.51</v>
+        <v>25.85</v>
       </c>
       <c r="D61" s="7">
-        <v>3.46</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.05</v>
+        <v>24.53</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>-11.11</v>
+        <v>5.73</v>
       </c>
       <c r="D62" s="7">
-        <v>-9.279999999999999</v>
+        <v>5.61</v>
       </c>
       <c r="E62" s="9">
-        <v>1.83</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>-11.32</v>
+        <v>91.7</v>
       </c>
       <c r="D63" s="7">
-        <v>-9.449999999999999</v>
+        <v>81.72</v>
       </c>
       <c r="E63" s="9">
-        <v>1.87</v>
+        <v>-9.98</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>11.89</v>
+        <v>-0.98</v>
       </c>
       <c r="D64" s="7">
-        <v>11.41</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.48</v>
+        <v>-2.05</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>-0.74</v>
+        <v>11.91</v>
       </c>
       <c r="D65" s="7">
-        <v>-1.02</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.28</v>
+        <v>9.859999999999999</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="7">
-        <v>-0.86</v>
+        <v>5.79</v>
       </c>
       <c r="D66" s="7">
-        <v>-1.16</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.3</v>
+        <v>5.27</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="7">
-        <v>-0.74</v>
+        <v>4.75</v>
       </c>
       <c r="D67" s="7">
-        <v>-1.12</v>
+        <v>5.1</v>
       </c>
       <c r="E67" s="8">
-        <v>-0.38</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" s="7">
-        <v>26.05</v>
+        <v>-8.4</v>
       </c>
       <c r="D68" s="7">
-        <v>25.85</v>
+        <v>-6.52</v>
       </c>
       <c r="E68" s="8">
-        <v>-0.2</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>6.48</v>
+        <v>-3.75</v>
       </c>
       <c r="D69" s="7">
-        <v>5.73</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.75</v>
+        <v>-3.92</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>97.67</v>
+        <v>-2.46</v>
       </c>
       <c r="D70" s="7">
-        <v>91.7</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-5.97</v>
+        <v>-3.33</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>-0.78</v>
+        <v>-2.26</v>
       </c>
       <c r="D71" s="7">
-        <v>-0.98</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-0.2</v>
+        <v>-3.19</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>12.04</v>
+        <v>-8.1</v>
       </c>
       <c r="D72" s="7">
-        <v>11.91</v>
+        <v>-6.6</v>
       </c>
       <c r="E72" s="8">
-        <v>-0.13</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>6.42</v>
+        <v>-0.19</v>
       </c>
       <c r="D73" s="7">
-        <v>5.79</v>
+        <v>0.52</v>
       </c>
       <c r="E73" s="8">
-        <v>-0.63</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="7">
-        <v>6.46</v>
+        <v>6.86</v>
       </c>
       <c r="D74" s="7">
-        <v>4.75</v>
+        <v>7.14</v>
       </c>
       <c r="E74" s="8">
-        <v>-1.71</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>-7.99</v>
+        <v>6.85</v>
       </c>
       <c r="D75" s="7">
-        <v>-8.4</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-0.41</v>
+        <v>6.64</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>-2.94</v>
+        <v>4.24</v>
       </c>
       <c r="D76" s="7">
-        <v>-3.75</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.8100000000000001</v>
+        <v>4.04</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>-0.25</v>
+        <v>2.88</v>
       </c>
       <c r="D77" s="7">
-        <v>-2.46</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-2.21</v>
+        <v>2.71</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>-0.08</v>
+        <v>2.91</v>
       </c>
       <c r="D78" s="7">
-        <v>-2.26</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-2.18</v>
+        <v>2.9</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>-8.140000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="D79" s="7">
-        <v>-8.1</v>
+        <v>2.69</v>
       </c>
       <c r="E79" s="9">
-        <v>0.04</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>-0.03</v>
+        <v>3.07</v>
       </c>
       <c r="D80" s="7">
-        <v>-0.19</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-0.16</v>
+        <v>2.74</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>5.37</v>
+        <v>2.79</v>
       </c>
       <c r="D81" s="7">
-        <v>6.86</v>
+        <v>2.7</v>
       </c>
       <c r="E81" s="9">
-        <v>1.49</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="7">
-        <v>5.15</v>
+        <v>5.27</v>
       </c>
       <c r="D82" s="7">
-        <v>6.85</v>
-      </c>
-      <c r="E82" s="9">
-        <v>1.7</v>
+        <v>5.38</v>
+      </c>
+      <c r="E82" s="8">
+        <v>0.11</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>5.32</v>
+        <v>-11.68</v>
       </c>
       <c r="D83" s="7">
-        <v>4.24</v>
+        <v>-11.47</v>
       </c>
       <c r="E83" s="8">
-        <v>-1.08</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>3.51</v>
+        <v>2.93</v>
       </c>
       <c r="D84" s="7">
-        <v>2.88</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.63</v>
+        <v>2.71</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>3.49</v>
+        <v>4.58</v>
       </c>
       <c r="D85" s="7">
-        <v>2.91</v>
-      </c>
-      <c r="E85" s="8">
-        <v>-0.58</v>
+        <v>3.75</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C86" s="7">
-        <v>3.26</v>
+        <v>-6.62</v>
       </c>
       <c r="D86" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-0.46</v>
+        <v>-6.78</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C87" s="7">
-        <v>3.47</v>
+        <v>-14.96</v>
       </c>
       <c r="D87" s="7">
-        <v>3.07</v>
+        <v>-13.94</v>
       </c>
       <c r="E87" s="8">
-        <v>-0.4</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7">
-        <v>3.87</v>
+        <v>-18.39</v>
       </c>
       <c r="D88" s="7">
-        <v>2.79</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-1.08</v>
+        <v>-18.46</v>
+      </c>
+      <c r="E88" s="9">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89" s="7">
-        <v>6.04</v>
+        <v>-14.46</v>
       </c>
       <c r="D89" s="7">
-        <v>5.27</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.77</v>
+        <v>-15.7</v>
+      </c>
+      <c r="E89" s="9">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C90" s="7">
-        <v>-9.619999999999999</v>
+        <v>-14.31</v>
       </c>
       <c r="D90" s="7">
-        <v>-11.68</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-2.06</v>
+        <v>-15.58</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91" s="7">
-        <v>3.63</v>
+        <v>-17.13</v>
       </c>
       <c r="D91" s="7">
-        <v>2.93</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-0.7</v>
+        <v>-17.25</v>
+      </c>
+      <c r="E91" s="9">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C92" s="7">
-        <v>5.27</v>
+        <v>-5.79</v>
       </c>
       <c r="D92" s="7">
-        <v>4.58</v>
+        <v>-5.48</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.6899999999999999</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="7">
-        <v>-6.33</v>
+        <v>-19.57</v>
       </c>
       <c r="D93" s="7">
-        <v>-6.62</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-0.29</v>
+        <v>-20.41</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="7">
-        <v>-90.64</v>
+        <v>-19.64</v>
       </c>
       <c r="D94" s="7">
-        <v>-90.69</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-0.05</v>
+        <v>-20.56</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-14.92</v>
+        <v>-2.57</v>
       </c>
       <c r="D95" s="7">
-        <v>-14.96</v>
+        <v>-2.55</v>
       </c>
       <c r="E95" s="8">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-17.87</v>
+        <v>-8.17</v>
       </c>
       <c r="D96" s="7">
-        <v>-18.39</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-0.52</v>
+        <v>-8.4</v>
+      </c>
+      <c r="E96" s="9">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-13.11</v>
+        <v>-8.02</v>
       </c>
       <c r="D97" s="7">
-        <v>-14.46</v>
-      </c>
-      <c r="E97" s="8">
-        <v>-1.35</v>
+        <v>-8.33</v>
+      </c>
+      <c r="E97" s="9">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-12.92</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="D98" s="7">
-        <v>-14.31</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-1.39</v>
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E98" s="9">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-16.94</v>
+        <v>-8.06</v>
       </c>
       <c r="D99" s="7">
-        <v>-17.13</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-0.19</v>
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E99" s="9">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-5.52</v>
+        <v>-13.85</v>
       </c>
       <c r="D100" s="7">
-        <v>-5.79</v>
+        <v>-13.74</v>
       </c>
       <c r="E100" s="8">
-        <v>-0.27</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-20.5</v>
+        <v>-5.11</v>
       </c>
       <c r="D101" s="7">
-        <v>-19.57</v>
-      </c>
-      <c r="E101" s="9">
-        <v>0.93</v>
+        <v>-4.57</v>
+      </c>
+      <c r="E101" s="8">
+        <v>0.54</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-20.72</v>
+        <v>-37.75</v>
       </c>
       <c r="D102" s="7">
-        <v>-19.64</v>
+        <v>-38.36</v>
       </c>
       <c r="E102" s="9">
-        <v>1.08</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-1.87</v>
+        <v>-8.1</v>
       </c>
       <c r="D103" s="7">
-        <v>-2.57</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-0.7</v>
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="E103" s="9">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-7.62</v>
+        <v>-2.39</v>
       </c>
       <c r="D104" s="7">
-        <v>-8.17</v>
-      </c>
-      <c r="E104" s="8">
-        <v>-0.55</v>
+        <v>-3</v>
+      </c>
+      <c r="E104" s="9">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C105" s="7">
-        <v>-7.62</v>
+        <v>593.79</v>
       </c>
       <c r="D105" s="7">
-        <v>-8.02</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-0.4</v>
+        <v>592.76</v>
+      </c>
+      <c r="E105" s="9">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C106" s="7">
-        <v>-7.88</v>
+        <v>59.31</v>
       </c>
       <c r="D106" s="7">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="E106" s="8">
-        <v>-0.42</v>
+        <v>59.3</v>
+      </c>
+      <c r="E106" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C107" s="7">
-        <v>-7.62</v>
+        <v>92.53</v>
       </c>
       <c r="D107" s="7">
-        <v>-8.06</v>
+        <v>93.64</v>
       </c>
       <c r="E107" s="8">
-        <v>-0.44</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C108" s="7">
-        <v>-13.38</v>
+        <v>49.78</v>
       </c>
       <c r="D108" s="7">
-        <v>-13.85</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-0.47</v>
+        <v>49.74</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C109" s="7">
-        <v>-4.41</v>
+        <v>125.34</v>
       </c>
       <c r="D109" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-0.7</v>
+        <v>123.52</v>
+      </c>
+      <c r="E109" s="9">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C110" s="7">
-        <v>-36.22</v>
+        <v>129.71</v>
       </c>
       <c r="D110" s="7">
-        <v>-37.75</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-1.53</v>
+        <v>127.8</v>
+      </c>
+      <c r="E110" s="9">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C111" s="7">
-        <v>-7.63</v>
+        <v>469.33</v>
       </c>
       <c r="D111" s="7">
-        <v>-8.1</v>
-      </c>
-      <c r="E111" s="8">
-        <v>-0.47</v>
+        <v>468.63</v>
+      </c>
+      <c r="E111" s="9">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C112" s="7">
-        <v>-1.93</v>
+        <v>950.4</v>
       </c>
       <c r="D112" s="7">
-        <v>-2.39</v>
+        <v>953.53</v>
       </c>
       <c r="E112" s="8">
-        <v>-0.46</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="7">
-        <v>595.58</v>
+        <v>34.72</v>
       </c>
       <c r="D113" s="7">
-        <v>593.79</v>
-      </c>
-      <c r="E113" s="8">
-        <v>-1.79</v>
+        <v>34.36</v>
+      </c>
+      <c r="E113" s="9">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="7">
-        <v>59.65</v>
+        <v>34.79</v>
       </c>
       <c r="D114" s="7">
-        <v>59.31</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-0.34</v>
+        <v>34.39</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>92.58</v>
+        <v>788.17</v>
       </c>
       <c r="D115" s="7">
-        <v>92.53</v>
+        <v>788.4</v>
       </c>
       <c r="E115" s="8">
-        <v>-0.05</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>50.1</v>
+        <v>273.25</v>
       </c>
       <c r="D116" s="7">
-        <v>49.78</v>
-      </c>
-      <c r="E116" s="8">
-        <v>-0.32</v>
+        <v>272.56</v>
+      </c>
+      <c r="E116" s="9">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>127.32</v>
+        <v>266.38</v>
       </c>
       <c r="D117" s="7">
-        <v>125.34</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-1.98</v>
+        <v>265.48</v>
+      </c>
+      <c r="E117" s="9">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>131.82</v>
+        <v>260.72</v>
       </c>
       <c r="D118" s="7">
-        <v>129.71</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-2.11</v>
+        <v>260.05</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>470.43</v>
+        <v>272.12</v>
       </c>
       <c r="D119" s="7">
-        <v>469.33</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-1.1</v>
+        <v>271.22</v>
+      </c>
+      <c r="E119" s="9">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>953.22</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="D120" s="7">
-        <v>950.4</v>
+        <v>94.77</v>
       </c>
       <c r="E120" s="8">
-        <v>-2.82</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>34.32</v>
+        <v>281.39</v>
       </c>
       <c r="D121" s="7">
-        <v>34.72</v>
-      </c>
-      <c r="E121" s="9">
-        <v>0.4</v>
+        <v>282.98</v>
+      </c>
+      <c r="E121" s="8">
+        <v>1.59</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>34.32</v>
+        <v>222.99</v>
       </c>
       <c r="D122" s="7">
-        <v>34.79</v>
+        <v>220.81</v>
       </c>
       <c r="E122" s="9">
-        <v>0.47</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>793.86</v>
+        <v>258.44</v>
       </c>
       <c r="D123" s="7">
-        <v>788.17</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-5.69</v>
+        <v>257.65</v>
+      </c>
+      <c r="E123" s="9">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>274.87</v>
+        <v>784.0599999999999</v>
       </c>
       <c r="D124" s="7">
-        <v>273.25</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-1.62</v>
+        <v>779.13</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-4.93</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C125" s="7">
-        <v>267.54</v>
+        <v>22</v>
       </c>
       <c r="D125" s="7">
-        <v>266.38</v>
+        <v>32</v>
       </c>
       <c r="E125" s="8">
-        <v>-1.16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C126" s="7">
-        <v>261.92</v>
+        <v>32</v>
       </c>
       <c r="D126" s="7">
-        <v>260.72</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-1.2</v>
+        <v>27</v>
+      </c>
+      <c r="E126" s="9">
+        <v>-5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C127" s="7">
-        <v>273.42</v>
+        <v>27</v>
       </c>
       <c r="D127" s="7">
-        <v>272.12</v>
-      </c>
-      <c r="E127" s="8">
-        <v>-1.3</v>
+        <v>22</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-5</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C128" s="7">
-        <v>95.17</v>
+        <v>73</v>
       </c>
       <c r="D128" s="7">
-        <v>94.65000000000001</v>
+        <v>78</v>
       </c>
       <c r="E128" s="8">
-        <v>-0.52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="7">
+        <v>42</v>
+      </c>
+      <c r="D129" s="7">
         <v>53</v>
       </c>
-      <c r="B129" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C129" s="7">
-        <v>283.45</v>
-      </c>
-      <c r="D129" s="7">
-        <v>281.39</v>
-      </c>
       <c r="E129" s="8">
-        <v>-2.06</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C130" s="7">
-        <v>228.47</v>
+        <v>53</v>
       </c>
       <c r="D130" s="7">
-        <v>222.99</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-5.48</v>
+        <v>47</v>
+      </c>
+      <c r="E130" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5576,16 +5488,16 @@
         <v>55</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C131" s="7">
-        <v>259.76</v>
+        <v>47</v>
       </c>
       <c r="D131" s="7">
-        <v>258.44</v>
-      </c>
-      <c r="E131" s="8">
-        <v>-1.32</v>
+        <v>42</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5593,804 +5505,702 @@
         <v>56</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C132" s="7">
-        <v>787.71</v>
+        <v>78</v>
       </c>
       <c r="D132" s="7">
-        <v>784.0599999999999</v>
-      </c>
-      <c r="E132" s="8">
-        <v>-3.65</v>
+        <v>73</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C133" s="7">
-        <v>32</v>
+        <v>47.16</v>
       </c>
       <c r="D133" s="7">
-        <v>22</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-10</v>
+        <v>45.55</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C134" s="7">
-        <v>27</v>
+        <v>44.31</v>
       </c>
       <c r="D134" s="7">
-        <v>32</v>
+        <v>44.19</v>
       </c>
       <c r="E134" s="9">
-        <v>5</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C135" s="7">
-        <v>22</v>
+        <v>33.16</v>
       </c>
       <c r="D135" s="7">
-        <v>27</v>
-      </c>
-      <c r="E135" s="9">
-        <v>5</v>
+        <v>46.21</v>
+      </c>
+      <c r="E135" s="8">
+        <v>13.05</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C136" s="7">
-        <v>47</v>
+        <v>26.86</v>
       </c>
       <c r="D136" s="7">
-        <v>42</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-5</v>
+        <v>26.59</v>
+      </c>
+      <c r="E136" s="9">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C137" s="7">
-        <v>42</v>
+        <v>48.76</v>
       </c>
       <c r="D137" s="7">
-        <v>53</v>
+        <v>44.26</v>
       </c>
       <c r="E137" s="9">
-        <v>11</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C138" s="7">
-        <v>53</v>
+        <v>49.01</v>
       </c>
       <c r="D138" s="7">
-        <v>47</v>
-      </c>
-      <c r="E138" s="8">
-        <v>-6</v>
+        <v>44.29</v>
+      </c>
+      <c r="E138" s="9">
+        <v>-4.72</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="7">
-        <v>50</v>
+        <v>35.67</v>
       </c>
       <c r="D139" s="7">
-        <v>47.16</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-2.84</v>
+        <v>35</v>
+      </c>
+      <c r="E139" s="9">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="7">
-        <v>48.45</v>
+        <v>34.46</v>
       </c>
       <c r="D140" s="7">
-        <v>44.31</v>
+        <v>38.38</v>
       </c>
       <c r="E140" s="8">
-        <v>-4.14</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="7">
-        <v>33.5</v>
+        <v>59.53</v>
       </c>
       <c r="D141" s="7">
-        <v>33.16</v>
-      </c>
-      <c r="E141" s="8">
-        <v>-0.34</v>
+        <v>55</v>
+      </c>
+      <c r="E141" s="9">
+        <v>-4.53</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="7">
-        <v>29.06</v>
+        <v>59.67</v>
       </c>
       <c r="D142" s="7">
-        <v>26.86</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-2.2</v>
+        <v>54.81</v>
+      </c>
+      <c r="E142" s="9">
+        <v>-4.86</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="7">
-        <v>54.35</v>
+        <v>39.35</v>
       </c>
       <c r="D143" s="7">
-        <v>48.76</v>
+        <v>39.67</v>
       </c>
       <c r="E143" s="8">
-        <v>-5.59</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="7">
-        <v>55.03</v>
+        <v>38.81</v>
       </c>
       <c r="D144" s="7">
-        <v>49.01</v>
-      </c>
-      <c r="E144" s="8">
-        <v>-6.02</v>
+        <v>36.84</v>
+      </c>
+      <c r="E144" s="9">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="7">
-        <v>36.7</v>
+        <v>39.86</v>
       </c>
       <c r="D145" s="7">
-        <v>35.67</v>
-      </c>
-      <c r="E145" s="8">
-        <v>-1.03</v>
+        <v>37.02</v>
+      </c>
+      <c r="E145" s="9">
+        <v>-2.84</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>36.4</v>
+        <v>39.05</v>
       </c>
       <c r="D146" s="7">
-        <v>34.46</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-1.94</v>
+        <v>37.16</v>
+      </c>
+      <c r="E146" s="9">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>55.78</v>
+        <v>39.22</v>
       </c>
       <c r="D147" s="7">
-        <v>59.53</v>
+        <v>36.51</v>
       </c>
       <c r="E147" s="9">
-        <v>3.75</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>55.35</v>
+        <v>44.19</v>
       </c>
       <c r="D148" s="7">
-        <v>59.67</v>
-      </c>
-      <c r="E148" s="9">
-        <v>4.32</v>
+        <v>44.93</v>
+      </c>
+      <c r="E148" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>44.72</v>
+        <v>48.48</v>
       </c>
       <c r="D149" s="7">
-        <v>39.35</v>
+        <v>52.86</v>
       </c>
       <c r="E149" s="8">
-        <v>-5.37</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>43.94</v>
+        <v>45.73</v>
       </c>
       <c r="D150" s="7">
-        <v>38.81</v>
-      </c>
-      <c r="E150" s="8">
-        <v>-5.13</v>
+        <v>43.68</v>
+      </c>
+      <c r="E150" s="9">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>43.88</v>
+        <v>39.22</v>
       </c>
       <c r="D151" s="7">
-        <v>39.86</v>
-      </c>
-      <c r="E151" s="8">
-        <v>-4.02</v>
+        <v>36.74</v>
+      </c>
+      <c r="E151" s="9">
+        <v>-2.48</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>42.65</v>
+        <v>43.3</v>
       </c>
       <c r="D152" s="7">
-        <v>39.05</v>
-      </c>
-      <c r="E152" s="8">
-        <v>-3.6</v>
+        <v>39.3</v>
+      </c>
+      <c r="E152" s="9">
+        <v>-4</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C153" s="7">
-        <v>43.55</v>
+        <v>-18.96</v>
       </c>
       <c r="D153" s="7">
-        <v>39.22</v>
+        <v>92.19</v>
       </c>
       <c r="E153" s="8">
-        <v>-4.33</v>
+        <v>111.15</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="6" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C154" s="7">
-        <v>46.71</v>
+        <v>-79.84</v>
       </c>
       <c r="D154" s="7">
-        <v>44.19</v>
+        <v>-74.95</v>
       </c>
       <c r="E154" s="8">
-        <v>-2.52</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C155" s="7">
-        <v>54.58</v>
+        <v>-45.88</v>
       </c>
       <c r="D155" s="7">
-        <v>48.48</v>
+        <v>30.79</v>
       </c>
       <c r="E155" s="8">
-        <v>-6.1</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C156" s="7">
-        <v>51.35</v>
+        <v>212.78</v>
       </c>
       <c r="D156" s="7">
-        <v>45.73</v>
-      </c>
-      <c r="E156" s="8">
-        <v>-5.62</v>
+        <v>-3.13</v>
+      </c>
+      <c r="E156" s="9">
+        <v>-215.91</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C157" s="7">
-        <v>43.8</v>
+        <v>22.09</v>
       </c>
       <c r="D157" s="7">
-        <v>39.22</v>
-      </c>
-      <c r="E157" s="8">
-        <v>-4.58</v>
+        <v>21.1</v>
+      </c>
+      <c r="E157" s="9">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C158" s="7">
-        <v>46.55</v>
+        <v>70.8</v>
       </c>
       <c r="D158" s="7">
-        <v>43.3</v>
-      </c>
-      <c r="E158" s="8">
-        <v>-3.25</v>
+        <v>23</v>
+      </c>
+      <c r="E158" s="9">
+        <v>-47.8</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="7">
-        <v>-42.27</v>
+        <v>0.37</v>
       </c>
       <c r="D159" s="7">
-        <v>-18.96</v>
+        <v>-40.44</v>
       </c>
       <c r="E159" s="9">
-        <v>23.31</v>
+        <v>-40.81</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="7">
-        <v>-75.20999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D160" s="7">
-        <v>-79.84</v>
-      </c>
-      <c r="E160" s="8">
-        <v>-4.63</v>
+        <v>42.78</v>
+      </c>
+      <c r="E160" s="9">
+        <v>-55.62</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="7">
-        <v>-42.01</v>
+        <v>75.41</v>
       </c>
       <c r="D161" s="7">
-        <v>-45.88</v>
-      </c>
-      <c r="E161" s="8">
-        <v>-3.87</v>
+        <v>-16.85</v>
+      </c>
+      <c r="E161" s="9">
+        <v>-92.26000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="7">
-        <v>3.73</v>
+        <v>36.3</v>
       </c>
       <c r="D162" s="7">
-        <v>212.78</v>
+        <v>-23.62</v>
       </c>
       <c r="E162" s="9">
-        <v>209.05</v>
+        <v>-59.92</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="7">
-        <v>78.65000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="D163" s="7">
-        <v>22.09</v>
+        <v>52.52</v>
       </c>
       <c r="E163" s="8">
-        <v>-56.56</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="7">
-        <v>37.52</v>
+        <v>13.79</v>
       </c>
       <c r="D164" s="7">
-        <v>70.8</v>
-      </c>
-      <c r="E164" s="9">
-        <v>33.28</v>
+        <v>60.4</v>
+      </c>
+      <c r="E164" s="8">
+        <v>46.61</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="7">
-        <v>-17.48</v>
+        <v>-70.97</v>
       </c>
       <c r="D165" s="7">
-        <v>0.37</v>
-      </c>
-      <c r="E165" s="9">
-        <v>17.85</v>
+        <v>135.85</v>
+      </c>
+      <c r="E165" s="8">
+        <v>206.82</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>-15.06</v>
+        <v>-53.54</v>
       </c>
       <c r="D166" s="7">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="E166" s="9">
-        <v>113.46</v>
+        <v>12.53</v>
+      </c>
+      <c r="E166" s="8">
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>-50.66</v>
+        <v>-16.54</v>
       </c>
       <c r="D167" s="7">
-        <v>75.41</v>
-      </c>
-      <c r="E167" s="9">
-        <v>126.07</v>
+        <v>3.08</v>
+      </c>
+      <c r="E167" s="8">
+        <v>19.62</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>-14.41</v>
+        <v>-58.84</v>
       </c>
       <c r="D168" s="7">
-        <v>36.3</v>
-      </c>
-      <c r="E168" s="9">
-        <v>50.71</v>
+        <v>-58.5</v>
+      </c>
+      <c r="E168" s="8">
+        <v>0.34</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>-4.54</v>
+        <v>-82.13</v>
       </c>
       <c r="D169" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="E169" s="9">
-        <v>5.55</v>
+        <v>-74.86</v>
+      </c>
+      <c r="E169" s="8">
+        <v>7.27</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>-4.61</v>
+        <v>6.19</v>
       </c>
       <c r="D170" s="7">
-        <v>13.79</v>
+        <v>-29.78</v>
       </c>
       <c r="E170" s="9">
-        <v>18.4</v>
+        <v>-35.97</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-20.89</v>
+        <v>33.99</v>
       </c>
       <c r="D171" s="7">
-        <v>-70.97</v>
+        <v>54.21</v>
       </c>
       <c r="E171" s="8">
-        <v>-50.08</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>-84.19</v>
+        <v>-13.59</v>
       </c>
       <c r="D172" s="7">
-        <v>-53.54</v>
-      </c>
-      <c r="E172" s="9">
-        <v>30.65</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C173" s="7">
-        <v>34.33</v>
-      </c>
-      <c r="D173" s="7">
-        <v>-16.54</v>
-      </c>
-      <c r="E173" s="8">
-        <v>-50.87</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C174" s="7">
-        <v>-42.32</v>
-      </c>
-      <c r="D174" s="7">
-        <v>-58.84</v>
-      </c>
-      <c r="E174" s="8">
-        <v>-16.52</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C175" s="7">
-        <v>-85.13</v>
-      </c>
-      <c r="D175" s="7">
-        <v>-82.13</v>
-      </c>
-      <c r="E175" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C176" s="7">
-        <v>71.17</v>
-      </c>
-      <c r="D176" s="7">
-        <v>6.19</v>
-      </c>
-      <c r="E176" s="8">
-        <v>-64.98</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C177" s="7">
-        <v>15.89</v>
-      </c>
-      <c r="D177" s="7">
-        <v>33.99</v>
-      </c>
-      <c r="E177" s="9">
-        <v>18.1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C178" s="7">
-        <v>0.48</v>
-      </c>
-      <c r="D178" s="7">
-        <v>-13.59</v>
-      </c>
-      <c r="E178" s="8">
-        <v>-14.07</v>
+        <v>19.26</v>
+      </c>
+      <c r="E172" s="8">
+        <v>32.85</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6414,28 +6224,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6443,22 +6253,22 @@
         <v>57</v>
       </c>
       <c r="B2" s="12">
-        <v>43.04000000000001</v>
+        <v>39.04000000000001</v>
       </c>
       <c r="C2" s="13">
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>42.8</v>
+        <v>41.9</v>
       </c>
       <c r="E2" s="12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F2" s="12">
         <v>-0.8</v>
       </c>
       <c r="G2" s="12">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H2" s="12">
         <v>52.6</v>
@@ -6584,59 +6394,59 @@
         <v>44</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5132</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3249</v>
+        <v>0.3185</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2976</v>
+        <v>0.2991</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2896</v>
+        <v>0.2921</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2515</v>
+        <v>0.2473</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1419</v>
+        <v>0.1402</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1254</v>
+        <v>0.1244</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1246</v>
+        <v>0.1216</v>
       </c>
       <c r="I2" s="15">
-        <v>0.09960000000000001</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="J2" s="15">
-        <v>0.0825</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>48</v>
@@ -6662,34 +6472,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.08199999999999999</v>
+        <v>0.0799</v>
       </c>
       <c r="B4" s="15">
-        <v>0.08199999999999999</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="C4" s="15">
-        <v>0.0819</v>
+        <v>0.0795</v>
       </c>
       <c r="D4" s="15">
-        <v>0.0819</v>
+        <v>0.0795</v>
       </c>
       <c r="E4" s="15">
-        <v>0.0713</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4" s="15">
-        <v>0.046</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="G4" s="15">
-        <v>0.0012</v>
+        <v>-0.0017</v>
       </c>
       <c r="H4" s="15">
-        <v>0.0001</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.09859999999999999</v>
+        <v>-0.1025</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.3066</v>
+        <v>-0.3076</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -935,10 +935,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>585.87</v>
+        <v>583.52</v>
       </c>
       <c r="D2">
-        <v>-0.55</v>
+        <v>-0.4</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -947,43 +947,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-7.86</v>
+        <v>-8.23</v>
       </c>
       <c r="H2">
-        <v>12.47</v>
+        <v>12.02</v>
       </c>
       <c r="I2">
-        <v>-1.16</v>
+        <v>-2.1</v>
       </c>
       <c r="J2">
-        <v>-1.51</v>
+        <v>-2.59</v>
       </c>
       <c r="K2">
-        <v>2.92</v>
+        <v>-1.04</v>
       </c>
       <c r="L2">
-        <v>4.53</v>
+        <v>4.17</v>
       </c>
       <c r="M2">
-        <v>9.69</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>591.75</v>
+        <v>589.25</v>
       </c>
       <c r="Q2">
-        <v>594.79</v>
+        <v>594.0599999999999</v>
       </c>
       <c r="R2">
-        <v>595.54</v>
+        <v>595.2</v>
       </c>
       <c r="S2">
-        <v>592.41</v>
+        <v>592.29</v>
       </c>
       <c r="T2">
-        <v>-1.1</v>
+        <v>-1.48</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -998,34 +998,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>36.65</v>
+        <v>34.04</v>
       </c>
       <c r="Z2">
-        <v>-1.23</v>
+        <v>-1.88</v>
       </c>
       <c r="AA2">
-        <v>-0.16</v>
+        <v>-0.51</v>
       </c>
       <c r="AB2">
-        <v>-1.07</v>
+        <v>-1.38</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>18.25</v>
+        <v>6.19</v>
       </c>
       <c r="AE2">
-        <v>6.33</v>
+        <v>6.16</v>
       </c>
       <c r="AF2">
-        <v>0.31</v>
+        <v>-29.16</v>
       </c>
       <c r="AG2">
-        <v>601.08</v>
+        <v>601.9400000000001</v>
       </c>
       <c r="AH2">
-        <v>588.49</v>
+        <v>586.1900000000001</v>
       </c>
       <c r="AI2">
         <v>580.51</v>
@@ -1034,7 +1034,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>24.44</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1045,10 +1045,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="D3">
-        <v>-0.68</v>
+        <v>-0.34</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1057,43 +1057,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.79000000000001</v>
+        <v>-90.83</v>
       </c>
       <c r="H3">
-        <v>12.55</v>
+        <v>12.16</v>
       </c>
       <c r="I3">
-        <v>-1.08</v>
+        <v>-2.16</v>
       </c>
       <c r="J3">
-        <v>-1.73</v>
+        <v>-2.81</v>
       </c>
       <c r="K3">
-        <v>2.68</v>
+        <v>-1.03</v>
       </c>
       <c r="L3">
-        <v>-89.55</v>
+        <v>-89.56</v>
       </c>
       <c r="M3">
-        <v>-30.81</v>
+        <v>-30.83</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>59.3</v>
+        <v>59.04</v>
       </c>
       <c r="Q3">
-        <v>59.59</v>
+        <v>59.52</v>
       </c>
       <c r="R3">
-        <v>59.71</v>
+        <v>59.67</v>
       </c>
       <c r="S3">
-        <v>242.84</v>
+        <v>240.09</v>
       </c>
       <c r="T3">
-        <v>-75.84</v>
+        <v>-75.65000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1108,34 +1108,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.54</v>
+        <v>35.58</v>
       </c>
       <c r="Z3">
-        <v>-0.16</v>
+        <v>-0.22</v>
       </c>
       <c r="AA3">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AB3">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="AC3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>23.22</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>-89.78</v>
+        <v>-86.73999999999999</v>
       </c>
       <c r="AG3">
-        <v>60.26</v>
+        <v>60.34</v>
       </c>
       <c r="AH3">
-        <v>58.92</v>
+        <v>58.7</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1144,7 +1144,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>29.59</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1155,10 +1155,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>94.79000000000001</v>
+        <v>94.78</v>
       </c>
       <c r="D4">
-        <v>0.59</v>
+        <v>-0.01</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1167,43 +1167,43 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-12.88</v>
+        <v>-12.89</v>
       </c>
       <c r="H4">
-        <v>7.39</v>
+        <v>7.38</v>
       </c>
       <c r="I4">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="J4">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="K4">
-        <v>-2.33</v>
+        <v>-2.24</v>
       </c>
       <c r="L4">
-        <v>6.59</v>
+        <v>6.79</v>
       </c>
       <c r="M4">
-        <v>28.94</v>
+        <v>28.86</v>
       </c>
       <c r="N4">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>93.95</v>
+        <v>94.19</v>
       </c>
       <c r="Q4">
-        <v>93.59999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="R4">
-        <v>94.81</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="S4">
-        <v>97.97</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="T4">
-        <v>-3.25</v>
+        <v>-3.28</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1218,34 +1218,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>57.4</v>
+        <v>57.29</v>
       </c>
       <c r="Z4">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="AA4">
-        <v>-0.51</v>
+        <v>-0.44</v>
       </c>
       <c r="AB4">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="AC4">
-        <v>95.39</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="AD4">
-        <v>94.94</v>
+        <v>96.87</v>
       </c>
       <c r="AE4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AF4">
-        <v>236.42</v>
+        <v>-39.89</v>
       </c>
       <c r="AG4">
-        <v>94.87</v>
+        <v>94.95</v>
       </c>
       <c r="AH4">
-        <v>92.31999999999999</v>
+        <v>92.28</v>
       </c>
       <c r="AI4">
         <v>97.83</v>
@@ -1254,7 +1254,7 @@
         <v>61</v>
       </c>
       <c r="AK4">
-        <v>28.71</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1265,55 +1265,55 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>48.89</v>
+        <v>48.65</v>
       </c>
       <c r="D5">
-        <v>-0.85</v>
+        <v>-0.49</v>
       </c>
       <c r="E5">
         <v>60.7</v>
       </c>
       <c r="F5">
-        <v>48.67</v>
+        <v>48.65</v>
       </c>
       <c r="G5">
-        <v>-19.46</v>
+        <v>-19.85</v>
       </c>
       <c r="H5">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-1.71</v>
+        <v>-1.64</v>
       </c>
       <c r="J5">
-        <v>-6.98</v>
+        <v>-6.51</v>
       </c>
       <c r="K5">
-        <v>-6.61</v>
+        <v>-7.6</v>
       </c>
       <c r="L5">
-        <v>-18.57</v>
+        <v>-19.41</v>
       </c>
       <c r="M5">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>49.26</v>
+        <v>49.1</v>
       </c>
       <c r="Q5">
-        <v>50.6</v>
+        <v>50.41</v>
       </c>
       <c r="R5">
-        <v>51.95</v>
+        <v>51.85</v>
       </c>
       <c r="S5">
-        <v>53.89</v>
+        <v>53.84</v>
       </c>
       <c r="T5">
-        <v>-9.289999999999999</v>
+        <v>-9.65</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1328,13 +1328,13 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>23.01</v>
+        <v>21.53</v>
       </c>
       <c r="Z5">
-        <v>-0.86</v>
+        <v>-0.9</v>
       </c>
       <c r="AA5">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="AB5">
         <v>-0.13</v>
@@ -1343,28 +1343,28 @@
         <v>6.13</v>
       </c>
       <c r="AD5">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AE5">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AF5">
-        <v>7.34</v>
+        <v>4.14</v>
       </c>
       <c r="AG5">
-        <v>52.75</v>
+        <v>52.55</v>
       </c>
       <c r="AH5">
-        <v>48.45</v>
+        <v>48.27</v>
       </c>
       <c r="AI5">
-        <v>51.9</v>
+        <v>51.84</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
       </c>
       <c r="AK5">
-        <v>37.77</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1375,10 +1375,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>125.78</v>
+        <v>126.2</v>
       </c>
       <c r="D6">
-        <v>-0.05</v>
+        <v>0.33</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1387,43 +1387,43 @@
         <v>90.62</v>
       </c>
       <c r="G6">
-        <v>-14.16</v>
+        <v>-13.87</v>
       </c>
       <c r="H6">
-        <v>38.8</v>
+        <v>39.26</v>
       </c>
       <c r="I6">
-        <v>1.83</v>
+        <v>-0.02</v>
       </c>
       <c r="J6">
-        <v>0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="K6">
-        <v>5.45</v>
+        <v>1.68</v>
       </c>
       <c r="L6">
-        <v>39.79</v>
+        <v>38.42</v>
       </c>
       <c r="M6">
-        <v>25.26</v>
+        <v>25.44</v>
       </c>
       <c r="N6">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P6">
-        <v>126.12</v>
+        <v>126.11</v>
       </c>
       <c r="Q6">
-        <v>127.7</v>
+        <v>127.73</v>
       </c>
       <c r="R6">
-        <v>122.37</v>
+        <v>122.54</v>
       </c>
       <c r="S6">
-        <v>121.99</v>
+        <v>122.1</v>
       </c>
       <c r="T6">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1438,34 +1438,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>50.04</v>
+        <v>51.27</v>
       </c>
       <c r="Z6">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="AA6">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="AC6">
-        <v>16.22</v>
+        <v>17.87</v>
       </c>
       <c r="AD6">
-        <v>18.92</v>
+        <v>17.92</v>
       </c>
       <c r="AE6">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AF6">
-        <v>-49.2</v>
+        <v>-44.92</v>
       </c>
       <c r="AG6">
-        <v>133.62</v>
+        <v>133.61</v>
       </c>
       <c r="AH6">
-        <v>121.77</v>
+        <v>121.86</v>
       </c>
       <c r="AI6">
         <v>130.3</v>
@@ -1474,7 +1474,7 @@
         <v>61</v>
       </c>
       <c r="AK6">
-        <v>24.78</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1485,10 +1485,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>130.06</v>
+        <v>130.49</v>
       </c>
       <c r="D7">
-        <v>-0.09</v>
+        <v>0.33</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1497,43 +1497,43 @@
         <v>93.53</v>
       </c>
       <c r="G7">
-        <v>-14.08</v>
+        <v>-13.8</v>
       </c>
       <c r="H7">
-        <v>39.06</v>
+        <v>39.52</v>
       </c>
       <c r="I7">
-        <v>1.77</v>
+        <v>0.09</v>
       </c>
       <c r="J7">
-        <v>0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="K7">
-        <v>3.34</v>
+        <v>1.8</v>
       </c>
       <c r="L7">
-        <v>40.03</v>
+        <v>38.61</v>
       </c>
       <c r="M7">
-        <v>32.35</v>
+        <v>32.45</v>
       </c>
       <c r="N7">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>130.39</v>
+        <v>130.41</v>
       </c>
       <c r="Q7">
-        <v>132.08</v>
+        <v>132.12</v>
       </c>
       <c r="R7">
-        <v>126.5</v>
+        <v>126.68</v>
       </c>
       <c r="S7">
-        <v>126.04</v>
+        <v>126.16</v>
       </c>
       <c r="T7">
-        <v>3.19</v>
+        <v>3.43</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1548,34 +1548,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>50.05</v>
+        <v>51.28</v>
       </c>
       <c r="Z7">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="AA7">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AB7">
-        <v>-0.76</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AC7">
-        <v>16.12</v>
+        <v>17.7</v>
       </c>
       <c r="AD7">
-        <v>18.63</v>
+        <v>17.79</v>
       </c>
       <c r="AE7">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="AF7">
-        <v>-40.1</v>
+        <v>-43.64</v>
       </c>
       <c r="AG7">
-        <v>138.03</v>
+        <v>138.01</v>
       </c>
       <c r="AH7">
-        <v>126.13</v>
+        <v>126.23</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1584,7 +1584,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>20.42</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1595,10 +1595,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>466.33</v>
+        <v>466.06</v>
       </c>
       <c r="D8">
-        <v>-0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1607,43 +1607,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-17.66</v>
+        <v>-17.71</v>
       </c>
       <c r="H8">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="I8">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="J8">
-        <v>-3.74</v>
+        <v>-2.97</v>
       </c>
       <c r="K8">
-        <v>-3.1</v>
+        <v>-6.11</v>
       </c>
       <c r="L8">
-        <v>-4.91</v>
+        <v>-7.21</v>
       </c>
       <c r="M8">
-        <v>7.12</v>
+        <v>7.15</v>
       </c>
       <c r="N8">
         <v>27</v>
       </c>
       <c r="P8">
-        <v>468.43</v>
+        <v>467.95</v>
       </c>
       <c r="Q8">
-        <v>474.44</v>
+        <v>473.75</v>
       </c>
       <c r="R8">
-        <v>480.88</v>
+        <v>480.65</v>
       </c>
       <c r="S8">
-        <v>507.26</v>
+        <v>507.08</v>
       </c>
       <c r="T8">
-        <v>-8.07</v>
+        <v>-8.09</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1658,43 +1658,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.39</v>
+        <v>34.08</v>
       </c>
       <c r="Z8">
-        <v>-4.54</v>
+        <v>-4.59</v>
       </c>
       <c r="AA8">
-        <v>-4.03</v>
+        <v>-4.14</v>
       </c>
       <c r="AB8">
-        <v>-0.51</v>
+        <v>-0.45</v>
       </c>
       <c r="AC8">
-        <v>8.1</v>
+        <v>0.67</v>
       </c>
       <c r="AD8">
-        <v>16.42</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AE8">
-        <v>9.609999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="AF8">
-        <v>-11.82</v>
+        <v>-31.11</v>
       </c>
       <c r="AG8">
-        <v>486.08</v>
+        <v>485.65</v>
       </c>
       <c r="AH8">
-        <v>462.81</v>
+        <v>461.84</v>
       </c>
       <c r="AI8">
-        <v>495.55</v>
+        <v>492.85</v>
       </c>
       <c r="AJ8" t="s">
         <v>61</v>
       </c>
       <c r="AK8">
-        <v>19.37</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1705,10 +1705,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>944.3200000000001</v>
+        <v>944.9</v>
       </c>
       <c r="D9">
-        <v>-0.31</v>
+        <v>0.06</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1717,22 +1717,22 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-6.4</v>
+        <v>-6.34</v>
       </c>
       <c r="H9">
-        <v>6.7</v>
+        <v>6.76</v>
       </c>
       <c r="I9">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="J9">
-        <v>-2.95</v>
+        <v>-2.46</v>
       </c>
       <c r="K9">
-        <v>1.47</v>
+        <v>-2.18</v>
       </c>
       <c r="L9">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="M9">
         <v>13.47</v>
@@ -1741,19 +1741,19 @@
         <v>53</v>
       </c>
       <c r="P9">
-        <v>950.36</v>
+        <v>948.48</v>
       </c>
       <c r="Q9">
-        <v>960.96</v>
+        <v>959.79</v>
       </c>
       <c r="R9">
-        <v>966.2</v>
+        <v>965.5599999999999</v>
       </c>
       <c r="S9">
-        <v>963.3099999999999</v>
+        <v>963.08</v>
       </c>
       <c r="T9">
-        <v>-1.97</v>
+        <v>-1.89</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1768,43 +1768,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>32.69</v>
+        <v>33.53</v>
       </c>
       <c r="Z9">
-        <v>-5.77</v>
+        <v>-6.08</v>
       </c>
       <c r="AA9">
-        <v>-4.05</v>
+        <v>-4.46</v>
       </c>
       <c r="AB9">
-        <v>-1.71</v>
+        <v>-1.62</v>
       </c>
       <c r="AC9">
-        <v>5.35</v>
+        <v>2.53</v>
       </c>
       <c r="AD9">
-        <v>17.22</v>
+        <v>9.17</v>
       </c>
       <c r="AE9">
-        <v>10.65</v>
+        <v>10.38</v>
       </c>
       <c r="AF9">
-        <v>45.68</v>
+        <v>-53.14</v>
       </c>
       <c r="AG9">
-        <v>980.67</v>
+        <v>980.4299999999999</v>
       </c>
       <c r="AH9">
-        <v>941.25</v>
+        <v>939.15</v>
       </c>
       <c r="AI9">
-        <v>977.28</v>
+        <v>975.12</v>
       </c>
       <c r="AJ9" t="s">
         <v>61</v>
       </c>
       <c r="AK9">
-        <v>21.16</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1815,10 +1815,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>32.13</v>
+        <v>32.06</v>
       </c>
       <c r="D10">
-        <v>-3.43</v>
+        <v>-0.22</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1827,43 +1827,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-25.57</v>
+        <v>-25.74</v>
       </c>
       <c r="H10">
-        <v>12.26</v>
+        <v>12.02</v>
       </c>
       <c r="I10">
-        <v>-6.49</v>
+        <v>-6.23</v>
       </c>
       <c r="J10">
-        <v>-8.77</v>
+        <v>-7.5</v>
       </c>
       <c r="K10">
-        <v>4.12</v>
+        <v>2.89</v>
       </c>
       <c r="L10">
-        <v>-13.95</v>
+        <v>-16.34</v>
       </c>
       <c r="M10">
-        <v>-1.67</v>
+        <v>-1.87</v>
       </c>
       <c r="N10">
         <v>22</v>
       </c>
       <c r="P10">
-        <v>33.4</v>
+        <v>32.97</v>
       </c>
       <c r="Q10">
-        <v>33.98</v>
+        <v>33.85</v>
       </c>
       <c r="R10">
-        <v>33.23</v>
+        <v>33.28</v>
       </c>
       <c r="S10">
-        <v>35.25</v>
+        <v>35.21</v>
       </c>
       <c r="T10">
-        <v>-8.859999999999999</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1878,43 +1878,43 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>33.75</v>
+        <v>33.28</v>
       </c>
       <c r="Z10">
-        <v>-0.08</v>
+        <v>-0.2</v>
       </c>
       <c r="AA10">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="AB10">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="AC10">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>7.76</v>
+        <v>2.44</v>
       </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="AF10">
-        <v>249.37</v>
+        <v>11.26</v>
       </c>
       <c r="AG10">
-        <v>35.26</v>
+        <v>35.34</v>
       </c>
       <c r="AH10">
-        <v>32.7</v>
+        <v>32.35</v>
       </c>
       <c r="AI10">
-        <v>35.62</v>
+        <v>35.18</v>
       </c>
       <c r="AJ10" t="s">
         <v>61</v>
       </c>
       <c r="AK10">
-        <v>28.34</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1925,10 +1925,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>32.15</v>
+        <v>32.06</v>
       </c>
       <c r="D11">
-        <v>-3.37</v>
+        <v>-0.28</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1937,43 +1937,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-25.73</v>
+        <v>-25.94</v>
       </c>
       <c r="H11">
-        <v>12.29</v>
+        <v>11.98</v>
       </c>
       <c r="I11">
-        <v>-6.51</v>
+        <v>-6.5</v>
       </c>
       <c r="J11">
-        <v>-8.77</v>
+        <v>-7.47</v>
       </c>
       <c r="K11">
-        <v>4.11</v>
+        <v>2.79</v>
       </c>
       <c r="L11">
-        <v>-14.24</v>
+        <v>-16.77</v>
       </c>
       <c r="M11">
-        <v>-1.91</v>
+        <v>-2.17</v>
       </c>
       <c r="N11">
         <v>16</v>
       </c>
       <c r="P11">
-        <v>33.43</v>
+        <v>32.98</v>
       </c>
       <c r="Q11">
-        <v>34.01</v>
+        <v>33.88</v>
       </c>
       <c r="R11">
-        <v>33.25</v>
+        <v>33.29</v>
       </c>
       <c r="S11">
-        <v>35.31</v>
+        <v>35.27</v>
       </c>
       <c r="T11">
-        <v>-8.949999999999999</v>
+        <v>-9.09</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -1988,43 +1988,43 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>34.07</v>
+        <v>33.47</v>
       </c>
       <c r="Z11">
-        <v>-0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="AA11">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="AB11">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="AC11">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>8.109999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>168.14</v>
+        <v>-4.52</v>
       </c>
       <c r="AG11">
-        <v>35.33</v>
+        <v>35.4</v>
       </c>
       <c r="AH11">
-        <v>32.7</v>
+        <v>32.35</v>
       </c>
       <c r="AI11">
-        <v>36.23</v>
+        <v>35.59</v>
       </c>
       <c r="AJ11" t="s">
         <v>61</v>
       </c>
       <c r="AK11">
-        <v>26.62</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2035,10 +2035,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>789.37</v>
+        <v>785.79</v>
       </c>
       <c r="D12">
-        <v>0.23</v>
+        <v>-0.45</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2047,43 +2047,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-2.43</v>
+        <v>-2.87</v>
       </c>
       <c r="H12">
-        <v>21.09</v>
+        <v>20.54</v>
       </c>
       <c r="I12">
-        <v>0.12</v>
+        <v>-0.37</v>
       </c>
       <c r="J12">
-        <v>-2.27</v>
+        <v>-2.54</v>
       </c>
       <c r="K12">
-        <v>6.89</v>
+        <v>1.6</v>
       </c>
       <c r="L12">
-        <v>9.029999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M12">
-        <v>12.02</v>
+        <v>11.85</v>
       </c>
       <c r="N12">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>788.61</v>
+        <v>788.02</v>
       </c>
       <c r="Q12">
-        <v>798.2</v>
+        <v>797.1</v>
       </c>
       <c r="R12">
-        <v>791.42</v>
+        <v>791.49</v>
       </c>
       <c r="S12">
-        <v>753.47</v>
+        <v>753.73</v>
       </c>
       <c r="T12">
-        <v>4.77</v>
+        <v>4.25</v>
       </c>
       <c r="U12" t="s">
         <v>59</v>
@@ -2098,34 +2098,34 @@
         <v>3</v>
       </c>
       <c r="Y12">
-        <v>43.31</v>
+        <v>39.49</v>
       </c>
       <c r="Z12">
-        <v>-1.76</v>
+        <v>-2.18</v>
       </c>
       <c r="AA12">
-        <v>0.43</v>
+        <v>-0.09</v>
       </c>
       <c r="AB12">
-        <v>-2.2</v>
+        <v>-2.09</v>
       </c>
       <c r="AC12">
-        <v>9.449999999999999</v>
+        <v>10.61</v>
       </c>
       <c r="AD12">
-        <v>8.06</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AE12">
-        <v>14.29</v>
+        <v>13.79</v>
       </c>
       <c r="AF12">
-        <v>-37.13</v>
+        <v>-50.39</v>
       </c>
       <c r="AG12">
-        <v>814.3200000000001</v>
+        <v>813.49</v>
       </c>
       <c r="AH12">
-        <v>782.0700000000001</v>
+        <v>780.72</v>
       </c>
       <c r="AI12">
         <v>772.14</v>
@@ -2134,7 +2134,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>42.2</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2145,10 +2145,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>268.15</v>
+        <v>267.17</v>
       </c>
       <c r="D13">
-        <v>-0.7</v>
+        <v>-0.37</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2157,43 +2157,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-9.880000000000001</v>
+        <v>-10.21</v>
       </c>
       <c r="H13">
-        <v>5.8</v>
+        <v>5.42</v>
       </c>
       <c r="I13">
-        <v>-1.62</v>
+        <v>-2</v>
       </c>
       <c r="J13">
-        <v>-3.93</v>
+        <v>-4.01</v>
       </c>
       <c r="K13">
-        <v>2.1</v>
+        <v>-1.28</v>
       </c>
       <c r="L13">
-        <v>-4.23</v>
+        <v>-4.77</v>
       </c>
       <c r="M13">
-        <v>7.43</v>
+        <v>7.4</v>
       </c>
       <c r="N13">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="P13">
-        <v>271.06</v>
+        <v>269.97</v>
       </c>
       <c r="Q13">
-        <v>274.8</v>
+        <v>274.25</v>
       </c>
       <c r="R13">
-        <v>275.48</v>
+        <v>275.34</v>
       </c>
       <c r="S13">
-        <v>278.34</v>
+        <v>278.21</v>
       </c>
       <c r="T13">
-        <v>-3.66</v>
+        <v>-3.97</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2208,34 +2208,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>27.34</v>
+        <v>25.51</v>
       </c>
       <c r="Z13">
-        <v>-1.59</v>
+        <v>-1.91</v>
       </c>
       <c r="AA13">
-        <v>-0.75</v>
+        <v>-0.98</v>
       </c>
       <c r="AB13">
-        <v>-0.85</v>
+        <v>-0.93</v>
       </c>
       <c r="AC13">
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>5.59</v>
+        <v>2.7</v>
       </c>
       <c r="AE13">
-        <v>3.44</v>
+        <v>3.73</v>
       </c>
       <c r="AF13">
-        <v>54.77</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AG13">
-        <v>280.45</v>
+        <v>280.62</v>
       </c>
       <c r="AH13">
-        <v>269.16</v>
+        <v>267.89</v>
       </c>
       <c r="AI13">
         <v>279.1</v>
@@ -2244,7 +2244,7 @@
         <v>61</v>
       </c>
       <c r="AK13">
-        <v>15.54</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2255,10 +2255,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>260.87</v>
+        <v>260.06</v>
       </c>
       <c r="D14">
-        <v>-0.76</v>
+        <v>-0.31</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2267,31 +2267,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-9.92</v>
+        <v>-10.2</v>
       </c>
       <c r="H14">
-        <v>5.8</v>
+        <v>5.48</v>
       </c>
       <c r="I14">
-        <v>-1.74</v>
+        <v>-1.83</v>
       </c>
       <c r="J14">
-        <v>-3.99</v>
+        <v>-3.91</v>
       </c>
       <c r="K14">
-        <v>0.03</v>
+        <v>-1.2</v>
       </c>
       <c r="M14">
-        <v>-12.12</v>
+        <v>-12.44</v>
       </c>
       <c r="P14">
-        <v>263.66</v>
+        <v>262.68</v>
       </c>
       <c r="Q14">
-        <v>267.44</v>
+        <v>266.9</v>
       </c>
       <c r="R14">
-        <v>268.11</v>
+        <v>267.97</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2303,34 +2303,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>27.09</v>
+        <v>25.53</v>
       </c>
       <c r="Z14">
-        <v>-1.56</v>
+        <v>-1.86</v>
       </c>
       <c r="AA14">
-        <v>-0.72</v>
+        <v>-0.95</v>
       </c>
       <c r="AB14">
-        <v>-0.84</v>
+        <v>-0.92</v>
       </c>
       <c r="AC14">
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>5.35</v>
+        <v>2.68</v>
       </c>
       <c r="AE14">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="AF14">
-        <v>-0.3</v>
+        <v>-64.7</v>
       </c>
       <c r="AG14">
-        <v>272.92</v>
+        <v>273.07</v>
       </c>
       <c r="AH14">
-        <v>261.95</v>
+        <v>260.74</v>
       </c>
       <c r="AI14">
         <v>274.03</v>
@@ -2339,7 +2339,7 @@
         <v>61</v>
       </c>
       <c r="AK14">
-        <v>38.45</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2350,10 +2350,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>255.83</v>
+        <v>255.09</v>
       </c>
       <c r="D15">
-        <v>-0.66</v>
+        <v>-0.29</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2362,22 +2362,22 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-10.02</v>
+        <v>-10.28</v>
       </c>
       <c r="H15">
-        <v>5.93</v>
+        <v>5.62</v>
       </c>
       <c r="I15">
-        <v>-1.62</v>
+        <v>-1.91</v>
       </c>
       <c r="J15">
-        <v>-4.03</v>
+        <v>-3.95</v>
       </c>
       <c r="K15">
-        <v>1.85</v>
+        <v>-1.28</v>
       </c>
       <c r="L15">
-        <v>-4.1</v>
+        <v>-4.85</v>
       </c>
       <c r="M15">
         <v>7.4</v>
@@ -2386,19 +2386,19 @@
         <v>32</v>
       </c>
       <c r="P15">
-        <v>258.5</v>
+        <v>257.51</v>
       </c>
       <c r="Q15">
-        <v>262.21</v>
+        <v>261.7</v>
       </c>
       <c r="R15">
-        <v>263.08</v>
+        <v>262.94</v>
       </c>
       <c r="S15">
-        <v>265.7</v>
+        <v>265.58</v>
       </c>
       <c r="T15">
-        <v>-3.72</v>
+        <v>-3.95</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2413,43 +2413,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>27.93</v>
+        <v>26.48</v>
       </c>
       <c r="Z15">
-        <v>-1.63</v>
+        <v>-1.91</v>
       </c>
       <c r="AA15">
-        <v>-0.82</v>
+        <v>-1.03</v>
       </c>
       <c r="AB15">
-        <v>-0.8100000000000001</v>
+        <v>-0.87</v>
       </c>
       <c r="AC15">
         <v>0</v>
       </c>
       <c r="AD15">
-        <v>4.72</v>
+        <v>2.36</v>
       </c>
       <c r="AE15">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="AF15">
-        <v>-48.65</v>
+        <v>-53.27</v>
       </c>
       <c r="AG15">
-        <v>267.77</v>
+        <v>267.9</v>
       </c>
       <c r="AH15">
-        <v>256.64</v>
+        <v>255.49</v>
       </c>
       <c r="AI15">
-        <v>266.69</v>
+        <v>265.33</v>
       </c>
       <c r="AJ15" t="s">
         <v>61</v>
       </c>
       <c r="AK15">
-        <v>38.68</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2460,10 +2460,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>266.76</v>
+        <v>265.84</v>
       </c>
       <c r="D16">
-        <v>-0.79</v>
+        <v>-0.34</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2472,43 +2472,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-9.869999999999999</v>
+        <v>-10.18</v>
       </c>
       <c r="H16">
-        <v>5.85</v>
+        <v>5.48</v>
       </c>
       <c r="I16">
-        <v>-1.64</v>
+        <v>-1.9</v>
       </c>
       <c r="J16">
-        <v>-3.93</v>
+        <v>-3.96</v>
       </c>
       <c r="K16">
-        <v>2.07</v>
+        <v>-1.24</v>
       </c>
       <c r="L16">
-        <v>-4.25</v>
+        <v>-4.73</v>
       </c>
       <c r="M16">
-        <v>7.48</v>
+        <v>7.41</v>
       </c>
       <c r="N16">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P16">
-        <v>269.62</v>
+        <v>268.59</v>
       </c>
       <c r="Q16">
-        <v>273.39</v>
+        <v>272.85</v>
       </c>
       <c r="R16">
-        <v>274.08</v>
+        <v>273.94</v>
       </c>
       <c r="S16">
-        <v>276.95</v>
+        <v>276.82</v>
       </c>
       <c r="T16">
-        <v>-3.68</v>
+        <v>-3.97</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2523,43 +2523,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>27.35</v>
+        <v>25.61</v>
       </c>
       <c r="Z16">
-        <v>-1.59</v>
+        <v>-1.9</v>
       </c>
       <c r="AA16">
-        <v>-0.75</v>
+        <v>-0.98</v>
       </c>
       <c r="AB16">
-        <v>-0.84</v>
+        <v>-0.93</v>
       </c>
       <c r="AC16">
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>6.55</v>
+        <v>3.27</v>
       </c>
       <c r="AE16">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="AF16">
-        <v>34.73</v>
+        <v>-18.21</v>
       </c>
       <c r="AG16">
-        <v>278.99</v>
+        <v>279.14</v>
       </c>
       <c r="AH16">
-        <v>267.8</v>
+        <v>266.55</v>
       </c>
       <c r="AI16">
-        <v>278.4</v>
+        <v>277.24</v>
       </c>
       <c r="AJ16" t="s">
         <v>61</v>
       </c>
       <c r="AK16">
-        <v>19.35</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2570,55 +2570,55 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>93.58</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="D17">
-        <v>-0.42</v>
+        <v>-0.04</v>
       </c>
       <c r="E17">
         <v>109.87</v>
       </c>
       <c r="F17">
-        <v>76.59</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="G17">
-        <v>-14.83</v>
+        <v>-14.86</v>
       </c>
       <c r="H17">
-        <v>22.18</v>
+        <v>19.48</v>
       </c>
       <c r="I17">
-        <v>-1.26</v>
+        <v>-2.24</v>
       </c>
       <c r="J17">
-        <v>-2.98</v>
+        <v>-4.81</v>
       </c>
       <c r="K17">
-        <v>0.92</v>
+        <v>-2.52</v>
       </c>
       <c r="L17">
-        <v>22.06</v>
+        <v>22.13</v>
       </c>
       <c r="M17">
-        <v>29.5</v>
+        <v>29.69</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>94.58</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="Q17">
-        <v>95.78</v>
+        <v>95.55</v>
       </c>
       <c r="R17">
-        <v>94.88</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="S17">
-        <v>95.90000000000001</v>
+        <v>95.89</v>
       </c>
       <c r="T17">
-        <v>-2.42</v>
+        <v>-2.45</v>
       </c>
       <c r="U17" t="s">
         <v>59</v>
@@ -2633,34 +2633,34 @@
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>39.64</v>
+        <v>39.44</v>
       </c>
       <c r="Z17">
+        <v>-0.41</v>
+      </c>
+      <c r="AA17">
+        <v>-0.09</v>
+      </c>
+      <c r="AB17">
         <v>-0.33</v>
-      </c>
-      <c r="AA17">
-        <v>-0</v>
-      </c>
-      <c r="AB17">
-        <v>-0.32</v>
       </c>
       <c r="AC17">
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>13.47</v>
+        <v>4.54</v>
       </c>
       <c r="AE17">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF17">
-        <v>-26.9</v>
+        <v>-1.56</v>
       </c>
       <c r="AG17">
-        <v>98.19</v>
+        <v>97.89</v>
       </c>
       <c r="AH17">
-        <v>93.36</v>
+        <v>93.2</v>
       </c>
       <c r="AI17">
         <v>91.81</v>
@@ -2669,7 +2669,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>26.09</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2680,10 +2680,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>280.11</v>
+        <v>278.52</v>
       </c>
       <c r="D18">
-        <v>-0.67</v>
+        <v>-0.57</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2692,43 +2692,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.54</v>
+        <v>-6.07</v>
       </c>
       <c r="H18">
-        <v>14.07</v>
+        <v>13.42</v>
       </c>
       <c r="I18">
-        <v>-1.01</v>
+        <v>-2.45</v>
       </c>
       <c r="J18">
-        <v>-0.03</v>
+        <v>-0.54</v>
       </c>
       <c r="K18">
-        <v>2.15</v>
+        <v>-1.49</v>
       </c>
       <c r="L18">
-        <v>4.23</v>
+        <v>3.67</v>
       </c>
       <c r="M18">
-        <v>8.08</v>
+        <v>8.02</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>282.94</v>
+        <v>281.55</v>
       </c>
       <c r="Q18">
-        <v>281.78</v>
+        <v>281.74</v>
       </c>
       <c r="R18">
-        <v>282.88</v>
+        <v>282.71</v>
       </c>
       <c r="S18">
-        <v>281.04</v>
+        <v>280.99</v>
       </c>
       <c r="T18">
-        <v>-0.33</v>
+        <v>-0.88</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2743,34 +2743,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>44.21</v>
+        <v>40.68</v>
       </c>
       <c r="Z18">
-        <v>0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="AA18">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="AB18">
-        <v>-0.09</v>
+        <v>-0.33</v>
       </c>
       <c r="AC18">
-        <v>31.06</v>
+        <v>9.75</v>
       </c>
       <c r="AD18">
-        <v>54.34</v>
+        <v>31.66</v>
       </c>
       <c r="AE18">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="AF18">
-        <v>-80.53</v>
+        <v>-86.36</v>
       </c>
       <c r="AG18">
-        <v>286.07</v>
+        <v>286.14</v>
       </c>
       <c r="AH18">
-        <v>277.49</v>
+        <v>277.34</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2779,7 +2779,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>22.51</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2790,10 +2790,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>227.94</v>
+        <v>229.15</v>
       </c>
       <c r="D19">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2802,43 +2802,43 @@
         <v>122.38</v>
       </c>
       <c r="G19">
-        <v>-36.37</v>
+        <v>-36.03</v>
       </c>
       <c r="H19">
-        <v>86.26000000000001</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="I19">
-        <v>3.23</v>
+        <v>1.62</v>
       </c>
       <c r="J19">
-        <v>0.03</v>
+        <v>-0.97</v>
       </c>
       <c r="K19">
-        <v>0.51</v>
+        <v>-6.42</v>
       </c>
       <c r="L19">
-        <v>84.76000000000001</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="M19">
-        <v>52.22</v>
+        <v>52.51</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>226.76</v>
+        <v>227.49</v>
       </c>
       <c r="Q19">
-        <v>228.98</v>
+        <v>229.12</v>
       </c>
       <c r="R19">
-        <v>222.09</v>
+        <v>222.24</v>
       </c>
       <c r="S19">
-        <v>233.02</v>
+        <v>233.4</v>
       </c>
       <c r="T19">
-        <v>-2.18</v>
+        <v>-1.82</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2853,34 +2853,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>51.6</v>
+        <v>52.98</v>
       </c>
       <c r="Z19">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AA19">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AB19">
-        <v>-0.8</v>
+        <v>-0.59</v>
       </c>
       <c r="AC19">
-        <v>27.76</v>
+        <v>34.74</v>
       </c>
       <c r="AD19">
-        <v>27.39</v>
+        <v>30.22</v>
       </c>
       <c r="AE19">
-        <v>5.99</v>
+        <v>5.85</v>
       </c>
       <c r="AF19">
-        <v>29.37</v>
+        <v>-20.97</v>
       </c>
       <c r="AG19">
-        <v>239.3</v>
+        <v>239.36</v>
       </c>
       <c r="AH19">
-        <v>218.66</v>
+        <v>218.88</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2889,7 +2889,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>18.58</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2900,10 +2900,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>253.43</v>
+        <v>252.61</v>
       </c>
       <c r="D20">
-        <v>-0.76</v>
+        <v>-0.32</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2912,43 +2912,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-9.880000000000001</v>
+        <v>-10.17</v>
       </c>
       <c r="H20">
-        <v>5.88</v>
+        <v>5.54</v>
       </c>
       <c r="I20">
-        <v>-1.64</v>
+        <v>-1.83</v>
       </c>
       <c r="J20">
-        <v>-3.92</v>
+        <v>-3.94</v>
       </c>
       <c r="K20">
-        <v>2.05</v>
+        <v>-1.22</v>
       </c>
       <c r="L20">
-        <v>-4.23</v>
+        <v>-4.69</v>
       </c>
       <c r="M20">
-        <v>7.44</v>
+        <v>7.37</v>
       </c>
       <c r="N20">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P20">
-        <v>256.11</v>
+        <v>255.17</v>
       </c>
       <c r="Q20">
-        <v>259.69</v>
+        <v>259.18</v>
       </c>
       <c r="R20">
-        <v>260.37</v>
+        <v>260.23</v>
       </c>
       <c r="S20">
-        <v>263.1</v>
+        <v>262.98</v>
       </c>
       <c r="T20">
-        <v>-3.68</v>
+        <v>-3.94</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -2963,34 +2963,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>27.31</v>
+        <v>25.67</v>
       </c>
       <c r="Z20">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="AA20">
-        <v>-0.72</v>
+        <v>-0.93</v>
       </c>
       <c r="AB20">
-        <v>-0.79</v>
+        <v>-0.87</v>
       </c>
       <c r="AC20">
         <v>0</v>
       </c>
       <c r="AD20">
-        <v>5.83</v>
+        <v>2.92</v>
       </c>
       <c r="AE20">
-        <v>3.96</v>
+        <v>4.22</v>
       </c>
       <c r="AF20">
-        <v>92.28</v>
+        <v>25.11</v>
       </c>
       <c r="AG20">
-        <v>264.99</v>
+        <v>265.13</v>
       </c>
       <c r="AH20">
-        <v>254.39</v>
+        <v>253.22</v>
       </c>
       <c r="AI20">
         <v>267.16</v>
@@ -2999,7 +2999,7 @@
         <v>61</v>
       </c>
       <c r="AK20">
-        <v>21.94</v>
+        <v>19.61</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3010,10 +3010,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>782.29</v>
+        <v>777.83</v>
       </c>
       <c r="D21">
-        <v>0.11</v>
+        <v>-0.57</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3022,43 +3022,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-2.61</v>
+        <v>-3.16</v>
       </c>
       <c r="H21">
-        <v>21.72</v>
+        <v>21.03</v>
       </c>
       <c r="I21">
-        <v>0.41</v>
+        <v>-0.74</v>
       </c>
       <c r="J21">
-        <v>-2.32</v>
+        <v>-2.73</v>
       </c>
       <c r="K21">
-        <v>6.99</v>
+        <v>1.47</v>
       </c>
       <c r="L21">
-        <v>9.130000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M21">
-        <v>12.1</v>
+        <v>11.91</v>
       </c>
       <c r="N21">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P21">
-        <v>782.48</v>
+        <v>781.33</v>
       </c>
       <c r="Q21">
-        <v>791.3099999999999</v>
+        <v>790.14</v>
       </c>
       <c r="R21">
-        <v>784.48</v>
+        <v>784.5700000000001</v>
       </c>
       <c r="S21">
-        <v>746.66</v>
+        <v>746.91</v>
       </c>
       <c r="T21">
-        <v>4.77</v>
+        <v>4.14</v>
       </c>
       <c r="U21" t="s">
         <v>59</v>
@@ -3073,34 +3073,34 @@
         <v>3</v>
       </c>
       <c r="Y21">
-        <v>44.17</v>
+        <v>40.14</v>
       </c>
       <c r="Z21">
-        <v>-1.55</v>
+        <v>-2.09</v>
       </c>
       <c r="AA21">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="AB21">
         <v>-2.15</v>
       </c>
       <c r="AC21">
-        <v>15.75</v>
+        <v>13.72</v>
       </c>
       <c r="AD21">
-        <v>17.88</v>
+        <v>15.9</v>
       </c>
       <c r="AE21">
-        <v>11.93</v>
+        <v>11.87</v>
       </c>
       <c r="AF21">
-        <v>39.04</v>
+        <v>-38.15</v>
       </c>
       <c r="AG21">
-        <v>806.55</v>
+        <v>805.78</v>
       </c>
       <c r="AH21">
-        <v>776.0599999999999</v>
+        <v>774.5</v>
       </c>
       <c r="AI21">
         <v>773.79</v>
@@ -3109,7 +3109,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>13.79</v>
+        <v>13.78</v>
       </c>
     </row>
   </sheetData>
@@ -3250,7 +3250,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F172"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3307,13 +3307,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-1.29</v>
+        <v>-1.51</v>
       </c>
       <c r="D7" s="5">
-        <v>-1.51</v>
+        <v>-2.59</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.22</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3324,13 +3324,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.55</v>
+        <v>-1.73</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.73</v>
+        <v>-2.81</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.18</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3341,13 +3341,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>0.46</v>
+        <v>1.01</v>
       </c>
       <c r="D9" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.55</v>
+        <v>0.98</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3358,13 +3358,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-6.93</v>
+        <v>-6.98</v>
       </c>
       <c r="D10" s="5">
-        <v>-6.98</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.05</v>
+        <v>-6.51</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3375,13 +3375,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>1.01</v>
+        <v>0.21</v>
       </c>
       <c r="D11" s="5">
-        <v>0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.8</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3392,13 +3392,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>1.09</v>
+        <v>0.26</v>
       </c>
       <c r="D12" s="5">
-        <v>0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.83</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3409,13 +3409,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-4.41</v>
+        <v>-3.74</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.74</v>
+        <v>-2.97</v>
       </c>
       <c r="E13" s="7">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3426,13 +3426,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-3.4</v>
+        <v>-2.95</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.95</v>
+        <v>-2.46</v>
       </c>
       <c r="E14" s="7">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3443,13 +3443,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-5.11</v>
+        <v>-8.77</v>
       </c>
       <c r="D15" s="5">
-        <v>-8.77</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-3.66</v>
+        <v>-7.5</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.27</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3460,13 +3460,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.24</v>
+        <v>-8.77</v>
       </c>
       <c r="D16" s="5">
-        <v>-8.77</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-3.53</v>
+        <v>-7.47</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3477,13 +3477,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="5">
-        <v>-2.65</v>
+        <v>-2.27</v>
       </c>
       <c r="D17" s="5">
-        <v>-2.27</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.38</v>
+        <v>-2.54</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3494,13 +3494,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.71</v>
+        <v>-3.93</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.93</v>
+        <v>-4.01</v>
       </c>
       <c r="E18" s="6">
-        <v>-0.22</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3511,13 +3511,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.63</v>
+        <v>-3.99</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.99</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.36</v>
+        <v>-3.91</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3528,13 +3528,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="5">
-        <v>-3.81</v>
+        <v>-4.03</v>
       </c>
       <c r="D20" s="5">
-        <v>-4.03</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.22</v>
+        <v>-3.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3545,13 +3545,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="5">
-        <v>-3.8</v>
+        <v>-3.93</v>
       </c>
       <c r="D21" s="5">
-        <v>-3.93</v>
+        <v>-3.96</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.13</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3562,13 +3562,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="5">
-        <v>-2.56</v>
+        <v>-2.98</v>
       </c>
       <c r="D22" s="5">
-        <v>-2.98</v>
+        <v>-4.81</v>
       </c>
       <c r="E22" s="6">
-        <v>-0.42</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3579,13 +3579,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="5">
-        <v>0.18</v>
+        <v>-0.03</v>
       </c>
       <c r="D23" s="5">
-        <v>-0.03</v>
+        <v>-0.54</v>
       </c>
       <c r="E23" s="6">
-        <v>-0.21</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3596,13 +3596,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="5">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="D24" s="5">
-        <v>0.03</v>
+        <v>-0.97</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.27</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3613,13 +3613,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="5">
-        <v>-3.63</v>
+        <v>-3.92</v>
       </c>
       <c r="D25" s="5">
-        <v>-3.92</v>
+        <v>-3.94</v>
       </c>
       <c r="E25" s="6">
-        <v>-0.29</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3630,13 +3630,13 @@
         <v>9</v>
       </c>
       <c r="C26" s="5">
-        <v>-2.72</v>
+        <v>-2.32</v>
       </c>
       <c r="D26" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.4</v>
+        <v>-2.73</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3647,13 +3647,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="5">
-        <v>-0.79</v>
+        <v>-1.16</v>
       </c>
       <c r="D27" s="5">
-        <v>-1.16</v>
+        <v>-2.1</v>
       </c>
       <c r="E27" s="6">
-        <v>-0.37</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3664,13 +3664,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="5">
-        <v>-0.42</v>
+        <v>-1.08</v>
       </c>
       <c r="D28" s="5">
+        <v>-2.16</v>
+      </c>
+      <c r="E28" s="6">
         <v>-1.08</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-0.66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3681,13 +3681,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="5">
-        <v>1.84</v>
+        <v>1.23</v>
       </c>
       <c r="D29" s="5">
-        <v>1.23</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.61</v>
+        <v>1.29</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="5">
-        <v>-0.9399999999999999</v>
+        <v>-1.71</v>
       </c>
       <c r="D30" s="5">
-        <v>-1.71</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.77</v>
+        <v>-1.64</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3715,13 +3715,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="5">
-        <v>0.4</v>
+        <v>1.83</v>
       </c>
       <c r="D31" s="5">
-        <v>1.83</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.43</v>
+        <v>-0.02</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3732,13 +3732,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="5">
-        <v>0.36</v>
+        <v>1.77</v>
       </c>
       <c r="D32" s="5">
-        <v>1.77</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.41</v>
+        <v>0.09</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3749,13 +3749,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="5">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="D33" s="5">
-        <v>-0.49</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.01</v>
+        <v>-0.51</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3766,13 +3766,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="5">
-        <v>-0.33</v>
+        <v>-0.97</v>
       </c>
       <c r="D34" s="5">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="E34" s="6">
-        <v>-0.64</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3783,13 +3783,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="5">
-        <v>-4.18</v>
+        <v>-6.49</v>
       </c>
       <c r="D35" s="5">
-        <v>-6.49</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-2.31</v>
+        <v>-6.23</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3800,13 +3800,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="5">
-        <v>-4.37</v>
+        <v>-6.51</v>
       </c>
       <c r="D36" s="5">
-        <v>-6.51</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-2.14</v>
+        <v>-6.5</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.01</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3817,13 +3817,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="5">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="D37" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.19</v>
+        <v>-0.37</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3834,13 +3834,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="5">
-        <v>-1.17</v>
+        <v>-1.62</v>
       </c>
       <c r="D38" s="5">
-        <v>-1.62</v>
+        <v>-2</v>
       </c>
       <c r="E38" s="6">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3851,13 +3851,13 @@
         <v>8</v>
       </c>
       <c r="C39" s="5">
-        <v>-1.32</v>
+        <v>-1.74</v>
       </c>
       <c r="D39" s="5">
-        <v>-1.74</v>
+        <v>-1.83</v>
       </c>
       <c r="E39" s="6">
-        <v>-0.42</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3868,13 +3868,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="5">
-        <v>-1.22</v>
+        <v>-1.62</v>
       </c>
       <c r="D40" s="5">
-        <v>-1.62</v>
+        <v>-1.91</v>
       </c>
       <c r="E40" s="6">
-        <v>-0.4</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3885,13 +3885,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="5">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="D41" s="5">
-        <v>-1.64</v>
+        <v>-1.9</v>
       </c>
       <c r="E41" s="6">
-        <v>-0.45</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3902,13 +3902,13 @@
         <v>8</v>
       </c>
       <c r="C42" s="5">
-        <v>-0.72</v>
+        <v>-1.26</v>
       </c>
       <c r="D42" s="5">
-        <v>-1.26</v>
+        <v>-2.24</v>
       </c>
       <c r="E42" s="6">
-        <v>-0.54</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3919,13 +3919,13 @@
         <v>8</v>
       </c>
       <c r="C43" s="5">
-        <v>0.21</v>
+        <v>-1.01</v>
       </c>
       <c r="D43" s="5">
-        <v>-1.01</v>
+        <v>-2.45</v>
       </c>
       <c r="E43" s="6">
-        <v>-1.22</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3936,13 +3936,13 @@
         <v>8</v>
       </c>
       <c r="C44" s="5">
-        <v>1.7</v>
+        <v>3.23</v>
       </c>
       <c r="D44" s="5">
-        <v>3.23</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.53</v>
+        <v>1.62</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3953,13 +3953,13 @@
         <v>8</v>
       </c>
       <c r="C45" s="5">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="D45" s="5">
-        <v>-1.64</v>
+        <v>-1.83</v>
       </c>
       <c r="E45" s="6">
-        <v>-0.45</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3970,13 +3970,13 @@
         <v>8</v>
       </c>
       <c r="C46" s="5">
-        <v>-0.34</v>
+        <v>0.41</v>
       </c>
       <c r="D46" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.75</v>
+        <v>-0.74</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3987,13 +3987,13 @@
         <v>11</v>
       </c>
       <c r="C47" s="5">
-        <v>5.35</v>
+        <v>4.53</v>
       </c>
       <c r="D47" s="5">
-        <v>4.53</v>
+        <v>4.17</v>
       </c>
       <c r="E47" s="6">
-        <v>-0.82</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4004,13 +4004,13 @@
         <v>11</v>
       </c>
       <c r="C48" s="5">
-        <v>-89.44</v>
+        <v>-89.55</v>
       </c>
       <c r="D48" s="5">
-        <v>-89.55</v>
+        <v>-89.56</v>
       </c>
       <c r="E48" s="6">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4021,13 +4021,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="5">
-        <v>5.45</v>
+        <v>6.59</v>
       </c>
       <c r="D49" s="5">
-        <v>6.59</v>
+        <v>6.79</v>
       </c>
       <c r="E49" s="7">
-        <v>1.14</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4038,13 +4038,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="5">
-        <v>-18.09</v>
+        <v>-18.57</v>
       </c>
       <c r="D50" s="5">
-        <v>-18.57</v>
+        <v>-19.41</v>
       </c>
       <c r="E50" s="6">
-        <v>-0.48</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4055,13 +4055,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="5">
-        <v>41.95</v>
+        <v>39.79</v>
       </c>
       <c r="D51" s="5">
-        <v>39.79</v>
+        <v>38.42</v>
       </c>
       <c r="E51" s="6">
-        <v>-2.16</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4072,13 +4072,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="5">
-        <v>42.29</v>
+        <v>40.03</v>
       </c>
       <c r="D52" s="5">
-        <v>40.03</v>
+        <v>38.61</v>
       </c>
       <c r="E52" s="6">
-        <v>-2.26</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4089,13 +4089,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="5">
-        <v>-3.19</v>
+        <v>-4.91</v>
       </c>
       <c r="D53" s="5">
-        <v>-4.91</v>
+        <v>-7.21</v>
       </c>
       <c r="E53" s="6">
-        <v>-1.72</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -4106,13 +4106,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="5">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="D54" s="5">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="E54" s="6">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -4123,13 +4123,13 @@
         <v>11</v>
       </c>
       <c r="C55" s="5">
-        <v>-11.75</v>
+        <v>-13.95</v>
       </c>
       <c r="D55" s="5">
-        <v>-13.95</v>
+        <v>-16.34</v>
       </c>
       <c r="E55" s="6">
-        <v>-2.2</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -4140,13 +4140,13 @@
         <v>11</v>
       </c>
       <c r="C56" s="5">
-        <v>-12.1</v>
+        <v>-14.24</v>
       </c>
       <c r="D56" s="5">
-        <v>-14.24</v>
+        <v>-16.77</v>
       </c>
       <c r="E56" s="6">
-        <v>-2.14</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -4157,13 +4157,13 @@
         <v>11</v>
       </c>
       <c r="C57" s="5">
-        <v>9.220000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D57" s="5">
-        <v>9.029999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E57" s="6">
-        <v>-0.19</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -4174,13 +4174,13 @@
         <v>11</v>
       </c>
       <c r="C58" s="5">
-        <v>-3.42</v>
+        <v>-4.23</v>
       </c>
       <c r="D58" s="5">
-        <v>-4.23</v>
+        <v>-4.77</v>
       </c>
       <c r="E58" s="6">
-        <v>-0.8100000000000001</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -4191,13 +4191,13 @@
         <v>11</v>
       </c>
       <c r="C59" s="5">
-        <v>-3.4</v>
+        <v>-4.1</v>
       </c>
       <c r="D59" s="5">
-        <v>-4.1</v>
+        <v>-4.85</v>
       </c>
       <c r="E59" s="6">
-        <v>-0.7</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -4208,13 +4208,13 @@
         <v>11</v>
       </c>
       <c r="C60" s="5">
-        <v>-3.32</v>
+        <v>-4.25</v>
       </c>
       <c r="D60" s="5">
-        <v>-4.25</v>
+        <v>-4.73</v>
       </c>
       <c r="E60" s="6">
-        <v>-0.93</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -4225,13 +4225,13 @@
         <v>11</v>
       </c>
       <c r="C61" s="5">
-        <v>23.21</v>
+        <v>22.06</v>
       </c>
       <c r="D61" s="5">
-        <v>22.06</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-1.15</v>
+        <v>22.13</v>
+      </c>
+      <c r="E61" s="7">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -4242,13 +4242,13 @@
         <v>11</v>
       </c>
       <c r="C62" s="5">
-        <v>5.21</v>
+        <v>4.23</v>
       </c>
       <c r="D62" s="5">
-        <v>4.23</v>
+        <v>3.67</v>
       </c>
       <c r="E62" s="6">
-        <v>-0.98</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -4259,13 +4259,13 @@
         <v>11</v>
       </c>
       <c r="C63" s="5">
-        <v>85.59999999999999</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="D63" s="5">
-        <v>84.76000000000001</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-0.84</v>
+        <v>84.93000000000001</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4276,13 +4276,13 @@
         <v>11</v>
       </c>
       <c r="C64" s="5">
-        <v>-3.38</v>
+        <v>-4.23</v>
       </c>
       <c r="D64" s="5">
-        <v>-4.23</v>
+        <v>-4.69</v>
       </c>
       <c r="E64" s="6">
-        <v>-0.85</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4293,13 +4293,13 @@
         <v>11</v>
       </c>
       <c r="C65" s="5">
-        <v>9.289999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D65" s="5">
-        <v>9.130000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E65" s="6">
-        <v>-0.16</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4310,13 +4310,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="5">
-        <v>3.49</v>
+        <v>2.92</v>
       </c>
       <c r="D66" s="5">
-        <v>2.92</v>
+        <v>-1.04</v>
       </c>
       <c r="E66" s="6">
-        <v>-0.57</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4327,13 +4327,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="5">
-        <v>3.38</v>
+        <v>2.68</v>
       </c>
       <c r="D67" s="5">
-        <v>2.68</v>
+        <v>-1.03</v>
       </c>
       <c r="E67" s="6">
-        <v>-0.7</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4344,13 +4344,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="5">
-        <v>-2.91</v>
+        <v>-2.33</v>
       </c>
       <c r="D68" s="5">
-        <v>-2.33</v>
+        <v>-2.24</v>
       </c>
       <c r="E68" s="7">
-        <v>0.58</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4361,13 +4361,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="5">
-        <v>-5.14</v>
+        <v>-6.61</v>
       </c>
       <c r="D69" s="5">
-        <v>-6.61</v>
+        <v>-7.6</v>
       </c>
       <c r="E69" s="6">
-        <v>-1.47</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4378,13 +4378,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="5">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="D70" s="5">
-        <v>5.45</v>
+        <v>1.68</v>
       </c>
       <c r="E70" s="6">
-        <v>-0.05</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4395,13 +4395,13 @@
         <v>10</v>
       </c>
       <c r="C71" s="5">
-        <v>5.63</v>
+        <v>3.34</v>
       </c>
       <c r="D71" s="5">
-        <v>3.34</v>
+        <v>1.8</v>
       </c>
       <c r="E71" s="6">
-        <v>-2.29</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4412,13 +4412,13 @@
         <v>10</v>
       </c>
       <c r="C72" s="5">
-        <v>-2.96</v>
+        <v>-3.1</v>
       </c>
       <c r="D72" s="5">
-        <v>-3.1</v>
+        <v>-6.11</v>
       </c>
       <c r="E72" s="6">
-        <v>-0.14</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4429,13 +4429,13 @@
         <v>10</v>
       </c>
       <c r="C73" s="5">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="D73" s="5">
-        <v>1.47</v>
+        <v>-2.18</v>
       </c>
       <c r="E73" s="6">
-        <v>-0.31</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4446,13 +4446,13 @@
         <v>10</v>
       </c>
       <c r="C74" s="5">
-        <v>7.81</v>
+        <v>4.12</v>
       </c>
       <c r="D74" s="5">
-        <v>4.12</v>
+        <v>2.89</v>
       </c>
       <c r="E74" s="6">
-        <v>-3.69</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4463,13 +4463,13 @@
         <v>10</v>
       </c>
       <c r="C75" s="5">
-        <v>7.74</v>
+        <v>4.11</v>
       </c>
       <c r="D75" s="5">
-        <v>4.11</v>
+        <v>2.79</v>
       </c>
       <c r="E75" s="6">
-        <v>-3.63</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4480,13 +4480,13 @@
         <v>10</v>
       </c>
       <c r="C76" s="5">
-        <v>6.65</v>
+        <v>6.89</v>
       </c>
       <c r="D76" s="5">
-        <v>6.89</v>
-      </c>
-      <c r="E76" s="7">
-        <v>0.24</v>
+        <v>1.6</v>
+      </c>
+      <c r="E76" s="6">
+        <v>-5.29</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4497,13 +4497,13 @@
         <v>10</v>
       </c>
       <c r="C77" s="5">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="D77" s="5">
-        <v>2.1</v>
+        <v>-1.28</v>
       </c>
       <c r="E77" s="6">
-        <v>-0.73</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4514,13 +4514,13 @@
         <v>10</v>
       </c>
       <c r="C78" s="5">
-        <v>2.7</v>
+        <v>0.03</v>
       </c>
       <c r="D78" s="5">
-        <v>0.03</v>
+        <v>-1.2</v>
       </c>
       <c r="E78" s="6">
-        <v>-2.67</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4531,13 +4531,13 @@
         <v>10</v>
       </c>
       <c r="C79" s="5">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="D79" s="5">
-        <v>1.85</v>
+        <v>-1.28</v>
       </c>
       <c r="E79" s="6">
-        <v>-0.68</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4548,13 +4548,13 @@
         <v>10</v>
       </c>
       <c r="C80" s="5">
-        <v>2.88</v>
+        <v>2.07</v>
       </c>
       <c r="D80" s="5">
-        <v>2.07</v>
+        <v>-1.24</v>
       </c>
       <c r="E80" s="6">
-        <v>-0.8100000000000001</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4565,13 +4565,13 @@
         <v>10</v>
       </c>
       <c r="C81" s="5">
-        <v>1.34</v>
+        <v>0.92</v>
       </c>
       <c r="D81" s="5">
-        <v>0.92</v>
+        <v>-2.52</v>
       </c>
       <c r="E81" s="6">
-        <v>-0.42</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4582,13 +4582,13 @@
         <v>10</v>
       </c>
       <c r="C82" s="5">
-        <v>2.83</v>
+        <v>2.15</v>
       </c>
       <c r="D82" s="5">
-        <v>2.15</v>
+        <v>-1.49</v>
       </c>
       <c r="E82" s="6">
-        <v>-0.68</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="C83" s="5">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="D83" s="5">
-        <v>0.51</v>
-      </c>
-      <c r="E83" s="7">
-        <v>0.51</v>
+        <v>-6.42</v>
+      </c>
+      <c r="E83" s="6">
+        <v>-6.93</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4616,13 +4616,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="5">
-        <v>2.83</v>
+        <v>2.05</v>
       </c>
       <c r="D84" s="5">
-        <v>2.05</v>
+        <v>-1.22</v>
       </c>
       <c r="E84" s="6">
-        <v>-0.78</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4633,13 +4633,13 @@
         <v>10</v>
       </c>
       <c r="C85" s="5">
-        <v>6.87</v>
+        <v>6.99</v>
       </c>
       <c r="D85" s="5">
-        <v>6.99</v>
-      </c>
-      <c r="E85" s="7">
-        <v>0.12</v>
+        <v>1.47</v>
+      </c>
+      <c r="E85" s="6">
+        <v>-5.52</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4650,13 +4650,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="5">
-        <v>-7.36</v>
+        <v>-7.86</v>
       </c>
       <c r="D86" s="5">
-        <v>-7.86</v>
+        <v>-8.23</v>
       </c>
       <c r="E86" s="6">
-        <v>-0.5</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4667,13 +4667,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="5">
-        <v>-90.73</v>
+        <v>-90.79000000000001</v>
       </c>
       <c r="D87" s="5">
-        <v>-90.79000000000001</v>
+        <v>-90.83</v>
       </c>
       <c r="E87" s="6">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4684,13 +4684,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="5">
-        <v>-13.4</v>
+        <v>-12.88</v>
       </c>
       <c r="D88" s="5">
-        <v>-12.88</v>
-      </c>
-      <c r="E88" s="7">
-        <v>0.52</v>
+        <v>-12.89</v>
+      </c>
+      <c r="E88" s="6">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4701,13 +4701,13 @@
         <v>6</v>
       </c>
       <c r="C89" s="5">
-        <v>-18.76</v>
+        <v>-19.46</v>
       </c>
       <c r="D89" s="5">
-        <v>-19.46</v>
+        <v>-19.85</v>
       </c>
       <c r="E89" s="6">
-        <v>-0.7</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4718,13 +4718,13 @@
         <v>6</v>
       </c>
       <c r="C90" s="5">
-        <v>-14.12</v>
+        <v>-14.16</v>
       </c>
       <c r="D90" s="5">
-        <v>-14.16</v>
-      </c>
-      <c r="E90" s="6">
-        <v>-0.04</v>
+        <v>-13.87</v>
+      </c>
+      <c r="E90" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4735,13 +4735,13 @@
         <v>6</v>
       </c>
       <c r="C91" s="5">
-        <v>-14</v>
+        <v>-14.08</v>
       </c>
       <c r="D91" s="5">
-        <v>-14.08</v>
-      </c>
-      <c r="E91" s="6">
-        <v>-0.08</v>
+        <v>-13.8</v>
+      </c>
+      <c r="E91" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4752,13 +4752,13 @@
         <v>6</v>
       </c>
       <c r="C92" s="5">
-        <v>-17.55</v>
+        <v>-17.66</v>
       </c>
       <c r="D92" s="5">
-        <v>-17.66</v>
+        <v>-17.71</v>
       </c>
       <c r="E92" s="6">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4769,13 +4769,13 @@
         <v>6</v>
       </c>
       <c r="C93" s="5">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="D93" s="5">
-        <v>-6.4</v>
-      </c>
-      <c r="E93" s="6">
-        <v>-0.3</v>
+        <v>-6.34</v>
+      </c>
+      <c r="E93" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4786,13 +4786,13 @@
         <v>6</v>
       </c>
       <c r="C94" s="5">
-        <v>-22.93</v>
+        <v>-25.57</v>
       </c>
       <c r="D94" s="5">
-        <v>-25.57</v>
+        <v>-25.74</v>
       </c>
       <c r="E94" s="6">
-        <v>-2.64</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4803,13 +4803,13 @@
         <v>6</v>
       </c>
       <c r="C95" s="5">
-        <v>-23.15</v>
+        <v>-25.73</v>
       </c>
       <c r="D95" s="5">
-        <v>-25.73</v>
+        <v>-25.94</v>
       </c>
       <c r="E95" s="6">
-        <v>-2.58</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4820,13 +4820,13 @@
         <v>6</v>
       </c>
       <c r="C96" s="5">
-        <v>-2.65</v>
+        <v>-2.43</v>
       </c>
       <c r="D96" s="5">
-        <v>-2.43</v>
-      </c>
-      <c r="E96" s="7">
-        <v>0.22</v>
+        <v>-2.87</v>
+      </c>
+      <c r="E96" s="6">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4837,13 +4837,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="5">
-        <v>-9.24</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D97" s="5">
-        <v>-9.880000000000001</v>
+        <v>-10.21</v>
       </c>
       <c r="E97" s="6">
-        <v>-0.64</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4854,13 +4854,13 @@
         <v>6</v>
       </c>
       <c r="C98" s="5">
-        <v>-9.23</v>
+        <v>-9.92</v>
       </c>
       <c r="D98" s="5">
-        <v>-9.92</v>
+        <v>-10.2</v>
       </c>
       <c r="E98" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4871,13 +4871,13 @@
         <v>6</v>
       </c>
       <c r="C99" s="5">
-        <v>-9.42</v>
+        <v>-10.02</v>
       </c>
       <c r="D99" s="5">
-        <v>-10.02</v>
+        <v>-10.28</v>
       </c>
       <c r="E99" s="6">
-        <v>-0.6</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4888,13 +4888,13 @@
         <v>6</v>
       </c>
       <c r="C100" s="5">
-        <v>-9.16</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D100" s="5">
-        <v>-9.869999999999999</v>
+        <v>-10.18</v>
       </c>
       <c r="E100" s="6">
-        <v>-0.71</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4905,13 +4905,13 @@
         <v>6</v>
       </c>
       <c r="C101" s="5">
-        <v>-14.47</v>
+        <v>-14.83</v>
       </c>
       <c r="D101" s="5">
-        <v>-14.83</v>
+        <v>-14.86</v>
       </c>
       <c r="E101" s="6">
-        <v>-0.36</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4922,13 +4922,13 @@
         <v>6</v>
       </c>
       <c r="C102" s="5">
-        <v>-4.9</v>
+        <v>-5.54</v>
       </c>
       <c r="D102" s="5">
-        <v>-5.54</v>
+        <v>-6.07</v>
       </c>
       <c r="E102" s="6">
-        <v>-0.64</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4939,13 +4939,13 @@
         <v>6</v>
       </c>
       <c r="C103" s="5">
-        <v>-36.69</v>
+        <v>-36.37</v>
       </c>
       <c r="D103" s="5">
-        <v>-36.37</v>
+        <v>-36.03</v>
       </c>
       <c r="E103" s="7">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4956,13 +4956,13 @@
         <v>6</v>
       </c>
       <c r="C104" s="5">
-        <v>-9.19</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D104" s="5">
-        <v>-9.880000000000001</v>
+        <v>-10.17</v>
       </c>
       <c r="E104" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4973,13 +4973,13 @@
         <v>6</v>
       </c>
       <c r="C105" s="5">
-        <v>-2.72</v>
+        <v>-2.61</v>
       </c>
       <c r="D105" s="5">
-        <v>-2.61</v>
-      </c>
-      <c r="E105" s="7">
-        <v>0.11</v>
+        <v>-3.16</v>
+      </c>
+      <c r="E105" s="6">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4990,13 +4990,13 @@
         <v>2</v>
       </c>
       <c r="C106" s="5">
-        <v>589.09</v>
+        <v>585.87</v>
       </c>
       <c r="D106" s="5">
-        <v>585.87</v>
+        <v>583.52</v>
       </c>
       <c r="E106" s="6">
-        <v>-3.22</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5007,13 +5007,13 @@
         <v>2</v>
       </c>
       <c r="C107" s="5">
-        <v>59.06</v>
+        <v>58.66</v>
       </c>
       <c r="D107" s="5">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="E107" s="6">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5024,13 +5024,13 @@
         <v>2</v>
       </c>
       <c r="C108" s="5">
-        <v>94.23</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="D108" s="5">
-        <v>94.79000000000001</v>
-      </c>
-      <c r="E108" s="7">
-        <v>0.5600000000000001</v>
+        <v>94.78</v>
+      </c>
+      <c r="E108" s="6">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5041,13 +5041,13 @@
         <v>2</v>
       </c>
       <c r="C109" s="5">
-        <v>49.31</v>
+        <v>48.89</v>
       </c>
       <c r="D109" s="5">
-        <v>48.89</v>
+        <v>48.65</v>
       </c>
       <c r="E109" s="6">
-        <v>-0.42</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5058,13 +5058,13 @@
         <v>2</v>
       </c>
       <c r="C110" s="5">
-        <v>125.84</v>
+        <v>125.78</v>
       </c>
       <c r="D110" s="5">
-        <v>125.78</v>
-      </c>
-      <c r="E110" s="6">
-        <v>-0.06</v>
+        <v>126.2</v>
+      </c>
+      <c r="E110" s="7">
+        <v>0.42</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5075,13 +5075,13 @@
         <v>2</v>
       </c>
       <c r="C111" s="5">
-        <v>130.18</v>
+        <v>130.06</v>
       </c>
       <c r="D111" s="5">
-        <v>130.06</v>
-      </c>
-      <c r="E111" s="6">
-        <v>-0.12</v>
+        <v>130.49</v>
+      </c>
+      <c r="E111" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5092,13 +5092,13 @@
         <v>2</v>
       </c>
       <c r="C112" s="5">
-        <v>466.97</v>
+        <v>466.33</v>
       </c>
       <c r="D112" s="5">
-        <v>466.33</v>
+        <v>466.06</v>
       </c>
       <c r="E112" s="6">
-        <v>-0.64</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5109,13 +5109,13 @@
         <v>2</v>
       </c>
       <c r="C113" s="5">
-        <v>947.27</v>
+        <v>944.3200000000001</v>
       </c>
       <c r="D113" s="5">
-        <v>944.3200000000001</v>
-      </c>
-      <c r="E113" s="6">
-        <v>-2.95</v>
+        <v>944.9</v>
+      </c>
+      <c r="E113" s="7">
+        <v>0.58</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5126,13 +5126,13 @@
         <v>2</v>
       </c>
       <c r="C114" s="5">
-        <v>33.27</v>
+        <v>32.13</v>
       </c>
       <c r="D114" s="5">
-        <v>32.13</v>
+        <v>32.06</v>
       </c>
       <c r="E114" s="6">
-        <v>-1.14</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5143,13 +5143,13 @@
         <v>2</v>
       </c>
       <c r="C115" s="5">
-        <v>33.27</v>
+        <v>32.15</v>
       </c>
       <c r="D115" s="5">
-        <v>32.15</v>
+        <v>32.06</v>
       </c>
       <c r="E115" s="6">
-        <v>-1.12</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5160,13 +5160,13 @@
         <v>2</v>
       </c>
       <c r="C116" s="5">
-        <v>787.59</v>
+        <v>789.37</v>
       </c>
       <c r="D116" s="5">
-        <v>789.37</v>
-      </c>
-      <c r="E116" s="7">
-        <v>1.78</v>
+        <v>785.79</v>
+      </c>
+      <c r="E116" s="6">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5177,13 +5177,13 @@
         <v>2</v>
       </c>
       <c r="C117" s="5">
-        <v>270.05</v>
+        <v>268.15</v>
       </c>
       <c r="D117" s="5">
-        <v>268.15</v>
+        <v>267.17</v>
       </c>
       <c r="E117" s="6">
-        <v>-1.9</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5194,13 +5194,13 @@
         <v>2</v>
       </c>
       <c r="C118" s="5">
-        <v>262.87</v>
+        <v>260.87</v>
       </c>
       <c r="D118" s="5">
-        <v>260.87</v>
+        <v>260.06</v>
       </c>
       <c r="E118" s="6">
-        <v>-2</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5211,13 +5211,13 @@
         <v>2</v>
       </c>
       <c r="C119" s="5">
-        <v>257.53</v>
+        <v>255.83</v>
       </c>
       <c r="D119" s="5">
-        <v>255.83</v>
+        <v>255.09</v>
       </c>
       <c r="E119" s="6">
-        <v>-1.7</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5228,13 +5228,13 @@
         <v>2</v>
       </c>
       <c r="C120" s="5">
-        <v>268.88</v>
+        <v>266.76</v>
       </c>
       <c r="D120" s="5">
-        <v>266.76</v>
+        <v>265.84</v>
       </c>
       <c r="E120" s="6">
-        <v>-2.12</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5245,13 +5245,13 @@
         <v>2</v>
       </c>
       <c r="C121" s="5">
-        <v>93.97</v>
+        <v>93.58</v>
       </c>
       <c r="D121" s="5">
-        <v>93.58</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="E121" s="6">
-        <v>-0.39</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5262,13 +5262,13 @@
         <v>2</v>
       </c>
       <c r="C122" s="5">
-        <v>281.99</v>
+        <v>280.11</v>
       </c>
       <c r="D122" s="5">
-        <v>280.11</v>
+        <v>278.52</v>
       </c>
       <c r="E122" s="6">
-        <v>-1.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5279,13 +5279,13 @@
         <v>2</v>
       </c>
       <c r="C123" s="5">
-        <v>226.79</v>
+        <v>227.94</v>
       </c>
       <c r="D123" s="5">
-        <v>227.94</v>
+        <v>229.15</v>
       </c>
       <c r="E123" s="7">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5296,13 +5296,13 @@
         <v>2</v>
       </c>
       <c r="C124" s="5">
-        <v>255.36</v>
+        <v>253.43</v>
       </c>
       <c r="D124" s="5">
-        <v>253.43</v>
+        <v>252.61</v>
       </c>
       <c r="E124" s="6">
-        <v>-1.93</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -5313,98 +5313,98 @@
         <v>2</v>
       </c>
       <c r="C125" s="5">
-        <v>781.42</v>
+        <v>782.29</v>
       </c>
       <c r="D125" s="5">
-        <v>782.29</v>
-      </c>
-      <c r="E125" s="7">
-        <v>0.87</v>
+        <v>777.83</v>
+      </c>
+      <c r="E125" s="6">
+        <v>-4.46</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C126" s="5">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D126" s="5">
-        <v>94</v>
-      </c>
-      <c r="E126" s="7">
-        <v>5</v>
+        <v>58</v>
+      </c>
+      <c r="E126" s="6">
+        <v>-10</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C127" s="5">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D127" s="5">
-        <v>89</v>
-      </c>
-      <c r="E127" s="6">
-        <v>-5</v>
+        <v>68</v>
+      </c>
+      <c r="E127" s="7">
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="5">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="D128" s="5">
-        <v>27</v>
-      </c>
-      <c r="E128" s="7">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="E128" s="6">
+        <v>-5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C129" s="5">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D129" s="5">
-        <v>22</v>
-      </c>
-      <c r="E129" s="6">
-        <v>-5</v>
+        <v>94</v>
+      </c>
+      <c r="E129" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="5">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D130" s="5">
-        <v>16</v>
-      </c>
-      <c r="E130" s="6">
-        <v>-6</v>
+        <v>78</v>
+      </c>
+      <c r="E130" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5415,13 +5415,13 @@
         <v>13</v>
       </c>
       <c r="C131" s="5">
+        <v>47</v>
+      </c>
+      <c r="D131" s="5">
         <v>37</v>
       </c>
-      <c r="D131" s="5">
-        <v>47</v>
-      </c>
-      <c r="E131" s="7">
-        <v>10</v>
+      <c r="E131" s="6">
+        <v>-10</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5432,693 +5432,727 @@
         <v>13</v>
       </c>
       <c r="C132" s="5">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D132" s="5">
-        <v>37</v>
-      </c>
-      <c r="E132" s="6">
-        <v>-10</v>
+        <v>42</v>
+      </c>
+      <c r="E132" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C133" s="5">
-        <v>40.62</v>
+        <v>42</v>
       </c>
       <c r="D133" s="5">
-        <v>36.65</v>
-      </c>
-      <c r="E133" s="6">
-        <v>-3.97</v>
+        <v>47</v>
+      </c>
+      <c r="E133" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C134" s="5">
-        <v>41.83</v>
+        <v>78</v>
       </c>
       <c r="D134" s="5">
-        <v>37.54</v>
+        <v>73</v>
       </c>
       <c r="E134" s="6">
-        <v>-4.29</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C135" s="5">
-        <v>52.62</v>
+        <v>36.65</v>
       </c>
       <c r="D135" s="5">
-        <v>57.4</v>
-      </c>
-      <c r="E135" s="7">
-        <v>4.78</v>
+        <v>34.04</v>
+      </c>
+      <c r="E135" s="6">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C136" s="5">
-        <v>25.91</v>
+        <v>37.54</v>
       </c>
       <c r="D136" s="5">
-        <v>23.01</v>
+        <v>35.58</v>
       </c>
       <c r="E136" s="6">
-        <v>-2.9</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="5">
-        <v>50.21</v>
+        <v>57.4</v>
       </c>
       <c r="D137" s="5">
-        <v>50.04</v>
+        <v>57.29</v>
       </c>
       <c r="E137" s="6">
-        <v>-0.17</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="5">
-        <v>50.38</v>
+        <v>23.01</v>
       </c>
       <c r="D138" s="5">
-        <v>50.05</v>
+        <v>21.53</v>
       </c>
       <c r="E138" s="6">
-        <v>-0.33</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="5">
-        <v>35.08</v>
+        <v>50.04</v>
       </c>
       <c r="D139" s="5">
-        <v>34.39</v>
-      </c>
-      <c r="E139" s="6">
-        <v>-0.6899999999999999</v>
+        <v>51.27</v>
+      </c>
+      <c r="E139" s="7">
+        <v>1.23</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="5">
-        <v>34.77</v>
+        <v>50.05</v>
       </c>
       <c r="D140" s="5">
-        <v>32.69</v>
-      </c>
-      <c r="E140" s="6">
-        <v>-2.08</v>
+        <v>51.28</v>
+      </c>
+      <c r="E140" s="7">
+        <v>1.23</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="5">
-        <v>42.95</v>
+        <v>34.39</v>
       </c>
       <c r="D141" s="5">
-        <v>33.75</v>
+        <v>34.08</v>
       </c>
       <c r="E141" s="6">
-        <v>-9.199999999999999</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="5">
-        <v>42.86</v>
+        <v>32.69</v>
       </c>
       <c r="D142" s="5">
-        <v>34.07</v>
-      </c>
-      <c r="E142" s="6">
-        <v>-8.789999999999999</v>
+        <v>33.53</v>
+      </c>
+      <c r="E142" s="7">
+        <v>0.84</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="5">
-        <v>40.66</v>
+        <v>33.75</v>
       </c>
       <c r="D143" s="5">
-        <v>43.31</v>
-      </c>
-      <c r="E143" s="7">
-        <v>2.65</v>
+        <v>33.28</v>
+      </c>
+      <c r="E143" s="6">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="5">
-        <v>31.41</v>
+        <v>34.07</v>
       </c>
       <c r="D144" s="5">
-        <v>27.34</v>
+        <v>33.47</v>
       </c>
       <c r="E144" s="6">
-        <v>-4.07</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="5">
-        <v>31.48</v>
+        <v>43.31</v>
       </c>
       <c r="D145" s="5">
-        <v>27.09</v>
+        <v>39.49</v>
       </c>
       <c r="E145" s="6">
-        <v>-4.39</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="5">
-        <v>31.62</v>
+        <v>27.34</v>
       </c>
       <c r="D146" s="5">
-        <v>27.93</v>
+        <v>25.51</v>
       </c>
       <c r="E146" s="6">
-        <v>-3.69</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="5">
-        <v>31.97</v>
+        <v>27.09</v>
       </c>
       <c r="D147" s="5">
-        <v>27.35</v>
+        <v>25.53</v>
       </c>
       <c r="E147" s="6">
-        <v>-4.62</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="5">
-        <v>41.47</v>
+        <v>27.93</v>
       </c>
       <c r="D148" s="5">
-        <v>39.64</v>
+        <v>26.48</v>
       </c>
       <c r="E148" s="6">
-        <v>-1.83</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="5">
-        <v>48.88</v>
+        <v>27.35</v>
       </c>
       <c r="D149" s="5">
-        <v>44.21</v>
+        <v>25.61</v>
       </c>
       <c r="E149" s="6">
-        <v>-4.67</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="5">
-        <v>50.32</v>
+        <v>39.64</v>
       </c>
       <c r="D150" s="5">
-        <v>51.6</v>
-      </c>
-      <c r="E150" s="7">
-        <v>1.28</v>
+        <v>39.44</v>
+      </c>
+      <c r="E150" s="6">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="5">
-        <v>31.74</v>
+        <v>44.21</v>
       </c>
       <c r="D151" s="5">
-        <v>27.31</v>
+        <v>40.68</v>
       </c>
       <c r="E151" s="6">
-        <v>-4.43</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="5">
-        <v>43.14</v>
+        <v>51.6</v>
       </c>
       <c r="D152" s="5">
-        <v>44.17</v>
+        <v>52.98</v>
       </c>
       <c r="E152" s="7">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C153" s="5">
-        <v>-41.95</v>
+        <v>27.31</v>
       </c>
       <c r="D153" s="5">
-        <v>0.31</v>
-      </c>
-      <c r="E153" s="7">
-        <v>42.26</v>
+        <v>25.67</v>
+      </c>
+      <c r="E153" s="6">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C154" s="5">
-        <v>-95.09</v>
+        <v>44.17</v>
       </c>
       <c r="D154" s="5">
-        <v>-89.78</v>
-      </c>
-      <c r="E154" s="7">
-        <v>5.31</v>
+        <v>40.14</v>
+      </c>
+      <c r="E154" s="6">
+        <v>-4.03</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C155" s="5">
-        <v>43.95</v>
+        <v>0.31</v>
       </c>
       <c r="D155" s="5">
-        <v>236.42</v>
-      </c>
-      <c r="E155" s="7">
-        <v>192.47</v>
+        <v>-29.16</v>
+      </c>
+      <c r="E155" s="6">
+        <v>-29.47</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C156" s="5">
-        <v>39.46</v>
+        <v>-89.78</v>
       </c>
       <c r="D156" s="5">
-        <v>7.34</v>
-      </c>
-      <c r="E156" s="6">
-        <v>-32.12</v>
+        <v>-86.73999999999999</v>
+      </c>
+      <c r="E156" s="7">
+        <v>3.04</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="5">
-        <v>-34.22</v>
+        <v>236.42</v>
       </c>
       <c r="D157" s="5">
-        <v>-49.2</v>
+        <v>-39.89</v>
       </c>
       <c r="E157" s="6">
-        <v>-14.98</v>
+        <v>-276.31</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="5">
-        <v>-26.09</v>
+        <v>7.34</v>
       </c>
       <c r="D158" s="5">
-        <v>-40.1</v>
+        <v>4.14</v>
       </c>
       <c r="E158" s="6">
-        <v>-14.01</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="5">
-        <v>-27.21</v>
+        <v>-49.2</v>
       </c>
       <c r="D159" s="5">
-        <v>-11.82</v>
+        <v>-44.92</v>
       </c>
       <c r="E159" s="7">
-        <v>15.39</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="5">
-        <v>-36.37</v>
+        <v>-40.1</v>
       </c>
       <c r="D160" s="5">
-        <v>45.68</v>
-      </c>
-      <c r="E160" s="7">
-        <v>82.05</v>
+        <v>-43.64</v>
+      </c>
+      <c r="E160" s="6">
+        <v>-3.54</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="5">
-        <v>106.61</v>
+        <v>-11.82</v>
       </c>
       <c r="D161" s="5">
-        <v>249.37</v>
-      </c>
-      <c r="E161" s="7">
-        <v>142.76</v>
+        <v>-31.11</v>
+      </c>
+      <c r="E161" s="6">
+        <v>-19.29</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="5">
-        <v>-33.54</v>
+        <v>45.68</v>
       </c>
       <c r="D162" s="5">
-        <v>168.14</v>
-      </c>
-      <c r="E162" s="7">
-        <v>201.68</v>
+        <v>-53.14</v>
+      </c>
+      <c r="E162" s="6">
+        <v>-98.81999999999999</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="5">
-        <v>-38.8</v>
+        <v>249.37</v>
       </c>
       <c r="D163" s="5">
-        <v>-37.13</v>
-      </c>
-      <c r="E163" s="7">
-        <v>1.67</v>
+        <v>11.26</v>
+      </c>
+      <c r="E163" s="6">
+        <v>-238.11</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="5">
-        <v>36.23</v>
+        <v>168.14</v>
       </c>
       <c r="D164" s="5">
-        <v>54.77</v>
-      </c>
-      <c r="E164" s="7">
-        <v>18.54</v>
+        <v>-4.52</v>
+      </c>
+      <c r="E164" s="6">
+        <v>-172.66</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="5">
-        <v>-52.88</v>
+        <v>-37.13</v>
       </c>
       <c r="D165" s="5">
-        <v>-0.3</v>
-      </c>
-      <c r="E165" s="7">
-        <v>52.58</v>
+        <v>-50.39</v>
+      </c>
+      <c r="E165" s="6">
+        <v>-13.26</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="5">
-        <v>-9.119999999999999</v>
+        <v>54.77</v>
       </c>
       <c r="D166" s="5">
-        <v>-48.65</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E166" s="6">
-        <v>-39.53</v>
+        <v>-45.24</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="5">
-        <v>2.41</v>
+        <v>-0.3</v>
       </c>
       <c r="D167" s="5">
-        <v>34.73</v>
-      </c>
-      <c r="E167" s="7">
-        <v>32.32</v>
+        <v>-64.7</v>
+      </c>
+      <c r="E167" s="6">
+        <v>-64.40000000000001</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="5">
-        <v>-44.16</v>
+        <v>-48.65</v>
       </c>
       <c r="D168" s="5">
-        <v>-26.9</v>
-      </c>
-      <c r="E168" s="7">
-        <v>17.26</v>
+        <v>-53.27</v>
+      </c>
+      <c r="E168" s="6">
+        <v>-4.62</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="5">
-        <v>-91.2</v>
+        <v>34.73</v>
       </c>
       <c r="D169" s="5">
-        <v>-80.53</v>
-      </c>
-      <c r="E169" s="7">
-        <v>10.67</v>
+        <v>-18.21</v>
+      </c>
+      <c r="E169" s="6">
+        <v>-52.94</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="5">
-        <v>-28.94</v>
+        <v>-26.9</v>
       </c>
       <c r="D170" s="5">
-        <v>29.37</v>
+        <v>-1.56</v>
       </c>
       <c r="E170" s="7">
-        <v>58.31</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="5">
-        <v>-0.74</v>
+        <v>-80.53</v>
       </c>
       <c r="D171" s="5">
-        <v>92.28</v>
-      </c>
-      <c r="E171" s="7">
-        <v>93.02</v>
+        <v>-86.36</v>
+      </c>
+      <c r="E171" s="6">
+        <v>-5.83</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="5">
-        <v>-23.25</v>
+        <v>29.37</v>
       </c>
       <c r="D172" s="5">
+        <v>-20.97</v>
+      </c>
+      <c r="E172" s="6">
+        <v>-50.34</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C173" s="5">
+        <v>92.28</v>
+      </c>
+      <c r="D173" s="5">
+        <v>25.11</v>
+      </c>
+      <c r="E173" s="6">
+        <v>-67.17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="5">
         <v>39.04</v>
       </c>
-      <c r="E172" s="7">
-        <v>62.29</v>
+      <c r="D174" s="5">
+        <v>-38.15</v>
+      </c>
+      <c r="E174" s="6">
+        <v>-77.19</v>
       </c>
     </row>
   </sheetData>
@@ -6183,16 +6217,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="10">
-        <v>37.5</v>
+        <v>36.3</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="10">
-        <v>1.9</v>
+        <v>-1.2</v>
       </c>
       <c r="H2" s="10">
         <v>52.6</v>
@@ -6332,34 +6366,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="13">
-        <v>0.5222</v>
+        <v>0.5251</v>
       </c>
       <c r="B2" s="13">
-        <v>0.3235</v>
+        <v>0.3245</v>
       </c>
       <c r="C2" s="13">
-        <v>0.295</v>
+        <v>0.2969</v>
       </c>
       <c r="D2" s="13">
-        <v>0.2894</v>
+        <v>0.2886</v>
       </c>
       <c r="E2" s="13">
-        <v>0.2526</v>
+        <v>0.2544</v>
       </c>
       <c r="F2" s="13">
         <v>0.1347</v>
       </c>
       <c r="G2" s="13">
-        <v>0.121</v>
+        <v>0.1191</v>
       </c>
       <c r="H2" s="13">
-        <v>0.1202</v>
+        <v>0.1185</v>
       </c>
       <c r="I2" s="13">
-        <v>0.0969</v>
+        <v>0.09720000000000001</v>
       </c>
       <c r="J2" s="13">
-        <v>0.0808</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6367,13 +6401,13 @@
         <v>51</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>43</v>
@@ -6396,34 +6430,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="13">
-        <v>0.07480000000000001</v>
+        <v>0.0741</v>
       </c>
       <c r="B4" s="13">
-        <v>0.07440000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C4" s="13">
-        <v>0.07429999999999999</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="D4" s="13">
-        <v>0.07400000000000001</v>
+        <v>0.0737</v>
       </c>
       <c r="E4" s="13">
-        <v>0.0712</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="F4" s="13">
-        <v>0.0382</v>
+        <v>0.0365</v>
       </c>
       <c r="G4" s="13">
-        <v>-0.0167</v>
+        <v>-0.0187</v>
       </c>
       <c r="H4" s="13">
-        <v>-0.0191</v>
+        <v>-0.0217</v>
       </c>
       <c r="I4" s="13">
-        <v>-0.1212</v>
+        <v>-0.1244</v>
       </c>
       <c r="J4" s="13">
-        <v>-0.3081</v>
+        <v>-0.3083</v>
       </c>
     </row>
   </sheetData>
